--- a/docs/attack-excel-files/v18.1/russia-colonialism/russia-colonialism-v18.1-relationships.xlsx
+++ b/docs/attack-excel-files/v18.1/russia-colonialism/russia-colonialism-v18.1-relationships.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13276" uniqueCount="2137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13364" uniqueCount="2225">
   <si>
     <t>source ID</t>
   </si>
@@ -782,367 +782,367 @@
     <t>Царская канцелярия</t>
   </si>
   <si>
-    <t>campaign--84bc21e9-f278-45cd-8acb-817742dcff21</t>
-  </si>
-  <si>
-    <t>campaign--4bf56bd2-d5ca-438b-a3aa-5cbc36381133</t>
-  </si>
-  <si>
-    <t>campaign--3bd127a5-73b3-4aac-8fd7-982a95669434</t>
-  </si>
-  <si>
-    <t>campaign--1b611c93-e848-4ee1-8527-8bbbdf2e62a5</t>
-  </si>
-  <si>
-    <t>campaign--09a157f6-2eda-4e89-85e1-0705374ca9ee</t>
-  </si>
-  <si>
-    <t>campaign--d2e92b25-7923-452d-8885-6245a64315da</t>
-  </si>
-  <si>
-    <t>campaign--20b4d9b6-86c9-414d-b7c2-ba45639bfae6</t>
-  </si>
-  <si>
-    <t>campaign--dbcf8329-be72-43a6-9503-bd3b5f80e167</t>
-  </si>
-  <si>
-    <t>campaign--06e4cf4f-1d7a-4669-bfe2-46cf114cf71f</t>
-  </si>
-  <si>
-    <t>campaign--21b1b148-99e1-447f-863e-5f179ec7aac7</t>
-  </si>
-  <si>
-    <t>campaign--d1a75343-e6bc-456b-af9c-67abfebd8778</t>
-  </si>
-  <si>
-    <t>campaign--a1253a3a-9d62-49e1-acc7-7430a198b8bc</t>
-  </si>
-  <si>
-    <t>campaign--7c61ae27-c860-4b7d-9dbc-12b393680025</t>
-  </si>
-  <si>
-    <t>campaign--0c5ea36b-4e12-47ff-8d99-a4a35e4327b0</t>
-  </si>
-  <si>
-    <t>campaign--8ba7050c-642b-4ab9-9ce1-6ca4a4676ab5</t>
-  </si>
-  <si>
-    <t>campaign--6232bf9b-bb63-402d-b03e-9a0515ee09d8</t>
-  </si>
-  <si>
-    <t>campaign--9f962768-2e42-4c2e-a172-9291db92461b</t>
-  </si>
-  <si>
-    <t>campaign--2e0766ba-2d5c-4bab-a68b-5fe011747831</t>
-  </si>
-  <si>
-    <t>campaign--4a0448c0-0001-4134-acd4-941aa1379172</t>
-  </si>
-  <si>
-    <t>campaign--eedf404e-3e21-4116-be4d-0d7601599b91</t>
-  </si>
-  <si>
-    <t>campaign--e62f4c80-a205-4fe1-91c4-85256ac37f31</t>
-  </si>
-  <si>
-    <t>campaign--6ceef077-03f6-482f-8e76-a98491db2913</t>
-  </si>
-  <si>
-    <t>campaign--2248df9e-ba27-43a8-98d8-9026a6b9de03</t>
-  </si>
-  <si>
-    <t>campaign--05daf063-815a-43c4-bdef-868e86a89149</t>
-  </si>
-  <si>
-    <t>campaign--584843e9-c5e0-4087-a142-c385deeb2bdf</t>
-  </si>
-  <si>
-    <t>campaign--a657f3f9-0df3-4ed7-a7a4-a5412ea7ecb6</t>
-  </si>
-  <si>
-    <t>campaign--8f323bf8-3b9b-4bf4-97ad-3d61fc33fd82</t>
-  </si>
-  <si>
-    <t>campaign--6e5202d1-fbbe-422b-84d5-246cb35c0b2d</t>
-  </si>
-  <si>
-    <t>campaign--8ba3d669-f614-429f-9b77-a9cf527ff71d</t>
-  </si>
-  <si>
-    <t>campaign--7ce1e89d-a9af-4fb3-81ee-15ea23718846</t>
-  </si>
-  <si>
-    <t>campaign--6c24cbbb-4ce2-45a1-981a-cf0fd9c34d97</t>
-  </si>
-  <si>
-    <t>campaign--b9baf1bc-a3fa-4050-8722-e4ac1d29b0aa</t>
-  </si>
-  <si>
-    <t>campaign--eb1f4e4b-b946-449e-8752-60b5a41d8094</t>
-  </si>
-  <si>
-    <t>campaign--fa1c9409-7b35-48bb-8f3f-1de992f2a9fe</t>
-  </si>
-  <si>
-    <t>campaign--485bc4b1-d6a0-4262-b92b-de60846a3cc2</t>
-  </si>
-  <si>
-    <t>campaign--f98d27b7-b9b2-4ee5-968d-2242b9fed57d</t>
-  </si>
-  <si>
-    <t>campaign--d9246b40-5b51-4294-bcd6-dba876074271</t>
-  </si>
-  <si>
-    <t>campaign--c084e1db-0f03-44c2-8697-12757be14ecf</t>
-  </si>
-  <si>
-    <t>campaign--78366146-c147-4bca-adbc-91cf59affa19</t>
-  </si>
-  <si>
-    <t>campaign--c4b1a1bd-5808-4f82-8404-cb671321f0b8</t>
-  </si>
-  <si>
-    <t>campaign--4cb4ba5f-3257-4a64-99a7-89c1c8584ea3</t>
-  </si>
-  <si>
-    <t>campaign--bb5621a4-0317-4a72-9557-a3309369a148</t>
-  </si>
-  <si>
-    <t>campaign--c00efded-d911-444c-8743-89ddb7c2a25b</t>
-  </si>
-  <si>
-    <t>campaign--33e7df73-0ba4-4031-911d-d9a34f23381e</t>
-  </si>
-  <si>
-    <t>campaign--398bbef2-59b4-4eae-b7fb-2ddb4325a3db</t>
-  </si>
-  <si>
-    <t>campaign--5e9e3ee9-0edc-47b8-b51f-27d825c93ba6</t>
-  </si>
-  <si>
-    <t>campaign--a928c5b5-bd92-4716-bd4b-8e2e42e22ee8</t>
-  </si>
-  <si>
-    <t>campaign--13a5e084-1143-4c42-82a1-97c7cc060f9c</t>
-  </si>
-  <si>
-    <t>campaign--2f03ada1-afc9-4e6a-b822-aa65414b1b02</t>
-  </si>
-  <si>
-    <t>campaign--6d1a46e6-ac73-4930-aabd-a8f533a687cf</t>
-  </si>
-  <si>
-    <t>campaign--5f6c1d2e-8b43-49f7-9d3f-f3a0c3ae48b1</t>
-  </si>
-  <si>
-    <t>campaign--2e2bed38-682c-4d2f-ad6c-e2bb4c4cfdd0</t>
-  </si>
-  <si>
-    <t>campaign--fcb45d3f-14e8-4834-8b2c-d18b4c8f5273</t>
-  </si>
-  <si>
-    <t>campaign--c86c2f91-e10d-4e8b-b767-78378e15121e</t>
-  </si>
-  <si>
-    <t>campaign--0ba3a916-5b43-4183-b453-0927882dba85</t>
-  </si>
-  <si>
-    <t>campaign--e0cc83b8-2a5f-42f8-8537-a7a3e72ee650</t>
-  </si>
-  <si>
-    <t>campaign--4fa7d988-4c1c-4971-84cf-ca0467775997</t>
-  </si>
-  <si>
-    <t>campaign--49d099af-a6dc-4afe-8188-c064ef26fde7</t>
-  </si>
-  <si>
-    <t>campaign--007f466b-7682-4d8a-b195-22c21ff3e565</t>
-  </si>
-  <si>
-    <t>campaign--8f1d796b-636c-4cd1-86b4-37c3ece5165a</t>
-  </si>
-  <si>
-    <t>campaign--3d806c36-94c1-487f-b65e-9ff91c2a9abb</t>
-  </si>
-  <si>
-    <t>campaign--f2ebdc18-4134-4740-9f13-2c482064e83a</t>
-  </si>
-  <si>
-    <t>campaign--c4507383-caba-4152-b825-48578038d866</t>
-  </si>
-  <si>
-    <t>campaign--127d73b7-ad29-4bc6-bae2-aec0c43bad66</t>
-  </si>
-  <si>
-    <t>campaign--b67d3570-8e41-417e-8f8e-7d5ecb7e1d31</t>
-  </si>
-  <si>
-    <t>campaign--7b0b746d-42c4-4b10-aa04-8bfec1343821</t>
-  </si>
-  <si>
-    <t>campaign--d00c3e48-4826-4f1e-bfb7-118f00d84861</t>
-  </si>
-  <si>
-    <t>campaign--51b9d6b1-568b-4d68-8f9c-19a0b548272b</t>
-  </si>
-  <si>
-    <t>campaign--ce760399-e985-4e95-bb41-7d3b796dd18b</t>
-  </si>
-  <si>
-    <t>campaign--4e66eed7-56a9-48ac-8a18-99a559927eb6</t>
-  </si>
-  <si>
-    <t>campaign--152cca2d-a341-45fd-a306-6690c012f021</t>
-  </si>
-  <si>
-    <t>campaign--387e09ec-bf7a-447c-a918-bcff0ee9da8b</t>
-  </si>
-  <si>
-    <t>campaign--beeb4667-4ab9-4028-94c4-b6b19eefabeb</t>
-  </si>
-  <si>
-    <t>campaign--40524974-ff86-4741-bc58-ccfb35d10bc7</t>
-  </si>
-  <si>
-    <t>campaign--d5059819-4fb3-4b0e-9e0a-5784b854386c</t>
-  </si>
-  <si>
-    <t>campaign--0dca3871-e3fd-47d7-a07f-e9ea15919c0d</t>
-  </si>
-  <si>
-    <t>campaign--d6da9526-4dd6-4eb9-abfd-44a5e1879d41</t>
-  </si>
-  <si>
-    <t>campaign--b1e8059c-3914-414e-8a6d-0fb74549bec8</t>
-  </si>
-  <si>
-    <t>campaign--2660323c-96cd-4d12-920b-3ca598fbdb74</t>
-  </si>
-  <si>
-    <t>campaign--a51dfeb5-c6ce-44b2-9bc5-c4c6687bd2f0</t>
-  </si>
-  <si>
-    <t>campaign--f3a217be-13bd-488e-b046-33d4a55b2cf3</t>
-  </si>
-  <si>
-    <t>campaign--5424b97c-0790-47c0-bc6a-99fda22a8e9d</t>
-  </si>
-  <si>
-    <t>campaign--6733da7e-2f67-4c13-97a6-00b05a549f10</t>
-  </si>
-  <si>
-    <t>campaign--ce5cc518-cbce-4e92-b8ff-30e504c15c2c</t>
-  </si>
-  <si>
-    <t>campaign--2907649b-fd94-42fa-8784-f18f4584d71a</t>
-  </si>
-  <si>
-    <t>campaign--dddb4201-585e-47c1-95e9-425b0730fb90</t>
-  </si>
-  <si>
-    <t>campaign--cf6632c9-6e3d-4cbc-9dce-724891b573c7</t>
-  </si>
-  <si>
-    <t>campaign--e7ee89b0-2cb6-4b84-948c-7057dd523852</t>
-  </si>
-  <si>
-    <t>campaign--eddd1738-28fd-4da0-b6f4-7c44a32152b7</t>
-  </si>
-  <si>
-    <t>campaign--5fa57ffc-7b8e-49c1-82da-60712fe1a716</t>
-  </si>
-  <si>
-    <t>campaign--466f1dd3-c4d2-4076-b0d7-d52a41e7bc83</t>
-  </si>
-  <si>
-    <t>campaign--11dce568-2d19-4c59-bdfd-64ec6fced3e6</t>
-  </si>
-  <si>
-    <t>campaign--0356e86e-0974-45cf-b41d-6997de20ba10</t>
-  </si>
-  <si>
-    <t>campaign--0956db31-89c5-43f3-aaa6-f6d9b3b7ff12</t>
-  </si>
-  <si>
-    <t>campaign--5177f321-68a6-4d63-a678-c5265f63243b</t>
-  </si>
-  <si>
-    <t>campaign--7402cc4a-618b-4851-8075-cb883379e3c0</t>
-  </si>
-  <si>
-    <t>campaign--b5ce00ca-7682-4ce8-9c4c-8be0c65df490</t>
-  </si>
-  <si>
-    <t>campaign--af98cd78-ddfd-4a73-8ab2-5b920e8221ac</t>
-  </si>
-  <si>
-    <t>campaign--9f187028-927d-4536-ba2f-3f2177c0e164</t>
-  </si>
-  <si>
-    <t>campaign--66970f35-4e71-491e-932e-1fee6b188e71</t>
-  </si>
-  <si>
-    <t>campaign--d419efc6-e0ba-4f5e-83a2-46e1d38cd231</t>
-  </si>
-  <si>
-    <t>campaign--09ffe87c-9f1c-4a9e-9879-3648aa2d3535</t>
-  </si>
-  <si>
-    <t>intrusion-set--6bb397ce-d257-45ef-9a68-fd682239dc91</t>
-  </si>
-  <si>
-    <t>intrusion-set--080fc39f-be32-4bdf-aa6b-d86e3dcd4f81</t>
-  </si>
-  <si>
-    <t>intrusion-set--6fcf2657-4840-4754-a318-5cee4b91d670</t>
-  </si>
-  <si>
-    <t>intrusion-set--4f0187aa-3964-42bb-8185-827fd9232dcb</t>
-  </si>
-  <si>
-    <t>intrusion-set--1e2aa43d-a27c-407c-b94a-405123ec52f9</t>
-  </si>
-  <si>
-    <t>intrusion-set--701ece7a-3998-432c-ab53-b4496887b072</t>
-  </si>
-  <si>
-    <t>tool--6fd47d4c-bac8-4dcd-b582-e6a42bb51313</t>
-  </si>
-  <si>
-    <t>tool--6faacf93-e3f5-43f6-8d94-9d2c7c6382a9</t>
-  </si>
-  <si>
-    <t>tool--43db716c-e55e-4798-8810-4606ebb81e52</t>
-  </si>
-  <si>
-    <t>tool--1652bd4f-c611-4f10-aedc-6581590e2df2</t>
-  </si>
-  <si>
-    <t>tool--4d2e439d-9619-4447-8a41-1af8960acc55</t>
-  </si>
-  <si>
-    <t>tool--4a55efd1-b775-4318-8adc-ebb029729960</t>
-  </si>
-  <si>
-    <t>tool--b591e96e-6cd5-4b20-9c6f-aa7dc5747255</t>
-  </si>
-  <si>
-    <t>tool--03b1e023-5469-49ea-9988-c7118a91b725</t>
-  </si>
-  <si>
-    <t>tool--ed0808d4-111e-4057-a345-7d951b669eb5</t>
-  </si>
-  <si>
-    <t>tool--60f65bd4-46b3-4eed-9418-254cf51965fd</t>
-  </si>
-  <si>
-    <t>tool--78806636-7cbc-4a54-9f61-2a5a98a33f13</t>
-  </si>
-  <si>
-    <t>tool--17849785-49e2-4f22-9488-618cbc11cec9</t>
-  </si>
-  <si>
-    <t>tool--b8bf442f-c688-4983-bc89-7fc0e5a2d70f</t>
+    <t>campaign--d5d3608b-1e2e-4e8e-9e3e-172b7ae8783f</t>
+  </si>
+  <si>
+    <t>campaign--da1bd8ae-397a-4c07-81d5-4ee62243c68b</t>
+  </si>
+  <si>
+    <t>campaign--6ba841e9-a6e2-4de1-ae16-ca96739e35ed</t>
+  </si>
+  <si>
+    <t>campaign--d25e87a6-7133-4e11-8e93-259d4f2bd994</t>
+  </si>
+  <si>
+    <t>campaign--327371af-9be7-44c2-8b57-7e51eea988c4</t>
+  </si>
+  <si>
+    <t>campaign--e31b1ed6-33c7-4d93-a2c6-a9b1dac0ac8c</t>
+  </si>
+  <si>
+    <t>campaign--000c635b-27f2-43b1-b98d-ff81a4105054</t>
+  </si>
+  <si>
+    <t>campaign--13625203-0aca-405b-9409-d6bb04dedcc2</t>
+  </si>
+  <si>
+    <t>campaign--c89888d0-b5d3-4947-b33d-d1d066710b8d</t>
+  </si>
+  <si>
+    <t>campaign--5b0cdeff-e761-4c3f-ba0c-feaec1ead563</t>
+  </si>
+  <si>
+    <t>campaign--cbda1a24-f09e-414b-ab6c-1177afcf6579</t>
+  </si>
+  <si>
+    <t>campaign--477d33b8-e868-4f14-994c-3ff87914d154</t>
+  </si>
+  <si>
+    <t>campaign--d07a6a51-42fd-4fca-9e60-9f47a2f3d55b</t>
+  </si>
+  <si>
+    <t>campaign--6dc22dba-186d-44f2-b8e5-932b3d3ae163</t>
+  </si>
+  <si>
+    <t>campaign--30e8ed62-d3e8-4143-9e5e-632bd7aa23cc</t>
+  </si>
+  <si>
+    <t>campaign--5a248622-bb69-496e-b7a9-6563aebba048</t>
+  </si>
+  <si>
+    <t>campaign--35ebb683-a8d6-4486-b3b2-f449826b17ce</t>
+  </si>
+  <si>
+    <t>campaign--9d8a0b71-9771-4b85-a072-eb7f2ebaaa79</t>
+  </si>
+  <si>
+    <t>campaign--04b69ccd-9489-447b-99a2-77765d33a863</t>
+  </si>
+  <si>
+    <t>campaign--e29a7c8b-78d8-4200-a28e-b29c47fd3db4</t>
+  </si>
+  <si>
+    <t>campaign--bee06f63-5b9a-40ee-8ded-3807e18b2794</t>
+  </si>
+  <si>
+    <t>campaign--12a31509-f6b1-4af2-ba71-d0d3f1a7e55c</t>
+  </si>
+  <si>
+    <t>campaign--cfd8e869-e600-4d3e-ab87-ab274a92891e</t>
+  </si>
+  <si>
+    <t>campaign--6569f13e-42ba-41d7-a075-7940b2fa7c53</t>
+  </si>
+  <si>
+    <t>campaign--b375cce2-197a-4d61-84e5-bc95c4f061aa</t>
+  </si>
+  <si>
+    <t>campaign--d1be4871-85b3-4161-b768-fcbdd3f3d268</t>
+  </si>
+  <si>
+    <t>campaign--b4a7dd59-002b-4a93-b13c-ab142a60073b</t>
+  </si>
+  <si>
+    <t>campaign--a06fac12-cd5a-4e5a-b61a-efbc0cd5c005</t>
+  </si>
+  <si>
+    <t>campaign--380516f0-c58a-4738-90e3-693af3883357</t>
+  </si>
+  <si>
+    <t>campaign--20b012fa-ab52-4e32-8992-ea76da37110f</t>
+  </si>
+  <si>
+    <t>campaign--d726fa7f-7c1c-4924-88a6-74444222bd9f</t>
+  </si>
+  <si>
+    <t>campaign--0a86d435-8e69-4f3a-bc96-b3ac668c82bc</t>
+  </si>
+  <si>
+    <t>campaign--fa5a41c0-90cb-4caf-860d-a3428108338f</t>
+  </si>
+  <si>
+    <t>campaign--93b9db3d-54e0-4cd1-a73d-8da9102e4009</t>
+  </si>
+  <si>
+    <t>campaign--2e5633ce-2d35-42b6-9ef4-0bf9c8b1bf35</t>
+  </si>
+  <si>
+    <t>campaign--cb207683-dcc4-4b73-ac2f-0be500edc74f</t>
+  </si>
+  <si>
+    <t>campaign--afb7bd59-6c2a-440a-a21d-5961efba5eff</t>
+  </si>
+  <si>
+    <t>campaign--43bcd15c-cf4f-4445-acbd-65ae81877442</t>
+  </si>
+  <si>
+    <t>campaign--d81de34f-47cd-428a-a41a-09a6f56a9da7</t>
+  </si>
+  <si>
+    <t>campaign--034fab01-25ca-406a-af72-18424cd8865e</t>
+  </si>
+  <si>
+    <t>campaign--65f10cf2-b7b9-4bba-99bd-850bd647691e</t>
+  </si>
+  <si>
+    <t>campaign--5a7b9428-869c-4411-836b-ac68418c3e88</t>
+  </si>
+  <si>
+    <t>campaign--993b7232-af60-4415-a814-7856a5aac9b0</t>
+  </si>
+  <si>
+    <t>campaign--adcbb713-6625-4bb2-bbdb-ca95dce75216</t>
+  </si>
+  <si>
+    <t>campaign--fc8f6110-efac-4b90-b548-1454dac7a19b</t>
+  </si>
+  <si>
+    <t>campaign--5c62e27c-a9a5-4f3d-8c9b-c9e0b90a244b</t>
+  </si>
+  <si>
+    <t>campaign--4ef7374d-4184-4e74-8a4d-61459b26d02f</t>
+  </si>
+  <si>
+    <t>campaign--cfee05cb-c034-4971-a531-902e845ccef3</t>
+  </si>
+  <si>
+    <t>campaign--34f93fca-7d2a-4e55-bc81-7f5697e97ef5</t>
+  </si>
+  <si>
+    <t>campaign--6664b694-3b86-465b-9e27-aea2b4bb1daa</t>
+  </si>
+  <si>
+    <t>campaign--3f943474-7a02-49f9-95d4-6284c13fcf28</t>
+  </si>
+  <si>
+    <t>campaign--8260bb29-de17-4c6d-8152-bcfe4b2b99ab</t>
+  </si>
+  <si>
+    <t>campaign--249316b5-9848-4974-bb96-36f491ad2ff3</t>
+  </si>
+  <si>
+    <t>campaign--51f52048-db4e-4bb3-a9d3-9c3ef5a7efdf</t>
+  </si>
+  <si>
+    <t>campaign--62d59075-a1be-4fc3-bb73-dfbba3d9890f</t>
+  </si>
+  <si>
+    <t>campaign--620a3478-b534-42fe-ae16-eef44729927d</t>
+  </si>
+  <si>
+    <t>campaign--33d73442-ef8e-4272-9b52-8409285e64d4</t>
+  </si>
+  <si>
+    <t>campaign--dde6e95d-8a5e-4d08-9cec-a7ff943a6316</t>
+  </si>
+  <si>
+    <t>campaign--451c6e51-6fd7-493b-82dd-f5b2d321469c</t>
+  </si>
+  <si>
+    <t>campaign--999f0ed3-c7f6-4cbe-b1a2-d7d8d6eedf7b</t>
+  </si>
+  <si>
+    <t>campaign--324dfd0b-8bb9-4e73-b770-c4878fa141b3</t>
+  </si>
+  <si>
+    <t>campaign--e48baa05-e5ad-4906-b269-18674c9abe58</t>
+  </si>
+  <si>
+    <t>campaign--5ac2c3e0-9d38-426d-81e5-09cf5a941ae2</t>
+  </si>
+  <si>
+    <t>campaign--b98a9b9a-6b83-45f6-b65e-38d9bffe4df7</t>
+  </si>
+  <si>
+    <t>campaign--71c8fe9d-7933-4793-8688-8ab211e64903</t>
+  </si>
+  <si>
+    <t>campaign--f8715c92-b16d-427b-8db4-e3a8d3c8f294</t>
+  </si>
+  <si>
+    <t>campaign--4d0ec18b-c72b-4515-9f5d-4246894f9414</t>
+  </si>
+  <si>
+    <t>campaign--d55f729d-5ef5-4b86-a509-1a176d91bbf5</t>
+  </si>
+  <si>
+    <t>campaign--5f5df72e-1fe1-43dd-82d6-8d828a183ff5</t>
+  </si>
+  <si>
+    <t>campaign--6c70c6bf-d458-4a42-a588-2d462edf232e</t>
+  </si>
+  <si>
+    <t>campaign--3e59ca2e-eae8-41fa-b2ec-cb039c9b4210</t>
+  </si>
+  <si>
+    <t>campaign--89ab3728-120a-41b6-b6f8-eee58aa5bf75</t>
+  </si>
+  <si>
+    <t>campaign--15dd6c2c-0e8f-4497-8d49-119a63052355</t>
+  </si>
+  <si>
+    <t>campaign--f5969a82-f450-48d2-a83f-31c2c2fcfc5a</t>
+  </si>
+  <si>
+    <t>campaign--8df71303-011a-488a-a3d5-cfabdf43a3bc</t>
+  </si>
+  <si>
+    <t>campaign--d59baa17-740d-4701-ac73-c8a740a1902e</t>
+  </si>
+  <si>
+    <t>campaign--bb2e0c40-4185-4a26-9a4a-843f0f42fb91</t>
+  </si>
+  <si>
+    <t>campaign--1c942e99-7fdf-43c2-a1c7-0c036960d550</t>
+  </si>
+  <si>
+    <t>campaign--2587cdb8-4685-4f49-ad80-4cf1673de499</t>
+  </si>
+  <si>
+    <t>campaign--4850b46c-5052-41fe-8b42-439a1d32be7b</t>
+  </si>
+  <si>
+    <t>campaign--160fbc62-8a4d-4576-86c8-bb6e8212b355</t>
+  </si>
+  <si>
+    <t>campaign--f726e55f-ac4b-4710-9b09-6b1bd5d7aca3</t>
+  </si>
+  <si>
+    <t>campaign--b12ec413-1bd9-46dd-b084-f775d59555ce</t>
+  </si>
+  <si>
+    <t>campaign--4b166b15-a737-4bfc-a873-ce378b04442b</t>
+  </si>
+  <si>
+    <t>campaign--7f39ffcb-c876-4ac1-97c7-77225d687cf7</t>
+  </si>
+  <si>
+    <t>campaign--c6287a90-fda2-414b-9536-7e8d7b333225</t>
+  </si>
+  <si>
+    <t>campaign--bfff8349-9b26-4bec-993e-4d3fb7792a21</t>
+  </si>
+  <si>
+    <t>campaign--a88279c6-8e3a-4610-98b4-61afdf9b1b00</t>
+  </si>
+  <si>
+    <t>campaign--a7923c48-f560-4ecf-99f5-9b6a59a4c658</t>
+  </si>
+  <si>
+    <t>campaign--bf2d7f34-0a40-4a70-8642-f68ef8dae022</t>
+  </si>
+  <si>
+    <t>campaign--86b88822-1271-4a0b-b652-bac9d6c1e4e8</t>
+  </si>
+  <si>
+    <t>campaign--ab434fb0-c7d3-4c1c-bcbd-c4c4498cf657</t>
+  </si>
+  <si>
+    <t>campaign--a156a043-c7da-45b0-aa0a-5299ead941bb</t>
+  </si>
+  <si>
+    <t>campaign--0cfea08d-0a35-4a62-a6b8-66a75b949383</t>
+  </si>
+  <si>
+    <t>campaign--8a97f881-3742-4d79-9bf1-0d2b3f8bacfe</t>
+  </si>
+  <si>
+    <t>campaign--b12ceb44-a32c-43df-82b7-e817321bdc3c</t>
+  </si>
+  <si>
+    <t>campaign--9c6d7b3b-bfe7-43c5-9b32-9928bf384cb3</t>
+  </si>
+  <si>
+    <t>campaign--2df6168b-6e9d-456f-a84a-30638a365400</t>
+  </si>
+  <si>
+    <t>campaign--d10ef172-c6c8-4f61-9f6c-4be1a77043ec</t>
+  </si>
+  <si>
+    <t>campaign--eecb9861-e70e-403d-bf70-88d38775c3b5</t>
+  </si>
+  <si>
+    <t>campaign--9a356b3e-0022-416c-bda6-336376c7b0f7</t>
+  </si>
+  <si>
+    <t>campaign--3b1dfe61-fc96-495a-92c1-e9617744d5b3</t>
+  </si>
+  <si>
+    <t>intrusion-set--3642f171-4667-4b82-b3c5-73f7f518396b</t>
+  </si>
+  <si>
+    <t>intrusion-set--224aa639-ced9-4891-bc3c-72ee1592cf05</t>
+  </si>
+  <si>
+    <t>intrusion-set--e3bc6b24-7eb3-408b-af74-b5924d08cd07</t>
+  </si>
+  <si>
+    <t>intrusion-set--1be81b91-037a-46a1-8e5e-b282c40ea297</t>
+  </si>
+  <si>
+    <t>intrusion-set--243887eb-e4f8-4b0e-a6d2-843e9676f671</t>
+  </si>
+  <si>
+    <t>intrusion-set--8b5f0098-75af-4fcd-9c7f-88149768cd8b</t>
+  </si>
+  <si>
+    <t>tool--b4c0d62c-b3f5-4069-a07d-c7e9a48427e5</t>
+  </si>
+  <si>
+    <t>tool--5c43501c-aa32-48a4-a151-6c6897e3b0dd</t>
+  </si>
+  <si>
+    <t>tool--e5929876-f3ec-466c-90a8-ec4a16cd8ac7</t>
+  </si>
+  <si>
+    <t>tool--5dcf4786-4e1a-44f2-8aa0-e4b5fdf1f93f</t>
+  </si>
+  <si>
+    <t>tool--d57519cc-1898-4106-8e8b-4798bf53d3b4</t>
+  </si>
+  <si>
+    <t>tool--4ba8494b-f590-4308-868c-37a12508f6a3</t>
+  </si>
+  <si>
+    <t>tool--fd9d33aa-46ee-48a8-b37c-b5813b8dd7cb</t>
+  </si>
+  <si>
+    <t>tool--af3c7286-be13-4569-ac9d-c96ebbac6a34</t>
+  </si>
+  <si>
+    <t>tool--413178e7-81d2-4bdd-ab53-c632febad570</t>
+  </si>
+  <si>
+    <t>tool--4ebdeb25-4eb2-43cd-a70b-e019e1a4ef6c</t>
+  </si>
+  <si>
+    <t>tool--5ceff728-9a89-463d-b71b-79b952d31693</t>
+  </si>
+  <si>
+    <t>tool--ff0e5cd8-b850-4df9-845a-ab14c6ba2104</t>
+  </si>
+  <si>
+    <t>tool--2de74860-9286-45c7-b350-d41ae6685351</t>
   </si>
   <si>
     <t>campaign</t>
@@ -1658,253 +1658,253 @@
     <t>Смена алфавита родного языка</t>
   </si>
   <si>
-    <t>attack-pattern--8623a36b-99de-4dfb-ba46-b2b5e9cf0d85</t>
-  </si>
-  <si>
-    <t>attack-pattern--95138ada-459f-440e-a79a-7fcf8874b584</t>
-  </si>
-  <si>
-    <t>attack-pattern--8feebaca-97cf-4478-b1d3-8e0a8ed2edc0</t>
-  </si>
-  <si>
-    <t>attack-pattern--286b8cda-f24d-4dde-a188-c0b140491a96</t>
-  </si>
-  <si>
-    <t>attack-pattern--b8fc16d6-7f03-4404-9d8d-f9782a0d4b3e</t>
-  </si>
-  <si>
-    <t>attack-pattern--60d5bdf7-06c3-4a53-b2d3-36b02a2230e3</t>
-  </si>
-  <si>
-    <t>attack-pattern--880b414d-a823-4193-b270-c0a7de9e6d12</t>
-  </si>
-  <si>
-    <t>attack-pattern--fe23fd12-ed27-416d-a891-53fd0945c418</t>
-  </si>
-  <si>
-    <t>attack-pattern--a92eb244-48f1-4d36-91b8-9ff6404bc66d</t>
-  </si>
-  <si>
-    <t>attack-pattern--08292bee-5177-4f79-bfa6-4f0345a5a446</t>
-  </si>
-  <si>
-    <t>attack-pattern--3a36e7b8-ad04-4cb0-8ffc-9b6502c66d77</t>
-  </si>
-  <si>
-    <t>attack-pattern--c8e73b27-78c5-4634-93ec-287a7cd80529</t>
-  </si>
-  <si>
-    <t>attack-pattern--8f5f6323-a749-4b89-a8ae-36633f183b54</t>
-  </si>
-  <si>
-    <t>attack-pattern--37759b81-258f-4d71-9703-9654ac67cab0</t>
-  </si>
-  <si>
-    <t>attack-pattern--60a4cda8-8154-4a3f-9826-f9d39155d257</t>
-  </si>
-  <si>
-    <t>attack-pattern--22e649d9-36b0-4f1f-88e9-e34fd12441c4</t>
-  </si>
-  <si>
-    <t>attack-pattern--2001e1d6-3887-44fe-892d-ce873833b382</t>
-  </si>
-  <si>
-    <t>attack-pattern--dc37deb9-2659-4fc2-b801-127690502a1e</t>
-  </si>
-  <si>
-    <t>attack-pattern--bf3afc82-5403-4ae9-9f69-3d9ef357c6c8</t>
-  </si>
-  <si>
-    <t>attack-pattern--563b0db6-14f7-4b63-8256-95de0ef5cf8c</t>
-  </si>
-  <si>
-    <t>attack-pattern--2421e2f6-4b1f-4f1e-8faa-69e9b14cbbe8</t>
-  </si>
-  <si>
-    <t>attack-pattern--7f745905-530b-4294-9eda-f8dafe9f0edd</t>
-  </si>
-  <si>
-    <t>attack-pattern--ca41993a-f62d-477b-802f-e63f4c050380</t>
-  </si>
-  <si>
-    <t>attack-pattern--0ffd53d6-5fd6-43e5-aff6-4e1d50a00743</t>
-  </si>
-  <si>
-    <t>attack-pattern--e49e8037-4bae-447d-86e6-23b275db8d96</t>
-  </si>
-  <si>
-    <t>attack-pattern--1a2eea19-fa56-4b46-b746-af741b0fbe4a</t>
-  </si>
-  <si>
-    <t>attack-pattern--fef93f62-3fe5-4d86-bad7-82607554a597</t>
-  </si>
-  <si>
-    <t>attack-pattern--fe33bd0c-bd06-451b-92ea-b2f65444329b</t>
-  </si>
-  <si>
-    <t>attack-pattern--dac8d747-5bf3-47af-9f54-b010ae92ccea</t>
-  </si>
-  <si>
-    <t>attack-pattern--d4b577cd-5a76-46f7-8c39-b96213fc4263</t>
-  </si>
-  <si>
-    <t>attack-pattern--7be66db5-2484-4f82-9c02-2c658aba5534</t>
-  </si>
-  <si>
-    <t>attack-pattern--8f5deb62-ed66-4518-9b21-c1557815cce5</t>
-  </si>
-  <si>
-    <t>attack-pattern--ac8f6735-f593-4862-b036-039679f6825d</t>
-  </si>
-  <si>
-    <t>attack-pattern--709b796b-4c14-4219-8b7d-848ccf3df33f</t>
-  </si>
-  <si>
-    <t>attack-pattern--229f46aa-5a77-41ce-a34b-4d978b1164ea</t>
-  </si>
-  <si>
-    <t>attack-pattern--91bd2ac0-d39a-4a37-b4ba-3b7d9cc48480</t>
-  </si>
-  <si>
-    <t>attack-pattern--8accb141-a1ff-471e-9a3a-988919bcceb6</t>
-  </si>
-  <si>
-    <t>attack-pattern--3c93037a-c467-4137-81e2-c058a9d90107</t>
-  </si>
-  <si>
-    <t>attack-pattern--595ddc1a-2efe-4154-a6d7-880fb2fe280f</t>
-  </si>
-  <si>
-    <t>attack-pattern--c0c59602-b27b-4b66-b864-82a05ff862db</t>
-  </si>
-  <si>
-    <t>attack-pattern--8fa70d63-cbe1-4ba7-b1a5-2573911cf454</t>
-  </si>
-  <si>
-    <t>attack-pattern--f69b9809-b9e2-4a3e-b8d9-cf3f74af4335</t>
-  </si>
-  <si>
-    <t>attack-pattern--575a4091-4083-4c93-8862-74543ad2f94c</t>
-  </si>
-  <si>
-    <t>attack-pattern--9fb6f979-a54f-46ce-9d0b-ce0c5db37e7a</t>
-  </si>
-  <si>
-    <t>attack-pattern--fd99f80b-0f34-4288-bc79-c0f3cf18e846</t>
-  </si>
-  <si>
-    <t>attack-pattern--aa11cd7e-92e7-43ec-af19-193b81bdb604</t>
-  </si>
-  <si>
-    <t>attack-pattern--0fa8defa-fb0b-4599-9491-7d725883c3fd</t>
-  </si>
-  <si>
-    <t>attack-pattern--37844351-6c24-42d8-99ba-2eb178febd3c</t>
-  </si>
-  <si>
-    <t>attack-pattern--aeca9532-ecda-49fc-9915-fe9b53956bf8</t>
-  </si>
-  <si>
-    <t>attack-pattern--4c4ac28a-0504-4efc-b7bb-a81682cab9ef</t>
-  </si>
-  <si>
-    <t>attack-pattern--0813df13-c30d-4a9c-badc-bf8ff641b717</t>
-  </si>
-  <si>
-    <t>attack-pattern--ae7d996b-f766-44ab-a46b-60abdd2b3ef6</t>
-  </si>
-  <si>
-    <t>attack-pattern--e1c8faff-7670-454e-a4f0-3da445f53ac9</t>
-  </si>
-  <si>
-    <t>attack-pattern--b041117e-4c21-419b-a1ad-f357fd63741f</t>
-  </si>
-  <si>
-    <t>attack-pattern--a6684ef1-fa45-4bf7-9ec1-db7ebe4dec10</t>
-  </si>
-  <si>
-    <t>attack-pattern--503486f3-22d3-4ed3-a8fb-f63db2718af0</t>
-  </si>
-  <si>
-    <t>attack-pattern--9f1e418c-f7d0-4526-9824-f880b69b0dc8</t>
-  </si>
-  <si>
-    <t>attack-pattern--019504d9-9143-4762-b36e-729108653789</t>
-  </si>
-  <si>
-    <t>attack-pattern--b8f0d38d-8111-4ef2-87ab-d970fb6f6d04</t>
-  </si>
-  <si>
-    <t>attack-pattern--3d97cbb0-3c4c-4fd3-9b5e-679517b777f3</t>
-  </si>
-  <si>
-    <t>attack-pattern--a8e7461e-9164-42e7-a275-578694585803</t>
-  </si>
-  <si>
-    <t>attack-pattern--cf3d899a-e96c-4063-bf08-65e437c19c7f</t>
-  </si>
-  <si>
-    <t>attack-pattern--73c181fd-e569-4225-9bfb-045b64df9b0c</t>
-  </si>
-  <si>
-    <t>attack-pattern--85208eb7-09ab-4287-a298-87298178d6c7</t>
-  </si>
-  <si>
-    <t>attack-pattern--fd811343-f4f3-4812-ad57-477da21a7e8d</t>
-  </si>
-  <si>
-    <t>attack-pattern--71797db1-dffd-44dd-8bfa-53446c0091df</t>
-  </si>
-  <si>
-    <t>attack-pattern--a08a6f55-9930-4233-8df3-cf86e10008ca</t>
-  </si>
-  <si>
-    <t>attack-pattern--72323e0d-b098-4e42-8cd1-544258dc8973</t>
-  </si>
-  <si>
-    <t>attack-pattern--3b132a9a-ecc8-4b8b-b93c-77771f5dc46c</t>
-  </si>
-  <si>
-    <t>attack-pattern--99619131-579e-49d3-aa32-d9ba015ed29a</t>
-  </si>
-  <si>
-    <t>attack-pattern--242eeb83-aeba-4f79-a3ae-2f62a5bc3706</t>
-  </si>
-  <si>
-    <t>attack-pattern--14d57931-21d5-4fd1-bf37-f26ce432a5ca</t>
-  </si>
-  <si>
-    <t>attack-pattern--ed09b02f-1bf8-4c07-859e-b28e828825d5</t>
-  </si>
-  <si>
-    <t>attack-pattern--e745fb62-c9c2-41af-affe-cac608952241</t>
-  </si>
-  <si>
-    <t>attack-pattern--062669ed-dadc-446f-992c-3425ac24dd1e</t>
-  </si>
-  <si>
-    <t>attack-pattern--61fccaa6-3ad9-4372-8b42-682b13577269</t>
-  </si>
-  <si>
-    <t>attack-pattern--624b5cee-3da2-4c18-906b-d1f1aca11306</t>
-  </si>
-  <si>
-    <t>attack-pattern--81623f2c-c724-43fa-bbab-429f8575f921</t>
-  </si>
-  <si>
-    <t>attack-pattern--a26ee77d-cf1a-4687-988f-932ccc9542bf</t>
-  </si>
-  <si>
-    <t>attack-pattern--fe1389e1-23dc-4f41-b2e1-15ed665a5840</t>
-  </si>
-  <si>
-    <t>attack-pattern--52c17a9d-8e67-4b7c-bddd-a0111496a6f5</t>
-  </si>
-  <si>
-    <t>attack-pattern--3fff8702-55b8-4c84-a528-2b14b7b980da</t>
-  </si>
-  <si>
-    <t>attack-pattern--b516107a-c248-4465-aa68-d5e20f3bf635</t>
+    <t>attack-pattern--22337eab-4ab5-4577-a766-4a514a636fe2</t>
+  </si>
+  <si>
+    <t>attack-pattern--d71852a6-d08a-4937-b2b1-ccf143798754</t>
+  </si>
+  <si>
+    <t>attack-pattern--67fd1251-9ad0-415e-94db-14c6fcda7c8c</t>
+  </si>
+  <si>
+    <t>attack-pattern--c55f58f1-faf2-498e-84f2-59993e1ecbcc</t>
+  </si>
+  <si>
+    <t>attack-pattern--1f8e90a1-2fa1-4e0c-9de7-2a6b61fc3412</t>
+  </si>
+  <si>
+    <t>attack-pattern--5e67abdd-9625-497c-8eed-591b2d0091a8</t>
+  </si>
+  <si>
+    <t>attack-pattern--8861e444-81bb-468e-9fc5-8b7e401e8898</t>
+  </si>
+  <si>
+    <t>attack-pattern--71b8603d-1b4a-45dd-bdc5-58df6fe6a1cb</t>
+  </si>
+  <si>
+    <t>attack-pattern--07605117-d49e-4edb-b205-a42d341fbafe</t>
+  </si>
+  <si>
+    <t>attack-pattern--0de3e487-7362-4416-91f8-3c71cc10d76d</t>
+  </si>
+  <si>
+    <t>attack-pattern--36fadd8e-e035-4c50-be0d-258be309a516</t>
+  </si>
+  <si>
+    <t>attack-pattern--9596e8a1-16fa-466f-b16e-b567018e83c6</t>
+  </si>
+  <si>
+    <t>attack-pattern--137a55c1-3751-4f3e-b038-0a8a31ae7b53</t>
+  </si>
+  <si>
+    <t>attack-pattern--ef5c8e81-c4de-408e-a0bb-eeba03e4ef41</t>
+  </si>
+  <si>
+    <t>attack-pattern--f62f4a3e-70ad-4d66-978f-70460748790e</t>
+  </si>
+  <si>
+    <t>attack-pattern--d4d22a9d-86be-4ed6-bb79-7792aad443f3</t>
+  </si>
+  <si>
+    <t>attack-pattern--4a811ffb-e200-4e7b-a48d-5dbb2e05d21b</t>
+  </si>
+  <si>
+    <t>attack-pattern--4b4499c1-7976-4838-ac5f-1b2503e91894</t>
+  </si>
+  <si>
+    <t>attack-pattern--2bb142f3-19c9-4d2d-ab6b-e91a6d1eb45d</t>
+  </si>
+  <si>
+    <t>attack-pattern--f60c3210-890a-4015-a4a9-e1966101ed5d</t>
+  </si>
+  <si>
+    <t>attack-pattern--6a388bfd-b3f8-4136-a3d0-3b6c92b62616</t>
+  </si>
+  <si>
+    <t>attack-pattern--3953a646-ca74-4d27-bb4b-801773351821</t>
+  </si>
+  <si>
+    <t>attack-pattern--c985b114-66f8-43e8-a9d5-09f7dcce76d2</t>
+  </si>
+  <si>
+    <t>attack-pattern--9861afc3-113a-4f8e-ba90-12d851653a4c</t>
+  </si>
+  <si>
+    <t>attack-pattern--6819df95-06a3-4c71-874f-8daea090f07e</t>
+  </si>
+  <si>
+    <t>attack-pattern--c671af96-e92c-44ff-820d-00bdb7de4fca</t>
+  </si>
+  <si>
+    <t>attack-pattern--d984185b-2502-414b-969d-f165cdeedc31</t>
+  </si>
+  <si>
+    <t>attack-pattern--03024756-3f6a-42b3-b93e-2d31c7ce6b6b</t>
+  </si>
+  <si>
+    <t>attack-pattern--8a5da3da-67cf-4659-bb91-0b28685766a1</t>
+  </si>
+  <si>
+    <t>attack-pattern--b3a3b655-dacd-4ee5-bae1-68801c3d15dc</t>
+  </si>
+  <si>
+    <t>attack-pattern--2f0e072e-5d5e-458e-a5c3-8efbaef46084</t>
+  </si>
+  <si>
+    <t>attack-pattern--8a804fba-621a-4868-b128-51cebf0ad2b2</t>
+  </si>
+  <si>
+    <t>attack-pattern--3eff3cd8-fbaf-4e5d-b38e-c72604acb3ce</t>
+  </si>
+  <si>
+    <t>attack-pattern--cbff6b3a-8340-4986-9183-3c02b87fd1b2</t>
+  </si>
+  <si>
+    <t>attack-pattern--c93829ec-d90f-41a9-9191-466a6365de51</t>
+  </si>
+  <si>
+    <t>attack-pattern--9facc2a5-8243-49aa-96cb-a94ef85b25c9</t>
+  </si>
+  <si>
+    <t>attack-pattern--9d3f3422-f494-42ab-9385-bc4e8ef727ca</t>
+  </si>
+  <si>
+    <t>attack-pattern--c7ccd834-4f08-4829-96ae-45e58d47945f</t>
+  </si>
+  <si>
+    <t>attack-pattern--b0851c83-e4d2-41c1-b5de-9115df406339</t>
+  </si>
+  <si>
+    <t>attack-pattern--0b6448a8-18a4-4d48-bfcf-172a74724542</t>
+  </si>
+  <si>
+    <t>attack-pattern--76b6c6fb-ce17-427d-b717-16011ae54b6e</t>
+  </si>
+  <si>
+    <t>attack-pattern--40f36bf9-2850-4992-b47f-4abe909a0e93</t>
+  </si>
+  <si>
+    <t>attack-pattern--02964caf-d52a-4d68-abcc-cdd1ef5fa69d</t>
+  </si>
+  <si>
+    <t>attack-pattern--cc782e40-0ae3-4f6d-94cb-2828cb2d5005</t>
+  </si>
+  <si>
+    <t>attack-pattern--09c9ca23-10d8-4f0f-a7dd-e99bb022299a</t>
+  </si>
+  <si>
+    <t>attack-pattern--9162f78a-1b72-4adc-9f8b-0a6b6410a3a7</t>
+  </si>
+  <si>
+    <t>attack-pattern--9e90f9e3-ced7-476d-acac-467e8c865ca0</t>
+  </si>
+  <si>
+    <t>attack-pattern--7ee9829e-072b-48f0-b801-b5b627c8bf1a</t>
+  </si>
+  <si>
+    <t>attack-pattern--ea9a2533-0faa-4b9d-bb0e-237ca902e1d7</t>
+  </si>
+  <si>
+    <t>attack-pattern--da48c22f-a5e2-41e7-97e4-07bfc4156350</t>
+  </si>
+  <si>
+    <t>attack-pattern--6e962dbe-f818-407b-b5a6-3eec9fbe9ec2</t>
+  </si>
+  <si>
+    <t>attack-pattern--6f08f0ef-8704-4d0e-90f5-ad421918d899</t>
+  </si>
+  <si>
+    <t>attack-pattern--09059676-291f-4053-a7b5-17d93eb87d30</t>
+  </si>
+  <si>
+    <t>attack-pattern--4b8920a8-f486-4065-aff8-4e7b6ee8b829</t>
+  </si>
+  <si>
+    <t>attack-pattern--3d1653fe-5ea0-4eb0-8c78-f849ecc43e11</t>
+  </si>
+  <si>
+    <t>attack-pattern--41699f0f-f822-4dbc-b201-dca7ac3eddce</t>
+  </si>
+  <si>
+    <t>attack-pattern--b34ebb98-d962-4987-8399-890eef9c69fe</t>
+  </si>
+  <si>
+    <t>attack-pattern--738e1811-a9a5-4407-be43-b726fd7e7589</t>
+  </si>
+  <si>
+    <t>attack-pattern--86f1c7c0-561e-4b45-97c0-faad41484e38</t>
+  </si>
+  <si>
+    <t>attack-pattern--d5f24756-885a-43f1-a9f0-b0088651bbc3</t>
+  </si>
+  <si>
+    <t>attack-pattern--c6da22a5-ceb4-4f40-a3bc-bcd6e655d591</t>
+  </si>
+  <si>
+    <t>attack-pattern--d38398cd-b820-4626-9510-465d56ba906c</t>
+  </si>
+  <si>
+    <t>attack-pattern--36e1d7c1-2f0e-41c6-8aee-177df4bdbc61</t>
+  </si>
+  <si>
+    <t>attack-pattern--0d6e1a1e-2c33-4280-86f2-8a1d0049b089</t>
+  </si>
+  <si>
+    <t>attack-pattern--a882288f-98fe-4c75-859a-17d669c08376</t>
+  </si>
+  <si>
+    <t>attack-pattern--5df092aa-9e0d-440d-8aa0-5f9988432ae3</t>
+  </si>
+  <si>
+    <t>attack-pattern--edd49cde-2190-45a8-9277-0fafcda1502c</t>
+  </si>
+  <si>
+    <t>attack-pattern--a87aa45d-2118-4e87-af92-e75e367453c9</t>
+  </si>
+  <si>
+    <t>attack-pattern--5f90feb8-5507-456c-9d1d-0e0e3cce55de</t>
+  </si>
+  <si>
+    <t>attack-pattern--d051e585-aa48-4964-b54e-2e08adc472f9</t>
+  </si>
+  <si>
+    <t>attack-pattern--edcb13e5-fbb1-4396-9e8c-1e3fe9dde52c</t>
+  </si>
+  <si>
+    <t>attack-pattern--2d723928-4bb8-45b5-86d4-a6f2398ca02f</t>
+  </si>
+  <si>
+    <t>attack-pattern--3c5f8bcd-ee2b-4396-9e79-3c99fcc96d81</t>
+  </si>
+  <si>
+    <t>attack-pattern--12023694-fdfd-480d-990d-fefa0cc12655</t>
+  </si>
+  <si>
+    <t>attack-pattern--ed457228-1fd9-4a65-ac85-388ba6460f94</t>
+  </si>
+  <si>
+    <t>attack-pattern--b2df162e-6cd7-4286-8841-dbeff90a7e20</t>
+  </si>
+  <si>
+    <t>attack-pattern--63335f7f-c1d8-42d3-bab5-4055c59e6a1e</t>
+  </si>
+  <si>
+    <t>attack-pattern--f2e939fc-283e-4bea-9fbf-f17acac31435</t>
+  </si>
+  <si>
+    <t>attack-pattern--8f3de97b-1ed5-4594-9889-41cd32d8adf5</t>
+  </si>
+  <si>
+    <t>attack-pattern--e1c78d1f-6f07-4f4b-9220-6d455354bc64</t>
+  </si>
+  <si>
+    <t>attack-pattern--02c5997b-a7da-48ac-96da-c4daa1aafc35</t>
+  </si>
+  <si>
+    <t>attack-pattern--fef3fc3b-399c-41e0-8c76-a6eb1d014ada</t>
+  </si>
+  <si>
+    <t>attack-pattern--77c6e8eb-0074-49c8-90cd-9c830db4859f</t>
   </si>
   <si>
     <t>technique</t>
@@ -2222,7 +2222,7 @@
     <t>Юридическая фиксация раскола страны на две части с превращением Правобережья в буферную зону: «По условиям Вечного мира Правобережье осталось за Польшей... договорили и постановили, что те места оставатись имеют пусты, так как ныне суть» (Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011)(Citation: Мазепа 2007).</t>
   </si>
   <si>
-    <t>Использование институтов государственного здравоохранения для политически мотивированного диагностирования инакомыслящих (диагноз «вялотекущая шизофрения») и их бессрочной изоляции в психиатрических больницах. (Citation: Карательная психиатрия в России: назад в СССР? 2026)</t>
+    <t>Использование институтов государственного здравоохранения для политически мотивированного диагностирования инакомыслящих (диагноз «вялотекущая шизофрения») и их бессрочной изоляции в психиатрических больницах. (Citation: Карательная психиатрия в России: назад в СССР? 2020)</t>
   </si>
   <si>
     <t>Принудительное использование казаков для строительства имперской инфраструктуры в тяжелых условиях: «в делании около киево-печерскаго монастыря фортификаций» (Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011)(Citation: Мазепа 2007).</t>
@@ -2396,7 +2396,7 @@
     <t>Тотальный информационный контроль и законодательный запрет внутри РФ называть вторжение «войной» (использование эвфемизма «специальная военная операция») для сокрытия преступлений и создания альтернативной реальности. (Citation: Рашизм: Звір з безодні 2023)</t>
   </si>
   <si>
-    <t>Систематические кибератаки на энергетические компании и муниципальные теплоснабжающие предприятия в условиях полномасштабной войны для прекращения подачи электроэнергии и тепла украинским гражданским потребителям. (Citation: 2022 Ukraine Electric Power Attack | MITRE ATT&amp;CK®) (Citation: FrostyGoop Incident | MITRE ATT&amp;CK® 2024). 
+    <t>Систематические кибератаки на энергетические компании и муниципальные теплоснабжающие предприятия в условиях полномасштабной войны для прекращения подачи электроэнергии и тепла украинским гражданским потребителям. (Citation: 2022 Ukraine Electric Power Attack | MITRE ATT&amp;CK® 2024) (Citation: FrostyGoop Incident | MITRE ATT&amp;CK® 2024). 
 Систематическое нанесение массированных ударов крылатыми ракетами и дронами-камикадзе (Shahed) по объектам генерации (Змиевская ТЭЦ, Харьковская ТЭЦ-5, Трипольская ТЭС, ДнепроГЭС) и трансформаторным подстанциям для создания блэкаутов. (Citation: Удари по об'єктах критичної інфраструктури України під час російсько-української війни — Вікіпедія 2026)</t>
   </si>
   <si>
@@ -2496,7 +2496,7 @@
     <t>Полное отстранение автономии от участия в международных переговорах о статусе ее же территорий. При юридическом разделе украинских земель мнение самого народа было проигнорировано: «Для Мазепы и всех украинцев это колоссальное унижение» (Citation: Война и наказание: Как Россия уничтожала Украину 2023)(Citation: Мазепа 2007).</t>
   </si>
   <si>
-    <t>Применение разрушительных медикаментозных препаратов (нейролептиков) в качестве средства физического и психологического давления на здоровых правозащитников в закрытых стационарах. (Citation: Карательная психиатрия в России: назад в СССР? 2026)</t>
+    <t>Применение разрушительных медикаментозных препаратов (нейролептиков) в качестве средства физического и психологического давления на здоровых правозащитников в закрытых стационарах. (Citation: Карательная психиатрия в России: назад в СССР? 2020)</t>
   </si>
   <si>
     <t>Секуляризация и конфискация в имперскую казну земель украинских православных монастырей (1786 год), лишившая локальную церковь экономической базы (Citation: Друга Малоросійська колегія — Вікіпедія 2026).</t>
@@ -2962,3031 +2962,3031 @@
     <t>Полный законодательный запрет на самоорганизацию: указ Столыпина «про заборону будь-яких українських організацій» (Citation: Русифікація України — Вікіпедія 2026).</t>
   </si>
   <si>
-    <t>relationship--12bc8904-99bc-4a55-a768-c6d397e1a829</t>
-  </si>
-  <si>
-    <t>relationship--f69b368a-adad-48c6-8f60-0c29f400c102</t>
-  </si>
-  <si>
-    <t>relationship--18c6088c-8841-4ec9-aac2-46a007ebcc21</t>
-  </si>
-  <si>
-    <t>relationship--a963ff2b-070c-4db6-a06d-e5e88f4f3325</t>
-  </si>
-  <si>
-    <t>relationship--797f6d6f-ef9f-4e5e-ae50-0adf72381d8d</t>
-  </si>
-  <si>
-    <t>relationship--aac285db-9b35-40f3-850d-3879630f39b0</t>
-  </si>
-  <si>
-    <t>relationship--01b73e42-a773-4c1d-ae11-0261602aa1d5</t>
-  </si>
-  <si>
-    <t>relationship--fd3683f7-5961-46fb-a76a-82b65e3a5b73</t>
-  </si>
-  <si>
-    <t>relationship--70eb29ba-2799-438a-823e-c446df6bb1c3</t>
-  </si>
-  <si>
-    <t>relationship--3034bb38-cc9e-4fe3-9842-ae672d1b5536</t>
-  </si>
-  <si>
-    <t>relationship--386bf42f-4150-4986-9814-edbe336dfe55</t>
-  </si>
-  <si>
-    <t>relationship--284bb962-aeb3-442f-b754-228c2dd8867e</t>
-  </si>
-  <si>
-    <t>relationship--d05d0b21-357b-4498-bc88-e7c4cc4f9f9f</t>
-  </si>
-  <si>
-    <t>relationship--d2022ffe-3862-4f2c-9b89-19cb8f674ff3</t>
-  </si>
-  <si>
-    <t>relationship--44935fe7-597d-4305-8969-7d4193d4937e</t>
-  </si>
-  <si>
-    <t>relationship--b237bf26-ef58-44ce-884b-12d24cef4ebc</t>
-  </si>
-  <si>
-    <t>relationship--78f059a7-2d33-49be-9c65-b63c987a69e8</t>
-  </si>
-  <si>
-    <t>relationship--6cd0cf96-c86f-49ec-8146-9ffbe9e15ab1</t>
-  </si>
-  <si>
-    <t>relationship--eb81fea3-4753-4b73-893f-16fd43321646</t>
-  </si>
-  <si>
-    <t>relationship--170c807a-1fe8-4130-977a-13bd8e119f56</t>
-  </si>
-  <si>
-    <t>relationship--cdf4555b-3027-4c26-8582-bdb5ea5f869a</t>
-  </si>
-  <si>
-    <t>relationship--53131930-c0c4-4d4b-9c82-ee16de54ce19</t>
-  </si>
-  <si>
-    <t>relationship--4821fa4d-5f4d-4bfb-8bd6-4a0299575b5b</t>
-  </si>
-  <si>
-    <t>relationship--37cfc5df-0284-43b0-8c9f-621300de40cb</t>
-  </si>
-  <si>
-    <t>relationship--31c52698-3b14-4ed3-b949-6f20a9f44ea9</t>
-  </si>
-  <si>
-    <t>relationship--b392a5a2-6f29-4155-b30e-c35d6e81164a</t>
-  </si>
-  <si>
-    <t>relationship--10b967cf-5d22-49ba-9593-7586cfb25d57</t>
-  </si>
-  <si>
-    <t>relationship--9a4cfe1d-243b-4da7-8f85-a5a234c0de46</t>
-  </si>
-  <si>
-    <t>relationship--229bc6e3-bd6e-4f00-920a-bf0b75aeb3ce</t>
-  </si>
-  <si>
-    <t>relationship--3b64a530-ee75-43af-ad56-3f7be087f2b6</t>
-  </si>
-  <si>
-    <t>relationship--24417c43-3986-4157-a47b-138ce21c1586</t>
-  </si>
-  <si>
-    <t>relationship--d2f3847c-ea68-485c-9b5c-5489b3c02399</t>
-  </si>
-  <si>
-    <t>relationship--243e8e41-8775-4d04-8cf5-4270b8f00b87</t>
-  </si>
-  <si>
-    <t>relationship--1e9db859-18a1-4b08-bbd4-9c8cb097729b</t>
-  </si>
-  <si>
-    <t>relationship--05eb80d0-303e-4b3d-8974-3be40c5a6cdc</t>
-  </si>
-  <si>
-    <t>relationship--c1b7dbad-95fa-4b86-aa0b-f4847943206f</t>
-  </si>
-  <si>
-    <t>relationship--712355d5-0423-4efa-910b-56b77ad545fa</t>
-  </si>
-  <si>
-    <t>relationship--5fbfc696-714c-42dc-a387-89d2a7bb4132</t>
-  </si>
-  <si>
-    <t>relationship--9179dcc8-fd36-43e7-8ebc-45c9b2d0c555</t>
-  </si>
-  <si>
-    <t>relationship--e179b84d-4d95-4dce-a854-38c32b638bc9</t>
-  </si>
-  <si>
-    <t>relationship--d019a938-c6f0-42a3-b4c7-00fc1eac691c</t>
-  </si>
-  <si>
-    <t>relationship--fc05427b-b7ed-4a94-b62c-2bb9ef30d7ad</t>
-  </si>
-  <si>
-    <t>relationship--c5355ea4-9dd7-41b9-a281-58dfe58bacd2</t>
-  </si>
-  <si>
-    <t>relationship--e322551c-b3c2-40e8-9efa-d9fe5c984aab</t>
-  </si>
-  <si>
-    <t>relationship--6fabfad7-778f-461e-9d87-7d2f8192ddc4</t>
-  </si>
-  <si>
-    <t>relationship--1cada7a0-7e70-4c74-85aa-54969bd99f6d</t>
-  </si>
-  <si>
-    <t>relationship--464ccc93-dc4f-4050-bb8b-07a28cef790e</t>
-  </si>
-  <si>
-    <t>relationship--b6b6b49c-9491-4e42-a665-09884c32fa52</t>
-  </si>
-  <si>
-    <t>relationship--0e9d2f82-e202-4317-94cf-8932067cdd33</t>
-  </si>
-  <si>
-    <t>relationship--5b7b09b3-9a51-4d65-a86c-4befe3ab7fbc</t>
-  </si>
-  <si>
-    <t>relationship--f30be867-5cae-40b0-8c91-06f5c306ff2b</t>
-  </si>
-  <si>
-    <t>relationship--ca78e3f5-edc4-46ff-86f6-89fb3c35288e</t>
-  </si>
-  <si>
-    <t>relationship--7752b90a-82a7-4e9c-b827-c26959415840</t>
-  </si>
-  <si>
-    <t>relationship--ffa36b52-804f-4e4a-a467-aff1ccaeb8b2</t>
-  </si>
-  <si>
-    <t>relationship--b1dd4bc9-7ef5-4050-b0f8-f5fb9c2019e0</t>
-  </si>
-  <si>
-    <t>relationship--2ee3efa5-74c8-4255-94b2-ce1b5ff81142</t>
-  </si>
-  <si>
-    <t>relationship--fe6278dd-37ff-4ae0-aaa2-15e5deec1bad</t>
-  </si>
-  <si>
-    <t>relationship--e6bf0e77-c31d-42b9-8cd6-f52b8fb3d2db</t>
-  </si>
-  <si>
-    <t>relationship--5e841f9c-b382-44fc-b069-31d7ed86d613</t>
-  </si>
-  <si>
-    <t>relationship--26b24ed3-bab4-48b5-af20-473d37df73a1</t>
-  </si>
-  <si>
-    <t>relationship--5dc7f800-2702-41e3-a999-ec18d12bdb0b</t>
-  </si>
-  <si>
-    <t>relationship--bb205bd8-3105-49e8-a966-8a5a4b80ce4b</t>
-  </si>
-  <si>
-    <t>relationship--066eb730-edbb-4eb7-be95-30ee7a67bbad</t>
-  </si>
-  <si>
-    <t>relationship--997ffb23-24f9-4bf6-ae61-1773c568c2d6</t>
-  </si>
-  <si>
-    <t>relationship--90927691-a826-45b1-aa61-4b0253556a02</t>
-  </si>
-  <si>
-    <t>relationship--da285461-ab09-48e4-bac7-6e4b7f5c2e1d</t>
-  </si>
-  <si>
-    <t>relationship--ae5ce0c4-d70d-40a0-891a-6472f31c7fa3</t>
-  </si>
-  <si>
-    <t>relationship--a16aa153-ab2d-49f9-96bf-61989c058b71</t>
-  </si>
-  <si>
-    <t>relationship--64487f17-db95-46e3-adff-3d3d2629772b</t>
-  </si>
-  <si>
-    <t>relationship--5c1bd692-3e7e-43aa-907a-435464271bc7</t>
-  </si>
-  <si>
-    <t>relationship--c2595a81-92d7-404b-ad9f-1b290af8866b</t>
-  </si>
-  <si>
-    <t>relationship--bd9c2824-ba1b-4fc6-b7be-815d4341d76c</t>
-  </si>
-  <si>
-    <t>relationship--13d8371a-bd47-4e2d-9833-64256ea7236e</t>
-  </si>
-  <si>
-    <t>relationship--d4f3bacb-f6e3-44e1-948e-fb11cc9afcdb</t>
-  </si>
-  <si>
-    <t>relationship--c561afa2-ce06-447a-8c4c-be71f21480c7</t>
-  </si>
-  <si>
-    <t>relationship--28cf8d5f-6d6f-453c-a201-317c04dee34d</t>
-  </si>
-  <si>
-    <t>relationship--769341f9-ee3b-42c3-b2ab-3398313428ec</t>
-  </si>
-  <si>
-    <t>relationship--2d753309-a85e-415c-a222-0301ec963f66</t>
-  </si>
-  <si>
-    <t>relationship--cc65d3dc-fb26-4e54-b54f-9d2c812c7cff</t>
-  </si>
-  <si>
-    <t>relationship--1eb1a282-23cc-43ab-b857-0d11d636e2a5</t>
-  </si>
-  <si>
-    <t>relationship--2bbbd285-77d1-4fd6-91c9-5d028c72f098</t>
-  </si>
-  <si>
-    <t>relationship--a1492f55-f3d8-429c-8ec4-384c57f58821</t>
-  </si>
-  <si>
-    <t>relationship--c63d2783-b3b7-47a3-9be9-d1677fa6945c</t>
-  </si>
-  <si>
-    <t>relationship--0b4d5b99-7039-4ab0-a99d-094ceaa1cd91</t>
-  </si>
-  <si>
-    <t>relationship--c3b294ff-66a0-4e31-a6b4-12d7a648a472</t>
-  </si>
-  <si>
-    <t>relationship--4eef5b22-d5ab-478f-8fcc-018f34f58e25</t>
-  </si>
-  <si>
-    <t>relationship--40042475-a205-4c1b-97e7-7c76c7865cbb</t>
-  </si>
-  <si>
-    <t>relationship--c67c90d0-effd-43e6-84de-05d750e98fe0</t>
-  </si>
-  <si>
-    <t>relationship--b12bd32f-d8c0-47c2-a1f0-cfddf25000c1</t>
-  </si>
-  <si>
-    <t>relationship--ba3fd383-b77d-4c48-9eb4-506a4833f1f2</t>
-  </si>
-  <si>
-    <t>relationship--15c27931-d7a9-4b5c-9058-bf081b37a8a3</t>
-  </si>
-  <si>
-    <t>relationship--1ad4791e-261a-4512-8123-89fc26e12b25</t>
-  </si>
-  <si>
-    <t>relationship--17997574-a161-4f2d-81d7-a8ffc9343dcf</t>
-  </si>
-  <si>
-    <t>relationship--39edf99e-7601-4a47-ad39-8e3d080fba7d</t>
-  </si>
-  <si>
-    <t>relationship--5173a2ce-e76a-4bb7-8685-3d30657cf7bb</t>
-  </si>
-  <si>
-    <t>relationship--36eb1714-2670-44e7-b9cb-96d0eb426b72</t>
-  </si>
-  <si>
-    <t>relationship--3d4c10fe-6943-48fd-b897-e90c3158744f</t>
-  </si>
-  <si>
-    <t>relationship--78c6f40f-c64c-4681-9061-63acf50a4bd6</t>
-  </si>
-  <si>
-    <t>relationship--b24d5aea-09e9-41bc-85a0-240a7b69a591</t>
-  </si>
-  <si>
-    <t>relationship--2bb139e8-1edc-4db2-b8c1-482176975ad4</t>
-  </si>
-  <si>
-    <t>relationship--ca8c42ef-8ef1-4ccb-8237-f9206f58f733</t>
-  </si>
-  <si>
-    <t>relationship--fd974d03-b680-4744-85c5-8e1ac2ce7c31</t>
-  </si>
-  <si>
-    <t>relationship--d88929a7-dc71-49ce-b9a1-bfedc801e8a8</t>
-  </si>
-  <si>
-    <t>relationship--889d82e4-c966-46ee-813f-71a4ed883cb3</t>
-  </si>
-  <si>
-    <t>relationship--da414b25-28e7-4ad0-8cca-2cd59cdc48e1</t>
-  </si>
-  <si>
-    <t>relationship--aad22950-d6b3-4fe0-b4b4-caad525e66f9</t>
-  </si>
-  <si>
-    <t>relationship--da141e9b-14f5-475d-99d3-c04fc29be05a</t>
-  </si>
-  <si>
-    <t>relationship--85595de6-5e82-4a7f-b38b-4b435d8cf145</t>
-  </si>
-  <si>
-    <t>relationship--7b26ad80-eb32-4bc4-862c-c1bea3fbb5b8</t>
-  </si>
-  <si>
-    <t>relationship--64c6a3db-95b7-4e80-8617-864066661402</t>
-  </si>
-  <si>
-    <t>relationship--35e874c2-2f0e-465c-84a3-1a52fb3c1b26</t>
-  </si>
-  <si>
-    <t>relationship--dcff66f2-928d-4376-b74d-88e6e8dbf2a5</t>
-  </si>
-  <si>
-    <t>relationship--d7492bb2-0caf-43b4-ae2b-8ee766277e6f</t>
-  </si>
-  <si>
-    <t>relationship--cbae46bb-6a35-426e-b26f-99c4dcfb2180</t>
-  </si>
-  <si>
-    <t>relationship--1708cf7c-b8a3-467b-bfc8-b4377ecd8c38</t>
-  </si>
-  <si>
-    <t>relationship--7574787e-7bb0-4142-9608-d3431597b447</t>
-  </si>
-  <si>
-    <t>relationship--11b3f371-48c5-4e60-aa9e-0916f44736d9</t>
-  </si>
-  <si>
-    <t>relationship--cc273750-9b46-4c99-b177-0a13451fa78b</t>
-  </si>
-  <si>
-    <t>relationship--622624c2-53db-46f8-be5e-d6e076333f46</t>
-  </si>
-  <si>
-    <t>relationship--22bea2fb-f567-4526-920e-59a0897693d6</t>
-  </si>
-  <si>
-    <t>relationship--44443958-236b-4f9d-8dd9-dd2639671b09</t>
-  </si>
-  <si>
-    <t>relationship--0eca743f-f114-4eda-8c60-ec4089510360</t>
-  </si>
-  <si>
-    <t>relationship--78491aa4-2e4c-497b-a148-f18a3699f56b</t>
-  </si>
-  <si>
-    <t>relationship--7b87aecc-4151-47c7-bdb2-52939bf7dbc3</t>
-  </si>
-  <si>
-    <t>relationship--c8b13959-0d01-4ec3-a0f5-48fc07bbf2cb</t>
-  </si>
-  <si>
-    <t>relationship--65a5ac54-0c22-4eb2-aa18-8fdad83e0379</t>
-  </si>
-  <si>
-    <t>relationship--ee484915-af85-415a-aee2-59f72dfabfee</t>
-  </si>
-  <si>
-    <t>relationship--54b740d5-dc2a-488a-9abe-15274e89c834</t>
-  </si>
-  <si>
-    <t>relationship--d4163bd3-d740-44b0-84b8-52453b734603</t>
-  </si>
-  <si>
-    <t>relationship--9f8b72df-9550-4e18-b5b9-5f6d5dbdb913</t>
-  </si>
-  <si>
-    <t>relationship--111463bd-bdd5-4238-b51c-d664db9a7527</t>
-  </si>
-  <si>
-    <t>relationship--e7d51b28-6ac8-4287-8edd-a7a2eebd5b96</t>
-  </si>
-  <si>
-    <t>relationship--c1d642c5-e1bf-4fcb-b15e-f3b758183aeb</t>
-  </si>
-  <si>
-    <t>relationship--644b2b16-6c0b-4193-9307-c7c5138365ad</t>
-  </si>
-  <si>
-    <t>relationship--5f5efdfd-5041-41ef-8ee9-25f9ab012dcf</t>
-  </si>
-  <si>
-    <t>relationship--543ae80c-998e-4a3d-87fc-2a0b9571daf1</t>
-  </si>
-  <si>
-    <t>relationship--5c23f23c-fa2c-42fc-a317-81435663b76b</t>
-  </si>
-  <si>
-    <t>relationship--90480a09-7e26-49ad-a06f-27abea71cd39</t>
-  </si>
-  <si>
-    <t>relationship--fa31a1e8-20be-4e59-acc3-f09fe1e88b70</t>
-  </si>
-  <si>
-    <t>relationship--06d0ed0b-2c51-4206-b60a-a6e4ff14aa9c</t>
-  </si>
-  <si>
-    <t>relationship--82488210-7fea-4709-b86a-ef25cc365ac6</t>
-  </si>
-  <si>
-    <t>relationship--961f7abb-d697-447f-937b-f617667fb890</t>
-  </si>
-  <si>
-    <t>relationship--afe322f3-20c6-4e19-bd5f-d934c0474718</t>
-  </si>
-  <si>
-    <t>relationship--c43b0019-ba2d-48ae-b94b-d9c00bdc7252</t>
-  </si>
-  <si>
-    <t>relationship--08a9e1b2-e85d-4cc5-bff1-39e0b459d38d</t>
-  </si>
-  <si>
-    <t>relationship--9fd32872-fa9b-4d10-a701-c9b9194b1faa</t>
-  </si>
-  <si>
-    <t>relationship--c20acf41-bf5b-459b-9d0e-13fac2907477</t>
-  </si>
-  <si>
-    <t>relationship--6a767d68-cfbb-4a18-8f10-94e866e5b8d7</t>
-  </si>
-  <si>
-    <t>relationship--a3737ab9-45f4-4cc1-b6a0-13c844b88dde</t>
-  </si>
-  <si>
-    <t>relationship--901f30d8-fc0c-4eb8-96f9-32d584a54246</t>
-  </si>
-  <si>
-    <t>relationship--b7663582-1572-4a44-b833-ad625c8cb24e</t>
-  </si>
-  <si>
-    <t>relationship--66e8ebce-a52b-4c43-9394-179226de2659</t>
-  </si>
-  <si>
-    <t>relationship--2fa363d9-3c0c-4552-90c7-8b8da0401f52</t>
-  </si>
-  <si>
-    <t>relationship--9f7e791a-cc20-4d06-9580-dd8ca3b03a4d</t>
-  </si>
-  <si>
-    <t>relationship--80b672fa-e491-44f1-9d66-d0c4886e6662</t>
-  </si>
-  <si>
-    <t>relationship--98d1d772-87b7-4001-b802-5b49faa65cee</t>
-  </si>
-  <si>
-    <t>relationship--213bdb84-51c4-45d0-89ac-99e1ee8522ee</t>
-  </si>
-  <si>
-    <t>relationship--17dea7f1-bad6-4016-b896-5ee021167a3c</t>
-  </si>
-  <si>
-    <t>relationship--7ac430ee-94d3-4633-8163-1e741c370134</t>
-  </si>
-  <si>
-    <t>relationship--422dfbc2-8291-4dc5-aefb-11bd94209cdc</t>
-  </si>
-  <si>
-    <t>relationship--11dc28fb-4450-4809-88bb-0c900fe1c2f3</t>
-  </si>
-  <si>
-    <t>relationship--dbf0b5c8-d27a-43c6-aedc-094feb1c0d90</t>
-  </si>
-  <si>
-    <t>relationship--51500d5f-2f2e-41c6-ad55-109ac321d20e</t>
-  </si>
-  <si>
-    <t>relationship--615b98b1-f463-4b83-b8a3-b570adafa3cc</t>
-  </si>
-  <si>
-    <t>relationship--f3d4e74c-fff3-4f81-b8fa-e219a78584cd</t>
-  </si>
-  <si>
-    <t>relationship--02303830-e777-4696-abd6-79af6cc46785</t>
-  </si>
-  <si>
-    <t>relationship--bd8df92b-4f7e-4fa1-a913-989c9b017938</t>
-  </si>
-  <si>
-    <t>relationship--3c03a0ec-6f48-48ea-b065-211f31f2894e</t>
-  </si>
-  <si>
-    <t>relationship--f8c0eb74-3575-4c55-a2d7-fba3ae802c40</t>
-  </si>
-  <si>
-    <t>relationship--da2da2f9-6084-45e5-a597-036208e9789e</t>
-  </si>
-  <si>
-    <t>relationship--c6ba7b3a-658d-4451-a98d-734322d8c54f</t>
-  </si>
-  <si>
-    <t>relationship--50ddb0a0-2867-44ed-91bc-b4dc901c80a3</t>
-  </si>
-  <si>
-    <t>relationship--88bccc8a-f7a2-49e1-a46f-367f8e27b642</t>
-  </si>
-  <si>
-    <t>relationship--3da1cb1c-cbae-43c0-bda4-07e3c264e71e</t>
-  </si>
-  <si>
-    <t>relationship--4f9574d4-02b8-4eca-9761-bbe5c069b344</t>
-  </si>
-  <si>
-    <t>relationship--9b16c020-b229-44f3-a8a1-c734308acc2a</t>
-  </si>
-  <si>
-    <t>relationship--4ae6a58e-d25b-48f8-ad29-e635c557e4fb</t>
-  </si>
-  <si>
-    <t>relationship--f53a0328-348d-41c6-8135-0ca1de900c44</t>
-  </si>
-  <si>
-    <t>relationship--3f994d91-2c90-41f2-92d8-263b6b544715</t>
-  </si>
-  <si>
-    <t>relationship--8df57727-064b-46cf-b734-615967f897af</t>
-  </si>
-  <si>
-    <t>relationship--0f783440-214a-4e1b-a578-17f990858926</t>
-  </si>
-  <si>
-    <t>relationship--57032a0b-d541-41be-b819-7d0d63f0b5e3</t>
-  </si>
-  <si>
-    <t>relationship--127fbaae-cb89-4739-a530-200a56c7969f</t>
-  </si>
-  <si>
-    <t>relationship--0f43555b-8d92-45d3-ba11-936e6545bc93</t>
-  </si>
-  <si>
-    <t>relationship--eeae3f06-5874-46d3-b082-b8562399910a</t>
-  </si>
-  <si>
-    <t>relationship--08d9608a-ea6a-41f0-af32-d0c899a83e7c</t>
-  </si>
-  <si>
-    <t>relationship--f1861116-7010-481e-8a86-6186461e7dbc</t>
-  </si>
-  <si>
-    <t>relationship--1821da0f-0ff6-4632-aec7-b813e5a83ca2</t>
-  </si>
-  <si>
-    <t>relationship--ae7cce33-6c06-40ca-8b00-7ba834cf1c0d</t>
-  </si>
-  <si>
-    <t>relationship--bb414712-b107-42a6-9d85-b650a2de464b</t>
-  </si>
-  <si>
-    <t>relationship--f6f0c367-67f9-48a0-a597-0ae07851f48a</t>
-  </si>
-  <si>
-    <t>relationship--d950ef63-aa43-40c9-8f83-813083d3d88f</t>
-  </si>
-  <si>
-    <t>relationship--78a7ef97-62b2-4fb4-ac12-997a6aed2ac6</t>
-  </si>
-  <si>
-    <t>relationship--8b727f87-2159-4163-939d-91e1821413e5</t>
-  </si>
-  <si>
-    <t>relationship--a04c3a8d-a32f-4a26-9115-bf067c7473c7</t>
-  </si>
-  <si>
-    <t>relationship--47631dd5-2035-4775-9342-c7a5d57463d2</t>
-  </si>
-  <si>
-    <t>relationship--22eff706-0769-49f0-9f2f-776115e3b86f</t>
-  </si>
-  <si>
-    <t>relationship--96909df7-d822-41ef-bce3-59aeb959f27f</t>
-  </si>
-  <si>
-    <t>relationship--a2be2f18-7418-4bc3-8d13-5a5cc0535a48</t>
-  </si>
-  <si>
-    <t>relationship--30fc98f5-39ab-4f73-9cf8-ecd4f13bad9c</t>
-  </si>
-  <si>
-    <t>relationship--20819672-cfc6-4d90-9978-67392464f9b5</t>
-  </si>
-  <si>
-    <t>relationship--0ea39f20-20c1-4f5a-97d8-19f243edd037</t>
-  </si>
-  <si>
-    <t>relationship--509c7f00-4bc2-49ff-93b0-830f5a811d4a</t>
-  </si>
-  <si>
-    <t>relationship--27307274-6d91-422f-892f-1920ff7f356d</t>
-  </si>
-  <si>
-    <t>relationship--ff40733b-8dae-4471-9e66-760250865fb7</t>
-  </si>
-  <si>
-    <t>relationship--493ade73-abf7-427c-9d87-81defb451d8b</t>
-  </si>
-  <si>
-    <t>relationship--e37eb846-1fc9-44d6-b0a4-05048966e228</t>
-  </si>
-  <si>
-    <t>relationship--a505add1-1a18-4ee5-b1db-fec9c4f48f9c</t>
-  </si>
-  <si>
-    <t>relationship--3b9ac042-c0a7-49ac-857f-05065c54075a</t>
-  </si>
-  <si>
-    <t>relationship--f4f67668-aa63-4766-9725-8f5b0aa8fe4e</t>
-  </si>
-  <si>
-    <t>relationship--1a0ed787-6e98-4d1c-8eaf-ad7622f746b6</t>
-  </si>
-  <si>
-    <t>relationship--51d34cd7-27af-4321-ad3b-c00925ef3bae</t>
-  </si>
-  <si>
-    <t>relationship--38934af6-e0df-4e99-8832-19dfc5aa76fb</t>
-  </si>
-  <si>
-    <t>relationship--8fe1cf5e-353d-49a0-9a18-5c9ce6519107</t>
-  </si>
-  <si>
-    <t>relationship--4b75d83e-aa45-4bdb-9e77-44ab08e9e40b</t>
-  </si>
-  <si>
-    <t>relationship--f06fd8d9-aef2-401f-a307-ca5a0e1285d2</t>
-  </si>
-  <si>
-    <t>relationship--62a5317c-5ba6-408f-9c80-5acfdbd32ee7</t>
-  </si>
-  <si>
-    <t>relationship--77903336-6ba1-40d5-91c7-6ca3ee9c4098</t>
-  </si>
-  <si>
-    <t>relationship--164df4fe-b365-4045-b692-006cc7379eaf</t>
-  </si>
-  <si>
-    <t>relationship--614cfb78-516d-4af0-a676-9f08e44f9179</t>
-  </si>
-  <si>
-    <t>relationship--49632cf4-f231-4539-bbc9-8d6680780a06</t>
-  </si>
-  <si>
-    <t>relationship--a6f31e13-5817-48e2-95f9-24e9d1cbbfc4</t>
-  </si>
-  <si>
-    <t>relationship--f8f236df-0be2-479d-9462-b5d67379bd51</t>
-  </si>
-  <si>
-    <t>relationship--408cd846-38c1-4247-9909-d37fb7b69199</t>
-  </si>
-  <si>
-    <t>relationship--b398d380-4b24-465a-a0a8-9ac8b2f5bd1b</t>
-  </si>
-  <si>
-    <t>relationship--221a7cb6-0e1b-4214-8620-8256aca937f3</t>
-  </si>
-  <si>
-    <t>relationship--b1876f95-fc2c-4f14-8cb5-afdf4ac78fd4</t>
-  </si>
-  <si>
-    <t>relationship--1a627c96-3d45-4503-b6d6-cf1bdac82c8c</t>
-  </si>
-  <si>
-    <t>relationship--abd1d624-9fb5-4369-940c-7d0015306b05</t>
-  </si>
-  <si>
-    <t>relationship--5aeacb37-7169-48d1-b03e-a8ffcf494f58</t>
-  </si>
-  <si>
-    <t>relationship--69546bbe-81ad-44d9-b7f3-7d3c24af479c</t>
-  </si>
-  <si>
-    <t>relationship--009eb8ba-56f4-4694-89af-17ea173d74cb</t>
-  </si>
-  <si>
-    <t>relationship--c0183cdf-818c-444a-9f3b-a2885749f658</t>
-  </si>
-  <si>
-    <t>relationship--07f0e483-8a65-4ad0-8068-b11e520db608</t>
-  </si>
-  <si>
-    <t>relationship--f39563eb-3ce1-408b-ad68-e1d4845500b5</t>
-  </si>
-  <si>
-    <t>relationship--fe28c216-cce3-41e9-b52d-2abf289d47ae</t>
-  </si>
-  <si>
-    <t>relationship--4065ee88-8afa-40c9-ac40-9d26f35b1f67</t>
-  </si>
-  <si>
-    <t>relationship--71f1a72d-7bbc-47d8-8e6c-8ff77ed33ea0</t>
-  </si>
-  <si>
-    <t>relationship--307b1228-84cf-49d8-853a-6af3a53c1627</t>
-  </si>
-  <si>
-    <t>relationship--d775343b-7fcc-4a1c-8e16-9a9cdb64e7a4</t>
-  </si>
-  <si>
-    <t>relationship--923a9d64-ddf0-4008-9bb2-af5d5ee0f230</t>
-  </si>
-  <si>
-    <t>relationship--82bc5611-617c-41ca-be4a-e5b3167d84ed</t>
-  </si>
-  <si>
-    <t>relationship--059aecae-97f4-4744-bcdd-a76d1a2f3f45</t>
-  </si>
-  <si>
-    <t>relationship--d7be5882-6700-4648-ba22-e980a2804072</t>
-  </si>
-  <si>
-    <t>relationship--1fe62db2-8ec1-4e0b-893d-b8c632009d9e</t>
-  </si>
-  <si>
-    <t>relationship--4826c5f8-4a5b-402c-bf84-bc13c03c3fb0</t>
-  </si>
-  <si>
-    <t>relationship--e55c1a27-ff44-4c2d-99a6-6fbd83ff60db</t>
-  </si>
-  <si>
-    <t>relationship--2912252d-746f-449f-9674-63b7caa18c56</t>
-  </si>
-  <si>
-    <t>relationship--61fe7007-0ed2-476c-a796-0d5c78694d88</t>
-  </si>
-  <si>
-    <t>relationship--289c43ba-2986-46ac-a3da-d69eef6f0a59</t>
-  </si>
-  <si>
-    <t>relationship--e2d69ef6-2ea3-4873-86f7-632c7a1fbc1c</t>
-  </si>
-  <si>
-    <t>relationship--b77d1234-dc45-4ad7-baec-4c75b7974d4e</t>
-  </si>
-  <si>
-    <t>relationship--73f6aed0-fefc-4888-8cca-cbe008ddf331</t>
-  </si>
-  <si>
-    <t>relationship--0a95e48e-b6fd-47c4-afed-08529f63fb39</t>
-  </si>
-  <si>
-    <t>relationship--9fbcddc5-9b75-451e-919a-d5e45e700a23</t>
-  </si>
-  <si>
-    <t>relationship--5d80c07d-5436-42ed-9ca4-3270c9c3d146</t>
-  </si>
-  <si>
-    <t>relationship--77cf91d2-6cb7-4ca0-9038-2b87606b5965</t>
-  </si>
-  <si>
-    <t>relationship--95635bce-78b4-4c59-b4d1-03622c8003ab</t>
-  </si>
-  <si>
-    <t>relationship--d12cff3c-fdbf-4fc7-bd6b-f1bb35b7304b</t>
-  </si>
-  <si>
-    <t>relationship--817daffb-a9b8-44e6-a395-6b7bf160e72c</t>
-  </si>
-  <si>
-    <t>relationship--fec74c64-d978-434e-bf80-197e2049f320</t>
-  </si>
-  <si>
-    <t>relationship--e93462ad-6c4e-48bd-a079-9519e3b5a04e</t>
-  </si>
-  <si>
-    <t>relationship--751f13ca-415c-4e84-a953-132107b7697e</t>
-  </si>
-  <si>
-    <t>relationship--da82a7ad-b4d7-4c94-8bea-057e671ae4a4</t>
-  </si>
-  <si>
-    <t>relationship--665cf86c-b8cf-4e87-a5e9-2cfcf18e0941</t>
-  </si>
-  <si>
-    <t>relationship--42757cb1-f4b1-4f96-9ea7-1e8e927da779</t>
-  </si>
-  <si>
-    <t>relationship--ed16aa83-affb-412b-b0e0-ff3c900821b4</t>
-  </si>
-  <si>
-    <t>relationship--abcaca4f-565d-478b-b717-29673f65534e</t>
-  </si>
-  <si>
-    <t>relationship--4254a725-81fd-452f-89f6-fc79843c701d</t>
-  </si>
-  <si>
-    <t>relationship--d05f11fd-62d3-4750-b34c-38d543b2b8c3</t>
-  </si>
-  <si>
-    <t>relationship--b68db160-d755-42d1-a36e-0971d3981d34</t>
-  </si>
-  <si>
-    <t>relationship--2735bc85-a60c-4465-a615-67902a033882</t>
-  </si>
-  <si>
-    <t>relationship--40f72abb-e0ef-4021-8aeb-0386d75fbbc5</t>
-  </si>
-  <si>
-    <t>relationship--f6de26ff-9458-4f70-9b43-8fb687b2d4d5</t>
-  </si>
-  <si>
-    <t>relationship--6dba15dc-fcbd-4e1c-963a-19a14fcaab3d</t>
-  </si>
-  <si>
-    <t>relationship--93ba7432-1e5d-4fe2-9c49-040925e42fcf</t>
-  </si>
-  <si>
-    <t>relationship--083eb465-7bc8-4e16-8155-41bbca4adf9e</t>
-  </si>
-  <si>
-    <t>relationship--bc31acf0-0893-4fc0-a6e1-b5041670f2b7</t>
-  </si>
-  <si>
-    <t>relationship--381d10a2-fd19-4e0e-9c59-0d20082fa5f1</t>
-  </si>
-  <si>
-    <t>relationship--ab67c82d-0704-4805-ad97-5b94f8e8e0dd</t>
-  </si>
-  <si>
-    <t>relationship--bc87995c-9763-461d-a407-c670d6a8772c</t>
-  </si>
-  <si>
-    <t>relationship--f039d33d-c0d7-4b3a-890c-f38e8127745a</t>
-  </si>
-  <si>
-    <t>relationship--5c06f90b-34e7-4af4-9051-814bdb4b2272</t>
-  </si>
-  <si>
-    <t>relationship--8656ea5a-2838-434f-b3e4-e46d58498762</t>
-  </si>
-  <si>
-    <t>relationship--b2de557b-fa55-4519-ac66-528e8af6a3dd</t>
-  </si>
-  <si>
-    <t>relationship--575e47df-7d05-4b63-a760-2fb8af22ca27</t>
-  </si>
-  <si>
-    <t>relationship--50904263-2021-46e6-9d4e-b17ef1767a32</t>
-  </si>
-  <si>
-    <t>relationship--9f1ce640-6cd4-41ce-b8e7-30beb441e07b</t>
-  </si>
-  <si>
-    <t>relationship--8dc84f9f-b861-46e6-9192-d6e0be26c243</t>
-  </si>
-  <si>
-    <t>relationship--ee281529-2dfd-403e-9712-983e5fdf4089</t>
-  </si>
-  <si>
-    <t>relationship--19c3ae9a-763c-41e6-93c4-459e7409edc5</t>
-  </si>
-  <si>
-    <t>relationship--7e2dbe56-d4a6-40bc-839b-a06fb70c72b6</t>
-  </si>
-  <si>
-    <t>relationship--bde30250-fec8-4075-9583-34e4d5abb426</t>
-  </si>
-  <si>
-    <t>relationship--92eaf1ec-0b9c-4931-a4a8-98844cba6e89</t>
-  </si>
-  <si>
-    <t>relationship--7b371fd1-75f7-478f-b1c7-00b939d0aece</t>
-  </si>
-  <si>
-    <t>relationship--35ec3b3a-eff2-44fb-aec8-6dd1b1a0cfd8</t>
-  </si>
-  <si>
-    <t>relationship--f090ddba-5fb5-4bf2-bd2e-03a64716ed7b</t>
-  </si>
-  <si>
-    <t>relationship--3125f806-4d48-4e7c-8996-51d6d5e0c75b</t>
-  </si>
-  <si>
-    <t>relationship--a71b6bc7-e18e-4552-a115-69058225ae37</t>
-  </si>
-  <si>
-    <t>relationship--11a39972-abd8-43b4-bb10-03a20a73c08f</t>
-  </si>
-  <si>
-    <t>relationship--8ab321f3-1338-4371-b149-1c668fabf0dd</t>
-  </si>
-  <si>
-    <t>relationship--e294b46c-20b9-4c7f-801f-d357310e305e</t>
-  </si>
-  <si>
-    <t>relationship--8b64c8ae-1518-41b9-a20e-6cf09ca2e48b</t>
-  </si>
-  <si>
-    <t>relationship--089d71fb-07ea-45f2-8da3-a01fe15dce00</t>
-  </si>
-  <si>
-    <t>relationship--491bb5c5-320b-4358-ad14-f8b5d225df94</t>
-  </si>
-  <si>
-    <t>relationship--7d35ca2d-4e05-4cbd-91cb-8a547ac0d139</t>
-  </si>
-  <si>
-    <t>relationship--450083a2-0f16-4351-bbf7-98f58a05acfa</t>
-  </si>
-  <si>
-    <t>relationship--cbcb0245-351e-46ed-b295-16ec259a9bca</t>
-  </si>
-  <si>
-    <t>relationship--8839435d-3403-46a8-864b-e44aa7e5ce64</t>
-  </si>
-  <si>
-    <t>relationship--36bd823d-8d29-4b40-8988-53c9f4147220</t>
-  </si>
-  <si>
-    <t>relationship--d8ae6fde-2c1c-43f4-a634-85ad68c21bf0</t>
-  </si>
-  <si>
-    <t>relationship--8f86c428-0b02-43cc-b405-2ef3507326af</t>
-  </si>
-  <si>
-    <t>relationship--1713ad45-2009-4023-8a34-096b6c63bcf0</t>
-  </si>
-  <si>
-    <t>relationship--fa034e46-b2bb-4c2e-a5e0-52cd498f8a0c</t>
-  </si>
-  <si>
-    <t>relationship--182066db-05cb-40a7-a484-1c8328bfcc10</t>
-  </si>
-  <si>
-    <t>relationship--2f7f4d25-08fb-45f8-93dc-6d79ae865b42</t>
-  </si>
-  <si>
-    <t>relationship--a0fb143f-aaca-45bf-855d-fa1b9d6cf79b</t>
-  </si>
-  <si>
-    <t>relationship--b1b2dcf2-ef8d-41a3-aeb2-f8e80a188c4b</t>
-  </si>
-  <si>
-    <t>relationship--d9494bd7-969c-47c9-ac09-a5458436690d</t>
-  </si>
-  <si>
-    <t>relationship--ca58fdb3-ae70-4904-9241-40e5e2bbfa00</t>
-  </si>
-  <si>
-    <t>relationship--571eb7c7-7df4-4156-9ef3-9ad5a5014462</t>
-  </si>
-  <si>
-    <t>relationship--f48604d5-3465-433f-9d3a-ca75e82895d6</t>
-  </si>
-  <si>
-    <t>relationship--d7110124-cc48-4827-a308-207ac8a3362b</t>
-  </si>
-  <si>
-    <t>relationship--3c04687a-7035-4136-bae0-60e37e3e332e</t>
-  </si>
-  <si>
-    <t>relationship--ade0f069-012a-4140-ad72-72fa3e3efb3b</t>
-  </si>
-  <si>
-    <t>relationship--0d732f10-2516-4f97-8cfb-0c71e4db8ec9</t>
-  </si>
-  <si>
-    <t>relationship--ce0f253a-59cd-4b2c-846e-ac087649efd3</t>
-  </si>
-  <si>
-    <t>relationship--1b8dd273-e71c-4916-8dfc-8e1f3128d50b</t>
-  </si>
-  <si>
-    <t>relationship--ae58917f-a6f0-44ee-a667-55dd75c4bb15</t>
-  </si>
-  <si>
-    <t>relationship--7fc97b2a-0ddb-4660-9de9-3ef19b82455b</t>
-  </si>
-  <si>
-    <t>relationship--93ef4a1f-61bb-4171-9c2f-5f3f4d10f7c4</t>
-  </si>
-  <si>
-    <t>relationship--62d431c1-cfc2-43e9-a9a8-da756690a928</t>
-  </si>
-  <si>
-    <t>relationship--3cf8a689-fc2c-47ac-bb19-79461b0f7161</t>
-  </si>
-  <si>
-    <t>relationship--7613d2e9-5949-43c3-8a05-4b51e5787b59</t>
-  </si>
-  <si>
-    <t>relationship--644f5cae-0211-467a-81f9-59b8421b070c</t>
-  </si>
-  <si>
-    <t>relationship--981a7c37-9588-4112-934e-b22231d066b9</t>
-  </si>
-  <si>
-    <t>relationship--179e4855-e609-484d-becf-994f523e2284</t>
-  </si>
-  <si>
-    <t>relationship--77592244-d658-495b-ad75-fb5f35cab59a</t>
-  </si>
-  <si>
-    <t>relationship--ed2bfd70-bcb7-4ce6-b694-fe610e493952</t>
-  </si>
-  <si>
-    <t>relationship--75a7a305-32b3-4766-8903-3ea13326b47e</t>
-  </si>
-  <si>
-    <t>relationship--88f6af26-efe3-4d98-866a-a87a0560d237</t>
-  </si>
-  <si>
-    <t>relationship--8f9a4b44-b810-4638-8805-1fbddfe84476</t>
-  </si>
-  <si>
-    <t>relationship--c84ba526-27a3-46e4-a8b3-f88d3592421d</t>
-  </si>
-  <si>
-    <t>relationship--6d118374-fffb-47c5-b006-5aacd9caa916</t>
-  </si>
-  <si>
-    <t>relationship--fbff1eb1-f6f7-4f3a-8ae1-5d4785bf9a71</t>
-  </si>
-  <si>
-    <t>relationship--3b656b51-fcc3-4f3e-a463-3cc3793cbf11</t>
-  </si>
-  <si>
-    <t>relationship--f5d4c998-2a74-4260-825f-1f9aac7206d1</t>
-  </si>
-  <si>
-    <t>relationship--9e36db8c-773e-48da-a73d-2660a2f6f69d</t>
-  </si>
-  <si>
-    <t>relationship--749dd6d1-ab34-4211-aaf1-2048a84a5d9d</t>
-  </si>
-  <si>
-    <t>relationship--c4c0d5ab-c6c3-4206-b3bc-1ab4447def2e</t>
-  </si>
-  <si>
-    <t>relationship--8d006552-45fe-4adb-bda4-1604e40e34a4</t>
-  </si>
-  <si>
-    <t>relationship--192a9394-d344-4c10-8fa0-8035a11e0567</t>
-  </si>
-  <si>
-    <t>relationship--4d4c0e29-2c3b-4933-9c72-832928f67ae0</t>
-  </si>
-  <si>
-    <t>relationship--35fe0a4a-1920-4c7a-9cad-039c08f48a5a</t>
-  </si>
-  <si>
-    <t>relationship--f176e5a6-adc5-485a-a206-d829fa767837</t>
-  </si>
-  <si>
-    <t>relationship--88ab7777-3a68-45af-9274-dedf6858fae7</t>
-  </si>
-  <si>
-    <t>relationship--a21d2834-8de3-4afe-9b34-bbb84f32aa9f</t>
-  </si>
-  <si>
-    <t>relationship--c118ef6f-6446-49d0-b220-bd5db2b83f32</t>
-  </si>
-  <si>
-    <t>relationship--07014a19-5d22-43de-8bf7-6f126d5b8949</t>
-  </si>
-  <si>
-    <t>relationship--219ec753-5aff-41db-ae4e-a8b416c3b2d8</t>
-  </si>
-  <si>
-    <t>relationship--a0ef1e81-0c7d-4e28-8d4f-deb30300d49d</t>
-  </si>
-  <si>
-    <t>relationship--3ff2429b-0b1b-43cc-9791-f0e3af03f6c8</t>
-  </si>
-  <si>
-    <t>relationship--2bfb8cc1-b9a1-4f71-a06a-c989eff11075</t>
-  </si>
-  <si>
-    <t>relationship--1fe27c33-d973-481f-b324-807fd5bc64f1</t>
-  </si>
-  <si>
-    <t>relationship--6b8b0038-bcb4-4d64-9d80-2896b6daf4f9</t>
-  </si>
-  <si>
-    <t>relationship--1c93eb84-954e-4d8d-984a-4734aca01dea</t>
-  </si>
-  <si>
-    <t>relationship--bf4cf27b-b1e2-4c4a-94d3-3d68731d7e4c</t>
-  </si>
-  <si>
-    <t>relationship--ad1cb304-d5da-4be7-a022-fa4edf156ff2</t>
-  </si>
-  <si>
-    <t>relationship--c7cc97e4-8f77-4b9b-8499-09d9587eebb9</t>
-  </si>
-  <si>
-    <t>relationship--3f9419ea-2c59-401c-a333-398a8d63f736</t>
-  </si>
-  <si>
-    <t>relationship--40bd6c27-ac79-4a64-ab3e-8392092c6632</t>
-  </si>
-  <si>
-    <t>relationship--288459a0-33bb-44c5-ade8-5a2d8dd53b93</t>
-  </si>
-  <si>
-    <t>relationship--55b061a5-ed77-45c8-a522-42b65265b577</t>
-  </si>
-  <si>
-    <t>relationship--4908d2b4-44d2-4215-911e-11323dc15e21</t>
-  </si>
-  <si>
-    <t>relationship--acc98d57-50f2-412d-938e-40b58cbeffdb</t>
-  </si>
-  <si>
-    <t>relationship--ea5508f4-6427-41da-9bdf-e130b0f06359</t>
-  </si>
-  <si>
-    <t>relationship--08db49f3-64ff-478e-99f5-794ec6f52b08</t>
-  </si>
-  <si>
-    <t>relationship--17ce3a2c-452a-487f-9e37-bf9fbd0e8836</t>
-  </si>
-  <si>
-    <t>relationship--fe79fc9a-d42b-48cb-8fe7-85ce18a3fcd5</t>
-  </si>
-  <si>
-    <t>relationship--5521b7b7-478c-43ff-b22e-803538668b6a</t>
-  </si>
-  <si>
-    <t>relationship--1a41a16f-819f-4a96-b53d-5262ccfd7de5</t>
-  </si>
-  <si>
-    <t>relationship--5fc94f2c-5fec-48b2-a9a2-6d0fd0ec1252</t>
-  </si>
-  <si>
-    <t>relationship--36a6516f-3289-48b3-98f2-ef25e6199d38</t>
-  </si>
-  <si>
-    <t>relationship--c020b2c9-6cf9-40fa-8110-196ec8ba6334</t>
-  </si>
-  <si>
-    <t>relationship--32253f9c-c9a2-45aa-87ed-5bd6634ae620</t>
-  </si>
-  <si>
-    <t>relationship--12776127-015b-4233-b4c2-488e85591bcc</t>
-  </si>
-  <si>
-    <t>relationship--ee751307-f3fb-4fdd-b6a6-dc03760b38cf</t>
-  </si>
-  <si>
-    <t>relationship--d15c000a-4caa-460b-bcae-74ec1a725589</t>
-  </si>
-  <si>
-    <t>relationship--9f379780-e370-4513-a4ad-03c0fcb98ca4</t>
-  </si>
-  <si>
-    <t>relationship--50e32249-8681-463e-bc7b-7e70aa84f004</t>
-  </si>
-  <si>
-    <t>relationship--55df5e32-047c-470f-b683-67a128ebcb89</t>
-  </si>
-  <si>
-    <t>relationship--e7c9b119-3dc1-44a0-ab06-b6ce09def61f</t>
-  </si>
-  <si>
-    <t>relationship--11a2a9c1-594c-4e43-9137-939a3bca12f4</t>
-  </si>
-  <si>
-    <t>relationship--88345c9f-c6b3-49b6-8d2b-d761c8e092f1</t>
-  </si>
-  <si>
-    <t>relationship--c745c745-31df-4393-97c9-82ae9c3e1097</t>
-  </si>
-  <si>
-    <t>relationship--13914f79-1256-4413-8d4c-5cbb3f566bd2</t>
-  </si>
-  <si>
-    <t>relationship--20d9d0de-0994-4387-a2b9-8eef101240d3</t>
-  </si>
-  <si>
-    <t>relationship--14d0858b-f62f-4502-b4ac-26fbc1848f86</t>
-  </si>
-  <si>
-    <t>relationship--188cbcf7-3088-4248-b47e-0fe5a3b9581e</t>
-  </si>
-  <si>
-    <t>relationship--5c3c4292-5fd2-4e61-9aab-759ef4faf510</t>
-  </si>
-  <si>
-    <t>relationship--9a305630-89b9-4bb7-8810-35820d619d09</t>
-  </si>
-  <si>
-    <t>relationship--cfe0d9be-4cb5-4264-9410-d0d30abe64d5</t>
-  </si>
-  <si>
-    <t>relationship--b145f77a-6f6e-4124-9555-898b97ce2a9b</t>
-  </si>
-  <si>
-    <t>relationship--f687f0b5-a326-4dfe-9af7-42aa9820d7ad</t>
-  </si>
-  <si>
-    <t>relationship--e73697a3-d274-45be-8679-5aba06634f98</t>
-  </si>
-  <si>
-    <t>relationship--377519d0-34be-488d-8297-2b75100fca38</t>
-  </si>
-  <si>
-    <t>relationship--013c628a-1353-4397-9f36-a2bb53b09d1e</t>
-  </si>
-  <si>
-    <t>relationship--5a1e51b1-880b-478a-a5f5-d9e4f4044a60</t>
-  </si>
-  <si>
-    <t>relationship--19507a4f-9ae3-4b15-9690-4cd61d81d1fb</t>
-  </si>
-  <si>
-    <t>relationship--e1701364-3ca9-465f-8890-d94d2c9591cd</t>
-  </si>
-  <si>
-    <t>relationship--746f2ff4-e097-4c76-812b-2111d50a0829</t>
-  </si>
-  <si>
-    <t>relationship--440f9065-974b-432b-9405-f703636d44cc</t>
-  </si>
-  <si>
-    <t>relationship--03546cba-397c-4d69-8e76-f411f36348da</t>
-  </si>
-  <si>
-    <t>relationship--9053f9af-f4d9-47d5-b155-8c5db5131c26</t>
-  </si>
-  <si>
-    <t>relationship--a1fe1f7d-5ea2-4318-b7aa-3758f7d2a53a</t>
-  </si>
-  <si>
-    <t>relationship--33028bfb-3e06-489c-b300-0e73eb807216</t>
-  </si>
-  <si>
-    <t>relationship--382fa7ac-8a40-41c1-92df-1b674855253b</t>
-  </si>
-  <si>
-    <t>relationship--23d9bc18-8cfb-4996-b8ab-321d470a48e8</t>
-  </si>
-  <si>
-    <t>relationship--25a90bdb-d410-478c-8b4a-3e8a1e7f7c8e</t>
-  </si>
-  <si>
-    <t>relationship--09e5fdaa-ed64-4f42-acf0-432e489f4914</t>
-  </si>
-  <si>
-    <t>relationship--1aa0f36f-2644-4f85-832d-3c4ed459cfbc</t>
-  </si>
-  <si>
-    <t>relationship--1ed8a4c6-5748-43e7-9aa7-8c86062f6dfa</t>
-  </si>
-  <si>
-    <t>relationship--0faee98e-2979-4e38-bf9d-cad9a019befe</t>
-  </si>
-  <si>
-    <t>relationship--ea93c2c7-5c56-45d6-835c-7b6ad925ec3f</t>
-  </si>
-  <si>
-    <t>relationship--fda1abb1-5109-4da0-a730-df689c03d86d</t>
-  </si>
-  <si>
-    <t>relationship--811de1f9-5922-4769-b7cb-3b7d1b3ed59e</t>
-  </si>
-  <si>
-    <t>relationship--53637650-7396-4d16-95b0-433945a0f293</t>
-  </si>
-  <si>
-    <t>relationship--50f81c9e-7a2d-4a6a-bf8f-0b4c75345cd3</t>
-  </si>
-  <si>
-    <t>relationship--fdbf1246-0803-4855-9f47-11a222d56191</t>
-  </si>
-  <si>
-    <t>relationship--a3fc8ffe-bb50-43c4-b71b-08dd56c21600</t>
-  </si>
-  <si>
-    <t>relationship--1ca267f2-3129-4113-9196-ea31c51c9622</t>
-  </si>
-  <si>
-    <t>relationship--f4f9f954-f273-493c-8f03-fee8f1fbcf3d</t>
-  </si>
-  <si>
-    <t>relationship--5ea6689e-1103-4f37-a94f-29c70fa545d1</t>
-  </si>
-  <si>
-    <t>relationship--cd68ab7b-c88d-487a-8d2a-b46ba7a8927c</t>
-  </si>
-  <si>
-    <t>relationship--77920298-0cb4-4403-af9a-73a7c9d5f133</t>
-  </si>
-  <si>
-    <t>relationship--e795f3b5-5726-46b3-a6bb-7cefad5b49ea</t>
-  </si>
-  <si>
-    <t>relationship--effbe952-fdb9-477c-af6e-ad79c6add145</t>
-  </si>
-  <si>
-    <t>relationship--5ca1671c-ed66-4460-a6a9-371c43c8e530</t>
-  </si>
-  <si>
-    <t>relationship--a347ea58-ade6-405d-9bd2-9444ca45a07a</t>
-  </si>
-  <si>
-    <t>relationship--73e503b1-35ac-46bd-86f6-3b8f66dc8d99</t>
-  </si>
-  <si>
-    <t>relationship--ab474b5b-85c1-49d1-b13c-e82136bf4245</t>
-  </si>
-  <si>
-    <t>relationship--f4b81044-3360-4745-a6a5-604428258690</t>
-  </si>
-  <si>
-    <t>relationship--bfdce7e4-bb7c-461b-b323-fb16d50c7108</t>
-  </si>
-  <si>
-    <t>relationship--a36683a2-f252-481b-85be-91a1ab0e852b</t>
-  </si>
-  <si>
-    <t>relationship--3ba47494-0ae9-437b-951e-eccdc360cb76</t>
-  </si>
-  <si>
-    <t>relationship--b65185f6-a567-4ad9-86a6-35c4aa0cd3c7</t>
-  </si>
-  <si>
-    <t>relationship--cd276be5-897a-4ee9-bf23-3ae952c8366b</t>
-  </si>
-  <si>
-    <t>relationship--31d910d6-aa75-4288-bbc0-5fe603c77c9a</t>
-  </si>
-  <si>
-    <t>relationship--c8c7d773-6860-48e0-a5a2-e8afe0a06e55</t>
-  </si>
-  <si>
-    <t>relationship--3794a50c-3cc8-4b52-8d09-55800ee7b711</t>
-  </si>
-  <si>
-    <t>relationship--7b224d20-3237-4bac-a5c1-837f4bc6a447</t>
-  </si>
-  <si>
-    <t>relationship--dc7d5a0d-96f6-4799-ac74-170996bc71d3</t>
-  </si>
-  <si>
-    <t>relationship--9d37710d-723a-4d98-aa6a-7b7103a92265</t>
-  </si>
-  <si>
-    <t>relationship--adb77168-5386-4c39-93bf-dd9a5287a28b</t>
-  </si>
-  <si>
-    <t>relationship--c625c8d0-aa45-4059-ba32-0cba7ae7fd6d</t>
-  </si>
-  <si>
-    <t>relationship--bb4d4bba-06f4-4059-b64b-a08925a2ba09</t>
-  </si>
-  <si>
-    <t>relationship--a6ac9ff7-c858-42d0-8b78-4f2f15e1e9e8</t>
-  </si>
-  <si>
-    <t>relationship--3e96f0b2-a6e4-4c35-835b-536a56534d61</t>
-  </si>
-  <si>
-    <t>relationship--1d1c8443-4a4c-4b1e-83fb-c573bcdd8609</t>
-  </si>
-  <si>
-    <t>relationship--c2467e24-aa89-4fdb-9aeb-de8cb4d60e92</t>
-  </si>
-  <si>
-    <t>relationship--1e1ef58e-60dc-4cd1-bd5d-9a1b7ffb82f5</t>
-  </si>
-  <si>
-    <t>relationship--8b3bc7f7-8f15-401c-a897-8b4f4c485fab</t>
-  </si>
-  <si>
-    <t>relationship--4ca0c5b1-e701-4ce2-8d12-8c846fbb39a6</t>
-  </si>
-  <si>
-    <t>relationship--6a6a77cb-87b1-40cc-84c6-06538b94c503</t>
-  </si>
-  <si>
-    <t>relationship--029e9bcb-3d83-44fe-856a-792de66e76ce</t>
-  </si>
-  <si>
-    <t>relationship--49d0d7bb-1bd0-411e-a6eb-d7c754d175c3</t>
-  </si>
-  <si>
-    <t>relationship--3b5ac779-c057-45f5-b6e6-bb0d17a3f5e6</t>
-  </si>
-  <si>
-    <t>relationship--d69c2709-1b3e-46b9-b153-dcdf657703cc</t>
-  </si>
-  <si>
-    <t>relationship--ccda6bf7-2d88-4373-9335-2c8437473815</t>
-  </si>
-  <si>
-    <t>relationship--7f4c14d2-03df-480a-aceb-66e6711d2976</t>
-  </si>
-  <si>
-    <t>relationship--1d1b0731-589f-4a1a-b4d7-67f1bd1bf7f0</t>
-  </si>
-  <si>
-    <t>relationship--4df2a787-fce7-4a2d-b0c6-b52205e0ac9b</t>
-  </si>
-  <si>
-    <t>relationship--c60325fe-17d1-4ebc-84c3-1749b59f1ef5</t>
-  </si>
-  <si>
-    <t>relationship--07abd7f2-4b59-4ae8-8872-ba650eb99292</t>
-  </si>
-  <si>
-    <t>relationship--fb304e21-2864-4509-8578-b38764c6aa00</t>
-  </si>
-  <si>
-    <t>relationship--3b47b21f-f45d-4fdd-b93f-7318b2958619</t>
-  </si>
-  <si>
-    <t>relationship--dcb7b4f6-a9b2-4c7b-921a-941109d148b9</t>
-  </si>
-  <si>
-    <t>relationship--bc105e57-f5b4-410b-b4e7-b053d6c8354f</t>
-  </si>
-  <si>
-    <t>relationship--da72f4e7-05a6-4697-a006-ebf7daae88b8</t>
-  </si>
-  <si>
-    <t>relationship--694af659-ddc6-4f95-9f83-e0b0e53d9f12</t>
-  </si>
-  <si>
-    <t>relationship--52b32816-0e96-4bf7-854b-1ea7f0fa5b17</t>
-  </si>
-  <si>
-    <t>relationship--5b472a98-d634-4a30-9980-4d9bcf5de1b1</t>
-  </si>
-  <si>
-    <t>relationship--f10bf7c8-2c1e-477b-947b-a36f9197dd6b</t>
-  </si>
-  <si>
-    <t>relationship--dc644e4c-114e-41da-8dca-70427b6e543c</t>
-  </si>
-  <si>
-    <t>relationship--42757dd2-4dfd-444a-866e-1dd44077393b</t>
-  </si>
-  <si>
-    <t>relationship--bf045a89-5e75-4e7f-bb4e-0106b1ee2ca3</t>
-  </si>
-  <si>
-    <t>relationship--88ec8d99-1d19-4ad9-899e-e0735817f3a3</t>
-  </si>
-  <si>
-    <t>relationship--277e3cf8-150b-4f33-b01d-99e116e67355</t>
-  </si>
-  <si>
-    <t>relationship--9b1d81a0-7dd9-4409-9a67-4fd8dd800d7d</t>
-  </si>
-  <si>
-    <t>relationship--a26b6fb9-1b45-4908-a2d5-cef3d48e1311</t>
-  </si>
-  <si>
-    <t>relationship--e90242f1-fb1b-46ee-ac12-e4ed12000b54</t>
-  </si>
-  <si>
-    <t>relationship--d80eca26-283a-4c92-97b5-c855466844d5</t>
-  </si>
-  <si>
-    <t>relationship--5da9d99c-c93d-4f93-b43d-e5cbab8838d0</t>
-  </si>
-  <si>
-    <t>relationship--7e887476-9de0-4550-9742-271d684ec662</t>
-  </si>
-  <si>
-    <t>relationship--3fa03eb5-e376-42a0-a7e3-bd88627cc549</t>
-  </si>
-  <si>
-    <t>relationship--4968eebd-22fe-4785-b045-ffe11ff5960f</t>
-  </si>
-  <si>
-    <t>relationship--b1342883-0249-4f0c-9295-835e4e344d33</t>
-  </si>
-  <si>
-    <t>relationship--d4f7f80e-0c52-4ead-a877-6952ecbdeb89</t>
-  </si>
-  <si>
-    <t>relationship--c47cf2d8-8ed2-4143-9d9a-1035a6bfd74e</t>
-  </si>
-  <si>
-    <t>relationship--4a44ab9f-4259-48e6-919b-0b309bf7d4a2</t>
-  </si>
-  <si>
-    <t>relationship--e562a8e2-3043-45e9-abd5-5fff979c8098</t>
-  </si>
-  <si>
-    <t>relationship--f7a006d7-a54c-4007-9b41-0e5a19d5f2f1</t>
-  </si>
-  <si>
-    <t>relationship--0df7ee93-4dbc-4556-8c9d-27ab0b7be332</t>
-  </si>
-  <si>
-    <t>relationship--fe6a98c0-3544-4d58-a73f-e7cb95ff7bfd</t>
-  </si>
-  <si>
-    <t>relationship--3b0e4544-935a-44dc-b52f-9e06276ed524</t>
-  </si>
-  <si>
-    <t>relationship--0b300349-3650-4cad-879d-740953d43b27</t>
-  </si>
-  <si>
-    <t>relationship--130b2f16-ed8c-4b38-9496-09070c114e0a</t>
-  </si>
-  <si>
-    <t>relationship--93c3c1a0-6654-4a44-9e51-d41d9b97318c</t>
-  </si>
-  <si>
-    <t>relationship--4a5d7189-7dbc-4839-bf0c-f8333ebcec14</t>
-  </si>
-  <si>
-    <t>relationship--27af09e6-f251-45a9-9e2b-b7bb39ac3ce6</t>
-  </si>
-  <si>
-    <t>relationship--60f58897-14af-4024-9a19-38440f2d8e05</t>
-  </si>
-  <si>
-    <t>relationship--889f3572-fbd5-4c12-90f2-8cf06668b3f4</t>
-  </si>
-  <si>
-    <t>relationship--e2b164ad-12a8-4d18-9a67-0303231353c3</t>
-  </si>
-  <si>
-    <t>relationship--3f0ec1a5-8fcd-41e6-baf4-c82ab31f459e</t>
-  </si>
-  <si>
-    <t>relationship--8c38da6e-a102-4b7e-b660-27757b7cf81f</t>
-  </si>
-  <si>
-    <t>relationship--bdb63612-62f7-4c8c-ab64-42945130d1e8</t>
-  </si>
-  <si>
-    <t>relationship--c9a29469-7d1d-490e-a924-f0a79b0c9416</t>
-  </si>
-  <si>
-    <t>relationship--765d1542-ace9-455e-92d6-2c00612ea1bf</t>
-  </si>
-  <si>
-    <t>relationship--87cf9512-34ab-4409-8f32-b417344f43b3</t>
-  </si>
-  <si>
-    <t>relationship--56197d6f-b102-4489-8901-3c57468fb17f</t>
-  </si>
-  <si>
-    <t>relationship--882bfee5-9b46-483e-87de-818d057e4d0a</t>
-  </si>
-  <si>
-    <t>relationship--e6513013-65fb-4e47-8045-2e30de2a53b0</t>
-  </si>
-  <si>
-    <t>relationship--b4788d80-1953-4277-b97e-3286edcce45b</t>
-  </si>
-  <si>
-    <t>relationship--9dd953ce-eb32-441a-999b-256acde953a0</t>
-  </si>
-  <si>
-    <t>relationship--a60a8032-8a50-496c-8d63-4bce8cd965b3</t>
-  </si>
-  <si>
-    <t>relationship--5430b0d9-9052-4e96-9d8b-b323dbbec3ad</t>
-  </si>
-  <si>
-    <t>relationship--9eca6ea4-bad5-4a91-bd5f-0e0077203913</t>
-  </si>
-  <si>
-    <t>relationship--b4978d4b-2005-4226-b084-f573af7dd0aa</t>
-  </si>
-  <si>
-    <t>relationship--672ee83d-f949-4094-b48b-79f4aaee64a3</t>
-  </si>
-  <si>
-    <t>relationship--861b31f5-218a-40a4-bb92-b7ae6cfca4bd</t>
-  </si>
-  <si>
-    <t>relationship--fd48d9f1-41fb-4690-b252-f36a07c826b9</t>
-  </si>
-  <si>
-    <t>relationship--9496ba54-26ac-4a0f-b1b3-5d5b332df3dc</t>
-  </si>
-  <si>
-    <t>relationship--77817d32-a822-45fc-a549-f2033f8a259f</t>
-  </si>
-  <si>
-    <t>relationship--689b5082-1860-4af9-94b5-a1a864174caf</t>
-  </si>
-  <si>
-    <t>relationship--bfb72f7a-7820-4ae8-91f9-c841cedcaf50</t>
-  </si>
-  <si>
-    <t>relationship--ce9ae2d9-1561-49d8-9b27-47b9ffae90aa</t>
-  </si>
-  <si>
-    <t>relationship--6c37e1ac-42c5-4dc5-9fdd-9c1db2985f02</t>
-  </si>
-  <si>
-    <t>relationship--e203f843-7152-43aa-ac53-6bc383abbde0</t>
-  </si>
-  <si>
-    <t>relationship--79f9fb53-369c-485a-b1e8-a648a4672881</t>
-  </si>
-  <si>
-    <t>relationship--cc3fa8c9-6563-4d07-8366-e3d1e9742f44</t>
-  </si>
-  <si>
-    <t>relationship--8114f1d6-a671-4ab9-8a15-12da06ce2b4c</t>
-  </si>
-  <si>
-    <t>relationship--6530ce2a-a597-4103-9004-5bf3279bf9af</t>
-  </si>
-  <si>
-    <t>relationship--b006bf6e-7885-4e63-b21c-a8b5c2c9b270</t>
-  </si>
-  <si>
-    <t>relationship--e7c40b8a-8910-4717-8d47-2f33af618e1a</t>
-  </si>
-  <si>
-    <t>relationship--0b71308c-d561-47c0-bd1f-c8d9c5b2e67a</t>
-  </si>
-  <si>
-    <t>relationship--e7e6017b-62a3-4bcc-ac91-78ab4d791032</t>
-  </si>
-  <si>
-    <t>relationship--b756d8cf-b208-4b09-9558-252a094aa457</t>
-  </si>
-  <si>
-    <t>relationship--6a00cbbd-b00f-4f22-ad9b-7b4702738962</t>
-  </si>
-  <si>
-    <t>relationship--5c440561-e38a-466e-9555-8b43b92f7d37</t>
-  </si>
-  <si>
-    <t>relationship--03745cba-1552-4c2e-b9b0-446989ce4c92</t>
-  </si>
-  <si>
-    <t>relationship--c4a26a4b-04e1-4bc0-8a52-827b3fd16d04</t>
-  </si>
-  <si>
-    <t>relationship--151837c8-e2b9-40af-90a4-90777bfeb569</t>
-  </si>
-  <si>
-    <t>relationship--562a719b-244f-4576-b3a1-e8f63570719b</t>
-  </si>
-  <si>
-    <t>relationship--61d06baa-1be9-4f29-b0d6-648689348347</t>
-  </si>
-  <si>
-    <t>relationship--3f91fa7d-fd5e-428b-b9e5-52b77c66a44b</t>
-  </si>
-  <si>
-    <t>relationship--35a1f702-f3d0-437f-b192-ab4eaf7072ec</t>
-  </si>
-  <si>
-    <t>relationship--88154d87-ee53-4f2a-bcae-443294dfd3d7</t>
-  </si>
-  <si>
-    <t>relationship--8fa6133e-2409-4086-a38e-295b3331fe1e</t>
-  </si>
-  <si>
-    <t>relationship--dae48123-e72c-457a-9b89-1d53a5ab26ed</t>
-  </si>
-  <si>
-    <t>relationship--8d9c2c90-1695-4a03-af4c-f001e9b734dc</t>
-  </si>
-  <si>
-    <t>relationship--c699b6c0-4b41-4e2f-80d6-0a19fe50ff6c</t>
-  </si>
-  <si>
-    <t>relationship--fd8bc4ef-5c0a-440b-8e4b-f7346743911c</t>
-  </si>
-  <si>
-    <t>relationship--4c184424-80e2-487f-b185-f868db6c80d4</t>
-  </si>
-  <si>
-    <t>relationship--885c19f5-029d-44f6-be78-e1d23c3d4cdf</t>
-  </si>
-  <si>
-    <t>relationship--c21abbed-ad81-4c81-b37b-3b569185c93c</t>
-  </si>
-  <si>
-    <t>relationship--7bbae35d-f3e3-4e5a-bab2-e26f88b03ff9</t>
-  </si>
-  <si>
-    <t>relationship--5be04712-bd35-4322-8a64-0f7b815bec52</t>
-  </si>
-  <si>
-    <t>relationship--1d2aa0bf-db07-411f-b63e-f4357e28ee36</t>
-  </si>
-  <si>
-    <t>relationship--393e4ecb-c528-42b2-bc46-1f4b495e97c8</t>
-  </si>
-  <si>
-    <t>relationship--ed647326-a799-42e4-bf59-60f96b1941ed</t>
-  </si>
-  <si>
-    <t>relationship--d7035e41-3d39-40bb-b1f8-1d0f1e9181fe</t>
-  </si>
-  <si>
-    <t>relationship--6419b1f9-067a-4614-9778-dbfc46da687f</t>
-  </si>
-  <si>
-    <t>relationship--380f7b6b-5d65-4348-b727-aa82d27815d0</t>
-  </si>
-  <si>
-    <t>relationship--a19e1e6c-f404-4fe1-8182-cc1e87b204f3</t>
-  </si>
-  <si>
-    <t>relationship--61dd9227-ed0e-4372-be64-8140025b5eff</t>
-  </si>
-  <si>
-    <t>relationship--d1ac60e1-3cc3-4f08-bc33-5f6bbb2c6b54</t>
-  </si>
-  <si>
-    <t>relationship--dfd93469-9cce-4692-8651-fb115933f1aa</t>
-  </si>
-  <si>
-    <t>relationship--e49ae246-29e6-4178-9470-b6c6ab526928</t>
-  </si>
-  <si>
-    <t>relationship--eec22026-5df2-4710-b6db-43ac5324d334</t>
-  </si>
-  <si>
-    <t>relationship--68dd4196-3255-4dfe-8d66-9305b96089db</t>
-  </si>
-  <si>
-    <t>relationship--05ead870-071e-40ef-b68c-11666edb81bc</t>
-  </si>
-  <si>
-    <t>relationship--b34fb22d-d5b5-4bd3-bb63-4c3523b53595</t>
-  </si>
-  <si>
-    <t>relationship--507c6601-beca-4d52-bff7-f2e48a7b5139</t>
-  </si>
-  <si>
-    <t>relationship--0379ec2f-c532-44b6-bdf4-dfbae108e651</t>
-  </si>
-  <si>
-    <t>relationship--ca06c89a-39cf-4797-8528-1e9ac6c1796f</t>
-  </si>
-  <si>
-    <t>relationship--3f35ff73-38cf-4dc3-9b71-eb659acb342a</t>
-  </si>
-  <si>
-    <t>relationship--a608d4e0-d88e-4f2c-a1a4-6ef8f4bf5513</t>
-  </si>
-  <si>
-    <t>relationship--1d5d36d4-748e-4f8c-8de5-a8e22c24bb90</t>
-  </si>
-  <si>
-    <t>relationship--0156d84c-3ab8-4de7-a67d-ac6ccef18ef4</t>
-  </si>
-  <si>
-    <t>relationship--9ad2fceb-6f19-4477-91f5-2d53ab52b824</t>
-  </si>
-  <si>
-    <t>relationship--a0d8191f-c0b7-4d30-a5a3-5a226b9e291a</t>
-  </si>
-  <si>
-    <t>relationship--123ad057-53b4-4cd7-9ec7-8b9dc58028bb</t>
-  </si>
-  <si>
-    <t>relationship--287f0a0f-8848-4412-8971-edf616559cfc</t>
-  </si>
-  <si>
-    <t>relationship--dc93ced9-0e46-44b9-9550-df5bcc710137</t>
-  </si>
-  <si>
-    <t>relationship--07485167-d7da-4a8d-afee-edd9f71e86d9</t>
-  </si>
-  <si>
-    <t>relationship--b989c0cc-da64-4a88-980e-0487c3a391df</t>
-  </si>
-  <si>
-    <t>relationship--a422e1fa-dd68-4964-8441-8a26f4c77060</t>
-  </si>
-  <si>
-    <t>relationship--76c4b983-5919-4770-ac1c-b65d6f62748e</t>
-  </si>
-  <si>
-    <t>relationship--47c69cc8-89e5-46ff-9c97-e6bf5b7365b4</t>
-  </si>
-  <si>
-    <t>relationship--c6a21ce8-0384-47ee-890f-9441d8daae83</t>
-  </si>
-  <si>
-    <t>relationship--88b11cdf-20d4-4fac-a308-42dd3855b3fe</t>
-  </si>
-  <si>
-    <t>relationship--5369f320-2551-45a0-a468-aaed1fb67b25</t>
-  </si>
-  <si>
-    <t>relationship--fb564629-2361-46f5-8b83-41c234332297</t>
-  </si>
-  <si>
-    <t>relationship--57a6fc91-0d56-4664-bf0b-8d1b8692a22c</t>
-  </si>
-  <si>
-    <t>relationship--b194d6aa-b386-40ca-86dd-6ec6931e7a2d</t>
-  </si>
-  <si>
-    <t>relationship--2c8600a4-63cd-4680-9ca0-e101928991ec</t>
-  </si>
-  <si>
-    <t>relationship--b44b10fc-fb7c-4238-b850-052f43c6b4c2</t>
-  </si>
-  <si>
-    <t>relationship--55673426-60b0-4c14-9204-e73188165b28</t>
-  </si>
-  <si>
-    <t>relationship--a5ba58a7-9082-4753-a72d-2869505f670d</t>
-  </si>
-  <si>
-    <t>relationship--f646bf62-a55d-4616-ad99-d9df181bc16f</t>
-  </si>
-  <si>
-    <t>relationship--2149d320-d5d2-451b-9346-7fa9d858dd84</t>
-  </si>
-  <si>
-    <t>relationship--4f2f8d74-770f-4250-b5bd-ae9f6eceeb2e</t>
-  </si>
-  <si>
-    <t>relationship--cf446416-e9a7-4ef6-bfdc-15a9a031360e</t>
-  </si>
-  <si>
-    <t>relationship--1441e698-9f62-4527-9ad6-097ce4f68bf8</t>
-  </si>
-  <si>
-    <t>relationship--6f50775d-cd46-48ba-a26f-31a5f857374b</t>
-  </si>
-  <si>
-    <t>relationship--eefc035c-2ad6-404e-a485-c28de920b885</t>
-  </si>
-  <si>
-    <t>relationship--2a0646ed-67da-4291-8d77-30b27297ef6c</t>
-  </si>
-  <si>
-    <t>relationship--5309f230-016e-4963-9f0a-4647f087f1ca</t>
-  </si>
-  <si>
-    <t>relationship--b4464e86-d4a4-4b0c-ba8e-b0091c28d837</t>
-  </si>
-  <si>
-    <t>relationship--46d06255-f976-4949-96ae-8dc191c08be3</t>
-  </si>
-  <si>
-    <t>relationship--abf6e3d0-332a-44a3-bb04-0037e7d6fa14</t>
-  </si>
-  <si>
-    <t>relationship--04e93ba0-d7c3-4074-a120-e6869ac24d90</t>
-  </si>
-  <si>
-    <t>relationship--cb08dc61-c06d-43e9-93d8-a52bd4bd9ce9</t>
-  </si>
-  <si>
-    <t>relationship--77d698f4-b4bb-4511-af0f-77911c182127</t>
-  </si>
-  <si>
-    <t>relationship--06f24406-847d-4dfc-b2f3-3a2584a74d78</t>
-  </si>
-  <si>
-    <t>relationship--23a96e08-7357-4834-8dfc-9f9465900cdc</t>
-  </si>
-  <si>
-    <t>relationship--072b2c8e-eea0-4fc0-8a26-3e534a134562</t>
-  </si>
-  <si>
-    <t>relationship--748adbe7-f59c-4bc0-97f4-de3ec43934c9</t>
-  </si>
-  <si>
-    <t>relationship--223dcaad-ae78-43af-86c8-5494371b1d37</t>
-  </si>
-  <si>
-    <t>relationship--54823f51-aa85-4d2f-ba24-5f50309914c7</t>
-  </si>
-  <si>
-    <t>relationship--ac746805-7a46-4ae9-8b34-a32e9a11c539</t>
-  </si>
-  <si>
-    <t>relationship--4964717a-b221-499a-927d-39dcb9db33a2</t>
-  </si>
-  <si>
-    <t>relationship--7c711dce-6dd9-45f8-8bc2-7343d77afe0f</t>
-  </si>
-  <si>
-    <t>relationship--6b10a528-82da-42f7-9cdc-1aa588fab481</t>
-  </si>
-  <si>
-    <t>relationship--bc8eb603-4feb-4413-bf43-80cb97d78378</t>
-  </si>
-  <si>
-    <t>relationship--6156c3c7-b5ba-49fd-b912-528c84e7a683</t>
-  </si>
-  <si>
-    <t>relationship--addd0ef0-894f-455c-8180-38cd60e04c37</t>
-  </si>
-  <si>
-    <t>relationship--ffc52e98-63f1-4ff9-9e6c-0ecf73c132a4</t>
-  </si>
-  <si>
-    <t>relationship--5e3dfb1e-eacc-43fe-ab72-12a4adcd0e10</t>
-  </si>
-  <si>
-    <t>relationship--b13a8a02-0a0e-461c-bb4b-4a4376ff35c6</t>
-  </si>
-  <si>
-    <t>relationship--6a268ffe-5e34-4dff-86c0-07aa08dcb5a2</t>
-  </si>
-  <si>
-    <t>relationship--be640a50-5ff4-4b10-ba98-384c9b0d55c8</t>
-  </si>
-  <si>
-    <t>relationship--7776534d-2830-47ec-a5f7-3cfce9bb3d44</t>
-  </si>
-  <si>
-    <t>relationship--374dc1bc-6679-4a55-9b31-fb16e91b7f00</t>
-  </si>
-  <si>
-    <t>relationship--c8637b07-3a35-46c8-aa81-13619be9953e</t>
-  </si>
-  <si>
-    <t>relationship--8dd4ccd1-6e48-4e5c-9b30-f06ab1d93521</t>
-  </si>
-  <si>
-    <t>relationship--5dcc9361-437b-4a59-a451-3d954258d94d</t>
-  </si>
-  <si>
-    <t>relationship--9d98aef8-2024-4ee4-84cc-07e3af7e47c5</t>
-  </si>
-  <si>
-    <t>relationship--856984be-eae4-4f32-b090-8ed806b87c1e</t>
-  </si>
-  <si>
-    <t>relationship--df3c4fca-1b31-4f57-a805-f4f74a87dfe7</t>
-  </si>
-  <si>
-    <t>relationship--014fda40-f5c3-47ed-a2ed-3b6b46c55878</t>
-  </si>
-  <si>
-    <t>relationship--f85f034d-6561-4988-abaa-ac7172a7bd76</t>
-  </si>
-  <si>
-    <t>relationship--55964349-3162-4e27-bb1e-abf01bb55215</t>
-  </si>
-  <si>
-    <t>relationship--4534db45-fe9b-4f0e-aedc-98ad60b13128</t>
-  </si>
-  <si>
-    <t>relationship--4330ffb9-d8ff-4288-ac43-6a065a313900</t>
-  </si>
-  <si>
-    <t>relationship--3d908446-973f-47fc-a39e-3789efe97ff3</t>
-  </si>
-  <si>
-    <t>relationship--232d9c6f-6ad7-4312-a2d8-c607f9ee0276</t>
-  </si>
-  <si>
-    <t>relationship--e642c95f-3e56-4c24-a977-d86cc4c20ba3</t>
-  </si>
-  <si>
-    <t>relationship--8227572b-82be-4c2c-861b-5113f97dfddd</t>
-  </si>
-  <si>
-    <t>relationship--f7a0de34-a733-435a-9ec1-62e98780f91a</t>
-  </si>
-  <si>
-    <t>relationship--06fe07f5-9a2f-47f1-b0a5-6e296fb85588</t>
-  </si>
-  <si>
-    <t>relationship--19f5ae4f-6f55-4234-8e02-b7849d67cb3e</t>
-  </si>
-  <si>
-    <t>relationship--a8c565aa-1b03-445d-ad0a-cfa9b9774625</t>
-  </si>
-  <si>
-    <t>relationship--1200f03f-0995-4007-bba8-9b9104523678</t>
-  </si>
-  <si>
-    <t>relationship--27c6c544-dbd7-447d-b13b-dd7cf18d09bd</t>
-  </si>
-  <si>
-    <t>relationship--745a6e9f-ae84-4c45-8455-dfaf312b5fdc</t>
-  </si>
-  <si>
-    <t>relationship--37839205-46ec-4e2f-8123-a85d91fe5d32</t>
-  </si>
-  <si>
-    <t>relationship--c04707e2-dee7-4657-b31b-5319724b0be3</t>
-  </si>
-  <si>
-    <t>relationship--7f12e6bd-3864-44df-9d27-9e79fd2cda83</t>
-  </si>
-  <si>
-    <t>relationship--65257f7e-4d5c-490a-a72b-c0e1abf828a7</t>
-  </si>
-  <si>
-    <t>relationship--fbf0263d-c0d7-405f-b574-c66a4956efe8</t>
-  </si>
-  <si>
-    <t>relationship--2e23a33f-3d39-41cc-befb-bbb2bec46212</t>
-  </si>
-  <si>
-    <t>relationship--115eb83d-7c72-4d69-9c7a-0a7dfb16567f</t>
-  </si>
-  <si>
-    <t>relationship--1cb5a9bc-28f5-4eaa-8c53-1ab0603b1115</t>
-  </si>
-  <si>
-    <t>relationship--c8051db6-217b-4b3c-a077-bc2246f2ca5d</t>
-  </si>
-  <si>
-    <t>relationship--69097e44-b340-41fb-b71b-a9e4bb5bdf34</t>
-  </si>
-  <si>
-    <t>relationship--da778b0c-13fe-4c8b-b58a-37a6413f985d</t>
-  </si>
-  <si>
-    <t>relationship--c6d2e80f-8b05-4297-a133-b19cc7359f40</t>
-  </si>
-  <si>
-    <t>relationship--fc016907-a6b1-4ccf-9aa3-0e5134d2efbb</t>
-  </si>
-  <si>
-    <t>relationship--303f721d-3aa6-4707-a40a-622fff9209ed</t>
-  </si>
-  <si>
-    <t>relationship--98a4a0fd-ffbd-4ae0-b54c-356cd63b6fe9</t>
-  </si>
-  <si>
-    <t>relationship--2ae8fd5a-8463-4519-b1a7-144cff5caae3</t>
-  </si>
-  <si>
-    <t>relationship--c7f93fbc-e3f5-4fc6-bd06-1d5f0ef8b534</t>
-  </si>
-  <si>
-    <t>relationship--829bbe12-1433-4ddc-86fe-a9f1576358d6</t>
-  </si>
-  <si>
-    <t>relationship--380f0ba5-40d6-4b11-8f4d-532071f0f8fc</t>
-  </si>
-  <si>
-    <t>relationship--5720eeb6-cb68-4aec-a169-61af53093498</t>
-  </si>
-  <si>
-    <t>relationship--2c53304b-a8ab-4cd6-96f9-47d007a41437</t>
-  </si>
-  <si>
-    <t>relationship--f5330dcf-6ea7-4953-86d3-afd38052cec3</t>
-  </si>
-  <si>
-    <t>relationship--4f973e78-494d-4faf-af03-628495b9e2e2</t>
-  </si>
-  <si>
-    <t>relationship--a8477547-160e-4f85-93b6-0dd8e8998c16</t>
-  </si>
-  <si>
-    <t>relationship--b1cf70e4-2ceb-44ee-b30e-ae14d097b02a</t>
-  </si>
-  <si>
-    <t>relationship--e55fd8fc-48c9-4389-9653-bb0460d9a8e6</t>
-  </si>
-  <si>
-    <t>relationship--b2f59554-4941-4365-81e1-9d9088a01b1d</t>
-  </si>
-  <si>
-    <t>relationship--ebb09495-6544-4894-98c1-d61731361695</t>
-  </si>
-  <si>
-    <t>relationship--5d027595-85a0-41f3-af88-51ea8d13445b</t>
-  </si>
-  <si>
-    <t>relationship--9ca3e2d3-e98d-42ad-a196-306d91954152</t>
-  </si>
-  <si>
-    <t>relationship--0dfe3dec-a7b5-46f6-91f7-d7f7d04cee19</t>
-  </si>
-  <si>
-    <t>relationship--44b60aea-8e56-49cc-ba63-c25d52d6b064</t>
-  </si>
-  <si>
-    <t>relationship--6922e89d-789c-4920-9971-c9e0aec8abef</t>
-  </si>
-  <si>
-    <t>relationship--643726f0-6b49-4ff0-bf27-524106570628</t>
-  </si>
-  <si>
-    <t>relationship--99750379-0991-49d2-845a-38e0534bb2b9</t>
-  </si>
-  <si>
-    <t>relationship--17af9190-ed2c-4d9c-bc94-fde195349df0</t>
-  </si>
-  <si>
-    <t>relationship--7813f1f2-b6fd-40fb-af15-dd9a2ca04a90</t>
-  </si>
-  <si>
-    <t>relationship--fecccdd6-4dba-4297-ae6b-860f0d654d51</t>
-  </si>
-  <si>
-    <t>relationship--247c1400-d20a-4f06-9958-75c299197f0d</t>
-  </si>
-  <si>
-    <t>relationship--ccc3baee-92ba-4d65-a274-591c4eca4754</t>
-  </si>
-  <si>
-    <t>relationship--c525349f-f773-4156-9f8b-9539d939dce0</t>
-  </si>
-  <si>
-    <t>relationship--5291ce1a-3273-4000-8902-06bb255bf8af</t>
-  </si>
-  <si>
-    <t>relationship--e319ff58-0abb-4c3d-a306-b795663ff85e</t>
-  </si>
-  <si>
-    <t>relationship--52f3ee40-6928-4e92-8645-10821b4fb24c</t>
-  </si>
-  <si>
-    <t>relationship--578721a1-f1b0-4860-b1b0-e6ec697710f3</t>
-  </si>
-  <si>
-    <t>relationship--157cc1c4-fb87-4900-98ac-90a0c2bee8c6</t>
-  </si>
-  <si>
-    <t>relationship--ef982e88-c329-463a-8244-7b373320d856</t>
-  </si>
-  <si>
-    <t>relationship--0ebf4f68-0ae0-48cb-b8e1-064f3cf37f14</t>
-  </si>
-  <si>
-    <t>relationship--422a69fb-b923-4fe2-b6f9-5cf222bff621</t>
-  </si>
-  <si>
-    <t>relationship--7f665ce4-c8c2-4fa5-a183-cf888b37dfad</t>
-  </si>
-  <si>
-    <t>relationship--97d8db77-03f1-4510-af5d-d57136d85cc4</t>
-  </si>
-  <si>
-    <t>relationship--66f6c6bb-f86c-4d70-98c4-a20458570037</t>
-  </si>
-  <si>
-    <t>relationship--4278dd17-e79a-4b66-991d-5b36d1301c23</t>
-  </si>
-  <si>
-    <t>relationship--cb4fc774-fa24-4943-8d13-193a0dcc00a9</t>
-  </si>
-  <si>
-    <t>relationship--83e456d4-226f-4816-ac4d-685c06c8b5d1</t>
-  </si>
-  <si>
-    <t>relationship--cf0446a2-000f-4ac1-8051-cb41f7571f94</t>
-  </si>
-  <si>
-    <t>relationship--70f0a8fc-c11f-4e8a-ab22-0b57ed0243fd</t>
-  </si>
-  <si>
-    <t>relationship--fde26adc-952e-4eae-8c32-90f8e2c289f1</t>
-  </si>
-  <si>
-    <t>relationship--ef96ae40-c63a-483c-af98-eb120db0d729</t>
-  </si>
-  <si>
-    <t>relationship--7e73fe42-7c64-47f3-98ed-490e5879d6cb</t>
-  </si>
-  <si>
-    <t>relationship--e495833b-e7fc-4a45-a3b0-088de55613ab</t>
-  </si>
-  <si>
-    <t>relationship--87b59acc-3517-4ef4-a487-ff0cb738d26b</t>
-  </si>
-  <si>
-    <t>relationship--5199a200-76f5-4226-a15c-2edff1f1dd8f</t>
-  </si>
-  <si>
-    <t>relationship--979dd474-a489-4302-820f-6b0fe99ac0b8</t>
-  </si>
-  <si>
-    <t>relationship--95be85f6-ea3f-49c7-8176-47fb2b14acc3</t>
-  </si>
-  <si>
-    <t>relationship--c5f89a37-f7ea-4fc3-8d53-44385be766c0</t>
-  </si>
-  <si>
-    <t>relationship--2460c04f-37b2-4b3b-986b-ca71811d32d2</t>
-  </si>
-  <si>
-    <t>relationship--b76c4f0c-9e86-405c-885c-2a6a1e03aacb</t>
-  </si>
-  <si>
-    <t>relationship--90d5f2c3-21ed-4495-a244-515610ebd773</t>
-  </si>
-  <si>
-    <t>relationship--04c02d46-fbe1-4ad2-9fb3-cb301cc21db0</t>
-  </si>
-  <si>
-    <t>relationship--14da342c-de4d-4fa0-9852-1822f2915a15</t>
-  </si>
-  <si>
-    <t>relationship--1a003ba2-1a44-4896-85a2-46ac6ed81310</t>
-  </si>
-  <si>
-    <t>relationship--ef90f573-128f-4d2a-8626-4d9b0a981ad1</t>
-  </si>
-  <si>
-    <t>relationship--4e429355-42b0-4de6-aa4f-6f3ebe099a86</t>
-  </si>
-  <si>
-    <t>relationship--deacdc42-71b6-4dd8-8aaf-69b66e210301</t>
-  </si>
-  <si>
-    <t>relationship--64b3a5f9-b367-4eed-81cd-808883bd7563</t>
-  </si>
-  <si>
-    <t>relationship--5beba3b0-257f-42ae-937c-76502cc6e4d6</t>
-  </si>
-  <si>
-    <t>relationship--6852c501-da52-4547-9314-82638d0cae16</t>
-  </si>
-  <si>
-    <t>relationship--d06c83c0-473d-44af-b216-94609b2ae705</t>
-  </si>
-  <si>
-    <t>relationship--38198316-4d10-46d4-8667-986f6ab7425b</t>
-  </si>
-  <si>
-    <t>relationship--80dee8f1-1b29-420d-9c15-fecf53ee3229</t>
-  </si>
-  <si>
-    <t>relationship--20d9dd2b-1d77-4b5f-b0a3-8edbdd544be6</t>
-  </si>
-  <si>
-    <t>relationship--b59a2993-5458-4be6-a1be-fc61ae3e2225</t>
-  </si>
-  <si>
-    <t>relationship--b0df84c2-ffdb-42c0-9d0a-04e4e769ff16</t>
-  </si>
-  <si>
-    <t>relationship--3db00a0a-a50a-4399-8d23-cbc942f47e7a</t>
-  </si>
-  <si>
-    <t>relationship--71d87ecd-a71b-4b1b-95a1-0b26f86e8f98</t>
-  </si>
-  <si>
-    <t>relationship--9bbeaaef-abf9-434e-b308-d523c2070af7</t>
-  </si>
-  <si>
-    <t>relationship--f68e21ae-6621-4ffc-9a90-70affdec2c77</t>
-  </si>
-  <si>
-    <t>relationship--d192470f-32da-438c-a680-713ad35a66ff</t>
-  </si>
-  <si>
-    <t>relationship--c9a4f0a0-2fb1-48db-96bb-9f4d75f5183c</t>
-  </si>
-  <si>
-    <t>relationship--d438fc28-b978-4835-a52b-9de40988fce1</t>
-  </si>
-  <si>
-    <t>relationship--c2bf44c9-7582-473c-92bf-6200c6e2b97d</t>
-  </si>
-  <si>
-    <t>relationship--6c4ab8b6-93db-4163-9f82-ef7f84d805f8</t>
-  </si>
-  <si>
-    <t>relationship--369a4d9b-8b07-4672-a7a4-bef505202f2d</t>
-  </si>
-  <si>
-    <t>relationship--be1d9a30-5d9f-48d6-94c6-4146b7a038ff</t>
-  </si>
-  <si>
-    <t>relationship--6e6c1595-7a47-4b2c-8b88-04b9af47eba6</t>
-  </si>
-  <si>
-    <t>relationship--3c95514f-4ea4-47eb-a08a-5cc3989990e3</t>
-  </si>
-  <si>
-    <t>relationship--058e246d-cf7c-4957-9fac-45022e7c46dd</t>
-  </si>
-  <si>
-    <t>relationship--59519324-c28f-47e3-a28e-6833ee4ef511</t>
-  </si>
-  <si>
-    <t>relationship--29300e50-6531-4e7e-8695-0e9aa52a44c5</t>
-  </si>
-  <si>
-    <t>relationship--eeef4c23-15df-4135-8d66-37934eedba06</t>
-  </si>
-  <si>
-    <t>relationship--747eaf17-b939-49d0-94c9-26d9e039c287</t>
-  </si>
-  <si>
-    <t>relationship--36e8d7e1-4708-44a6-bc91-8fc9d1960db7</t>
-  </si>
-  <si>
-    <t>relationship--7897de01-e8e3-439c-937f-58471ac53ad1</t>
-  </si>
-  <si>
-    <t>relationship--458e1dca-67b7-48d8-9f8d-ba4fba34172d</t>
-  </si>
-  <si>
-    <t>relationship--69db264e-cfb6-4084-8699-74a3451b8d89</t>
-  </si>
-  <si>
-    <t>relationship--f266400a-d882-49da-8cd0-94d53a8440a7</t>
-  </si>
-  <si>
-    <t>relationship--6dd81fb8-1b0f-414a-b66d-249f578281dc</t>
-  </si>
-  <si>
-    <t>relationship--dfc8a5c6-887e-4c06-a6af-96d5f0a70c71</t>
-  </si>
-  <si>
-    <t>relationship--4a66513f-b03c-404c-8229-00ed0ba5d2bb</t>
-  </si>
-  <si>
-    <t>relationship--bfa2a6bc-d95e-4a9e-bdce-eb211b1b05f0</t>
-  </si>
-  <si>
-    <t>relationship--97b5a942-0c74-4429-b75e-a5f56986e4bc</t>
-  </si>
-  <si>
-    <t>relationship--2be93575-1965-4fb8-9e27-cff22794a83c</t>
-  </si>
-  <si>
-    <t>relationship--30536913-ff45-40b4-97bc-cc83c2842a6c</t>
-  </si>
-  <si>
-    <t>relationship--7c3da382-c3aa-497e-b9e8-34b57f50a40c</t>
-  </si>
-  <si>
-    <t>relationship--9ccfb40e-3145-4cef-8c25-541a85085a7a</t>
-  </si>
-  <si>
-    <t>relationship--48d3bd6c-6d67-427a-a918-a229472348fe</t>
-  </si>
-  <si>
-    <t>relationship--aa3ffd81-87db-4dc1-acbe-7ab2b835c1da</t>
-  </si>
-  <si>
-    <t>relationship--b5aaa679-ad3f-4bb1-aeab-3f280c7fb972</t>
-  </si>
-  <si>
-    <t>relationship--975197fc-2168-4040-a841-c3cb46d1da64</t>
-  </si>
-  <si>
-    <t>relationship--c6a49cec-51e2-42e4-8944-71a297fff307</t>
-  </si>
-  <si>
-    <t>relationship--bf415a60-02ac-4937-b134-7ab28b8f509a</t>
-  </si>
-  <si>
-    <t>relationship--08409ba1-6544-46cf-82d3-ab57b733c2c0</t>
-  </si>
-  <si>
-    <t>relationship--2e9e7a4d-97ef-4b84-9422-8bd0e3408640</t>
-  </si>
-  <si>
-    <t>relationship--d888712b-f1f0-4a72-9def-9f80bf399441</t>
-  </si>
-  <si>
-    <t>relationship--6920c644-8f01-4504-bd46-0f8cb4d9c03b</t>
-  </si>
-  <si>
-    <t>relationship--8fce6d91-96be-4a36-95f0-d9129add2414</t>
-  </si>
-  <si>
-    <t>relationship--f2d26557-8399-4687-b41a-7a9d7d2d6991</t>
-  </si>
-  <si>
-    <t>relationship--7e5d14c5-eee2-4516-a591-6ab114b39616</t>
-  </si>
-  <si>
-    <t>relationship--4aedfcbf-0b21-4cc4-bbc3-5fcd7133e96b</t>
-  </si>
-  <si>
-    <t>relationship--91505aef-64b8-4c19-a36b-00572428daae</t>
-  </si>
-  <si>
-    <t>relationship--27f0c620-33ac-4941-ad34-8ad92fb951bb</t>
-  </si>
-  <si>
-    <t>relationship--12987ed8-ae41-4a2b-9119-048b0d1c2a29</t>
-  </si>
-  <si>
-    <t>relationship--8761c9a9-1bca-43d7-b73b-063e2ccb5892</t>
-  </si>
-  <si>
-    <t>relationship--9859d030-c359-4277-a7c0-f4c0dc8ebea0</t>
-  </si>
-  <si>
-    <t>relationship--c6621408-c216-4632-8830-2cb368b491b2</t>
-  </si>
-  <si>
-    <t>relationship--cb149f6a-70ff-44d6-a7a4-dc7705413b7e</t>
-  </si>
-  <si>
-    <t>relationship--ffeec6db-89d9-44b8-a2d8-03c873161126</t>
-  </si>
-  <si>
-    <t>relationship--926fc305-439f-4e90-9d7e-fe20ee9f3b42</t>
-  </si>
-  <si>
-    <t>relationship--01ca3970-7a1f-46c5-8382-cfd35f0c730e</t>
-  </si>
-  <si>
-    <t>relationship--3980e6e6-b81b-4dec-b045-4241533377f8</t>
-  </si>
-  <si>
-    <t>relationship--53f62f92-2229-4f2d-b5e2-1bae14576a8d</t>
-  </si>
-  <si>
-    <t>relationship--10d7e27d-7a6e-4ea2-becb-b09ff7f5c73b</t>
-  </si>
-  <si>
-    <t>relationship--cd8fa868-85aa-4da3-9741-8badb8968112</t>
-  </si>
-  <si>
-    <t>relationship--3c08beb3-52a0-40d1-9c57-534aedd48ebf</t>
-  </si>
-  <si>
-    <t>relationship--bb007e67-caa9-4d3d-ac1f-3d618ab1de0d</t>
-  </si>
-  <si>
-    <t>relationship--84e048ac-fa44-4dce-bd05-e7825e346f5a</t>
-  </si>
-  <si>
-    <t>relationship--328bebba-f51c-42c7-bb3b-3002b8200a7b</t>
-  </si>
-  <si>
-    <t>relationship--2c64d9ce-762f-4b0a-a028-e35551463e03</t>
-  </si>
-  <si>
-    <t>relationship--8c3d77ea-8756-400d-b154-ec811df67412</t>
-  </si>
-  <si>
-    <t>relationship--f5168c16-e698-4bb4-9f50-7debdd5a3630</t>
-  </si>
-  <si>
-    <t>relationship--533afae2-4c7e-47a9-8ba3-ed82137df35a</t>
-  </si>
-  <si>
-    <t>relationship--90ca0b3c-4c3b-4a5b-8af9-4be8770d1bc1</t>
-  </si>
-  <si>
-    <t>relationship--86f0d89f-5cfb-4aa1-89c5-ca829fb54f0f</t>
-  </si>
-  <si>
-    <t>relationship--7e401d36-2524-4677-8cfb-b91674c12d2c</t>
-  </si>
-  <si>
-    <t>relationship--c166204b-0ede-4ddc-b15f-79b040bac7c1</t>
-  </si>
-  <si>
-    <t>relationship--f11f9b9b-57c5-4847-a328-fb70b2c9538c</t>
-  </si>
-  <si>
-    <t>relationship--a9f8de35-3128-45a4-b1cb-eee7174b014b</t>
-  </si>
-  <si>
-    <t>relationship--3db39e09-580e-44b3-8524-bbedcbddbad8</t>
-  </si>
-  <si>
-    <t>relationship--473e0e90-0dd6-42a5-9db8-860333d080e7</t>
-  </si>
-  <si>
-    <t>relationship--4ed2adee-2957-48f2-b787-771ff24842cc</t>
-  </si>
-  <si>
-    <t>relationship--f9253b57-b541-4864-ae70-84fdb5a9a009</t>
-  </si>
-  <si>
-    <t>relationship--ae77458f-2e73-44af-a4fe-568ac150a084</t>
-  </si>
-  <si>
-    <t>relationship--68f8ab90-d155-4302-b323-62f169f8e2f5</t>
-  </si>
-  <si>
-    <t>relationship--4d8fe415-5ba3-4218-b152-93400c0c05c9</t>
-  </si>
-  <si>
-    <t>relationship--328b830e-5848-4d69-aa54-9b9a9d0d71bd</t>
-  </si>
-  <si>
-    <t>relationship--fe1bb675-0c5e-4443-92e1-5e6cb50b2638</t>
-  </si>
-  <si>
-    <t>relationship--852935b0-0e77-4146-a270-7209b4dc693b</t>
-  </si>
-  <si>
-    <t>relationship--aeb32c7a-6284-4a47-b399-d8e136b116e6</t>
-  </si>
-  <si>
-    <t>relationship--5538f8fc-0291-4895-be52-13f6c2a31d03</t>
-  </si>
-  <si>
-    <t>relationship--bef9e71a-f7c1-4419-a5c3-d23d0b7a621d</t>
-  </si>
-  <si>
-    <t>relationship--4d72ad95-a4af-4a8b-832d-c862c922f58e</t>
-  </si>
-  <si>
-    <t>relationship--994616e8-ab99-4e2e-865f-e85308ffbf78</t>
-  </si>
-  <si>
-    <t>relationship--229019bf-8e78-44c5-88aa-d8c0061872c8</t>
-  </si>
-  <si>
-    <t>relationship--a30dfd3f-6cc1-4757-9d3b-910225e77dee</t>
-  </si>
-  <si>
-    <t>relationship--a2282a7f-2ea9-4f73-a79e-ec48d1f5818c</t>
-  </si>
-  <si>
-    <t>relationship--1766db0b-cecf-47d3-a1a1-5b57b20aa5f8</t>
-  </si>
-  <si>
-    <t>relationship--ee97460c-7ddc-4504-b619-a0fd72e0021b</t>
-  </si>
-  <si>
-    <t>relationship--58cc72d7-9597-4352-ace7-99cfbc5bf722</t>
-  </si>
-  <si>
-    <t>relationship--2e5b2622-ab7f-47cf-a1b8-4bc7ecad202c</t>
-  </si>
-  <si>
-    <t>relationship--75adf5f2-87ce-491b-84e6-41803005c30e</t>
-  </si>
-  <si>
-    <t>relationship--f7b6576c-0180-4f1c-af20-95a63a684aaa</t>
-  </si>
-  <si>
-    <t>relationship--bfddeccc-d818-4e1b-986e-a84e6fc111f4</t>
-  </si>
-  <si>
-    <t>relationship--dc7c1483-8d89-4e6a-a8dc-a2ea9f38e025</t>
-  </si>
-  <si>
-    <t>relationship--898475e8-ebc6-40cf-9fd0-2ce5c185521c</t>
-  </si>
-  <si>
-    <t>relationship--152ba51f-eb52-4cb8-8a8c-39b5986e6f48</t>
-  </si>
-  <si>
-    <t>relationship--52e9757d-719f-45c0-9f57-a1373c929a70</t>
-  </si>
-  <si>
-    <t>relationship--b4158964-4d2d-4cfd-af14-07ad553063ca</t>
-  </si>
-  <si>
-    <t>relationship--c28addcb-3c84-4759-a937-7ef8d581a30c</t>
-  </si>
-  <si>
-    <t>relationship--600e1d1a-0904-425d-80bd-ae586e9c11c6</t>
-  </si>
-  <si>
-    <t>relationship--e8a7484f-7c4a-42c7-91f8-783be6ea95aa</t>
-  </si>
-  <si>
-    <t>relationship--4cbda5ed-2f03-4e10-8c9a-eb5979cc80aa</t>
-  </si>
-  <si>
-    <t>relationship--4f725b45-e523-44ef-b305-390164de3615</t>
-  </si>
-  <si>
-    <t>relationship--59ef994d-607d-46aa-bb29-857eb6f2b8ca</t>
-  </si>
-  <si>
-    <t>relationship--832b34e9-f5a4-47ce-b977-0f9bb63c3fcc</t>
-  </si>
-  <si>
-    <t>relationship--1ce88d63-1141-477e-9b38-931613413a6d</t>
-  </si>
-  <si>
-    <t>relationship--8f27bafb-f2d4-4470-af0f-79aca850b563</t>
-  </si>
-  <si>
-    <t>relationship--0821b1a1-15b3-414c-ab25-0c7c90c18540</t>
-  </si>
-  <si>
-    <t>relationship--96da083d-a23c-43cb-b709-92e712bce2fa</t>
-  </si>
-  <si>
-    <t>relationship--20d69c3b-be1d-4f35-a0b3-6341cdb4f3b2</t>
-  </si>
-  <si>
-    <t>relationship--64f43e2e-94d8-4e82-a9b3-394f1e06dd6d</t>
-  </si>
-  <si>
-    <t>relationship--84c4cac7-3756-409a-bf8a-5972cc3094cd</t>
-  </si>
-  <si>
-    <t>relationship--d63f16d1-1b39-4990-81b7-e03885abaf05</t>
-  </si>
-  <si>
-    <t>relationship--49c648af-fec3-4059-bf6b-9f07c4d9b1b9</t>
-  </si>
-  <si>
-    <t>relationship--e5a36c2f-adcc-4ba7-940c-5da32b713e7d</t>
-  </si>
-  <si>
-    <t>relationship--4015b538-bbcf-47d6-8495-2ecb81ef3135</t>
-  </si>
-  <si>
-    <t>relationship--78c470fa-b57b-4ec4-8462-1be58f44348f</t>
-  </si>
-  <si>
-    <t>relationship--75c2148d-7caf-44f6-9922-42576bec690f</t>
-  </si>
-  <si>
-    <t>relationship--520de64d-4c88-40d0-94ae-2857c606a373</t>
-  </si>
-  <si>
-    <t>relationship--dc6b8ca9-dfa6-4643-b9bb-3f0aff72ca24</t>
-  </si>
-  <si>
-    <t>relationship--4029f29b-f441-46ec-accd-60e98f8e60ae</t>
-  </si>
-  <si>
-    <t>relationship--74615a43-ac1f-45e5-a3d2-e3eac51c3d41</t>
-  </si>
-  <si>
-    <t>relationship--aaad3049-4e16-43d5-b00d-3f5ebd5fb04c</t>
-  </si>
-  <si>
-    <t>relationship--b7af7b9c-1e6c-428a-8387-afdab549652e</t>
-  </si>
-  <si>
-    <t>relationship--f54b229f-306f-4f88-9f8b-ac8dcd728c09</t>
-  </si>
-  <si>
-    <t>relationship--d4a1cee7-ae63-446f-9adf-e9b6e514c8d9</t>
-  </si>
-  <si>
-    <t>relationship--962d374e-49d8-4c93-8dba-c4a614dbc984</t>
-  </si>
-  <si>
-    <t>relationship--74e1ecbc-1bd7-48e9-bc0f-5d60d38a4d20</t>
-  </si>
-  <si>
-    <t>relationship--7f4db076-bf6c-43d9-bb5f-092e4ba95986</t>
-  </si>
-  <si>
-    <t>relationship--c1a4e4f5-6a73-4fed-bd14-7791771f6712</t>
-  </si>
-  <si>
-    <t>relationship--55ebdb20-8b0c-40c8-9a2f-3e1d08835cce</t>
-  </si>
-  <si>
-    <t>relationship--9d2dea45-2bd1-4b2e-8d7a-73d3a12a430e</t>
-  </si>
-  <si>
-    <t>relationship--f043b659-76a9-4b6a-b824-411010596be3</t>
-  </si>
-  <si>
-    <t>relationship--de6aebe2-a780-4a3b-a697-237b41701090</t>
-  </si>
-  <si>
-    <t>relationship--4659c792-a8f7-4e07-a1cd-82a9ea575b59</t>
-  </si>
-  <si>
-    <t>relationship--97f92d42-e04b-44fd-a24a-878f253676ca</t>
-  </si>
-  <si>
-    <t>relationship--74133ab4-4ac7-47ea-a920-924fb9a17113</t>
-  </si>
-  <si>
-    <t>relationship--2fafd992-6e0c-4a34-bcb0-bea3518108e3</t>
-  </si>
-  <si>
-    <t>relationship--a8d25bd5-9f16-44fc-88ed-156a76c85216</t>
-  </si>
-  <si>
-    <t>relationship--d8fc0f85-92c3-4b35-bba3-23fb00b34150</t>
-  </si>
-  <si>
-    <t>relationship--27c61602-1178-4ff1-99ab-6f49e5e5a21f</t>
-  </si>
-  <si>
-    <t>relationship--7363bb0c-68fb-4702-a7d7-fa42f9098c43</t>
-  </si>
-  <si>
-    <t>relationship--573b6b81-bcb9-4124-9851-57b5bd288d6d</t>
-  </si>
-  <si>
-    <t>relationship--dbf85c12-c689-4e6e-9105-2ea7a440cca2</t>
-  </si>
-  <si>
-    <t>relationship--a82659b7-c6ca-46e5-9fca-c4892d2df804</t>
-  </si>
-  <si>
-    <t>relationship--6ce11b1c-435d-4409-97c8-e39e4d4c06e7</t>
-  </si>
-  <si>
-    <t>relationship--ea06ea35-f027-45e7-9d7f-28a47a5c5c20</t>
-  </si>
-  <si>
-    <t>relationship--9d581d41-ea63-4cf1-ac6a-43efa647c556</t>
-  </si>
-  <si>
-    <t>relationship--756b275f-5c10-4751-b6ce-d58f7866edf2</t>
-  </si>
-  <si>
-    <t>relationship--2423c9bd-8308-44ab-a418-744d9ececcb1</t>
-  </si>
-  <si>
-    <t>relationship--b0eb4799-a95f-4534-97b1-ec6e43f0fc13</t>
-  </si>
-  <si>
-    <t>relationship--5d174e08-8b38-4930-a8e8-43e8dbbd654a</t>
-  </si>
-  <si>
-    <t>relationship--407b647c-a2f6-4254-9531-40e4161caa59</t>
-  </si>
-  <si>
-    <t>relationship--40a2c3a1-48a7-451e-87f4-08f7523ccdc8</t>
-  </si>
-  <si>
-    <t>relationship--c49858b7-7d2f-43b3-8ecc-8836af82b441</t>
-  </si>
-  <si>
-    <t>relationship--35cc6e24-fb14-48cc-87a6-6be33d68df85</t>
-  </si>
-  <si>
-    <t>relationship--578d5030-f47a-4d9c-9d51-f36eb2f1a6c7</t>
-  </si>
-  <si>
-    <t>relationship--94c95bcc-f95b-439b-9f18-0db1fdd0a680</t>
-  </si>
-  <si>
-    <t>relationship--5f42756f-0720-432b-a8cd-d86743a7bdb2</t>
-  </si>
-  <si>
-    <t>relationship--78e423ca-351c-409c-9fc4-68bee4c557c6</t>
-  </si>
-  <si>
-    <t>relationship--5e6374aa-e39a-41c9-b5aa-540c79e019f7</t>
-  </si>
-  <si>
-    <t>relationship--84f88caa-f439-40f6-9b9c-97398faa8f28</t>
-  </si>
-  <si>
-    <t>relationship--73e5b3c4-f741-4c88-86a8-dbe2b8969a9f</t>
-  </si>
-  <si>
-    <t>relationship--eccd5f91-d1f3-45f2-84d4-83f6eef080f9</t>
-  </si>
-  <si>
-    <t>relationship--e82060b6-9af1-406f-87d7-858c6cd3c61d</t>
-  </si>
-  <si>
-    <t>relationship--6f037053-4cfc-468a-9a7c-4554a0cd3ef3</t>
-  </si>
-  <si>
-    <t>relationship--8d84724b-aa50-4c84-850c-0abaae413772</t>
-  </si>
-  <si>
-    <t>relationship--7da2dcb7-a03b-4eba-89b2-59f4c4d65a2a</t>
-  </si>
-  <si>
-    <t>relationship--ac80003e-716a-47c1-8f05-aa12ca7ed584</t>
-  </si>
-  <si>
-    <t>relationship--a733d4c4-5666-445b-9201-30a60ecce020</t>
-  </si>
-  <si>
-    <t>relationship--c495de5d-c2e1-4c57-a959-fe45dddd0445</t>
-  </si>
-  <si>
-    <t>relationship--57725f33-3924-4850-a21e-9341c4cc014e</t>
-  </si>
-  <si>
-    <t>relationship--d4a18cd8-6d38-48ad-844d-d0f31f0f0529</t>
-  </si>
-  <si>
-    <t>relationship--51bf0925-bb22-4499-9eb1-6a614ae6ab3f</t>
-  </si>
-  <si>
-    <t>relationship--89651c38-be85-47a8-afc1-30bc1601f5a4</t>
-  </si>
-  <si>
-    <t>relationship--036d230d-877c-4deb-98fc-24ac59613ee6</t>
-  </si>
-  <si>
-    <t>relationship--c606b95d-4ec5-4ec8-aa82-1126469d12db</t>
-  </si>
-  <si>
-    <t>relationship--890ffe89-219c-4d68-9be5-03b0ba553e6a</t>
-  </si>
-  <si>
-    <t>relationship--4844f590-14d0-4fe5-9af2-2812a96ef249</t>
-  </si>
-  <si>
-    <t>relationship--11d35489-04e2-4c12-b1f2-7443031406f5</t>
-  </si>
-  <si>
-    <t>relationship--2b2eb228-6449-43a8-9d85-3e83196149d0</t>
-  </si>
-  <si>
-    <t>relationship--67a09861-6af1-4a04-a1ca-9b65f5e406a3</t>
-  </si>
-  <si>
-    <t>relationship--7251cbcf-ca88-4025-93f0-069bffc149d7</t>
-  </si>
-  <si>
-    <t>relationship--b8480c6e-3555-44e5-b672-3edbfc31241a</t>
-  </si>
-  <si>
-    <t>relationship--796757e1-c2a7-4670-b4f9-26799910eaa2</t>
-  </si>
-  <si>
-    <t>relationship--8efa44d4-d824-4868-834c-9a507d10e3d6</t>
-  </si>
-  <si>
-    <t>relationship--a4e34657-03ac-4801-b5f8-87072335310d</t>
-  </si>
-  <si>
-    <t>relationship--e30b4876-d60b-4ed0-9e9c-27d105c1ce6c</t>
-  </si>
-  <si>
-    <t>relationship--2deed8a8-8869-47a3-8d6a-607a2b055dec</t>
-  </si>
-  <si>
-    <t>relationship--9349f86e-a976-431a-9138-ae9e53e96ee0</t>
-  </si>
-  <si>
-    <t>relationship--f4ccc2ed-19f4-4cae-94c2-bbe3f207d85c</t>
-  </si>
-  <si>
-    <t>relationship--2b5787dd-0bd2-4e43-a6e6-f959f39d1acb</t>
-  </si>
-  <si>
-    <t>relationship--57065beb-9d2f-4c60-9a2c-fa961c6e48d9</t>
-  </si>
-  <si>
-    <t>relationship--06d2c06a-6f4f-4d27-82e5-8224d984525d</t>
-  </si>
-  <si>
-    <t>relationship--8ca908a6-620d-4bea-b7ec-bab44c24bea6</t>
-  </si>
-  <si>
-    <t>relationship--2f1b0d82-a607-4a8b-a071-ca9c0c86425e</t>
-  </si>
-  <si>
-    <t>relationship--d195f54a-133d-47d2-a8f1-eaaa55f1894e</t>
-  </si>
-  <si>
-    <t>relationship--67d62057-2d68-415d-9157-be8b86ee5048</t>
-  </si>
-  <si>
-    <t>relationship--f44acf97-e801-4b54-ba2f-ea3f67f3b583</t>
-  </si>
-  <si>
-    <t>relationship--279e7ba6-3c28-4584-bbee-d24a6a3e06b9</t>
-  </si>
-  <si>
-    <t>relationship--e7f1922e-2837-471e-9165-76b1a8a20ef8</t>
-  </si>
-  <si>
-    <t>relationship--91a02d9c-f828-4f69-93ce-f7a720b8fa6e</t>
-  </si>
-  <si>
-    <t>relationship--b2f38ad0-2224-4961-8a2d-1a98f60f4a64</t>
-  </si>
-  <si>
-    <t>relationship--64862ccd-dea2-469c-846f-b981ee0b105d</t>
-  </si>
-  <si>
-    <t>relationship--7823aca2-b9c8-4295-927d-b674e33be225</t>
-  </si>
-  <si>
-    <t>relationship--4ec13159-0578-406e-93c9-fecac68eb471</t>
-  </si>
-  <si>
-    <t>relationship--95544ad2-03da-47fe-b3e7-cbb77c90a687</t>
-  </si>
-  <si>
-    <t>relationship--3a664eed-abf3-468f-8ea7-0c2f56a6d797</t>
-  </si>
-  <si>
-    <t>relationship--a95870b2-df9c-4e83-8afb-288bf5a64f65</t>
-  </si>
-  <si>
-    <t>relationship--fac7f4a6-b1cf-4de8-95fd-c0572a3b49e3</t>
-  </si>
-  <si>
-    <t>relationship--634a8fb1-512a-4832-b13d-41c010932da2</t>
-  </si>
-  <si>
-    <t>relationship--504ed725-252c-49a2-8689-73512c003a43</t>
-  </si>
-  <si>
-    <t>relationship--6289257b-7a80-4ddd-99f1-cf2abd113b06</t>
-  </si>
-  <si>
-    <t>relationship--960fb835-db39-4b2c-86d0-c7568efc8c98</t>
-  </si>
-  <si>
-    <t>relationship--e846b587-1c44-4e4b-a735-f273fd1259db</t>
-  </si>
-  <si>
-    <t>relationship--86dfbe3b-c925-4dd8-951b-7e0b7023cc86</t>
-  </si>
-  <si>
-    <t>relationship--e63eb9c4-15eb-491c-866e-d30ad20f203b</t>
-  </si>
-  <si>
-    <t>relationship--a287da2c-b1f1-4f30-99a0-805cb9a711e2</t>
-  </si>
-  <si>
-    <t>relationship--b78b5df4-e2f9-4c84-8db3-49f82b02b613</t>
-  </si>
-  <si>
-    <t>relationship--d38a1a85-7935-487b-856d-dafee61523bb</t>
-  </si>
-  <si>
-    <t>relationship--efd3dc16-0b5d-45a4-b080-ee7366d1e0ab</t>
-  </si>
-  <si>
-    <t>relationship--21bc97d0-3a54-4f31-b7da-3eb6691079ce</t>
-  </si>
-  <si>
-    <t>relationship--96b7b2d3-29a8-4ad0-ac06-bb86f85c9624</t>
-  </si>
-  <si>
-    <t>relationship--6f66e358-9cc6-4991-b1c3-1bda79e978b9</t>
-  </si>
-  <si>
-    <t>relationship--7a609ccd-35e2-4ad9-9713-56aa25d8c63e</t>
-  </si>
-  <si>
-    <t>relationship--19cef2a5-a003-4cb6-8176-6f3127d1edd7</t>
-  </si>
-  <si>
-    <t>relationship--438442e6-72b6-4328-9614-bd84c18e9f37</t>
-  </si>
-  <si>
-    <t>relationship--398381aa-531c-405f-aed7-3d38dd3a237f</t>
-  </si>
-  <si>
-    <t>relationship--02eb3122-dee8-4bfc-b204-218d8b684f7a</t>
-  </si>
-  <si>
-    <t>relationship--d53bce89-a103-4d7c-8ea8-2333c6489fd6</t>
-  </si>
-  <si>
-    <t>relationship--a46628fd-fd9d-40a6-a015-c7f7be110dfb</t>
-  </si>
-  <si>
-    <t>relationship--51f3d5f4-0652-499c-80ec-45a93b0be7a5</t>
-  </si>
-  <si>
-    <t>relationship--b3f627d6-84a3-455b-bccf-7e3fa526b578</t>
-  </si>
-  <si>
-    <t>relationship--60ba7a78-9fd9-499a-a003-0cce676e699d</t>
-  </si>
-  <si>
-    <t>relationship--39739d1a-0650-4d22-8a38-7f939f45b8d8</t>
-  </si>
-  <si>
-    <t>relationship--f2d2c9d7-b46d-47e4-8fd5-742252ccd620</t>
-  </si>
-  <si>
-    <t>relationship--4153ab9f-943b-4995-943c-c14b1b339d1a</t>
-  </si>
-  <si>
-    <t>relationship--8d65f873-a4e1-4744-a9e4-ab61a7378e80</t>
-  </si>
-  <si>
-    <t>relationship--e9745134-7839-4af0-8210-bf47f45f20cc</t>
-  </si>
-  <si>
-    <t>relationship--846ac497-b1ec-4a7b-a247-8cddc509b219</t>
-  </si>
-  <si>
-    <t>relationship--9a57833c-cb56-4de0-a552-62c9f65da7a7</t>
-  </si>
-  <si>
-    <t>relationship--55c47b90-fef5-4d98-a974-2e3dba81e9f4</t>
-  </si>
-  <si>
-    <t>relationship--779b1051-442e-489d-b573-2427e75a6ec6</t>
-  </si>
-  <si>
-    <t>relationship--5134de7e-c701-4184-a01a-3d496683bf7c</t>
-  </si>
-  <si>
-    <t>relationship--c645c076-a8b7-4a94-b921-dbc3cd3e020b</t>
-  </si>
-  <si>
-    <t>relationship--d48c63a8-e715-44f4-8d8f-d6dcf924fb88</t>
-  </si>
-  <si>
-    <t>relationship--c806f5dd-16ff-48f8-8a5d-5c127f9c33af</t>
-  </si>
-  <si>
-    <t>relationship--91b5ca84-3790-43f1-94bb-8124e34bbf80</t>
-  </si>
-  <si>
-    <t>relationship--8b46fafd-0d49-4d50-afe0-86cd95871c0d</t>
-  </si>
-  <si>
-    <t>relationship--2b29244e-1ac5-4f80-828e-9aabd64d4e2d</t>
-  </si>
-  <si>
-    <t>relationship--a1ea235c-d52a-4f3d-ae88-9845dbcfc8b8</t>
-  </si>
-  <si>
-    <t>relationship--521c0b27-b0b7-4b31-a67f-f9dc575eff73</t>
-  </si>
-  <si>
-    <t>relationship--0f8eedc0-a461-476b-b8bf-57da6914a22e</t>
+    <t>relationship--579007f9-28a0-48e4-9185-c1e2d0b17ae3</t>
+  </si>
+  <si>
+    <t>relationship--cbe422cd-9fe9-4132-84f1-96be195ac993</t>
+  </si>
+  <si>
+    <t>relationship--5667cd4d-ca36-46d4-a17a-9d54006f1f5b</t>
+  </si>
+  <si>
+    <t>relationship--f281ae66-2d30-4085-b524-194af26c8459</t>
+  </si>
+  <si>
+    <t>relationship--36dcc214-651c-4657-acdf-5a62bef3ec0f</t>
+  </si>
+  <si>
+    <t>relationship--13a0e8d5-cd26-41ad-989a-1ffb8a550016</t>
+  </si>
+  <si>
+    <t>relationship--2bf4f3c6-637c-41b5-b365-73fd8f1340fa</t>
+  </si>
+  <si>
+    <t>relationship--bc31601d-18b2-4aed-90e3-208e5d49b78a</t>
+  </si>
+  <si>
+    <t>relationship--9807e38f-6ad6-447a-ae60-a64f9f343370</t>
+  </si>
+  <si>
+    <t>relationship--8a514380-8a2d-4c81-9db0-93a248171fba</t>
+  </si>
+  <si>
+    <t>relationship--b2f79bb7-979e-4ea3-86ef-eebc886aaa6b</t>
+  </si>
+  <si>
+    <t>relationship--545039f1-fa7a-4f32-9e79-7584f9399a5a</t>
+  </si>
+  <si>
+    <t>relationship--bb7c01ba-b6d1-40f6-a6d0-3e4b0cdddbef</t>
+  </si>
+  <si>
+    <t>relationship--974dffe7-2fe4-45f0-bf21-5df9f49100d0</t>
+  </si>
+  <si>
+    <t>relationship--590d5394-a905-4b57-8ea4-38e941c36875</t>
+  </si>
+  <si>
+    <t>relationship--c76b1d3c-c2e5-45d1-a417-d580c9825105</t>
+  </si>
+  <si>
+    <t>relationship--3037be7e-2186-4f85-beb4-bfc477eef251</t>
+  </si>
+  <si>
+    <t>relationship--ceeb598f-298b-4fdd-aa06-06c66f75cb93</t>
+  </si>
+  <si>
+    <t>relationship--6e2eee1c-1d01-4aa2-b34b-1ce62806dae9</t>
+  </si>
+  <si>
+    <t>relationship--c347dbcd-3768-45bb-85b5-ee75069b5731</t>
+  </si>
+  <si>
+    <t>relationship--eacab9fe-e01f-49fc-a53a-bdbdacec0a5d</t>
+  </si>
+  <si>
+    <t>relationship--0a00c5e3-fc83-48cd-8ddb-09ef4bbedfe0</t>
+  </si>
+  <si>
+    <t>relationship--0ee2ab17-a17d-488c-a01f-4cc29fa47acc</t>
+  </si>
+  <si>
+    <t>relationship--72e5cce2-bbff-48a2-b689-589ad7bde2fb</t>
+  </si>
+  <si>
+    <t>relationship--d3b4874f-ecb2-4381-9b8d-7927f05858d0</t>
+  </si>
+  <si>
+    <t>relationship--ca5afe22-bac2-4077-b67b-337995a60f43</t>
+  </si>
+  <si>
+    <t>relationship--77b67bf7-363d-4a9d-9f8b-9742086db6c6</t>
+  </si>
+  <si>
+    <t>relationship--63fe6e4d-581d-431b-8116-9e090e8a745c</t>
+  </si>
+  <si>
+    <t>relationship--94908fc4-bb5b-4683-805a-dbd8dc5e4999</t>
+  </si>
+  <si>
+    <t>relationship--d9fe5d2b-3357-4241-901b-39166dd33941</t>
+  </si>
+  <si>
+    <t>relationship--035ae41a-01e9-4155-9738-28abee46fa01</t>
+  </si>
+  <si>
+    <t>relationship--22ee9109-c21a-4017-a011-8847cb95d8af</t>
+  </si>
+  <si>
+    <t>relationship--de151bf0-ed08-4e2c-924e-d1e4fcd66047</t>
+  </si>
+  <si>
+    <t>relationship--1b8dfcb3-509e-4b06-a3eb-15219d4b259f</t>
+  </si>
+  <si>
+    <t>relationship--d9c1c0f7-5386-45dd-90f5-cdcf145f2c40</t>
+  </si>
+  <si>
+    <t>relationship--a7369f3d-8b80-46e3-bb86-52408e4d0a70</t>
+  </si>
+  <si>
+    <t>relationship--924eeef7-4ac6-4094-a9d7-36befeac2c17</t>
+  </si>
+  <si>
+    <t>relationship--4135c852-a440-4feb-a662-d639156221ad</t>
+  </si>
+  <si>
+    <t>relationship--b50f9c63-ba9d-4a49-a4f7-45d9b53d8ef0</t>
+  </si>
+  <si>
+    <t>relationship--02f7b89f-53fa-478f-a1b5-7b61d8dcbff2</t>
+  </si>
+  <si>
+    <t>relationship--64360548-9a83-41f8-90e4-d73d3eb2c33a</t>
+  </si>
+  <si>
+    <t>relationship--8283b0e0-32c7-4708-9057-d42e6598176b</t>
+  </si>
+  <si>
+    <t>relationship--c1c921d9-699e-4928-8506-67dcd2061170</t>
+  </si>
+  <si>
+    <t>relationship--f2726f56-5487-4b4f-af8a-7031b19d1d76</t>
+  </si>
+  <si>
+    <t>relationship--d84105e6-4a04-4cf4-8a2c-c4a12e5dea08</t>
+  </si>
+  <si>
+    <t>relationship--3b452af0-3666-4c28-974e-a4fb53bbf295</t>
+  </si>
+  <si>
+    <t>relationship--f8ab7e5a-e300-48c9-b77c-8e67a4d7df27</t>
+  </si>
+  <si>
+    <t>relationship--40666857-41f2-4d46-bf70-47aa0c34dcc7</t>
+  </si>
+  <si>
+    <t>relationship--771548ba-7416-4cde-95d1-c788b08aaa71</t>
+  </si>
+  <si>
+    <t>relationship--779d583e-d222-4b26-956a-1e19ac4b77e2</t>
+  </si>
+  <si>
+    <t>relationship--d82e2525-0fdd-49cb-b3f1-1f2efa99ee08</t>
+  </si>
+  <si>
+    <t>relationship--31777070-381d-45d3-b313-00646e092c07</t>
+  </si>
+  <si>
+    <t>relationship--0f4de468-fd2f-4285-9db2-740ef8555069</t>
+  </si>
+  <si>
+    <t>relationship--24ad6afb-6426-413a-a29f-38668ad6ff90</t>
+  </si>
+  <si>
+    <t>relationship--946d5ae9-8056-4e22-9cd4-417de7f38d82</t>
+  </si>
+  <si>
+    <t>relationship--2a1f9d54-b16b-46ad-a923-604adfe79e1e</t>
+  </si>
+  <si>
+    <t>relationship--9a57978d-fe99-4297-8eb2-9746f0966990</t>
+  </si>
+  <si>
+    <t>relationship--366127f5-ecfd-431d-8baa-60078e576cef</t>
+  </si>
+  <si>
+    <t>relationship--835e8e03-39f2-4a00-a970-4f85d13ecae3</t>
+  </si>
+  <si>
+    <t>relationship--8a4a0c57-9338-42e3-8d0f-f04cc7e4970f</t>
+  </si>
+  <si>
+    <t>relationship--13eee957-a48f-466d-833c-b05db7b68537</t>
+  </si>
+  <si>
+    <t>relationship--5c8531a1-d41b-4b0b-8a4e-dfae8afcfa13</t>
+  </si>
+  <si>
+    <t>relationship--823a5587-50a0-40bc-9bde-70e3c2182300</t>
+  </si>
+  <si>
+    <t>relationship--293ad61a-8091-43f2-9fdc-e1adb4c75bc9</t>
+  </si>
+  <si>
+    <t>relationship--08e3ea95-b7f8-4937-b29c-4a1672614f9c</t>
+  </si>
+  <si>
+    <t>relationship--49edb497-7c42-44fc-bb53-870ca69c42d0</t>
+  </si>
+  <si>
+    <t>relationship--2051eeb2-4f36-497b-b503-5da4e20d78a0</t>
+  </si>
+  <si>
+    <t>relationship--30d0c38d-f5e6-4c94-a312-bb0202c53235</t>
+  </si>
+  <si>
+    <t>relationship--a372bff6-e803-4af7-ba39-d0996ef7de00</t>
+  </si>
+  <si>
+    <t>relationship--16bf97f2-e1ac-451b-93db-61a5ca25cfa5</t>
+  </si>
+  <si>
+    <t>relationship--b4456713-6f1a-423c-9417-3fd9318794b5</t>
+  </si>
+  <si>
+    <t>relationship--7368aac6-f55d-45e8-bcd2-0150164725c0</t>
+  </si>
+  <si>
+    <t>relationship--8fa92939-0395-495a-a2cc-25920befafd6</t>
+  </si>
+  <si>
+    <t>relationship--7f8c1d68-a431-4053-a40c-08397553d9f8</t>
+  </si>
+  <si>
+    <t>relationship--fe830b39-4d93-4844-92e9-630d112bb1cc</t>
+  </si>
+  <si>
+    <t>relationship--ba30d8c0-0a8a-43e3-884e-9ebc68c8b18b</t>
+  </si>
+  <si>
+    <t>relationship--a9ada7e1-57e6-4aba-95c7-33f97a61382d</t>
+  </si>
+  <si>
+    <t>relationship--4e5af6b1-7d02-4647-843f-917014cbfee5</t>
+  </si>
+  <si>
+    <t>relationship--a41e87ab-e2f0-472e-8b8b-b96ee2a8dbfb</t>
+  </si>
+  <si>
+    <t>relationship--7a731bc9-9092-4523-8921-dd7a3d94426f</t>
+  </si>
+  <si>
+    <t>relationship--b2beb81b-3b22-4e86-9770-beb7bcb9e418</t>
+  </si>
+  <si>
+    <t>relationship--eba89ba0-a62f-4d7a-aac2-58639ab713f8</t>
+  </si>
+  <si>
+    <t>relationship--cd2cd507-1be3-4d9a-b9fc-fcbddeac37be</t>
+  </si>
+  <si>
+    <t>relationship--0cfbf64b-f9a8-4961-bdcc-328c9364a656</t>
+  </si>
+  <si>
+    <t>relationship--3db40fe1-6e0d-4323-8da9-f0359cfa8be7</t>
+  </si>
+  <si>
+    <t>relationship--077d87d9-6da7-4b46-9cfc-4c84e7f788af</t>
+  </si>
+  <si>
+    <t>relationship--86e9c863-5ae5-46bf-b0e4-b02eaa185bd7</t>
+  </si>
+  <si>
+    <t>relationship--434ffa6e-8e3f-42bf-8887-3b685da7afe2</t>
+  </si>
+  <si>
+    <t>relationship--61560840-331e-4982-ab6f-90edf192c51f</t>
+  </si>
+  <si>
+    <t>relationship--5ed32bcc-ffac-41fb-ade7-6baf29882120</t>
+  </si>
+  <si>
+    <t>relationship--abce58d8-6877-4dcb-a877-9e213452f4b6</t>
+  </si>
+  <si>
+    <t>relationship--0b3c0a27-bbc5-4005-ac5d-bb05a255a1fd</t>
+  </si>
+  <si>
+    <t>relationship--9f3989ee-e8dd-48ba-a582-6a1fb2c277cf</t>
+  </si>
+  <si>
+    <t>relationship--5f947b73-c283-438a-b661-e922ef128815</t>
+  </si>
+  <si>
+    <t>relationship--f2028f92-96ba-481d-a719-e43200be30eb</t>
+  </si>
+  <si>
+    <t>relationship--9b0772cb-acd9-4f8a-82b1-c429efd3c3fc</t>
+  </si>
+  <si>
+    <t>relationship--cf2a8f50-c042-4978-8ac9-040f681a0902</t>
+  </si>
+  <si>
+    <t>relationship--dd0249b1-41cf-49f2-8b39-909edba54fbb</t>
+  </si>
+  <si>
+    <t>relationship--0863f965-e8ec-4d07-86db-37554adca29b</t>
+  </si>
+  <si>
+    <t>relationship--e86d43ec-a735-4d99-ad60-b0135dbfb42f</t>
+  </si>
+  <si>
+    <t>relationship--fc6c0597-d0d4-4933-8519-4d7a7c7297f6</t>
+  </si>
+  <si>
+    <t>relationship--27d3b66b-60c5-4691-884a-af621f775026</t>
+  </si>
+  <si>
+    <t>relationship--653d9b5d-056b-4633-8ccb-46dd884fe269</t>
+  </si>
+  <si>
+    <t>relationship--5614d86d-6211-45cd-ac6c-26a97c7ed3cf</t>
+  </si>
+  <si>
+    <t>relationship--c00bd06c-4bf5-4ab2-ab25-c5d571553d0c</t>
+  </si>
+  <si>
+    <t>relationship--7201fe1e-0fea-4d3b-97bf-6355ebf82318</t>
+  </si>
+  <si>
+    <t>relationship--d1870805-3ccc-4beb-b2a4-8402f288d864</t>
+  </si>
+  <si>
+    <t>relationship--a1eee09b-bd43-43e9-b586-a6b939c06a11</t>
+  </si>
+  <si>
+    <t>relationship--c274175b-6c03-49c5-a647-607cd5b0e4d2</t>
+  </si>
+  <si>
+    <t>relationship--187b5fcd-6c5c-4c42-8d07-07adbdbecd2d</t>
+  </si>
+  <si>
+    <t>relationship--1006e39a-452b-4831-be5c-fc31a3710a4c</t>
+  </si>
+  <si>
+    <t>relationship--998fc32c-1362-4fe1-badc-2c3295a58dae</t>
+  </si>
+  <si>
+    <t>relationship--b50491d9-1ef9-4e6a-a7d8-ed3bdd53bb26</t>
+  </si>
+  <si>
+    <t>relationship--816bc3db-9456-4de8-a943-e308683f2326</t>
+  </si>
+  <si>
+    <t>relationship--7e5cb007-6d19-46d2-a049-9fb76730abfc</t>
+  </si>
+  <si>
+    <t>relationship--4b7df337-6761-4f4a-8663-ffc85abd9bd7</t>
+  </si>
+  <si>
+    <t>relationship--3e1c35b2-ac79-4f76-b026-a30f8e566a41</t>
+  </si>
+  <si>
+    <t>relationship--a849cb40-97db-4468-a725-2eb757b9285f</t>
+  </si>
+  <si>
+    <t>relationship--47ff22b7-0fad-4eaa-8f49-c7ee57b2bcf5</t>
+  </si>
+  <si>
+    <t>relationship--50db3a6a-bc86-4653-92b1-cc25f4fd3b63</t>
+  </si>
+  <si>
+    <t>relationship--8312e15d-9501-45f6-b5c7-dd40ad215dc7</t>
+  </si>
+  <si>
+    <t>relationship--0cc9ae91-2019-49d4-9ae9-74cf940ab326</t>
+  </si>
+  <si>
+    <t>relationship--62cc7c54-5c61-4755-b62b-11df9f67bc7c</t>
+  </si>
+  <si>
+    <t>relationship--9520ceeb-3ab0-40cd-9976-308b5382c604</t>
+  </si>
+  <si>
+    <t>relationship--df0590aa-456d-4dcd-b3ef-9db58fcdde4d</t>
+  </si>
+  <si>
+    <t>relationship--25875951-42bf-4bd1-8846-1e2b082462c7</t>
+  </si>
+  <si>
+    <t>relationship--363d00f2-89e0-45eb-aeff-56c3eb0b7d1b</t>
+  </si>
+  <si>
+    <t>relationship--ccc50e83-1034-4626-9fad-142e49094870</t>
+  </si>
+  <si>
+    <t>relationship--0e6f9307-ac79-4d43-90f6-e73960d6ec75</t>
+  </si>
+  <si>
+    <t>relationship--24ef7132-be8a-41ec-bacf-c64882a1171d</t>
+  </si>
+  <si>
+    <t>relationship--0cf1df00-44a9-42ec-b61d-3e10fb8c67d6</t>
+  </si>
+  <si>
+    <t>relationship--03e9274c-b7a4-42d6-8f7f-78b71e30af09</t>
+  </si>
+  <si>
+    <t>relationship--5c38fc95-7bc5-4a6a-8681-48be32c65a82</t>
+  </si>
+  <si>
+    <t>relationship--066eb77b-c6df-4d8e-8599-0beb192907e4</t>
+  </si>
+  <si>
+    <t>relationship--541a4d88-df09-4c75-92ae-356afd194692</t>
+  </si>
+  <si>
+    <t>relationship--3af6830d-8cc7-4fed-b927-108a41fd4178</t>
+  </si>
+  <si>
+    <t>relationship--57631293-2a02-4489-8c56-f583e9bc5585</t>
+  </si>
+  <si>
+    <t>relationship--862f0336-33bd-4370-8af3-d29a004f0fc8</t>
+  </si>
+  <si>
+    <t>relationship--9ec2a708-84bf-4339-afb0-0162bb4748ff</t>
+  </si>
+  <si>
+    <t>relationship--4485df60-3f40-40ca-93c4-89378405dc43</t>
+  </si>
+  <si>
+    <t>relationship--722ca219-044e-4221-a0f4-444790a937ba</t>
+  </si>
+  <si>
+    <t>relationship--0819322a-18d8-4e24-b55c-206658d07525</t>
+  </si>
+  <si>
+    <t>relationship--cfa59c71-254e-4a90-903c-fcce14903069</t>
+  </si>
+  <si>
+    <t>relationship--672d610b-b36d-4dd8-b55d-8b986db8b16c</t>
+  </si>
+  <si>
+    <t>relationship--3c9fe144-c86e-42cf-b46f-9fbac0138093</t>
+  </si>
+  <si>
+    <t>relationship--0416c3e3-00bc-44e4-88b4-e2837a311840</t>
+  </si>
+  <si>
+    <t>relationship--0e328b60-be4c-4a17-a480-68f9a95774c9</t>
+  </si>
+  <si>
+    <t>relationship--05358bf0-1b8f-4d3d-9b01-37d1e4f6b814</t>
+  </si>
+  <si>
+    <t>relationship--d8ee9123-00a9-45e8-b9ed-78eaf52fd03c</t>
+  </si>
+  <si>
+    <t>relationship--c99cdf0b-238f-4f4a-bd62-e777028d0888</t>
+  </si>
+  <si>
+    <t>relationship--eb3d94ce-42c1-4f6d-9104-149587001ee8</t>
+  </si>
+  <si>
+    <t>relationship--34fa7ae0-57e6-4802-b731-2a8397e43f5c</t>
+  </si>
+  <si>
+    <t>relationship--658426eb-6159-48b7-834a-d2cba5929840</t>
+  </si>
+  <si>
+    <t>relationship--1b8afd01-f00e-4fb9-8e53-23bf378a5743</t>
+  </si>
+  <si>
+    <t>relationship--c4b84975-0d5b-41da-8dde-a1e4752f8223</t>
+  </si>
+  <si>
+    <t>relationship--3c23657a-af00-4c00-be50-0c2211096383</t>
+  </si>
+  <si>
+    <t>relationship--34f1cc09-99b9-4b55-8a11-a27b71d36a56</t>
+  </si>
+  <si>
+    <t>relationship--2d2d4647-66d2-468f-b5fa-08a23e9f3b52</t>
+  </si>
+  <si>
+    <t>relationship--32fef7ce-3ca8-42d2-9806-8f07130dc59a</t>
+  </si>
+  <si>
+    <t>relationship--45a232f8-5767-419e-9acc-94a2592789a1</t>
+  </si>
+  <si>
+    <t>relationship--8bd14d24-f013-4648-9e45-231c66bee802</t>
+  </si>
+  <si>
+    <t>relationship--e9bd60a6-0325-45da-9bda-fd854a7ce87b</t>
+  </si>
+  <si>
+    <t>relationship--724cc625-5556-40a5-ae14-3d9de64c9a19</t>
+  </si>
+  <si>
+    <t>relationship--00da6316-6f4a-4ee9-84ab-f3bf74b840dc</t>
+  </si>
+  <si>
+    <t>relationship--37a6d563-2564-4062-8967-14950a0a6ff1</t>
+  </si>
+  <si>
+    <t>relationship--5c5eb460-e73e-4c4b-8929-2f3a55616623</t>
+  </si>
+  <si>
+    <t>relationship--41bac798-9a1a-4b92-930c-227474d4cabb</t>
+  </si>
+  <si>
+    <t>relationship--5b9787dc-aaed-4206-acb6-3135336f00dc</t>
+  </si>
+  <si>
+    <t>relationship--92e54ce9-a70b-4436-be5a-e66e682935ec</t>
+  </si>
+  <si>
+    <t>relationship--689c088d-7e07-43c6-a3a3-2059035a0956</t>
+  </si>
+  <si>
+    <t>relationship--1d4bd310-a5da-42a0-896e-ea3ccf0735ef</t>
+  </si>
+  <si>
+    <t>relationship--58b1092a-2708-4e1d-b796-7570f699b314</t>
+  </si>
+  <si>
+    <t>relationship--a700b400-cfb5-4c2d-8ac6-6d3f3a976502</t>
+  </si>
+  <si>
+    <t>relationship--463138d3-daf2-4734-b553-fcc80a9f7245</t>
+  </si>
+  <si>
+    <t>relationship--12c1d59e-77ae-4c17-bd89-4f0d0855db2b</t>
+  </si>
+  <si>
+    <t>relationship--6dd4ef8d-d116-4667-98cd-25d0b4ca2eb2</t>
+  </si>
+  <si>
+    <t>relationship--28bdfc3d-faa4-4c45-8c25-506dc03861d2</t>
+  </si>
+  <si>
+    <t>relationship--2da181d8-efdd-46a5-bc48-a7e761e7700c</t>
+  </si>
+  <si>
+    <t>relationship--30caab21-d762-4082-9483-c4e4b58c8140</t>
+  </si>
+  <si>
+    <t>relationship--edd083ea-aadc-4345-844f-5d40e476e7c8</t>
+  </si>
+  <si>
+    <t>relationship--61c6a3e1-337d-4150-8e33-062db9bf48fb</t>
+  </si>
+  <si>
+    <t>relationship--69593cf2-77f5-4528-95bc-867a7cd474a6</t>
+  </si>
+  <si>
+    <t>relationship--fe839167-b221-48ff-8478-496d40f26604</t>
+  </si>
+  <si>
+    <t>relationship--33cc973e-fa84-415a-a0b3-dc6101374315</t>
+  </si>
+  <si>
+    <t>relationship--0c8a308f-fb09-4df6-9a8b-03dc281625c8</t>
+  </si>
+  <si>
+    <t>relationship--13a0fcb0-b324-4579-a852-51d59b9cfea7</t>
+  </si>
+  <si>
+    <t>relationship--03876e2e-c730-426e-9cf7-5c2d2eacfd12</t>
+  </si>
+  <si>
+    <t>relationship--ac403c59-fdb2-451d-82d5-b227f3fb004e</t>
+  </si>
+  <si>
+    <t>relationship--17501bfb-76d5-452a-a5b7-bb40a2734033</t>
+  </si>
+  <si>
+    <t>relationship--3751fcb4-a779-4bd1-8b91-b4d03da77810</t>
+  </si>
+  <si>
+    <t>relationship--db0bfcda-eb29-4562-aca0-c098711d0d07</t>
+  </si>
+  <si>
+    <t>relationship--092d1143-9f0d-4f94-b49b-b4a78e22aa1f</t>
+  </si>
+  <si>
+    <t>relationship--ff4a5303-2db3-49ae-a53f-7c2dffb9e6ee</t>
+  </si>
+  <si>
+    <t>relationship--2291dd05-1ba6-427c-8f66-f483409905d3</t>
+  </si>
+  <si>
+    <t>relationship--bdf81bef-d89b-49f8-a818-e7348ead0e7d</t>
+  </si>
+  <si>
+    <t>relationship--c0a0ed7b-7375-475c-967c-9635560013b7</t>
+  </si>
+  <si>
+    <t>relationship--35f20b51-ebde-4f96-b4f6-4612f3bceea5</t>
+  </si>
+  <si>
+    <t>relationship--b5c01c41-b1bd-403f-9c86-ee33d9233bb8</t>
+  </si>
+  <si>
+    <t>relationship--9bc2a9d1-da58-403d-98c8-6b56bfd51523</t>
+  </si>
+  <si>
+    <t>relationship--e9b6b440-e6ef-4112-91b7-a10e828f215f</t>
+  </si>
+  <si>
+    <t>relationship--d13278fb-2254-49ef-b205-01e887848910</t>
+  </si>
+  <si>
+    <t>relationship--5efc8b32-1b60-4fad-ae02-e340941487af</t>
+  </si>
+  <si>
+    <t>relationship--2511d69d-6f60-4597-8c57-c435f01cb56c</t>
+  </si>
+  <si>
+    <t>relationship--34272f39-5284-4cd8-aed4-3ac4b7afe9c0</t>
+  </si>
+  <si>
+    <t>relationship--78c44437-c23b-44e3-9b0a-dea9d31afab3</t>
+  </si>
+  <si>
+    <t>relationship--86e8bc77-6840-43e1-9b08-388dd6ce4a71</t>
+  </si>
+  <si>
+    <t>relationship--95a7d566-0538-4e17-b03f-d840ac5a6485</t>
+  </si>
+  <si>
+    <t>relationship--e08df791-6312-4452-a037-50b1c552eae6</t>
+  </si>
+  <si>
+    <t>relationship--ce048198-374c-4f04-8fc5-58aa78334838</t>
+  </si>
+  <si>
+    <t>relationship--ed1b3558-fa7e-4b78-94a6-ede294e5982b</t>
+  </si>
+  <si>
+    <t>relationship--fdb52f1a-9fce-4466-9113-080a43b19d24</t>
+  </si>
+  <si>
+    <t>relationship--a45d91e8-042e-4dde-8bf0-57d321efd381</t>
+  </si>
+  <si>
+    <t>relationship--4c063840-371e-41c6-8f16-15c3bb3b6a07</t>
+  </si>
+  <si>
+    <t>relationship--01302958-accb-41b5-bd1c-cad6bc07a1d6</t>
+  </si>
+  <si>
+    <t>relationship--1e280e04-acc2-4d3a-ad9c-8e779be2623f</t>
+  </si>
+  <si>
+    <t>relationship--68148d92-85e1-47a8-86ad-88953aad0f77</t>
+  </si>
+  <si>
+    <t>relationship--313f6ee5-9364-48f9-839d-edf4e6d25f2a</t>
+  </si>
+  <si>
+    <t>relationship--fb779776-e9f6-45e3-9cb8-c9e509c3e8a7</t>
+  </si>
+  <si>
+    <t>relationship--47e73f6e-a733-46f1-a09b-51f4a0c2574a</t>
+  </si>
+  <si>
+    <t>relationship--d48b2f17-752e-4ef0-85ca-8c5626fe5832</t>
+  </si>
+  <si>
+    <t>relationship--55b721b2-6229-4de6-9655-32647d86e186</t>
+  </si>
+  <si>
+    <t>relationship--e7753b65-5fcf-453a-9139-c1d9028cf696</t>
+  </si>
+  <si>
+    <t>relationship--5f7f0d17-361f-4a98-b1bd-0122c4d69f1d</t>
+  </si>
+  <si>
+    <t>relationship--2e1b7d0a-bc28-4539-92dd-ebfc2bb2a6fc</t>
+  </si>
+  <si>
+    <t>relationship--14628952-a9d9-4da9-a5e2-c807bebc2dbc</t>
+  </si>
+  <si>
+    <t>relationship--9708078b-3306-4693-bf99-43999bd18b3a</t>
+  </si>
+  <si>
+    <t>relationship--ac66737c-9eeb-4d82-a7ef-b0a31bba3e60</t>
+  </si>
+  <si>
+    <t>relationship--e68e8a70-ae5d-4374-9f08-1313f12c0795</t>
+  </si>
+  <si>
+    <t>relationship--f8ea8127-0143-4136-9355-f0672cc93626</t>
+  </si>
+  <si>
+    <t>relationship--9c139044-ce9e-491c-95e2-00ba93a1b5db</t>
+  </si>
+  <si>
+    <t>relationship--a74f7c11-3bc0-48bf-973f-f38cd1531a2e</t>
+  </si>
+  <si>
+    <t>relationship--7d492b91-2741-42d1-a14b-5c68ef16cdde</t>
+  </si>
+  <si>
+    <t>relationship--2e21705c-7535-43ea-971e-ae1c720f97f0</t>
+  </si>
+  <si>
+    <t>relationship--6012c812-46fa-4441-a18e-caca14be105e</t>
+  </si>
+  <si>
+    <t>relationship--7276f7e3-19cc-4f36-b52a-df9b09039d86</t>
+  </si>
+  <si>
+    <t>relationship--38b9b77e-9ac6-4123-ad64-7ee44572da1b</t>
+  </si>
+  <si>
+    <t>relationship--8ab8f626-ae23-4007-bb32-dc128a13c452</t>
+  </si>
+  <si>
+    <t>relationship--a3705dfd-d211-4b6c-b8de-a60b61232ccf</t>
+  </si>
+  <si>
+    <t>relationship--176d7e94-acc7-4510-ab33-fc50ec2eb016</t>
+  </si>
+  <si>
+    <t>relationship--72911605-8706-44a8-9133-cc55f61fbe01</t>
+  </si>
+  <si>
+    <t>relationship--3cecfb1c-8f09-451d-9727-99f8f2060f9a</t>
+  </si>
+  <si>
+    <t>relationship--889bdd3d-7042-4b09-9b8a-2c1063492550</t>
+  </si>
+  <si>
+    <t>relationship--93820292-0d07-4e8a-a732-af6f7fac18f3</t>
+  </si>
+  <si>
+    <t>relationship--d63962bf-f3fd-4159-986d-fb404f8e5c4f</t>
+  </si>
+  <si>
+    <t>relationship--8b4d20df-6e8d-48ed-ad71-b0b73b855a56</t>
+  </si>
+  <si>
+    <t>relationship--9b06ea4e-c75e-41ad-9ba0-b8050f79c4c9</t>
+  </si>
+  <si>
+    <t>relationship--304d883a-85fd-4eb0-8c79-a70babe9fa54</t>
+  </si>
+  <si>
+    <t>relationship--f2124474-a45e-4d8c-b9c3-a4485991a23e</t>
+  </si>
+  <si>
+    <t>relationship--f90a7c85-e4de-457e-b281-b8945307db07</t>
+  </si>
+  <si>
+    <t>relationship--1658c08e-93b2-490d-b21e-2dddf38e2b5c</t>
+  </si>
+  <si>
+    <t>relationship--f3fded44-1a57-418f-b6ae-29b4dbd1bc91</t>
+  </si>
+  <si>
+    <t>relationship--3f971d8b-a5a0-4f8f-b42d-a325cd802149</t>
+  </si>
+  <si>
+    <t>relationship--f45ed62a-12e3-466e-84ea-56ee39b45fe3</t>
+  </si>
+  <si>
+    <t>relationship--acab761b-d19f-4216-a982-e4e9fee04109</t>
+  </si>
+  <si>
+    <t>relationship--bd2a142c-0144-4d20-8e3d-b73ace1abff6</t>
+  </si>
+  <si>
+    <t>relationship--263060ab-6afa-4efa-8121-56ca8c19dea3</t>
+  </si>
+  <si>
+    <t>relationship--18b4ed3f-7d9c-457a-ba75-9b36acdf1b39</t>
+  </si>
+  <si>
+    <t>relationship--4bb0977b-3d05-4362-aeea-cc150865bd4b</t>
+  </si>
+  <si>
+    <t>relationship--9732d9c4-866e-4ec3-acdf-9116f0bd3293</t>
+  </si>
+  <si>
+    <t>relationship--f5e63ee5-77e5-4992-833d-257e32e5ce3e</t>
+  </si>
+  <si>
+    <t>relationship--49d946ff-1e6b-4bf2-a9f1-a9e54213b6ba</t>
+  </si>
+  <si>
+    <t>relationship--3df7af44-b568-4a7c-adf5-95885e794a2f</t>
+  </si>
+  <si>
+    <t>relationship--9e5fe4f7-cd1e-4703-bea2-829fef05d626</t>
+  </si>
+  <si>
+    <t>relationship--14bade66-db15-4761-9e73-2928a3a3891e</t>
+  </si>
+  <si>
+    <t>relationship--2acac976-88b9-4fc7-a0bd-4d03a5f3a9bf</t>
+  </si>
+  <si>
+    <t>relationship--4c3795cc-a1e9-45d1-9a1e-bbf2cde64a15</t>
+  </si>
+  <si>
+    <t>relationship--fe565642-eab5-4ff9-91e1-cea181876211</t>
+  </si>
+  <si>
+    <t>relationship--6278e5d4-ab06-4def-bece-6991bf4b857b</t>
+  </si>
+  <si>
+    <t>relationship--8ae29663-1f05-422d-ba3c-0337760daf4d</t>
+  </si>
+  <si>
+    <t>relationship--7ac36b6b-a053-4b5f-8160-03f2709d8434</t>
+  </si>
+  <si>
+    <t>relationship--33b4f3d5-4d6e-421f-a932-e2ffa44fc7a9</t>
+  </si>
+  <si>
+    <t>relationship--95d794f0-5dc8-4362-b0ff-7ed3dc1eeabd</t>
+  </si>
+  <si>
+    <t>relationship--fbf7379e-6953-413c-8932-a51888aac57e</t>
+  </si>
+  <si>
+    <t>relationship--16390e3a-f86b-4725-907f-991e84d3e0fe</t>
+  </si>
+  <si>
+    <t>relationship--c3d4eae6-f0ec-4700-91e4-270a1b5c6f38</t>
+  </si>
+  <si>
+    <t>relationship--742cbbdd-94d7-4072-9a8b-ecafc56604db</t>
+  </si>
+  <si>
+    <t>relationship--2828cfca-5ceb-4c5a-bb2f-8ffc611954fc</t>
+  </si>
+  <si>
+    <t>relationship--cb6aa417-c3bf-41e3-9e44-209705207413</t>
+  </si>
+  <si>
+    <t>relationship--9f99304a-1059-47a4-bbdf-1f76b23b8ac2</t>
+  </si>
+  <si>
+    <t>relationship--2346dccd-238f-46e8-9aba-6341e3783eda</t>
+  </si>
+  <si>
+    <t>relationship--3138c704-adf0-4cad-8d6a-ad204687d4df</t>
+  </si>
+  <si>
+    <t>relationship--0880242b-9689-482e-9459-4ebd56320f4e</t>
+  </si>
+  <si>
+    <t>relationship--9417f950-d2a7-4417-9c05-6fe57828917e</t>
+  </si>
+  <si>
+    <t>relationship--a2b54231-6b5c-40b3-a417-074b60b3b9e2</t>
+  </si>
+  <si>
+    <t>relationship--23735a53-068a-4d2a-9476-7857dd7e1b74</t>
+  </si>
+  <si>
+    <t>relationship--161fe2ca-c2dc-4d21-a9b0-95935f7d1a52</t>
+  </si>
+  <si>
+    <t>relationship--2e3ad4d6-4817-44d6-a810-1f698a978be1</t>
+  </si>
+  <si>
+    <t>relationship--15f996d2-eaeb-4d08-a6d3-775e6a2f8fbc</t>
+  </si>
+  <si>
+    <t>relationship--04fb06f2-36c2-42da-ba70-c29842d9f3a8</t>
+  </si>
+  <si>
+    <t>relationship--d36f4e6e-728d-4a94-bf5f-9656edeea1da</t>
+  </si>
+  <si>
+    <t>relationship--d15c118c-55a7-4935-aeef-0806723fc244</t>
+  </si>
+  <si>
+    <t>relationship--1fd62ded-faf1-40f6-9a80-8936866af763</t>
+  </si>
+  <si>
+    <t>relationship--2d8b27f2-c98c-4b39-88f4-5b574cb9b16e</t>
+  </si>
+  <si>
+    <t>relationship--c5079e4d-1e54-477a-8e87-858564de885c</t>
+  </si>
+  <si>
+    <t>relationship--0b7931ad-13c9-4e31-bb22-89a1b3b5c3d8</t>
+  </si>
+  <si>
+    <t>relationship--3e43cceb-804e-4e9f-9eb9-980ceea91b04</t>
+  </si>
+  <si>
+    <t>relationship--ba91c710-f339-4c01-a363-be7e7bbf27f3</t>
+  </si>
+  <si>
+    <t>relationship--aac5ca0c-b5f4-4d56-afe6-efa851eef9d5</t>
+  </si>
+  <si>
+    <t>relationship--3237f077-a7a4-4db3-bcc0-8dd58cdf8f28</t>
+  </si>
+  <si>
+    <t>relationship--0612d69c-356a-433b-b2be-0041a7ea6311</t>
+  </si>
+  <si>
+    <t>relationship--736d6234-a45a-4b13-8d65-9d78531f8c15</t>
+  </si>
+  <si>
+    <t>relationship--4a4c98b5-4eb3-4f7b-9472-10828dfa027a</t>
+  </si>
+  <si>
+    <t>relationship--e89ed10a-5ac2-4324-a479-c757c443c9f2</t>
+  </si>
+  <si>
+    <t>relationship--a1ce28ab-391c-4839-864d-65981ace7e50</t>
+  </si>
+  <si>
+    <t>relationship--81f9f1de-ff42-4716-b8ae-58db05eb14e9</t>
+  </si>
+  <si>
+    <t>relationship--5a4845b2-82b0-4319-a7df-3ec49cd4caa1</t>
+  </si>
+  <si>
+    <t>relationship--aba5c12c-37dd-4141-988c-c40248ab20e4</t>
+  </si>
+  <si>
+    <t>relationship--9532b2f2-fe57-4003-81c0-ced8230649a0</t>
+  </si>
+  <si>
+    <t>relationship--9e2bd625-9c8a-491b-88af-fa56bef0cb01</t>
+  </si>
+  <si>
+    <t>relationship--a9e9f64b-4279-4970-b5a6-a888ab472781</t>
+  </si>
+  <si>
+    <t>relationship--7ef9f9d7-6b11-4527-931d-4be1859b8455</t>
+  </si>
+  <si>
+    <t>relationship--95e3cb37-74b2-4501-9ea7-56692dc24879</t>
+  </si>
+  <si>
+    <t>relationship--ac49cbf5-277a-474b-8b5a-db00c63fa9e2</t>
+  </si>
+  <si>
+    <t>relationship--248c0613-5d29-4b5a-b780-9d3faba8e10b</t>
+  </si>
+  <si>
+    <t>relationship--9a059b65-1ded-4470-b2f6-42747e77ba68</t>
+  </si>
+  <si>
+    <t>relationship--b3c79ef3-3d27-463c-9284-93bdb89ba863</t>
+  </si>
+  <si>
+    <t>relationship--dda52d9b-48f7-437a-bf7f-8d1431a370bf</t>
+  </si>
+  <si>
+    <t>relationship--ab8b6530-fe93-49bc-abaf-b6f11504f098</t>
+  </si>
+  <si>
+    <t>relationship--c53182a4-e78b-4543-affd-b08ddd57606a</t>
+  </si>
+  <si>
+    <t>relationship--1adbac6f-5b26-41e7-8629-024177c49d43</t>
+  </si>
+  <si>
+    <t>relationship--5bbd8003-05ff-4bff-bdb6-f3e7069a9d56</t>
+  </si>
+  <si>
+    <t>relationship--1860e0ed-660b-4853-9ff9-acf4008a1c60</t>
+  </si>
+  <si>
+    <t>relationship--0f626ab6-b22c-43cc-a529-427f27d4cd4a</t>
+  </si>
+  <si>
+    <t>relationship--b121753a-fe68-4d5c-a739-da48fca417e4</t>
+  </si>
+  <si>
+    <t>relationship--7ce06181-38d2-41b8-a75f-79d0e7ec6bae</t>
+  </si>
+  <si>
+    <t>relationship--783a6d7a-1c0e-4d55-84fe-375b495a73ef</t>
+  </si>
+  <si>
+    <t>relationship--91896033-1306-4164-ad3c-f7c9af44a58b</t>
+  </si>
+  <si>
+    <t>relationship--5e4917f1-5bd5-4bfc-a170-040e70d2f3c1</t>
+  </si>
+  <si>
+    <t>relationship--7990f3bc-8d0a-42cd-acaf-0bb0cb647a90</t>
+  </si>
+  <si>
+    <t>relationship--bfc9348a-9983-430a-8931-b7e35613d7b2</t>
+  </si>
+  <si>
+    <t>relationship--b9f40bc8-8e9f-473f-9d66-672b653721f9</t>
+  </si>
+  <si>
+    <t>relationship--0848b07e-1b83-4ee0-82e2-d8f1e17ee99a</t>
+  </si>
+  <si>
+    <t>relationship--d7eafec2-7c5e-4a6e-ad62-d713cc14b414</t>
+  </si>
+  <si>
+    <t>relationship--84602b4a-38d6-48e6-9d35-7e4275415071</t>
+  </si>
+  <si>
+    <t>relationship--617026e5-fd9d-49ea-a9d1-a84d87f652f0</t>
+  </si>
+  <si>
+    <t>relationship--69b45d78-b769-4614-b1e1-58942289ffe1</t>
+  </si>
+  <si>
+    <t>relationship--beecf6d7-36fe-43f7-a1da-7315c042bd10</t>
+  </si>
+  <si>
+    <t>relationship--74af7e90-dd63-418a-b257-84f0e3aee0dc</t>
+  </si>
+  <si>
+    <t>relationship--41dbbfbb-bb93-4e80-9a3d-4f84a36e5826</t>
+  </si>
+  <si>
+    <t>relationship--4962e2ed-68d1-4488-86de-3a303a238a2b</t>
+  </si>
+  <si>
+    <t>relationship--6647a361-ee08-4d1c-9707-c5313ef988a8</t>
+  </si>
+  <si>
+    <t>relationship--afaad920-53d7-45fe-b133-cb0ed1b0d297</t>
+  </si>
+  <si>
+    <t>relationship--733568b7-95ed-47e0-a741-ccf995cdf001</t>
+  </si>
+  <si>
+    <t>relationship--ac8da5f2-078f-4051-a6ab-82ef4221043a</t>
+  </si>
+  <si>
+    <t>relationship--52a05cca-efba-4875-8158-74fc9db94cbc</t>
+  </si>
+  <si>
+    <t>relationship--a62fe462-c0fd-45ea-bd02-b7ae576b0a77</t>
+  </si>
+  <si>
+    <t>relationship--71253b77-8675-46fb-b8d7-4fbbf8f381ab</t>
+  </si>
+  <si>
+    <t>relationship--e2bbc820-11de-4385-9f33-39aed660e08e</t>
+  </si>
+  <si>
+    <t>relationship--de9f3fc1-16dd-424d-98e0-7ce81ed92ce3</t>
+  </si>
+  <si>
+    <t>relationship--c554de6a-4ca1-4258-9c30-de58c01f848e</t>
+  </si>
+  <si>
+    <t>relationship--88bb3243-d057-4c18-902e-4135bf1045fc</t>
+  </si>
+  <si>
+    <t>relationship--d55af97a-39e5-47a7-8f40-7c20c61e8654</t>
+  </si>
+  <si>
+    <t>relationship--62b71848-b849-4080-911f-aba18b3b6a1c</t>
+  </si>
+  <si>
+    <t>relationship--8410eca9-cfe9-4cb2-bc0b-34794e3a1dc1</t>
+  </si>
+  <si>
+    <t>relationship--15401ffc-3093-40be-9f11-825cc9e3484e</t>
+  </si>
+  <si>
+    <t>relationship--2a84694e-0961-4bb8-b770-22dd2420c4af</t>
+  </si>
+  <si>
+    <t>relationship--2cfb2ee2-2574-453e-bb71-d1330a8c310f</t>
+  </si>
+  <si>
+    <t>relationship--09190a94-3902-4948-94cf-f1859831afec</t>
+  </si>
+  <si>
+    <t>relationship--265d1479-d38b-4859-b41b-d3240b6ab7aa</t>
+  </si>
+  <si>
+    <t>relationship--ff33a5bc-6d82-452d-937b-ec9c08cdc50b</t>
+  </si>
+  <si>
+    <t>relationship--803e9bbf-161a-4e5e-9731-a3dea5f24369</t>
+  </si>
+  <si>
+    <t>relationship--e4d6e73a-af5a-4d83-b335-2e083045ce97</t>
+  </si>
+  <si>
+    <t>relationship--1d17f76d-5b3d-4615-adab-9aba717c3f50</t>
+  </si>
+  <si>
+    <t>relationship--5d161d88-7f5e-4e40-9601-7425c8fad16d</t>
+  </si>
+  <si>
+    <t>relationship--8debb06e-d43e-4e19-bf07-4a870ec0fb66</t>
+  </si>
+  <si>
+    <t>relationship--ad8449b4-ef75-4f64-a179-6c16292e769a</t>
+  </si>
+  <si>
+    <t>relationship--4a10a6c1-b091-4a62-b86d-39236c9798a0</t>
+  </si>
+  <si>
+    <t>relationship--35b3910e-ed22-4888-bfc5-f349e0bb22c1</t>
+  </si>
+  <si>
+    <t>relationship--09310efa-0ebb-4cef-be5c-0c04372cbab4</t>
+  </si>
+  <si>
+    <t>relationship--a0cab5c2-6d75-4c7e-a1d1-9104e6f4d382</t>
+  </si>
+  <si>
+    <t>relationship--c67f914b-7aee-4b52-80be-14ff0de19509</t>
+  </si>
+  <si>
+    <t>relationship--2c7ea63d-f8ce-4f79-a51b-aee5da46d382</t>
+  </si>
+  <si>
+    <t>relationship--9ba73000-425c-4eef-8d23-0eddd5fbe5b8</t>
+  </si>
+  <si>
+    <t>relationship--b97c6c8f-4556-4f0c-b727-b7c1ee3bbc29</t>
+  </si>
+  <si>
+    <t>relationship--f7bb10ae-1dd7-4d5d-9c54-78bf99b976d6</t>
+  </si>
+  <si>
+    <t>relationship--5552c579-ca7a-4a01-b8b3-3ca980cba14b</t>
+  </si>
+  <si>
+    <t>relationship--156e8d02-57d9-4d23-b134-3a2ca6eadf60</t>
+  </si>
+  <si>
+    <t>relationship--d96da0bc-fbf6-411f-8bc3-2ca02f16725c</t>
+  </si>
+  <si>
+    <t>relationship--bed818e0-76ce-4506-bc5f-a8a1ec1a295d</t>
+  </si>
+  <si>
+    <t>relationship--3f5df155-5aae-44da-9af9-1a226d03e6ab</t>
+  </si>
+  <si>
+    <t>relationship--e5728e9c-6648-4dc0-b6ec-78774623accc</t>
+  </si>
+  <si>
+    <t>relationship--4ab76bec-c8cf-4c6e-a539-0ada2cfeb687</t>
+  </si>
+  <si>
+    <t>relationship--5d8f1aa8-f58f-4286-b678-6fe780d8ef89</t>
+  </si>
+  <si>
+    <t>relationship--37225940-e78f-463d-aae7-9c295d1690a5</t>
+  </si>
+  <si>
+    <t>relationship--c232b6ce-e4e3-492a-8ae7-cc0cfe0ae42b</t>
+  </si>
+  <si>
+    <t>relationship--0fdcd987-9d89-452a-bf7f-845555e8c2b8</t>
+  </si>
+  <si>
+    <t>relationship--46189e0b-5bb5-4884-a2a2-6252bd84b2ca</t>
+  </si>
+  <si>
+    <t>relationship--986f87b8-7ad8-489a-9938-b1068257ebe0</t>
+  </si>
+  <si>
+    <t>relationship--03375ddd-96af-4bf3-a288-92a3be6af9b4</t>
+  </si>
+  <si>
+    <t>relationship--d2d2421b-0ea8-427e-9d70-f0506dc0c64d</t>
+  </si>
+  <si>
+    <t>relationship--a0226ea2-b120-4749-b341-18b2a3de7dd0</t>
+  </si>
+  <si>
+    <t>relationship--84ab087d-7457-42f3-898d-5fee54bd0483</t>
+  </si>
+  <si>
+    <t>relationship--c7c9485c-39ed-4fba-a7ad-beb89b7cf56f</t>
+  </si>
+  <si>
+    <t>relationship--239d7608-34a5-4835-b7f7-c02ac2a9a6af</t>
+  </si>
+  <si>
+    <t>relationship--f287ba30-6aed-42b3-b3bc-5bee0294e476</t>
+  </si>
+  <si>
+    <t>relationship--fb3b5767-aec3-481e-95b4-b71c2ef6de96</t>
+  </si>
+  <si>
+    <t>relationship--501812d7-1650-4734-a274-3ef98476cd55</t>
+  </si>
+  <si>
+    <t>relationship--b0444f41-3c81-4a1a-b481-3f49ec4a4e31</t>
+  </si>
+  <si>
+    <t>relationship--b80cabe7-6934-4b3a-9b89-02bef7d6c618</t>
+  </si>
+  <si>
+    <t>relationship--f5dc9fa0-9614-4a88-9e07-f45255c10932</t>
+  </si>
+  <si>
+    <t>relationship--0c1ef22b-d183-4824-b170-bffcec8a57ee</t>
+  </si>
+  <si>
+    <t>relationship--45203285-e86a-4b6b-bb9e-7405a51a3c34</t>
+  </si>
+  <si>
+    <t>relationship--c02c8bfd-f9a6-4d25-b9bc-fee664d7846d</t>
+  </si>
+  <si>
+    <t>relationship--526d32f2-6608-473d-96a9-0128fd8c4d65</t>
+  </si>
+  <si>
+    <t>relationship--707b76d4-6b45-4def-a530-fba1a7697323</t>
+  </si>
+  <si>
+    <t>relationship--af67535f-654c-476d-933a-70b357f7ad7d</t>
+  </si>
+  <si>
+    <t>relationship--70c92e60-aa83-4abd-9f0f-9a07452090a8</t>
+  </si>
+  <si>
+    <t>relationship--34b4188e-a222-419b-a8a7-87dc5979b184</t>
+  </si>
+  <si>
+    <t>relationship--ba6bcb7f-a2c3-4a1e-a231-847c8c3c25af</t>
+  </si>
+  <si>
+    <t>relationship--ec5aefef-ed6b-4569-9562-52bc2218958f</t>
+  </si>
+  <si>
+    <t>relationship--8333d52c-373c-4705-8b6a-fc8f60f4acb9</t>
+  </si>
+  <si>
+    <t>relationship--2b10ba2c-3e5c-4493-90a9-6a4969709943</t>
+  </si>
+  <si>
+    <t>relationship--d6588f70-b2c0-4f7b-a7de-4234a7d3d393</t>
+  </si>
+  <si>
+    <t>relationship--c8608ea5-5c2e-4d1f-af4e-a403e58a1ddc</t>
+  </si>
+  <si>
+    <t>relationship--3362b6b6-9539-44fb-bbb1-77ca62463972</t>
+  </si>
+  <si>
+    <t>relationship--86f9b1d0-343f-4d2a-b067-baeaa1a5e2ae</t>
+  </si>
+  <si>
+    <t>relationship--ee4218f6-1ce4-4b3d-8d0f-c35d633fa5fd</t>
+  </si>
+  <si>
+    <t>relationship--5e65b072-02c9-4fd1-927e-fe73a3b9c3cc</t>
+  </si>
+  <si>
+    <t>relationship--43f4cbac-131e-477f-ba40-a48a4f09bae7</t>
+  </si>
+  <si>
+    <t>relationship--1703c07c-db59-4561-9aef-0e98c02b9770</t>
+  </si>
+  <si>
+    <t>relationship--d4963880-dd41-4212-afa4-2fdd2806447b</t>
+  </si>
+  <si>
+    <t>relationship--ff8a2389-f5dc-4ca6-ab72-fa4f2934be66</t>
+  </si>
+  <si>
+    <t>relationship--b289c407-48a4-4c20-acde-4fc18f0793aa</t>
+  </si>
+  <si>
+    <t>relationship--8e516f24-9475-40a8-bf4d-e32d3ab3b0f8</t>
+  </si>
+  <si>
+    <t>relationship--a783f428-93f7-4d30-8b8c-3cea3af59dbd</t>
+  </si>
+  <si>
+    <t>relationship--510e5f0c-f40b-4613-b116-7905ed679254</t>
+  </si>
+  <si>
+    <t>relationship--5ee050bb-caa5-4027-8c86-d89457143b70</t>
+  </si>
+  <si>
+    <t>relationship--570688c9-d884-4a11-8a88-dce68ac57c6d</t>
+  </si>
+  <si>
+    <t>relationship--038d1bfe-28b7-44c2-a6a0-ee5e025aedc0</t>
+  </si>
+  <si>
+    <t>relationship--ef099864-160b-40b4-a485-abae77993da8</t>
+  </si>
+  <si>
+    <t>relationship--8d18a790-bb6d-4123-b992-bff8839edc74</t>
+  </si>
+  <si>
+    <t>relationship--dcd721b8-0e41-47d5-b197-ced965eef40c</t>
+  </si>
+  <si>
+    <t>relationship--a467f8b9-78d7-4bad-acfb-978800a868c6</t>
+  </si>
+  <si>
+    <t>relationship--1cce5d0a-384f-407f-8829-0a81968155ce</t>
+  </si>
+  <si>
+    <t>relationship--f1d13d8d-c7fb-43ea-a060-1a5a1a177c2f</t>
+  </si>
+  <si>
+    <t>relationship--ea2ebc72-d18a-448b-9b13-7823bf2b0020</t>
+  </si>
+  <si>
+    <t>relationship--4324d530-438a-4a08-a4a5-450f34b19740</t>
+  </si>
+  <si>
+    <t>relationship--d7aa4588-8ac3-4532-af96-1a85eb79795f</t>
+  </si>
+  <si>
+    <t>relationship--790bc734-b044-4365-ae92-81e0d489b7f1</t>
+  </si>
+  <si>
+    <t>relationship--88c49f62-bbc9-4dbb-b171-f40ca7468289</t>
+  </si>
+  <si>
+    <t>relationship--1d0432ae-0659-41ba-a845-4d858ffe37e2</t>
+  </si>
+  <si>
+    <t>relationship--05dd34a2-9957-4e86-9534-e400d6dcf24a</t>
+  </si>
+  <si>
+    <t>relationship--676bcf81-589f-48d4-852f-44a7687fd5bb</t>
+  </si>
+  <si>
+    <t>relationship--ad47e557-908d-4ff3-b767-9809667070b2</t>
+  </si>
+  <si>
+    <t>relationship--c7f696be-a1d0-434e-8c6e-45c6cb26d255</t>
+  </si>
+  <si>
+    <t>relationship--29e04dd7-5a43-408b-a8ff-8c8b3516666e</t>
+  </si>
+  <si>
+    <t>relationship--53885f25-29da-4650-a3ab-c780b8b681ed</t>
+  </si>
+  <si>
+    <t>relationship--5522fb34-89d3-4d94-8943-19a95cfd80a8</t>
+  </si>
+  <si>
+    <t>relationship--00054969-0bcd-410a-a089-d1c4f48f4ced</t>
+  </si>
+  <si>
+    <t>relationship--fa66eb5a-75ee-432c-b536-d6b2f38b929b</t>
+  </si>
+  <si>
+    <t>relationship--fac1d288-ae4a-4c88-833f-854bed4c2fff</t>
+  </si>
+  <si>
+    <t>relationship--44d2840b-fe2f-45d6-b326-c73f8e8f0f1c</t>
+  </si>
+  <si>
+    <t>relationship--2daf3b19-b9bf-4d3b-87cb-a316e35f4e23</t>
+  </si>
+  <si>
+    <t>relationship--445ef799-5441-4780-858a-d669d25d61a5</t>
+  </si>
+  <si>
+    <t>relationship--cc8ed1d5-ac37-4c4c-8144-10b4803716d5</t>
+  </si>
+  <si>
+    <t>relationship--3a8fd0f8-288e-4644-9df2-8b8fa0a7d324</t>
+  </si>
+  <si>
+    <t>relationship--e2f78c0c-cfd5-43b5-9b1d-61dfe130674d</t>
+  </si>
+  <si>
+    <t>relationship--c38ab01c-8556-430e-8eb6-9fbcf10e0dd9</t>
+  </si>
+  <si>
+    <t>relationship--6494ae06-a2ca-46ef-9b80-3595bbb7393c</t>
+  </si>
+  <si>
+    <t>relationship--aa3904df-e13b-43ea-a06e-d284ba324f6e</t>
+  </si>
+  <si>
+    <t>relationship--424767de-ec68-4018-91b1-880c745a3d5a</t>
+  </si>
+  <si>
+    <t>relationship--cfbd9282-fdc2-4d1c-8035-fac2e924d447</t>
+  </si>
+  <si>
+    <t>relationship--cb07b69c-2cc8-4e90-9658-3995beba2394</t>
+  </si>
+  <si>
+    <t>relationship--48b3fccb-7a56-44f2-a4b3-45eb812e2726</t>
+  </si>
+  <si>
+    <t>relationship--2094783b-721a-411d-a142-06bfb458e71a</t>
+  </si>
+  <si>
+    <t>relationship--6f26e46d-aea8-4f6a-8a13-b598f88d16d9</t>
+  </si>
+  <si>
+    <t>relationship--ec759562-bbd9-4b75-a7b6-79108da59569</t>
+  </si>
+  <si>
+    <t>relationship--d3d29946-55b5-4e56-bb77-4817111ed284</t>
+  </si>
+  <si>
+    <t>relationship--823dadbb-4af3-46e8-af9d-b39b17ca84d5</t>
+  </si>
+  <si>
+    <t>relationship--88e28cf4-e804-47bd-99b3-ddcb8497b4a4</t>
+  </si>
+  <si>
+    <t>relationship--876f4555-3d08-4bfd-8a9d-73479599d3d6</t>
+  </si>
+  <si>
+    <t>relationship--a7ec7934-e4f4-4026-b71f-7990ecb296b7</t>
+  </si>
+  <si>
+    <t>relationship--487de349-615b-48ad-80d7-b95236eecc02</t>
+  </si>
+  <si>
+    <t>relationship--13995ae8-f441-41b5-9724-aab410eaa87f</t>
+  </si>
+  <si>
+    <t>relationship--afd12d83-7475-4510-8c3f-72e983b88113</t>
+  </si>
+  <si>
+    <t>relationship--11a8a1e0-ece3-43f9-8821-02e803bda225</t>
+  </si>
+  <si>
+    <t>relationship--55a46f0e-5aae-462d-80a2-1fee0880dcef</t>
+  </si>
+  <si>
+    <t>relationship--ea520e3e-d699-477c-8969-2c6d6e3d36d4</t>
+  </si>
+  <si>
+    <t>relationship--9b9aae58-6a65-4e11-a5ec-e9510321fea1</t>
+  </si>
+  <si>
+    <t>relationship--b063931d-c06e-4f16-9cfc-b0dddb3e3c43</t>
+  </si>
+  <si>
+    <t>relationship--db2c8d09-3e56-4685-ab16-f063526b19b2</t>
+  </si>
+  <si>
+    <t>relationship--a8e4b3d5-dc03-4f52-8f65-1ee2fa2f0162</t>
+  </si>
+  <si>
+    <t>relationship--707512ad-77bd-4472-ba56-13352a5d0859</t>
+  </si>
+  <si>
+    <t>relationship--85a3d8fe-68d5-41cf-86ae-d20bab16132b</t>
+  </si>
+  <si>
+    <t>relationship--6cff1afe-2cb8-4db9-840b-01edf39d52bc</t>
+  </si>
+  <si>
+    <t>relationship--db76e378-fc70-4c63-97ca-2aabe1818f45</t>
+  </si>
+  <si>
+    <t>relationship--f3f1dcd0-5834-4149-9583-df73aabde910</t>
+  </si>
+  <si>
+    <t>relationship--3c5f7264-7249-466b-b2ff-1aab1cfcf7a8</t>
+  </si>
+  <si>
+    <t>relationship--10b8424a-5a18-48f7-8460-9b56f02c64a9</t>
+  </si>
+  <si>
+    <t>relationship--420bac05-ec0c-457e-b10d-05709ed00508</t>
+  </si>
+  <si>
+    <t>relationship--e4a1859d-56db-473f-8f3a-01d1ecff9865</t>
+  </si>
+  <si>
+    <t>relationship--6f10115c-4687-4bb1-ad80-a8286e8d7ea1</t>
+  </si>
+  <si>
+    <t>relationship--af89ecff-ebd0-48b1-a999-cf7e090359f5</t>
+  </si>
+  <si>
+    <t>relationship--900f0776-6af6-4e52-9d40-407a14a1b10b</t>
+  </si>
+  <si>
+    <t>relationship--ad5911ae-9931-4303-917c-8bf0af554ba2</t>
+  </si>
+  <si>
+    <t>relationship--27fe1e23-9e8e-4e9a-867c-e971f5b27938</t>
+  </si>
+  <si>
+    <t>relationship--cbb50fab-7e8e-4d6c-86d5-832106d6b535</t>
+  </si>
+  <si>
+    <t>relationship--67460a1f-ba46-4ccd-b625-bd6f2659da8a</t>
+  </si>
+  <si>
+    <t>relationship--c79370be-6bfa-4f46-b747-87900992f20c</t>
+  </si>
+  <si>
+    <t>relationship--66de0818-b1aa-4fdf-8b59-41657de9a959</t>
+  </si>
+  <si>
+    <t>relationship--6c62bd91-cec9-43e4-96c0-7de19a976626</t>
+  </si>
+  <si>
+    <t>relationship--10b316d6-a09c-4d60-988f-646e42467869</t>
+  </si>
+  <si>
+    <t>relationship--6e328eb1-08b5-4e49-975c-94c709bd409b</t>
+  </si>
+  <si>
+    <t>relationship--3406d69f-e0ac-4f8e-87a4-6dff7e804f99</t>
+  </si>
+  <si>
+    <t>relationship--269c07e7-e785-4fbe-9b44-37915c651501</t>
+  </si>
+  <si>
+    <t>relationship--f6705a7b-13a9-46b0-bcdb-4e1d69b9d930</t>
+  </si>
+  <si>
+    <t>relationship--232b88a1-d90d-4d5e-8167-da7b7c35c1e3</t>
+  </si>
+  <si>
+    <t>relationship--2cb4cae9-3ff4-4d54-8779-eabc3825c303</t>
+  </si>
+  <si>
+    <t>relationship--2a8ee6fa-55f4-4ad6-9954-df7b9cd95e87</t>
+  </si>
+  <si>
+    <t>relationship--c6724897-4f7a-486a-9976-c1e916d1539d</t>
+  </si>
+  <si>
+    <t>relationship--9eec828d-aff9-4828-856a-ad89e8adc4be</t>
+  </si>
+  <si>
+    <t>relationship--0679e913-f222-4d1f-9a96-6fd772a674ba</t>
+  </si>
+  <si>
+    <t>relationship--c51a31a2-b9e1-4b98-bc26-f590dad3dd7e</t>
+  </si>
+  <si>
+    <t>relationship--0be151f9-7e48-4fd1-b215-5c05f2729c36</t>
+  </si>
+  <si>
+    <t>relationship--61a209ed-7f03-488e-ad53-53aefd2e9ebb</t>
+  </si>
+  <si>
+    <t>relationship--ead62c20-6c77-4fd3-949e-c9a6954be6e7</t>
+  </si>
+  <si>
+    <t>relationship--3dcb1927-c157-4cc5-a204-237cc422e526</t>
+  </si>
+  <si>
+    <t>relationship--f5e5f729-f586-4c58-a2ac-9121ffe6abda</t>
+  </si>
+  <si>
+    <t>relationship--dbe7fab1-5ef3-491d-a1e7-a8c0a701c0aa</t>
+  </si>
+  <si>
+    <t>relationship--e73af7f5-6e5f-49a9-8ed3-d13e0868880d</t>
+  </si>
+  <si>
+    <t>relationship--e20bd310-d4bc-4df3-bfb3-a9836ddfb310</t>
+  </si>
+  <si>
+    <t>relationship--10158e66-8cd1-4b8c-86b9-f88759d46427</t>
+  </si>
+  <si>
+    <t>relationship--d1cb891e-1cad-4db4-8bc7-f62fdabf433e</t>
+  </si>
+  <si>
+    <t>relationship--baf7aa9e-6e05-43a1-b972-90441df19a3e</t>
+  </si>
+  <si>
+    <t>relationship--ec58d906-6864-4068-89bb-bebe7ae99785</t>
+  </si>
+  <si>
+    <t>relationship--d298e28d-250f-4cd0-a856-b89e5ce7b88d</t>
+  </si>
+  <si>
+    <t>relationship--c269fe15-c5be-4823-a518-f9fc55959bc6</t>
+  </si>
+  <si>
+    <t>relationship--50050696-12a8-4fa3-a415-53b8b82dea85</t>
+  </si>
+  <si>
+    <t>relationship--874d162e-2c50-4199-b6a4-39079e1afd2c</t>
+  </si>
+  <si>
+    <t>relationship--f4a5485f-8491-422f-8796-eb43f662ef04</t>
+  </si>
+  <si>
+    <t>relationship--70afaa59-d579-4c48-a4f7-e5f655976d8e</t>
+  </si>
+  <si>
+    <t>relationship--a423a829-7a8d-45da-b736-9a04cf98b61a</t>
+  </si>
+  <si>
+    <t>relationship--70bbeb57-4b3c-4fab-adc1-1dc6198e13b4</t>
+  </si>
+  <si>
+    <t>relationship--0a67dac3-b381-434b-abb7-ef513e09f6cf</t>
+  </si>
+  <si>
+    <t>relationship--4f678204-fcd8-4267-9153-9a4371987f30</t>
+  </si>
+  <si>
+    <t>relationship--ef486430-74c7-4fe2-b673-5fc558d8a341</t>
+  </si>
+  <si>
+    <t>relationship--33b362c3-ef66-4952-a0ed-0dedcc6fb7ff</t>
+  </si>
+  <si>
+    <t>relationship--b792f9e3-9b9c-4536-a89f-174effa04791</t>
+  </si>
+  <si>
+    <t>relationship--8f35ece3-fb19-421a-9f69-555f1050e821</t>
+  </si>
+  <si>
+    <t>relationship--f7a42814-cfdc-4ee8-b3aa-f621d054d2bd</t>
+  </si>
+  <si>
+    <t>relationship--6d5ec928-0460-4088-bf4d-a84766632043</t>
+  </si>
+  <si>
+    <t>relationship--2577f486-51c5-4c4f-bc31-c358edfae31d</t>
+  </si>
+  <si>
+    <t>relationship--957dac06-84ad-428b-95bf-66a508e5d916</t>
+  </si>
+  <si>
+    <t>relationship--6533395a-88f1-4ea2-b736-36c326d771a9</t>
+  </si>
+  <si>
+    <t>relationship--57f29431-847a-43e0-b7e6-1a431a2058e8</t>
+  </si>
+  <si>
+    <t>relationship--e4a98f6c-89c4-440c-b379-ab19a0b17e01</t>
+  </si>
+  <si>
+    <t>relationship--00ab4613-70a8-4939-9c07-372c0bc9860c</t>
+  </si>
+  <si>
+    <t>relationship--cc04b3b3-67ae-44e0-9436-7ff30af33bf7</t>
+  </si>
+  <si>
+    <t>relationship--c1eaee30-f633-4217-bd44-8d15f9d8c065</t>
+  </si>
+  <si>
+    <t>relationship--077a5af9-f296-4f30-967a-ab5cd4faf152</t>
+  </si>
+  <si>
+    <t>relationship--7e59d2ea-b884-41f7-92fd-edc063f147c8</t>
+  </si>
+  <si>
+    <t>relationship--ed7fbb91-8764-4af0-8a62-052e4e6d95d4</t>
+  </si>
+  <si>
+    <t>relationship--cb1bd2c3-a763-4fd2-8c8d-29ca5b1c6ff7</t>
+  </si>
+  <si>
+    <t>relationship--383f4b08-21e5-4e95-a92a-190a74bec975</t>
+  </si>
+  <si>
+    <t>relationship--b8487f86-404d-4580-bb96-4bf795ba066b</t>
+  </si>
+  <si>
+    <t>relationship--52d1bb56-b482-4ba3-8323-d423f21a8c6e</t>
+  </si>
+  <si>
+    <t>relationship--55236e8d-545e-4952-a518-32d267b79248</t>
+  </si>
+  <si>
+    <t>relationship--630137a1-fab5-4996-b489-94b760c08587</t>
+  </si>
+  <si>
+    <t>relationship--8c718d39-0585-4e91-a06f-d9366b81648b</t>
+  </si>
+  <si>
+    <t>relationship--7d415e7b-01a9-478e-9e71-65687ae5091a</t>
+  </si>
+  <si>
+    <t>relationship--aac45e98-80d3-4f9b-bee1-28f0397d63c5</t>
+  </si>
+  <si>
+    <t>relationship--2435cd1e-cd99-425b-832c-7d629f6ee15a</t>
+  </si>
+  <si>
+    <t>relationship--dd956bb0-b061-4a33-8b45-ce09ae518653</t>
+  </si>
+  <si>
+    <t>relationship--b9968c17-292b-4890-aac2-73f7458b4efc</t>
+  </si>
+  <si>
+    <t>relationship--d8c5dfde-2fa6-4075-a4ee-14afcf5356db</t>
+  </si>
+  <si>
+    <t>relationship--ee02a592-fd90-451d-90d5-d2c8d4467ecc</t>
+  </si>
+  <si>
+    <t>relationship--8e295d63-6597-43da-9840-66b7e6ca81b7</t>
+  </si>
+  <si>
+    <t>relationship--92a21bbe-ad5f-4baf-91b0-734d79c01d80</t>
+  </si>
+  <si>
+    <t>relationship--46b0d5ce-0d5c-45b9-9803-2ae4190d0c4c</t>
+  </si>
+  <si>
+    <t>relationship--805a683c-6989-4638-a65d-bcbc3764742a</t>
+  </si>
+  <si>
+    <t>relationship--7e36c1c8-aeb0-4f4f-84ea-86db8d462300</t>
+  </si>
+  <si>
+    <t>relationship--160f57d0-2863-43a6-bfa1-267076ca1d6a</t>
+  </si>
+  <si>
+    <t>relationship--367f3fa8-0c9c-4a10-94a5-5d72b06f96b7</t>
+  </si>
+  <si>
+    <t>relationship--0ec2c2c7-802b-40c0-8428-c963a8e4f90c</t>
+  </si>
+  <si>
+    <t>relationship--e71cbf0d-3d7b-4dbd-ac52-cc1a5866aad4</t>
+  </si>
+  <si>
+    <t>relationship--d852a84f-3c45-4ef2-8fd1-13a3c224137f</t>
+  </si>
+  <si>
+    <t>relationship--878c28e1-7169-459c-91a4-3ed447223d70</t>
+  </si>
+  <si>
+    <t>relationship--81b6bc77-c102-4a05-a579-5e89bd13cc12</t>
+  </si>
+  <si>
+    <t>relationship--77ffef49-fa37-4d05-b1a4-1d7751f79ee4</t>
+  </si>
+  <si>
+    <t>relationship--577e0dbe-1ef5-4fd2-a187-44324ce4a72e</t>
+  </si>
+  <si>
+    <t>relationship--b500e8e8-9847-4766-8f94-34b72b6689c8</t>
+  </si>
+  <si>
+    <t>relationship--29b1511e-eca2-451c-90c5-d4a2b3b608e7</t>
+  </si>
+  <si>
+    <t>relationship--c7fbd8ed-a720-4bec-bd85-41cbe4cdc22f</t>
+  </si>
+  <si>
+    <t>relationship--c74ac39e-968c-46f0-9d68-0c89efe7d6d7</t>
+  </si>
+  <si>
+    <t>relationship--ed809171-4923-43da-a9ad-138283fb7eaf</t>
+  </si>
+  <si>
+    <t>relationship--d6a739e6-c1dd-4cd3-a692-753d5edfcafa</t>
+  </si>
+  <si>
+    <t>relationship--89dd3e0e-2239-4e0c-8cb6-8861b76e0d3c</t>
+  </si>
+  <si>
+    <t>relationship--70f3bbdf-9325-4013-8c73-4f02cb19a47f</t>
+  </si>
+  <si>
+    <t>relationship--0d3ee557-dd08-4c96-baa0-b81cb941cf3e</t>
+  </si>
+  <si>
+    <t>relationship--9591863f-3471-44ae-8a35-1bc56d3a62c1</t>
+  </si>
+  <si>
+    <t>relationship--6f169388-5ee6-4848-805b-165b3fa47dff</t>
+  </si>
+  <si>
+    <t>relationship--33b65c8d-6b41-4163-b2d3-1666c37a9032</t>
+  </si>
+  <si>
+    <t>relationship--f4df1e00-8a91-4b71-b675-25d60bad6a98</t>
+  </si>
+  <si>
+    <t>relationship--24d503a3-8f4f-4244-ad19-1b222b59e7ef</t>
+  </si>
+  <si>
+    <t>relationship--2b63bdcf-a516-4ee3-b148-08bdd7a7cb9d</t>
+  </si>
+  <si>
+    <t>relationship--c0d66f67-d5fc-4718-87b7-13907602bba3</t>
+  </si>
+  <si>
+    <t>relationship--e67e91a0-480a-4ef4-8eeb-81989eadf823</t>
+  </si>
+  <si>
+    <t>relationship--cf7e2563-1bd6-49b2-b95d-70e7b2d5ef86</t>
+  </si>
+  <si>
+    <t>relationship--3519f430-e040-4aee-951d-4527c6545b36</t>
+  </si>
+  <si>
+    <t>relationship--76186630-c101-4f9d-a1ff-6aec5709b600</t>
+  </si>
+  <si>
+    <t>relationship--85357ec1-3dc2-4f90-854e-433509aab018</t>
+  </si>
+  <si>
+    <t>relationship--20780665-a60b-4f7f-971f-5184a072cefc</t>
+  </si>
+  <si>
+    <t>relationship--8b9d3fc3-1e2e-4ca0-ac96-0153a479d186</t>
+  </si>
+  <si>
+    <t>relationship--a74f2cd1-670a-4c86-9add-59a4fda87cbf</t>
+  </si>
+  <si>
+    <t>relationship--295d93e4-0fd4-401e-9b07-610d743be347</t>
+  </si>
+  <si>
+    <t>relationship--8770ccbf-0457-469f-b0eb-bf0fc740dd31</t>
+  </si>
+  <si>
+    <t>relationship--6780bd12-6e75-4185-b1a9-6ea68e82f9a5</t>
+  </si>
+  <si>
+    <t>relationship--363dd54a-6b6c-4d29-b12b-7633f127ae4f</t>
+  </si>
+  <si>
+    <t>relationship--c6fae978-de61-436a-b541-b9ccb8b8ddea</t>
+  </si>
+  <si>
+    <t>relationship--87e4a348-08b9-4ba3-aeed-4e125c080132</t>
+  </si>
+  <si>
+    <t>relationship--515541a7-6128-4a36-bad8-b4a99b8d1f25</t>
+  </si>
+  <si>
+    <t>relationship--627f7ec5-e07a-4a9e-a179-f56072219e23</t>
+  </si>
+  <si>
+    <t>relationship--9950a4bf-9fc5-48aa-8149-a7cc237741b6</t>
+  </si>
+  <si>
+    <t>relationship--47d76080-8a63-4b2b-a690-ecdd1ac8a447</t>
+  </si>
+  <si>
+    <t>relationship--52320481-114d-4984-ae7c-159c0ade1951</t>
+  </si>
+  <si>
+    <t>relationship--b962befb-5ce9-4090-a7ae-d21e5213b24e</t>
+  </si>
+  <si>
+    <t>relationship--98d9c5dd-04c8-41f6-b66b-72031418daa8</t>
+  </si>
+  <si>
+    <t>relationship--b3145501-4aef-4bd4-a84b-56abc85bf491</t>
+  </si>
+  <si>
+    <t>relationship--94c95dc2-8858-4f49-8ece-3ec79609c4c4</t>
+  </si>
+  <si>
+    <t>relationship--75e0cd78-c4ab-4ad1-b1b1-dfad9c2d7b41</t>
+  </si>
+  <si>
+    <t>relationship--1e3e92b7-4def-4664-b9c7-3fab81304d41</t>
+  </si>
+  <si>
+    <t>relationship--a69c6c2e-b12f-47cc-8e0e-db22bccf842d</t>
+  </si>
+  <si>
+    <t>relationship--cf5f23ba-6c2b-402c-9fe3-ae75fa116ee2</t>
+  </si>
+  <si>
+    <t>relationship--f90aefa2-2a8d-4e22-b012-96035822427f</t>
+  </si>
+  <si>
+    <t>relationship--7b93a63c-7ddb-46ed-b1f5-689c84b6dd44</t>
+  </si>
+  <si>
+    <t>relationship--3ab348ce-8d96-4260-bf68-9c2abbeb728e</t>
+  </si>
+  <si>
+    <t>relationship--13bce4b8-606b-4b06-b217-1513ec54251a</t>
+  </si>
+  <si>
+    <t>relationship--ee1770df-945f-4564-9553-b1d84f490dcd</t>
+  </si>
+  <si>
+    <t>relationship--8bc54604-c986-43f2-a701-b12592389a95</t>
+  </si>
+  <si>
+    <t>relationship--653bfee4-8148-4228-b9ad-a0dd9f6fb024</t>
+  </si>
+  <si>
+    <t>relationship--8c5d41d1-9fc6-4849-a964-d4d4cd88d808</t>
+  </si>
+  <si>
+    <t>relationship--5be4de54-a976-41cf-9a3e-801a66dd4ab0</t>
+  </si>
+  <si>
+    <t>relationship--f005b199-111a-4b05-aefa-24a35febc482</t>
+  </si>
+  <si>
+    <t>relationship--0dbf3ce6-19bd-478e-adf9-32c6e80ed0ea</t>
+  </si>
+  <si>
+    <t>relationship--c208739a-827c-4d0e-bf28-61b916f15cfe</t>
+  </si>
+  <si>
+    <t>relationship--614fbc69-8cba-40a0-98f9-936eaac5419e</t>
+  </si>
+  <si>
+    <t>relationship--ca9d96ad-f282-4c8a-a7f1-c49268bc3a88</t>
+  </si>
+  <si>
+    <t>relationship--086b6153-43f4-47de-80df-44693f738943</t>
+  </si>
+  <si>
+    <t>relationship--8a4808c1-777c-40fc-aa35-f6cd68dc33c2</t>
+  </si>
+  <si>
+    <t>relationship--37a411b5-a9ad-4aa3-b275-64db44664d5d</t>
+  </si>
+  <si>
+    <t>relationship--aee80eb9-ab23-4760-8add-e0216bd30a05</t>
+  </si>
+  <si>
+    <t>relationship--ca3971ca-3608-4f4b-ba38-3b8e016ebf03</t>
+  </si>
+  <si>
+    <t>relationship--80974889-50af-4c79-93b8-102362fc0530</t>
+  </si>
+  <si>
+    <t>relationship--e6ca03f6-6ec1-4870-bcb9-a3c507268afb</t>
+  </si>
+  <si>
+    <t>relationship--2a6b0d1a-4fc7-40de-9362-c8eb8abcb9fa</t>
+  </si>
+  <si>
+    <t>relationship--df0ae14a-9167-4c70-bba9-d917ecd1bcbe</t>
+  </si>
+  <si>
+    <t>relationship--38cbf6e2-05be-4c93-9361-7c3355dec29f</t>
+  </si>
+  <si>
+    <t>relationship--eb3986b1-fecd-4d37-92dd-0c8250ef0740</t>
+  </si>
+  <si>
+    <t>relationship--388cb58a-f6b1-432c-aa19-57cc86f8713f</t>
+  </si>
+  <si>
+    <t>relationship--c6850c22-f194-48a1-b786-c5cf857b99cd</t>
+  </si>
+  <si>
+    <t>relationship--917fb287-22e5-452a-9dc2-8c5c8aca7d1b</t>
+  </si>
+  <si>
+    <t>relationship--34cf12dd-b962-4ebe-830a-d8f1c7ff5c4f</t>
+  </si>
+  <si>
+    <t>relationship--94711d8b-0578-438a-9d73-eafd0c1bc983</t>
+  </si>
+  <si>
+    <t>relationship--8045380f-5282-4b2f-ab8f-cb92ffd304a3</t>
+  </si>
+  <si>
+    <t>relationship--3536b790-3098-4639-9c74-ac882b5ab83e</t>
+  </si>
+  <si>
+    <t>relationship--c09a449b-0b73-4e67-abc0-922897a14e61</t>
+  </si>
+  <si>
+    <t>relationship--079404c8-fadc-4028-b464-f31ba21f9514</t>
+  </si>
+  <si>
+    <t>relationship--51aabffe-86e6-4eaa-bf10-1d5525e930ad</t>
+  </si>
+  <si>
+    <t>relationship--49567418-6145-460a-ab69-bcb7861395ac</t>
+  </si>
+  <si>
+    <t>relationship--69dc0331-617e-4089-ac23-257dbeee91a6</t>
+  </si>
+  <si>
+    <t>relationship--57e6a8bb-5b08-4144-8f3d-8b095b08d609</t>
+  </si>
+  <si>
+    <t>relationship--e51c177b-f601-47d5-9ae9-f6adb3dc397d</t>
+  </si>
+  <si>
+    <t>relationship--baecff7e-dc21-44ea-b863-ca8da3c62424</t>
+  </si>
+  <si>
+    <t>relationship--19d3a78f-c438-41f5-a55e-42a419a860ed</t>
+  </si>
+  <si>
+    <t>relationship--1cff25ec-e815-4f02-a656-6f61d9b4302b</t>
+  </si>
+  <si>
+    <t>relationship--574346d1-3eca-43c0-804a-6a49b0fedfbc</t>
+  </si>
+  <si>
+    <t>relationship--e0c46f26-e4dc-44f2-931a-3de7a380d82c</t>
+  </si>
+  <si>
+    <t>relationship--13b93f7a-eceb-4ba1-985b-9f182d1f8959</t>
+  </si>
+  <si>
+    <t>relationship--c094c5e2-4681-47c6-b649-aac2e30ef63e</t>
+  </si>
+  <si>
+    <t>relationship--6b756697-3af1-4921-8afa-de43e8494726</t>
+  </si>
+  <si>
+    <t>relationship--7cd3a274-997e-4fd8-96bd-ed11dbd871ae</t>
+  </si>
+  <si>
+    <t>relationship--e5064444-57d6-4ead-9e9f-a9797549b00a</t>
+  </si>
+  <si>
+    <t>relationship--a977d06e-c9fb-44fb-be91-d9d4ca6f6739</t>
+  </si>
+  <si>
+    <t>relationship--85d74a25-2849-44c5-be0e-0b95c58d05f8</t>
+  </si>
+  <si>
+    <t>relationship--5601426d-de66-4843-a720-640c317e943a</t>
+  </si>
+  <si>
+    <t>relationship--6b8df6aa-2628-49da-9686-9f4ce8ca52b4</t>
+  </si>
+  <si>
+    <t>relationship--02fbe54f-4fe3-4152-9a95-e00d089ad2d0</t>
+  </si>
+  <si>
+    <t>relationship--b74dbe90-0bd4-44ca-9b39-3217a14f9230</t>
+  </si>
+  <si>
+    <t>relationship--37b54435-8bbc-408e-80ac-ccb32adf9d74</t>
+  </si>
+  <si>
+    <t>relationship--e8277521-5c12-4beb-afa2-1d923b1370fa</t>
+  </si>
+  <si>
+    <t>relationship--aac62415-47fd-4339-998a-96774dc28e1a</t>
+  </si>
+  <si>
+    <t>relationship--d884d995-cb3e-42e1-a219-5b8593d7f55d</t>
+  </si>
+  <si>
+    <t>relationship--e63288e7-7429-4d44-93f8-fbae85b7d73c</t>
+  </si>
+  <si>
+    <t>relationship--88530d1b-75a5-40da-a530-138b7ed1bccb</t>
+  </si>
+  <si>
+    <t>relationship--9ff1122a-8920-4536-a6c9-b3651fe87a41</t>
+  </si>
+  <si>
+    <t>relationship--27d5e8cd-20cd-46d3-9497-57611e95e581</t>
+  </si>
+  <si>
+    <t>relationship--bbd6ac57-e29b-42c1-be57-9bbd7676104e</t>
+  </si>
+  <si>
+    <t>relationship--92239776-053f-40a0-aee3-5f0b9a1c07b5</t>
+  </si>
+  <si>
+    <t>relationship--8a3be6db-85c6-4603-a7fc-bb3acfabea88</t>
+  </si>
+  <si>
+    <t>relationship--5fb44550-4eee-4ab7-b478-d2805c2ba9b4</t>
+  </si>
+  <si>
+    <t>relationship--ca087af6-d503-43b8-abc2-10d6090c5a27</t>
+  </si>
+  <si>
+    <t>relationship--8f906083-a1b0-4547-96cc-b43ba604f276</t>
+  </si>
+  <si>
+    <t>relationship--8b2be964-dd7c-4e0b-82b6-6428d3bf1d42</t>
+  </si>
+  <si>
+    <t>relationship--80915558-dd86-465b-9b1a-e747fb99671c</t>
+  </si>
+  <si>
+    <t>relationship--edcf285d-1f1a-46ea-b28f-a4fcee5a385b</t>
+  </si>
+  <si>
+    <t>relationship--20245c10-e5f3-407c-a3b2-96c8c085b0f1</t>
+  </si>
+  <si>
+    <t>relationship--10e85415-c003-4ef7-a284-05708b6b72be</t>
+  </si>
+  <si>
+    <t>relationship--0fff1f96-3a68-42e4-8e4a-8c8fcb3ce386</t>
+  </si>
+  <si>
+    <t>relationship--5847e598-577d-463a-a3e9-5ca130dd4507</t>
+  </si>
+  <si>
+    <t>relationship--0352eb5f-1132-41ac-9206-b0e16b54436f</t>
+  </si>
+  <si>
+    <t>relationship--852117e1-8630-47eb-8e2e-e22cb2a1564a</t>
+  </si>
+  <si>
+    <t>relationship--5f4533c6-d5e7-41ed-8e89-ce7a3cb061bf</t>
+  </si>
+  <si>
+    <t>relationship--9707dd7d-b5a0-43e2-a6a5-6abce54b7edb</t>
+  </si>
+  <si>
+    <t>relationship--2398c8cc-88a5-4549-b19b-911958d2abe5</t>
+  </si>
+  <si>
+    <t>relationship--c7016342-e47b-4470-a344-672819c70b0d</t>
+  </si>
+  <si>
+    <t>relationship--34666ba1-5c30-4d83-bf2f-c127bb848dcb</t>
+  </si>
+  <si>
+    <t>relationship--5fbe8112-b86f-44db-b323-2f27083564e0</t>
+  </si>
+  <si>
+    <t>relationship--5e064122-2c0d-4930-bf68-fa20ec7fcdea</t>
+  </si>
+  <si>
+    <t>relationship--465dfbec-c935-48b8-ba7c-e8fe3561ca94</t>
+  </si>
+  <si>
+    <t>relationship--1604968c-dab0-43dc-8511-292fcd5575d9</t>
+  </si>
+  <si>
+    <t>relationship--be9a0880-9570-4610-93ec-e350f360d63f</t>
+  </si>
+  <si>
+    <t>relationship--c72b0b22-0cf9-4346-9637-60b6e5b705f9</t>
+  </si>
+  <si>
+    <t>relationship--1f637adc-e5b4-471d-8de1-d477966b1125</t>
+  </si>
+  <si>
+    <t>relationship--56625bef-dd57-4978-9a56-f155789ef3be</t>
+  </si>
+  <si>
+    <t>relationship--b791a492-2bf2-4995-b2d0-6910745d9754</t>
+  </si>
+  <si>
+    <t>relationship--623213a6-abdf-44df-a6fb-c086a684f8b2</t>
+  </si>
+  <si>
+    <t>relationship--468473e7-12c2-46de-88cc-734eafde2868</t>
+  </si>
+  <si>
+    <t>relationship--df901f67-e71f-4192-bcde-7f50d2d9373d</t>
+  </si>
+  <si>
+    <t>relationship--4f31c0bc-a24c-4193-bff2-3a66dae4772f</t>
+  </si>
+  <si>
+    <t>relationship--ec428e67-8568-4f37-a49e-cd580e5c38bd</t>
+  </si>
+  <si>
+    <t>relationship--4ec4ad3d-beca-450e-b6e9-5a93785c5bb0</t>
+  </si>
+  <si>
+    <t>relationship--6effb145-0cd4-4b9f-929f-4c4d89f84ef0</t>
+  </si>
+  <si>
+    <t>relationship--ad081b29-5c12-4d02-8bd1-046b674f4c7c</t>
+  </si>
+  <si>
+    <t>relationship--8f1b3d6f-23b6-4f9b-a8dd-9b3454bd2117</t>
+  </si>
+  <si>
+    <t>relationship--dc5bf458-56f0-43cb-a78d-8bb4bd127e99</t>
+  </si>
+  <si>
+    <t>relationship--9f863b15-ef76-4d35-a0a2-5d4c24c6e6f6</t>
+  </si>
+  <si>
+    <t>relationship--0a76fed9-efeb-4a8e-af6e-d874bc53f71d</t>
+  </si>
+  <si>
+    <t>relationship--465166f8-6a08-4320-aa5b-197bee427cfc</t>
+  </si>
+  <si>
+    <t>relationship--50d6da69-13b5-4383-9a4d-9e6af0892636</t>
+  </si>
+  <si>
+    <t>relationship--67b802bf-c650-4b6b-beac-08a3c96358c8</t>
+  </si>
+  <si>
+    <t>relationship--53719d9d-7011-4032-a70e-8c6138033d7e</t>
+  </si>
+  <si>
+    <t>relationship--5d155807-495a-48a4-be27-5ae299f1c38e</t>
+  </si>
+  <si>
+    <t>relationship--24d049ad-df50-41bf-ba64-070a5db3f232</t>
+  </si>
+  <si>
+    <t>relationship--1912344f-c2b1-497b-8c79-885dac85519f</t>
+  </si>
+  <si>
+    <t>relationship--66da841a-9ba5-4698-9434-a0716c584fcd</t>
+  </si>
+  <si>
+    <t>relationship--a0e26193-7b83-4fac-ba81-a14473696c12</t>
+  </si>
+  <si>
+    <t>relationship--e5ff6d58-7126-41d2-bffc-22be3e559d4c</t>
+  </si>
+  <si>
+    <t>relationship--87e28e8e-0c89-4acc-8d96-191a08c0c4ca</t>
+  </si>
+  <si>
+    <t>relationship--3fc53e7f-aabf-48b1-b1ca-92d9188c5fee</t>
+  </si>
+  <si>
+    <t>relationship--08f43466-659f-422c-be58-91c863e7b936</t>
+  </si>
+  <si>
+    <t>relationship--8160d9a6-4943-4736-a8aa-f256cb2628e3</t>
+  </si>
+  <si>
+    <t>relationship--0fd1b83a-0e8c-485a-9eea-9f1c28469003</t>
+  </si>
+  <si>
+    <t>relationship--955f1858-3345-4ba3-a027-ebbbdc018d52</t>
+  </si>
+  <si>
+    <t>relationship--5f967830-b2b4-4835-b8b3-78e3bb061c70</t>
+  </si>
+  <si>
+    <t>relationship--3662bcda-cf5d-4fd0-9313-620bd45d8adf</t>
+  </si>
+  <si>
+    <t>relationship--97eea6b0-abef-4c35-9150-15ffb0cfd642</t>
+  </si>
+  <si>
+    <t>relationship--4374b082-17aa-4a1e-9780-00373446507e</t>
+  </si>
+  <si>
+    <t>relationship--a38375ec-bc00-4e85-a5b2-013e20b1c61d</t>
+  </si>
+  <si>
+    <t>relationship--dd2f3bc2-fac5-4b98-a5ef-9687daaaa6fc</t>
+  </si>
+  <si>
+    <t>relationship--366d7ed8-a586-4109-9559-6c939ffd576a</t>
+  </si>
+  <si>
+    <t>relationship--402e6d4b-59c4-4e77-9b16-57a4076ae2d5</t>
+  </si>
+  <si>
+    <t>relationship--e9909627-4a7d-495a-834c-315541ab15fd</t>
+  </si>
+  <si>
+    <t>relationship--4b76cb9a-0bed-478d-b892-63357f2f24c9</t>
+  </si>
+  <si>
+    <t>relationship--a93a651a-ffac-4fc7-b9d4-6cc0d508089f</t>
+  </si>
+  <si>
+    <t>relationship--cc43e87c-69f3-4e15-a919-8898b8215090</t>
+  </si>
+  <si>
+    <t>relationship--83e6df16-07fe-41e5-a65b-6ed35c215cc2</t>
+  </si>
+  <si>
+    <t>relationship--5b878410-76cf-418c-b857-a2449022a172</t>
+  </si>
+  <si>
+    <t>relationship--1f29a6cf-c9bd-4e1a-af91-4490d00c1ea6</t>
+  </si>
+  <si>
+    <t>relationship--2cf31521-70c1-4491-a5ae-fe3c4bbc5246</t>
+  </si>
+  <si>
+    <t>relationship--157809ff-2ffb-485c-8b54-1a89d4dcb435</t>
+  </si>
+  <si>
+    <t>relationship--0461225b-8179-4aae-bc0f-d3b7851d4346</t>
+  </si>
+  <si>
+    <t>relationship--5e1ebc3e-adbb-46e4-afea-ca56f35aa3b8</t>
+  </si>
+  <si>
+    <t>relationship--20dfaeff-38ff-450e-b141-6512f93d479c</t>
+  </si>
+  <si>
+    <t>relationship--f6651003-cdfd-476e-964b-b9c1f9814aea</t>
+  </si>
+  <si>
+    <t>relationship--db030bae-c5f5-49ed-8ff4-af0e20ee225d</t>
+  </si>
+  <si>
+    <t>relationship--060b2bb4-62b6-4c64-9527-12b75f6856fb</t>
+  </si>
+  <si>
+    <t>relationship--f105b8ec-d05f-4968-b2d5-c5e5adff5a61</t>
+  </si>
+  <si>
+    <t>relationship--9de38fe8-f56c-4b6d-937c-b36b9e6b8972</t>
+  </si>
+  <si>
+    <t>relationship--f1e432e9-d627-42c5-8582-b9091113bb86</t>
+  </si>
+  <si>
+    <t>relationship--bc55738f-b0ed-416f-844b-6b1f22a7f345</t>
+  </si>
+  <si>
+    <t>relationship--4b753a57-ecd3-4fc6-a713-e0ad97968b62</t>
+  </si>
+  <si>
+    <t>relationship--4e0d7262-08ba-4fb5-bb63-dc30429b3fab</t>
+  </si>
+  <si>
+    <t>relationship--781b4bbf-8a2c-4057-baf5-1878ea619b0c</t>
+  </si>
+  <si>
+    <t>relationship--79f87c09-c697-4dd0-99f2-9fe176f8755c</t>
+  </si>
+  <si>
+    <t>relationship--badcf672-80b4-4756-bc72-46ed253671e1</t>
+  </si>
+  <si>
+    <t>relationship--77906d62-bf50-4cac-88ce-1dd773bab573</t>
+  </si>
+  <si>
+    <t>relationship--16eaf531-3997-47f0-a83e-7f32c635c0fc</t>
+  </si>
+  <si>
+    <t>relationship--8212aa70-f140-43d6-ba87-bfc75ec72e5f</t>
+  </si>
+  <si>
+    <t>relationship--aaa22663-967a-4b00-a539-b09ff557e821</t>
+  </si>
+  <si>
+    <t>relationship--fb30d154-83b6-4539-afb5-0c3888d3bec9</t>
+  </si>
+  <si>
+    <t>relationship--55aba2a5-f217-4d99-9c5b-5f3dac640b92</t>
+  </si>
+  <si>
+    <t>relationship--e8afeeaf-035c-4c76-b5bc-7e4af0f3395c</t>
+  </si>
+  <si>
+    <t>relationship--41a8b0a2-e56f-4893-9cd8-7c65ff389bf8</t>
+  </si>
+  <si>
+    <t>relationship--fb15b942-85d3-4fc7-991d-d9d2041a09e1</t>
+  </si>
+  <si>
+    <t>relationship--c5d8a571-ee0d-419d-8c01-bede9443b942</t>
+  </si>
+  <si>
+    <t>relationship--da556bf9-dba9-4c54-a5e8-c44cb6e48c3d</t>
+  </si>
+  <si>
+    <t>relationship--035189d5-3e56-41ed-98a6-a7efa1dda59a</t>
+  </si>
+  <si>
+    <t>relationship--ba7fc371-952e-4b6b-a61c-45b699357b3d</t>
+  </si>
+  <si>
+    <t>relationship--c35844cb-0555-42da-ba1f-cd933eebe624</t>
+  </si>
+  <si>
+    <t>relationship--4acd9755-b416-4b00-acc6-250ae9622465</t>
+  </si>
+  <si>
+    <t>relationship--0c0d5d6e-42fc-4d8e-902a-a19fe207848e</t>
+  </si>
+  <si>
+    <t>relationship--85e68b26-66be-4060-bc7e-a280bacd4e3a</t>
+  </si>
+  <si>
+    <t>relationship--a74700f2-597f-4f08-aeba-e87654802d35</t>
+  </si>
+  <si>
+    <t>relationship--47cbce4a-835a-4782-be3f-3f40fed7a3c8</t>
+  </si>
+  <si>
+    <t>relationship--03840c67-b080-459b-afa5-dabebcb4d44d</t>
+  </si>
+  <si>
+    <t>relationship--b7e30afc-7d74-4b1e-a1c5-653abf36c875</t>
+  </si>
+  <si>
+    <t>relationship--5f1bc6d9-5417-4f2c-9c50-d84caa46cb19</t>
+  </si>
+  <si>
+    <t>relationship--21c44f8f-68f3-4578-acb9-ef09c6722ab8</t>
+  </si>
+  <si>
+    <t>relationship--13e01f4c-8dd4-4b7d-9a30-3900d9fed55c</t>
+  </si>
+  <si>
+    <t>relationship--9702d5d0-42c1-46ce-b8dd-b0bfb6b33a3c</t>
+  </si>
+  <si>
+    <t>relationship--0a9ba803-afc5-414d-9159-cbe1dec86fdb</t>
+  </si>
+  <si>
+    <t>relationship--59db0a16-d7b1-472c-ba90-58d8e720dc4c</t>
+  </si>
+  <si>
+    <t>relationship--06e37dc0-aec3-40a5-9fdc-0a3900505d13</t>
+  </si>
+  <si>
+    <t>relationship--bffe6e07-ed4b-4734-aa19-1477f29364d2</t>
+  </si>
+  <si>
+    <t>relationship--1c36c5be-b13c-4f11-960f-9b03cbc87f8d</t>
+  </si>
+  <si>
+    <t>relationship--d3fd53b4-18fa-45e9-b69f-6a0d7520a5ca</t>
+  </si>
+  <si>
+    <t>relationship--756d0f2d-207e-4f7b-b0b2-b48292f01566</t>
+  </si>
+  <si>
+    <t>relationship--9a868a03-666e-4f64-b596-5c48bdee52c3</t>
+  </si>
+  <si>
+    <t>relationship--d7fc2066-edf6-47c6-a83c-7206850f0ab5</t>
+  </si>
+  <si>
+    <t>relationship--5d579a13-67d5-448a-adc5-83a4fafe6397</t>
+  </si>
+  <si>
+    <t>relationship--de480653-7c48-4149-8c94-9b269c7d47a4</t>
+  </si>
+  <si>
+    <t>relationship--6a67ff6b-94aa-4750-ab1b-fc32683bdef6</t>
+  </si>
+  <si>
+    <t>relationship--7d309686-d313-4099-bb16-28e1c507b4de</t>
+  </si>
+  <si>
+    <t>relationship--da8866ae-3f47-46eb-94b8-372a984469cd</t>
+  </si>
+  <si>
+    <t>relationship--3a5d6f95-14ab-46c5-b8da-032669b0bae2</t>
+  </si>
+  <si>
+    <t>relationship--024a7113-e248-4822-bea2-30f77d9a7a8f</t>
+  </si>
+  <si>
+    <t>relationship--00ca73d0-0387-42d0-84bc-936fda075d8d</t>
+  </si>
+  <si>
+    <t>relationship--1c8c0f26-e354-4f16-866b-c4ed7978e820</t>
+  </si>
+  <si>
+    <t>relationship--37ca5c6c-a8bd-4cc0-a94a-94c62380ad01</t>
+  </si>
+  <si>
+    <t>relationship--09ca5108-558b-4995-9467-494a354a918a</t>
+  </si>
+  <si>
+    <t>relationship--0e1317d3-00a0-4713-9781-766b42db644e</t>
+  </si>
+  <si>
+    <t>relationship--ba57efe2-3653-460c-a6d1-5293aa19b7ce</t>
+  </si>
+  <si>
+    <t>relationship--19a86362-7955-4dbf-bbb0-1c8de038abc9</t>
+  </si>
+  <si>
+    <t>relationship--105776f8-fb6e-40b1-90d5-51a56bacf1c1</t>
+  </si>
+  <si>
+    <t>relationship--26e34a40-646e-40bd-97fd-af7707fec87e</t>
+  </si>
+  <si>
+    <t>relationship--43674d3b-1755-45c6-be2c-b5e6b83dc1fd</t>
+  </si>
+  <si>
+    <t>relationship--56c13e79-da44-4855-abc6-d1119ccf296a</t>
+  </si>
+  <si>
+    <t>relationship--2b20ec1c-dcf1-4f91-abeb-ebe52c94ed06</t>
+  </si>
+  <si>
+    <t>relationship--7bb3178c-db31-4233-9649-cde63f598fde</t>
+  </si>
+  <si>
+    <t>relationship--8840ff74-0db6-4bb2-b7fb-90692fae5cf7</t>
+  </si>
+  <si>
+    <t>relationship--1abc678f-dce8-47c5-90b4-26b570e01f03</t>
+  </si>
+  <si>
+    <t>relationship--a10fcf23-dced-4c62-8b72-de9252e3dd3e</t>
+  </si>
+  <si>
+    <t>relationship--16744069-cca1-4a02-b485-33f838b5ab31</t>
+  </si>
+  <si>
+    <t>relationship--c4da07a0-ac6b-43bb-acb4-0e1eebb72e1d</t>
+  </si>
+  <si>
+    <t>relationship--b13c20bf-f6f3-496b-9bbc-756d27bcc338</t>
+  </si>
+  <si>
+    <t>relationship--ead18e3d-243e-4bfc-9e35-dcef978fa1a6</t>
+  </si>
+  <si>
+    <t>relationship--daa06fd4-7ec9-441c-9dad-d0b476425de6</t>
+  </si>
+  <si>
+    <t>relationship--efe698ab-5c0f-471e-965f-49902fb52ff3</t>
+  </si>
+  <si>
+    <t>relationship--bc99b34b-c89e-4a48-93d6-98e18c56bd9c</t>
+  </si>
+  <si>
+    <t>relationship--1c294501-8bda-4b29-b345-880b8d39a07c</t>
+  </si>
+  <si>
+    <t>relationship--1420dce4-e170-412c-8605-5ec9480fb9e2</t>
+  </si>
+  <si>
+    <t>relationship--a88ea7e3-49fd-4f48-a25f-2aa2a4cfda6c</t>
+  </si>
+  <si>
+    <t>relationship--4fde23f7-a081-497c-907b-a3499be478c1</t>
+  </si>
+  <si>
+    <t>relationship--c894f2d6-6b3d-43a9-ad2c-6d2c1c596045</t>
+  </si>
+  <si>
+    <t>relationship--01673386-068e-4501-ac11-1263c9fe485e</t>
+  </si>
+  <si>
+    <t>relationship--2c5dfe88-33fb-44bb-9dbc-b2430f5b1ecf</t>
+  </si>
+  <si>
+    <t>relationship--34bf02af-e6fa-4c0e-ad5c-d45c46d77832</t>
+  </si>
+  <si>
+    <t>relationship--52bddd02-b48a-4510-910a-094c4433eb2d</t>
+  </si>
+  <si>
+    <t>relationship--5506c3cf-59c7-46bb-9bf2-902908d87126</t>
+  </si>
+  <si>
+    <t>relationship--3984cea3-d47b-4481-8888-c0b1f35969c1</t>
+  </si>
+  <si>
+    <t>relationship--54c4d918-8bc7-4364-80f9-b0caf2bf0969</t>
+  </si>
+  <si>
+    <t>relationship--73189ccc-2381-4e23-95ce-ae7a30a09f43</t>
+  </si>
+  <si>
+    <t>relationship--04b40aa1-c056-4a12-a4ca-9a5b999da66e</t>
+  </si>
+  <si>
+    <t>relationship--6fc62b9c-7886-4974-ab01-cc635d166860</t>
+  </si>
+  <si>
+    <t>relationship--17316c02-b0c3-455f-8bcd-157aba4b808d</t>
+  </si>
+  <si>
+    <t>relationship--9a4c2560-ff66-4227-a982-86d97e2ffbed</t>
+  </si>
+  <si>
+    <t>relationship--4403eef2-fe84-4921-a94f-6257d3547b6e</t>
+  </si>
+  <si>
+    <t>relationship--84d3e218-1a16-4f3d-bf83-29abb545e970</t>
+  </si>
+  <si>
+    <t>relationship--62854ef1-cc65-4a00-85d8-968cabe77970</t>
+  </si>
+  <si>
+    <t>relationship--34a8027e-bb56-4c8c-a6e5-f2eff445b635</t>
+  </si>
+  <si>
+    <t>relationship--7a5673bf-43ca-4139-ac6b-d5bb967c11e6</t>
+  </si>
+  <si>
+    <t>relationship--96d6ea01-4a3b-4a31-834e-f6a1b25d3d01</t>
+  </si>
+  <si>
+    <t>relationship--65b32450-6df6-4327-9411-bb11dd24e186</t>
+  </si>
+  <si>
+    <t>relationship--cbbeb0ed-42c2-4724-b202-23d4856aff33</t>
+  </si>
+  <si>
+    <t>relationship--f2f90e4d-5a63-40b4-adad-90332f88a7be</t>
+  </si>
+  <si>
+    <t>relationship--11b1266c-d020-420d-9c40-318b57e0bbeb</t>
+  </si>
+  <si>
+    <t>relationship--5195893a-8224-493f-bdbb-b276f796dbb8</t>
+  </si>
+  <si>
+    <t>relationship--6165994a-b952-429b-8905-431c9e06f4cf</t>
+  </si>
+  <si>
+    <t>relationship--25f80921-0d9d-4d56-8a10-0b1c86bd8490</t>
+  </si>
+  <si>
+    <t>relationship--a1ce3595-ecd4-41b1-83f7-5aa32a7a4c25</t>
+  </si>
+  <si>
+    <t>relationship--b2d2b23a-2561-4b1b-b23b-60ec84ac8559</t>
+  </si>
+  <si>
+    <t>relationship--1a5c8ccb-b7f9-4118-9977-904a79d8cd91</t>
+  </si>
+  <si>
+    <t>relationship--499220bf-45f5-42dc-9842-b2104ef2385b</t>
+  </si>
+  <si>
+    <t>relationship--975edf7f-38d6-4125-86ae-6df413e02b64</t>
+  </si>
+  <si>
+    <t>relationship--13fe682c-4d2b-498e-b0fe-5faa9627f478</t>
+  </si>
+  <si>
+    <t>relationship--f98d2762-9dda-4bb9-a018-e77fcb87b59c</t>
+  </si>
+  <si>
+    <t>relationship--cda16288-3df9-4f63-8073-a4b437c71004</t>
+  </si>
+  <si>
+    <t>relationship--1f5a1489-2483-4e84-a40e-04efed8b94b4</t>
+  </si>
+  <si>
+    <t>relationship--fb03a109-6075-4b58-afb4-6a2557f2c215</t>
+  </si>
+  <si>
+    <t>relationship--9ec9acf6-7154-4532-913c-ccdf66091156</t>
+  </si>
+  <si>
+    <t>relationship--63452325-03d3-49b1-bf54-66dfb125ec87</t>
+  </si>
+  <si>
+    <t>relationship--0e802b5c-2403-479e-ac20-06e9aa5c43ae</t>
+  </si>
+  <si>
+    <t>relationship--dfc52397-92e1-4160-a98f-34948d016360</t>
+  </si>
+  <si>
+    <t>relationship--d6cc70a9-9c36-42e2-b4a9-454d252faa7a</t>
+  </si>
+  <si>
+    <t>relationship--7c07f851-9a41-4d35-b79f-fb7069c0d04d</t>
+  </si>
+  <si>
+    <t>relationship--971fa3bc-ca45-4715-9d2c-da25aab64756</t>
+  </si>
+  <si>
+    <t>relationship--676dfa2f-887b-4a44-869a-7ef3d8e61b0a</t>
+  </si>
+  <si>
+    <t>relationship--a476ccc4-9b09-40e8-85fa-c2cb5269f2b1</t>
+  </si>
+  <si>
+    <t>relationship--e9e57c76-c09b-4fd5-b89f-46f96cca140d</t>
+  </si>
+  <si>
+    <t>relationship--cedcc327-db8f-4d4c-b1f0-f6c89260dda8</t>
+  </si>
+  <si>
+    <t>relationship--cc6b2561-a78f-4f37-aee5-e8248c3db565</t>
+  </si>
+  <si>
+    <t>relationship--685565b6-7584-4468-b179-52fe99c48584</t>
+  </si>
+  <si>
+    <t>relationship--40f1a33f-1390-4a00-b1be-cf9f1d3c976b</t>
+  </si>
+  <si>
+    <t>relationship--66b98a2b-4c8f-4386-958d-02048df51fc3</t>
+  </si>
+  <si>
+    <t>relationship--7f56817f-8b83-4c6c-b2fd-a0b7f86dec1f</t>
+  </si>
+  <si>
+    <t>relationship--1ac9ff58-8efb-419c-928c-fe3847c9188c</t>
+  </si>
+  <si>
+    <t>relationship--9c48b5cd-56e8-49a0-9b61-a580368cf0e1</t>
+  </si>
+  <si>
+    <t>relationship--9b25f341-01f3-4dfd-a588-165a86bcaace</t>
+  </si>
+  <si>
+    <t>relationship--9da377c2-38ff-439c-823b-34a5d1998571</t>
+  </si>
+  <si>
+    <t>relationship--279284af-ae24-4c2b-bc5e-17e518c8868e</t>
+  </si>
+  <si>
+    <t>relationship--a07d27b0-07d8-4981-a5a0-be24cbe07191</t>
+  </si>
+  <si>
+    <t>relationship--3e6cea56-29f5-4715-a858-a40804c68293</t>
+  </si>
+  <si>
+    <t>relationship--ffafc4ad-f136-4aae-9beb-72a49eea5020</t>
+  </si>
+  <si>
+    <t>relationship--0ff6a61c-38db-4435-9190-d7afac3f982d</t>
+  </si>
+  <si>
+    <t>relationship--1ca8158f-e8b9-4dad-a4d9-63c5e5f7b814</t>
+  </si>
+  <si>
+    <t>relationship--7039815a-5bb6-4ae6-add1-1d88c03ca42f</t>
+  </si>
+  <si>
+    <t>relationship--07c3aeaa-21f2-42bd-a3d0-ebd14c8dbf1b</t>
+  </si>
+  <si>
+    <t>relationship--38e83d08-2485-4ebe-bf67-1c981ee314ba</t>
+  </si>
+  <si>
+    <t>relationship--f9f2ba02-56ea-4444-9e3f-a47c6972d6e7</t>
+  </si>
+  <si>
+    <t>relationship--a971ee1c-e0d2-4f15-9cd2-62e3d0d32ca0</t>
+  </si>
+  <si>
+    <t>relationship--d6699f88-a5cb-40dd-ae75-19f280aeb4cb</t>
+  </si>
+  <si>
+    <t>relationship--ece83b83-27bc-4e09-a313-ad8cee5ebeb7</t>
+  </si>
+  <si>
+    <t>relationship--cb5e7817-a24b-4246-a285-3699c9a6faa1</t>
+  </si>
+  <si>
+    <t>relationship--3be951b7-a21a-4015-8629-51c108cb9c26</t>
+  </si>
+  <si>
+    <t>relationship--de9774c2-f9b4-4b84-825a-2e1b90f22f46</t>
+  </si>
+  <si>
+    <t>relationship--c94c095f-581b-4666-bc33-15a56a4f7b95</t>
+  </si>
+  <si>
+    <t>relationship--d1aa0946-d87c-45ae-b424-d9c9146f01e9</t>
+  </si>
+  <si>
+    <t>relationship--bd156b28-4368-4ef7-9442-99a4037f8990</t>
+  </si>
+  <si>
+    <t>relationship--51b252c6-f25a-4868-ba2f-5c4c5dce3575</t>
+  </si>
+  <si>
+    <t>relationship--ea59c0a9-5e60-42a9-b62c-7b1c2c235920</t>
+  </si>
+  <si>
+    <t>relationship--472e25d9-877e-4eea-8777-ff8fb1f2cf1d</t>
+  </si>
+  <si>
+    <t>relationship--15b4a1ec-a4c0-4c0d-af6b-9ce3c60dc53c</t>
+  </si>
+  <si>
+    <t>relationship--45b6dca8-89ca-4d24-89ea-a829323807cb</t>
+  </si>
+  <si>
+    <t>relationship--73e7a9e7-fd3a-4ec8-8d58-ad42c116c5e5</t>
+  </si>
+  <si>
+    <t>relationship--e25881ca-c77f-4de2-9a5a-93e603d6089d</t>
+  </si>
+  <si>
+    <t>relationship--ccbb2c32-1b08-4489-9281-a4e802aebe2c</t>
+  </si>
+  <si>
+    <t>relationship--b1254916-a50c-4122-8a8b-ddae6cb4bf3b</t>
+  </si>
+  <si>
+    <t>relationship--436a367d-751f-46ae-865b-1b08b2c94b0b</t>
+  </si>
+  <si>
+    <t>relationship--ae1830ae-193d-49fd-88b8-9ca09acab278</t>
+  </si>
+  <si>
+    <t>relationship--a00d775f-db2b-4bf4-9738-882d507f14a3</t>
+  </si>
+  <si>
+    <t>relationship--91d493cc-ed9d-410a-87da-737f90d29d5f</t>
+  </si>
+  <si>
+    <t>relationship--2a31099b-0274-4bcb-bcd8-1ab0dd82ca1a</t>
+  </si>
+  <si>
+    <t>relationship--613a2833-e940-4b58-90d7-22663e80ee19</t>
+  </si>
+  <si>
+    <t>relationship--e2b3c79f-8da6-406e-b66b-35ee86951b5c</t>
+  </si>
+  <si>
+    <t>relationship--a27107bb-ee98-440b-b975-fbe403b7d011</t>
+  </si>
+  <si>
+    <t>relationship--22684718-ebff-48c1-835a-4dbcaae467d6</t>
+  </si>
+  <si>
+    <t>relationship--6c0f5f2d-13a9-4854-b56a-31267e3e57d4</t>
+  </si>
+  <si>
+    <t>relationship--2d8f0eaa-86d6-4ec2-b131-fb0176dde252</t>
+  </si>
+  <si>
+    <t>relationship--7acaf2ec-5332-4376-b9e6-e5f7a5d4e396</t>
+  </si>
+  <si>
+    <t>relationship--51ef3804-21ae-4b4d-90ff-66961d7c3031</t>
+  </si>
+  <si>
+    <t>relationship--46f3bd13-d9a3-40ce-9833-559c430cf1de</t>
+  </si>
+  <si>
+    <t>relationship--2e7a2655-e1f7-4be0-8560-99a7ce302fda</t>
+  </si>
+  <si>
+    <t>relationship--2b1d8bec-1187-47fc-a890-9171d0af4206</t>
+  </si>
+  <si>
+    <t>relationship--0c6b277f-6616-428d-8dde-d133beab7c6b</t>
+  </si>
+  <si>
+    <t>relationship--00266455-3f2b-4b3c-8e1f-6ce6193cb8f4</t>
+  </si>
+  <si>
+    <t>relationship--7981c6df-980d-427f-b355-4ce7650a11fa</t>
+  </si>
+  <si>
+    <t>relationship--58a2fd8c-b163-4fd7-af8e-4e5f518cf565</t>
+  </si>
+  <si>
+    <t>relationship--55fad24c-1298-46ae-8628-2eec64a7d75c</t>
+  </si>
+  <si>
+    <t>relationship--1bb41d58-bb9f-4f26-b8b2-5a6600fe25d5</t>
+  </si>
+  <si>
+    <t>relationship--3e20551e-d442-43b7-9893-b825832447f8</t>
+  </si>
+  <si>
+    <t>relationship--aef61ea4-d2d3-4b7d-b3f2-eb09d9954aba</t>
+  </si>
+  <si>
+    <t>relationship--fceb239a-b0ae-48e6-bec0-0c8c7357ebd9</t>
+  </si>
+  <si>
+    <t>relationship--3380f24c-4e14-49a4-a119-a87f1b9eecd9</t>
+  </si>
+  <si>
+    <t>relationship--a22a0b8c-4032-40b7-a0ea-12e9dbf2961b</t>
+  </si>
+  <si>
+    <t>relationship--217bd9d8-a378-463f-9cc8-e7fadf8aa13d</t>
+  </si>
+  <si>
+    <t>relationship--2f9a83f4-d17c-4e2f-b852-7e1823502480</t>
+  </si>
+  <si>
+    <t>relationship--1227d382-496a-4e5d-8e55-ff384f5424d1</t>
+  </si>
+  <si>
+    <t>relationship--14448630-38e2-458b-b4e9-f8184c4c7809</t>
+  </si>
+  <si>
+    <t>relationship--893aac3e-99cc-4a45-96b3-d9cc67be9476</t>
+  </si>
+  <si>
+    <t>relationship--1a5bc425-80c9-491b-8c61-699e84666675</t>
+  </si>
+  <si>
+    <t>relationship--3129830c-d6e0-43ad-aac8-fa955eec7292</t>
+  </si>
+  <si>
+    <t>relationship--ad8190b9-1ea3-422d-9cc0-79fe25111c3b</t>
+  </si>
+  <si>
+    <t>relationship--2a74ddf8-7017-4935-821c-bcd120366aec</t>
+  </si>
+  <si>
+    <t>relationship--65ad9ce1-3c06-4312-9781-f4ab0a1b4576</t>
+  </si>
+  <si>
+    <t>relationship--0d90ba2b-7b16-4c53-9b8f-26c329a24988</t>
+  </si>
+  <si>
+    <t>relationship--a3fe44a7-14ec-4ea0-b4f4-6846c5fbc24d</t>
+  </si>
+  <si>
+    <t>relationship--5e869d43-c351-4be0-a267-f79006c39d2d</t>
+  </si>
+  <si>
+    <t>relationship--10ef8b9a-6360-401d-8baf-86e9b805780c</t>
+  </si>
+  <si>
+    <t>relationship--15dd688a-f80a-4db8-b9bc-c1cdacee5bf9</t>
+  </si>
+  <si>
+    <t>relationship--21f6c7af-2c6e-4bf7-850c-61b5194aa999</t>
+  </si>
+  <si>
+    <t>relationship--839f6e5b-5e89-44c0-a3e6-71397137e2c0</t>
+  </si>
+  <si>
+    <t>relationship--3db1a8d4-08de-47d8-b608-1855ef5fc32e</t>
+  </si>
+  <si>
+    <t>relationship--8834c869-09ab-4a5b-9269-c40d5a257df4</t>
+  </si>
+  <si>
+    <t>relationship--fdce753f-4c29-4b25-91ff-7f7d8b2afea8</t>
+  </si>
+  <si>
+    <t>relationship--a87b6855-782c-4452-bdb9-86e7e2ec6059</t>
+  </si>
+  <si>
+    <t>relationship--f81e8eb7-d4f6-4e9a-b29f-4f25d579e7da</t>
+  </si>
+  <si>
+    <t>relationship--f696fb29-1c07-45b5-b568-64f4f6fe8fec</t>
+  </si>
+  <si>
+    <t>relationship--d9fa28d8-1f00-498b-918b-26c1e7ae1c53</t>
+  </si>
+  <si>
+    <t>relationship--f045efb9-8922-4775-970d-481418f671a0</t>
+  </si>
+  <si>
+    <t>relationship--205dff75-fc00-4858-8a43-d0391dd8c888</t>
+  </si>
+  <si>
+    <t>relationship--0a3003bf-966e-423b-b592-01d663788603</t>
+  </si>
+  <si>
+    <t>relationship--90f65ece-ab59-4b9f-aa48-6f3f18d3e1eb</t>
+  </si>
+  <si>
+    <t>relationship--1d1cb160-1ad8-4e2b-a6fb-cd4745e040b4</t>
+  </si>
+  <si>
+    <t>relationship--d883cc91-90fa-4cca-a50c-7267c0aff891</t>
+  </si>
+  <si>
+    <t>relationship--5aaf25d0-bc32-4203-9c9d-d9f66bd960d1</t>
+  </si>
+  <si>
+    <t>relationship--30b46d33-7b73-4334-a1db-d91a5850d0f8</t>
+  </si>
+  <si>
+    <t>relationship--1415d9e2-3ec8-4950-a3cf-0a771978afa9</t>
+  </si>
+  <si>
+    <t>relationship--4fdb62a5-fb3e-4fb6-aa8a-b682cb4e1c20</t>
+  </si>
+  <si>
+    <t>relationship--bbe1b9bc-6806-402f-b985-2f64a72ff0e3</t>
+  </si>
+  <si>
+    <t>relationship--4262f5bf-7ff8-4bb6-84c4-e0226ad3b11d</t>
+  </si>
+  <si>
+    <t>relationship--d62debb4-770b-4b6f-8173-018af2a5b325</t>
+  </si>
+  <si>
+    <t>relationship--2c6e107e-e860-40fb-8f76-ce5682d72b02</t>
+  </si>
+  <si>
+    <t>relationship--49922116-adf1-4974-b9b4-8baef88d2dd9</t>
+  </si>
+  <si>
+    <t>relationship--d2d79914-471e-457f-ae36-41d34ccaeff6</t>
+  </si>
+  <si>
+    <t>relationship--f44aba76-9d85-4d72-a071-a2e09093df88</t>
+  </si>
+  <si>
+    <t>relationship--502e33d2-3654-4b52-a2d2-08a6a6c709f3</t>
+  </si>
+  <si>
+    <t>relationship--b0b9692d-77af-4890-986f-fc4b37d7dfa3</t>
+  </si>
+  <si>
+    <t>relationship--e5e638ab-fd72-4af1-9f8d-e2bb7d44142c</t>
+  </si>
+  <si>
+    <t>relationship--5bcf5e3f-e1a0-4b65-a5ef-c087360b918b</t>
+  </si>
+  <si>
+    <t>relationship--b8cf1b28-e865-4cd7-93f6-565527b4a923</t>
+  </si>
+  <si>
+    <t>relationship--a7a7b234-a9dd-4b62-b9ed-73f511c5adf8</t>
+  </si>
+  <si>
+    <t>relationship--63474f71-ecda-42ff-8bc1-475a951eb9d4</t>
+  </si>
+  <si>
+    <t>relationship--06e2c87e-97c1-425e-aa49-49a43aaf8c38</t>
+  </si>
+  <si>
+    <t>relationship--c5907c16-a6b2-4585-8587-743dbd102eb4</t>
+  </si>
+  <si>
+    <t>relationship--ef4b5e37-4b77-41ef-a9fd-ed32e7dd71d1</t>
+  </si>
+  <si>
+    <t>relationship--7d60876d-abd3-49cb-9646-9d3ce55e8eaa</t>
+  </si>
+  <si>
+    <t>relationship--00d76dd5-547f-4d91-a2b2-a68120947401</t>
+  </si>
+  <si>
+    <t>relationship--5d240505-32ed-4a6f-897e-bc114bded524</t>
+  </si>
+  <si>
+    <t>relationship--6867b04c-5665-48ce-a4a9-d0e025aae5b3</t>
   </si>
   <si>
     <t>27 April 2026</t>
@@ -6007,6 +6007,9 @@
     <t>2016 Ukraine Electric Power Attack | MITRE ATT&amp;CK® 2023</t>
   </si>
   <si>
+    <t>2022 Ukraine Electric Power Attack | MITRE ATT&amp;CK® 2024</t>
+  </si>
+  <si>
     <t>APT28 Nearest Neighbor Campaign | MITRE ATT&amp;CK® 2025</t>
   </si>
   <si>
@@ -6019,18 +6022,45 @@
     <t>Іван Мазепа — Вікіпедія 2026</t>
   </si>
   <si>
+    <t>Історія Донецької області — Вікіпедія 2026</t>
+  </si>
+  <si>
     <t>Історія України — Вікіпедія 2026</t>
   </si>
   <si>
+    <t>Азовські походи (1695—1696) — Вікіпедія 2026</t>
+  </si>
+  <si>
+    <t>Андрусовское перемирие - Википедия 2026</t>
+  </si>
+  <si>
     <t>Анексія Київської митрополії Московським патріархатом — Вікіпедія 2026</t>
   </si>
   <si>
+    <t>Аннексия Бессарабии Российской империей (1812) — Википедия 2026</t>
+  </si>
+  <si>
+    <t>Антикріпосницький рух в Україні (1789-1861) — Вікіпедія 2026</t>
+  </si>
+  <si>
+    <t>Батуринська трагедія — Вікіпедія 2026</t>
+  </si>
+  <si>
+    <t>В ТЕНИ «БОЛЬШОГО БРАТА» ЗАПАДНЫЕ НАЦИОНАЛЬНЫЕ МЕНЬШИНСТВА В СССР 1917-1938 ГГ . 2011</t>
+  </si>
+  <si>
     <t>Война и наказание: Как Россия уничтожала Украину 2023</t>
   </si>
   <si>
     <t>Всесоюзний референдум про збереження СРСР — Вікіпедія 2026</t>
   </si>
   <si>
+    <t>Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.) 2013</t>
+  </si>
+  <si>
+    <t>ДИССИДЕНТСКОЕ ДВИЖЕНИЕ В УКРАИНЕ (1954 – 1987) 2026</t>
+  </si>
+  <si>
     <t>Двойное преступление СССР: как советы скрывали Чернобыльскую катастрофу 2026</t>
   </si>
   <si>
@@ -6049,6 +6079,9 @@
     <t>ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011</t>
   </si>
   <si>
+    <t>Карательная психиатрия в России: назад в СССР? 2020</t>
+  </si>
+  <si>
     <t>Кенгирское восстание заключённых - Википедия 2026</t>
   </si>
   <si>
@@ -6064,42 +6097,84 @@
     <t>Конотопські статті — Вікіпедія 2026</t>
   </si>
   <si>
+    <t>Котлета по-київськи (промова) — Вікіпедія 2026</t>
+  </si>
+  <si>
     <t>Крымская война — Википедия 2026</t>
   </si>
   <si>
+    <t>Листопадове повстання (1830—1831) — Вікіпедія 2026</t>
+  </si>
+  <si>
     <t>Лубенський договір — Вікіпедія 2026</t>
   </si>
   <si>
+    <t>Ліквідація Запорозької Січі (1775) — Вікіпедія 2026</t>
+  </si>
+  <si>
     <t>Ліквідація автономії Гетьманщини — Вікіпедія 2026</t>
   </si>
   <si>
+    <t>Ліквідація козацтва на Правобережній Україні (1699) — Вікіпедія 2026</t>
+  </si>
+  <si>
     <t>Мазепа 2007</t>
   </si>
   <si>
+    <t>Мазепа, Иван Степанович — Википедия 2026</t>
+  </si>
+  <si>
     <t>Малоросійське генерал-губернаторство — Вікіпедія 2026</t>
   </si>
   <si>
     <t>Малоросійський приказ — Вікіпедія 2026</t>
   </si>
   <si>
+    <t>Московсько-українська війна (1658—1659) — Вікіпедія 2026</t>
+  </si>
+  <si>
+    <t>Московські статті (1665) — Вікіпедія 2026</t>
+  </si>
+  <si>
     <t>Народний рух України — Вікіпедія 2026</t>
   </si>
   <si>
+    <t>Національно-культурне життя етнічних меншостей України ( 20-30-ті роки ): коренізація і денаціоналізація (1) 1998</t>
+  </si>
+  <si>
     <t>Норильское восстание - Википедия 2026</t>
   </si>
   <si>
+    <t>Перепис населення Російської імперії (1897) — Вікіпедія 2026</t>
+  </si>
+  <si>
     <t>Переяславська рада — Вікіпедія 2026</t>
   </si>
   <si>
+    <t>Переяславські статті (1659) — Вікіпедія 2026</t>
+  </si>
+  <si>
     <t>Письмо-протест 139 - Википедия 2026</t>
   </si>
   <si>
+    <t>Повстання бузьких козаків (1817) — Вікіпедія 2026</t>
+  </si>
+  <si>
     <t>Поділи Речі Посполитої — Вікіпедія 2026</t>
   </si>
   <si>
+    <t>Польское восстание (1863—1864) — Википедия 2026</t>
+  </si>
+  <si>
+    <t>Похід Пилипа Орлика на Правобережну Україну (1711) — Вікіпедія 2026</t>
+  </si>
+  <si>
     <t>Правління гетьманського уряду — Вікіпедія 2026</t>
   </si>
   <si>
+    <t>Північна війна (1700—1721) — Вікіпедія 2026</t>
+  </si>
+  <si>
     <t>Рашизм: Звір з безодні 2023</t>
   </si>
   <si>
@@ -6112,9 +6187,21 @@
     <t>Россия - Чечня - цепь ошибок и преступлений. 1994—1996 2010</t>
   </si>
   <si>
+    <t>Російсько-турецька війна (1806—1812) — Вікіпедія 2026</t>
+  </si>
+  <si>
+    <t>Російсько-українська війна (з 2014) — Вікіпедія 2026</t>
+  </si>
+  <si>
     <t>Русифікація України — Вікіпедія 2026</t>
   </si>
   <si>
+    <t>Русско-турецкая война (1877—1878) — Википедия 2026</t>
+  </si>
+  <si>
+    <t>Русско-турецкая война (1768—1774) — Википедия 2026</t>
+  </si>
+  <si>
     <t>Руїна — Вікіпедія 2026</t>
   </si>
   <si>
@@ -6139,6 +6226,9 @@
     <t>Україна в Першій світовій війні — Вікіпедія 2026</t>
   </si>
   <si>
+    <t>Україна й українці в постімперську добу (1917—1939) 2021</t>
+  </si>
+  <si>
     <t>Україна у війнах Наполеона — Вікіпедія 2026</t>
   </si>
   <si>
@@ -6154,6 +6244,9 @@
     <t>MITRE ATT&amp;CK®. (2023). 2016 Ukraine Electric Power Attack | MITRE ATT&amp;CK®.</t>
   </si>
   <si>
+    <t>MITRE ATT&amp;CK®. (2024). 2022 Ukraine Electric Power Attack | MITRE ATT&amp;CK®.</t>
+  </si>
+  <si>
     <t>MITRE ATT&amp;CK®. (2025). APT28 Nearest Neighbor Campaign | MITRE ATT&amp;CK®.</t>
   </si>
   <si>
@@ -6166,18 +6259,45 @@
     <t>Вікіпедія. (2026). Іван Мазепа — Вікіпедія.</t>
   </si>
   <si>
+    <t>Вікіпедія. (2026). Історія Донецької області — Вікіпедія.</t>
+  </si>
+  <si>
     <t>Вікіпедія. (2026). Історія України — Вікіпедія.</t>
   </si>
   <si>
+    <t>Вікіпедія. (2026). Азовські походи (1695—1696) — Вікіпедія.</t>
+  </si>
+  <si>
+    <t>Википедия. (2026). Андрусовское перемирие - Википедия.</t>
+  </si>
+  <si>
     <t>Вікіпедія. (2026). Анексія Київської митрополії Московським патріархатом — Вікіпедія.</t>
   </si>
   <si>
+    <t>Википедия. (2026). Аннексия Бессарабии Российской империей (1812) — Википедия.</t>
+  </si>
+  <si>
+    <t>Вікіпедія. (2026). Антикріпосницький рух в Україні (1789-1861) — Вікіпедія.</t>
+  </si>
+  <si>
+    <t>Вікіпедія. (2026). Батуринська трагедія — Вікіпедія.</t>
+  </si>
+  <si>
+    <t>Виктор Дённингхаус. (2011). В ТЕНИ «БОЛЬШОГО БРАТА» ЗАПАДНЫЕ НАЦИОНАЛЬНЫЕ МЕНЬШИНСТВА В СССР 1917-1938 ГГ ..</t>
+  </si>
+  <si>
     <t>Михаил Зыгарь. (2023). Война и наказание: Как Россия уничтожала Украину.</t>
   </si>
   <si>
     <t>Википедия. (2026). Всесоюзний референдум про збереження СРСР — Вікіпедія.</t>
   </si>
   <si>
+    <t>Лариса Якубова, большая команда. (2013). Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.).</t>
+  </si>
+  <si>
+    <t>Евгений Захаров, Харьковская правозащитная группа. (2026). ДИССИДЕНТСКОЕ ДВИЖЕНИЕ В УКРАИНЕ (1954 – 1987).</t>
+  </si>
+  <si>
     <t>Obozrevatel. (2026). Двойное преступление СССР: как советы скрывали Чернобыльскую катастрофу.</t>
   </si>
   <si>
@@ -6196,6 +6316,9 @@
     <t>Татьяна Таирова-Яковлева. (2011). ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА».</t>
   </si>
   <si>
+    <t>Riddle Russia. (2020). Карательная психиатрия в России: назад в СССР?.</t>
+  </si>
+  <si>
     <t>Википедия. (2026). Кенгирское восстание заключённых - Википедия.</t>
   </si>
   <si>
@@ -6211,42 +6334,84 @@
     <t>Вікіпедія. (2026). Конотопські статті — Вікіпедія.</t>
   </si>
   <si>
+    <t>Вікіпедія. (2026). Котлета по-київськи (промова) — Вікіпедія.</t>
+  </si>
+  <si>
     <t>Википедия. (2026). Крымская война — Википедия.</t>
   </si>
   <si>
+    <t>Вікіпедія. (2026). Листопадове повстання (1830—1831) — Вікіпедія.</t>
+  </si>
+  <si>
     <t>Вікіпедія. (2026). Лубенський договір — Вікіпедія.</t>
   </si>
   <si>
+    <t>Вікіпедія. (2026). Ліквідація Запорозької Січі (1775) — Вікіпедія.</t>
+  </si>
+  <si>
     <t>Вікіпедія. (2026). Ліквідація автономії Гетьманщини — Вікіпедія.</t>
   </si>
   <si>
+    <t>Вікіпедія. (2026). Ліквідація козацтва на Правобережній Україні (1699) — Вікіпедія.</t>
+  </si>
+  <si>
     <t>Татьяна Таирова-Яковлева. (2007). Мазепа.</t>
   </si>
   <si>
+    <t>Википедия. (2026). Мазепа, Иван Степанович — Википедия.</t>
+  </si>
+  <si>
     <t>Вікіпедія. (2026). Малоросійське генерал-губернаторство — Вікіпедія.</t>
   </si>
   <si>
     <t>Вікіпедія. (2026). Малоросійський приказ — Вікіпедія.</t>
   </si>
   <si>
+    <t>Википедия. (2026). Московсько-українська війна (1658—1659) — Вікіпедія.</t>
+  </si>
+  <si>
+    <t>Вікіпедія. (2026). Московські статті (1665) — Вікіпедія.</t>
+  </si>
+  <si>
     <t>Википедия. (2026). Народний рух України — Вікіпедія.</t>
   </si>
   <si>
+    <t>Лариса Якубова. (1998). Національно-культурне життя етнічних меншостей України ( 20-30-ті роки ): коренізація і денаціоналізація (1).</t>
+  </si>
+  <si>
     <t>Википедия. (2026). Норильское восстание - Википедия.</t>
   </si>
   <si>
+    <t>Вікіпедія. (2026). Перепис населення Російської імперії (1897) — Вікіпедія.</t>
+  </si>
+  <si>
     <t>Википедия. (2026). Переяславська рада — Вікіпедія.</t>
   </si>
   <si>
+    <t>Википедия. (2026). Переяславські статті (1659) — Вікіпедія.</t>
+  </si>
+  <si>
     <t>Википедия. (2026). Письмо-протест 139 - Википедия.</t>
   </si>
   <si>
+    <t>Вікіпедія. (2026). Повстання бузьких козаків (1817) — Вікіпедія.</t>
+  </si>
+  <si>
     <t>Вікіпедія. (2026). Поділи Речі Посполитої — Вікіпедія.</t>
   </si>
   <si>
+    <t>Википедия. (2026). Польское восстание (1863—1864) — Википедия.</t>
+  </si>
+  <si>
+    <t>Вікіпедія. (2026). Похід Пилипа Орлика на Правобережну Україну (1711) — Вікіпедія.</t>
+  </si>
+  <si>
     <t>Вікіпедія. (2026). Правління гетьманського уряду — Вікіпедія.</t>
   </si>
   <si>
+    <t>Вікіпедія. (2026). Північна війна (1700—1721) — Вікіпедія.</t>
+  </si>
+  <si>
     <t>Лариса Якубова. (2023). Рашизм: Звір з безодні.</t>
   </si>
   <si>
@@ -6259,9 +6424,21 @@
     <t>Мемориал, О.П.Орлов, А.В.Черкасов. (2010). Россия - Чечня - цепь ошибок и преступлений. 1994—1996.</t>
   </si>
   <si>
+    <t>Вікіпедія. (2026). Російсько-турецька війна (1806—1812) — Вікіпедія.</t>
+  </si>
+  <si>
+    <t>Вікіпедія. (2026). Російсько-українська війна (з 2014) — Вікіпедія.</t>
+  </si>
+  <si>
     <t>Вікіпедія. (2026). Русифікація України — Вікіпедія.</t>
   </si>
   <si>
+    <t>Википедия. (2026). Русско-турецкая война (1877—1878) — Википедия.</t>
+  </si>
+  <si>
+    <t>Вікіпедія. (2026). Русско-турецкая война (1768—1774) — Википедия.</t>
+  </si>
+  <si>
     <t>Википедия. (2026). Руїна — Вікіпедія.</t>
   </si>
   <si>
@@ -6286,6 +6463,9 @@
     <t>Википедия. (2026). Україна в Першій світовій війні — Вікіпедія.</t>
   </si>
   <si>
+    <t>Єфіменко Г. Г., Кульчицький С. В., Пиріг Р. Я., Скальський В. В., Якубова Л. Д.. (2021). Україна й українці в постімперську добу (1917—1939).</t>
+  </si>
+  <si>
     <t>Вікіпедія. (2026). Україна у війнах Наполеона — Вікіпедія.</t>
   </si>
   <si>
@@ -6301,6 +6481,9 @@
     <t>https://attack.mitre.org/campaigns/C0025/</t>
   </si>
   <si>
+    <t>https://attack.mitre.org/campaigns/C0034/</t>
+  </si>
+  <si>
     <t>https://attack.mitre.org/campaigns/C0051/</t>
   </si>
   <si>
@@ -6313,15 +6496,36 @@
     <t>https://uk.wikipedia.org/wiki/%25D0%2586%25D0%25B2%25D0%25B0%25D0%25BD_%25D0%259C%25D0%25B0%25D0%25B7%25D0%25B5%25D0%25BF%25D0%25B0</t>
   </si>
   <si>
+    <t>https://uk.wikipedia.org/wiki/%25D0%2586%25D1%2581%25D1%2582%25D0%25BE%25D1%2580%25D1%2596%25D1%258F_%25D0%2594%25D0%25BE%25D0%25BD%25D0%25B5%25D1%2586%25D1%258C%25D0%25BA%25D0%25BE%25D1%2597_%25D0%25BE%25D0%25B1%25D0%25BB%25D0%25B0%25D1%2581%25D1%2582%25D1%2596</t>
+  </si>
+  <si>
     <t>https://uk.wikipedia.org/wiki/%25D0%2586%25D1%2581%25D1%2582%25D0%25BE%25D1%2580%25D1%2596%25D1%258F_%25D0%25A3%25D0%25BA%25D1%2580%25D0%25B0%25D1%2597%25D0%25BD%25D0%25B8</t>
   </si>
   <si>
+    <t>https://uk.wikipedia.org/wiki/%25D0%2590%25D0%25B7%25D0%25BE%25D0%25B2%25D1%2581%25D1%258C%25D0%25BA%25D1%2596_%25D0%25BF%25D0%25BE%25D1%2585%25D0%25BE%25D0%25B4%25D0%25B8_%281695%25E2%2580%25941696%29</t>
+  </si>
+  <si>
+    <t>https://ru.wikipedia.org/wiki/%25D0%2590%25D0%25BD%25D0%25B4%25D1%2580%25D1%2583%25D1%2581%25D0%25BE%25D0%25B2%25D1%2581%25D0%25BA%25D0%25BE%25D0%25B5_%25D0%25BF%25D0%25B5%25D1%2580%25D0%25B5%25D0%25BC%25D0%25B8%25D1%2580%25D0%25B8%25D0%25B5</t>
+  </si>
+  <si>
     <t>https://uk.wikipedia.org/wiki/%25D0%2590%25D0%25BD%25D0%25B5%25D0%25BA%25D1%2581%25D1%2596%25D1%258F_%25D0%259A%25D0%25B8%25D1%2597%25D0%25B2%25D1%2581%25D1%258C%25D0%25BA%25D0%25BE%25D1%2597_%25D0%25BC%25D0%25B8%25D1%2582%25D1%2580%25D0%25BE%25D0%25BF%25D0%25BE%25D0%25BB%25D1%2596%25D1%2597_%25D0%259C%25D0%25BE%25D1%2581%25D0%25BA%25D0%25BE%25D0%25B2%25D1%2581%25D1%258C%25D0%25BA%25D0%25B8%25D0%25BC_%25D0%25BF%25D0%25B0%25D1%2582%25D1%2580%25D1%2596%25D0%25B0%25D1%2580%25D1%2585%25D0%25B0%25D1%2582%25D0%25BE%25D0%25BC</t>
   </si>
   <si>
+    <t>https://ru.wikipedia.org/wiki/%25D0%2590%25D0%25BD%25D0%25BD%25D0%25B5%25D0%25BA%25D1%2581%25D0%25B8%25D1%258F_%25D0%2591%25D0%25B5%25D1%2581%25D1%2581%25D0%25B0%25D1%2580%25D0%25B0%25D0%25B1%25D0%25B8%25D0%25B8_%25D0%25A0%25D0%25BE%25D1%2581%25D1%2581%25D0%25B8%25D0%25B9%25D1%2581%25D0%25BA%25D0%25BE%25D0%25B9_%25D0%25B8%25D0%25BC%25D0%25BF%25D0%25B5%25D1%2580%25D0%25B8%25D0%25B5%25D0%25B9_%281812%29</t>
+  </si>
+  <si>
+    <t>https://uk.wikipedia.org/wiki/%25D0%2590%25D0%25BD%25D1%2582%25D0%25B8%25D0%25BA%25D1%2580%25D1%2596%25D0%25BF%25D0%25BE%25D1%2581%25D0%25BD%25D0%25B8%25D1%2586%25D1%258C%25D0%25BA%25D0%25B8%25D0%25B9_%25D1%2580%25D1%2583%25D1%2585_%25D0%25B2_%25D0%25A3%25D0%25BA%25D1%2580%25D0%25B0%25D1%2597%25D0%25BD%25D1%2596_%281789-1861%29</t>
+  </si>
+  <si>
+    <t>https://uk.wikipedia.org/wiki/%25D0%2591%25D0%25B0%25D1%2582%25D1%2583%25D1%2580%25D0%25B8%25D0%25BD%25D1%2581%25D1%258C%25D0%25BA%25D0%25B0_%25D1%2582%25D1%2580%25D0%25B0%25D0%25B3%25D0%25B5%25D0%25B4%25D1%2596%25D1%258F</t>
+  </si>
+  <si>
     <t>https://uk.wikipedia.org/wiki/%25D0%2592%25D1%2581%25D0%25B5%25D1%2581%25D0%25BE%25D1%258E%25D0%25B7%25D0%25BD%25D0%25B8%25D0%25B9_%25D1%2580%25D0%25B5%25D1%2584%25D0%25B5%25D1%2580%25D0%25B5%25D0%25BD%25D0%25B4%25D1%2583%25D0%25BC_%25D0%25BF%25D1%2580%25D0%25BE_%25D0%25B7%25D0%25B1%25D0%25B5%25D1%2580%25D0%25B5%25D0%25B6%25D0%25B5%25D0%25BD%25D0%25BD%25D1%258F_%25D0%25A1%25D0%25A0%25D0%25A1%25D0%25A0</t>
   </si>
   <si>
+    <t>https://museum.khpg.org/ru/1628664422</t>
+  </si>
+  <si>
     <t>https://www.obozrevatel.com/novosti-obschestvo/dvojnoe-prestuplenie-sssr-kak-sovetyi-skryivali-chernobyilskuyu-katastrofu.htm</t>
   </si>
   <si>
@@ -6337,6 +6541,9 @@
     <t>https://uk.wikipedia.org/wiki/%25D0%2597%25D0%25B0%25D0%25BF%25D0%25BE%25D1%2580%25D0%25BE%25D0%25B7%25D1%258C%25D0%25BA%25D0%25B0_%25D0%25A1%25D1%2596%25D1%2587</t>
   </si>
   <si>
+    <t>https://ridl.io/ru/karatelnaja-psihiatrija-v-rossii-nazad-v-sssr/</t>
+  </si>
+  <si>
     <t>https://ru.wikipedia.org/wiki/%25D0%259A%25D0%25B5%25D0%25BD%25D0%25B3%25D0%25B8%25D1%2580%25D1%2581%25D0%25BA%25D0%25BE%25D0%25B5_%25D0%25B2%25D0%25BE%25D1%2581%25D1%2581%25D1%2582%25D0%25B0%25D0%25BD%25D0%25B8%25D0%25B5_%25D0%25B7%25D0%25B0%25D0%25BA%25D0%25BB%25D1%258E%25D1%2587%25D1%2591%25D0%25BD%25D0%25BD%25D1%258B%25D1%2585</t>
   </si>
   <si>
@@ -6352,39 +6559,81 @@
     <t>https://uk.wikipedia.org/wiki/%25D0%259A%25D0%25BE%25D0%25BD%25D0%25BE%25D1%2582%25D0%25BE%25D0%25BF%25D1%2581%25D1%258C%25D0%25BA%25D1%2596_%25D1%2581%25D1%2582%25D0%25B0%25D1%2582%25D1%2582%25D1%2596</t>
   </si>
   <si>
+    <t>https://uk.wikipedia.org/wiki/%25D0%259A%25D0%25BE%25D1%2582%25D0%25BB%25D0%25B5%25D1%2582%25D0%25B0_%25D0%25BF%25D0%25BE-%25D0%25BA%25D0%25B8%25D1%2597%25D0%25B2%25D1%2581%25D1%258C%25D0%25BA%25D0%25B8_%28%25D0%25BF%25D1%2580%25D0%25BE%25D0%25BC%25D0%25BE%25D0%25B2%25D0%25B0%29</t>
+  </si>
+  <si>
     <t>https://ru.wikipedia.org/wiki/%25D0%259A%25D1%2580%25D1%258B%25D0%25BC%25D1%2581%25D0%25BA%25D0%25B0%25D1%258F_%25D0%25B2%25D0%25BE%25D0%25B9%25D0%25BD%25D0%25B0</t>
   </si>
   <si>
+    <t>https://uk.wikipedia.org/wiki/%25D0%259B%25D0%25B8%25D1%2581%25D1%2582%25D0%25BE%25D0%25BF%25D0%25B0%25D0%25B4%25D0%25BE%25D0%25B2%25D0%25B5_%25D0%25BF%25D0%25BE%25D0%25B2%25D1%2581%25D1%2582%25D0%25B0%25D0%25BD%25D0%25BD%25D1%258F_%281830%25E2%2580%25941831%29</t>
+  </si>
+  <si>
     <t>https://uk.wikipedia.org/wiki/%25D0%259B%25D1%2583%25D0%25B1%25D0%25B5%25D0%25BD%25D1%2581%25D1%258C%25D0%25BA%25D0%25B8%25D0%25B9_%25D0%25B4%25D0%25BE%25D0%25B3%25D0%25BE%25D0%25B2%25D1%2596%25D1%2580</t>
   </si>
   <si>
+    <t>https://uk.wikipedia.org/wiki/%25D0%259B%25D1%2596%25D0%25BA%25D0%25B2%25D1%2596%25D0%25B4%25D0%25B0%25D1%2586%25D1%2596%25D1%258F_%25D0%2597%25D0%25B0%25D0%25BF%25D0%25BE%25D1%2580%25D0%25BE%25D0%25B7%25D1%258C%25D0%25BA%25D0%25BE%25D1%2597_%25D0%25A1%25D1%2596%25D1%2587%25D1%2596_%281775%29</t>
+  </si>
+  <si>
     <t>https://uk.wikipedia.org/wiki/%25D0%259B%25D1%2596%25D0%25BA%25D0%25B2%25D1%2596%25D0%25B4%25D0%25B0%25D1%2586%25D1%2596%25D1%258F_%25D0%25B0%25D0%25B2%25D1%2582%25D0%25BE%25D0%25BD%25D0%25BE%25D0%25BC%25D1%2596%25D1%2597_%25D0%2593%25D0%25B5%25D1%2582%25D1%258C%25D0%25BC%25D0%25B0%25D0%25BD%25D1%2589%25D0%25B8%25D0%25BD%25D0%25B8</t>
   </si>
   <si>
+    <t>https://uk.wikipedia.org/wiki/%25D0%259B%25D1%2596%25D0%25BA%25D0%25B2%25D1%2596%25D0%25B4%25D0%25B0%25D1%2586%25D1%2596%25D1%258F_%25D0%25BA%25D0%25BE%25D0%25B7%25D0%25B0%25D1%2586%25D1%2582%25D0%25B2%25D0%25B0_%25D0%25BD%25D0%25B0_%25D0%259F%25D1%2580%25D0%25B0%25D0%25B2%25D0%25BE%25D0%25B1%25D0%25B5%25D1%2580%25D0%25B5%25D0%25B6%25D0%25BD%25D1%2596%25D0%25B9_%25D0%25A3%25D0%25BA%25D1%2580%25D0%25B0%25D1%2597%25D0%25BD%25D1%2596_%281699%29</t>
+  </si>
+  <si>
+    <t>https://ru.wikipedia.org/wiki/%25D0%259C%25D0%25B0%25D0%25B7%25D0%25B5%25D0%25BF%25D0%25B0%2C_%25D0%2598%25D0%25B2%25D0%25B0%25D0%25BD_%25D0%25A1%25D1%2582%25D0%25B5%25D0%25BF%25D0%25B0%25D0%25BD%25D0%25BE%25D0%25B2%25D0%25B8%25D1%2587</t>
+  </si>
+  <si>
     <t>https://uk.wikipedia.org/wiki/%25D0%259C%25D0%25B0%25D0%25BB%25D0%25BE%25D1%2580%25D0%25BE%25D1%2581%25D1%2596%25D0%25B9%25D1%2581%25D1%258C%25D0%25BA%25D0%25B5_%25D0%25B3%25D0%25B5%25D0%25BD%25D0%25B5%25D1%2580%25D0%25B0%25D0%25BB-%25D0%25B3%25D1%2583%25D0%25B1%25D0%25B5%25D1%2580%25D0%25BD%25D0%25B0%25D1%2582%25D0%25BE%25D1%2580%25D1%2581%25D1%2582%25D0%25B2%25D0%25BE</t>
   </si>
   <si>
     <t>https://uk.wikipedia.org/wiki/%25D0%259C%25D0%25B0%25D0%25BB%25D0%25BE%25D1%2580%25D0%25BE%25D1%2581%25D1%2596%25D0%25B9%25D1%2581%25D1%258C%25D0%25BA%25D0%25B8%25D0%25B9_%25D0%25BF%25D1%2580%25D0%25B8%25D0%25BA%25D0%25B0%25D0%25B7</t>
   </si>
   <si>
+    <t>https://uk.wikipedia.org/wiki/%D0%9C%D0%BE%D1%81%D0%BA%D0%BE%D0%B2%D1%81%D1%8C%D0%BA%D0%BE-%D1%83%D0%BA%D1%80%D0%B0%D1%97%D0%BD%D1%81%D1%8C%D0%BA%D0%B0_%D0%B2%D1%96%D0%B9%D0%BD%D0%B0_%281658%E2%80%941659%29</t>
+  </si>
+  <si>
+    <t>https://uk.wikipedia.org/wiki/%25D0%259C%25D0%25BE%25D1%2581%25D0%25BA%25D0%25BE%25D0%25B2%25D1%2581%25D1%258C%25D0%25BA%25D1%2596_%25D1%2581%25D1%2582%25D0%25B0%25D1%2582%25D1%2582%25D1%2596_%281665%29</t>
+  </si>
+  <si>
     <t>https://uk.wikipedia.org/wiki/%25D0%259D%25D0%25B0%25D1%2580%25D0%25BE%25D0%25B4%25D0%25BD%25D0%25B8%25D0%25B9_%25D1%2580%25D1%2583%25D1%2585_%25D0%25A3%25D0%25BA%25D1%2580%25D0%25B0%25D1%2597%25D0%25BD%25D0%25B8</t>
   </si>
   <si>
+    <t>http://resource.history.org.ua/publ/journal_1998_6_22</t>
+  </si>
+  <si>
     <t>https://ru.wikipedia.org/wiki/%25D0%259D%25D0%25BE%25D1%2580%25D0%25B8%25D0%25BB%25D1%258C%25D1%2581%25D0%25BA%25D0%25BE%25D0%25B5_%25D0%25B2%25D0%25BE%25D1%2581%25D1%2581%25D1%2582%25D0%25B0%25D0%25BD%25D0%25B8%25D0%25B5</t>
   </si>
   <si>
+    <t>https://uk.wikipedia.org/wiki/%25D0%259F%25D0%25B5%25D1%2580%25D0%25B5%25D0%25BF%25D0%25B8%25D1%2581_%25D0%25BD%25D0%25B0%25D1%2581%25D0%25B5%25D0%25BB%25D0%25B5%25D0%25BD%25D0%25BD%25D1%258F_%25D0%25A0%25D0%25BE%25D1%2581%25D1%2596%25D0%25B9%25D1%2581%25D1%258C%25D0%25BA%25D0%25BE%25D1%2597_%25D1%2596%25D0%25BC%25D0%25BF%25D0%25B5%25D1%2580%25D1%2596%25D1%2597_%281897%29</t>
+  </si>
+  <si>
     <t>https://uk.wikipedia.org/wiki/%D0%9F%D0%B5%D1%80%D0%B5%D1%8F%D1%81%D0%BB%D0%B0%D0%B2%D1%81%D1%8C%D0%BA%D0%B0_%D1%80%D0%B0%D0%B4%D0%B0</t>
   </si>
   <si>
+    <t>https://uk.wikipedia.org/wiki/%D0%9F%D0%B5%D1%80%D0%B5%D1%8F%D1%81%D0%BB%D0%B0%D0%B2%D1%81%D1%8C%D0%BA%D1%96_%D1%81%D1%82%D0%B0%D1%82%D1%82%D1%96_%281659%29</t>
+  </si>
+  <si>
     <t>https://ru.wikipedia.org/wiki/%25D0%259F%25D0%25B8%25D1%2581%25D1%258C%25D0%25BC%25D0%25BE-%25D0%25BF%25D1%2580%25D0%25BE%25D1%2582%25D0%25B5%25D1%2581%25D1%2582_139</t>
   </si>
   <si>
+    <t>https://uk.wikipedia.org/wiki/%25D0%259F%25D0%25BE%25D0%25B2%25D1%2581%25D1%2582%25D0%25B0%25D0%25BD%25D0%25BD%25D1%258F_%25D0%25B1%25D1%2583%25D0%25B7%25D1%258C%25D0%25BA%25D0%25B8%25D1%2585_%25D0%25BA%25D0%25BE%25D0%25B7%25D0%25B0%25D0%25BA%25D1%2596%25D0%25B2_%281817%29</t>
+  </si>
+  <si>
     <t>https://uk.wikipedia.org/wiki/%25D0%259F%25D0%25BE%25D0%25B4%25D1%2596%25D0%25BB%25D0%25B8_%25D0%25A0%25D0%25B5%25D1%2587%25D1%2596_%25D0%259F%25D0%25BE%25D1%2581%25D0%25BF%25D0%25BE%25D0%25BB%25D0%25B8%25D1%2582%25D0%25BE%25D1%2597</t>
   </si>
   <si>
+    <t>https://ru.wikipedia.org/wiki/%25D0%259F%25D0%25BE%25D0%25BB%25D1%258C%25D1%2581%25D0%25BA%25D0%25BE%25D0%25B5_%25D0%25B2%25D0%25BE%25D1%2581%25D1%2581%25D1%2582%25D0%25B0%25D0%25BD%25D0%25B8%25D0%25B5_%281863%25E2%2580%25941864%29</t>
+  </si>
+  <si>
+    <t>https://uk.wikipedia.org/wiki/%25D0%259F%25D0%25BE%25D1%2585%25D1%2596%25D0%25B4_%25D0%259F%25D0%25B8%25D0%25BB%25D0%25B8%25D0%25BF%25D0%25B0_%25D0%259E%25D1%2580%25D0%25BB%25D0%25B8%25D0%25BA%25D0%25B0_%25D0%25BD%25D0%25B0_%25D0%259F%25D1%2580%25D0%25B0%25D0%25B2%25D0%25BE%25D0%25B1%25D0%25B5%25D1%2580%25D0%25B5%25D0%25B6%25D0%25BD%25D1%2583_%25D0%25A3%25D0%25BA%25D1%2580%25D0%25B0%25D1%2597%25D0%25BD%25D1%2583_%281711%29</t>
+  </si>
+  <si>
     <t>https://uk.wikipedia.org/wiki/%25D0%259F%25D1%2580%25D0%25B0%25D0%25B2%25D0%25BB%25D1%2596%25D0%25BD%25D0%25BD%25D1%258F_%25D0%25B3%25D0%25B5%25D1%2582%25D1%258C%25D0%25BC%25D0%25B0%25D0%25BD%25D1%2581%25D1%258C%25D0%25BA%25D0%25BE%25D0%25B3%25D0%25BE_%25D1%2583%25D1%2580%25D1%258F%25D0%25B4%25D1%2583</t>
   </si>
   <si>
+    <t>https://uk.wikipedia.org/wiki/%25D0%259F%25D1%2596%25D0%25B2%25D0%25BD%25D1%2596%25D1%2587%25D0%25BD%25D0%25B0_%25D0%25B2%25D1%2596%25D0%25B9%25D0%25BD%25D0%25B0_%281700%25E2%2580%25941721%29</t>
+  </si>
+  <si>
     <t>https://uk.wikipedia.org/wiki/%25D0%25A0%25D0%25B5%25D1%2588%25D0%25B5%25D1%2582%25D0%25B8%25D0%25BB%25D1%2596%25D0%25B2%25D1%2581%25D1%258C%25D0%25BA%25D1%2596_%25D1%2581%25D1%2582%25D0%25B0%25D1%2582%25D1%2582%25D1%2596</t>
   </si>
   <si>
@@ -6394,9 +6643,21 @@
     <t>https://web.archive.org/web/20160304195659/http%3A//www.memo.ru/2010/09/27/rch.pdf</t>
   </si>
   <si>
+    <t>https://uk.wikipedia.org/wiki/%25D0%25A0%25D0%25BE%25D1%2581%25D1%2596%25D0%25B9%25D1%2581%25D1%258C%25D0%25BA%25D0%25BE-%25D1%2582%25D1%2583%25D1%2580%25D0%25B5%25D1%2586%25D1%258C%25D0%25BA%25D0%25B0_%25D0%25B2%25D1%2596%25D0%25B9%25D0%25BD%25D0%25B0_%281806%25E2%2580%25941812%29</t>
+  </si>
+  <si>
+    <t>https://uk.wikipedia.org/wiki/%25D0%25A0%25D0%25BE%25D1%2581%25D1%2596%25D0%25B9%25D1%2581%25D1%258C%25D0%25BA%25D0%25BE-%25D1%2583%25D0%25BA%25D1%2580%25D0%25B0%25D1%2597%25D0%25BD%25D1%2581%25D1%258C%25D0%25BA%25D0%25B0_%25D0%25B2%25D1%2596%25D0%25B9%25D0%25BD%25D0%25B0_%28%25D0%25B7_2014%29</t>
+  </si>
+  <si>
     <t>https://uk.wikipedia.org/wiki/%25D0%25A0%25D1%2583%25D1%2581%25D0%25B8%25D1%2584%25D1%2596%25D0%25BA%25D0%25B0%25D1%2586%25D1%2596%25D1%258F_%25D0%25A3%25D0%25BA%25D1%2580%25D0%25B0%25D1%2597%25D0%25BD%25D0%25B8</t>
   </si>
   <si>
+    <t>https://ru.wikipedia.org/wiki/%25D0%25A0%25D1%2583%25D1%2581%25D1%2581%25D0%25BA%25D0%25BE-%25D1%2582%25D1%2583%25D1%2580%25D0%25B5%25D1%2586%25D0%25BA%25D0%25B0%25D1%258F_%25D0%25B2%25D0%25BE%25D0%25B9%25D0%25BD%25D0%25B0_%281877%25E2%2580%25941878%29</t>
+  </si>
+  <si>
+    <t>https://ru.wikipedia.org/wiki/%25D0%25A0%25D1%2583%25D1%2581%25D1%2581%25D0%25BA%25D0%25BE-%25D1%2582%25D1%2583%25D1%2580%25D0%25B5%25D1%2586%25D0%25BA%25D0%25B0%25D1%258F_%25D0%25B2%25D0%25BE%25D0%25B9%25D0%25BD%25D0%25B0_%281768%25E2%2580%25941774%29</t>
+  </si>
+  <si>
     <t>https://uk.wikipedia.org/wiki/%D0%A0%D1%83%D1%97%D0%BD%D0%B0</t>
   </si>
   <si>
@@ -6419,6 +6680,9 @@
   </si>
   <si>
     <t>https://uk.wikipedia.org/wiki/%25D0%25A3%25D0%25BA%25D1%2580%25D0%25B0%25D1%2597%25D0%25BD%25D0%25B0_%25D0%25B2_%25D0%259F%25D0%25B5%25D1%2580%25D1%2588%25D1%2596%25D0%25B9_%25D1%2581%25D0%25B2%25D1%2596%25D1%2582%25D0%25BE%25D0%25B2%25D1%2596%25D0%25B9_%25D0%25B2%25D1%2596%25D0%25B9%25D0%25BD%25D1%2596</t>
+  </si>
+  <si>
+    <t>http://resource.history.org.ua/item/0016476</t>
   </si>
   <si>
     <t>https://uk.wikipedia.org/wiki/%25D0%25A3%25D0%25BA%25D1%2580%25D0%25B0%25D1%2597%25D0%25BD%25D0%25B0_%25D1%2583_%25D0%25B2%25D1%2596%25D0%25B9%25D0%25BD%25D0%25B0%25D1%2585_%25D0%259D%25D0%25B0%25D0%25BF%25D0%25BE%25D0%25BB%25D0%25B5%25D0%25BE%25D0%25BD%25D0%25B0</t>
@@ -48192,7 +48456,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C50"/>
+  <dimension ref="A1:C80"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -48211,10 +48475,10 @@
         <v>1994</v>
       </c>
       <c r="B2" t="s">
-        <v>2043</v>
+        <v>2073</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>2092</v>
+        <v>2152</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -48222,10 +48486,10 @@
         <v>1995</v>
       </c>
       <c r="B3" t="s">
-        <v>2044</v>
+        <v>2074</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>2093</v>
+        <v>2153</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -48233,10 +48497,10 @@
         <v>1996</v>
       </c>
       <c r="B4" t="s">
-        <v>2045</v>
+        <v>2075</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>2094</v>
+        <v>2154</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -48244,10 +48508,10 @@
         <v>1997</v>
       </c>
       <c r="B5" t="s">
-        <v>2046</v>
+        <v>2076</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>2095</v>
+        <v>2155</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -48255,10 +48519,10 @@
         <v>1998</v>
       </c>
       <c r="B6" t="s">
-        <v>2047</v>
+        <v>2077</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>2096</v>
+        <v>2156</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -48266,10 +48530,10 @@
         <v>1999</v>
       </c>
       <c r="B7" t="s">
-        <v>2048</v>
+        <v>2078</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>2097</v>
+        <v>2157</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -48277,10 +48541,10 @@
         <v>2000</v>
       </c>
       <c r="B8" t="s">
-        <v>2049</v>
+        <v>2079</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>2098</v>
+        <v>2158</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -48288,10 +48552,10 @@
         <v>2001</v>
       </c>
       <c r="B9" t="s">
-        <v>2050</v>
+        <v>2080</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>2099</v>
+        <v>2159</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -48299,7 +48563,10 @@
         <v>2002</v>
       </c>
       <c r="B10" t="s">
-        <v>2051</v>
+        <v>2081</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>2160</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -48307,10 +48574,10 @@
         <v>2003</v>
       </c>
       <c r="B11" t="s">
-        <v>2052</v>
+        <v>2082</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>2100</v>
+        <v>2161</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -48318,10 +48585,10 @@
         <v>2004</v>
       </c>
       <c r="B12" t="s">
-        <v>2053</v>
+        <v>2083</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>2101</v>
+        <v>2162</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -48329,10 +48596,10 @@
         <v>2005</v>
       </c>
       <c r="B13" t="s">
-        <v>2054</v>
+        <v>2084</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>2102</v>
+        <v>2163</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -48340,10 +48607,10 @@
         <v>2006</v>
       </c>
       <c r="B14" t="s">
-        <v>2055</v>
+        <v>2085</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>2103</v>
+        <v>2164</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -48351,10 +48618,10 @@
         <v>2007</v>
       </c>
       <c r="B15" t="s">
-        <v>2056</v>
+        <v>2086</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>2104</v>
+        <v>2165</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -48362,10 +48629,10 @@
         <v>2008</v>
       </c>
       <c r="B16" t="s">
-        <v>2057</v>
+        <v>2087</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>2105</v>
+        <v>2166</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -48373,7 +48640,7 @@
         <v>2009</v>
       </c>
       <c r="B17" t="s">
-        <v>2058</v>
+        <v>2088</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -48381,10 +48648,7 @@
         <v>2010</v>
       </c>
       <c r="B18" t="s">
-        <v>2059</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>2106</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -48392,10 +48656,10 @@
         <v>2011</v>
       </c>
       <c r="B19" t="s">
-        <v>2060</v>
+        <v>2090</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>2107</v>
+        <v>2167</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -48403,10 +48667,7 @@
         <v>2012</v>
       </c>
       <c r="B20" t="s">
-        <v>2061</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>2108</v>
+        <v>2091</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -48414,10 +48675,10 @@
         <v>2013</v>
       </c>
       <c r="B21" t="s">
-        <v>2062</v>
+        <v>2092</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>2109</v>
+        <v>2168</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -48425,10 +48686,10 @@
         <v>2014</v>
       </c>
       <c r="B22" t="s">
-        <v>2063</v>
+        <v>2093</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>2110</v>
+        <v>2169</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -48436,10 +48697,10 @@
         <v>2015</v>
       </c>
       <c r="B23" t="s">
-        <v>2064</v>
+        <v>2094</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>2111</v>
+        <v>2170</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -48447,10 +48708,10 @@
         <v>2016</v>
       </c>
       <c r="B24" t="s">
-        <v>2065</v>
+        <v>2095</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>2112</v>
+        <v>2171</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -48458,10 +48719,10 @@
         <v>2017</v>
       </c>
       <c r="B25" t="s">
-        <v>2066</v>
+        <v>2096</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>2113</v>
+        <v>2172</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -48469,7 +48730,10 @@
         <v>2018</v>
       </c>
       <c r="B26" t="s">
-        <v>2067</v>
+        <v>2097</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>2173</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -48477,10 +48741,7 @@
         <v>2019</v>
       </c>
       <c r="B27" t="s">
-        <v>2068</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>2114</v>
+        <v>2098</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -48488,10 +48749,10 @@
         <v>2020</v>
       </c>
       <c r="B28" t="s">
-        <v>2069</v>
+        <v>2099</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>2115</v>
+        <v>2174</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -48499,10 +48760,10 @@
         <v>2021</v>
       </c>
       <c r="B29" t="s">
-        <v>2070</v>
+        <v>2100</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>2116</v>
+        <v>2175</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -48510,10 +48771,10 @@
         <v>2022</v>
       </c>
       <c r="B30" t="s">
-        <v>2071</v>
+        <v>2101</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>2117</v>
+        <v>2176</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -48521,10 +48782,10 @@
         <v>2023</v>
       </c>
       <c r="B31" t="s">
-        <v>2072</v>
+        <v>2102</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>2118</v>
+        <v>2177</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -48532,10 +48793,10 @@
         <v>2024</v>
       </c>
       <c r="B32" t="s">
-        <v>2073</v>
+        <v>2103</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>2119</v>
+        <v>2178</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -48543,10 +48804,10 @@
         <v>2025</v>
       </c>
       <c r="B33" t="s">
-        <v>2074</v>
+        <v>2104</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>2120</v>
+        <v>2179</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -48554,10 +48815,10 @@
         <v>2026</v>
       </c>
       <c r="B34" t="s">
-        <v>2075</v>
+        <v>2105</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>2121</v>
+        <v>2180</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -48565,7 +48826,10 @@
         <v>2027</v>
       </c>
       <c r="B35" t="s">
-        <v>2076</v>
+        <v>2106</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>2181</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -48573,10 +48837,10 @@
         <v>2028</v>
       </c>
       <c r="B36" t="s">
-        <v>2077</v>
+        <v>2107</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>2122</v>
+        <v>2182</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -48584,10 +48848,10 @@
         <v>2029</v>
       </c>
       <c r="B37" t="s">
-        <v>2078</v>
+        <v>2108</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>2123</v>
+        <v>2183</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -48595,10 +48859,10 @@
         <v>2030</v>
       </c>
       <c r="B38" t="s">
-        <v>2079</v>
+        <v>2109</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>2124</v>
+        <v>2184</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -48606,10 +48870,10 @@
         <v>2031</v>
       </c>
       <c r="B39" t="s">
-        <v>2080</v>
+        <v>2110</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>2125</v>
+        <v>2185</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -48617,10 +48881,10 @@
         <v>2032</v>
       </c>
       <c r="B40" t="s">
-        <v>2081</v>
+        <v>2111</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>2126</v>
+        <v>2186</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -48628,10 +48892,7 @@
         <v>2033</v>
       </c>
       <c r="B41" t="s">
-        <v>2082</v>
-      </c>
-      <c r="C41" s="1" t="s">
-        <v>2127</v>
+        <v>2112</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -48639,10 +48900,10 @@
         <v>2034</v>
       </c>
       <c r="B42" t="s">
-        <v>2083</v>
+        <v>2113</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>2128</v>
+        <v>2187</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -48650,10 +48911,10 @@
         <v>2035</v>
       </c>
       <c r="B43" t="s">
-        <v>2084</v>
+        <v>2114</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>2129</v>
+        <v>2188</v>
       </c>
     </row>
     <row r="44" spans="1:3">
@@ -48661,10 +48922,10 @@
         <v>2036</v>
       </c>
       <c r="B44" t="s">
-        <v>2085</v>
+        <v>2115</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>2130</v>
+        <v>2189</v>
       </c>
     </row>
     <row r="45" spans="1:3">
@@ -48672,10 +48933,10 @@
         <v>2037</v>
       </c>
       <c r="B45" t="s">
-        <v>2086</v>
+        <v>2116</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>2131</v>
+        <v>2190</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -48683,10 +48944,10 @@
         <v>2038</v>
       </c>
       <c r="B46" t="s">
-        <v>2087</v>
+        <v>2117</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>2132</v>
+        <v>2191</v>
       </c>
     </row>
     <row r="47" spans="1:3">
@@ -48694,10 +48955,10 @@
         <v>2039</v>
       </c>
       <c r="B47" t="s">
-        <v>2088</v>
+        <v>2118</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>2133</v>
+        <v>2192</v>
       </c>
     </row>
     <row r="48" spans="1:3">
@@ -48705,10 +48966,10 @@
         <v>2040</v>
       </c>
       <c r="B48" t="s">
-        <v>2089</v>
+        <v>2119</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>2134</v>
+        <v>2193</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -48716,10 +48977,10 @@
         <v>2041</v>
       </c>
       <c r="B49" t="s">
-        <v>2090</v>
+        <v>2120</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>2135</v>
+        <v>2194</v>
       </c>
     </row>
     <row r="50" spans="1:3">
@@ -48727,10 +48988,337 @@
         <v>2042</v>
       </c>
       <c r="B50" t="s">
-        <v>2091</v>
+        <v>2121</v>
       </c>
       <c r="C50" s="1" t="s">
+        <v>2195</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3">
+      <c r="A51" t="s">
+        <v>2043</v>
+      </c>
+      <c r="B51" t="s">
+        <v>2122</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>2196</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3">
+      <c r="A52" t="s">
+        <v>2044</v>
+      </c>
+      <c r="B52" t="s">
+        <v>2123</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>2197</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3">
+      <c r="A53" t="s">
+        <v>2045</v>
+      </c>
+      <c r="B53" t="s">
+        <v>2124</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>2198</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3">
+      <c r="A54" t="s">
+        <v>2046</v>
+      </c>
+      <c r="B54" t="s">
+        <v>2125</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>2199</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3">
+      <c r="A55" t="s">
+        <v>2047</v>
+      </c>
+      <c r="B55" t="s">
+        <v>2126</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>2200</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3">
+      <c r="A56" t="s">
+        <v>2048</v>
+      </c>
+      <c r="B56" t="s">
+        <v>2127</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>2201</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3">
+      <c r="A57" t="s">
+        <v>2049</v>
+      </c>
+      <c r="B57" t="s">
+        <v>2128</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>2202</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3">
+      <c r="A58" t="s">
+        <v>2050</v>
+      </c>
+      <c r="B58" t="s">
+        <v>2129</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>2203</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3">
+      <c r="A59" t="s">
+        <v>2051</v>
+      </c>
+      <c r="B59" t="s">
+        <v>2130</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>2204</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3">
+      <c r="A60" t="s">
+        <v>2052</v>
+      </c>
+      <c r="B60" t="s">
+        <v>2131</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3">
+      <c r="A61" t="s">
+        <v>2053</v>
+      </c>
+      <c r="B61" t="s">
+        <v>2132</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>2205</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3">
+      <c r="A62" t="s">
+        <v>2054</v>
+      </c>
+      <c r="B62" t="s">
+        <v>2133</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>2206</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3">
+      <c r="A63" t="s">
+        <v>2055</v>
+      </c>
+      <c r="B63" t="s">
+        <v>2134</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>2207</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3">
+      <c r="A64" t="s">
+        <v>2056</v>
+      </c>
+      <c r="B64" t="s">
+        <v>2135</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>2208</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3">
+      <c r="A65" t="s">
+        <v>2057</v>
+      </c>
+      <c r="B65" t="s">
         <v>2136</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>2209</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3">
+      <c r="A66" t="s">
+        <v>2058</v>
+      </c>
+      <c r="B66" t="s">
+        <v>2137</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>2210</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3">
+      <c r="A67" t="s">
+        <v>2059</v>
+      </c>
+      <c r="B67" t="s">
+        <v>2138</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>2211</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3">
+      <c r="A68" t="s">
+        <v>2060</v>
+      </c>
+      <c r="B68" t="s">
+        <v>2139</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>2212</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3">
+      <c r="A69" t="s">
+        <v>2061</v>
+      </c>
+      <c r="B69" t="s">
+        <v>2140</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>2213</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3">
+      <c r="A70" t="s">
+        <v>2062</v>
+      </c>
+      <c r="B70" t="s">
+        <v>2141</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>2214</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3">
+      <c r="A71" t="s">
+        <v>2063</v>
+      </c>
+      <c r="B71" t="s">
+        <v>2142</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>2215</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3">
+      <c r="A72" t="s">
+        <v>2064</v>
+      </c>
+      <c r="B72" t="s">
+        <v>2143</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>2216</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3">
+      <c r="A73" t="s">
+        <v>2065</v>
+      </c>
+      <c r="B73" t="s">
+        <v>2144</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>2217</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3">
+      <c r="A74" t="s">
+        <v>2066</v>
+      </c>
+      <c r="B74" t="s">
+        <v>2145</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>2218</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3">
+      <c r="A75" t="s">
+        <v>2067</v>
+      </c>
+      <c r="B75" t="s">
+        <v>2146</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>2219</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3">
+      <c r="A76" t="s">
+        <v>2068</v>
+      </c>
+      <c r="B76" t="s">
+        <v>2147</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>2220</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3">
+      <c r="A77" t="s">
+        <v>2069</v>
+      </c>
+      <c r="B77" t="s">
+        <v>2148</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>2221</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3">
+      <c r="A78" t="s">
+        <v>2070</v>
+      </c>
+      <c r="B78" t="s">
+        <v>2149</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>2222</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3">
+      <c r="A79" t="s">
+        <v>2071</v>
+      </c>
+      <c r="B79" t="s">
+        <v>2150</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>2223</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3">
+      <c r="A80" t="s">
+        <v>2072</v>
+      </c>
+      <c r="B80" t="s">
+        <v>2151</v>
+      </c>
+      <c r="C80" s="1" t="s">
+        <v>2224</v>
       </c>
     </row>
   </sheetData>
@@ -48743,43 +49331,71 @@
     <hyperlink ref="C7" r:id="rId6"/>
     <hyperlink ref="C8" r:id="rId7"/>
     <hyperlink ref="C9" r:id="rId8"/>
-    <hyperlink ref="C11" r:id="rId9"/>
-    <hyperlink ref="C12" r:id="rId10"/>
-    <hyperlink ref="C13" r:id="rId11"/>
-    <hyperlink ref="C14" r:id="rId12"/>
-    <hyperlink ref="C15" r:id="rId13"/>
-    <hyperlink ref="C16" r:id="rId14"/>
-    <hyperlink ref="C18" r:id="rId15"/>
+    <hyperlink ref="C10" r:id="rId9"/>
+    <hyperlink ref="C11" r:id="rId10"/>
+    <hyperlink ref="C12" r:id="rId11"/>
+    <hyperlink ref="C13" r:id="rId12"/>
+    <hyperlink ref="C14" r:id="rId13"/>
+    <hyperlink ref="C15" r:id="rId14"/>
+    <hyperlink ref="C16" r:id="rId15"/>
     <hyperlink ref="C19" r:id="rId16"/>
-    <hyperlink ref="C20" r:id="rId17"/>
-    <hyperlink ref="C21" r:id="rId18"/>
-    <hyperlink ref="C22" r:id="rId19"/>
-    <hyperlink ref="C23" r:id="rId20"/>
-    <hyperlink ref="C24" r:id="rId21"/>
-    <hyperlink ref="C25" r:id="rId22"/>
-    <hyperlink ref="C27" r:id="rId23"/>
-    <hyperlink ref="C28" r:id="rId24"/>
-    <hyperlink ref="C29" r:id="rId25"/>
-    <hyperlink ref="C30" r:id="rId26"/>
-    <hyperlink ref="C31" r:id="rId27"/>
-    <hyperlink ref="C32" r:id="rId28"/>
-    <hyperlink ref="C33" r:id="rId29"/>
-    <hyperlink ref="C34" r:id="rId30"/>
+    <hyperlink ref="C21" r:id="rId17"/>
+    <hyperlink ref="C22" r:id="rId18"/>
+    <hyperlink ref="C23" r:id="rId19"/>
+    <hyperlink ref="C24" r:id="rId20"/>
+    <hyperlink ref="C25" r:id="rId21"/>
+    <hyperlink ref="C26" r:id="rId22"/>
+    <hyperlink ref="C28" r:id="rId23"/>
+    <hyperlink ref="C29" r:id="rId24"/>
+    <hyperlink ref="C30" r:id="rId25"/>
+    <hyperlink ref="C31" r:id="rId26"/>
+    <hyperlink ref="C32" r:id="rId27"/>
+    <hyperlink ref="C33" r:id="rId28"/>
+    <hyperlink ref="C34" r:id="rId29"/>
+    <hyperlink ref="C35" r:id="rId30"/>
     <hyperlink ref="C36" r:id="rId31"/>
     <hyperlink ref="C37" r:id="rId32"/>
     <hyperlink ref="C38" r:id="rId33"/>
     <hyperlink ref="C39" r:id="rId34"/>
     <hyperlink ref="C40" r:id="rId35"/>
-    <hyperlink ref="C41" r:id="rId36"/>
-    <hyperlink ref="C42" r:id="rId37"/>
-    <hyperlink ref="C43" r:id="rId38"/>
-    <hyperlink ref="C44" r:id="rId39"/>
-    <hyperlink ref="C45" r:id="rId40"/>
-    <hyperlink ref="C46" r:id="rId41"/>
-    <hyperlink ref="C47" r:id="rId42"/>
-    <hyperlink ref="C48" r:id="rId43"/>
-    <hyperlink ref="C49" r:id="rId44"/>
-    <hyperlink ref="C50" r:id="rId45"/>
+    <hyperlink ref="C42" r:id="rId36"/>
+    <hyperlink ref="C43" r:id="rId37"/>
+    <hyperlink ref="C44" r:id="rId38"/>
+    <hyperlink ref="C45" r:id="rId39"/>
+    <hyperlink ref="C46" r:id="rId40"/>
+    <hyperlink ref="C47" r:id="rId41"/>
+    <hyperlink ref="C48" r:id="rId42"/>
+    <hyperlink ref="C49" r:id="rId43"/>
+    <hyperlink ref="C50" r:id="rId44"/>
+    <hyperlink ref="C51" r:id="rId45"/>
+    <hyperlink ref="C52" r:id="rId46"/>
+    <hyperlink ref="C53" r:id="rId47"/>
+    <hyperlink ref="C54" r:id="rId48"/>
+    <hyperlink ref="C55" r:id="rId49"/>
+    <hyperlink ref="C56" r:id="rId50"/>
+    <hyperlink ref="C57" r:id="rId51"/>
+    <hyperlink ref="C58" r:id="rId52"/>
+    <hyperlink ref="C59" r:id="rId53"/>
+    <hyperlink ref="C61" r:id="rId54"/>
+    <hyperlink ref="C62" r:id="rId55"/>
+    <hyperlink ref="C63" r:id="rId56"/>
+    <hyperlink ref="C64" r:id="rId57"/>
+    <hyperlink ref="C65" r:id="rId58"/>
+    <hyperlink ref="C66" r:id="rId59"/>
+    <hyperlink ref="C67" r:id="rId60"/>
+    <hyperlink ref="C68" r:id="rId61"/>
+    <hyperlink ref="C69" r:id="rId62"/>
+    <hyperlink ref="C70" r:id="rId63"/>
+    <hyperlink ref="C71" r:id="rId64"/>
+    <hyperlink ref="C72" r:id="rId65"/>
+    <hyperlink ref="C73" r:id="rId66"/>
+    <hyperlink ref="C74" r:id="rId67"/>
+    <hyperlink ref="C75" r:id="rId68"/>
+    <hyperlink ref="C76" r:id="rId69"/>
+    <hyperlink ref="C77" r:id="rId70"/>
+    <hyperlink ref="C78" r:id="rId71"/>
+    <hyperlink ref="C79" r:id="rId72"/>
+    <hyperlink ref="C80" r:id="rId73"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docs/attack-excel-files/v18.1/russia-colonialism/russia-colonialism-v18.1-relationships.xlsx
+++ b/docs/attack-excel-files/v18.1/russia-colonialism/russia-colonialism-v18.1-relationships.xlsx
@@ -782,367 +782,367 @@
     <t>Царская канцелярия</t>
   </si>
   <si>
-    <t>campaign--d5d3608b-1e2e-4e8e-9e3e-172b7ae8783f</t>
-  </si>
-  <si>
-    <t>campaign--da1bd8ae-397a-4c07-81d5-4ee62243c68b</t>
-  </si>
-  <si>
-    <t>campaign--6ba841e9-a6e2-4de1-ae16-ca96739e35ed</t>
-  </si>
-  <si>
-    <t>campaign--d25e87a6-7133-4e11-8e93-259d4f2bd994</t>
-  </si>
-  <si>
-    <t>campaign--327371af-9be7-44c2-8b57-7e51eea988c4</t>
-  </si>
-  <si>
-    <t>campaign--e31b1ed6-33c7-4d93-a2c6-a9b1dac0ac8c</t>
-  </si>
-  <si>
-    <t>campaign--000c635b-27f2-43b1-b98d-ff81a4105054</t>
-  </si>
-  <si>
-    <t>campaign--13625203-0aca-405b-9409-d6bb04dedcc2</t>
-  </si>
-  <si>
-    <t>campaign--c89888d0-b5d3-4947-b33d-d1d066710b8d</t>
-  </si>
-  <si>
-    <t>campaign--5b0cdeff-e761-4c3f-ba0c-feaec1ead563</t>
-  </si>
-  <si>
-    <t>campaign--cbda1a24-f09e-414b-ab6c-1177afcf6579</t>
-  </si>
-  <si>
-    <t>campaign--477d33b8-e868-4f14-994c-3ff87914d154</t>
-  </si>
-  <si>
-    <t>campaign--d07a6a51-42fd-4fca-9e60-9f47a2f3d55b</t>
-  </si>
-  <si>
-    <t>campaign--6dc22dba-186d-44f2-b8e5-932b3d3ae163</t>
-  </si>
-  <si>
-    <t>campaign--30e8ed62-d3e8-4143-9e5e-632bd7aa23cc</t>
-  </si>
-  <si>
-    <t>campaign--5a248622-bb69-496e-b7a9-6563aebba048</t>
-  </si>
-  <si>
-    <t>campaign--35ebb683-a8d6-4486-b3b2-f449826b17ce</t>
-  </si>
-  <si>
-    <t>campaign--9d8a0b71-9771-4b85-a072-eb7f2ebaaa79</t>
-  </si>
-  <si>
-    <t>campaign--04b69ccd-9489-447b-99a2-77765d33a863</t>
-  </si>
-  <si>
-    <t>campaign--e29a7c8b-78d8-4200-a28e-b29c47fd3db4</t>
-  </si>
-  <si>
-    <t>campaign--bee06f63-5b9a-40ee-8ded-3807e18b2794</t>
-  </si>
-  <si>
-    <t>campaign--12a31509-f6b1-4af2-ba71-d0d3f1a7e55c</t>
-  </si>
-  <si>
-    <t>campaign--cfd8e869-e600-4d3e-ab87-ab274a92891e</t>
-  </si>
-  <si>
-    <t>campaign--6569f13e-42ba-41d7-a075-7940b2fa7c53</t>
-  </si>
-  <si>
-    <t>campaign--b375cce2-197a-4d61-84e5-bc95c4f061aa</t>
-  </si>
-  <si>
-    <t>campaign--d1be4871-85b3-4161-b768-fcbdd3f3d268</t>
-  </si>
-  <si>
-    <t>campaign--b4a7dd59-002b-4a93-b13c-ab142a60073b</t>
-  </si>
-  <si>
-    <t>campaign--a06fac12-cd5a-4e5a-b61a-efbc0cd5c005</t>
-  </si>
-  <si>
-    <t>campaign--380516f0-c58a-4738-90e3-693af3883357</t>
-  </si>
-  <si>
-    <t>campaign--20b012fa-ab52-4e32-8992-ea76da37110f</t>
-  </si>
-  <si>
-    <t>campaign--d726fa7f-7c1c-4924-88a6-74444222bd9f</t>
-  </si>
-  <si>
-    <t>campaign--0a86d435-8e69-4f3a-bc96-b3ac668c82bc</t>
-  </si>
-  <si>
-    <t>campaign--fa5a41c0-90cb-4caf-860d-a3428108338f</t>
-  </si>
-  <si>
-    <t>campaign--93b9db3d-54e0-4cd1-a73d-8da9102e4009</t>
-  </si>
-  <si>
-    <t>campaign--2e5633ce-2d35-42b6-9ef4-0bf9c8b1bf35</t>
-  </si>
-  <si>
-    <t>campaign--cb207683-dcc4-4b73-ac2f-0be500edc74f</t>
-  </si>
-  <si>
-    <t>campaign--afb7bd59-6c2a-440a-a21d-5961efba5eff</t>
-  </si>
-  <si>
-    <t>campaign--43bcd15c-cf4f-4445-acbd-65ae81877442</t>
-  </si>
-  <si>
-    <t>campaign--d81de34f-47cd-428a-a41a-09a6f56a9da7</t>
-  </si>
-  <si>
-    <t>campaign--034fab01-25ca-406a-af72-18424cd8865e</t>
-  </si>
-  <si>
-    <t>campaign--65f10cf2-b7b9-4bba-99bd-850bd647691e</t>
-  </si>
-  <si>
-    <t>campaign--5a7b9428-869c-4411-836b-ac68418c3e88</t>
-  </si>
-  <si>
-    <t>campaign--993b7232-af60-4415-a814-7856a5aac9b0</t>
-  </si>
-  <si>
-    <t>campaign--adcbb713-6625-4bb2-bbdb-ca95dce75216</t>
-  </si>
-  <si>
-    <t>campaign--fc8f6110-efac-4b90-b548-1454dac7a19b</t>
-  </si>
-  <si>
-    <t>campaign--5c62e27c-a9a5-4f3d-8c9b-c9e0b90a244b</t>
-  </si>
-  <si>
-    <t>campaign--4ef7374d-4184-4e74-8a4d-61459b26d02f</t>
-  </si>
-  <si>
-    <t>campaign--cfee05cb-c034-4971-a531-902e845ccef3</t>
-  </si>
-  <si>
-    <t>campaign--34f93fca-7d2a-4e55-bc81-7f5697e97ef5</t>
-  </si>
-  <si>
-    <t>campaign--6664b694-3b86-465b-9e27-aea2b4bb1daa</t>
-  </si>
-  <si>
-    <t>campaign--3f943474-7a02-49f9-95d4-6284c13fcf28</t>
-  </si>
-  <si>
-    <t>campaign--8260bb29-de17-4c6d-8152-bcfe4b2b99ab</t>
-  </si>
-  <si>
-    <t>campaign--249316b5-9848-4974-bb96-36f491ad2ff3</t>
-  </si>
-  <si>
-    <t>campaign--51f52048-db4e-4bb3-a9d3-9c3ef5a7efdf</t>
-  </si>
-  <si>
-    <t>campaign--62d59075-a1be-4fc3-bb73-dfbba3d9890f</t>
-  </si>
-  <si>
-    <t>campaign--620a3478-b534-42fe-ae16-eef44729927d</t>
-  </si>
-  <si>
-    <t>campaign--33d73442-ef8e-4272-9b52-8409285e64d4</t>
-  </si>
-  <si>
-    <t>campaign--dde6e95d-8a5e-4d08-9cec-a7ff943a6316</t>
-  </si>
-  <si>
-    <t>campaign--451c6e51-6fd7-493b-82dd-f5b2d321469c</t>
-  </si>
-  <si>
-    <t>campaign--999f0ed3-c7f6-4cbe-b1a2-d7d8d6eedf7b</t>
-  </si>
-  <si>
-    <t>campaign--324dfd0b-8bb9-4e73-b770-c4878fa141b3</t>
-  </si>
-  <si>
-    <t>campaign--e48baa05-e5ad-4906-b269-18674c9abe58</t>
-  </si>
-  <si>
-    <t>campaign--5ac2c3e0-9d38-426d-81e5-09cf5a941ae2</t>
-  </si>
-  <si>
-    <t>campaign--b98a9b9a-6b83-45f6-b65e-38d9bffe4df7</t>
-  </si>
-  <si>
-    <t>campaign--71c8fe9d-7933-4793-8688-8ab211e64903</t>
-  </si>
-  <si>
-    <t>campaign--f8715c92-b16d-427b-8db4-e3a8d3c8f294</t>
-  </si>
-  <si>
-    <t>campaign--4d0ec18b-c72b-4515-9f5d-4246894f9414</t>
-  </si>
-  <si>
-    <t>campaign--d55f729d-5ef5-4b86-a509-1a176d91bbf5</t>
-  </si>
-  <si>
-    <t>campaign--5f5df72e-1fe1-43dd-82d6-8d828a183ff5</t>
-  </si>
-  <si>
-    <t>campaign--6c70c6bf-d458-4a42-a588-2d462edf232e</t>
-  </si>
-  <si>
-    <t>campaign--3e59ca2e-eae8-41fa-b2ec-cb039c9b4210</t>
-  </si>
-  <si>
-    <t>campaign--89ab3728-120a-41b6-b6f8-eee58aa5bf75</t>
-  </si>
-  <si>
-    <t>campaign--15dd6c2c-0e8f-4497-8d49-119a63052355</t>
-  </si>
-  <si>
-    <t>campaign--f5969a82-f450-48d2-a83f-31c2c2fcfc5a</t>
-  </si>
-  <si>
-    <t>campaign--8df71303-011a-488a-a3d5-cfabdf43a3bc</t>
-  </si>
-  <si>
-    <t>campaign--d59baa17-740d-4701-ac73-c8a740a1902e</t>
-  </si>
-  <si>
-    <t>campaign--bb2e0c40-4185-4a26-9a4a-843f0f42fb91</t>
-  </si>
-  <si>
-    <t>campaign--1c942e99-7fdf-43c2-a1c7-0c036960d550</t>
-  </si>
-  <si>
-    <t>campaign--2587cdb8-4685-4f49-ad80-4cf1673de499</t>
-  </si>
-  <si>
-    <t>campaign--4850b46c-5052-41fe-8b42-439a1d32be7b</t>
-  </si>
-  <si>
-    <t>campaign--160fbc62-8a4d-4576-86c8-bb6e8212b355</t>
-  </si>
-  <si>
-    <t>campaign--f726e55f-ac4b-4710-9b09-6b1bd5d7aca3</t>
-  </si>
-  <si>
-    <t>campaign--b12ec413-1bd9-46dd-b084-f775d59555ce</t>
-  </si>
-  <si>
-    <t>campaign--4b166b15-a737-4bfc-a873-ce378b04442b</t>
-  </si>
-  <si>
-    <t>campaign--7f39ffcb-c876-4ac1-97c7-77225d687cf7</t>
-  </si>
-  <si>
-    <t>campaign--c6287a90-fda2-414b-9536-7e8d7b333225</t>
-  </si>
-  <si>
-    <t>campaign--bfff8349-9b26-4bec-993e-4d3fb7792a21</t>
-  </si>
-  <si>
-    <t>campaign--a88279c6-8e3a-4610-98b4-61afdf9b1b00</t>
-  </si>
-  <si>
-    <t>campaign--a7923c48-f560-4ecf-99f5-9b6a59a4c658</t>
-  </si>
-  <si>
-    <t>campaign--bf2d7f34-0a40-4a70-8642-f68ef8dae022</t>
-  </si>
-  <si>
-    <t>campaign--86b88822-1271-4a0b-b652-bac9d6c1e4e8</t>
-  </si>
-  <si>
-    <t>campaign--ab434fb0-c7d3-4c1c-bcbd-c4c4498cf657</t>
-  </si>
-  <si>
-    <t>campaign--a156a043-c7da-45b0-aa0a-5299ead941bb</t>
-  </si>
-  <si>
-    <t>campaign--0cfea08d-0a35-4a62-a6b8-66a75b949383</t>
-  </si>
-  <si>
-    <t>campaign--8a97f881-3742-4d79-9bf1-0d2b3f8bacfe</t>
-  </si>
-  <si>
-    <t>campaign--b12ceb44-a32c-43df-82b7-e817321bdc3c</t>
-  </si>
-  <si>
-    <t>campaign--9c6d7b3b-bfe7-43c5-9b32-9928bf384cb3</t>
-  </si>
-  <si>
-    <t>campaign--2df6168b-6e9d-456f-a84a-30638a365400</t>
-  </si>
-  <si>
-    <t>campaign--d10ef172-c6c8-4f61-9f6c-4be1a77043ec</t>
-  </si>
-  <si>
-    <t>campaign--eecb9861-e70e-403d-bf70-88d38775c3b5</t>
-  </si>
-  <si>
-    <t>campaign--9a356b3e-0022-416c-bda6-336376c7b0f7</t>
-  </si>
-  <si>
-    <t>campaign--3b1dfe61-fc96-495a-92c1-e9617744d5b3</t>
-  </si>
-  <si>
-    <t>intrusion-set--3642f171-4667-4b82-b3c5-73f7f518396b</t>
-  </si>
-  <si>
-    <t>intrusion-set--224aa639-ced9-4891-bc3c-72ee1592cf05</t>
-  </si>
-  <si>
-    <t>intrusion-set--e3bc6b24-7eb3-408b-af74-b5924d08cd07</t>
-  </si>
-  <si>
-    <t>intrusion-set--1be81b91-037a-46a1-8e5e-b282c40ea297</t>
-  </si>
-  <si>
-    <t>intrusion-set--243887eb-e4f8-4b0e-a6d2-843e9676f671</t>
-  </si>
-  <si>
-    <t>intrusion-set--8b5f0098-75af-4fcd-9c7f-88149768cd8b</t>
-  </si>
-  <si>
-    <t>tool--b4c0d62c-b3f5-4069-a07d-c7e9a48427e5</t>
-  </si>
-  <si>
-    <t>tool--5c43501c-aa32-48a4-a151-6c6897e3b0dd</t>
-  </si>
-  <si>
-    <t>tool--e5929876-f3ec-466c-90a8-ec4a16cd8ac7</t>
-  </si>
-  <si>
-    <t>tool--5dcf4786-4e1a-44f2-8aa0-e4b5fdf1f93f</t>
-  </si>
-  <si>
-    <t>tool--d57519cc-1898-4106-8e8b-4798bf53d3b4</t>
-  </si>
-  <si>
-    <t>tool--4ba8494b-f590-4308-868c-37a12508f6a3</t>
-  </si>
-  <si>
-    <t>tool--fd9d33aa-46ee-48a8-b37c-b5813b8dd7cb</t>
-  </si>
-  <si>
-    <t>tool--af3c7286-be13-4569-ac9d-c96ebbac6a34</t>
-  </si>
-  <si>
-    <t>tool--413178e7-81d2-4bdd-ab53-c632febad570</t>
-  </si>
-  <si>
-    <t>tool--4ebdeb25-4eb2-43cd-a70b-e019e1a4ef6c</t>
-  </si>
-  <si>
-    <t>tool--5ceff728-9a89-463d-b71b-79b952d31693</t>
-  </si>
-  <si>
-    <t>tool--ff0e5cd8-b850-4df9-845a-ab14c6ba2104</t>
-  </si>
-  <si>
-    <t>tool--2de74860-9286-45c7-b350-d41ae6685351</t>
+    <t>campaign--97185b62-b756-44d3-b841-c26ff2caa435</t>
+  </si>
+  <si>
+    <t>campaign--28368dc3-bac3-40ca-9be2-53cd5b18ae5a</t>
+  </si>
+  <si>
+    <t>campaign--3e7aca06-438d-4972-b481-5eef5dddab91</t>
+  </si>
+  <si>
+    <t>campaign--42c2db2c-bca8-4f4c-90a1-feed7ccb5499</t>
+  </si>
+  <si>
+    <t>campaign--0e489ab4-57c8-4ea9-b1c1-35a091e8dcf5</t>
+  </si>
+  <si>
+    <t>campaign--3951c130-926c-4354-b30a-d9b845e20711</t>
+  </si>
+  <si>
+    <t>campaign--5df5ab6d-110b-41b0-914c-d68a42814b3f</t>
+  </si>
+  <si>
+    <t>campaign--332047f3-d991-48d5-a8d0-d626d70b1520</t>
+  </si>
+  <si>
+    <t>campaign--35760d2a-4bf9-493b-ab94-fa67c4ff8fcd</t>
+  </si>
+  <si>
+    <t>campaign--780db662-7237-47c6-9d76-e0a9c213b1ca</t>
+  </si>
+  <si>
+    <t>campaign--d38fee72-8a5f-42cd-a0e6-08b3642e49e2</t>
+  </si>
+  <si>
+    <t>campaign--ae71667a-64b0-4a35-bd4b-2212af26d6f2</t>
+  </si>
+  <si>
+    <t>campaign--1063f60a-3894-4344-97eb-1a62a8d09e50</t>
+  </si>
+  <si>
+    <t>campaign--1f2bd0e1-55a3-4605-9910-a28c81b3aba4</t>
+  </si>
+  <si>
+    <t>campaign--21ac6d95-7b1e-4b4a-a039-c789d4ded516</t>
+  </si>
+  <si>
+    <t>campaign--7fc58166-effa-406a-8ca4-a7e4fb477a96</t>
+  </si>
+  <si>
+    <t>campaign--374ff3ac-7e13-4ceb-870a-1c25a5e81f45</t>
+  </si>
+  <si>
+    <t>campaign--2514ee85-51a9-477d-893a-bb45313d0bd5</t>
+  </si>
+  <si>
+    <t>campaign--89014d54-7b08-4fba-83ac-c8722773fad8</t>
+  </si>
+  <si>
+    <t>campaign--ba097673-a412-4203-bb06-447f860a51d3</t>
+  </si>
+  <si>
+    <t>campaign--a55ffc4f-129f-4d38-8324-fdd1ebbb5a4b</t>
+  </si>
+  <si>
+    <t>campaign--01e2f625-82e2-488e-8622-00ebde701e23</t>
+  </si>
+  <si>
+    <t>campaign--fd958d24-a4bf-4243-ae08-e860c13ea805</t>
+  </si>
+  <si>
+    <t>campaign--a6face44-139d-466a-a5ff-e8c3ff709ace</t>
+  </si>
+  <si>
+    <t>campaign--a413d1f2-8330-4668-b8bd-fd8086250234</t>
+  </si>
+  <si>
+    <t>campaign--48e3bbbf-203d-40a1-bc6d-aa8b18e5598e</t>
+  </si>
+  <si>
+    <t>campaign--08d1bb96-2342-4cdb-b6b9-55a161a88419</t>
+  </si>
+  <si>
+    <t>campaign--76935537-cdec-406c-9f4a-a4cbc121cc00</t>
+  </si>
+  <si>
+    <t>campaign--f4466bbc-027a-4e44-935a-035f903ef19e</t>
+  </si>
+  <si>
+    <t>campaign--c7e7bcde-9c6c-437b-ad59-5e5bd2d5c514</t>
+  </si>
+  <si>
+    <t>campaign--236b5c9a-15f6-43ce-9667-200af4732480</t>
+  </si>
+  <si>
+    <t>campaign--b8c59485-94d3-40a6-b0fc-23d338986d1f</t>
+  </si>
+  <si>
+    <t>campaign--167376d8-aab7-4cbb-b314-230969e6a7a3</t>
+  </si>
+  <si>
+    <t>campaign--b2510237-29ac-4193-8722-444a86b52190</t>
+  </si>
+  <si>
+    <t>campaign--c8bcfd3d-d39b-4d28-9b5c-c5f3e8e0728f</t>
+  </si>
+  <si>
+    <t>campaign--8432f3de-ec66-4e20-88e9-54ed4587df9b</t>
+  </si>
+  <si>
+    <t>campaign--5bf5d20e-3e8f-4b7f-beb9-1a3189e2cadf</t>
+  </si>
+  <si>
+    <t>campaign--5f5766b1-030a-4e87-b165-48a1f821e9a6</t>
+  </si>
+  <si>
+    <t>campaign--ac432357-fb30-4c0f-9123-ff894b2784de</t>
+  </si>
+  <si>
+    <t>campaign--4bc43f67-3dc2-4c2b-9539-a42ff3e48f8f</t>
+  </si>
+  <si>
+    <t>campaign--a89eb731-49da-49ec-94fd-10f7ec7e3212</t>
+  </si>
+  <si>
+    <t>campaign--db4a09bc-80d8-443b-8be6-9a04e643eab5</t>
+  </si>
+  <si>
+    <t>campaign--0c92bef0-ae48-4178-a4e8-2845fe5e43ba</t>
+  </si>
+  <si>
+    <t>campaign--1a54b369-cecd-4acf-aeeb-addc0eee2b65</t>
+  </si>
+  <si>
+    <t>campaign--fc415691-46e4-4d5b-88ef-568d20e2f82a</t>
+  </si>
+  <si>
+    <t>campaign--30bc8d41-e4ff-476d-a84a-d5435273ad2e</t>
+  </si>
+  <si>
+    <t>campaign--37aea0f8-0538-4f63-994d-621cd042cbe7</t>
+  </si>
+  <si>
+    <t>campaign--b9035652-ec19-498f-ad70-c1e7c3af8809</t>
+  </si>
+  <si>
+    <t>campaign--25c5110f-77ed-4932-b111-1dfc5e875a95</t>
+  </si>
+  <si>
+    <t>campaign--84ee7058-67a7-46ba-b6ee-a9087bb87634</t>
+  </si>
+  <si>
+    <t>campaign--75cf364b-6744-4d5a-bb26-0abd1753609f</t>
+  </si>
+  <si>
+    <t>campaign--192a1e9c-2e3d-43d2-b6a6-175a55e941b5</t>
+  </si>
+  <si>
+    <t>campaign--071a2be9-c5af-4201-9e25-71e6c6dc63cf</t>
+  </si>
+  <si>
+    <t>campaign--ed10ebb7-caaa-481f-8655-7cc6acbade91</t>
+  </si>
+  <si>
+    <t>campaign--dc27daac-0791-47f7-aaee-d0e5c7a16918</t>
+  </si>
+  <si>
+    <t>campaign--7c31c341-4948-4d76-bc9a-d602657f0db3</t>
+  </si>
+  <si>
+    <t>campaign--f136d4ca-d08c-4b0b-9e1d-368e30dbfa5b</t>
+  </si>
+  <si>
+    <t>campaign--3f35fe1f-00d3-4e41-98a9-2e406c219312</t>
+  </si>
+  <si>
+    <t>campaign--31aacef3-25a8-4fba-ac95-bae1bb0592fb</t>
+  </si>
+  <si>
+    <t>campaign--491b0716-9561-4ea6-a89b-4ba9e0953e3c</t>
+  </si>
+  <si>
+    <t>campaign--a4455377-a120-45a5-9089-99fb95fdb59a</t>
+  </si>
+  <si>
+    <t>campaign--ea61a171-fa35-4ed1-9287-41e3ca667409</t>
+  </si>
+  <si>
+    <t>campaign--7771ca5f-0b5b-4fbb-9f0b-f37801347fca</t>
+  </si>
+  <si>
+    <t>campaign--0b3c9ce1-a0be-4440-b0f0-c762880ed332</t>
+  </si>
+  <si>
+    <t>campaign--96ec7087-d1b0-4076-a568-5f8a779eef00</t>
+  </si>
+  <si>
+    <t>campaign--46077bfe-ce3a-4542-8b5c-b8b6d8d6fdef</t>
+  </si>
+  <si>
+    <t>campaign--1e47c887-315a-4c3d-bea5-d9632702b517</t>
+  </si>
+  <si>
+    <t>campaign--61012452-31df-4e70-80b3-74be0914a200</t>
+  </si>
+  <si>
+    <t>campaign--bf409339-c5e5-4ab8-8b1a-246071ed19b5</t>
+  </si>
+  <si>
+    <t>campaign--d0eb71bc-3823-42d6-b3e5-427e2a915763</t>
+  </si>
+  <si>
+    <t>campaign--9a0c9c17-48be-4239-ae4b-ba408248d9ba</t>
+  </si>
+  <si>
+    <t>campaign--6a3d44b3-9d73-4774-a015-293e5ff7c59f</t>
+  </si>
+  <si>
+    <t>campaign--6058b9a2-6422-4498-bc1f-466e8f5404d0</t>
+  </si>
+  <si>
+    <t>campaign--a3e43158-57aa-48a2-8b22-c4338061ebe6</t>
+  </si>
+  <si>
+    <t>campaign--556f85fe-e335-4694-aa72-2e4da45a572d</t>
+  </si>
+  <si>
+    <t>campaign--3fc52fc0-1fc8-40f8-99fe-daee0cafc351</t>
+  </si>
+  <si>
+    <t>campaign--dee519da-cbc0-4a3f-8f64-811927f8fa8a</t>
+  </si>
+  <si>
+    <t>campaign--fcb5345d-ae74-4a0d-8859-00654996201a</t>
+  </si>
+  <si>
+    <t>campaign--ca069712-0be3-42d8-a175-c8e568760aba</t>
+  </si>
+  <si>
+    <t>campaign--9fd8c082-9e7d-4657-b402-c6b5164ebb7c</t>
+  </si>
+  <si>
+    <t>campaign--62313c07-9360-40f3-9a67-f106b3a9901f</t>
+  </si>
+  <si>
+    <t>campaign--a92151c2-5f7d-4c2e-a659-7a10e298595d</t>
+  </si>
+  <si>
+    <t>campaign--e2dc6026-4b3e-4088-8687-ee5e8efc0fcc</t>
+  </si>
+  <si>
+    <t>campaign--b8913d57-e3f2-43cc-989e-b5dc2cd92219</t>
+  </si>
+  <si>
+    <t>campaign--771a290d-43a0-43fb-89a5-2aaf271da029</t>
+  </si>
+  <si>
+    <t>campaign--c29e446f-6d4f-4920-91d5-fc54dedf1f5f</t>
+  </si>
+  <si>
+    <t>campaign--0bd21e62-2023-485d-9c17-c2684d1bebdb</t>
+  </si>
+  <si>
+    <t>campaign--7c688b14-67e6-476e-8096-a44c3fb95db9</t>
+  </si>
+  <si>
+    <t>campaign--567e3204-7775-46bb-b5f9-874bfeaf0c6f</t>
+  </si>
+  <si>
+    <t>campaign--dbde897a-31a7-4684-a98d-5805601ba4c2</t>
+  </si>
+  <si>
+    <t>campaign--906ac28e-dbce-42ff-9e99-9b6cc4aaa5e3</t>
+  </si>
+  <si>
+    <t>campaign--ce2366df-0b95-4d79-8f46-07ffa76c4215</t>
+  </si>
+  <si>
+    <t>campaign--efaaf655-e666-48b6-b47f-c6778bee3360</t>
+  </si>
+  <si>
+    <t>campaign--00f784da-4f20-4b91-acbe-8f9b76ff9596</t>
+  </si>
+  <si>
+    <t>campaign--59c82e4e-f119-41db-98a0-42312fac19cb</t>
+  </si>
+  <si>
+    <t>campaign--5478a268-e577-4b91-8abc-920e07341e66</t>
+  </si>
+  <si>
+    <t>campaign--b7c7a3d4-e14e-4089-805e-0d6bd5d494c2</t>
+  </si>
+  <si>
+    <t>campaign--acd8df7a-c420-435e-a7c2-1b8fd5170fab</t>
+  </si>
+  <si>
+    <t>campaign--d36ba52b-faba-4013-81c1-bc5462725fe9</t>
+  </si>
+  <si>
+    <t>campaign--cec91334-cad3-439c-9fd6-a172aa9d1c68</t>
+  </si>
+  <si>
+    <t>campaign--487d3e61-633a-4a79-8421-e58f556d93e1</t>
+  </si>
+  <si>
+    <t>campaign--dffc0208-5ef6-47c3-99a3-57d880da041e</t>
+  </si>
+  <si>
+    <t>intrusion-set--7b976569-98f0-4fa3-82fe-02d61389de3e</t>
+  </si>
+  <si>
+    <t>intrusion-set--d5113a56-7d11-4ccf-b29b-db0230a3deb5</t>
+  </si>
+  <si>
+    <t>intrusion-set--ccad1a64-f9f9-4595-8650-92f87954b4a0</t>
+  </si>
+  <si>
+    <t>intrusion-set--763a114d-2942-4a6d-9907-1170a64fae86</t>
+  </si>
+  <si>
+    <t>intrusion-set--efc55d3b-975e-4784-879d-5e1771bcdfb2</t>
+  </si>
+  <si>
+    <t>intrusion-set--d6cb53bb-bf87-46da-99d2-d218130dd4c9</t>
+  </si>
+  <si>
+    <t>tool--24a04dcd-846a-4c5b-bfcd-47828e9ddd57</t>
+  </si>
+  <si>
+    <t>tool--fb5d65db-23c3-4502-8fd9-7b40965d2ed8</t>
+  </si>
+  <si>
+    <t>tool--df0ba05b-fd65-4437-9c8f-5fbbf4498f51</t>
+  </si>
+  <si>
+    <t>tool--634cf340-6e8c-49d7-b45f-c9fb4f722daa</t>
+  </si>
+  <si>
+    <t>tool--06c48a32-5cf5-4cef-8992-72c541bfdfac</t>
+  </si>
+  <si>
+    <t>tool--e8d0468c-8a92-4294-baa2-a91bcd6f19e4</t>
+  </si>
+  <si>
+    <t>tool--88d6ef27-a088-40e6-b97f-8a49b8c508e1</t>
+  </si>
+  <si>
+    <t>tool--4d016c34-bb94-4b61-88bc-7e9cacc2185b</t>
+  </si>
+  <si>
+    <t>tool--2bf94bf0-b6e0-4e29-bef7-8745173179cb</t>
+  </si>
+  <si>
+    <t>tool--82bcdaea-f53f-45de-8281-b671db596090</t>
+  </si>
+  <si>
+    <t>tool--66dcf02c-a2aa-4a17-9e43-2e456ebdee31</t>
+  </si>
+  <si>
+    <t>tool--d0e502ca-3ba5-4364-b2ab-30d53b87c681</t>
+  </si>
+  <si>
+    <t>tool--e07eeae6-c3e5-45f1-b8f1-c3e50a179665</t>
   </si>
   <si>
     <t>campaign</t>
@@ -1658,253 +1658,253 @@
     <t>Смена алфавита родного языка</t>
   </si>
   <si>
-    <t>attack-pattern--22337eab-4ab5-4577-a766-4a514a636fe2</t>
-  </si>
-  <si>
-    <t>attack-pattern--d71852a6-d08a-4937-b2b1-ccf143798754</t>
-  </si>
-  <si>
-    <t>attack-pattern--67fd1251-9ad0-415e-94db-14c6fcda7c8c</t>
-  </si>
-  <si>
-    <t>attack-pattern--c55f58f1-faf2-498e-84f2-59993e1ecbcc</t>
-  </si>
-  <si>
-    <t>attack-pattern--1f8e90a1-2fa1-4e0c-9de7-2a6b61fc3412</t>
-  </si>
-  <si>
-    <t>attack-pattern--5e67abdd-9625-497c-8eed-591b2d0091a8</t>
-  </si>
-  <si>
-    <t>attack-pattern--8861e444-81bb-468e-9fc5-8b7e401e8898</t>
-  </si>
-  <si>
-    <t>attack-pattern--71b8603d-1b4a-45dd-bdc5-58df6fe6a1cb</t>
-  </si>
-  <si>
-    <t>attack-pattern--07605117-d49e-4edb-b205-a42d341fbafe</t>
-  </si>
-  <si>
-    <t>attack-pattern--0de3e487-7362-4416-91f8-3c71cc10d76d</t>
-  </si>
-  <si>
-    <t>attack-pattern--36fadd8e-e035-4c50-be0d-258be309a516</t>
-  </si>
-  <si>
-    <t>attack-pattern--9596e8a1-16fa-466f-b16e-b567018e83c6</t>
-  </si>
-  <si>
-    <t>attack-pattern--137a55c1-3751-4f3e-b038-0a8a31ae7b53</t>
-  </si>
-  <si>
-    <t>attack-pattern--ef5c8e81-c4de-408e-a0bb-eeba03e4ef41</t>
-  </si>
-  <si>
-    <t>attack-pattern--f62f4a3e-70ad-4d66-978f-70460748790e</t>
-  </si>
-  <si>
-    <t>attack-pattern--d4d22a9d-86be-4ed6-bb79-7792aad443f3</t>
-  </si>
-  <si>
-    <t>attack-pattern--4a811ffb-e200-4e7b-a48d-5dbb2e05d21b</t>
-  </si>
-  <si>
-    <t>attack-pattern--4b4499c1-7976-4838-ac5f-1b2503e91894</t>
-  </si>
-  <si>
-    <t>attack-pattern--2bb142f3-19c9-4d2d-ab6b-e91a6d1eb45d</t>
-  </si>
-  <si>
-    <t>attack-pattern--f60c3210-890a-4015-a4a9-e1966101ed5d</t>
-  </si>
-  <si>
-    <t>attack-pattern--6a388bfd-b3f8-4136-a3d0-3b6c92b62616</t>
-  </si>
-  <si>
-    <t>attack-pattern--3953a646-ca74-4d27-bb4b-801773351821</t>
-  </si>
-  <si>
-    <t>attack-pattern--c985b114-66f8-43e8-a9d5-09f7dcce76d2</t>
-  </si>
-  <si>
-    <t>attack-pattern--9861afc3-113a-4f8e-ba90-12d851653a4c</t>
-  </si>
-  <si>
-    <t>attack-pattern--6819df95-06a3-4c71-874f-8daea090f07e</t>
-  </si>
-  <si>
-    <t>attack-pattern--c671af96-e92c-44ff-820d-00bdb7de4fca</t>
-  </si>
-  <si>
-    <t>attack-pattern--d984185b-2502-414b-969d-f165cdeedc31</t>
-  </si>
-  <si>
-    <t>attack-pattern--03024756-3f6a-42b3-b93e-2d31c7ce6b6b</t>
-  </si>
-  <si>
-    <t>attack-pattern--8a5da3da-67cf-4659-bb91-0b28685766a1</t>
-  </si>
-  <si>
-    <t>attack-pattern--b3a3b655-dacd-4ee5-bae1-68801c3d15dc</t>
-  </si>
-  <si>
-    <t>attack-pattern--2f0e072e-5d5e-458e-a5c3-8efbaef46084</t>
-  </si>
-  <si>
-    <t>attack-pattern--8a804fba-621a-4868-b128-51cebf0ad2b2</t>
-  </si>
-  <si>
-    <t>attack-pattern--3eff3cd8-fbaf-4e5d-b38e-c72604acb3ce</t>
-  </si>
-  <si>
-    <t>attack-pattern--cbff6b3a-8340-4986-9183-3c02b87fd1b2</t>
-  </si>
-  <si>
-    <t>attack-pattern--c93829ec-d90f-41a9-9191-466a6365de51</t>
-  </si>
-  <si>
-    <t>attack-pattern--9facc2a5-8243-49aa-96cb-a94ef85b25c9</t>
-  </si>
-  <si>
-    <t>attack-pattern--9d3f3422-f494-42ab-9385-bc4e8ef727ca</t>
-  </si>
-  <si>
-    <t>attack-pattern--c7ccd834-4f08-4829-96ae-45e58d47945f</t>
-  </si>
-  <si>
-    <t>attack-pattern--b0851c83-e4d2-41c1-b5de-9115df406339</t>
-  </si>
-  <si>
-    <t>attack-pattern--0b6448a8-18a4-4d48-bfcf-172a74724542</t>
-  </si>
-  <si>
-    <t>attack-pattern--76b6c6fb-ce17-427d-b717-16011ae54b6e</t>
-  </si>
-  <si>
-    <t>attack-pattern--40f36bf9-2850-4992-b47f-4abe909a0e93</t>
-  </si>
-  <si>
-    <t>attack-pattern--02964caf-d52a-4d68-abcc-cdd1ef5fa69d</t>
-  </si>
-  <si>
-    <t>attack-pattern--cc782e40-0ae3-4f6d-94cb-2828cb2d5005</t>
-  </si>
-  <si>
-    <t>attack-pattern--09c9ca23-10d8-4f0f-a7dd-e99bb022299a</t>
-  </si>
-  <si>
-    <t>attack-pattern--9162f78a-1b72-4adc-9f8b-0a6b6410a3a7</t>
-  </si>
-  <si>
-    <t>attack-pattern--9e90f9e3-ced7-476d-acac-467e8c865ca0</t>
-  </si>
-  <si>
-    <t>attack-pattern--7ee9829e-072b-48f0-b801-b5b627c8bf1a</t>
-  </si>
-  <si>
-    <t>attack-pattern--ea9a2533-0faa-4b9d-bb0e-237ca902e1d7</t>
-  </si>
-  <si>
-    <t>attack-pattern--da48c22f-a5e2-41e7-97e4-07bfc4156350</t>
-  </si>
-  <si>
-    <t>attack-pattern--6e962dbe-f818-407b-b5a6-3eec9fbe9ec2</t>
-  </si>
-  <si>
-    <t>attack-pattern--6f08f0ef-8704-4d0e-90f5-ad421918d899</t>
-  </si>
-  <si>
-    <t>attack-pattern--09059676-291f-4053-a7b5-17d93eb87d30</t>
-  </si>
-  <si>
-    <t>attack-pattern--4b8920a8-f486-4065-aff8-4e7b6ee8b829</t>
-  </si>
-  <si>
-    <t>attack-pattern--3d1653fe-5ea0-4eb0-8c78-f849ecc43e11</t>
-  </si>
-  <si>
-    <t>attack-pattern--41699f0f-f822-4dbc-b201-dca7ac3eddce</t>
-  </si>
-  <si>
-    <t>attack-pattern--b34ebb98-d962-4987-8399-890eef9c69fe</t>
-  </si>
-  <si>
-    <t>attack-pattern--738e1811-a9a5-4407-be43-b726fd7e7589</t>
-  </si>
-  <si>
-    <t>attack-pattern--86f1c7c0-561e-4b45-97c0-faad41484e38</t>
-  </si>
-  <si>
-    <t>attack-pattern--d5f24756-885a-43f1-a9f0-b0088651bbc3</t>
-  </si>
-  <si>
-    <t>attack-pattern--c6da22a5-ceb4-4f40-a3bc-bcd6e655d591</t>
-  </si>
-  <si>
-    <t>attack-pattern--d38398cd-b820-4626-9510-465d56ba906c</t>
-  </si>
-  <si>
-    <t>attack-pattern--36e1d7c1-2f0e-41c6-8aee-177df4bdbc61</t>
-  </si>
-  <si>
-    <t>attack-pattern--0d6e1a1e-2c33-4280-86f2-8a1d0049b089</t>
-  </si>
-  <si>
-    <t>attack-pattern--a882288f-98fe-4c75-859a-17d669c08376</t>
-  </si>
-  <si>
-    <t>attack-pattern--5df092aa-9e0d-440d-8aa0-5f9988432ae3</t>
-  </si>
-  <si>
-    <t>attack-pattern--edd49cde-2190-45a8-9277-0fafcda1502c</t>
-  </si>
-  <si>
-    <t>attack-pattern--a87aa45d-2118-4e87-af92-e75e367453c9</t>
-  </si>
-  <si>
-    <t>attack-pattern--5f90feb8-5507-456c-9d1d-0e0e3cce55de</t>
-  </si>
-  <si>
-    <t>attack-pattern--d051e585-aa48-4964-b54e-2e08adc472f9</t>
-  </si>
-  <si>
-    <t>attack-pattern--edcb13e5-fbb1-4396-9e8c-1e3fe9dde52c</t>
-  </si>
-  <si>
-    <t>attack-pattern--2d723928-4bb8-45b5-86d4-a6f2398ca02f</t>
-  </si>
-  <si>
-    <t>attack-pattern--3c5f8bcd-ee2b-4396-9e79-3c99fcc96d81</t>
-  </si>
-  <si>
-    <t>attack-pattern--12023694-fdfd-480d-990d-fefa0cc12655</t>
-  </si>
-  <si>
-    <t>attack-pattern--ed457228-1fd9-4a65-ac85-388ba6460f94</t>
-  </si>
-  <si>
-    <t>attack-pattern--b2df162e-6cd7-4286-8841-dbeff90a7e20</t>
-  </si>
-  <si>
-    <t>attack-pattern--63335f7f-c1d8-42d3-bab5-4055c59e6a1e</t>
-  </si>
-  <si>
-    <t>attack-pattern--f2e939fc-283e-4bea-9fbf-f17acac31435</t>
-  </si>
-  <si>
-    <t>attack-pattern--8f3de97b-1ed5-4594-9889-41cd32d8adf5</t>
-  </si>
-  <si>
-    <t>attack-pattern--e1c78d1f-6f07-4f4b-9220-6d455354bc64</t>
-  </si>
-  <si>
-    <t>attack-pattern--02c5997b-a7da-48ac-96da-c4daa1aafc35</t>
-  </si>
-  <si>
-    <t>attack-pattern--fef3fc3b-399c-41e0-8c76-a6eb1d014ada</t>
-  </si>
-  <si>
-    <t>attack-pattern--77c6e8eb-0074-49c8-90cd-9c830db4859f</t>
+    <t>attack-pattern--d67e92a1-567a-4443-b196-42eee7df7df9</t>
+  </si>
+  <si>
+    <t>attack-pattern--f87361eb-4cc0-472a-9d20-d8814c3dcb83</t>
+  </si>
+  <si>
+    <t>attack-pattern--11df0e1b-fb0b-495a-8517-fe9629386cc7</t>
+  </si>
+  <si>
+    <t>attack-pattern--69b5ecb8-ed59-476a-a8d0-692d61060065</t>
+  </si>
+  <si>
+    <t>attack-pattern--b1616020-3221-457d-9111-770be3da803f</t>
+  </si>
+  <si>
+    <t>attack-pattern--23537b01-052d-4788-a1c5-ac64ea3a5440</t>
+  </si>
+  <si>
+    <t>attack-pattern--b1ae5e87-2d91-4460-ab24-a874f71d0aa3</t>
+  </si>
+  <si>
+    <t>attack-pattern--14ddac56-e61c-489c-9f2a-0ead47acab72</t>
+  </si>
+  <si>
+    <t>attack-pattern--cfe0ba66-044c-4fae-899d-2776ecd25970</t>
+  </si>
+  <si>
+    <t>attack-pattern--7302168b-1756-4aa2-9831-57b042e5e79c</t>
+  </si>
+  <si>
+    <t>attack-pattern--0e9f8dfa-7044-47a4-99c4-b8108e0c3531</t>
+  </si>
+  <si>
+    <t>attack-pattern--541f9c2f-5e7e-40bd-8807-e27b27bf27f9</t>
+  </si>
+  <si>
+    <t>attack-pattern--d1450cbb-9ca9-4637-a3d4-415897d678b3</t>
+  </si>
+  <si>
+    <t>attack-pattern--f8863479-abf3-40aa-909f-422ff587ef75</t>
+  </si>
+  <si>
+    <t>attack-pattern--1c3cc896-6014-4a38-bb84-f755661f9f8a</t>
+  </si>
+  <si>
+    <t>attack-pattern--3d477757-3882-43e5-b3b5-5c453472af4e</t>
+  </si>
+  <si>
+    <t>attack-pattern--0a36cf96-d155-4205-badf-fce21153e3d3</t>
+  </si>
+  <si>
+    <t>attack-pattern--0f543b48-8526-45f6-9f4c-c0aabf08b950</t>
+  </si>
+  <si>
+    <t>attack-pattern--f7a7642e-6431-4d94-8930-784669743a6e</t>
+  </si>
+  <si>
+    <t>attack-pattern--d8fec2ab-fe86-4530-9801-bbbe5c3baf44</t>
+  </si>
+  <si>
+    <t>attack-pattern--77f583b6-9202-4712-9a61-f28cba87bf1b</t>
+  </si>
+  <si>
+    <t>attack-pattern--ca19f909-8e73-4014-ab69-a521482caa77</t>
+  </si>
+  <si>
+    <t>attack-pattern--e06e27d3-c18f-4bac-9bb6-17121de4850b</t>
+  </si>
+  <si>
+    <t>attack-pattern--0f207f69-c49f-4bd9-a2c8-81d5903af798</t>
+  </si>
+  <si>
+    <t>attack-pattern--d039ccb5-695e-4e9c-903d-4a25d80a5e91</t>
+  </si>
+  <si>
+    <t>attack-pattern--281cf3bf-8184-4148-8d26-8ae24ac5facd</t>
+  </si>
+  <si>
+    <t>attack-pattern--20e9f442-a9aa-49d2-86e7-10b3677d2b71</t>
+  </si>
+  <si>
+    <t>attack-pattern--7b5e8502-6625-4bfb-becf-4701773fc345</t>
+  </si>
+  <si>
+    <t>attack-pattern--01cef48e-e90c-42c2-b99f-c6ce6b48b026</t>
+  </si>
+  <si>
+    <t>attack-pattern--954103ab-7172-4bc3-80d2-6eda761140c7</t>
+  </si>
+  <si>
+    <t>attack-pattern--47a73afc-602e-4840-98f7-559a0583a02f</t>
+  </si>
+  <si>
+    <t>attack-pattern--ce173a13-3838-4451-bcde-529c8c9cbf4d</t>
+  </si>
+  <si>
+    <t>attack-pattern--0c6b2071-1b00-4c4e-ad42-c086fe85e44d</t>
+  </si>
+  <si>
+    <t>attack-pattern--3b7ebd5a-2989-4a5f-8187-7dcbb6319ecd</t>
+  </si>
+  <si>
+    <t>attack-pattern--3c2787d0-9bb3-4445-baf7-affe99ffc75d</t>
+  </si>
+  <si>
+    <t>attack-pattern--255d85ab-8ae5-4855-9d4d-398d57bfb428</t>
+  </si>
+  <si>
+    <t>attack-pattern--ab6eb169-9d35-462e-8540-e600dcfcc755</t>
+  </si>
+  <si>
+    <t>attack-pattern--a67dba4e-5c9c-4a96-8564-cc1477847aa2</t>
+  </si>
+  <si>
+    <t>attack-pattern--2665c1bf-c793-4ff8-81e1-8cdfb042a050</t>
+  </si>
+  <si>
+    <t>attack-pattern--01660591-eff8-4002-8b86-edbc8ddcff75</t>
+  </si>
+  <si>
+    <t>attack-pattern--df7b78e3-6709-4b71-ae0c-08ed1a47de6b</t>
+  </si>
+  <si>
+    <t>attack-pattern--31403032-89b6-4a29-af26-bdb2c907f869</t>
+  </si>
+  <si>
+    <t>attack-pattern--e1500254-a805-457b-9c9f-eaa7ed4441c2</t>
+  </si>
+  <si>
+    <t>attack-pattern--15b42e50-034b-48ec-a530-08f4da421ced</t>
+  </si>
+  <si>
+    <t>attack-pattern--2eccd110-1bf6-4854-a82c-0a45775e907f</t>
+  </si>
+  <si>
+    <t>attack-pattern--bbbea8cd-eb4e-4314-abc8-2293225ab5e6</t>
+  </si>
+  <si>
+    <t>attack-pattern--ba18aeed-1fa0-4221-b5c3-2951c695226d</t>
+  </si>
+  <si>
+    <t>attack-pattern--58aadf94-c0fc-45fe-b84d-86af05ac2a41</t>
+  </si>
+  <si>
+    <t>attack-pattern--f409ed58-993e-4cd3-816b-35cb16df5f13</t>
+  </si>
+  <si>
+    <t>attack-pattern--3408f6b9-9851-47a8-8c46-591cab11c267</t>
+  </si>
+  <si>
+    <t>attack-pattern--661bd189-a8b3-42ff-bf5b-33de03ae6136</t>
+  </si>
+  <si>
+    <t>attack-pattern--7ef5f9c4-8044-44bc-88a6-9395e47e160a</t>
+  </si>
+  <si>
+    <t>attack-pattern--d2982864-148c-45ed-9a9d-73124e552f59</t>
+  </si>
+  <si>
+    <t>attack-pattern--60789ba9-9b1e-4a2d-804d-b16342fe5f3d</t>
+  </si>
+  <si>
+    <t>attack-pattern--63e9746b-4223-4c4d-bb27-a4c2f724f832</t>
+  </si>
+  <si>
+    <t>attack-pattern--b6ab653b-b93b-46b8-9fc3-d24ccf9a86a1</t>
+  </si>
+  <si>
+    <t>attack-pattern--59e9ef1f-3d12-4523-a3ac-0b4c11c35573</t>
+  </si>
+  <si>
+    <t>attack-pattern--3c3ab581-f839-4439-bf70-a00298d8cbb7</t>
+  </si>
+  <si>
+    <t>attack-pattern--b7f8cff2-87c7-48c1-aeb7-5cf9187b1090</t>
+  </si>
+  <si>
+    <t>attack-pattern--40ddc318-d9d7-4035-80a9-21f5de23c666</t>
+  </si>
+  <si>
+    <t>attack-pattern--9a46e5ee-7093-4048-9d7e-501463c0424d</t>
+  </si>
+  <si>
+    <t>attack-pattern--3c78bc06-b7d9-4d72-87cc-3896a83a79c1</t>
+  </si>
+  <si>
+    <t>attack-pattern--3ec89812-91d7-48b1-aa07-b78e44175f91</t>
+  </si>
+  <si>
+    <t>attack-pattern--1a21e55e-d799-41ce-a799-461e1995bd5a</t>
+  </si>
+  <si>
+    <t>attack-pattern--5ba903c1-2421-4964-8ca4-f56dcc96a1c3</t>
+  </si>
+  <si>
+    <t>attack-pattern--f6f80852-da09-4571-bd87-ab371a289296</t>
+  </si>
+  <si>
+    <t>attack-pattern--1337b0db-4d5f-447f-83d1-3682c83da1be</t>
+  </si>
+  <si>
+    <t>attack-pattern--50e11ffa-fd63-4200-af97-d723ceb03f87</t>
+  </si>
+  <si>
+    <t>attack-pattern--3c07dbf7-3e3e-47d9-b439-53989a64f430</t>
+  </si>
+  <si>
+    <t>attack-pattern--948886a4-efe9-40cc-8153-3370afff323e</t>
+  </si>
+  <si>
+    <t>attack-pattern--c21a61e0-99df-4c01-abf2-5e46d8345613</t>
+  </si>
+  <si>
+    <t>attack-pattern--d4ba7ff5-0107-437e-853c-b8c4d37ea441</t>
+  </si>
+  <si>
+    <t>attack-pattern--c69305fb-035a-4c61-8929-2e22cea42d61</t>
+  </si>
+  <si>
+    <t>attack-pattern--39c46a2f-f777-48c7-b903-20ce80bca89b</t>
+  </si>
+  <si>
+    <t>attack-pattern--9f4aa723-88b2-42d4-b7f0-58bfc3f42435</t>
+  </si>
+  <si>
+    <t>attack-pattern--9b1b420b-4d1a-4108-a086-73ba81138b1a</t>
+  </si>
+  <si>
+    <t>attack-pattern--cfd09f3f-20c2-4148-a51e-c7533a4f6866</t>
+  </si>
+  <si>
+    <t>attack-pattern--5da8aa0b-7c9c-4638-bc17-9ed6bf1aafa6</t>
+  </si>
+  <si>
+    <t>attack-pattern--2685f739-43ca-4258-8e7f-0cf545de3477</t>
+  </si>
+  <si>
+    <t>attack-pattern--b9b7420d-58cf-49d6-9884-18e4d72f0a38</t>
+  </si>
+  <si>
+    <t>attack-pattern--1a522e5a-e65b-443f-8aae-2bc39534e85e</t>
+  </si>
+  <si>
+    <t>attack-pattern--f2121d22-b6ab-4c8d-b1a6-a65df30bd836</t>
+  </si>
+  <si>
+    <t>attack-pattern--faf29c5e-51f3-4afd-9b72-70769986b561</t>
   </si>
   <si>
     <t>technique</t>
@@ -2962,3031 +2962,3031 @@
     <t>Полный законодательный запрет на самоорганизацию: указ Столыпина «про заборону будь-яких українських організацій» (Citation: Русифікація України — Вікіпедія 2026).</t>
   </si>
   <si>
-    <t>relationship--579007f9-28a0-48e4-9185-c1e2d0b17ae3</t>
-  </si>
-  <si>
-    <t>relationship--cbe422cd-9fe9-4132-84f1-96be195ac993</t>
-  </si>
-  <si>
-    <t>relationship--5667cd4d-ca36-46d4-a17a-9d54006f1f5b</t>
-  </si>
-  <si>
-    <t>relationship--f281ae66-2d30-4085-b524-194af26c8459</t>
-  </si>
-  <si>
-    <t>relationship--36dcc214-651c-4657-acdf-5a62bef3ec0f</t>
-  </si>
-  <si>
-    <t>relationship--13a0e8d5-cd26-41ad-989a-1ffb8a550016</t>
-  </si>
-  <si>
-    <t>relationship--2bf4f3c6-637c-41b5-b365-73fd8f1340fa</t>
-  </si>
-  <si>
-    <t>relationship--bc31601d-18b2-4aed-90e3-208e5d49b78a</t>
-  </si>
-  <si>
-    <t>relationship--9807e38f-6ad6-447a-ae60-a64f9f343370</t>
-  </si>
-  <si>
-    <t>relationship--8a514380-8a2d-4c81-9db0-93a248171fba</t>
-  </si>
-  <si>
-    <t>relationship--b2f79bb7-979e-4ea3-86ef-eebc886aaa6b</t>
-  </si>
-  <si>
-    <t>relationship--545039f1-fa7a-4f32-9e79-7584f9399a5a</t>
-  </si>
-  <si>
-    <t>relationship--bb7c01ba-b6d1-40f6-a6d0-3e4b0cdddbef</t>
-  </si>
-  <si>
-    <t>relationship--974dffe7-2fe4-45f0-bf21-5df9f49100d0</t>
-  </si>
-  <si>
-    <t>relationship--590d5394-a905-4b57-8ea4-38e941c36875</t>
-  </si>
-  <si>
-    <t>relationship--c76b1d3c-c2e5-45d1-a417-d580c9825105</t>
-  </si>
-  <si>
-    <t>relationship--3037be7e-2186-4f85-beb4-bfc477eef251</t>
-  </si>
-  <si>
-    <t>relationship--ceeb598f-298b-4fdd-aa06-06c66f75cb93</t>
-  </si>
-  <si>
-    <t>relationship--6e2eee1c-1d01-4aa2-b34b-1ce62806dae9</t>
-  </si>
-  <si>
-    <t>relationship--c347dbcd-3768-45bb-85b5-ee75069b5731</t>
-  </si>
-  <si>
-    <t>relationship--eacab9fe-e01f-49fc-a53a-bdbdacec0a5d</t>
-  </si>
-  <si>
-    <t>relationship--0a00c5e3-fc83-48cd-8ddb-09ef4bbedfe0</t>
-  </si>
-  <si>
-    <t>relationship--0ee2ab17-a17d-488c-a01f-4cc29fa47acc</t>
-  </si>
-  <si>
-    <t>relationship--72e5cce2-bbff-48a2-b689-589ad7bde2fb</t>
-  </si>
-  <si>
-    <t>relationship--d3b4874f-ecb2-4381-9b8d-7927f05858d0</t>
-  </si>
-  <si>
-    <t>relationship--ca5afe22-bac2-4077-b67b-337995a60f43</t>
-  </si>
-  <si>
-    <t>relationship--77b67bf7-363d-4a9d-9f8b-9742086db6c6</t>
-  </si>
-  <si>
-    <t>relationship--63fe6e4d-581d-431b-8116-9e090e8a745c</t>
-  </si>
-  <si>
-    <t>relationship--94908fc4-bb5b-4683-805a-dbd8dc5e4999</t>
-  </si>
-  <si>
-    <t>relationship--d9fe5d2b-3357-4241-901b-39166dd33941</t>
-  </si>
-  <si>
-    <t>relationship--035ae41a-01e9-4155-9738-28abee46fa01</t>
-  </si>
-  <si>
-    <t>relationship--22ee9109-c21a-4017-a011-8847cb95d8af</t>
-  </si>
-  <si>
-    <t>relationship--de151bf0-ed08-4e2c-924e-d1e4fcd66047</t>
-  </si>
-  <si>
-    <t>relationship--1b8dfcb3-509e-4b06-a3eb-15219d4b259f</t>
-  </si>
-  <si>
-    <t>relationship--d9c1c0f7-5386-45dd-90f5-cdcf145f2c40</t>
-  </si>
-  <si>
-    <t>relationship--a7369f3d-8b80-46e3-bb86-52408e4d0a70</t>
-  </si>
-  <si>
-    <t>relationship--924eeef7-4ac6-4094-a9d7-36befeac2c17</t>
-  </si>
-  <si>
-    <t>relationship--4135c852-a440-4feb-a662-d639156221ad</t>
-  </si>
-  <si>
-    <t>relationship--b50f9c63-ba9d-4a49-a4f7-45d9b53d8ef0</t>
-  </si>
-  <si>
-    <t>relationship--02f7b89f-53fa-478f-a1b5-7b61d8dcbff2</t>
-  </si>
-  <si>
-    <t>relationship--64360548-9a83-41f8-90e4-d73d3eb2c33a</t>
-  </si>
-  <si>
-    <t>relationship--8283b0e0-32c7-4708-9057-d42e6598176b</t>
-  </si>
-  <si>
-    <t>relationship--c1c921d9-699e-4928-8506-67dcd2061170</t>
-  </si>
-  <si>
-    <t>relationship--f2726f56-5487-4b4f-af8a-7031b19d1d76</t>
-  </si>
-  <si>
-    <t>relationship--d84105e6-4a04-4cf4-8a2c-c4a12e5dea08</t>
-  </si>
-  <si>
-    <t>relationship--3b452af0-3666-4c28-974e-a4fb53bbf295</t>
-  </si>
-  <si>
-    <t>relationship--f8ab7e5a-e300-48c9-b77c-8e67a4d7df27</t>
-  </si>
-  <si>
-    <t>relationship--40666857-41f2-4d46-bf70-47aa0c34dcc7</t>
-  </si>
-  <si>
-    <t>relationship--771548ba-7416-4cde-95d1-c788b08aaa71</t>
-  </si>
-  <si>
-    <t>relationship--779d583e-d222-4b26-956a-1e19ac4b77e2</t>
-  </si>
-  <si>
-    <t>relationship--d82e2525-0fdd-49cb-b3f1-1f2efa99ee08</t>
-  </si>
-  <si>
-    <t>relationship--31777070-381d-45d3-b313-00646e092c07</t>
-  </si>
-  <si>
-    <t>relationship--0f4de468-fd2f-4285-9db2-740ef8555069</t>
-  </si>
-  <si>
-    <t>relationship--24ad6afb-6426-413a-a29f-38668ad6ff90</t>
-  </si>
-  <si>
-    <t>relationship--946d5ae9-8056-4e22-9cd4-417de7f38d82</t>
-  </si>
-  <si>
-    <t>relationship--2a1f9d54-b16b-46ad-a923-604adfe79e1e</t>
-  </si>
-  <si>
-    <t>relationship--9a57978d-fe99-4297-8eb2-9746f0966990</t>
-  </si>
-  <si>
-    <t>relationship--366127f5-ecfd-431d-8baa-60078e576cef</t>
-  </si>
-  <si>
-    <t>relationship--835e8e03-39f2-4a00-a970-4f85d13ecae3</t>
-  </si>
-  <si>
-    <t>relationship--8a4a0c57-9338-42e3-8d0f-f04cc7e4970f</t>
-  </si>
-  <si>
-    <t>relationship--13eee957-a48f-466d-833c-b05db7b68537</t>
-  </si>
-  <si>
-    <t>relationship--5c8531a1-d41b-4b0b-8a4e-dfae8afcfa13</t>
-  </si>
-  <si>
-    <t>relationship--823a5587-50a0-40bc-9bde-70e3c2182300</t>
-  </si>
-  <si>
-    <t>relationship--293ad61a-8091-43f2-9fdc-e1adb4c75bc9</t>
-  </si>
-  <si>
-    <t>relationship--08e3ea95-b7f8-4937-b29c-4a1672614f9c</t>
-  </si>
-  <si>
-    <t>relationship--49edb497-7c42-44fc-bb53-870ca69c42d0</t>
-  </si>
-  <si>
-    <t>relationship--2051eeb2-4f36-497b-b503-5da4e20d78a0</t>
-  </si>
-  <si>
-    <t>relationship--30d0c38d-f5e6-4c94-a312-bb0202c53235</t>
-  </si>
-  <si>
-    <t>relationship--a372bff6-e803-4af7-ba39-d0996ef7de00</t>
-  </si>
-  <si>
-    <t>relationship--16bf97f2-e1ac-451b-93db-61a5ca25cfa5</t>
-  </si>
-  <si>
-    <t>relationship--b4456713-6f1a-423c-9417-3fd9318794b5</t>
-  </si>
-  <si>
-    <t>relationship--7368aac6-f55d-45e8-bcd2-0150164725c0</t>
-  </si>
-  <si>
-    <t>relationship--8fa92939-0395-495a-a2cc-25920befafd6</t>
-  </si>
-  <si>
-    <t>relationship--7f8c1d68-a431-4053-a40c-08397553d9f8</t>
-  </si>
-  <si>
-    <t>relationship--fe830b39-4d93-4844-92e9-630d112bb1cc</t>
-  </si>
-  <si>
-    <t>relationship--ba30d8c0-0a8a-43e3-884e-9ebc68c8b18b</t>
-  </si>
-  <si>
-    <t>relationship--a9ada7e1-57e6-4aba-95c7-33f97a61382d</t>
-  </si>
-  <si>
-    <t>relationship--4e5af6b1-7d02-4647-843f-917014cbfee5</t>
-  </si>
-  <si>
-    <t>relationship--a41e87ab-e2f0-472e-8b8b-b96ee2a8dbfb</t>
-  </si>
-  <si>
-    <t>relationship--7a731bc9-9092-4523-8921-dd7a3d94426f</t>
-  </si>
-  <si>
-    <t>relationship--b2beb81b-3b22-4e86-9770-beb7bcb9e418</t>
-  </si>
-  <si>
-    <t>relationship--eba89ba0-a62f-4d7a-aac2-58639ab713f8</t>
-  </si>
-  <si>
-    <t>relationship--cd2cd507-1be3-4d9a-b9fc-fcbddeac37be</t>
-  </si>
-  <si>
-    <t>relationship--0cfbf64b-f9a8-4961-bdcc-328c9364a656</t>
-  </si>
-  <si>
-    <t>relationship--3db40fe1-6e0d-4323-8da9-f0359cfa8be7</t>
-  </si>
-  <si>
-    <t>relationship--077d87d9-6da7-4b46-9cfc-4c84e7f788af</t>
-  </si>
-  <si>
-    <t>relationship--86e9c863-5ae5-46bf-b0e4-b02eaa185bd7</t>
-  </si>
-  <si>
-    <t>relationship--434ffa6e-8e3f-42bf-8887-3b685da7afe2</t>
-  </si>
-  <si>
-    <t>relationship--61560840-331e-4982-ab6f-90edf192c51f</t>
-  </si>
-  <si>
-    <t>relationship--5ed32bcc-ffac-41fb-ade7-6baf29882120</t>
-  </si>
-  <si>
-    <t>relationship--abce58d8-6877-4dcb-a877-9e213452f4b6</t>
-  </si>
-  <si>
-    <t>relationship--0b3c0a27-bbc5-4005-ac5d-bb05a255a1fd</t>
-  </si>
-  <si>
-    <t>relationship--9f3989ee-e8dd-48ba-a582-6a1fb2c277cf</t>
-  </si>
-  <si>
-    <t>relationship--5f947b73-c283-438a-b661-e922ef128815</t>
-  </si>
-  <si>
-    <t>relationship--f2028f92-96ba-481d-a719-e43200be30eb</t>
-  </si>
-  <si>
-    <t>relationship--9b0772cb-acd9-4f8a-82b1-c429efd3c3fc</t>
-  </si>
-  <si>
-    <t>relationship--cf2a8f50-c042-4978-8ac9-040f681a0902</t>
-  </si>
-  <si>
-    <t>relationship--dd0249b1-41cf-49f2-8b39-909edba54fbb</t>
-  </si>
-  <si>
-    <t>relationship--0863f965-e8ec-4d07-86db-37554adca29b</t>
-  </si>
-  <si>
-    <t>relationship--e86d43ec-a735-4d99-ad60-b0135dbfb42f</t>
-  </si>
-  <si>
-    <t>relationship--fc6c0597-d0d4-4933-8519-4d7a7c7297f6</t>
-  </si>
-  <si>
-    <t>relationship--27d3b66b-60c5-4691-884a-af621f775026</t>
-  </si>
-  <si>
-    <t>relationship--653d9b5d-056b-4633-8ccb-46dd884fe269</t>
-  </si>
-  <si>
-    <t>relationship--5614d86d-6211-45cd-ac6c-26a97c7ed3cf</t>
-  </si>
-  <si>
-    <t>relationship--c00bd06c-4bf5-4ab2-ab25-c5d571553d0c</t>
-  </si>
-  <si>
-    <t>relationship--7201fe1e-0fea-4d3b-97bf-6355ebf82318</t>
-  </si>
-  <si>
-    <t>relationship--d1870805-3ccc-4beb-b2a4-8402f288d864</t>
-  </si>
-  <si>
-    <t>relationship--a1eee09b-bd43-43e9-b586-a6b939c06a11</t>
-  </si>
-  <si>
-    <t>relationship--c274175b-6c03-49c5-a647-607cd5b0e4d2</t>
-  </si>
-  <si>
-    <t>relationship--187b5fcd-6c5c-4c42-8d07-07adbdbecd2d</t>
-  </si>
-  <si>
-    <t>relationship--1006e39a-452b-4831-be5c-fc31a3710a4c</t>
-  </si>
-  <si>
-    <t>relationship--998fc32c-1362-4fe1-badc-2c3295a58dae</t>
-  </si>
-  <si>
-    <t>relationship--b50491d9-1ef9-4e6a-a7d8-ed3bdd53bb26</t>
-  </si>
-  <si>
-    <t>relationship--816bc3db-9456-4de8-a943-e308683f2326</t>
-  </si>
-  <si>
-    <t>relationship--7e5cb007-6d19-46d2-a049-9fb76730abfc</t>
-  </si>
-  <si>
-    <t>relationship--4b7df337-6761-4f4a-8663-ffc85abd9bd7</t>
-  </si>
-  <si>
-    <t>relationship--3e1c35b2-ac79-4f76-b026-a30f8e566a41</t>
-  </si>
-  <si>
-    <t>relationship--a849cb40-97db-4468-a725-2eb757b9285f</t>
-  </si>
-  <si>
-    <t>relationship--47ff22b7-0fad-4eaa-8f49-c7ee57b2bcf5</t>
-  </si>
-  <si>
-    <t>relationship--50db3a6a-bc86-4653-92b1-cc25f4fd3b63</t>
-  </si>
-  <si>
-    <t>relationship--8312e15d-9501-45f6-b5c7-dd40ad215dc7</t>
-  </si>
-  <si>
-    <t>relationship--0cc9ae91-2019-49d4-9ae9-74cf940ab326</t>
-  </si>
-  <si>
-    <t>relationship--62cc7c54-5c61-4755-b62b-11df9f67bc7c</t>
-  </si>
-  <si>
-    <t>relationship--9520ceeb-3ab0-40cd-9976-308b5382c604</t>
-  </si>
-  <si>
-    <t>relationship--df0590aa-456d-4dcd-b3ef-9db58fcdde4d</t>
-  </si>
-  <si>
-    <t>relationship--25875951-42bf-4bd1-8846-1e2b082462c7</t>
-  </si>
-  <si>
-    <t>relationship--363d00f2-89e0-45eb-aeff-56c3eb0b7d1b</t>
-  </si>
-  <si>
-    <t>relationship--ccc50e83-1034-4626-9fad-142e49094870</t>
-  </si>
-  <si>
-    <t>relationship--0e6f9307-ac79-4d43-90f6-e73960d6ec75</t>
-  </si>
-  <si>
-    <t>relationship--24ef7132-be8a-41ec-bacf-c64882a1171d</t>
-  </si>
-  <si>
-    <t>relationship--0cf1df00-44a9-42ec-b61d-3e10fb8c67d6</t>
-  </si>
-  <si>
-    <t>relationship--03e9274c-b7a4-42d6-8f7f-78b71e30af09</t>
-  </si>
-  <si>
-    <t>relationship--5c38fc95-7bc5-4a6a-8681-48be32c65a82</t>
-  </si>
-  <si>
-    <t>relationship--066eb77b-c6df-4d8e-8599-0beb192907e4</t>
-  </si>
-  <si>
-    <t>relationship--541a4d88-df09-4c75-92ae-356afd194692</t>
-  </si>
-  <si>
-    <t>relationship--3af6830d-8cc7-4fed-b927-108a41fd4178</t>
-  </si>
-  <si>
-    <t>relationship--57631293-2a02-4489-8c56-f583e9bc5585</t>
-  </si>
-  <si>
-    <t>relationship--862f0336-33bd-4370-8af3-d29a004f0fc8</t>
-  </si>
-  <si>
-    <t>relationship--9ec2a708-84bf-4339-afb0-0162bb4748ff</t>
-  </si>
-  <si>
-    <t>relationship--4485df60-3f40-40ca-93c4-89378405dc43</t>
-  </si>
-  <si>
-    <t>relationship--722ca219-044e-4221-a0f4-444790a937ba</t>
-  </si>
-  <si>
-    <t>relationship--0819322a-18d8-4e24-b55c-206658d07525</t>
-  </si>
-  <si>
-    <t>relationship--cfa59c71-254e-4a90-903c-fcce14903069</t>
-  </si>
-  <si>
-    <t>relationship--672d610b-b36d-4dd8-b55d-8b986db8b16c</t>
-  </si>
-  <si>
-    <t>relationship--3c9fe144-c86e-42cf-b46f-9fbac0138093</t>
-  </si>
-  <si>
-    <t>relationship--0416c3e3-00bc-44e4-88b4-e2837a311840</t>
-  </si>
-  <si>
-    <t>relationship--0e328b60-be4c-4a17-a480-68f9a95774c9</t>
-  </si>
-  <si>
-    <t>relationship--05358bf0-1b8f-4d3d-9b01-37d1e4f6b814</t>
-  </si>
-  <si>
-    <t>relationship--d8ee9123-00a9-45e8-b9ed-78eaf52fd03c</t>
-  </si>
-  <si>
-    <t>relationship--c99cdf0b-238f-4f4a-bd62-e777028d0888</t>
-  </si>
-  <si>
-    <t>relationship--eb3d94ce-42c1-4f6d-9104-149587001ee8</t>
-  </si>
-  <si>
-    <t>relationship--34fa7ae0-57e6-4802-b731-2a8397e43f5c</t>
-  </si>
-  <si>
-    <t>relationship--658426eb-6159-48b7-834a-d2cba5929840</t>
-  </si>
-  <si>
-    <t>relationship--1b8afd01-f00e-4fb9-8e53-23bf378a5743</t>
-  </si>
-  <si>
-    <t>relationship--c4b84975-0d5b-41da-8dde-a1e4752f8223</t>
-  </si>
-  <si>
-    <t>relationship--3c23657a-af00-4c00-be50-0c2211096383</t>
-  </si>
-  <si>
-    <t>relationship--34f1cc09-99b9-4b55-8a11-a27b71d36a56</t>
-  </si>
-  <si>
-    <t>relationship--2d2d4647-66d2-468f-b5fa-08a23e9f3b52</t>
-  </si>
-  <si>
-    <t>relationship--32fef7ce-3ca8-42d2-9806-8f07130dc59a</t>
-  </si>
-  <si>
-    <t>relationship--45a232f8-5767-419e-9acc-94a2592789a1</t>
-  </si>
-  <si>
-    <t>relationship--8bd14d24-f013-4648-9e45-231c66bee802</t>
-  </si>
-  <si>
-    <t>relationship--e9bd60a6-0325-45da-9bda-fd854a7ce87b</t>
-  </si>
-  <si>
-    <t>relationship--724cc625-5556-40a5-ae14-3d9de64c9a19</t>
-  </si>
-  <si>
-    <t>relationship--00da6316-6f4a-4ee9-84ab-f3bf74b840dc</t>
-  </si>
-  <si>
-    <t>relationship--37a6d563-2564-4062-8967-14950a0a6ff1</t>
-  </si>
-  <si>
-    <t>relationship--5c5eb460-e73e-4c4b-8929-2f3a55616623</t>
-  </si>
-  <si>
-    <t>relationship--41bac798-9a1a-4b92-930c-227474d4cabb</t>
-  </si>
-  <si>
-    <t>relationship--5b9787dc-aaed-4206-acb6-3135336f00dc</t>
-  </si>
-  <si>
-    <t>relationship--92e54ce9-a70b-4436-be5a-e66e682935ec</t>
-  </si>
-  <si>
-    <t>relationship--689c088d-7e07-43c6-a3a3-2059035a0956</t>
-  </si>
-  <si>
-    <t>relationship--1d4bd310-a5da-42a0-896e-ea3ccf0735ef</t>
-  </si>
-  <si>
-    <t>relationship--58b1092a-2708-4e1d-b796-7570f699b314</t>
-  </si>
-  <si>
-    <t>relationship--a700b400-cfb5-4c2d-8ac6-6d3f3a976502</t>
-  </si>
-  <si>
-    <t>relationship--463138d3-daf2-4734-b553-fcc80a9f7245</t>
-  </si>
-  <si>
-    <t>relationship--12c1d59e-77ae-4c17-bd89-4f0d0855db2b</t>
-  </si>
-  <si>
-    <t>relationship--6dd4ef8d-d116-4667-98cd-25d0b4ca2eb2</t>
-  </si>
-  <si>
-    <t>relationship--28bdfc3d-faa4-4c45-8c25-506dc03861d2</t>
-  </si>
-  <si>
-    <t>relationship--2da181d8-efdd-46a5-bc48-a7e761e7700c</t>
-  </si>
-  <si>
-    <t>relationship--30caab21-d762-4082-9483-c4e4b58c8140</t>
-  </si>
-  <si>
-    <t>relationship--edd083ea-aadc-4345-844f-5d40e476e7c8</t>
-  </si>
-  <si>
-    <t>relationship--61c6a3e1-337d-4150-8e33-062db9bf48fb</t>
-  </si>
-  <si>
-    <t>relationship--69593cf2-77f5-4528-95bc-867a7cd474a6</t>
-  </si>
-  <si>
-    <t>relationship--fe839167-b221-48ff-8478-496d40f26604</t>
-  </si>
-  <si>
-    <t>relationship--33cc973e-fa84-415a-a0b3-dc6101374315</t>
-  </si>
-  <si>
-    <t>relationship--0c8a308f-fb09-4df6-9a8b-03dc281625c8</t>
-  </si>
-  <si>
-    <t>relationship--13a0fcb0-b324-4579-a852-51d59b9cfea7</t>
-  </si>
-  <si>
-    <t>relationship--03876e2e-c730-426e-9cf7-5c2d2eacfd12</t>
-  </si>
-  <si>
-    <t>relationship--ac403c59-fdb2-451d-82d5-b227f3fb004e</t>
-  </si>
-  <si>
-    <t>relationship--17501bfb-76d5-452a-a5b7-bb40a2734033</t>
-  </si>
-  <si>
-    <t>relationship--3751fcb4-a779-4bd1-8b91-b4d03da77810</t>
-  </si>
-  <si>
-    <t>relationship--db0bfcda-eb29-4562-aca0-c098711d0d07</t>
-  </si>
-  <si>
-    <t>relationship--092d1143-9f0d-4f94-b49b-b4a78e22aa1f</t>
-  </si>
-  <si>
-    <t>relationship--ff4a5303-2db3-49ae-a53f-7c2dffb9e6ee</t>
-  </si>
-  <si>
-    <t>relationship--2291dd05-1ba6-427c-8f66-f483409905d3</t>
-  </si>
-  <si>
-    <t>relationship--bdf81bef-d89b-49f8-a818-e7348ead0e7d</t>
-  </si>
-  <si>
-    <t>relationship--c0a0ed7b-7375-475c-967c-9635560013b7</t>
-  </si>
-  <si>
-    <t>relationship--35f20b51-ebde-4f96-b4f6-4612f3bceea5</t>
-  </si>
-  <si>
-    <t>relationship--b5c01c41-b1bd-403f-9c86-ee33d9233bb8</t>
-  </si>
-  <si>
-    <t>relationship--9bc2a9d1-da58-403d-98c8-6b56bfd51523</t>
-  </si>
-  <si>
-    <t>relationship--e9b6b440-e6ef-4112-91b7-a10e828f215f</t>
-  </si>
-  <si>
-    <t>relationship--d13278fb-2254-49ef-b205-01e887848910</t>
-  </si>
-  <si>
-    <t>relationship--5efc8b32-1b60-4fad-ae02-e340941487af</t>
-  </si>
-  <si>
-    <t>relationship--2511d69d-6f60-4597-8c57-c435f01cb56c</t>
-  </si>
-  <si>
-    <t>relationship--34272f39-5284-4cd8-aed4-3ac4b7afe9c0</t>
-  </si>
-  <si>
-    <t>relationship--78c44437-c23b-44e3-9b0a-dea9d31afab3</t>
-  </si>
-  <si>
-    <t>relationship--86e8bc77-6840-43e1-9b08-388dd6ce4a71</t>
-  </si>
-  <si>
-    <t>relationship--95a7d566-0538-4e17-b03f-d840ac5a6485</t>
-  </si>
-  <si>
-    <t>relationship--e08df791-6312-4452-a037-50b1c552eae6</t>
-  </si>
-  <si>
-    <t>relationship--ce048198-374c-4f04-8fc5-58aa78334838</t>
-  </si>
-  <si>
-    <t>relationship--ed1b3558-fa7e-4b78-94a6-ede294e5982b</t>
-  </si>
-  <si>
-    <t>relationship--fdb52f1a-9fce-4466-9113-080a43b19d24</t>
-  </si>
-  <si>
-    <t>relationship--a45d91e8-042e-4dde-8bf0-57d321efd381</t>
-  </si>
-  <si>
-    <t>relationship--4c063840-371e-41c6-8f16-15c3bb3b6a07</t>
-  </si>
-  <si>
-    <t>relationship--01302958-accb-41b5-bd1c-cad6bc07a1d6</t>
-  </si>
-  <si>
-    <t>relationship--1e280e04-acc2-4d3a-ad9c-8e779be2623f</t>
-  </si>
-  <si>
-    <t>relationship--68148d92-85e1-47a8-86ad-88953aad0f77</t>
-  </si>
-  <si>
-    <t>relationship--313f6ee5-9364-48f9-839d-edf4e6d25f2a</t>
-  </si>
-  <si>
-    <t>relationship--fb779776-e9f6-45e3-9cb8-c9e509c3e8a7</t>
-  </si>
-  <si>
-    <t>relationship--47e73f6e-a733-46f1-a09b-51f4a0c2574a</t>
-  </si>
-  <si>
-    <t>relationship--d48b2f17-752e-4ef0-85ca-8c5626fe5832</t>
-  </si>
-  <si>
-    <t>relationship--55b721b2-6229-4de6-9655-32647d86e186</t>
-  </si>
-  <si>
-    <t>relationship--e7753b65-5fcf-453a-9139-c1d9028cf696</t>
-  </si>
-  <si>
-    <t>relationship--5f7f0d17-361f-4a98-b1bd-0122c4d69f1d</t>
-  </si>
-  <si>
-    <t>relationship--2e1b7d0a-bc28-4539-92dd-ebfc2bb2a6fc</t>
-  </si>
-  <si>
-    <t>relationship--14628952-a9d9-4da9-a5e2-c807bebc2dbc</t>
-  </si>
-  <si>
-    <t>relationship--9708078b-3306-4693-bf99-43999bd18b3a</t>
-  </si>
-  <si>
-    <t>relationship--ac66737c-9eeb-4d82-a7ef-b0a31bba3e60</t>
-  </si>
-  <si>
-    <t>relationship--e68e8a70-ae5d-4374-9f08-1313f12c0795</t>
-  </si>
-  <si>
-    <t>relationship--f8ea8127-0143-4136-9355-f0672cc93626</t>
-  </si>
-  <si>
-    <t>relationship--9c139044-ce9e-491c-95e2-00ba93a1b5db</t>
-  </si>
-  <si>
-    <t>relationship--a74f7c11-3bc0-48bf-973f-f38cd1531a2e</t>
-  </si>
-  <si>
-    <t>relationship--7d492b91-2741-42d1-a14b-5c68ef16cdde</t>
-  </si>
-  <si>
-    <t>relationship--2e21705c-7535-43ea-971e-ae1c720f97f0</t>
-  </si>
-  <si>
-    <t>relationship--6012c812-46fa-4441-a18e-caca14be105e</t>
-  </si>
-  <si>
-    <t>relationship--7276f7e3-19cc-4f36-b52a-df9b09039d86</t>
-  </si>
-  <si>
-    <t>relationship--38b9b77e-9ac6-4123-ad64-7ee44572da1b</t>
-  </si>
-  <si>
-    <t>relationship--8ab8f626-ae23-4007-bb32-dc128a13c452</t>
-  </si>
-  <si>
-    <t>relationship--a3705dfd-d211-4b6c-b8de-a60b61232ccf</t>
-  </si>
-  <si>
-    <t>relationship--176d7e94-acc7-4510-ab33-fc50ec2eb016</t>
-  </si>
-  <si>
-    <t>relationship--72911605-8706-44a8-9133-cc55f61fbe01</t>
-  </si>
-  <si>
-    <t>relationship--3cecfb1c-8f09-451d-9727-99f8f2060f9a</t>
-  </si>
-  <si>
-    <t>relationship--889bdd3d-7042-4b09-9b8a-2c1063492550</t>
-  </si>
-  <si>
-    <t>relationship--93820292-0d07-4e8a-a732-af6f7fac18f3</t>
-  </si>
-  <si>
-    <t>relationship--d63962bf-f3fd-4159-986d-fb404f8e5c4f</t>
-  </si>
-  <si>
-    <t>relationship--8b4d20df-6e8d-48ed-ad71-b0b73b855a56</t>
-  </si>
-  <si>
-    <t>relationship--9b06ea4e-c75e-41ad-9ba0-b8050f79c4c9</t>
-  </si>
-  <si>
-    <t>relationship--304d883a-85fd-4eb0-8c79-a70babe9fa54</t>
-  </si>
-  <si>
-    <t>relationship--f2124474-a45e-4d8c-b9c3-a4485991a23e</t>
-  </si>
-  <si>
-    <t>relationship--f90a7c85-e4de-457e-b281-b8945307db07</t>
-  </si>
-  <si>
-    <t>relationship--1658c08e-93b2-490d-b21e-2dddf38e2b5c</t>
-  </si>
-  <si>
-    <t>relationship--f3fded44-1a57-418f-b6ae-29b4dbd1bc91</t>
-  </si>
-  <si>
-    <t>relationship--3f971d8b-a5a0-4f8f-b42d-a325cd802149</t>
-  </si>
-  <si>
-    <t>relationship--f45ed62a-12e3-466e-84ea-56ee39b45fe3</t>
-  </si>
-  <si>
-    <t>relationship--acab761b-d19f-4216-a982-e4e9fee04109</t>
-  </si>
-  <si>
-    <t>relationship--bd2a142c-0144-4d20-8e3d-b73ace1abff6</t>
-  </si>
-  <si>
-    <t>relationship--263060ab-6afa-4efa-8121-56ca8c19dea3</t>
-  </si>
-  <si>
-    <t>relationship--18b4ed3f-7d9c-457a-ba75-9b36acdf1b39</t>
-  </si>
-  <si>
-    <t>relationship--4bb0977b-3d05-4362-aeea-cc150865bd4b</t>
-  </si>
-  <si>
-    <t>relationship--9732d9c4-866e-4ec3-acdf-9116f0bd3293</t>
-  </si>
-  <si>
-    <t>relationship--f5e63ee5-77e5-4992-833d-257e32e5ce3e</t>
-  </si>
-  <si>
-    <t>relationship--49d946ff-1e6b-4bf2-a9f1-a9e54213b6ba</t>
-  </si>
-  <si>
-    <t>relationship--3df7af44-b568-4a7c-adf5-95885e794a2f</t>
-  </si>
-  <si>
-    <t>relationship--9e5fe4f7-cd1e-4703-bea2-829fef05d626</t>
-  </si>
-  <si>
-    <t>relationship--14bade66-db15-4761-9e73-2928a3a3891e</t>
-  </si>
-  <si>
-    <t>relationship--2acac976-88b9-4fc7-a0bd-4d03a5f3a9bf</t>
-  </si>
-  <si>
-    <t>relationship--4c3795cc-a1e9-45d1-9a1e-bbf2cde64a15</t>
-  </si>
-  <si>
-    <t>relationship--fe565642-eab5-4ff9-91e1-cea181876211</t>
-  </si>
-  <si>
-    <t>relationship--6278e5d4-ab06-4def-bece-6991bf4b857b</t>
-  </si>
-  <si>
-    <t>relationship--8ae29663-1f05-422d-ba3c-0337760daf4d</t>
-  </si>
-  <si>
-    <t>relationship--7ac36b6b-a053-4b5f-8160-03f2709d8434</t>
-  </si>
-  <si>
-    <t>relationship--33b4f3d5-4d6e-421f-a932-e2ffa44fc7a9</t>
-  </si>
-  <si>
-    <t>relationship--95d794f0-5dc8-4362-b0ff-7ed3dc1eeabd</t>
-  </si>
-  <si>
-    <t>relationship--fbf7379e-6953-413c-8932-a51888aac57e</t>
-  </si>
-  <si>
-    <t>relationship--16390e3a-f86b-4725-907f-991e84d3e0fe</t>
-  </si>
-  <si>
-    <t>relationship--c3d4eae6-f0ec-4700-91e4-270a1b5c6f38</t>
-  </si>
-  <si>
-    <t>relationship--742cbbdd-94d7-4072-9a8b-ecafc56604db</t>
-  </si>
-  <si>
-    <t>relationship--2828cfca-5ceb-4c5a-bb2f-8ffc611954fc</t>
-  </si>
-  <si>
-    <t>relationship--cb6aa417-c3bf-41e3-9e44-209705207413</t>
-  </si>
-  <si>
-    <t>relationship--9f99304a-1059-47a4-bbdf-1f76b23b8ac2</t>
-  </si>
-  <si>
-    <t>relationship--2346dccd-238f-46e8-9aba-6341e3783eda</t>
-  </si>
-  <si>
-    <t>relationship--3138c704-adf0-4cad-8d6a-ad204687d4df</t>
-  </si>
-  <si>
-    <t>relationship--0880242b-9689-482e-9459-4ebd56320f4e</t>
-  </si>
-  <si>
-    <t>relationship--9417f950-d2a7-4417-9c05-6fe57828917e</t>
-  </si>
-  <si>
-    <t>relationship--a2b54231-6b5c-40b3-a417-074b60b3b9e2</t>
-  </si>
-  <si>
-    <t>relationship--23735a53-068a-4d2a-9476-7857dd7e1b74</t>
-  </si>
-  <si>
-    <t>relationship--161fe2ca-c2dc-4d21-a9b0-95935f7d1a52</t>
-  </si>
-  <si>
-    <t>relationship--2e3ad4d6-4817-44d6-a810-1f698a978be1</t>
-  </si>
-  <si>
-    <t>relationship--15f996d2-eaeb-4d08-a6d3-775e6a2f8fbc</t>
-  </si>
-  <si>
-    <t>relationship--04fb06f2-36c2-42da-ba70-c29842d9f3a8</t>
-  </si>
-  <si>
-    <t>relationship--d36f4e6e-728d-4a94-bf5f-9656edeea1da</t>
-  </si>
-  <si>
-    <t>relationship--d15c118c-55a7-4935-aeef-0806723fc244</t>
-  </si>
-  <si>
-    <t>relationship--1fd62ded-faf1-40f6-9a80-8936866af763</t>
-  </si>
-  <si>
-    <t>relationship--2d8b27f2-c98c-4b39-88f4-5b574cb9b16e</t>
-  </si>
-  <si>
-    <t>relationship--c5079e4d-1e54-477a-8e87-858564de885c</t>
-  </si>
-  <si>
-    <t>relationship--0b7931ad-13c9-4e31-bb22-89a1b3b5c3d8</t>
-  </si>
-  <si>
-    <t>relationship--3e43cceb-804e-4e9f-9eb9-980ceea91b04</t>
-  </si>
-  <si>
-    <t>relationship--ba91c710-f339-4c01-a363-be7e7bbf27f3</t>
-  </si>
-  <si>
-    <t>relationship--aac5ca0c-b5f4-4d56-afe6-efa851eef9d5</t>
-  </si>
-  <si>
-    <t>relationship--3237f077-a7a4-4db3-bcc0-8dd58cdf8f28</t>
-  </si>
-  <si>
-    <t>relationship--0612d69c-356a-433b-b2be-0041a7ea6311</t>
-  </si>
-  <si>
-    <t>relationship--736d6234-a45a-4b13-8d65-9d78531f8c15</t>
-  </si>
-  <si>
-    <t>relationship--4a4c98b5-4eb3-4f7b-9472-10828dfa027a</t>
-  </si>
-  <si>
-    <t>relationship--e89ed10a-5ac2-4324-a479-c757c443c9f2</t>
-  </si>
-  <si>
-    <t>relationship--a1ce28ab-391c-4839-864d-65981ace7e50</t>
-  </si>
-  <si>
-    <t>relationship--81f9f1de-ff42-4716-b8ae-58db05eb14e9</t>
-  </si>
-  <si>
-    <t>relationship--5a4845b2-82b0-4319-a7df-3ec49cd4caa1</t>
-  </si>
-  <si>
-    <t>relationship--aba5c12c-37dd-4141-988c-c40248ab20e4</t>
-  </si>
-  <si>
-    <t>relationship--9532b2f2-fe57-4003-81c0-ced8230649a0</t>
-  </si>
-  <si>
-    <t>relationship--9e2bd625-9c8a-491b-88af-fa56bef0cb01</t>
-  </si>
-  <si>
-    <t>relationship--a9e9f64b-4279-4970-b5a6-a888ab472781</t>
-  </si>
-  <si>
-    <t>relationship--7ef9f9d7-6b11-4527-931d-4be1859b8455</t>
-  </si>
-  <si>
-    <t>relationship--95e3cb37-74b2-4501-9ea7-56692dc24879</t>
-  </si>
-  <si>
-    <t>relationship--ac49cbf5-277a-474b-8b5a-db00c63fa9e2</t>
-  </si>
-  <si>
-    <t>relationship--248c0613-5d29-4b5a-b780-9d3faba8e10b</t>
-  </si>
-  <si>
-    <t>relationship--9a059b65-1ded-4470-b2f6-42747e77ba68</t>
-  </si>
-  <si>
-    <t>relationship--b3c79ef3-3d27-463c-9284-93bdb89ba863</t>
-  </si>
-  <si>
-    <t>relationship--dda52d9b-48f7-437a-bf7f-8d1431a370bf</t>
-  </si>
-  <si>
-    <t>relationship--ab8b6530-fe93-49bc-abaf-b6f11504f098</t>
-  </si>
-  <si>
-    <t>relationship--c53182a4-e78b-4543-affd-b08ddd57606a</t>
-  </si>
-  <si>
-    <t>relationship--1adbac6f-5b26-41e7-8629-024177c49d43</t>
-  </si>
-  <si>
-    <t>relationship--5bbd8003-05ff-4bff-bdb6-f3e7069a9d56</t>
-  </si>
-  <si>
-    <t>relationship--1860e0ed-660b-4853-9ff9-acf4008a1c60</t>
-  </si>
-  <si>
-    <t>relationship--0f626ab6-b22c-43cc-a529-427f27d4cd4a</t>
-  </si>
-  <si>
-    <t>relationship--b121753a-fe68-4d5c-a739-da48fca417e4</t>
-  </si>
-  <si>
-    <t>relationship--7ce06181-38d2-41b8-a75f-79d0e7ec6bae</t>
-  </si>
-  <si>
-    <t>relationship--783a6d7a-1c0e-4d55-84fe-375b495a73ef</t>
-  </si>
-  <si>
-    <t>relationship--91896033-1306-4164-ad3c-f7c9af44a58b</t>
-  </si>
-  <si>
-    <t>relationship--5e4917f1-5bd5-4bfc-a170-040e70d2f3c1</t>
-  </si>
-  <si>
-    <t>relationship--7990f3bc-8d0a-42cd-acaf-0bb0cb647a90</t>
-  </si>
-  <si>
-    <t>relationship--bfc9348a-9983-430a-8931-b7e35613d7b2</t>
-  </si>
-  <si>
-    <t>relationship--b9f40bc8-8e9f-473f-9d66-672b653721f9</t>
-  </si>
-  <si>
-    <t>relationship--0848b07e-1b83-4ee0-82e2-d8f1e17ee99a</t>
-  </si>
-  <si>
-    <t>relationship--d7eafec2-7c5e-4a6e-ad62-d713cc14b414</t>
-  </si>
-  <si>
-    <t>relationship--84602b4a-38d6-48e6-9d35-7e4275415071</t>
-  </si>
-  <si>
-    <t>relationship--617026e5-fd9d-49ea-a9d1-a84d87f652f0</t>
-  </si>
-  <si>
-    <t>relationship--69b45d78-b769-4614-b1e1-58942289ffe1</t>
-  </si>
-  <si>
-    <t>relationship--beecf6d7-36fe-43f7-a1da-7315c042bd10</t>
-  </si>
-  <si>
-    <t>relationship--74af7e90-dd63-418a-b257-84f0e3aee0dc</t>
-  </si>
-  <si>
-    <t>relationship--41dbbfbb-bb93-4e80-9a3d-4f84a36e5826</t>
-  </si>
-  <si>
-    <t>relationship--4962e2ed-68d1-4488-86de-3a303a238a2b</t>
-  </si>
-  <si>
-    <t>relationship--6647a361-ee08-4d1c-9707-c5313ef988a8</t>
-  </si>
-  <si>
-    <t>relationship--afaad920-53d7-45fe-b133-cb0ed1b0d297</t>
-  </si>
-  <si>
-    <t>relationship--733568b7-95ed-47e0-a741-ccf995cdf001</t>
-  </si>
-  <si>
-    <t>relationship--ac8da5f2-078f-4051-a6ab-82ef4221043a</t>
-  </si>
-  <si>
-    <t>relationship--52a05cca-efba-4875-8158-74fc9db94cbc</t>
-  </si>
-  <si>
-    <t>relationship--a62fe462-c0fd-45ea-bd02-b7ae576b0a77</t>
-  </si>
-  <si>
-    <t>relationship--71253b77-8675-46fb-b8d7-4fbbf8f381ab</t>
-  </si>
-  <si>
-    <t>relationship--e2bbc820-11de-4385-9f33-39aed660e08e</t>
-  </si>
-  <si>
-    <t>relationship--de9f3fc1-16dd-424d-98e0-7ce81ed92ce3</t>
-  </si>
-  <si>
-    <t>relationship--c554de6a-4ca1-4258-9c30-de58c01f848e</t>
-  </si>
-  <si>
-    <t>relationship--88bb3243-d057-4c18-902e-4135bf1045fc</t>
-  </si>
-  <si>
-    <t>relationship--d55af97a-39e5-47a7-8f40-7c20c61e8654</t>
-  </si>
-  <si>
-    <t>relationship--62b71848-b849-4080-911f-aba18b3b6a1c</t>
-  </si>
-  <si>
-    <t>relationship--8410eca9-cfe9-4cb2-bc0b-34794e3a1dc1</t>
-  </si>
-  <si>
-    <t>relationship--15401ffc-3093-40be-9f11-825cc9e3484e</t>
-  </si>
-  <si>
-    <t>relationship--2a84694e-0961-4bb8-b770-22dd2420c4af</t>
-  </si>
-  <si>
-    <t>relationship--2cfb2ee2-2574-453e-bb71-d1330a8c310f</t>
-  </si>
-  <si>
-    <t>relationship--09190a94-3902-4948-94cf-f1859831afec</t>
-  </si>
-  <si>
-    <t>relationship--265d1479-d38b-4859-b41b-d3240b6ab7aa</t>
-  </si>
-  <si>
-    <t>relationship--ff33a5bc-6d82-452d-937b-ec9c08cdc50b</t>
-  </si>
-  <si>
-    <t>relationship--803e9bbf-161a-4e5e-9731-a3dea5f24369</t>
-  </si>
-  <si>
-    <t>relationship--e4d6e73a-af5a-4d83-b335-2e083045ce97</t>
-  </si>
-  <si>
-    <t>relationship--1d17f76d-5b3d-4615-adab-9aba717c3f50</t>
-  </si>
-  <si>
-    <t>relationship--5d161d88-7f5e-4e40-9601-7425c8fad16d</t>
-  </si>
-  <si>
-    <t>relationship--8debb06e-d43e-4e19-bf07-4a870ec0fb66</t>
-  </si>
-  <si>
-    <t>relationship--ad8449b4-ef75-4f64-a179-6c16292e769a</t>
-  </si>
-  <si>
-    <t>relationship--4a10a6c1-b091-4a62-b86d-39236c9798a0</t>
-  </si>
-  <si>
-    <t>relationship--35b3910e-ed22-4888-bfc5-f349e0bb22c1</t>
-  </si>
-  <si>
-    <t>relationship--09310efa-0ebb-4cef-be5c-0c04372cbab4</t>
-  </si>
-  <si>
-    <t>relationship--a0cab5c2-6d75-4c7e-a1d1-9104e6f4d382</t>
-  </si>
-  <si>
-    <t>relationship--c67f914b-7aee-4b52-80be-14ff0de19509</t>
-  </si>
-  <si>
-    <t>relationship--2c7ea63d-f8ce-4f79-a51b-aee5da46d382</t>
-  </si>
-  <si>
-    <t>relationship--9ba73000-425c-4eef-8d23-0eddd5fbe5b8</t>
-  </si>
-  <si>
-    <t>relationship--b97c6c8f-4556-4f0c-b727-b7c1ee3bbc29</t>
-  </si>
-  <si>
-    <t>relationship--f7bb10ae-1dd7-4d5d-9c54-78bf99b976d6</t>
-  </si>
-  <si>
-    <t>relationship--5552c579-ca7a-4a01-b8b3-3ca980cba14b</t>
-  </si>
-  <si>
-    <t>relationship--156e8d02-57d9-4d23-b134-3a2ca6eadf60</t>
-  </si>
-  <si>
-    <t>relationship--d96da0bc-fbf6-411f-8bc3-2ca02f16725c</t>
-  </si>
-  <si>
-    <t>relationship--bed818e0-76ce-4506-bc5f-a8a1ec1a295d</t>
-  </si>
-  <si>
-    <t>relationship--3f5df155-5aae-44da-9af9-1a226d03e6ab</t>
-  </si>
-  <si>
-    <t>relationship--e5728e9c-6648-4dc0-b6ec-78774623accc</t>
-  </si>
-  <si>
-    <t>relationship--4ab76bec-c8cf-4c6e-a539-0ada2cfeb687</t>
-  </si>
-  <si>
-    <t>relationship--5d8f1aa8-f58f-4286-b678-6fe780d8ef89</t>
-  </si>
-  <si>
-    <t>relationship--37225940-e78f-463d-aae7-9c295d1690a5</t>
-  </si>
-  <si>
-    <t>relationship--c232b6ce-e4e3-492a-8ae7-cc0cfe0ae42b</t>
-  </si>
-  <si>
-    <t>relationship--0fdcd987-9d89-452a-bf7f-845555e8c2b8</t>
-  </si>
-  <si>
-    <t>relationship--46189e0b-5bb5-4884-a2a2-6252bd84b2ca</t>
-  </si>
-  <si>
-    <t>relationship--986f87b8-7ad8-489a-9938-b1068257ebe0</t>
-  </si>
-  <si>
-    <t>relationship--03375ddd-96af-4bf3-a288-92a3be6af9b4</t>
-  </si>
-  <si>
-    <t>relationship--d2d2421b-0ea8-427e-9d70-f0506dc0c64d</t>
-  </si>
-  <si>
-    <t>relationship--a0226ea2-b120-4749-b341-18b2a3de7dd0</t>
-  </si>
-  <si>
-    <t>relationship--84ab087d-7457-42f3-898d-5fee54bd0483</t>
-  </si>
-  <si>
-    <t>relationship--c7c9485c-39ed-4fba-a7ad-beb89b7cf56f</t>
-  </si>
-  <si>
-    <t>relationship--239d7608-34a5-4835-b7f7-c02ac2a9a6af</t>
-  </si>
-  <si>
-    <t>relationship--f287ba30-6aed-42b3-b3bc-5bee0294e476</t>
-  </si>
-  <si>
-    <t>relationship--fb3b5767-aec3-481e-95b4-b71c2ef6de96</t>
-  </si>
-  <si>
-    <t>relationship--501812d7-1650-4734-a274-3ef98476cd55</t>
-  </si>
-  <si>
-    <t>relationship--b0444f41-3c81-4a1a-b481-3f49ec4a4e31</t>
-  </si>
-  <si>
-    <t>relationship--b80cabe7-6934-4b3a-9b89-02bef7d6c618</t>
-  </si>
-  <si>
-    <t>relationship--f5dc9fa0-9614-4a88-9e07-f45255c10932</t>
-  </si>
-  <si>
-    <t>relationship--0c1ef22b-d183-4824-b170-bffcec8a57ee</t>
-  </si>
-  <si>
-    <t>relationship--45203285-e86a-4b6b-bb9e-7405a51a3c34</t>
-  </si>
-  <si>
-    <t>relationship--c02c8bfd-f9a6-4d25-b9bc-fee664d7846d</t>
-  </si>
-  <si>
-    <t>relationship--526d32f2-6608-473d-96a9-0128fd8c4d65</t>
-  </si>
-  <si>
-    <t>relationship--707b76d4-6b45-4def-a530-fba1a7697323</t>
-  </si>
-  <si>
-    <t>relationship--af67535f-654c-476d-933a-70b357f7ad7d</t>
-  </si>
-  <si>
-    <t>relationship--70c92e60-aa83-4abd-9f0f-9a07452090a8</t>
-  </si>
-  <si>
-    <t>relationship--34b4188e-a222-419b-a8a7-87dc5979b184</t>
-  </si>
-  <si>
-    <t>relationship--ba6bcb7f-a2c3-4a1e-a231-847c8c3c25af</t>
-  </si>
-  <si>
-    <t>relationship--ec5aefef-ed6b-4569-9562-52bc2218958f</t>
-  </si>
-  <si>
-    <t>relationship--8333d52c-373c-4705-8b6a-fc8f60f4acb9</t>
-  </si>
-  <si>
-    <t>relationship--2b10ba2c-3e5c-4493-90a9-6a4969709943</t>
-  </si>
-  <si>
-    <t>relationship--d6588f70-b2c0-4f7b-a7de-4234a7d3d393</t>
-  </si>
-  <si>
-    <t>relationship--c8608ea5-5c2e-4d1f-af4e-a403e58a1ddc</t>
-  </si>
-  <si>
-    <t>relationship--3362b6b6-9539-44fb-bbb1-77ca62463972</t>
-  </si>
-  <si>
-    <t>relationship--86f9b1d0-343f-4d2a-b067-baeaa1a5e2ae</t>
-  </si>
-  <si>
-    <t>relationship--ee4218f6-1ce4-4b3d-8d0f-c35d633fa5fd</t>
-  </si>
-  <si>
-    <t>relationship--5e65b072-02c9-4fd1-927e-fe73a3b9c3cc</t>
-  </si>
-  <si>
-    <t>relationship--43f4cbac-131e-477f-ba40-a48a4f09bae7</t>
-  </si>
-  <si>
-    <t>relationship--1703c07c-db59-4561-9aef-0e98c02b9770</t>
-  </si>
-  <si>
-    <t>relationship--d4963880-dd41-4212-afa4-2fdd2806447b</t>
-  </si>
-  <si>
-    <t>relationship--ff8a2389-f5dc-4ca6-ab72-fa4f2934be66</t>
-  </si>
-  <si>
-    <t>relationship--b289c407-48a4-4c20-acde-4fc18f0793aa</t>
-  </si>
-  <si>
-    <t>relationship--8e516f24-9475-40a8-bf4d-e32d3ab3b0f8</t>
-  </si>
-  <si>
-    <t>relationship--a783f428-93f7-4d30-8b8c-3cea3af59dbd</t>
-  </si>
-  <si>
-    <t>relationship--510e5f0c-f40b-4613-b116-7905ed679254</t>
-  </si>
-  <si>
-    <t>relationship--5ee050bb-caa5-4027-8c86-d89457143b70</t>
-  </si>
-  <si>
-    <t>relationship--570688c9-d884-4a11-8a88-dce68ac57c6d</t>
-  </si>
-  <si>
-    <t>relationship--038d1bfe-28b7-44c2-a6a0-ee5e025aedc0</t>
-  </si>
-  <si>
-    <t>relationship--ef099864-160b-40b4-a485-abae77993da8</t>
-  </si>
-  <si>
-    <t>relationship--8d18a790-bb6d-4123-b992-bff8839edc74</t>
-  </si>
-  <si>
-    <t>relationship--dcd721b8-0e41-47d5-b197-ced965eef40c</t>
-  </si>
-  <si>
-    <t>relationship--a467f8b9-78d7-4bad-acfb-978800a868c6</t>
-  </si>
-  <si>
-    <t>relationship--1cce5d0a-384f-407f-8829-0a81968155ce</t>
-  </si>
-  <si>
-    <t>relationship--f1d13d8d-c7fb-43ea-a060-1a5a1a177c2f</t>
-  </si>
-  <si>
-    <t>relationship--ea2ebc72-d18a-448b-9b13-7823bf2b0020</t>
-  </si>
-  <si>
-    <t>relationship--4324d530-438a-4a08-a4a5-450f34b19740</t>
-  </si>
-  <si>
-    <t>relationship--d7aa4588-8ac3-4532-af96-1a85eb79795f</t>
-  </si>
-  <si>
-    <t>relationship--790bc734-b044-4365-ae92-81e0d489b7f1</t>
-  </si>
-  <si>
-    <t>relationship--88c49f62-bbc9-4dbb-b171-f40ca7468289</t>
-  </si>
-  <si>
-    <t>relationship--1d0432ae-0659-41ba-a845-4d858ffe37e2</t>
-  </si>
-  <si>
-    <t>relationship--05dd34a2-9957-4e86-9534-e400d6dcf24a</t>
-  </si>
-  <si>
-    <t>relationship--676bcf81-589f-48d4-852f-44a7687fd5bb</t>
-  </si>
-  <si>
-    <t>relationship--ad47e557-908d-4ff3-b767-9809667070b2</t>
-  </si>
-  <si>
-    <t>relationship--c7f696be-a1d0-434e-8c6e-45c6cb26d255</t>
-  </si>
-  <si>
-    <t>relationship--29e04dd7-5a43-408b-a8ff-8c8b3516666e</t>
-  </si>
-  <si>
-    <t>relationship--53885f25-29da-4650-a3ab-c780b8b681ed</t>
-  </si>
-  <si>
-    <t>relationship--5522fb34-89d3-4d94-8943-19a95cfd80a8</t>
-  </si>
-  <si>
-    <t>relationship--00054969-0bcd-410a-a089-d1c4f48f4ced</t>
-  </si>
-  <si>
-    <t>relationship--fa66eb5a-75ee-432c-b536-d6b2f38b929b</t>
-  </si>
-  <si>
-    <t>relationship--fac1d288-ae4a-4c88-833f-854bed4c2fff</t>
-  </si>
-  <si>
-    <t>relationship--44d2840b-fe2f-45d6-b326-c73f8e8f0f1c</t>
-  </si>
-  <si>
-    <t>relationship--2daf3b19-b9bf-4d3b-87cb-a316e35f4e23</t>
-  </si>
-  <si>
-    <t>relationship--445ef799-5441-4780-858a-d669d25d61a5</t>
-  </si>
-  <si>
-    <t>relationship--cc8ed1d5-ac37-4c4c-8144-10b4803716d5</t>
-  </si>
-  <si>
-    <t>relationship--3a8fd0f8-288e-4644-9df2-8b8fa0a7d324</t>
-  </si>
-  <si>
-    <t>relationship--e2f78c0c-cfd5-43b5-9b1d-61dfe130674d</t>
-  </si>
-  <si>
-    <t>relationship--c38ab01c-8556-430e-8eb6-9fbcf10e0dd9</t>
-  </si>
-  <si>
-    <t>relationship--6494ae06-a2ca-46ef-9b80-3595bbb7393c</t>
-  </si>
-  <si>
-    <t>relationship--aa3904df-e13b-43ea-a06e-d284ba324f6e</t>
-  </si>
-  <si>
-    <t>relationship--424767de-ec68-4018-91b1-880c745a3d5a</t>
-  </si>
-  <si>
-    <t>relationship--cfbd9282-fdc2-4d1c-8035-fac2e924d447</t>
-  </si>
-  <si>
-    <t>relationship--cb07b69c-2cc8-4e90-9658-3995beba2394</t>
-  </si>
-  <si>
-    <t>relationship--48b3fccb-7a56-44f2-a4b3-45eb812e2726</t>
-  </si>
-  <si>
-    <t>relationship--2094783b-721a-411d-a142-06bfb458e71a</t>
-  </si>
-  <si>
-    <t>relationship--6f26e46d-aea8-4f6a-8a13-b598f88d16d9</t>
-  </si>
-  <si>
-    <t>relationship--ec759562-bbd9-4b75-a7b6-79108da59569</t>
-  </si>
-  <si>
-    <t>relationship--d3d29946-55b5-4e56-bb77-4817111ed284</t>
-  </si>
-  <si>
-    <t>relationship--823dadbb-4af3-46e8-af9d-b39b17ca84d5</t>
-  </si>
-  <si>
-    <t>relationship--88e28cf4-e804-47bd-99b3-ddcb8497b4a4</t>
-  </si>
-  <si>
-    <t>relationship--876f4555-3d08-4bfd-8a9d-73479599d3d6</t>
-  </si>
-  <si>
-    <t>relationship--a7ec7934-e4f4-4026-b71f-7990ecb296b7</t>
-  </si>
-  <si>
-    <t>relationship--487de349-615b-48ad-80d7-b95236eecc02</t>
-  </si>
-  <si>
-    <t>relationship--13995ae8-f441-41b5-9724-aab410eaa87f</t>
-  </si>
-  <si>
-    <t>relationship--afd12d83-7475-4510-8c3f-72e983b88113</t>
-  </si>
-  <si>
-    <t>relationship--11a8a1e0-ece3-43f9-8821-02e803bda225</t>
-  </si>
-  <si>
-    <t>relationship--55a46f0e-5aae-462d-80a2-1fee0880dcef</t>
-  </si>
-  <si>
-    <t>relationship--ea520e3e-d699-477c-8969-2c6d6e3d36d4</t>
-  </si>
-  <si>
-    <t>relationship--9b9aae58-6a65-4e11-a5ec-e9510321fea1</t>
-  </si>
-  <si>
-    <t>relationship--b063931d-c06e-4f16-9cfc-b0dddb3e3c43</t>
-  </si>
-  <si>
-    <t>relationship--db2c8d09-3e56-4685-ab16-f063526b19b2</t>
-  </si>
-  <si>
-    <t>relationship--a8e4b3d5-dc03-4f52-8f65-1ee2fa2f0162</t>
-  </si>
-  <si>
-    <t>relationship--707512ad-77bd-4472-ba56-13352a5d0859</t>
-  </si>
-  <si>
-    <t>relationship--85a3d8fe-68d5-41cf-86ae-d20bab16132b</t>
-  </si>
-  <si>
-    <t>relationship--6cff1afe-2cb8-4db9-840b-01edf39d52bc</t>
-  </si>
-  <si>
-    <t>relationship--db76e378-fc70-4c63-97ca-2aabe1818f45</t>
-  </si>
-  <si>
-    <t>relationship--f3f1dcd0-5834-4149-9583-df73aabde910</t>
-  </si>
-  <si>
-    <t>relationship--3c5f7264-7249-466b-b2ff-1aab1cfcf7a8</t>
-  </si>
-  <si>
-    <t>relationship--10b8424a-5a18-48f7-8460-9b56f02c64a9</t>
-  </si>
-  <si>
-    <t>relationship--420bac05-ec0c-457e-b10d-05709ed00508</t>
-  </si>
-  <si>
-    <t>relationship--e4a1859d-56db-473f-8f3a-01d1ecff9865</t>
-  </si>
-  <si>
-    <t>relationship--6f10115c-4687-4bb1-ad80-a8286e8d7ea1</t>
-  </si>
-  <si>
-    <t>relationship--af89ecff-ebd0-48b1-a999-cf7e090359f5</t>
-  </si>
-  <si>
-    <t>relationship--900f0776-6af6-4e52-9d40-407a14a1b10b</t>
-  </si>
-  <si>
-    <t>relationship--ad5911ae-9931-4303-917c-8bf0af554ba2</t>
-  </si>
-  <si>
-    <t>relationship--27fe1e23-9e8e-4e9a-867c-e971f5b27938</t>
-  </si>
-  <si>
-    <t>relationship--cbb50fab-7e8e-4d6c-86d5-832106d6b535</t>
-  </si>
-  <si>
-    <t>relationship--67460a1f-ba46-4ccd-b625-bd6f2659da8a</t>
-  </si>
-  <si>
-    <t>relationship--c79370be-6bfa-4f46-b747-87900992f20c</t>
-  </si>
-  <si>
-    <t>relationship--66de0818-b1aa-4fdf-8b59-41657de9a959</t>
-  </si>
-  <si>
-    <t>relationship--6c62bd91-cec9-43e4-96c0-7de19a976626</t>
-  </si>
-  <si>
-    <t>relationship--10b316d6-a09c-4d60-988f-646e42467869</t>
-  </si>
-  <si>
-    <t>relationship--6e328eb1-08b5-4e49-975c-94c709bd409b</t>
-  </si>
-  <si>
-    <t>relationship--3406d69f-e0ac-4f8e-87a4-6dff7e804f99</t>
-  </si>
-  <si>
-    <t>relationship--269c07e7-e785-4fbe-9b44-37915c651501</t>
-  </si>
-  <si>
-    <t>relationship--f6705a7b-13a9-46b0-bcdb-4e1d69b9d930</t>
-  </si>
-  <si>
-    <t>relationship--232b88a1-d90d-4d5e-8167-da7b7c35c1e3</t>
-  </si>
-  <si>
-    <t>relationship--2cb4cae9-3ff4-4d54-8779-eabc3825c303</t>
-  </si>
-  <si>
-    <t>relationship--2a8ee6fa-55f4-4ad6-9954-df7b9cd95e87</t>
-  </si>
-  <si>
-    <t>relationship--c6724897-4f7a-486a-9976-c1e916d1539d</t>
-  </si>
-  <si>
-    <t>relationship--9eec828d-aff9-4828-856a-ad89e8adc4be</t>
-  </si>
-  <si>
-    <t>relationship--0679e913-f222-4d1f-9a96-6fd772a674ba</t>
-  </si>
-  <si>
-    <t>relationship--c51a31a2-b9e1-4b98-bc26-f590dad3dd7e</t>
-  </si>
-  <si>
-    <t>relationship--0be151f9-7e48-4fd1-b215-5c05f2729c36</t>
-  </si>
-  <si>
-    <t>relationship--61a209ed-7f03-488e-ad53-53aefd2e9ebb</t>
-  </si>
-  <si>
-    <t>relationship--ead62c20-6c77-4fd3-949e-c9a6954be6e7</t>
-  </si>
-  <si>
-    <t>relationship--3dcb1927-c157-4cc5-a204-237cc422e526</t>
-  </si>
-  <si>
-    <t>relationship--f5e5f729-f586-4c58-a2ac-9121ffe6abda</t>
-  </si>
-  <si>
-    <t>relationship--dbe7fab1-5ef3-491d-a1e7-a8c0a701c0aa</t>
-  </si>
-  <si>
-    <t>relationship--e73af7f5-6e5f-49a9-8ed3-d13e0868880d</t>
-  </si>
-  <si>
-    <t>relationship--e20bd310-d4bc-4df3-bfb3-a9836ddfb310</t>
-  </si>
-  <si>
-    <t>relationship--10158e66-8cd1-4b8c-86b9-f88759d46427</t>
-  </si>
-  <si>
-    <t>relationship--d1cb891e-1cad-4db4-8bc7-f62fdabf433e</t>
-  </si>
-  <si>
-    <t>relationship--baf7aa9e-6e05-43a1-b972-90441df19a3e</t>
-  </si>
-  <si>
-    <t>relationship--ec58d906-6864-4068-89bb-bebe7ae99785</t>
-  </si>
-  <si>
-    <t>relationship--d298e28d-250f-4cd0-a856-b89e5ce7b88d</t>
-  </si>
-  <si>
-    <t>relationship--c269fe15-c5be-4823-a518-f9fc55959bc6</t>
-  </si>
-  <si>
-    <t>relationship--50050696-12a8-4fa3-a415-53b8b82dea85</t>
-  </si>
-  <si>
-    <t>relationship--874d162e-2c50-4199-b6a4-39079e1afd2c</t>
-  </si>
-  <si>
-    <t>relationship--f4a5485f-8491-422f-8796-eb43f662ef04</t>
-  </si>
-  <si>
-    <t>relationship--70afaa59-d579-4c48-a4f7-e5f655976d8e</t>
-  </si>
-  <si>
-    <t>relationship--a423a829-7a8d-45da-b736-9a04cf98b61a</t>
-  </si>
-  <si>
-    <t>relationship--70bbeb57-4b3c-4fab-adc1-1dc6198e13b4</t>
-  </si>
-  <si>
-    <t>relationship--0a67dac3-b381-434b-abb7-ef513e09f6cf</t>
-  </si>
-  <si>
-    <t>relationship--4f678204-fcd8-4267-9153-9a4371987f30</t>
-  </si>
-  <si>
-    <t>relationship--ef486430-74c7-4fe2-b673-5fc558d8a341</t>
-  </si>
-  <si>
-    <t>relationship--33b362c3-ef66-4952-a0ed-0dedcc6fb7ff</t>
-  </si>
-  <si>
-    <t>relationship--b792f9e3-9b9c-4536-a89f-174effa04791</t>
-  </si>
-  <si>
-    <t>relationship--8f35ece3-fb19-421a-9f69-555f1050e821</t>
-  </si>
-  <si>
-    <t>relationship--f7a42814-cfdc-4ee8-b3aa-f621d054d2bd</t>
-  </si>
-  <si>
-    <t>relationship--6d5ec928-0460-4088-bf4d-a84766632043</t>
-  </si>
-  <si>
-    <t>relationship--2577f486-51c5-4c4f-bc31-c358edfae31d</t>
-  </si>
-  <si>
-    <t>relationship--957dac06-84ad-428b-95bf-66a508e5d916</t>
-  </si>
-  <si>
-    <t>relationship--6533395a-88f1-4ea2-b736-36c326d771a9</t>
-  </si>
-  <si>
-    <t>relationship--57f29431-847a-43e0-b7e6-1a431a2058e8</t>
-  </si>
-  <si>
-    <t>relationship--e4a98f6c-89c4-440c-b379-ab19a0b17e01</t>
-  </si>
-  <si>
-    <t>relationship--00ab4613-70a8-4939-9c07-372c0bc9860c</t>
-  </si>
-  <si>
-    <t>relationship--cc04b3b3-67ae-44e0-9436-7ff30af33bf7</t>
-  </si>
-  <si>
-    <t>relationship--c1eaee30-f633-4217-bd44-8d15f9d8c065</t>
-  </si>
-  <si>
-    <t>relationship--077a5af9-f296-4f30-967a-ab5cd4faf152</t>
-  </si>
-  <si>
-    <t>relationship--7e59d2ea-b884-41f7-92fd-edc063f147c8</t>
-  </si>
-  <si>
-    <t>relationship--ed7fbb91-8764-4af0-8a62-052e4e6d95d4</t>
-  </si>
-  <si>
-    <t>relationship--cb1bd2c3-a763-4fd2-8c8d-29ca5b1c6ff7</t>
-  </si>
-  <si>
-    <t>relationship--383f4b08-21e5-4e95-a92a-190a74bec975</t>
-  </si>
-  <si>
-    <t>relationship--b8487f86-404d-4580-bb96-4bf795ba066b</t>
-  </si>
-  <si>
-    <t>relationship--52d1bb56-b482-4ba3-8323-d423f21a8c6e</t>
-  </si>
-  <si>
-    <t>relationship--55236e8d-545e-4952-a518-32d267b79248</t>
-  </si>
-  <si>
-    <t>relationship--630137a1-fab5-4996-b489-94b760c08587</t>
-  </si>
-  <si>
-    <t>relationship--8c718d39-0585-4e91-a06f-d9366b81648b</t>
-  </si>
-  <si>
-    <t>relationship--7d415e7b-01a9-478e-9e71-65687ae5091a</t>
-  </si>
-  <si>
-    <t>relationship--aac45e98-80d3-4f9b-bee1-28f0397d63c5</t>
-  </si>
-  <si>
-    <t>relationship--2435cd1e-cd99-425b-832c-7d629f6ee15a</t>
-  </si>
-  <si>
-    <t>relationship--dd956bb0-b061-4a33-8b45-ce09ae518653</t>
-  </si>
-  <si>
-    <t>relationship--b9968c17-292b-4890-aac2-73f7458b4efc</t>
-  </si>
-  <si>
-    <t>relationship--d8c5dfde-2fa6-4075-a4ee-14afcf5356db</t>
-  </si>
-  <si>
-    <t>relationship--ee02a592-fd90-451d-90d5-d2c8d4467ecc</t>
-  </si>
-  <si>
-    <t>relationship--8e295d63-6597-43da-9840-66b7e6ca81b7</t>
-  </si>
-  <si>
-    <t>relationship--92a21bbe-ad5f-4baf-91b0-734d79c01d80</t>
-  </si>
-  <si>
-    <t>relationship--46b0d5ce-0d5c-45b9-9803-2ae4190d0c4c</t>
-  </si>
-  <si>
-    <t>relationship--805a683c-6989-4638-a65d-bcbc3764742a</t>
-  </si>
-  <si>
-    <t>relationship--7e36c1c8-aeb0-4f4f-84ea-86db8d462300</t>
-  </si>
-  <si>
-    <t>relationship--160f57d0-2863-43a6-bfa1-267076ca1d6a</t>
-  </si>
-  <si>
-    <t>relationship--367f3fa8-0c9c-4a10-94a5-5d72b06f96b7</t>
-  </si>
-  <si>
-    <t>relationship--0ec2c2c7-802b-40c0-8428-c963a8e4f90c</t>
-  </si>
-  <si>
-    <t>relationship--e71cbf0d-3d7b-4dbd-ac52-cc1a5866aad4</t>
-  </si>
-  <si>
-    <t>relationship--d852a84f-3c45-4ef2-8fd1-13a3c224137f</t>
-  </si>
-  <si>
-    <t>relationship--878c28e1-7169-459c-91a4-3ed447223d70</t>
-  </si>
-  <si>
-    <t>relationship--81b6bc77-c102-4a05-a579-5e89bd13cc12</t>
-  </si>
-  <si>
-    <t>relationship--77ffef49-fa37-4d05-b1a4-1d7751f79ee4</t>
-  </si>
-  <si>
-    <t>relationship--577e0dbe-1ef5-4fd2-a187-44324ce4a72e</t>
-  </si>
-  <si>
-    <t>relationship--b500e8e8-9847-4766-8f94-34b72b6689c8</t>
-  </si>
-  <si>
-    <t>relationship--29b1511e-eca2-451c-90c5-d4a2b3b608e7</t>
-  </si>
-  <si>
-    <t>relationship--c7fbd8ed-a720-4bec-bd85-41cbe4cdc22f</t>
-  </si>
-  <si>
-    <t>relationship--c74ac39e-968c-46f0-9d68-0c89efe7d6d7</t>
-  </si>
-  <si>
-    <t>relationship--ed809171-4923-43da-a9ad-138283fb7eaf</t>
-  </si>
-  <si>
-    <t>relationship--d6a739e6-c1dd-4cd3-a692-753d5edfcafa</t>
-  </si>
-  <si>
-    <t>relationship--89dd3e0e-2239-4e0c-8cb6-8861b76e0d3c</t>
-  </si>
-  <si>
-    <t>relationship--70f3bbdf-9325-4013-8c73-4f02cb19a47f</t>
-  </si>
-  <si>
-    <t>relationship--0d3ee557-dd08-4c96-baa0-b81cb941cf3e</t>
-  </si>
-  <si>
-    <t>relationship--9591863f-3471-44ae-8a35-1bc56d3a62c1</t>
-  </si>
-  <si>
-    <t>relationship--6f169388-5ee6-4848-805b-165b3fa47dff</t>
-  </si>
-  <si>
-    <t>relationship--33b65c8d-6b41-4163-b2d3-1666c37a9032</t>
-  </si>
-  <si>
-    <t>relationship--f4df1e00-8a91-4b71-b675-25d60bad6a98</t>
-  </si>
-  <si>
-    <t>relationship--24d503a3-8f4f-4244-ad19-1b222b59e7ef</t>
-  </si>
-  <si>
-    <t>relationship--2b63bdcf-a516-4ee3-b148-08bdd7a7cb9d</t>
-  </si>
-  <si>
-    <t>relationship--c0d66f67-d5fc-4718-87b7-13907602bba3</t>
-  </si>
-  <si>
-    <t>relationship--e67e91a0-480a-4ef4-8eeb-81989eadf823</t>
-  </si>
-  <si>
-    <t>relationship--cf7e2563-1bd6-49b2-b95d-70e7b2d5ef86</t>
-  </si>
-  <si>
-    <t>relationship--3519f430-e040-4aee-951d-4527c6545b36</t>
-  </si>
-  <si>
-    <t>relationship--76186630-c101-4f9d-a1ff-6aec5709b600</t>
-  </si>
-  <si>
-    <t>relationship--85357ec1-3dc2-4f90-854e-433509aab018</t>
-  </si>
-  <si>
-    <t>relationship--20780665-a60b-4f7f-971f-5184a072cefc</t>
-  </si>
-  <si>
-    <t>relationship--8b9d3fc3-1e2e-4ca0-ac96-0153a479d186</t>
-  </si>
-  <si>
-    <t>relationship--a74f2cd1-670a-4c86-9add-59a4fda87cbf</t>
-  </si>
-  <si>
-    <t>relationship--295d93e4-0fd4-401e-9b07-610d743be347</t>
-  </si>
-  <si>
-    <t>relationship--8770ccbf-0457-469f-b0eb-bf0fc740dd31</t>
-  </si>
-  <si>
-    <t>relationship--6780bd12-6e75-4185-b1a9-6ea68e82f9a5</t>
-  </si>
-  <si>
-    <t>relationship--363dd54a-6b6c-4d29-b12b-7633f127ae4f</t>
-  </si>
-  <si>
-    <t>relationship--c6fae978-de61-436a-b541-b9ccb8b8ddea</t>
-  </si>
-  <si>
-    <t>relationship--87e4a348-08b9-4ba3-aeed-4e125c080132</t>
-  </si>
-  <si>
-    <t>relationship--515541a7-6128-4a36-bad8-b4a99b8d1f25</t>
-  </si>
-  <si>
-    <t>relationship--627f7ec5-e07a-4a9e-a179-f56072219e23</t>
-  </si>
-  <si>
-    <t>relationship--9950a4bf-9fc5-48aa-8149-a7cc237741b6</t>
-  </si>
-  <si>
-    <t>relationship--47d76080-8a63-4b2b-a690-ecdd1ac8a447</t>
-  </si>
-  <si>
-    <t>relationship--52320481-114d-4984-ae7c-159c0ade1951</t>
-  </si>
-  <si>
-    <t>relationship--b962befb-5ce9-4090-a7ae-d21e5213b24e</t>
-  </si>
-  <si>
-    <t>relationship--98d9c5dd-04c8-41f6-b66b-72031418daa8</t>
-  </si>
-  <si>
-    <t>relationship--b3145501-4aef-4bd4-a84b-56abc85bf491</t>
-  </si>
-  <si>
-    <t>relationship--94c95dc2-8858-4f49-8ece-3ec79609c4c4</t>
-  </si>
-  <si>
-    <t>relationship--75e0cd78-c4ab-4ad1-b1b1-dfad9c2d7b41</t>
-  </si>
-  <si>
-    <t>relationship--1e3e92b7-4def-4664-b9c7-3fab81304d41</t>
-  </si>
-  <si>
-    <t>relationship--a69c6c2e-b12f-47cc-8e0e-db22bccf842d</t>
-  </si>
-  <si>
-    <t>relationship--cf5f23ba-6c2b-402c-9fe3-ae75fa116ee2</t>
-  </si>
-  <si>
-    <t>relationship--f90aefa2-2a8d-4e22-b012-96035822427f</t>
-  </si>
-  <si>
-    <t>relationship--7b93a63c-7ddb-46ed-b1f5-689c84b6dd44</t>
-  </si>
-  <si>
-    <t>relationship--3ab348ce-8d96-4260-bf68-9c2abbeb728e</t>
-  </si>
-  <si>
-    <t>relationship--13bce4b8-606b-4b06-b217-1513ec54251a</t>
-  </si>
-  <si>
-    <t>relationship--ee1770df-945f-4564-9553-b1d84f490dcd</t>
-  </si>
-  <si>
-    <t>relationship--8bc54604-c986-43f2-a701-b12592389a95</t>
-  </si>
-  <si>
-    <t>relationship--653bfee4-8148-4228-b9ad-a0dd9f6fb024</t>
-  </si>
-  <si>
-    <t>relationship--8c5d41d1-9fc6-4849-a964-d4d4cd88d808</t>
-  </si>
-  <si>
-    <t>relationship--5be4de54-a976-41cf-9a3e-801a66dd4ab0</t>
-  </si>
-  <si>
-    <t>relationship--f005b199-111a-4b05-aefa-24a35febc482</t>
-  </si>
-  <si>
-    <t>relationship--0dbf3ce6-19bd-478e-adf9-32c6e80ed0ea</t>
-  </si>
-  <si>
-    <t>relationship--c208739a-827c-4d0e-bf28-61b916f15cfe</t>
-  </si>
-  <si>
-    <t>relationship--614fbc69-8cba-40a0-98f9-936eaac5419e</t>
-  </si>
-  <si>
-    <t>relationship--ca9d96ad-f282-4c8a-a7f1-c49268bc3a88</t>
-  </si>
-  <si>
-    <t>relationship--086b6153-43f4-47de-80df-44693f738943</t>
-  </si>
-  <si>
-    <t>relationship--8a4808c1-777c-40fc-aa35-f6cd68dc33c2</t>
-  </si>
-  <si>
-    <t>relationship--37a411b5-a9ad-4aa3-b275-64db44664d5d</t>
-  </si>
-  <si>
-    <t>relationship--aee80eb9-ab23-4760-8add-e0216bd30a05</t>
-  </si>
-  <si>
-    <t>relationship--ca3971ca-3608-4f4b-ba38-3b8e016ebf03</t>
-  </si>
-  <si>
-    <t>relationship--80974889-50af-4c79-93b8-102362fc0530</t>
-  </si>
-  <si>
-    <t>relationship--e6ca03f6-6ec1-4870-bcb9-a3c507268afb</t>
-  </si>
-  <si>
-    <t>relationship--2a6b0d1a-4fc7-40de-9362-c8eb8abcb9fa</t>
-  </si>
-  <si>
-    <t>relationship--df0ae14a-9167-4c70-bba9-d917ecd1bcbe</t>
-  </si>
-  <si>
-    <t>relationship--38cbf6e2-05be-4c93-9361-7c3355dec29f</t>
-  </si>
-  <si>
-    <t>relationship--eb3986b1-fecd-4d37-92dd-0c8250ef0740</t>
-  </si>
-  <si>
-    <t>relationship--388cb58a-f6b1-432c-aa19-57cc86f8713f</t>
-  </si>
-  <si>
-    <t>relationship--c6850c22-f194-48a1-b786-c5cf857b99cd</t>
-  </si>
-  <si>
-    <t>relationship--917fb287-22e5-452a-9dc2-8c5c8aca7d1b</t>
-  </si>
-  <si>
-    <t>relationship--34cf12dd-b962-4ebe-830a-d8f1c7ff5c4f</t>
-  </si>
-  <si>
-    <t>relationship--94711d8b-0578-438a-9d73-eafd0c1bc983</t>
-  </si>
-  <si>
-    <t>relationship--8045380f-5282-4b2f-ab8f-cb92ffd304a3</t>
-  </si>
-  <si>
-    <t>relationship--3536b790-3098-4639-9c74-ac882b5ab83e</t>
-  </si>
-  <si>
-    <t>relationship--c09a449b-0b73-4e67-abc0-922897a14e61</t>
-  </si>
-  <si>
-    <t>relationship--079404c8-fadc-4028-b464-f31ba21f9514</t>
-  </si>
-  <si>
-    <t>relationship--51aabffe-86e6-4eaa-bf10-1d5525e930ad</t>
-  </si>
-  <si>
-    <t>relationship--49567418-6145-460a-ab69-bcb7861395ac</t>
-  </si>
-  <si>
-    <t>relationship--69dc0331-617e-4089-ac23-257dbeee91a6</t>
-  </si>
-  <si>
-    <t>relationship--57e6a8bb-5b08-4144-8f3d-8b095b08d609</t>
-  </si>
-  <si>
-    <t>relationship--e51c177b-f601-47d5-9ae9-f6adb3dc397d</t>
-  </si>
-  <si>
-    <t>relationship--baecff7e-dc21-44ea-b863-ca8da3c62424</t>
-  </si>
-  <si>
-    <t>relationship--19d3a78f-c438-41f5-a55e-42a419a860ed</t>
-  </si>
-  <si>
-    <t>relationship--1cff25ec-e815-4f02-a656-6f61d9b4302b</t>
-  </si>
-  <si>
-    <t>relationship--574346d1-3eca-43c0-804a-6a49b0fedfbc</t>
-  </si>
-  <si>
-    <t>relationship--e0c46f26-e4dc-44f2-931a-3de7a380d82c</t>
-  </si>
-  <si>
-    <t>relationship--13b93f7a-eceb-4ba1-985b-9f182d1f8959</t>
-  </si>
-  <si>
-    <t>relationship--c094c5e2-4681-47c6-b649-aac2e30ef63e</t>
-  </si>
-  <si>
-    <t>relationship--6b756697-3af1-4921-8afa-de43e8494726</t>
-  </si>
-  <si>
-    <t>relationship--7cd3a274-997e-4fd8-96bd-ed11dbd871ae</t>
-  </si>
-  <si>
-    <t>relationship--e5064444-57d6-4ead-9e9f-a9797549b00a</t>
-  </si>
-  <si>
-    <t>relationship--a977d06e-c9fb-44fb-be91-d9d4ca6f6739</t>
-  </si>
-  <si>
-    <t>relationship--85d74a25-2849-44c5-be0e-0b95c58d05f8</t>
-  </si>
-  <si>
-    <t>relationship--5601426d-de66-4843-a720-640c317e943a</t>
-  </si>
-  <si>
-    <t>relationship--6b8df6aa-2628-49da-9686-9f4ce8ca52b4</t>
-  </si>
-  <si>
-    <t>relationship--02fbe54f-4fe3-4152-9a95-e00d089ad2d0</t>
-  </si>
-  <si>
-    <t>relationship--b74dbe90-0bd4-44ca-9b39-3217a14f9230</t>
-  </si>
-  <si>
-    <t>relationship--37b54435-8bbc-408e-80ac-ccb32adf9d74</t>
-  </si>
-  <si>
-    <t>relationship--e8277521-5c12-4beb-afa2-1d923b1370fa</t>
-  </si>
-  <si>
-    <t>relationship--aac62415-47fd-4339-998a-96774dc28e1a</t>
-  </si>
-  <si>
-    <t>relationship--d884d995-cb3e-42e1-a219-5b8593d7f55d</t>
-  </si>
-  <si>
-    <t>relationship--e63288e7-7429-4d44-93f8-fbae85b7d73c</t>
-  </si>
-  <si>
-    <t>relationship--88530d1b-75a5-40da-a530-138b7ed1bccb</t>
-  </si>
-  <si>
-    <t>relationship--9ff1122a-8920-4536-a6c9-b3651fe87a41</t>
-  </si>
-  <si>
-    <t>relationship--27d5e8cd-20cd-46d3-9497-57611e95e581</t>
-  </si>
-  <si>
-    <t>relationship--bbd6ac57-e29b-42c1-be57-9bbd7676104e</t>
-  </si>
-  <si>
-    <t>relationship--92239776-053f-40a0-aee3-5f0b9a1c07b5</t>
-  </si>
-  <si>
-    <t>relationship--8a3be6db-85c6-4603-a7fc-bb3acfabea88</t>
-  </si>
-  <si>
-    <t>relationship--5fb44550-4eee-4ab7-b478-d2805c2ba9b4</t>
-  </si>
-  <si>
-    <t>relationship--ca087af6-d503-43b8-abc2-10d6090c5a27</t>
-  </si>
-  <si>
-    <t>relationship--8f906083-a1b0-4547-96cc-b43ba604f276</t>
-  </si>
-  <si>
-    <t>relationship--8b2be964-dd7c-4e0b-82b6-6428d3bf1d42</t>
-  </si>
-  <si>
-    <t>relationship--80915558-dd86-465b-9b1a-e747fb99671c</t>
-  </si>
-  <si>
-    <t>relationship--edcf285d-1f1a-46ea-b28f-a4fcee5a385b</t>
-  </si>
-  <si>
-    <t>relationship--20245c10-e5f3-407c-a3b2-96c8c085b0f1</t>
-  </si>
-  <si>
-    <t>relationship--10e85415-c003-4ef7-a284-05708b6b72be</t>
-  </si>
-  <si>
-    <t>relationship--0fff1f96-3a68-42e4-8e4a-8c8fcb3ce386</t>
-  </si>
-  <si>
-    <t>relationship--5847e598-577d-463a-a3e9-5ca130dd4507</t>
-  </si>
-  <si>
-    <t>relationship--0352eb5f-1132-41ac-9206-b0e16b54436f</t>
-  </si>
-  <si>
-    <t>relationship--852117e1-8630-47eb-8e2e-e22cb2a1564a</t>
-  </si>
-  <si>
-    <t>relationship--5f4533c6-d5e7-41ed-8e89-ce7a3cb061bf</t>
-  </si>
-  <si>
-    <t>relationship--9707dd7d-b5a0-43e2-a6a5-6abce54b7edb</t>
-  </si>
-  <si>
-    <t>relationship--2398c8cc-88a5-4549-b19b-911958d2abe5</t>
-  </si>
-  <si>
-    <t>relationship--c7016342-e47b-4470-a344-672819c70b0d</t>
-  </si>
-  <si>
-    <t>relationship--34666ba1-5c30-4d83-bf2f-c127bb848dcb</t>
-  </si>
-  <si>
-    <t>relationship--5fbe8112-b86f-44db-b323-2f27083564e0</t>
-  </si>
-  <si>
-    <t>relationship--5e064122-2c0d-4930-bf68-fa20ec7fcdea</t>
-  </si>
-  <si>
-    <t>relationship--465dfbec-c935-48b8-ba7c-e8fe3561ca94</t>
-  </si>
-  <si>
-    <t>relationship--1604968c-dab0-43dc-8511-292fcd5575d9</t>
-  </si>
-  <si>
-    <t>relationship--be9a0880-9570-4610-93ec-e350f360d63f</t>
-  </si>
-  <si>
-    <t>relationship--c72b0b22-0cf9-4346-9637-60b6e5b705f9</t>
-  </si>
-  <si>
-    <t>relationship--1f637adc-e5b4-471d-8de1-d477966b1125</t>
-  </si>
-  <si>
-    <t>relationship--56625bef-dd57-4978-9a56-f155789ef3be</t>
-  </si>
-  <si>
-    <t>relationship--b791a492-2bf2-4995-b2d0-6910745d9754</t>
-  </si>
-  <si>
-    <t>relationship--623213a6-abdf-44df-a6fb-c086a684f8b2</t>
-  </si>
-  <si>
-    <t>relationship--468473e7-12c2-46de-88cc-734eafde2868</t>
-  </si>
-  <si>
-    <t>relationship--df901f67-e71f-4192-bcde-7f50d2d9373d</t>
-  </si>
-  <si>
-    <t>relationship--4f31c0bc-a24c-4193-bff2-3a66dae4772f</t>
-  </si>
-  <si>
-    <t>relationship--ec428e67-8568-4f37-a49e-cd580e5c38bd</t>
-  </si>
-  <si>
-    <t>relationship--4ec4ad3d-beca-450e-b6e9-5a93785c5bb0</t>
-  </si>
-  <si>
-    <t>relationship--6effb145-0cd4-4b9f-929f-4c4d89f84ef0</t>
-  </si>
-  <si>
-    <t>relationship--ad081b29-5c12-4d02-8bd1-046b674f4c7c</t>
-  </si>
-  <si>
-    <t>relationship--8f1b3d6f-23b6-4f9b-a8dd-9b3454bd2117</t>
-  </si>
-  <si>
-    <t>relationship--dc5bf458-56f0-43cb-a78d-8bb4bd127e99</t>
-  </si>
-  <si>
-    <t>relationship--9f863b15-ef76-4d35-a0a2-5d4c24c6e6f6</t>
-  </si>
-  <si>
-    <t>relationship--0a76fed9-efeb-4a8e-af6e-d874bc53f71d</t>
-  </si>
-  <si>
-    <t>relationship--465166f8-6a08-4320-aa5b-197bee427cfc</t>
-  </si>
-  <si>
-    <t>relationship--50d6da69-13b5-4383-9a4d-9e6af0892636</t>
-  </si>
-  <si>
-    <t>relationship--67b802bf-c650-4b6b-beac-08a3c96358c8</t>
-  </si>
-  <si>
-    <t>relationship--53719d9d-7011-4032-a70e-8c6138033d7e</t>
-  </si>
-  <si>
-    <t>relationship--5d155807-495a-48a4-be27-5ae299f1c38e</t>
-  </si>
-  <si>
-    <t>relationship--24d049ad-df50-41bf-ba64-070a5db3f232</t>
-  </si>
-  <si>
-    <t>relationship--1912344f-c2b1-497b-8c79-885dac85519f</t>
-  </si>
-  <si>
-    <t>relationship--66da841a-9ba5-4698-9434-a0716c584fcd</t>
-  </si>
-  <si>
-    <t>relationship--a0e26193-7b83-4fac-ba81-a14473696c12</t>
-  </si>
-  <si>
-    <t>relationship--e5ff6d58-7126-41d2-bffc-22be3e559d4c</t>
-  </si>
-  <si>
-    <t>relationship--87e28e8e-0c89-4acc-8d96-191a08c0c4ca</t>
-  </si>
-  <si>
-    <t>relationship--3fc53e7f-aabf-48b1-b1ca-92d9188c5fee</t>
-  </si>
-  <si>
-    <t>relationship--08f43466-659f-422c-be58-91c863e7b936</t>
-  </si>
-  <si>
-    <t>relationship--8160d9a6-4943-4736-a8aa-f256cb2628e3</t>
-  </si>
-  <si>
-    <t>relationship--0fd1b83a-0e8c-485a-9eea-9f1c28469003</t>
-  </si>
-  <si>
-    <t>relationship--955f1858-3345-4ba3-a027-ebbbdc018d52</t>
-  </si>
-  <si>
-    <t>relationship--5f967830-b2b4-4835-b8b3-78e3bb061c70</t>
-  </si>
-  <si>
-    <t>relationship--3662bcda-cf5d-4fd0-9313-620bd45d8adf</t>
-  </si>
-  <si>
-    <t>relationship--97eea6b0-abef-4c35-9150-15ffb0cfd642</t>
-  </si>
-  <si>
-    <t>relationship--4374b082-17aa-4a1e-9780-00373446507e</t>
-  </si>
-  <si>
-    <t>relationship--a38375ec-bc00-4e85-a5b2-013e20b1c61d</t>
-  </si>
-  <si>
-    <t>relationship--dd2f3bc2-fac5-4b98-a5ef-9687daaaa6fc</t>
-  </si>
-  <si>
-    <t>relationship--366d7ed8-a586-4109-9559-6c939ffd576a</t>
-  </si>
-  <si>
-    <t>relationship--402e6d4b-59c4-4e77-9b16-57a4076ae2d5</t>
-  </si>
-  <si>
-    <t>relationship--e9909627-4a7d-495a-834c-315541ab15fd</t>
-  </si>
-  <si>
-    <t>relationship--4b76cb9a-0bed-478d-b892-63357f2f24c9</t>
-  </si>
-  <si>
-    <t>relationship--a93a651a-ffac-4fc7-b9d4-6cc0d508089f</t>
-  </si>
-  <si>
-    <t>relationship--cc43e87c-69f3-4e15-a919-8898b8215090</t>
-  </si>
-  <si>
-    <t>relationship--83e6df16-07fe-41e5-a65b-6ed35c215cc2</t>
-  </si>
-  <si>
-    <t>relationship--5b878410-76cf-418c-b857-a2449022a172</t>
-  </si>
-  <si>
-    <t>relationship--1f29a6cf-c9bd-4e1a-af91-4490d00c1ea6</t>
-  </si>
-  <si>
-    <t>relationship--2cf31521-70c1-4491-a5ae-fe3c4bbc5246</t>
-  </si>
-  <si>
-    <t>relationship--157809ff-2ffb-485c-8b54-1a89d4dcb435</t>
-  </si>
-  <si>
-    <t>relationship--0461225b-8179-4aae-bc0f-d3b7851d4346</t>
-  </si>
-  <si>
-    <t>relationship--5e1ebc3e-adbb-46e4-afea-ca56f35aa3b8</t>
-  </si>
-  <si>
-    <t>relationship--20dfaeff-38ff-450e-b141-6512f93d479c</t>
-  </si>
-  <si>
-    <t>relationship--f6651003-cdfd-476e-964b-b9c1f9814aea</t>
-  </si>
-  <si>
-    <t>relationship--db030bae-c5f5-49ed-8ff4-af0e20ee225d</t>
-  </si>
-  <si>
-    <t>relationship--060b2bb4-62b6-4c64-9527-12b75f6856fb</t>
-  </si>
-  <si>
-    <t>relationship--f105b8ec-d05f-4968-b2d5-c5e5adff5a61</t>
-  </si>
-  <si>
-    <t>relationship--9de38fe8-f56c-4b6d-937c-b36b9e6b8972</t>
-  </si>
-  <si>
-    <t>relationship--f1e432e9-d627-42c5-8582-b9091113bb86</t>
-  </si>
-  <si>
-    <t>relationship--bc55738f-b0ed-416f-844b-6b1f22a7f345</t>
-  </si>
-  <si>
-    <t>relationship--4b753a57-ecd3-4fc6-a713-e0ad97968b62</t>
-  </si>
-  <si>
-    <t>relationship--4e0d7262-08ba-4fb5-bb63-dc30429b3fab</t>
-  </si>
-  <si>
-    <t>relationship--781b4bbf-8a2c-4057-baf5-1878ea619b0c</t>
-  </si>
-  <si>
-    <t>relationship--79f87c09-c697-4dd0-99f2-9fe176f8755c</t>
-  </si>
-  <si>
-    <t>relationship--badcf672-80b4-4756-bc72-46ed253671e1</t>
-  </si>
-  <si>
-    <t>relationship--77906d62-bf50-4cac-88ce-1dd773bab573</t>
-  </si>
-  <si>
-    <t>relationship--16eaf531-3997-47f0-a83e-7f32c635c0fc</t>
-  </si>
-  <si>
-    <t>relationship--8212aa70-f140-43d6-ba87-bfc75ec72e5f</t>
-  </si>
-  <si>
-    <t>relationship--aaa22663-967a-4b00-a539-b09ff557e821</t>
-  </si>
-  <si>
-    <t>relationship--fb30d154-83b6-4539-afb5-0c3888d3bec9</t>
-  </si>
-  <si>
-    <t>relationship--55aba2a5-f217-4d99-9c5b-5f3dac640b92</t>
-  </si>
-  <si>
-    <t>relationship--e8afeeaf-035c-4c76-b5bc-7e4af0f3395c</t>
-  </si>
-  <si>
-    <t>relationship--41a8b0a2-e56f-4893-9cd8-7c65ff389bf8</t>
-  </si>
-  <si>
-    <t>relationship--fb15b942-85d3-4fc7-991d-d9d2041a09e1</t>
-  </si>
-  <si>
-    <t>relationship--c5d8a571-ee0d-419d-8c01-bede9443b942</t>
-  </si>
-  <si>
-    <t>relationship--da556bf9-dba9-4c54-a5e8-c44cb6e48c3d</t>
-  </si>
-  <si>
-    <t>relationship--035189d5-3e56-41ed-98a6-a7efa1dda59a</t>
-  </si>
-  <si>
-    <t>relationship--ba7fc371-952e-4b6b-a61c-45b699357b3d</t>
-  </si>
-  <si>
-    <t>relationship--c35844cb-0555-42da-ba1f-cd933eebe624</t>
-  </si>
-  <si>
-    <t>relationship--4acd9755-b416-4b00-acc6-250ae9622465</t>
-  </si>
-  <si>
-    <t>relationship--0c0d5d6e-42fc-4d8e-902a-a19fe207848e</t>
-  </si>
-  <si>
-    <t>relationship--85e68b26-66be-4060-bc7e-a280bacd4e3a</t>
-  </si>
-  <si>
-    <t>relationship--a74700f2-597f-4f08-aeba-e87654802d35</t>
-  </si>
-  <si>
-    <t>relationship--47cbce4a-835a-4782-be3f-3f40fed7a3c8</t>
-  </si>
-  <si>
-    <t>relationship--03840c67-b080-459b-afa5-dabebcb4d44d</t>
-  </si>
-  <si>
-    <t>relationship--b7e30afc-7d74-4b1e-a1c5-653abf36c875</t>
-  </si>
-  <si>
-    <t>relationship--5f1bc6d9-5417-4f2c-9c50-d84caa46cb19</t>
-  </si>
-  <si>
-    <t>relationship--21c44f8f-68f3-4578-acb9-ef09c6722ab8</t>
-  </si>
-  <si>
-    <t>relationship--13e01f4c-8dd4-4b7d-9a30-3900d9fed55c</t>
-  </si>
-  <si>
-    <t>relationship--9702d5d0-42c1-46ce-b8dd-b0bfb6b33a3c</t>
-  </si>
-  <si>
-    <t>relationship--0a9ba803-afc5-414d-9159-cbe1dec86fdb</t>
-  </si>
-  <si>
-    <t>relationship--59db0a16-d7b1-472c-ba90-58d8e720dc4c</t>
-  </si>
-  <si>
-    <t>relationship--06e37dc0-aec3-40a5-9fdc-0a3900505d13</t>
-  </si>
-  <si>
-    <t>relationship--bffe6e07-ed4b-4734-aa19-1477f29364d2</t>
-  </si>
-  <si>
-    <t>relationship--1c36c5be-b13c-4f11-960f-9b03cbc87f8d</t>
-  </si>
-  <si>
-    <t>relationship--d3fd53b4-18fa-45e9-b69f-6a0d7520a5ca</t>
-  </si>
-  <si>
-    <t>relationship--756d0f2d-207e-4f7b-b0b2-b48292f01566</t>
-  </si>
-  <si>
-    <t>relationship--9a868a03-666e-4f64-b596-5c48bdee52c3</t>
-  </si>
-  <si>
-    <t>relationship--d7fc2066-edf6-47c6-a83c-7206850f0ab5</t>
-  </si>
-  <si>
-    <t>relationship--5d579a13-67d5-448a-adc5-83a4fafe6397</t>
-  </si>
-  <si>
-    <t>relationship--de480653-7c48-4149-8c94-9b269c7d47a4</t>
-  </si>
-  <si>
-    <t>relationship--6a67ff6b-94aa-4750-ab1b-fc32683bdef6</t>
-  </si>
-  <si>
-    <t>relationship--7d309686-d313-4099-bb16-28e1c507b4de</t>
-  </si>
-  <si>
-    <t>relationship--da8866ae-3f47-46eb-94b8-372a984469cd</t>
-  </si>
-  <si>
-    <t>relationship--3a5d6f95-14ab-46c5-b8da-032669b0bae2</t>
-  </si>
-  <si>
-    <t>relationship--024a7113-e248-4822-bea2-30f77d9a7a8f</t>
-  </si>
-  <si>
-    <t>relationship--00ca73d0-0387-42d0-84bc-936fda075d8d</t>
-  </si>
-  <si>
-    <t>relationship--1c8c0f26-e354-4f16-866b-c4ed7978e820</t>
-  </si>
-  <si>
-    <t>relationship--37ca5c6c-a8bd-4cc0-a94a-94c62380ad01</t>
-  </si>
-  <si>
-    <t>relationship--09ca5108-558b-4995-9467-494a354a918a</t>
-  </si>
-  <si>
-    <t>relationship--0e1317d3-00a0-4713-9781-766b42db644e</t>
-  </si>
-  <si>
-    <t>relationship--ba57efe2-3653-460c-a6d1-5293aa19b7ce</t>
-  </si>
-  <si>
-    <t>relationship--19a86362-7955-4dbf-bbb0-1c8de038abc9</t>
-  </si>
-  <si>
-    <t>relationship--105776f8-fb6e-40b1-90d5-51a56bacf1c1</t>
-  </si>
-  <si>
-    <t>relationship--26e34a40-646e-40bd-97fd-af7707fec87e</t>
-  </si>
-  <si>
-    <t>relationship--43674d3b-1755-45c6-be2c-b5e6b83dc1fd</t>
-  </si>
-  <si>
-    <t>relationship--56c13e79-da44-4855-abc6-d1119ccf296a</t>
-  </si>
-  <si>
-    <t>relationship--2b20ec1c-dcf1-4f91-abeb-ebe52c94ed06</t>
-  </si>
-  <si>
-    <t>relationship--7bb3178c-db31-4233-9649-cde63f598fde</t>
-  </si>
-  <si>
-    <t>relationship--8840ff74-0db6-4bb2-b7fb-90692fae5cf7</t>
-  </si>
-  <si>
-    <t>relationship--1abc678f-dce8-47c5-90b4-26b570e01f03</t>
-  </si>
-  <si>
-    <t>relationship--a10fcf23-dced-4c62-8b72-de9252e3dd3e</t>
-  </si>
-  <si>
-    <t>relationship--16744069-cca1-4a02-b485-33f838b5ab31</t>
-  </si>
-  <si>
-    <t>relationship--c4da07a0-ac6b-43bb-acb4-0e1eebb72e1d</t>
-  </si>
-  <si>
-    <t>relationship--b13c20bf-f6f3-496b-9bbc-756d27bcc338</t>
-  </si>
-  <si>
-    <t>relationship--ead18e3d-243e-4bfc-9e35-dcef978fa1a6</t>
-  </si>
-  <si>
-    <t>relationship--daa06fd4-7ec9-441c-9dad-d0b476425de6</t>
-  </si>
-  <si>
-    <t>relationship--efe698ab-5c0f-471e-965f-49902fb52ff3</t>
-  </si>
-  <si>
-    <t>relationship--bc99b34b-c89e-4a48-93d6-98e18c56bd9c</t>
-  </si>
-  <si>
-    <t>relationship--1c294501-8bda-4b29-b345-880b8d39a07c</t>
-  </si>
-  <si>
-    <t>relationship--1420dce4-e170-412c-8605-5ec9480fb9e2</t>
-  </si>
-  <si>
-    <t>relationship--a88ea7e3-49fd-4f48-a25f-2aa2a4cfda6c</t>
-  </si>
-  <si>
-    <t>relationship--4fde23f7-a081-497c-907b-a3499be478c1</t>
-  </si>
-  <si>
-    <t>relationship--c894f2d6-6b3d-43a9-ad2c-6d2c1c596045</t>
-  </si>
-  <si>
-    <t>relationship--01673386-068e-4501-ac11-1263c9fe485e</t>
-  </si>
-  <si>
-    <t>relationship--2c5dfe88-33fb-44bb-9dbc-b2430f5b1ecf</t>
-  </si>
-  <si>
-    <t>relationship--34bf02af-e6fa-4c0e-ad5c-d45c46d77832</t>
-  </si>
-  <si>
-    <t>relationship--52bddd02-b48a-4510-910a-094c4433eb2d</t>
-  </si>
-  <si>
-    <t>relationship--5506c3cf-59c7-46bb-9bf2-902908d87126</t>
-  </si>
-  <si>
-    <t>relationship--3984cea3-d47b-4481-8888-c0b1f35969c1</t>
-  </si>
-  <si>
-    <t>relationship--54c4d918-8bc7-4364-80f9-b0caf2bf0969</t>
-  </si>
-  <si>
-    <t>relationship--73189ccc-2381-4e23-95ce-ae7a30a09f43</t>
-  </si>
-  <si>
-    <t>relationship--04b40aa1-c056-4a12-a4ca-9a5b999da66e</t>
-  </si>
-  <si>
-    <t>relationship--6fc62b9c-7886-4974-ab01-cc635d166860</t>
-  </si>
-  <si>
-    <t>relationship--17316c02-b0c3-455f-8bcd-157aba4b808d</t>
-  </si>
-  <si>
-    <t>relationship--9a4c2560-ff66-4227-a982-86d97e2ffbed</t>
-  </si>
-  <si>
-    <t>relationship--4403eef2-fe84-4921-a94f-6257d3547b6e</t>
-  </si>
-  <si>
-    <t>relationship--84d3e218-1a16-4f3d-bf83-29abb545e970</t>
-  </si>
-  <si>
-    <t>relationship--62854ef1-cc65-4a00-85d8-968cabe77970</t>
-  </si>
-  <si>
-    <t>relationship--34a8027e-bb56-4c8c-a6e5-f2eff445b635</t>
-  </si>
-  <si>
-    <t>relationship--7a5673bf-43ca-4139-ac6b-d5bb967c11e6</t>
-  </si>
-  <si>
-    <t>relationship--96d6ea01-4a3b-4a31-834e-f6a1b25d3d01</t>
-  </si>
-  <si>
-    <t>relationship--65b32450-6df6-4327-9411-bb11dd24e186</t>
-  </si>
-  <si>
-    <t>relationship--cbbeb0ed-42c2-4724-b202-23d4856aff33</t>
-  </si>
-  <si>
-    <t>relationship--f2f90e4d-5a63-40b4-adad-90332f88a7be</t>
-  </si>
-  <si>
-    <t>relationship--11b1266c-d020-420d-9c40-318b57e0bbeb</t>
-  </si>
-  <si>
-    <t>relationship--5195893a-8224-493f-bdbb-b276f796dbb8</t>
-  </si>
-  <si>
-    <t>relationship--6165994a-b952-429b-8905-431c9e06f4cf</t>
-  </si>
-  <si>
-    <t>relationship--25f80921-0d9d-4d56-8a10-0b1c86bd8490</t>
-  </si>
-  <si>
-    <t>relationship--a1ce3595-ecd4-41b1-83f7-5aa32a7a4c25</t>
-  </si>
-  <si>
-    <t>relationship--b2d2b23a-2561-4b1b-b23b-60ec84ac8559</t>
-  </si>
-  <si>
-    <t>relationship--1a5c8ccb-b7f9-4118-9977-904a79d8cd91</t>
-  </si>
-  <si>
-    <t>relationship--499220bf-45f5-42dc-9842-b2104ef2385b</t>
-  </si>
-  <si>
-    <t>relationship--975edf7f-38d6-4125-86ae-6df413e02b64</t>
-  </si>
-  <si>
-    <t>relationship--13fe682c-4d2b-498e-b0fe-5faa9627f478</t>
-  </si>
-  <si>
-    <t>relationship--f98d2762-9dda-4bb9-a018-e77fcb87b59c</t>
-  </si>
-  <si>
-    <t>relationship--cda16288-3df9-4f63-8073-a4b437c71004</t>
-  </si>
-  <si>
-    <t>relationship--1f5a1489-2483-4e84-a40e-04efed8b94b4</t>
-  </si>
-  <si>
-    <t>relationship--fb03a109-6075-4b58-afb4-6a2557f2c215</t>
-  </si>
-  <si>
-    <t>relationship--9ec9acf6-7154-4532-913c-ccdf66091156</t>
-  </si>
-  <si>
-    <t>relationship--63452325-03d3-49b1-bf54-66dfb125ec87</t>
-  </si>
-  <si>
-    <t>relationship--0e802b5c-2403-479e-ac20-06e9aa5c43ae</t>
-  </si>
-  <si>
-    <t>relationship--dfc52397-92e1-4160-a98f-34948d016360</t>
-  </si>
-  <si>
-    <t>relationship--d6cc70a9-9c36-42e2-b4a9-454d252faa7a</t>
-  </si>
-  <si>
-    <t>relationship--7c07f851-9a41-4d35-b79f-fb7069c0d04d</t>
-  </si>
-  <si>
-    <t>relationship--971fa3bc-ca45-4715-9d2c-da25aab64756</t>
-  </si>
-  <si>
-    <t>relationship--676dfa2f-887b-4a44-869a-7ef3d8e61b0a</t>
-  </si>
-  <si>
-    <t>relationship--a476ccc4-9b09-40e8-85fa-c2cb5269f2b1</t>
-  </si>
-  <si>
-    <t>relationship--e9e57c76-c09b-4fd5-b89f-46f96cca140d</t>
-  </si>
-  <si>
-    <t>relationship--cedcc327-db8f-4d4c-b1f0-f6c89260dda8</t>
-  </si>
-  <si>
-    <t>relationship--cc6b2561-a78f-4f37-aee5-e8248c3db565</t>
-  </si>
-  <si>
-    <t>relationship--685565b6-7584-4468-b179-52fe99c48584</t>
-  </si>
-  <si>
-    <t>relationship--40f1a33f-1390-4a00-b1be-cf9f1d3c976b</t>
-  </si>
-  <si>
-    <t>relationship--66b98a2b-4c8f-4386-958d-02048df51fc3</t>
-  </si>
-  <si>
-    <t>relationship--7f56817f-8b83-4c6c-b2fd-a0b7f86dec1f</t>
-  </si>
-  <si>
-    <t>relationship--1ac9ff58-8efb-419c-928c-fe3847c9188c</t>
-  </si>
-  <si>
-    <t>relationship--9c48b5cd-56e8-49a0-9b61-a580368cf0e1</t>
-  </si>
-  <si>
-    <t>relationship--9b25f341-01f3-4dfd-a588-165a86bcaace</t>
-  </si>
-  <si>
-    <t>relationship--9da377c2-38ff-439c-823b-34a5d1998571</t>
-  </si>
-  <si>
-    <t>relationship--279284af-ae24-4c2b-bc5e-17e518c8868e</t>
-  </si>
-  <si>
-    <t>relationship--a07d27b0-07d8-4981-a5a0-be24cbe07191</t>
-  </si>
-  <si>
-    <t>relationship--3e6cea56-29f5-4715-a858-a40804c68293</t>
-  </si>
-  <si>
-    <t>relationship--ffafc4ad-f136-4aae-9beb-72a49eea5020</t>
-  </si>
-  <si>
-    <t>relationship--0ff6a61c-38db-4435-9190-d7afac3f982d</t>
-  </si>
-  <si>
-    <t>relationship--1ca8158f-e8b9-4dad-a4d9-63c5e5f7b814</t>
-  </si>
-  <si>
-    <t>relationship--7039815a-5bb6-4ae6-add1-1d88c03ca42f</t>
-  </si>
-  <si>
-    <t>relationship--07c3aeaa-21f2-42bd-a3d0-ebd14c8dbf1b</t>
-  </si>
-  <si>
-    <t>relationship--38e83d08-2485-4ebe-bf67-1c981ee314ba</t>
-  </si>
-  <si>
-    <t>relationship--f9f2ba02-56ea-4444-9e3f-a47c6972d6e7</t>
-  </si>
-  <si>
-    <t>relationship--a971ee1c-e0d2-4f15-9cd2-62e3d0d32ca0</t>
-  </si>
-  <si>
-    <t>relationship--d6699f88-a5cb-40dd-ae75-19f280aeb4cb</t>
-  </si>
-  <si>
-    <t>relationship--ece83b83-27bc-4e09-a313-ad8cee5ebeb7</t>
-  </si>
-  <si>
-    <t>relationship--cb5e7817-a24b-4246-a285-3699c9a6faa1</t>
-  </si>
-  <si>
-    <t>relationship--3be951b7-a21a-4015-8629-51c108cb9c26</t>
-  </si>
-  <si>
-    <t>relationship--de9774c2-f9b4-4b84-825a-2e1b90f22f46</t>
-  </si>
-  <si>
-    <t>relationship--c94c095f-581b-4666-bc33-15a56a4f7b95</t>
-  </si>
-  <si>
-    <t>relationship--d1aa0946-d87c-45ae-b424-d9c9146f01e9</t>
-  </si>
-  <si>
-    <t>relationship--bd156b28-4368-4ef7-9442-99a4037f8990</t>
-  </si>
-  <si>
-    <t>relationship--51b252c6-f25a-4868-ba2f-5c4c5dce3575</t>
-  </si>
-  <si>
-    <t>relationship--ea59c0a9-5e60-42a9-b62c-7b1c2c235920</t>
-  </si>
-  <si>
-    <t>relationship--472e25d9-877e-4eea-8777-ff8fb1f2cf1d</t>
-  </si>
-  <si>
-    <t>relationship--15b4a1ec-a4c0-4c0d-af6b-9ce3c60dc53c</t>
-  </si>
-  <si>
-    <t>relationship--45b6dca8-89ca-4d24-89ea-a829323807cb</t>
-  </si>
-  <si>
-    <t>relationship--73e7a9e7-fd3a-4ec8-8d58-ad42c116c5e5</t>
-  </si>
-  <si>
-    <t>relationship--e25881ca-c77f-4de2-9a5a-93e603d6089d</t>
-  </si>
-  <si>
-    <t>relationship--ccbb2c32-1b08-4489-9281-a4e802aebe2c</t>
-  </si>
-  <si>
-    <t>relationship--b1254916-a50c-4122-8a8b-ddae6cb4bf3b</t>
-  </si>
-  <si>
-    <t>relationship--436a367d-751f-46ae-865b-1b08b2c94b0b</t>
-  </si>
-  <si>
-    <t>relationship--ae1830ae-193d-49fd-88b8-9ca09acab278</t>
-  </si>
-  <si>
-    <t>relationship--a00d775f-db2b-4bf4-9738-882d507f14a3</t>
-  </si>
-  <si>
-    <t>relationship--91d493cc-ed9d-410a-87da-737f90d29d5f</t>
-  </si>
-  <si>
-    <t>relationship--2a31099b-0274-4bcb-bcd8-1ab0dd82ca1a</t>
-  </si>
-  <si>
-    <t>relationship--613a2833-e940-4b58-90d7-22663e80ee19</t>
-  </si>
-  <si>
-    <t>relationship--e2b3c79f-8da6-406e-b66b-35ee86951b5c</t>
-  </si>
-  <si>
-    <t>relationship--a27107bb-ee98-440b-b975-fbe403b7d011</t>
-  </si>
-  <si>
-    <t>relationship--22684718-ebff-48c1-835a-4dbcaae467d6</t>
-  </si>
-  <si>
-    <t>relationship--6c0f5f2d-13a9-4854-b56a-31267e3e57d4</t>
-  </si>
-  <si>
-    <t>relationship--2d8f0eaa-86d6-4ec2-b131-fb0176dde252</t>
-  </si>
-  <si>
-    <t>relationship--7acaf2ec-5332-4376-b9e6-e5f7a5d4e396</t>
-  </si>
-  <si>
-    <t>relationship--51ef3804-21ae-4b4d-90ff-66961d7c3031</t>
-  </si>
-  <si>
-    <t>relationship--46f3bd13-d9a3-40ce-9833-559c430cf1de</t>
-  </si>
-  <si>
-    <t>relationship--2e7a2655-e1f7-4be0-8560-99a7ce302fda</t>
-  </si>
-  <si>
-    <t>relationship--2b1d8bec-1187-47fc-a890-9171d0af4206</t>
-  </si>
-  <si>
-    <t>relationship--0c6b277f-6616-428d-8dde-d133beab7c6b</t>
-  </si>
-  <si>
-    <t>relationship--00266455-3f2b-4b3c-8e1f-6ce6193cb8f4</t>
-  </si>
-  <si>
-    <t>relationship--7981c6df-980d-427f-b355-4ce7650a11fa</t>
-  </si>
-  <si>
-    <t>relationship--58a2fd8c-b163-4fd7-af8e-4e5f518cf565</t>
-  </si>
-  <si>
-    <t>relationship--55fad24c-1298-46ae-8628-2eec64a7d75c</t>
-  </si>
-  <si>
-    <t>relationship--1bb41d58-bb9f-4f26-b8b2-5a6600fe25d5</t>
-  </si>
-  <si>
-    <t>relationship--3e20551e-d442-43b7-9893-b825832447f8</t>
-  </si>
-  <si>
-    <t>relationship--aef61ea4-d2d3-4b7d-b3f2-eb09d9954aba</t>
-  </si>
-  <si>
-    <t>relationship--fceb239a-b0ae-48e6-bec0-0c8c7357ebd9</t>
-  </si>
-  <si>
-    <t>relationship--3380f24c-4e14-49a4-a119-a87f1b9eecd9</t>
-  </si>
-  <si>
-    <t>relationship--a22a0b8c-4032-40b7-a0ea-12e9dbf2961b</t>
-  </si>
-  <si>
-    <t>relationship--217bd9d8-a378-463f-9cc8-e7fadf8aa13d</t>
-  </si>
-  <si>
-    <t>relationship--2f9a83f4-d17c-4e2f-b852-7e1823502480</t>
-  </si>
-  <si>
-    <t>relationship--1227d382-496a-4e5d-8e55-ff384f5424d1</t>
-  </si>
-  <si>
-    <t>relationship--14448630-38e2-458b-b4e9-f8184c4c7809</t>
-  </si>
-  <si>
-    <t>relationship--893aac3e-99cc-4a45-96b3-d9cc67be9476</t>
-  </si>
-  <si>
-    <t>relationship--1a5bc425-80c9-491b-8c61-699e84666675</t>
-  </si>
-  <si>
-    <t>relationship--3129830c-d6e0-43ad-aac8-fa955eec7292</t>
-  </si>
-  <si>
-    <t>relationship--ad8190b9-1ea3-422d-9cc0-79fe25111c3b</t>
-  </si>
-  <si>
-    <t>relationship--2a74ddf8-7017-4935-821c-bcd120366aec</t>
-  </si>
-  <si>
-    <t>relationship--65ad9ce1-3c06-4312-9781-f4ab0a1b4576</t>
-  </si>
-  <si>
-    <t>relationship--0d90ba2b-7b16-4c53-9b8f-26c329a24988</t>
-  </si>
-  <si>
-    <t>relationship--a3fe44a7-14ec-4ea0-b4f4-6846c5fbc24d</t>
-  </si>
-  <si>
-    <t>relationship--5e869d43-c351-4be0-a267-f79006c39d2d</t>
-  </si>
-  <si>
-    <t>relationship--10ef8b9a-6360-401d-8baf-86e9b805780c</t>
-  </si>
-  <si>
-    <t>relationship--15dd688a-f80a-4db8-b9bc-c1cdacee5bf9</t>
-  </si>
-  <si>
-    <t>relationship--21f6c7af-2c6e-4bf7-850c-61b5194aa999</t>
-  </si>
-  <si>
-    <t>relationship--839f6e5b-5e89-44c0-a3e6-71397137e2c0</t>
-  </si>
-  <si>
-    <t>relationship--3db1a8d4-08de-47d8-b608-1855ef5fc32e</t>
-  </si>
-  <si>
-    <t>relationship--8834c869-09ab-4a5b-9269-c40d5a257df4</t>
-  </si>
-  <si>
-    <t>relationship--fdce753f-4c29-4b25-91ff-7f7d8b2afea8</t>
-  </si>
-  <si>
-    <t>relationship--a87b6855-782c-4452-bdb9-86e7e2ec6059</t>
-  </si>
-  <si>
-    <t>relationship--f81e8eb7-d4f6-4e9a-b29f-4f25d579e7da</t>
-  </si>
-  <si>
-    <t>relationship--f696fb29-1c07-45b5-b568-64f4f6fe8fec</t>
-  </si>
-  <si>
-    <t>relationship--d9fa28d8-1f00-498b-918b-26c1e7ae1c53</t>
-  </si>
-  <si>
-    <t>relationship--f045efb9-8922-4775-970d-481418f671a0</t>
-  </si>
-  <si>
-    <t>relationship--205dff75-fc00-4858-8a43-d0391dd8c888</t>
-  </si>
-  <si>
-    <t>relationship--0a3003bf-966e-423b-b592-01d663788603</t>
-  </si>
-  <si>
-    <t>relationship--90f65ece-ab59-4b9f-aa48-6f3f18d3e1eb</t>
-  </si>
-  <si>
-    <t>relationship--1d1cb160-1ad8-4e2b-a6fb-cd4745e040b4</t>
-  </si>
-  <si>
-    <t>relationship--d883cc91-90fa-4cca-a50c-7267c0aff891</t>
-  </si>
-  <si>
-    <t>relationship--5aaf25d0-bc32-4203-9c9d-d9f66bd960d1</t>
-  </si>
-  <si>
-    <t>relationship--30b46d33-7b73-4334-a1db-d91a5850d0f8</t>
-  </si>
-  <si>
-    <t>relationship--1415d9e2-3ec8-4950-a3cf-0a771978afa9</t>
-  </si>
-  <si>
-    <t>relationship--4fdb62a5-fb3e-4fb6-aa8a-b682cb4e1c20</t>
-  </si>
-  <si>
-    <t>relationship--bbe1b9bc-6806-402f-b985-2f64a72ff0e3</t>
-  </si>
-  <si>
-    <t>relationship--4262f5bf-7ff8-4bb6-84c4-e0226ad3b11d</t>
-  </si>
-  <si>
-    <t>relationship--d62debb4-770b-4b6f-8173-018af2a5b325</t>
-  </si>
-  <si>
-    <t>relationship--2c6e107e-e860-40fb-8f76-ce5682d72b02</t>
-  </si>
-  <si>
-    <t>relationship--49922116-adf1-4974-b9b4-8baef88d2dd9</t>
-  </si>
-  <si>
-    <t>relationship--d2d79914-471e-457f-ae36-41d34ccaeff6</t>
-  </si>
-  <si>
-    <t>relationship--f44aba76-9d85-4d72-a071-a2e09093df88</t>
-  </si>
-  <si>
-    <t>relationship--502e33d2-3654-4b52-a2d2-08a6a6c709f3</t>
-  </si>
-  <si>
-    <t>relationship--b0b9692d-77af-4890-986f-fc4b37d7dfa3</t>
-  </si>
-  <si>
-    <t>relationship--e5e638ab-fd72-4af1-9f8d-e2bb7d44142c</t>
-  </si>
-  <si>
-    <t>relationship--5bcf5e3f-e1a0-4b65-a5ef-c087360b918b</t>
-  </si>
-  <si>
-    <t>relationship--b8cf1b28-e865-4cd7-93f6-565527b4a923</t>
-  </si>
-  <si>
-    <t>relationship--a7a7b234-a9dd-4b62-b9ed-73f511c5adf8</t>
-  </si>
-  <si>
-    <t>relationship--63474f71-ecda-42ff-8bc1-475a951eb9d4</t>
-  </si>
-  <si>
-    <t>relationship--06e2c87e-97c1-425e-aa49-49a43aaf8c38</t>
-  </si>
-  <si>
-    <t>relationship--c5907c16-a6b2-4585-8587-743dbd102eb4</t>
-  </si>
-  <si>
-    <t>relationship--ef4b5e37-4b77-41ef-a9fd-ed32e7dd71d1</t>
-  </si>
-  <si>
-    <t>relationship--7d60876d-abd3-49cb-9646-9d3ce55e8eaa</t>
-  </si>
-  <si>
-    <t>relationship--00d76dd5-547f-4d91-a2b2-a68120947401</t>
-  </si>
-  <si>
-    <t>relationship--5d240505-32ed-4a6f-897e-bc114bded524</t>
-  </si>
-  <si>
-    <t>relationship--6867b04c-5665-48ce-a4a9-d0e025aae5b3</t>
+    <t>relationship--a95066fb-1718-46d3-8e6e-49e87d4751b7</t>
+  </si>
+  <si>
+    <t>relationship--e9a22d2b-cb0b-4938-9005-5533000e7b38</t>
+  </si>
+  <si>
+    <t>relationship--565adc13-b06e-47cd-ba71-049604f1c97e</t>
+  </si>
+  <si>
+    <t>relationship--1c284d41-421a-4be5-9678-bb2ac621c866</t>
+  </si>
+  <si>
+    <t>relationship--32210d72-5a5a-447f-bc97-012c21a9d180</t>
+  </si>
+  <si>
+    <t>relationship--48fe585f-60a2-4e8c-8063-2ef406ecabbc</t>
+  </si>
+  <si>
+    <t>relationship--1aa6f707-5ad2-4cee-9940-beb43e0bbd57</t>
+  </si>
+  <si>
+    <t>relationship--6810df1c-387a-422d-8a88-f1e5ac631c8c</t>
+  </si>
+  <si>
+    <t>relationship--ebf45aa9-ab01-471e-989c-cf1348b5d70a</t>
+  </si>
+  <si>
+    <t>relationship--4807f9f0-92c6-446d-9180-7913879270a1</t>
+  </si>
+  <si>
+    <t>relationship--2fd65693-90a1-4f44-8274-b473a3bb173f</t>
+  </si>
+  <si>
+    <t>relationship--a0e6d595-4668-4dda-806b-b016e035a696</t>
+  </si>
+  <si>
+    <t>relationship--d47a8fb4-6c97-4b93-a1d6-61eb3f535597</t>
+  </si>
+  <si>
+    <t>relationship--f5c06e1b-f14f-492b-95e0-e82889dcc877</t>
+  </si>
+  <si>
+    <t>relationship--11eee327-9c1f-4151-931a-fbeb9b35bb4c</t>
+  </si>
+  <si>
+    <t>relationship--e435b9fd-332a-4d75-9476-d406f9c37a61</t>
+  </si>
+  <si>
+    <t>relationship--c13f714f-67f4-4e3f-a5fb-410a7d86df85</t>
+  </si>
+  <si>
+    <t>relationship--34d5c786-e1a6-4953-8f03-d138258da3d4</t>
+  </si>
+  <si>
+    <t>relationship--ed0e4c1e-4a29-4e56-99b3-c40191c272cc</t>
+  </si>
+  <si>
+    <t>relationship--dc8be056-141e-4424-80c7-a593fb2736fb</t>
+  </si>
+  <si>
+    <t>relationship--7ba58dbe-7676-4d12-a9da-718738083fe5</t>
+  </si>
+  <si>
+    <t>relationship--fc74cc6a-7592-4289-985b-94d3f359ade3</t>
+  </si>
+  <si>
+    <t>relationship--5541fa16-864d-4d8f-bdd9-8f442103ea16</t>
+  </si>
+  <si>
+    <t>relationship--7d115ed9-39e7-4def-b4a0-79972420802d</t>
+  </si>
+  <si>
+    <t>relationship--1bca7e42-1da9-4ea3-bb66-afa4c1df3443</t>
+  </si>
+  <si>
+    <t>relationship--bbdcb1e8-692d-41fe-88e1-d1fc06f4a8d5</t>
+  </si>
+  <si>
+    <t>relationship--dfb42873-75dc-45b8-8abd-96f5da31a2fa</t>
+  </si>
+  <si>
+    <t>relationship--48aaa29f-ac3e-47ee-982c-8541c26117c5</t>
+  </si>
+  <si>
+    <t>relationship--30d03301-95c7-4a01-86ab-fc56fab12bd0</t>
+  </si>
+  <si>
+    <t>relationship--33c28a36-b522-4c5c-b33c-28d4390bd800</t>
+  </si>
+  <si>
+    <t>relationship--463bd61c-a8d3-40ab-ace9-4515dfa76476</t>
+  </si>
+  <si>
+    <t>relationship--32ff96a6-0b0a-4ca7-8f19-3ed9dce19f80</t>
+  </si>
+  <si>
+    <t>relationship--f743c22a-ebef-4a93-847b-3b6e3122b994</t>
+  </si>
+  <si>
+    <t>relationship--619ee101-358b-4aad-b5d0-14bced2f13c8</t>
+  </si>
+  <si>
+    <t>relationship--abf8a785-6875-4d28-8fe5-01247f5425d9</t>
+  </si>
+  <si>
+    <t>relationship--0eadb0af-59ea-46cf-929c-73d9b9764492</t>
+  </si>
+  <si>
+    <t>relationship--261854c3-1617-45ff-baa8-6dbe52976c77</t>
+  </si>
+  <si>
+    <t>relationship--b027ab64-92aa-4d21-af4e-2337894240b5</t>
+  </si>
+  <si>
+    <t>relationship--b58f403d-9810-45d5-86d3-41e89f270bcf</t>
+  </si>
+  <si>
+    <t>relationship--f56b40d8-819a-40bc-a68e-c60d01db7f0f</t>
+  </si>
+  <si>
+    <t>relationship--3ef446d6-bbb7-433b-af9a-46857a3bc555</t>
+  </si>
+  <si>
+    <t>relationship--0cfbc2d3-05dd-44a8-bc82-7887467e3928</t>
+  </si>
+  <si>
+    <t>relationship--646e8a40-ca48-4925-9031-204da00b650e</t>
+  </si>
+  <si>
+    <t>relationship--a5959dbf-f0f2-45a0-bb14-5e41bdb8e585</t>
+  </si>
+  <si>
+    <t>relationship--e634e455-5505-4898-b305-982f72306fc4</t>
+  </si>
+  <si>
+    <t>relationship--3ae42177-2839-483a-80ef-2f3a2d15803c</t>
+  </si>
+  <si>
+    <t>relationship--79f23e7a-d1dc-44a2-bc4c-6d7c0604d9d9</t>
+  </si>
+  <si>
+    <t>relationship--41d16cff-028a-45b7-9773-b7ed73ac0855</t>
+  </si>
+  <si>
+    <t>relationship--26683c7f-b18d-4f0b-8240-1474c128b1ed</t>
+  </si>
+  <si>
+    <t>relationship--1116351d-6972-444b-90a0-1f8e7e66d75e</t>
+  </si>
+  <si>
+    <t>relationship--8c0281e5-c7a7-4e8c-a340-f4c9c0e727e9</t>
+  </si>
+  <si>
+    <t>relationship--9cedb62b-574a-4771-bf01-3eb83d2c19e7</t>
+  </si>
+  <si>
+    <t>relationship--2c051a16-4463-4ce0-8045-05edbecdb96e</t>
+  </si>
+  <si>
+    <t>relationship--cb40224b-fde2-4bd9-b5f4-1c7fca7631b9</t>
+  </si>
+  <si>
+    <t>relationship--ce3e3dce-c741-4765-a1f3-44e4543d4b3d</t>
+  </si>
+  <si>
+    <t>relationship--58d301f9-9b44-47c3-8013-ae1ec11c5913</t>
+  </si>
+  <si>
+    <t>relationship--97129600-dfdc-46fc-87ea-0815c54c2726</t>
+  </si>
+  <si>
+    <t>relationship--bfea3bd1-1ce5-4d9e-b016-73478a483537</t>
+  </si>
+  <si>
+    <t>relationship--87f2faef-e5fd-49df-99d1-3d1b54ca7640</t>
+  </si>
+  <si>
+    <t>relationship--fab8f5da-e65c-435e-8311-720b6c9eeabf</t>
+  </si>
+  <si>
+    <t>relationship--3aa6ec34-f393-430c-9cbd-4841f9920f0e</t>
+  </si>
+  <si>
+    <t>relationship--31366991-d83e-4eaf-88ba-c26255847e3f</t>
+  </si>
+  <si>
+    <t>relationship--d87ce476-23f9-4fc6-b13c-047097357dcf</t>
+  </si>
+  <si>
+    <t>relationship--5badbe27-c263-478a-b68d-c0c28b4f8ef1</t>
+  </si>
+  <si>
+    <t>relationship--a351e0a9-ae44-4578-8b4d-c6b47da74308</t>
+  </si>
+  <si>
+    <t>relationship--a56ff3ba-96e6-4973-bcd0-c4bef23b5d38</t>
+  </si>
+  <si>
+    <t>relationship--0ce7bddd-50d5-48be-afb7-d3e06b285ef0</t>
+  </si>
+  <si>
+    <t>relationship--05e4c4c5-0966-4337-8275-c4907b8d4673</t>
+  </si>
+  <si>
+    <t>relationship--565130fe-3386-42b6-b475-f02f8474bd39</t>
+  </si>
+  <si>
+    <t>relationship--cef88e9a-6cb7-49e6-9b5b-ba08c8ca6b88</t>
+  </si>
+  <si>
+    <t>relationship--e1ac74fc-d530-4cc3-a105-56087b595c2c</t>
+  </si>
+  <si>
+    <t>relationship--516e3400-7942-4d72-b4b0-e3b39d62f9e7</t>
+  </si>
+  <si>
+    <t>relationship--df7ec859-d883-4c8f-8b0e-372570d2a736</t>
+  </si>
+  <si>
+    <t>relationship--da299c4e-9630-4b38-b717-b6583dbe26fc</t>
+  </si>
+  <si>
+    <t>relationship--c8edbb88-14ff-4d8e-9c74-b2712da0ab11</t>
+  </si>
+  <si>
+    <t>relationship--278b8d8c-0a20-4a8f-9bad-a72df718c17c</t>
+  </si>
+  <si>
+    <t>relationship--ed38512a-db10-4611-b123-d56d3b981c1e</t>
+  </si>
+  <si>
+    <t>relationship--83dd8b38-931f-40f7-bc4b-d56173bcfe73</t>
+  </si>
+  <si>
+    <t>relationship--7f6d56c5-6612-489c-9b18-8c24dc75af58</t>
+  </si>
+  <si>
+    <t>relationship--118c7ea5-f1e1-495b-a5a2-963b25933ac6</t>
+  </si>
+  <si>
+    <t>relationship--b7c59cd1-369f-4de9-a3a4-5b5cdae3d166</t>
+  </si>
+  <si>
+    <t>relationship--b907d83f-4982-4baa-b5f8-fc364e9b33cc</t>
+  </si>
+  <si>
+    <t>relationship--7c44d0bb-7378-48de-af57-28bbb3af8b8b</t>
+  </si>
+  <si>
+    <t>relationship--eda1dbd4-3b39-44ff-90c1-96e6046320fc</t>
+  </si>
+  <si>
+    <t>relationship--3b210ccc-f8be-470c-adc2-cd060d11ffbe</t>
+  </si>
+  <si>
+    <t>relationship--7bf4e691-2470-49cd-a172-5df8af2263c5</t>
+  </si>
+  <si>
+    <t>relationship--57227651-67a7-4ede-b3bd-9309c9dede53</t>
+  </si>
+  <si>
+    <t>relationship--692ea191-a544-4a50-9449-6ac7d09a1930</t>
+  </si>
+  <si>
+    <t>relationship--6e0c35a5-3a68-4c67-af6d-bd0866e51274</t>
+  </si>
+  <si>
+    <t>relationship--c4285b2d-5078-4331-9d59-fe17df33e8d0</t>
+  </si>
+  <si>
+    <t>relationship--c55f3f86-c5b9-4fc3-82f3-3ef59966c26b</t>
+  </si>
+  <si>
+    <t>relationship--a2a349c4-fcd3-47cf-913c-db97245ac089</t>
+  </si>
+  <si>
+    <t>relationship--d12e139d-c65a-4553-832b-62ec4ad574ca</t>
+  </si>
+  <si>
+    <t>relationship--80d2485a-1628-48d9-bb5f-e5b985c816ef</t>
+  </si>
+  <si>
+    <t>relationship--c0eb327a-d351-41c7-ad63-def80454e574</t>
+  </si>
+  <si>
+    <t>relationship--b8166e54-71e5-4ec9-b871-e2bfa18c5cbf</t>
+  </si>
+  <si>
+    <t>relationship--859a06b7-36a7-4ff8-bf25-dd0593d202f3</t>
+  </si>
+  <si>
+    <t>relationship--8c419d72-e7d3-43ef-abcc-b264990cc673</t>
+  </si>
+  <si>
+    <t>relationship--7eac7055-d3e2-4b34-9559-1360309757c9</t>
+  </si>
+  <si>
+    <t>relationship--cd9f0e86-64ce-438f-9767-6b4081d8079f</t>
+  </si>
+  <si>
+    <t>relationship--22ace871-0cc2-4b40-901d-51c4fd38aebd</t>
+  </si>
+  <si>
+    <t>relationship--2ebd7677-4776-4837-9240-39ff6493c0d9</t>
+  </si>
+  <si>
+    <t>relationship--123596cd-c28b-46e5-a300-7400a612cb67</t>
+  </si>
+  <si>
+    <t>relationship--16144da2-91f9-49e6-917d-a71bbff07b37</t>
+  </si>
+  <si>
+    <t>relationship--9697c005-6797-4bf7-a837-4f028c927ee6</t>
+  </si>
+  <si>
+    <t>relationship--6e404788-5d9d-414b-a956-d54684562ead</t>
+  </si>
+  <si>
+    <t>relationship--2c434e02-6e26-4156-ae31-6b299dae7863</t>
+  </si>
+  <si>
+    <t>relationship--37a22f39-51a3-4b42-8cbf-4682cb984c5f</t>
+  </si>
+  <si>
+    <t>relationship--de3e18c5-8e55-4213-b7a5-016f634f52d6</t>
+  </si>
+  <si>
+    <t>relationship--b294a298-4572-45ba-83cd-6febe20eb9c8</t>
+  </si>
+  <si>
+    <t>relationship--2a87fd2a-b184-456a-9ff3-5287906fb03f</t>
+  </si>
+  <si>
+    <t>relationship--2984ab74-0098-40b3-910a-a4468d5b1140</t>
+  </si>
+  <si>
+    <t>relationship--f455f2ef-5c5e-4c45-ad3f-b7e6496eb027</t>
+  </si>
+  <si>
+    <t>relationship--4bc8e783-3567-4fb8-867d-b2b0591c3676</t>
+  </si>
+  <si>
+    <t>relationship--ae99f88c-b34e-48a8-b884-8751b57831c3</t>
+  </si>
+  <si>
+    <t>relationship--913af001-f7cb-4207-8322-14ef2f4f006b</t>
+  </si>
+  <si>
+    <t>relationship--fcb25d74-cfa2-45a2-af99-29eb0ad4b064</t>
+  </si>
+  <si>
+    <t>relationship--ba3d5ece-0df2-4f39-a0e6-2ab151c4f803</t>
+  </si>
+  <si>
+    <t>relationship--98d13a8f-5671-46ab-98bf-dcee471a7416</t>
+  </si>
+  <si>
+    <t>relationship--6dd55282-c047-46db-b47d-ffef75634f32</t>
+  </si>
+  <si>
+    <t>relationship--6576dbf2-9887-46d4-b7c0-077b0aa6d520</t>
+  </si>
+  <si>
+    <t>relationship--82e78eaa-a5b5-4328-a73f-d51422047701</t>
+  </si>
+  <si>
+    <t>relationship--c407b553-608e-42df-8f20-99867374029b</t>
+  </si>
+  <si>
+    <t>relationship--58cbd296-f428-4f07-9627-ef721bca5e24</t>
+  </si>
+  <si>
+    <t>relationship--4e4c1786-5c5a-49fc-bd5f-4f98209e04a8</t>
+  </si>
+  <si>
+    <t>relationship--3fd82cd0-8553-4535-9d88-2432d8d6c588</t>
+  </si>
+  <si>
+    <t>relationship--1dbbc37e-23d4-44c4-acdc-e3cac17cc385</t>
+  </si>
+  <si>
+    <t>relationship--fbde6f1d-be2f-4e5f-92a5-c9e21f6b00e6</t>
+  </si>
+  <si>
+    <t>relationship--44b541d4-16cd-4697-91ed-8959150b93ea</t>
+  </si>
+  <si>
+    <t>relationship--bc00c803-905b-483d-a214-b756ab179b45</t>
+  </si>
+  <si>
+    <t>relationship--930512ae-f088-4597-bae8-dcc756d386d6</t>
+  </si>
+  <si>
+    <t>relationship--1e3bdd39-f6fd-459b-953c-ddafac2af3ee</t>
+  </si>
+  <si>
+    <t>relationship--6cda8772-c59c-40f6-951e-7203c973239e</t>
+  </si>
+  <si>
+    <t>relationship--26435369-1682-4a9f-a340-a6ff3307ec65</t>
+  </si>
+  <si>
+    <t>relationship--46ba6b14-29ac-4278-b078-f34ba26b1be5</t>
+  </si>
+  <si>
+    <t>relationship--b0380dea-279d-4897-9888-5307871a3acb</t>
+  </si>
+  <si>
+    <t>relationship--ade84795-f059-4866-a09e-37e6ac5adf40</t>
+  </si>
+  <si>
+    <t>relationship--62bee3ce-caad-42e9-b7bd-9c2262a342cc</t>
+  </si>
+  <si>
+    <t>relationship--d7952f2c-eaf9-43a6-a7b0-b46555772b73</t>
+  </si>
+  <si>
+    <t>relationship--3d23f2db-b299-4698-8767-c4d5bc249f9c</t>
+  </si>
+  <si>
+    <t>relationship--51baad2a-4458-43c3-a534-392226563e3e</t>
+  </si>
+  <si>
+    <t>relationship--f125e8d8-5e5f-4821-9e91-21780cd1efd6</t>
+  </si>
+  <si>
+    <t>relationship--c9d89fd2-934d-49d0-bcc6-892b5bc54c05</t>
+  </si>
+  <si>
+    <t>relationship--ce4f2eda-e514-4c3d-8877-f503c4fcee9d</t>
+  </si>
+  <si>
+    <t>relationship--6c0df7e5-7d02-4aeb-961c-dc80d2bb33b6</t>
+  </si>
+  <si>
+    <t>relationship--7dc82937-c2c7-4121-b82f-1b15049d4567</t>
+  </si>
+  <si>
+    <t>relationship--1438c8ef-dd0f-46a1-a329-7a84094089a7</t>
+  </si>
+  <si>
+    <t>relationship--10b591e9-7eed-4d3f-9cb3-261d8bdf56f5</t>
+  </si>
+  <si>
+    <t>relationship--6320ca25-0dec-426b-a89f-1901840d4a9b</t>
+  </si>
+  <si>
+    <t>relationship--cc37dc30-86e3-4e5b-826c-87bc71b2f98b</t>
+  </si>
+  <si>
+    <t>relationship--434be38d-f7c2-4833-98af-4f52da9cc033</t>
+  </si>
+  <si>
+    <t>relationship--58c8f148-2f0b-40dd-9946-4e4b08b5a9e1</t>
+  </si>
+  <si>
+    <t>relationship--6e559c18-f8de-46cc-8a2c-903c7173ba23</t>
+  </si>
+  <si>
+    <t>relationship--7bccdde2-9194-47a0-a92f-44b4e77a8a1b</t>
+  </si>
+  <si>
+    <t>relationship--8cae63fe-5d4f-407d-bbdd-3ffbdacaa5f7</t>
+  </si>
+  <si>
+    <t>relationship--e15f196e-7079-436f-80ff-106dfbfcb050</t>
+  </si>
+  <si>
+    <t>relationship--5818dc97-498b-4db4-821f-eabf92cc0147</t>
+  </si>
+  <si>
+    <t>relationship--a31d3284-f6df-4832-8e81-ca077371c7a0</t>
+  </si>
+  <si>
+    <t>relationship--07d341f1-5e24-4da9-96ed-ceaeec948632</t>
+  </si>
+  <si>
+    <t>relationship--36acbe6c-f5be-48c5-8910-6f4d6a84c5b2</t>
+  </si>
+  <si>
+    <t>relationship--b079861e-56d8-44f5-9e8c-a969b05fd089</t>
+  </si>
+  <si>
+    <t>relationship--878b41f7-4aa2-4254-bda7-45809fbcf30e</t>
+  </si>
+  <si>
+    <t>relationship--05cc6a6d-7c0c-4ec8-babb-4f489f107014</t>
+  </si>
+  <si>
+    <t>relationship--8e01371e-9a5c-4f4e-b109-a7f005b94faa</t>
+  </si>
+  <si>
+    <t>relationship--5081685d-0e81-4e84-b914-876e5723e0b1</t>
+  </si>
+  <si>
+    <t>relationship--9a11a133-cf32-4216-bd62-e8d351e98517</t>
+  </si>
+  <si>
+    <t>relationship--b33a6108-0645-4a98-8bdc-2cfe83bfbd05</t>
+  </si>
+  <si>
+    <t>relationship--bf3b16c7-2687-4e50-b058-2b9980d05443</t>
+  </si>
+  <si>
+    <t>relationship--c67ab420-a3b8-4617-b942-fa34e0df8c81</t>
+  </si>
+  <si>
+    <t>relationship--c8bc29c2-0d05-4b84-b82e-576a60d9ca1b</t>
+  </si>
+  <si>
+    <t>relationship--818b14a7-3bf9-4917-974c-7283e66d21fc</t>
+  </si>
+  <si>
+    <t>relationship--d99f39d0-fb23-460a-a041-4d9557b9b445</t>
+  </si>
+  <si>
+    <t>relationship--f3c6f5e7-4e68-4633-b7d9-e2b35b32bd0d</t>
+  </si>
+  <si>
+    <t>relationship--d28c162f-cc0d-45ef-926b-5ecc38320d78</t>
+  </si>
+  <si>
+    <t>relationship--bf09b1a3-7528-424a-ad44-13d32054a3aa</t>
+  </si>
+  <si>
+    <t>relationship--2f3cdf54-d10f-43ea-8e57-ec386e7a5a04</t>
+  </si>
+  <si>
+    <t>relationship--736363d3-ad9d-49b8-8469-50f98e2ffcc6</t>
+  </si>
+  <si>
+    <t>relationship--7d80956f-0e1d-4804-83c2-3fb5e44342e0</t>
+  </si>
+  <si>
+    <t>relationship--8ed5c2d1-de73-46aa-a16a-aaed5f37518e</t>
+  </si>
+  <si>
+    <t>relationship--332abc6c-519c-49ea-8fdf-4c2ad58c5d30</t>
+  </si>
+  <si>
+    <t>relationship--65ee3d9c-ae09-4e8d-987d-6cc1d219e01f</t>
+  </si>
+  <si>
+    <t>relationship--1bee2722-fd00-4414-b078-719bb1bc13fc</t>
+  </si>
+  <si>
+    <t>relationship--e13a70ac-3b25-4075-bb54-0d44ba465878</t>
+  </si>
+  <si>
+    <t>relationship--29a3ce2b-6be4-44fb-8fae-beef5f0296a1</t>
+  </si>
+  <si>
+    <t>relationship--9c61218c-a3e3-4688-8723-8a681f5d4799</t>
+  </si>
+  <si>
+    <t>relationship--9b31e25d-8cbe-455c-954b-206d112c4a0a</t>
+  </si>
+  <si>
+    <t>relationship--da89423c-a636-491c-b7a6-20300d79e176</t>
+  </si>
+  <si>
+    <t>relationship--65d9dcda-82e0-4983-98d9-09100bf11f69</t>
+  </si>
+  <si>
+    <t>relationship--a66e5426-deea-479c-9b33-48831ef1f74f</t>
+  </si>
+  <si>
+    <t>relationship--8a7f492f-6d0f-48ef-8475-cf6d9343beae</t>
+  </si>
+  <si>
+    <t>relationship--d7cba973-52a5-4ffa-8792-fad9de0f4ff5</t>
+  </si>
+  <si>
+    <t>relationship--66c41619-1a71-4cdf-959c-b20e132a9feb</t>
+  </si>
+  <si>
+    <t>relationship--1c5a2877-55d2-47f0-852c-41cffd9ea9cd</t>
+  </si>
+  <si>
+    <t>relationship--338d5a11-cbad-444b-b042-b4aaae1152ef</t>
+  </si>
+  <si>
+    <t>relationship--15a7a091-9597-443c-9546-c8c0b6f7015e</t>
+  </si>
+  <si>
+    <t>relationship--b397365a-1c8a-4bf6-9323-b3fa37ec8120</t>
+  </si>
+  <si>
+    <t>relationship--0944d14f-213e-42c6-9227-990789faa016</t>
+  </si>
+  <si>
+    <t>relationship--93c54f83-b658-4267-9ebd-1d808cf45f79</t>
+  </si>
+  <si>
+    <t>relationship--83510ac8-d535-4650-8d81-ebdbe8b636d3</t>
+  </si>
+  <si>
+    <t>relationship--834f449c-b379-41ab-8593-fdc8a6f7da85</t>
+  </si>
+  <si>
+    <t>relationship--25bfdfd7-c584-4eee-badb-e362294f2728</t>
+  </si>
+  <si>
+    <t>relationship--6540b8e2-98fe-49f7-8a99-50d9dd1b8a11</t>
+  </si>
+  <si>
+    <t>relationship--ea9fe07e-1615-4dcf-a3bd-33abcf4ffd14</t>
+  </si>
+  <si>
+    <t>relationship--95761fd2-eff3-4bbd-a79a-d47e24029c7f</t>
+  </si>
+  <si>
+    <t>relationship--9ac65c10-b5e4-4ae1-ac04-e2577a4aff40</t>
+  </si>
+  <si>
+    <t>relationship--b8c173ac-8a9e-4765-bb1c-39b1ee53caac</t>
+  </si>
+  <si>
+    <t>relationship--117354e0-cd7d-484e-8756-87c5bb5fcd00</t>
+  </si>
+  <si>
+    <t>relationship--d435d200-8dbb-4172-80cb-ec869208eca5</t>
+  </si>
+  <si>
+    <t>relationship--eff1e690-9246-4cf9-b550-79f17cb29b68</t>
+  </si>
+  <si>
+    <t>relationship--9bae57d2-f5dc-42a0-836b-0f349e4cdc25</t>
+  </si>
+  <si>
+    <t>relationship--0156d507-7b40-45ec-8289-0f4fa5ba6163</t>
+  </si>
+  <si>
+    <t>relationship--33ab6ec3-19cf-4b49-8724-2b4af682af04</t>
+  </si>
+  <si>
+    <t>relationship--e1842498-5a34-4609-8db6-b2f82df3b197</t>
+  </si>
+  <si>
+    <t>relationship--719527aa-6dc8-4a61-a342-91d03a5c2d21</t>
+  </si>
+  <si>
+    <t>relationship--ba2437e9-e819-46a7-bab0-0878dbf9846d</t>
+  </si>
+  <si>
+    <t>relationship--818f6226-9afb-4912-b6a3-b69725ad0e2a</t>
+  </si>
+  <si>
+    <t>relationship--3a49096f-d797-4844-a514-37aadfb14943</t>
+  </si>
+  <si>
+    <t>relationship--a210a033-712a-4265-af86-ce866ebe8502</t>
+  </si>
+  <si>
+    <t>relationship--0e65dd55-8151-4a51-9adb-ad2b722c7b11</t>
+  </si>
+  <si>
+    <t>relationship--36958ad9-6617-44a9-ad62-03aa55bac03a</t>
+  </si>
+  <si>
+    <t>relationship--ace3997d-4e21-4b81-b6d6-147e08c0b0c2</t>
+  </si>
+  <si>
+    <t>relationship--65dfe9e2-f92b-41f5-a8d7-4d0cb775fd3c</t>
+  </si>
+  <si>
+    <t>relationship--57e70d24-0604-4783-99d1-8efa72bc229d</t>
+  </si>
+  <si>
+    <t>relationship--040c9390-eb5e-49cb-b5bf-d96b81a19376</t>
+  </si>
+  <si>
+    <t>relationship--d1bd4886-86ef-4466-a263-446fe6e1866f</t>
+  </si>
+  <si>
+    <t>relationship--f0b97568-130b-464d-8b32-c4d044aab10d</t>
+  </si>
+  <si>
+    <t>relationship--3dc31397-38e8-4bc1-bd09-06e562e88e3e</t>
+  </si>
+  <si>
+    <t>relationship--938ee97f-1383-42f4-a3fb-f79e9c820e3e</t>
+  </si>
+  <si>
+    <t>relationship--76049fb7-5bc2-4c9e-ba0e-297af2a4ef6b</t>
+  </si>
+  <si>
+    <t>relationship--ff825748-c271-4e23-981a-ace5d89e2f0d</t>
+  </si>
+  <si>
+    <t>relationship--c82e0390-57e7-451d-a05b-56a4cc08989b</t>
+  </si>
+  <si>
+    <t>relationship--777a2696-e49b-4777-9f59-3361cf2d959b</t>
+  </si>
+  <si>
+    <t>relationship--8bdae4af-4576-4585-9cc5-e67149a7a200</t>
+  </si>
+  <si>
+    <t>relationship--399137a2-b686-429b-a19e-996acc7a7bdb</t>
+  </si>
+  <si>
+    <t>relationship--78f7ba38-124d-49f4-aed3-9d01c6378d20</t>
+  </si>
+  <si>
+    <t>relationship--8e2c490b-78d0-4915-85f2-227774d6bb35</t>
+  </si>
+  <si>
+    <t>relationship--7d6fed15-cb67-4aeb-ba7e-4a5ac7f66e2e</t>
+  </si>
+  <si>
+    <t>relationship--93000c5d-435d-4b59-9bd9-6d18f4e88428</t>
+  </si>
+  <si>
+    <t>relationship--78cbaae0-d659-4816-9359-5700b0606cdf</t>
+  </si>
+  <si>
+    <t>relationship--ab8e5783-d185-4c0f-a17a-74ad9e6a2395</t>
+  </si>
+  <si>
+    <t>relationship--b2df047b-98d1-45d7-b379-53985bddf1c4</t>
+  </si>
+  <si>
+    <t>relationship--093ff580-0911-4ef5-aaae-92411c9b6597</t>
+  </si>
+  <si>
+    <t>relationship--16ee1bba-6e3c-440b-ba1f-56293093ae00</t>
+  </si>
+  <si>
+    <t>relationship--b884c378-1ffb-4f35-9e95-278a0657ecb7</t>
+  </si>
+  <si>
+    <t>relationship--f45365a5-32b0-417c-95f2-19c2f90abf3f</t>
+  </si>
+  <si>
+    <t>relationship--fbc3460b-ad11-409e-8859-f19a4ebe8d2e</t>
+  </si>
+  <si>
+    <t>relationship--d0393c1a-f522-4c8a-b58c-a9946069de19</t>
+  </si>
+  <si>
+    <t>relationship--155f9979-73ec-4eba-8808-38de97758784</t>
+  </si>
+  <si>
+    <t>relationship--f85f0758-4c57-4e59-a2b0-dd5977a28769</t>
+  </si>
+  <si>
+    <t>relationship--cc9b386b-845a-4409-a53c-e88fe3165ca7</t>
+  </si>
+  <si>
+    <t>relationship--c02574e7-28f8-4149-9e60-de548f2b2739</t>
+  </si>
+  <si>
+    <t>relationship--c70d52db-bc94-4b2e-af45-20f3874bfedd</t>
+  </si>
+  <si>
+    <t>relationship--e4d5e664-a09e-41aa-8901-163d02b7287b</t>
+  </si>
+  <si>
+    <t>relationship--3b3277ba-6e98-4c8e-8b72-d65d2c00ae61</t>
+  </si>
+  <si>
+    <t>relationship--190fb4f5-b465-4775-9528-46d207d120b2</t>
+  </si>
+  <si>
+    <t>relationship--12db5486-053c-48ed-bb49-48b1e4b11391</t>
+  </si>
+  <si>
+    <t>relationship--fc4c3558-5f44-4a25-898a-91cd7a53e0c4</t>
+  </si>
+  <si>
+    <t>relationship--32fbbc5a-d409-4e61-9a20-e1c8ef9a9f42</t>
+  </si>
+  <si>
+    <t>relationship--443f6959-879a-43a2-ae33-c42f99cf5108</t>
+  </si>
+  <si>
+    <t>relationship--63d649b8-b431-413e-b07d-eca5e0019b2a</t>
+  </si>
+  <si>
+    <t>relationship--8302cd38-5016-42ed-accb-70cdb1d2996e</t>
+  </si>
+  <si>
+    <t>relationship--461e13fb-702e-42e7-91b5-f27c6db3ea70</t>
+  </si>
+  <si>
+    <t>relationship--b85d0c7b-f276-4a67-a101-da016bce172a</t>
+  </si>
+  <si>
+    <t>relationship--b0d665a3-7b3c-4aa3-9687-a3a5368ac34e</t>
+  </si>
+  <si>
+    <t>relationship--3101592e-1242-464d-adcb-9c68c43f6ac1</t>
+  </si>
+  <si>
+    <t>relationship--6e72e46e-9f47-43db-9851-59d899089853</t>
+  </si>
+  <si>
+    <t>relationship--d872ba7d-f1bd-4e7d-83cb-4237e5a6ccae</t>
+  </si>
+  <si>
+    <t>relationship--205a45c2-7248-43c9-8fbc-b25eb7af9d3e</t>
+  </si>
+  <si>
+    <t>relationship--4b2a8dc7-2b7b-42ab-90c2-c202d6c481e9</t>
+  </si>
+  <si>
+    <t>relationship--bc9a8aa8-b287-4ec4-bb2d-5f64eadcc530</t>
+  </si>
+  <si>
+    <t>relationship--fa65970c-ac67-4d39-aaf4-cd3c7bbbadcd</t>
+  </si>
+  <si>
+    <t>relationship--b781b174-17d4-41fa-879e-962fa3c6472e</t>
+  </si>
+  <si>
+    <t>relationship--ec58069d-2af0-4181-bac9-4dddda88c28c</t>
+  </si>
+  <si>
+    <t>relationship--f8ae12cf-66ec-4c01-a250-46bb97f99c7d</t>
+  </si>
+  <si>
+    <t>relationship--6e8f3632-6158-4971-bf6c-f6b75abaa66d</t>
+  </si>
+  <si>
+    <t>relationship--3d819923-9d97-4a8b-a67c-30fde21645b9</t>
+  </si>
+  <si>
+    <t>relationship--f3e7964d-4204-43d9-95ba-a61a39073b86</t>
+  </si>
+  <si>
+    <t>relationship--a9a82add-18b6-4428-b7d4-a07995c91849</t>
+  </si>
+  <si>
+    <t>relationship--8df00cdb-e745-4f6f-b241-b40ee4cad23c</t>
+  </si>
+  <si>
+    <t>relationship--4f13473b-9a37-4531-b782-850ced97e89d</t>
+  </si>
+  <si>
+    <t>relationship--8b6fa31a-3839-49f7-9e18-677cc43b927d</t>
+  </si>
+  <si>
+    <t>relationship--2fb417b5-205b-4b9f-98fc-c9db2c7172b3</t>
+  </si>
+  <si>
+    <t>relationship--24a70091-a353-470d-81e3-cf75b2979c7c</t>
+  </si>
+  <si>
+    <t>relationship--63722a18-6f07-4a93-8e38-135c8fbcbb56</t>
+  </si>
+  <si>
+    <t>relationship--d43afa20-2d6c-47c9-abbb-fba45f539dc7</t>
+  </si>
+  <si>
+    <t>relationship--e513611f-dbb7-41ad-8e96-eeab94495952</t>
+  </si>
+  <si>
+    <t>relationship--4138b4da-9b4a-4810-8234-01f088b2ef84</t>
+  </si>
+  <si>
+    <t>relationship--187d585c-3c8c-452b-af29-a98dd6d0c790</t>
+  </si>
+  <si>
+    <t>relationship--a2a277a8-d68f-4890-b6ad-2f062fe5eb52</t>
+  </si>
+  <si>
+    <t>relationship--49bfcdee-0811-4e07-99d3-ea60966de109</t>
+  </si>
+  <si>
+    <t>relationship--f05621c7-ad01-4355-901d-20c3bed12c54</t>
+  </si>
+  <si>
+    <t>relationship--609ed9e0-8e20-4cf4-84b5-53571e3e2f02</t>
+  </si>
+  <si>
+    <t>relationship--8f712af0-daec-4fec-ac07-e716982da013</t>
+  </si>
+  <si>
+    <t>relationship--530d8452-141f-4f05-b35d-3196f6474b62</t>
+  </si>
+  <si>
+    <t>relationship--b53961b4-1ae8-4160-ae4d-42264492598d</t>
+  </si>
+  <si>
+    <t>relationship--a07a243a-5196-4d10-bd4c-6710b8b351e0</t>
+  </si>
+  <si>
+    <t>relationship--1bfa5390-07ec-418e-adf0-d1bb78d429e5</t>
+  </si>
+  <si>
+    <t>relationship--5f1bded5-3de0-4e81-8e96-b51d5bc64368</t>
+  </si>
+  <si>
+    <t>relationship--1bdc7cd5-2ee1-42f6-b684-ff7531fa9e4a</t>
+  </si>
+  <si>
+    <t>relationship--0ac78c44-7b00-4a46-8c4e-8fc97e87a671</t>
+  </si>
+  <si>
+    <t>relationship--4f149647-7dda-40a9-97d4-a0172656a6a2</t>
+  </si>
+  <si>
+    <t>relationship--9f70a209-0fce-4de7-8560-bd747b68f230</t>
+  </si>
+  <si>
+    <t>relationship--bd191415-4590-49eb-8995-1518efd9a587</t>
+  </si>
+  <si>
+    <t>relationship--d54dea5c-d6ff-4830-8a7e-5761b68f462d</t>
+  </si>
+  <si>
+    <t>relationship--2b77291f-cb53-4bb2-a480-2d675534486a</t>
+  </si>
+  <si>
+    <t>relationship--31992d27-7e29-464c-bfb4-5e6ec101ae9a</t>
+  </si>
+  <si>
+    <t>relationship--7f3df424-3f0a-4e8b-ad21-e2bb30e03b70</t>
+  </si>
+  <si>
+    <t>relationship--b210e0a4-77b8-45b4-8302-acc843eee7c9</t>
+  </si>
+  <si>
+    <t>relationship--d85132e9-70aa-46bf-b3b0-68deb7dccc03</t>
+  </si>
+  <si>
+    <t>relationship--ed82f8c0-0118-4b29-adbb-3ff2283b3758</t>
+  </si>
+  <si>
+    <t>relationship--75b01daa-79c8-41b0-aa84-e6776c9bfe7e</t>
+  </si>
+  <si>
+    <t>relationship--1ac1f0cb-ea14-4307-b3f4-c7e8c78acbb9</t>
+  </si>
+  <si>
+    <t>relationship--ce23341a-f769-4548-b480-775518d22c72</t>
+  </si>
+  <si>
+    <t>relationship--a3623915-8451-4484-a638-9cc79759edf8</t>
+  </si>
+  <si>
+    <t>relationship--f2f5d0fd-c627-4148-becf-ed7bf72046fd</t>
+  </si>
+  <si>
+    <t>relationship--da796365-b316-430f-ba32-e083db19acdd</t>
+  </si>
+  <si>
+    <t>relationship--819e7857-7f0e-42ce-89d3-ca6cf925d01c</t>
+  </si>
+  <si>
+    <t>relationship--a834fafe-2e75-43d6-9bdb-a572809b116d</t>
+  </si>
+  <si>
+    <t>relationship--f3b88869-903a-4db6-a5b4-fb5d2acd997d</t>
+  </si>
+  <si>
+    <t>relationship--683c17cc-8a59-4e91-b473-27b0791ae0ce</t>
+  </si>
+  <si>
+    <t>relationship--097b2e9c-ebb0-42ff-8f3f-663a11d77b7c</t>
+  </si>
+  <si>
+    <t>relationship--6c7003f5-9e62-45fc-a64d-fcbe0339eace</t>
+  </si>
+  <si>
+    <t>relationship--60cef4be-fc20-4e92-9dc0-b7ae246d89d8</t>
+  </si>
+  <si>
+    <t>relationship--5c73d2f3-61e2-46fb-bcd2-b62142a5d7e7</t>
+  </si>
+  <si>
+    <t>relationship--2b65c9dd-0df7-4429-8fb5-25b10f196fa3</t>
+  </si>
+  <si>
+    <t>relationship--be680fd1-cdf9-48f9-b32b-af03edcd5f49</t>
+  </si>
+  <si>
+    <t>relationship--24cd3805-31bf-4d10-bc4e-689fad4be8a7</t>
+  </si>
+  <si>
+    <t>relationship--a10a418b-47c7-4162-85f3-bfa1eace9d91</t>
+  </si>
+  <si>
+    <t>relationship--3b355b20-d54d-486f-8971-0cfe0534cd4a</t>
+  </si>
+  <si>
+    <t>relationship--82d16f2f-0a2c-4561-a6e8-4b9e36ac6e6d</t>
+  </si>
+  <si>
+    <t>relationship--dcecb634-8324-42b1-b91b-9dc407202d5c</t>
+  </si>
+  <si>
+    <t>relationship--2dedb174-ce09-4791-ac10-81a064e97e43</t>
+  </si>
+  <si>
+    <t>relationship--d06f3699-71e9-4994-aed3-fc6c1d4c103d</t>
+  </si>
+  <si>
+    <t>relationship--991acbe3-46b4-4ece-8191-6ca86a63cedd</t>
+  </si>
+  <si>
+    <t>relationship--5bff5a94-791a-438c-a7c4-898a49eda6a4</t>
+  </si>
+  <si>
+    <t>relationship--9d4c8082-15fb-49c3-a058-1e6f230473bc</t>
+  </si>
+  <si>
+    <t>relationship--9e8bd416-a9a5-4207-9acc-46f25aacbdb1</t>
+  </si>
+  <si>
+    <t>relationship--f1ba875e-abe4-43d3-bdca-9f5b299753f2</t>
+  </si>
+  <si>
+    <t>relationship--9583c8de-f3ff-4a8b-8163-dab5fb1e24ad</t>
+  </si>
+  <si>
+    <t>relationship--8d884304-83d9-4af2-a3e8-94c2e27ed308</t>
+  </si>
+  <si>
+    <t>relationship--40d7fbe3-8fbb-455c-9220-93e4002ef10d</t>
+  </si>
+  <si>
+    <t>relationship--6a628742-c864-4748-abd9-da2f3f180740</t>
+  </si>
+  <si>
+    <t>relationship--74b6a8d6-621f-4e0d-a039-7f3d7fb5cb26</t>
+  </si>
+  <si>
+    <t>relationship--e04e78cc-5f18-41d9-9898-c4c59b651beb</t>
+  </si>
+  <si>
+    <t>relationship--49cea33e-bc3f-4c27-a018-bd25a3cb90b8</t>
+  </si>
+  <si>
+    <t>relationship--075a9738-f9f7-4364-89d0-a7c6d1483457</t>
+  </si>
+  <si>
+    <t>relationship--1e5802f2-2fa3-4929-826c-8dc3240ca1f4</t>
+  </si>
+  <si>
+    <t>relationship--3cdc29c6-4557-4e25-a305-457aa88441ae</t>
+  </si>
+  <si>
+    <t>relationship--9b2d4f54-0818-4e04-bf2c-7464ff329b22</t>
+  </si>
+  <si>
+    <t>relationship--980e5e48-abdb-47df-be26-10b127e090d3</t>
+  </si>
+  <si>
+    <t>relationship--39aeec91-4b13-4530-bc9c-810361e46cb7</t>
+  </si>
+  <si>
+    <t>relationship--a4cad2fb-a5c1-498c-b6ca-2517937adb79</t>
+  </si>
+  <si>
+    <t>relationship--95e387fa-0515-4a56-a500-3fb7c415a376</t>
+  </si>
+  <si>
+    <t>relationship--c2b2e394-676e-4412-8781-3cc9d8f9621e</t>
+  </si>
+  <si>
+    <t>relationship--7b958cef-f8f4-49cf-a5b1-af13644c3252</t>
+  </si>
+  <si>
+    <t>relationship--cc4f6fe7-9aea-43a3-ba9a-e77eaa3b8d77</t>
+  </si>
+  <si>
+    <t>relationship--f93a4c95-eed0-426e-be95-9c603951319b</t>
+  </si>
+  <si>
+    <t>relationship--af47548c-8ed8-455d-a2db-0bc93f4030b3</t>
+  </si>
+  <si>
+    <t>relationship--c1745f80-3290-4984-9dd6-ee4299f490b1</t>
+  </si>
+  <si>
+    <t>relationship--d4e6d433-b83a-4fec-b78c-6470cedbed0e</t>
+  </si>
+  <si>
+    <t>relationship--baba5c19-c8f3-4534-ad1a-864f3e9c8af6</t>
+  </si>
+  <si>
+    <t>relationship--cf4ec701-fa7a-4fba-bd7a-851429b88cc0</t>
+  </si>
+  <si>
+    <t>relationship--6dae93ac-f5ef-4b59-82f3-78dcabd8e94e</t>
+  </si>
+  <si>
+    <t>relationship--0b279b18-ce31-4fa5-8f87-6a4a394eb886</t>
+  </si>
+  <si>
+    <t>relationship--0a58485f-695b-4ea9-808d-ab4d235463e3</t>
+  </si>
+  <si>
+    <t>relationship--848bdfbe-75d2-472f-9331-3d956b9d7322</t>
+  </si>
+  <si>
+    <t>relationship--2c5c1c46-398a-40aa-9914-2449ea6edf94</t>
+  </si>
+  <si>
+    <t>relationship--21a7018b-055f-4605-8b79-32213036025a</t>
+  </si>
+  <si>
+    <t>relationship--ad35db0d-4857-4207-a772-86ae1524bc73</t>
+  </si>
+  <si>
+    <t>relationship--c054d111-0cab-4194-b81b-602738e62f1e</t>
+  </si>
+  <si>
+    <t>relationship--335c70ce-5be3-43b9-a53f-6ccf0002bf1c</t>
+  </si>
+  <si>
+    <t>relationship--6ea1a5d4-7467-4b7d-948f-21a358049e4d</t>
+  </si>
+  <si>
+    <t>relationship--e6bad643-553c-4ba0-bc40-264d85592851</t>
+  </si>
+  <si>
+    <t>relationship--7a9d0203-aef0-41b5-bb77-00a1a902ee42</t>
+  </si>
+  <si>
+    <t>relationship--c89c0b7a-f023-479e-9753-40097186f046</t>
+  </si>
+  <si>
+    <t>relationship--e04b5366-8c23-448d-9b88-fe56bd29942d</t>
+  </si>
+  <si>
+    <t>relationship--2ed74d6a-11c8-4f33-bd08-1ec2f25bd0b7</t>
+  </si>
+  <si>
+    <t>relationship--a785db23-c56a-4693-beda-7dcf166e6227</t>
+  </si>
+  <si>
+    <t>relationship--2f92b345-b9fc-4643-898b-3904e77069bf</t>
+  </si>
+  <si>
+    <t>relationship--b1c463fa-8f1a-4b77-9a65-16e5852c003c</t>
+  </si>
+  <si>
+    <t>relationship--d374ff17-73dd-4ac7-8381-62eed7137469</t>
+  </si>
+  <si>
+    <t>relationship--72d78c0d-8e6f-437f-92a7-4c076720dece</t>
+  </si>
+  <si>
+    <t>relationship--116a18fb-8c67-4fe1-a7ca-986001ce149f</t>
+  </si>
+  <si>
+    <t>relationship--53d0fca9-36f5-4eda-8632-d72031d8d198</t>
+  </si>
+  <si>
+    <t>relationship--a125c3e6-5ea4-416d-81b4-c0169bf5d36d</t>
+  </si>
+  <si>
+    <t>relationship--eda34a23-d83c-44f9-936c-c8e3107288a3</t>
+  </si>
+  <si>
+    <t>relationship--4f5120eb-12a6-4033-8c98-af20365d4fd1</t>
+  </si>
+  <si>
+    <t>relationship--3bc86575-0c4b-490a-b373-68bec683add4</t>
+  </si>
+  <si>
+    <t>relationship--f87d3aef-083b-4d69-8745-50345d6587f3</t>
+  </si>
+  <si>
+    <t>relationship--c90f8eeb-d6b2-44fd-9b02-e3e18e6db474</t>
+  </si>
+  <si>
+    <t>relationship--36650039-0241-4c19-9659-3ca5f72971de</t>
+  </si>
+  <si>
+    <t>relationship--18089baf-d9c4-482b-ac26-91bfd97eb777</t>
+  </si>
+  <si>
+    <t>relationship--fc13aee5-9eaa-449e-ae59-330eb32fea05</t>
+  </si>
+  <si>
+    <t>relationship--c947d95f-8656-4324-b486-cd13ca0927cc</t>
+  </si>
+  <si>
+    <t>relationship--b336cb42-3bb1-435c-846f-0c00febf1277</t>
+  </si>
+  <si>
+    <t>relationship--ce900a33-70c5-4a1a-9781-c87b88e967b2</t>
+  </si>
+  <si>
+    <t>relationship--933b2afa-e26f-4aa9-ad59-5e3f5125e589</t>
+  </si>
+  <si>
+    <t>relationship--18c57bf7-ae3c-4657-9739-d786015969e2</t>
+  </si>
+  <si>
+    <t>relationship--852be3d7-aa50-47cc-8650-4d1d96e5eada</t>
+  </si>
+  <si>
+    <t>relationship--fc878e7d-9269-4bc0-9a8d-5bd96a8a21e3</t>
+  </si>
+  <si>
+    <t>relationship--cea2cea0-ad64-4fb2-9ec3-2f0703d860fe</t>
+  </si>
+  <si>
+    <t>relationship--a1b44447-6383-44a1-8be5-4c130931885d</t>
+  </si>
+  <si>
+    <t>relationship--aa2208c4-3aa8-4b41-b43b-881b9da22239</t>
+  </si>
+  <si>
+    <t>relationship--660f2aca-acdb-4d7a-a623-c1c4bd072590</t>
+  </si>
+  <si>
+    <t>relationship--16250663-d5c7-44a0-b47d-51e08be54785</t>
+  </si>
+  <si>
+    <t>relationship--b21c33d5-2489-4693-bbc8-d90ac913967f</t>
+  </si>
+  <si>
+    <t>relationship--790eea08-3f25-4d6b-b2ca-194bd4040dbc</t>
+  </si>
+  <si>
+    <t>relationship--09747095-11f6-42fe-80c9-035fe244f624</t>
+  </si>
+  <si>
+    <t>relationship--678ca8eb-6f43-4ac7-9e5f-c0d16ada12cb</t>
+  </si>
+  <si>
+    <t>relationship--507287f7-225d-4c78-8250-18934f0ad3b0</t>
+  </si>
+  <si>
+    <t>relationship--4fa18265-9a9c-4b4b-9221-f87ee590b740</t>
+  </si>
+  <si>
+    <t>relationship--9974065b-d135-4983-bc93-6d4c8a41ccfa</t>
+  </si>
+  <si>
+    <t>relationship--366bb653-b0cb-4f76-a261-cc1acf7b2786</t>
+  </si>
+  <si>
+    <t>relationship--852dfeaa-f92c-4b07-b20b-6666060cb1f6</t>
+  </si>
+  <si>
+    <t>relationship--9dbb42b0-39e3-4c8f-a726-522c83944680</t>
+  </si>
+  <si>
+    <t>relationship--45bbf762-8c52-4374-a5f3-ae6ed92beacc</t>
+  </si>
+  <si>
+    <t>relationship--6451fe6f-8f1e-474b-b36c-37bfb8d171d3</t>
+  </si>
+  <si>
+    <t>relationship--52d6dae1-ae2a-413f-9b16-93ec199212fb</t>
+  </si>
+  <si>
+    <t>relationship--68afc738-9241-447a-b99e-c7d1fd301ed0</t>
+  </si>
+  <si>
+    <t>relationship--aba19d3c-eb07-4976-b2a8-3e5e01b1baf3</t>
+  </si>
+  <si>
+    <t>relationship--57d02153-c6a4-4528-a314-c22631dd526d</t>
+  </si>
+  <si>
+    <t>relationship--8922e0b6-24f5-451e-b25b-7792c71f272b</t>
+  </si>
+  <si>
+    <t>relationship--b79e8b45-b8c8-464a-a735-141b2bc48e92</t>
+  </si>
+  <si>
+    <t>relationship--d21e5e1f-dd33-41ec-8df7-4d2d800a09a8</t>
+  </si>
+  <si>
+    <t>relationship--677dfe65-b189-4f72-ab09-4df65c1c1d7b</t>
+  </si>
+  <si>
+    <t>relationship--7162dd20-7933-48a5-884d-00783ffe735d</t>
+  </si>
+  <si>
+    <t>relationship--502fed6c-2913-48a0-bef8-448cd530e753</t>
+  </si>
+  <si>
+    <t>relationship--3c219078-acd9-4d8b-8b01-326313855dc2</t>
+  </si>
+  <si>
+    <t>relationship--01c0f813-b9e4-4596-9e78-fd93563ca609</t>
+  </si>
+  <si>
+    <t>relationship--fe7ccf7a-c024-4340-8ba2-4e919213a8c6</t>
+  </si>
+  <si>
+    <t>relationship--8088ae80-0e2d-4653-a2e1-c1c29f777a4c</t>
+  </si>
+  <si>
+    <t>relationship--90a37a3a-9577-49fc-9989-771444e7c56a</t>
+  </si>
+  <si>
+    <t>relationship--9d0a828d-f81f-4601-9850-d3564b968a54</t>
+  </si>
+  <si>
+    <t>relationship--dd1598cd-ec13-4064-a1c7-e16f7a81aa74</t>
+  </si>
+  <si>
+    <t>relationship--ecd69714-1d25-43cd-a432-f70962a54b62</t>
+  </si>
+  <si>
+    <t>relationship--106ad2d5-ed5a-4680-b28d-e40e2c73fb1a</t>
+  </si>
+  <si>
+    <t>relationship--6aee2f28-8a03-4e64-9700-7f07e73500ba</t>
+  </si>
+  <si>
+    <t>relationship--d2f0e81a-2057-4e93-ab36-c61afef37fd7</t>
+  </si>
+  <si>
+    <t>relationship--40ec47e6-77e6-42b8-8a25-7853fe687141</t>
+  </si>
+  <si>
+    <t>relationship--5536f8ea-dade-4bfb-8665-3958d824469d</t>
+  </si>
+  <si>
+    <t>relationship--5b39901b-f285-4060-a711-77c092bbeeca</t>
+  </si>
+  <si>
+    <t>relationship--0d5d3c2a-9dd4-47c5-939d-3b1ada5f714b</t>
+  </si>
+  <si>
+    <t>relationship--c356afec-73f2-4a7c-b4ac-87686f124c98</t>
+  </si>
+  <si>
+    <t>relationship--d65586b6-8843-436b-868b-5643747c1458</t>
+  </si>
+  <si>
+    <t>relationship--c9514420-06b6-411d-b29d-698d7c0c32a5</t>
+  </si>
+  <si>
+    <t>relationship--8595d180-0b01-4d71-81fc-50c503a5cc7c</t>
+  </si>
+  <si>
+    <t>relationship--c9595494-ee98-4a68-8948-aae74bc0a24e</t>
+  </si>
+  <si>
+    <t>relationship--422c3b87-86fe-48d9-a056-fed6294e1b0c</t>
+  </si>
+  <si>
+    <t>relationship--fe24862b-3be8-4d94-a070-5f31d2561b03</t>
+  </si>
+  <si>
+    <t>relationship--10e845b5-afc8-47c4-898d-65db358fd2f9</t>
+  </si>
+  <si>
+    <t>relationship--d60c19e7-f755-4610-8537-2984ee4bc95b</t>
+  </si>
+  <si>
+    <t>relationship--460e3f22-5e70-4e1a-ae77-4d4e519fa881</t>
+  </si>
+  <si>
+    <t>relationship--4b4eeb4e-46d4-4f71-96d8-d0026bba1ed8</t>
+  </si>
+  <si>
+    <t>relationship--fb629e4a-e6f2-46bb-b4c0-49f44f821092</t>
+  </si>
+  <si>
+    <t>relationship--df1ce40a-dac8-45ed-b042-05dfc77c05bb</t>
+  </si>
+  <si>
+    <t>relationship--89e96d40-fea4-40bf-8ce4-85129bc59274</t>
+  </si>
+  <si>
+    <t>relationship--675aae63-9167-444e-bfe1-06d0b895a842</t>
+  </si>
+  <si>
+    <t>relationship--0283d952-9f00-413f-ba8f-8ee476a1dbc1</t>
+  </si>
+  <si>
+    <t>relationship--95ea5184-bb3b-43a1-8782-cd81e17d7263</t>
+  </si>
+  <si>
+    <t>relationship--2d86f586-095d-4616-9fe3-7a14d4e2cae2</t>
+  </si>
+  <si>
+    <t>relationship--11324577-43b4-4627-ad35-aa562a54c341</t>
+  </si>
+  <si>
+    <t>relationship--bfbbd33a-e5e1-4852-9306-1d7c43b641ee</t>
+  </si>
+  <si>
+    <t>relationship--f35ecf84-ea47-4385-a2b3-48d5e21387d8</t>
+  </si>
+  <si>
+    <t>relationship--7104efed-9524-4ecc-b0f9-a417774f8d6a</t>
+  </si>
+  <si>
+    <t>relationship--5e7fd10d-6c05-4c29-be4d-41386fa93ee2</t>
+  </si>
+  <si>
+    <t>relationship--26ae8fdd-f418-4e90-a1cb-0514e89f5396</t>
+  </si>
+  <si>
+    <t>relationship--0c8f00b9-4929-4a91-9e67-f2287a69961d</t>
+  </si>
+  <si>
+    <t>relationship--e1d35297-ead4-43c0-b8bd-886275c5b1a1</t>
+  </si>
+  <si>
+    <t>relationship--4e84a9a4-8941-4267-aa48-5d7635ccb758</t>
+  </si>
+  <si>
+    <t>relationship--992593de-3273-45fc-815b-0f71e42c59c3</t>
+  </si>
+  <si>
+    <t>relationship--d9d53a8e-ad3d-4ae1-8626-a2e101cb53bc</t>
+  </si>
+  <si>
+    <t>relationship--42dc016f-7e38-40f2-862b-d1407135e1ba</t>
+  </si>
+  <si>
+    <t>relationship--548c662b-e702-454d-894d-aa00bd15daee</t>
+  </si>
+  <si>
+    <t>relationship--3c8c661d-e662-420b-87c9-1e78cce48160</t>
+  </si>
+  <si>
+    <t>relationship--8d5ce96b-3e5a-46b5-986e-066f30e7d102</t>
+  </si>
+  <si>
+    <t>relationship--c9b11839-0972-4c4f-a08d-5ad4edcd08a8</t>
+  </si>
+  <si>
+    <t>relationship--0715ddc8-2bc3-4465-8dec-19f8a5fca47d</t>
+  </si>
+  <si>
+    <t>relationship--18e9ee37-32eb-40c7-ba80-6603163572a4</t>
+  </si>
+  <si>
+    <t>relationship--e38c7839-a190-4247-814f-b87bc7c09c4e</t>
+  </si>
+  <si>
+    <t>relationship--cb5bb378-e4f8-4018-894a-ba6e6eb56939</t>
+  </si>
+  <si>
+    <t>relationship--624b4a09-8d37-41e3-a5f5-4d7dd67fbd34</t>
+  </si>
+  <si>
+    <t>relationship--473143d3-de77-484c-8794-06621a40f738</t>
+  </si>
+  <si>
+    <t>relationship--96c1b3a1-7e12-4e2f-9d37-f6fae16a6c22</t>
+  </si>
+  <si>
+    <t>relationship--3cb7fc74-614e-4d58-a946-c344a9a8f7e1</t>
+  </si>
+  <si>
+    <t>relationship--b8fb19c3-7a18-4353-8692-77753d25b876</t>
+  </si>
+  <si>
+    <t>relationship--4e6e6dda-1ef8-48bc-9fec-6168a81ba00a</t>
+  </si>
+  <si>
+    <t>relationship--8264538f-bef4-4f84-bf9f-021cac6c2c6d</t>
+  </si>
+  <si>
+    <t>relationship--131c51bd-34b1-4f67-b7d8-fa840fc69750</t>
+  </si>
+  <si>
+    <t>relationship--33f9b731-538b-4627-930f-eec899282ce8</t>
+  </si>
+  <si>
+    <t>relationship--a8bbf553-d68c-416e-ab2e-db8d7b010d8c</t>
+  </si>
+  <si>
+    <t>relationship--79e705c1-4fd7-4e27-b889-0fe04825fd33</t>
+  </si>
+  <si>
+    <t>relationship--1194a81b-5134-4fe9-bba4-65b9b1d80a69</t>
+  </si>
+  <si>
+    <t>relationship--2572aa85-70c9-4048-af8e-a800a6b9019a</t>
+  </si>
+  <si>
+    <t>relationship--44c1b005-058c-4fc8-9fa6-4bfb6b77ab72</t>
+  </si>
+  <si>
+    <t>relationship--9379159d-ac2b-46a4-b4e1-446d885f0b8a</t>
+  </si>
+  <si>
+    <t>relationship--fd0c1b84-2b4b-4e53-bef5-c90ddd5bf36a</t>
+  </si>
+  <si>
+    <t>relationship--a8538c78-7fe9-4005-af59-b1cb97e9bbe6</t>
+  </si>
+  <si>
+    <t>relationship--fc975dd9-2a58-413d-bef4-8f326dadc42d</t>
+  </si>
+  <si>
+    <t>relationship--cf237a49-124f-450d-9f82-6687bf7c2bbd</t>
+  </si>
+  <si>
+    <t>relationship--34433b84-24b7-46db-8a89-69d5c1842212</t>
+  </si>
+  <si>
+    <t>relationship--1056ae9d-16ed-4245-936e-fb1f0ea739fc</t>
+  </si>
+  <si>
+    <t>relationship--bb17a815-48e7-41d2-a2d7-ced0649b6a72</t>
+  </si>
+  <si>
+    <t>relationship--88d66211-d6e8-43e0-bce4-73b5ccf11cfe</t>
+  </si>
+  <si>
+    <t>relationship--ad816f19-7ef4-42ad-a0d8-6f3cdc5dc7b5</t>
+  </si>
+  <si>
+    <t>relationship--b0b9fa79-b8c6-4d56-91af-e78ae8868a18</t>
+  </si>
+  <si>
+    <t>relationship--a65db1f2-21ff-424b-a521-2050ca1f3b09</t>
+  </si>
+  <si>
+    <t>relationship--cc771afe-611a-412f-a747-fc87cc56f804</t>
+  </si>
+  <si>
+    <t>relationship--f931f4cc-b4b2-4a74-bf94-42588c3b19b9</t>
+  </si>
+  <si>
+    <t>relationship--46cbb067-12a0-4002-affb-9787f3ae6286</t>
+  </si>
+  <si>
+    <t>relationship--03eaa6f9-e266-4cda-aa1f-8e47162842b0</t>
+  </si>
+  <si>
+    <t>relationship--79c0ba76-7d1e-4ce1-a4b7-adbe4dc0495f</t>
+  </si>
+  <si>
+    <t>relationship--81eaafe9-f9b7-4ce4-a525-fdb78fc968f3</t>
+  </si>
+  <si>
+    <t>relationship--d1a55c8c-6e2b-4faf-b8f3-de995fe69739</t>
+  </si>
+  <si>
+    <t>relationship--d9c02db0-bbab-4ea0-b9ae-c95bf97f8432</t>
+  </si>
+  <si>
+    <t>relationship--ba81173b-aefd-40d5-aac2-400c5329a8bf</t>
+  </si>
+  <si>
+    <t>relationship--431549c5-c30a-400a-a674-46bda0e54599</t>
+  </si>
+  <si>
+    <t>relationship--f05c1e28-7669-45a0-8ecb-8a24b74120d2</t>
+  </si>
+  <si>
+    <t>relationship--693adc63-b1db-4758-a2d7-d21c854c50a4</t>
+  </si>
+  <si>
+    <t>relationship--1ab306f6-f695-4873-b3fa-10c2176c1305</t>
+  </si>
+  <si>
+    <t>relationship--6a9f86b8-a71d-429c-b08f-84ccfae7f31b</t>
+  </si>
+  <si>
+    <t>relationship--df29b69f-0ced-4fc0-b6c8-94434e751e36</t>
+  </si>
+  <si>
+    <t>relationship--2f8a5ca2-f944-4f76-a6ff-435cc073cef6</t>
+  </si>
+  <si>
+    <t>relationship--c8c060f6-4af2-4b4b-8340-d5f24e6448fc</t>
+  </si>
+  <si>
+    <t>relationship--62ccfc5c-2e25-4fd4-82fd-1e09115778a5</t>
+  </si>
+  <si>
+    <t>relationship--a602df81-ddcb-4bc9-ada4-23b1daf04e19</t>
+  </si>
+  <si>
+    <t>relationship--48e7cb0d-f697-4853-93ca-855cf57b6b7f</t>
+  </si>
+  <si>
+    <t>relationship--71ceb742-b2c2-4c6e-93c4-b6396eb1203a</t>
+  </si>
+  <si>
+    <t>relationship--120f6ccb-a375-455f-8b5d-4660f7d8f703</t>
+  </si>
+  <si>
+    <t>relationship--b1cfc045-f959-45e5-8a1e-4e75a6a3ac06</t>
+  </si>
+  <si>
+    <t>relationship--3a7d524e-bc71-446e-8008-02a27f3537d7</t>
+  </si>
+  <si>
+    <t>relationship--3f7db20f-12f2-4e3e-83d9-c7039d9f2862</t>
+  </si>
+  <si>
+    <t>relationship--eb5ce8c1-f59b-4ad0-b0df-63feed62464d</t>
+  </si>
+  <si>
+    <t>relationship--af84b5a3-d24a-4407-8944-31ac8f69fa7d</t>
+  </si>
+  <si>
+    <t>relationship--374ef7fd-766a-4b89-9c40-7c85da4864aa</t>
+  </si>
+  <si>
+    <t>relationship--6c3336c0-2dec-46e9-a424-b86461f6719c</t>
+  </si>
+  <si>
+    <t>relationship--e8c953da-2943-46e0-b7ae-cffe3bf274b4</t>
+  </si>
+  <si>
+    <t>relationship--6b497a64-0f53-4b22-a8f3-b8c42489ff57</t>
+  </si>
+  <si>
+    <t>relationship--2b21c131-5910-4163-8e65-5cedc0d9a624</t>
+  </si>
+  <si>
+    <t>relationship--7d51687b-6630-4fea-be92-b2aa8af5a624</t>
+  </si>
+  <si>
+    <t>relationship--1e67e6e6-b2ca-4f65-a822-a322d24f1f34</t>
+  </si>
+  <si>
+    <t>relationship--5b5be8c6-1acd-4481-b4a5-6cfaf12bf30c</t>
+  </si>
+  <si>
+    <t>relationship--b6b93397-50d8-4cbc-aa34-5a4ae18fe1f6</t>
+  </si>
+  <si>
+    <t>relationship--449039e3-2d6c-4747-950f-150777d01333</t>
+  </si>
+  <si>
+    <t>relationship--c77fe291-d151-4070-9216-0a4c3cb6ab6d</t>
+  </si>
+  <si>
+    <t>relationship--60422152-5817-4023-9554-55b6804ab0b3</t>
+  </si>
+  <si>
+    <t>relationship--30720fdc-5bbe-47fb-977a-b11b297a5789</t>
+  </si>
+  <si>
+    <t>relationship--a8711592-b934-4a3b-869b-18e5476eab29</t>
+  </si>
+  <si>
+    <t>relationship--dd35529a-4997-46ec-a5dd-da669f251d73</t>
+  </si>
+  <si>
+    <t>relationship--88d3266c-359b-4c7b-8e8f-d7629066ae51</t>
+  </si>
+  <si>
+    <t>relationship--5db7225b-a9bc-4701-87eb-4e7dd112c8ba</t>
+  </si>
+  <si>
+    <t>relationship--2f5a4e73-7bad-4088-9e28-70f12bfdf432</t>
+  </si>
+  <si>
+    <t>relationship--8353609f-ce10-446d-84f7-8c21c9f7f096</t>
+  </si>
+  <si>
+    <t>relationship--23ccab69-3f81-4c46-80fe-33f7a22e1c62</t>
+  </si>
+  <si>
+    <t>relationship--cc29b464-6b26-4da3-8915-73f02e530701</t>
+  </si>
+  <si>
+    <t>relationship--f1a8948f-16ab-451c-acc1-3238d76022c1</t>
+  </si>
+  <si>
+    <t>relationship--6fda1ee2-0726-4007-b48a-1945a93298c2</t>
+  </si>
+  <si>
+    <t>relationship--fb5eb070-ce49-4baf-8088-567ec8758a73</t>
+  </si>
+  <si>
+    <t>relationship--c33588fa-3c04-41d7-880f-4d5ba3a62257</t>
+  </si>
+  <si>
+    <t>relationship--1b293662-380b-49c4-a5cf-82d5b88fb365</t>
+  </si>
+  <si>
+    <t>relationship--c356e43d-81d8-422a-a923-9440186d5da8</t>
+  </si>
+  <si>
+    <t>relationship--f7088fba-e1b9-40e8-80ab-74732a0142b7</t>
+  </si>
+  <si>
+    <t>relationship--784277fe-fbd4-4804-b281-b35b465246f2</t>
+  </si>
+  <si>
+    <t>relationship--6b0db16c-fe90-433b-9d21-1873f4107b5e</t>
+  </si>
+  <si>
+    <t>relationship--78496c31-9c7b-41f9-885d-a11935a3c801</t>
+  </si>
+  <si>
+    <t>relationship--f1dcf389-f9cb-4c56-933a-254856a5c22c</t>
+  </si>
+  <si>
+    <t>relationship--810487dc-e56a-4f46-9916-38ebc608b03f</t>
+  </si>
+  <si>
+    <t>relationship--f3376006-b855-4134-9112-259ce1e4f288</t>
+  </si>
+  <si>
+    <t>relationship--90dcc9ee-f45d-4ea8-8061-e9f01669e772</t>
+  </si>
+  <si>
+    <t>relationship--82c5ad2b-327a-48d2-9a27-6698ca60d175</t>
+  </si>
+  <si>
+    <t>relationship--43f6f3e4-1036-4136-a44f-ad84b138390e</t>
+  </si>
+  <si>
+    <t>relationship--08322f90-a8fc-426c-85d9-787500a60d63</t>
+  </si>
+  <si>
+    <t>relationship--f1cb7b2d-0e2f-4563-8b20-e4664fcc34bb</t>
+  </si>
+  <si>
+    <t>relationship--fbe68433-0c9f-4840-94e3-d5dcd921bb10</t>
+  </si>
+  <si>
+    <t>relationship--ed94bec6-c33a-4161-8f91-bcf071c6eb46</t>
+  </si>
+  <si>
+    <t>relationship--2acd4183-f1fe-48a6-8591-b5be8c2c1488</t>
+  </si>
+  <si>
+    <t>relationship--46db6129-0cf5-41c0-b746-870a9da6c6ca</t>
+  </si>
+  <si>
+    <t>relationship--bb438ef2-f8aa-459b-92e7-15f651028dc5</t>
+  </si>
+  <si>
+    <t>relationship--8dc26f58-662b-4697-a121-4f14c80f0be0</t>
+  </si>
+  <si>
+    <t>relationship--43158157-4152-4ba8-8e5e-fa2fe3e48843</t>
+  </si>
+  <si>
+    <t>relationship--4e006450-1794-40a0-b790-0426bf3f4f6e</t>
+  </si>
+  <si>
+    <t>relationship--20b2cbd3-7083-47d5-a549-7b97aa39bd94</t>
+  </si>
+  <si>
+    <t>relationship--0fb09034-a316-4985-a7be-a8b1b6f9f165</t>
+  </si>
+  <si>
+    <t>relationship--3635be6e-c8e2-40e3-a500-2c53ae904742</t>
+  </si>
+  <si>
+    <t>relationship--2339f969-9e4a-48cd-b14d-299aa821a93f</t>
+  </si>
+  <si>
+    <t>relationship--6bc3b7e8-4234-4413-ae0e-93fad72efc1b</t>
+  </si>
+  <si>
+    <t>relationship--474974cd-7096-4155-836a-3372bb9adef3</t>
+  </si>
+  <si>
+    <t>relationship--23a630c9-f4cf-4ce9-8e27-bf98c563755c</t>
+  </si>
+  <si>
+    <t>relationship--dcaa3cde-6bee-492b-97c8-93219168c428</t>
+  </si>
+  <si>
+    <t>relationship--fef63a3e-9e07-446a-8024-4189414ee178</t>
+  </si>
+  <si>
+    <t>relationship--fab72703-5abc-424a-a91c-600f9eeec639</t>
+  </si>
+  <si>
+    <t>relationship--8c9a605b-d389-4590-9f50-126b1476878b</t>
+  </si>
+  <si>
+    <t>relationship--05993f87-bf71-48b7-843d-65a2839b8038</t>
+  </si>
+  <si>
+    <t>relationship--340d16ba-6b7f-4fde-951a-0fb9bad84f14</t>
+  </si>
+  <si>
+    <t>relationship--f77f3771-804e-45c0-80f4-aa0ba8e33152</t>
+  </si>
+  <si>
+    <t>relationship--d494703e-bdbd-4f63-9e09-a860b0d04a45</t>
+  </si>
+  <si>
+    <t>relationship--f091b18f-7bbd-436d-b795-9853f63d2c06</t>
+  </si>
+  <si>
+    <t>relationship--113a4168-01dc-4c6c-b534-60e9b6103f40</t>
+  </si>
+  <si>
+    <t>relationship--56736bee-e40d-49ea-b8e4-8d28f52e7019</t>
+  </si>
+  <si>
+    <t>relationship--a95adb07-cba8-4748-a590-4fa4597cc2e0</t>
+  </si>
+  <si>
+    <t>relationship--5165809e-c747-4c3e-b8b5-187ebb59a4e1</t>
+  </si>
+  <si>
+    <t>relationship--fa984c1e-b337-45d2-9f9a-35d3da33bb84</t>
+  </si>
+  <si>
+    <t>relationship--6bd93943-6fb5-4944-b871-3cb306b0d8f5</t>
+  </si>
+  <si>
+    <t>relationship--f37ac11b-8ba3-4ed7-ab5c-779ab658ac71</t>
+  </si>
+  <si>
+    <t>relationship--234a532e-ce20-42ae-a7d3-b9ff7d26f67e</t>
+  </si>
+  <si>
+    <t>relationship--199c76ae-e3bb-43f0-80bf-cbcc8a279774</t>
+  </si>
+  <si>
+    <t>relationship--080f2018-4093-4255-8e61-fd187c804ddc</t>
+  </si>
+  <si>
+    <t>relationship--94abd5d6-363e-4bcb-b2ba-086a4e0efd34</t>
+  </si>
+  <si>
+    <t>relationship--d9a22fc3-bce5-46e7-bf71-d6a9dc72096e</t>
+  </si>
+  <si>
+    <t>relationship--634aecb6-4c9e-411c-85fc-65a86519645e</t>
+  </si>
+  <si>
+    <t>relationship--7a66b59e-63b3-44e3-8ab7-30fb93e70030</t>
+  </si>
+  <si>
+    <t>relationship--82b33b34-5a06-4928-bd23-5bc7b7877f2c</t>
+  </si>
+  <si>
+    <t>relationship--93ecb16d-3498-42b1-b96f-5b2f99e0066d</t>
+  </si>
+  <si>
+    <t>relationship--4d1bdeb5-c434-407b-9ec3-545b82703cdb</t>
+  </si>
+  <si>
+    <t>relationship--a6589388-5be1-469d-8283-ba853387ec2d</t>
+  </si>
+  <si>
+    <t>relationship--7d27df0e-2a93-48f7-8d2b-0779279990e7</t>
+  </si>
+  <si>
+    <t>relationship--aebeed5c-1b6f-4ddd-b270-80ed5a8fe855</t>
+  </si>
+  <si>
+    <t>relationship--858b9702-4376-47fe-8a89-25ef646ca9ec</t>
+  </si>
+  <si>
+    <t>relationship--33f740b8-88b6-479e-925a-1427d3974c96</t>
+  </si>
+  <si>
+    <t>relationship--aaf29cd8-ec5a-4f55-aae4-c4058fbad0b1</t>
+  </si>
+  <si>
+    <t>relationship--928ce81b-cdb4-4a64-b856-596f0237f31a</t>
+  </si>
+  <si>
+    <t>relationship--d511b6f2-e2bd-45c2-aa81-fab304c95498</t>
+  </si>
+  <si>
+    <t>relationship--c506a666-6acd-4ed3-8446-d208a9994676</t>
+  </si>
+  <si>
+    <t>relationship--5629044e-11ea-43ce-b553-d53ba7ceebfc</t>
+  </si>
+  <si>
+    <t>relationship--63209b40-aefd-465e-bb8c-292a6db66960</t>
+  </si>
+  <si>
+    <t>relationship--8f341786-757e-478b-8d08-c03f32a9dad6</t>
+  </si>
+  <si>
+    <t>relationship--78410111-368b-4bde-a7dc-75f718d0feac</t>
+  </si>
+  <si>
+    <t>relationship--19726ca7-9360-4b05-9bda-1597046cad49</t>
+  </si>
+  <si>
+    <t>relationship--bb009c88-365d-4fab-bf01-19c7661e62af</t>
+  </si>
+  <si>
+    <t>relationship--77b46dc8-4a63-44dd-9bd7-031969ec253c</t>
+  </si>
+  <si>
+    <t>relationship--5bde57b1-9715-42f1-b049-e06f015a1772</t>
+  </si>
+  <si>
+    <t>relationship--a14a9035-fa57-4d41-89f7-891ac9fcf81f</t>
+  </si>
+  <si>
+    <t>relationship--1c1b685c-3181-4352-b249-432542879ed6</t>
+  </si>
+  <si>
+    <t>relationship--475161f8-6686-424b-9917-db6889a0fcf3</t>
+  </si>
+  <si>
+    <t>relationship--13ac5123-1a57-4b3a-8d5a-662c89bf41a2</t>
+  </si>
+  <si>
+    <t>relationship--f5209d1a-7895-4020-acae-5dc4e5d8bfc0</t>
+  </si>
+  <si>
+    <t>relationship--5ee5526e-96eb-41af-b8b8-c90b91e64049</t>
+  </si>
+  <si>
+    <t>relationship--3be37c13-b9bc-47bb-8653-fa401dabd4e7</t>
+  </si>
+  <si>
+    <t>relationship--b0c2c062-c89e-4085-8716-bad67e98026e</t>
+  </si>
+  <si>
+    <t>relationship--31fd82da-dfa8-42b5-95dd-f168e6627746</t>
+  </si>
+  <si>
+    <t>relationship--2c5e4520-1275-4ab3-a9a8-2e2b1e964c13</t>
+  </si>
+  <si>
+    <t>relationship--b55647cc-a783-4225-b64b-618bc0c73e2b</t>
+  </si>
+  <si>
+    <t>relationship--6014c6c0-0579-4b5e-a854-2e87b36442cf</t>
+  </si>
+  <si>
+    <t>relationship--9c8d906b-4588-4163-b779-c3b8321985df</t>
+  </si>
+  <si>
+    <t>relationship--1419cb9b-276d-4b72-a3f1-6788f5712c97</t>
+  </si>
+  <si>
+    <t>relationship--a0a599d6-96f3-46a9-8021-f95ca90c5c60</t>
+  </si>
+  <si>
+    <t>relationship--422caa87-ac34-4167-80a3-e3f294b52304</t>
+  </si>
+  <si>
+    <t>relationship--d95d1848-9eb8-41a1-9eb4-0dab6d9b048c</t>
+  </si>
+  <si>
+    <t>relationship--c8ddd7ea-ed8e-4c46-8d00-0188061a5430</t>
+  </si>
+  <si>
+    <t>relationship--b4237490-0e8a-46d4-95a6-1cdaa172bcc8</t>
+  </si>
+  <si>
+    <t>relationship--6d106e24-cb8f-42ae-8ea2-c24c3ac66a5e</t>
+  </si>
+  <si>
+    <t>relationship--d3e614da-a65e-49a8-b28c-1bda5c4ff9ad</t>
+  </si>
+  <si>
+    <t>relationship--673fe51c-7945-423e-9767-3b824d79a43f</t>
+  </si>
+  <si>
+    <t>relationship--b4b464b3-2e82-48ba-b3e5-8680a6803204</t>
+  </si>
+  <si>
+    <t>relationship--ec2419f7-91b8-4498-b50c-0deec7e9eed4</t>
+  </si>
+  <si>
+    <t>relationship--62fc2c5e-3c4f-4760-ba3a-320af5a52635</t>
+  </si>
+  <si>
+    <t>relationship--5c3c5267-b7aa-47e8-a640-d413fe3d0e2b</t>
+  </si>
+  <si>
+    <t>relationship--559bac5f-e601-4430-a4d1-3e40065ec036</t>
+  </si>
+  <si>
+    <t>relationship--aaed89ae-ca29-4a00-9e21-1cc9143a649e</t>
+  </si>
+  <si>
+    <t>relationship--acd4d015-7a92-4a60-8741-9e316340e075</t>
+  </si>
+  <si>
+    <t>relationship--3d963d7d-a454-4e0a-9940-35584a671824</t>
+  </si>
+  <si>
+    <t>relationship--e1c4bbc4-90c4-48de-8589-c0a639fef400</t>
+  </si>
+  <si>
+    <t>relationship--14ff5c13-bd58-4f3e-8847-116ab3781971</t>
+  </si>
+  <si>
+    <t>relationship--b8a1efd8-c26a-40b5-aee5-821ce44b4e16</t>
+  </si>
+  <si>
+    <t>relationship--8b9ecf43-5f5e-4e27-b61d-4fceafa47b81</t>
+  </si>
+  <si>
+    <t>relationship--2280f18d-76c9-4ede-885e-1f9f023d5edf</t>
+  </si>
+  <si>
+    <t>relationship--8b5ce05d-0dc5-44bb-a980-427c816728fd</t>
+  </si>
+  <si>
+    <t>relationship--84a726d6-aa58-4936-b16d-e720c1b9a864</t>
+  </si>
+  <si>
+    <t>relationship--f1d4c82a-9578-4e69-8a56-31829df9fbe5</t>
+  </si>
+  <si>
+    <t>relationship--b04fb82c-ac5f-488a-8dcd-fee6bb377ac3</t>
+  </si>
+  <si>
+    <t>relationship--21ab8f08-5ff9-4e53-8833-b03519bd6cd1</t>
+  </si>
+  <si>
+    <t>relationship--c86a5336-5315-4098-aa83-cd2f97e64823</t>
+  </si>
+  <si>
+    <t>relationship--803320d8-15ba-4348-8c32-bccf3db9f530</t>
+  </si>
+  <si>
+    <t>relationship--b413164f-24a7-4fc4-8ea9-138b0044ce12</t>
+  </si>
+  <si>
+    <t>relationship--f5b536e6-69d1-4bbe-83d9-1ba923dfcb36</t>
+  </si>
+  <si>
+    <t>relationship--7039355e-000e-46d0-8e30-1f7d9dfb4f5e</t>
+  </si>
+  <si>
+    <t>relationship--0efafd8f-ad20-4211-94bd-b94e514a4f77</t>
+  </si>
+  <si>
+    <t>relationship--95b25427-2e1f-495c-a35f-4da450c13301</t>
+  </si>
+  <si>
+    <t>relationship--a6e2c789-2ec6-48f4-bdef-117bd254f13a</t>
+  </si>
+  <si>
+    <t>relationship--af609251-5be4-4f65-90c8-fb3cc9a3dbb4</t>
+  </si>
+  <si>
+    <t>relationship--5cd48454-813b-4331-9c08-66ab490f7c61</t>
+  </si>
+  <si>
+    <t>relationship--0c4c43ea-624a-44d5-ba8b-7758a90422b9</t>
+  </si>
+  <si>
+    <t>relationship--9cf98d26-dcde-4e15-9b77-f531dfaaa42c</t>
+  </si>
+  <si>
+    <t>relationship--d62fcf47-1ed7-4e8e-89ae-ae2b35893e89</t>
+  </si>
+  <si>
+    <t>relationship--a3a14ae4-5efd-4ab9-95b0-7fe445ebaba9</t>
+  </si>
+  <si>
+    <t>relationship--02467645-18f1-44b3-9807-2febf2484815</t>
+  </si>
+  <si>
+    <t>relationship--bf8dd70b-311f-4582-b644-bef5c2fb33b6</t>
+  </si>
+  <si>
+    <t>relationship--dd9311f1-d090-402e-95ba-563ab46c7d70</t>
+  </si>
+  <si>
+    <t>relationship--f2d6a2cf-89d4-471d-954f-85ebca68df09</t>
+  </si>
+  <si>
+    <t>relationship--16305f31-01fb-4769-adda-fb68bdb5bdf5</t>
+  </si>
+  <si>
+    <t>relationship--f2506c16-b956-47b5-8994-61403315d62f</t>
+  </si>
+  <si>
+    <t>relationship--287fce25-2f71-4417-86e4-73d207d621d4</t>
+  </si>
+  <si>
+    <t>relationship--0cd1d9f5-1b62-4894-9c7a-887333274daa</t>
+  </si>
+  <si>
+    <t>relationship--bcfcbe09-5315-4558-a202-b0c3549f574c</t>
+  </si>
+  <si>
+    <t>relationship--72c5aa19-3333-497c-bc10-22276193dbe0</t>
+  </si>
+  <si>
+    <t>relationship--15c9a760-9071-47c3-8b86-207c651c3f9d</t>
+  </si>
+  <si>
+    <t>relationship--4834d7b9-4aad-4db8-b067-793cae286279</t>
+  </si>
+  <si>
+    <t>relationship--fc84144f-1d31-45d5-a091-7122aeffdb3a</t>
+  </si>
+  <si>
+    <t>relationship--ab5fb347-4be5-47d7-ac92-a21f54383f24</t>
+  </si>
+  <si>
+    <t>relationship--2fa33b37-bbe4-4bd4-8235-b137f4579659</t>
+  </si>
+  <si>
+    <t>relationship--c2dc6232-da70-47d5-8e03-23c22d15201e</t>
+  </si>
+  <si>
+    <t>relationship--69b5a3eb-88ee-4898-b5eb-bf99882e755a</t>
+  </si>
+  <si>
+    <t>relationship--8f834fe2-1ea9-4f4e-904e-03480b71fc0c</t>
+  </si>
+  <si>
+    <t>relationship--4c910602-8a1f-4a1b-ae96-78ff77141c32</t>
+  </si>
+  <si>
+    <t>relationship--bb2fb6c6-2082-4128-9aa2-6fd397d4b077</t>
+  </si>
+  <si>
+    <t>relationship--6217bbde-7bd4-4ff9-8084-1bb50aa35f0a</t>
+  </si>
+  <si>
+    <t>relationship--ae394320-962d-4311-a23d-f02679fc432f</t>
+  </si>
+  <si>
+    <t>relationship--5e9166c6-f3f3-4067-b9fb-81ac58ccea57</t>
+  </si>
+  <si>
+    <t>relationship--a77f7b5f-7b61-4700-8fda-341ffc586aa3</t>
+  </si>
+  <si>
+    <t>relationship--17249a22-d960-4c98-bd73-2176cff9a66d</t>
+  </si>
+  <si>
+    <t>relationship--2a6b25b3-2106-4cc5-9daf-69080545023a</t>
+  </si>
+  <si>
+    <t>relationship--7b1b9159-5728-4caa-b025-e233988eed18</t>
+  </si>
+  <si>
+    <t>relationship--bc9dae11-ee8d-437a-a5f2-151aad2a22b9</t>
+  </si>
+  <si>
+    <t>relationship--957f013b-288a-43a5-9b47-0b8ae24ecf5a</t>
+  </si>
+  <si>
+    <t>relationship--aa2e1b37-5b37-49f7-aa1b-6ae619b5c0f4</t>
+  </si>
+  <si>
+    <t>relationship--3f22a8b4-118a-4f55-9a26-b1ba62fa35b2</t>
+  </si>
+  <si>
+    <t>relationship--bcddaa91-a8a1-47ba-885d-b9525a1001aa</t>
+  </si>
+  <si>
+    <t>relationship--ef01b363-58f1-4d39-83d0-99ac81ffc65b</t>
+  </si>
+  <si>
+    <t>relationship--5e7fd20e-84e5-4350-b635-8cbfe36923cb</t>
+  </si>
+  <si>
+    <t>relationship--68d4e642-f528-4420-abae-afc75e93414f</t>
+  </si>
+  <si>
+    <t>relationship--aafb6322-5c65-4a69-831f-ce7c553efb7a</t>
+  </si>
+  <si>
+    <t>relationship--d5f27e9e-a55f-43aa-9040-20018524f869</t>
+  </si>
+  <si>
+    <t>relationship--3f9d7bd8-83c9-4fd9-9aa4-3b54a80bdb79</t>
+  </si>
+  <si>
+    <t>relationship--ec6b5a74-c9d6-4d5d-851d-4340a2c1e77a</t>
+  </si>
+  <si>
+    <t>relationship--1bd2d7ca-6d0d-45b7-aa5c-92d1af9ab047</t>
+  </si>
+  <si>
+    <t>relationship--1788c4e6-bd1e-42f4-bc4c-53a28ea72247</t>
+  </si>
+  <si>
+    <t>relationship--d1bd8bf5-4e79-47ca-bcd8-cb3ceed828ed</t>
+  </si>
+  <si>
+    <t>relationship--9707a4a3-85fc-4326-b941-6e3f4ba3d66e</t>
+  </si>
+  <si>
+    <t>relationship--ce616361-b9c6-41d7-9fa1-c6800c8569b7</t>
+  </si>
+  <si>
+    <t>relationship--c16c1d51-00c9-42e2-a472-267146714a16</t>
+  </si>
+  <si>
+    <t>relationship--8be9daf3-3283-4014-bb07-58b184b74d93</t>
+  </si>
+  <si>
+    <t>relationship--1e810079-efd1-4437-8550-e46be0afa71e</t>
+  </si>
+  <si>
+    <t>relationship--23db1a49-8cfc-4e88-baa9-6cdc44a115a2</t>
+  </si>
+  <si>
+    <t>relationship--cd711de5-eeb1-4125-b828-3b8a8f1b07f3</t>
+  </si>
+  <si>
+    <t>relationship--349ef81a-2f99-4a9c-9c81-e57f79f07d82</t>
+  </si>
+  <si>
+    <t>relationship--60c11da2-7800-43b7-8d1f-76c8aa05a5c9</t>
+  </si>
+  <si>
+    <t>relationship--98c02793-243e-4135-9a39-882178ad8a96</t>
+  </si>
+  <si>
+    <t>relationship--55ff4a91-8661-475f-8ad7-0f09f83c5e85</t>
+  </si>
+  <si>
+    <t>relationship--f198baec-e5e1-4737-8a14-de81017b8eea</t>
+  </si>
+  <si>
+    <t>relationship--d6938961-a091-45b1-bffc-87c242cf25a2</t>
+  </si>
+  <si>
+    <t>relationship--4cfdc688-c4fc-4bb4-a16d-fe39a1f133f7</t>
+  </si>
+  <si>
+    <t>relationship--4c8204a0-a1be-45e1-86b8-3f4cdd438ce7</t>
+  </si>
+  <si>
+    <t>relationship--7b3c83f1-d4d5-48b3-aadf-dceaea68b4ed</t>
+  </si>
+  <si>
+    <t>relationship--d9e0502c-e40e-4515-8c12-b3097dc7475a</t>
+  </si>
+  <si>
+    <t>relationship--33335b1d-f384-436a-9b2f-6977401616dd</t>
+  </si>
+  <si>
+    <t>relationship--563da1b2-2363-4bca-a36f-9427fbb0eeb1</t>
+  </si>
+  <si>
+    <t>relationship--d513bfcd-ce05-438e-ae32-b2aa913d07c8</t>
+  </si>
+  <si>
+    <t>relationship--26a2ccda-f08b-4248-a25b-0e55035acef5</t>
+  </si>
+  <si>
+    <t>relationship--74fd0492-7a79-4dda-8c2d-24e17c4bdab3</t>
+  </si>
+  <si>
+    <t>relationship--c249bddd-af15-4cad-90ed-82cdbeb66aa8</t>
+  </si>
+  <si>
+    <t>relationship--a73dab7a-cba3-4295-9a68-163953884ba6</t>
+  </si>
+  <si>
+    <t>relationship--43501e8a-b825-42ec-b6ec-e295e5cc2e08</t>
+  </si>
+  <si>
+    <t>relationship--bcbf16b1-48cf-4bc1-bb2f-5c361772e1f1</t>
+  </si>
+  <si>
+    <t>relationship--42d0b716-8699-4628-a8d2-d043f5334d2f</t>
+  </si>
+  <si>
+    <t>relationship--e91bf280-5cb2-4f22-973d-ca790c6a9765</t>
+  </si>
+  <si>
+    <t>relationship--1a85808f-513b-446c-8752-4b2ec5da5ee5</t>
+  </si>
+  <si>
+    <t>relationship--b89f2f86-e815-40bd-a82f-3bb6a732125d</t>
+  </si>
+  <si>
+    <t>relationship--fe71a8b2-0517-4fd7-bfec-9e1cd4b701c0</t>
+  </si>
+  <si>
+    <t>relationship--c0561e87-1c03-480c-86ee-6e8e79673848</t>
+  </si>
+  <si>
+    <t>relationship--3542d62b-9969-4f15-87ec-f94b5e6b4405</t>
+  </si>
+  <si>
+    <t>relationship--d217853a-a549-41ec-b95b-00caca3410b2</t>
+  </si>
+  <si>
+    <t>relationship--a2bab682-f3ac-4992-a542-5cecc03e0074</t>
+  </si>
+  <si>
+    <t>relationship--431f4e5a-5596-4a39-b84d-cd1f38d861b3</t>
+  </si>
+  <si>
+    <t>relationship--48ffcfbb-741a-478a-baa6-a36149793de8</t>
+  </si>
+  <si>
+    <t>relationship--827e00b3-a532-4a87-82e5-77f4de601e05</t>
+  </si>
+  <si>
+    <t>relationship--65222228-0b79-420f-a997-9c20f99ecaa4</t>
+  </si>
+  <si>
+    <t>relationship--231fa5f0-a19b-44f4-bc6f-dfa148cc8679</t>
+  </si>
+  <si>
+    <t>relationship--01861179-0186-4305-a71f-27f5e670b04f</t>
+  </si>
+  <si>
+    <t>relationship--5324471d-3a9d-4dcd-989c-0d95bd2d23e9</t>
+  </si>
+  <si>
+    <t>relationship--137d4968-3b9a-4eac-845b-ba164af2867e</t>
+  </si>
+  <si>
+    <t>relationship--5f10c7ac-d87d-4407-add7-7166679dd1f5</t>
+  </si>
+  <si>
+    <t>relationship--e7163b63-492c-4886-9dc2-6e859aa6d034</t>
+  </si>
+  <si>
+    <t>relationship--fc01a550-6494-40e0-8c0d-5c380763303b</t>
+  </si>
+  <si>
+    <t>relationship--822f19d2-5f87-4880-afbe-f1a2b98a3dbf</t>
+  </si>
+  <si>
+    <t>relationship--93fa1b38-db1c-4c2c-aac4-835e21431a8b</t>
+  </si>
+  <si>
+    <t>relationship--9d405089-6db2-4242-9be1-901cd852b765</t>
+  </si>
+  <si>
+    <t>relationship--391c1305-e015-4bd7-bb03-22bfba33c82b</t>
+  </si>
+  <si>
+    <t>relationship--4a68d93b-f1da-4a51-812b-5bf2f0c60a7b</t>
+  </si>
+  <si>
+    <t>relationship--7a210575-716a-406f-9d8e-172a2dbba802</t>
+  </si>
+  <si>
+    <t>relationship--e8029807-08ca-48d9-8572-6a38d99bd2c2</t>
+  </si>
+  <si>
+    <t>relationship--1e9b5938-8fed-4bc2-8d92-9525edd34e24</t>
+  </si>
+  <si>
+    <t>relationship--5268dc98-c56e-46a9-9bef-63cf230d237b</t>
+  </si>
+  <si>
+    <t>relationship--5ea6892d-4b0d-4cbd-8020-6aed168df5a4</t>
+  </si>
+  <si>
+    <t>relationship--55780959-01ec-4069-844d-6df18f57da1f</t>
+  </si>
+  <si>
+    <t>relationship--c46122a2-0e53-4c4b-8b0c-21bfd5940873</t>
+  </si>
+  <si>
+    <t>relationship--6e256514-03e4-45c9-b522-525f27ce759d</t>
+  </si>
+  <si>
+    <t>relationship--87de8c02-0bc1-4b2a-b3a5-facabf410a9b</t>
+  </si>
+  <si>
+    <t>relationship--cfa25437-a45c-4215-891f-c88fb1c6854e</t>
+  </si>
+  <si>
+    <t>relationship--7672e7ae-da3c-4880-9317-481e88285ca7</t>
+  </si>
+  <si>
+    <t>relationship--8c84f972-8d80-4970-b47e-a43e07b700a3</t>
+  </si>
+  <si>
+    <t>relationship--ae23fbce-cefd-4b11-81e8-a74bed5bef7b</t>
+  </si>
+  <si>
+    <t>relationship--f2d91af3-aff9-4b74-a087-c4e8554811b8</t>
+  </si>
+  <si>
+    <t>relationship--eff280bc-ca08-449f-a941-43ea0f060726</t>
+  </si>
+  <si>
+    <t>relationship--c56e03d1-3287-4cde-95c6-23146e302c3e</t>
+  </si>
+  <si>
+    <t>relationship--c6a6164a-b374-493d-a404-68d7cfe61825</t>
+  </si>
+  <si>
+    <t>relationship--ad667537-8c1d-4601-8f6f-4b65f4440940</t>
+  </si>
+  <si>
+    <t>relationship--0071f400-1c99-437b-a1f1-e6433c057f6f</t>
+  </si>
+  <si>
+    <t>relationship--41366efa-5b40-4d9c-a10f-da330d4c22a0</t>
+  </si>
+  <si>
+    <t>relationship--ba8dc7cc-a4a7-495c-9492-90f49e8d1153</t>
+  </si>
+  <si>
+    <t>relationship--2f06cb0c-dcb4-4cd6-bb11-95526ecd709b</t>
+  </si>
+  <si>
+    <t>relationship--43bfb130-3a03-4742-885d-1a4958c7189b</t>
+  </si>
+  <si>
+    <t>relationship--a01766a1-519b-4338-8c88-0c0e2b937dd3</t>
+  </si>
+  <si>
+    <t>relationship--43545b6d-7cb5-463e-a53d-6528245de722</t>
+  </si>
+  <si>
+    <t>relationship--3ff9678f-3704-4082-a10b-9615cb64ce97</t>
+  </si>
+  <si>
+    <t>relationship--23f4ec20-2a56-48e3-9436-dc947eb85662</t>
+  </si>
+  <si>
+    <t>relationship--26d110af-bfc4-46bd-89a6-b25ec0077a25</t>
+  </si>
+  <si>
+    <t>relationship--749eab61-1c86-4133-8036-76b4667d387a</t>
+  </si>
+  <si>
+    <t>relationship--604c0228-a8aa-45ca-b3d9-009780cd0c93</t>
+  </si>
+  <si>
+    <t>relationship--b5f73c4d-eb9d-4ccc-8058-9891de23f8e6</t>
+  </si>
+  <si>
+    <t>relationship--82c4b68f-c4a9-4899-862a-20954adc01a3</t>
+  </si>
+  <si>
+    <t>relationship--5955053a-b87b-4b43-a152-f15bd6d5c523</t>
+  </si>
+  <si>
+    <t>relationship--2893c79c-adb3-4d67-a698-f859a0bbca0f</t>
+  </si>
+  <si>
+    <t>relationship--e5e199d4-6538-431c-94a2-85eabd8a9920</t>
+  </si>
+  <si>
+    <t>relationship--e1378deb-56c4-46c7-bf35-bcf7ab3a9ce2</t>
+  </si>
+  <si>
+    <t>relationship--9d5634ce-16b9-4d9b-a3d5-45a02d743968</t>
+  </si>
+  <si>
+    <t>relationship--c84a3b83-e414-4a18-b5ab-21d88156b13b</t>
+  </si>
+  <si>
+    <t>relationship--9a4aca14-a9a7-4761-90c4-a315313fa85f</t>
+  </si>
+  <si>
+    <t>relationship--07722c0c-5fc9-4dd0-86fd-06f3bdefc0b1</t>
+  </si>
+  <si>
+    <t>relationship--25b395e7-6c6b-43f4-a5ce-1a7c43a4c4a5</t>
+  </si>
+  <si>
+    <t>relationship--e8603dba-be2c-4d39-a158-05a34a8b2248</t>
+  </si>
+  <si>
+    <t>relationship--9f66288a-6101-45f1-a2e9-b6055dc72b7d</t>
+  </si>
+  <si>
+    <t>relationship--c6689428-236d-4e35-8f40-97343e6b4e4c</t>
+  </si>
+  <si>
+    <t>relationship--a7a247e1-e55c-4946-a6fe-8e89fff30460</t>
+  </si>
+  <si>
+    <t>relationship--bbd6f1fb-1697-4bf7-94eb-9bf778bd21fa</t>
+  </si>
+  <si>
+    <t>relationship--673687e5-33e3-4e10-853a-039ec9bbba0f</t>
+  </si>
+  <si>
+    <t>relationship--d8a80fd2-e649-403f-891a-f81e07386728</t>
+  </si>
+  <si>
+    <t>relationship--a182d298-ac49-4812-83d9-7c918bfdcff8</t>
+  </si>
+  <si>
+    <t>relationship--4e3d4cda-bc26-4e9a-944b-efcfa6e7dc78</t>
+  </si>
+  <si>
+    <t>relationship--89b24472-ef28-47d1-a136-9f156a129bf5</t>
+  </si>
+  <si>
+    <t>relationship--97230a5b-b9e5-4e98-a279-1afb93b1beeb</t>
+  </si>
+  <si>
+    <t>relationship--21b7fe4a-162a-4209-98d4-d360f5c94290</t>
+  </si>
+  <si>
+    <t>relationship--a03544ee-5257-4bc5-9f3d-941053278b0d</t>
+  </si>
+  <si>
+    <t>relationship--055c5491-8ec1-46ed-89bf-d00d10057a44</t>
+  </si>
+  <si>
+    <t>relationship--beff9c5d-311e-4dc5-810a-2898c3d5ef95</t>
+  </si>
+  <si>
+    <t>relationship--eb7f7d87-f0d9-415c-9d85-ec9d6995e371</t>
+  </si>
+  <si>
+    <t>relationship--d11d5a60-b488-4beb-b1e1-6cfeee9b512d</t>
+  </si>
+  <si>
+    <t>relationship--27449a60-290d-4640-9c7c-a4a87cb036d2</t>
+  </si>
+  <si>
+    <t>relationship--e4e82c07-b0d0-4fa0-b0ff-71a24ce8c031</t>
+  </si>
+  <si>
+    <t>relationship--f08aff09-5868-4f68-9056-fde79b6714e0</t>
+  </si>
+  <si>
+    <t>relationship--0eb3e9f8-ed56-49f9-961f-45b74f24d6b6</t>
+  </si>
+  <si>
+    <t>relationship--fe1ed08d-9a16-46e1-a211-946d17efabca</t>
+  </si>
+  <si>
+    <t>relationship--fddd4820-b3a3-42ab-8143-76a8a24e1e54</t>
+  </si>
+  <si>
+    <t>relationship--ad21a81f-9db2-419a-add3-717c177a80cb</t>
+  </si>
+  <si>
+    <t>relationship--3ccacaaf-c9c6-4bcf-8000-0f6f62ffe3a1</t>
+  </si>
+  <si>
+    <t>relationship--04df6efb-a4cd-4802-b309-fc2a7d94bdfa</t>
+  </si>
+  <si>
+    <t>relationship--52ba97a8-e66d-44a9-8e11-62a829dbb246</t>
+  </si>
+  <si>
+    <t>relationship--44b4500d-0d89-47da-aaed-e949cee74c3b</t>
+  </si>
+  <si>
+    <t>relationship--62164b6b-d164-41e7-9481-6223553cf173</t>
+  </si>
+  <si>
+    <t>relationship--50cd576b-7652-4699-b71f-0e4aa10e7538</t>
+  </si>
+  <si>
+    <t>relationship--858ee4ec-8c2e-4d81-a63a-6caaa3b1724e</t>
+  </si>
+  <si>
+    <t>relationship--956b8623-ce91-4d57-ab87-e214dcd8d1e6</t>
+  </si>
+  <si>
+    <t>relationship--0fc9df02-2663-4be2-ae57-b47e321d5c5b</t>
+  </si>
+  <si>
+    <t>relationship--e5b4df88-6b23-491f-b483-8551a0ea2bf0</t>
+  </si>
+  <si>
+    <t>relationship--0644e98b-0ba5-405e-890c-fb8c222e1439</t>
+  </si>
+  <si>
+    <t>relationship--8ac25ca3-96cf-4c52-a237-b9062e106f74</t>
+  </si>
+  <si>
+    <t>relationship--3e8a36d8-88aa-468c-9c2c-dc6a2763f906</t>
+  </si>
+  <si>
+    <t>relationship--da148c65-5f4a-4a95-87a3-c6b87f8379ea</t>
+  </si>
+  <si>
+    <t>relationship--f701788a-e221-4dd1-9128-95b9a0d023c8</t>
+  </si>
+  <si>
+    <t>relationship--bf4a83fc-a160-498d-b894-772828c88b1c</t>
+  </si>
+  <si>
+    <t>relationship--57bd8188-1eec-4025-b4f3-e7efaef6549b</t>
+  </si>
+  <si>
+    <t>relationship--a936931c-9625-4d84-9987-ca3f67d5fe58</t>
+  </si>
+  <si>
+    <t>relationship--7e8e6538-c636-4e58-9203-c7b1520d6c27</t>
+  </si>
+  <si>
+    <t>relationship--969684f6-68ed-4fd1-bc86-632f849b1bbd</t>
+  </si>
+  <si>
+    <t>relationship--29b789a0-4a47-4569-b028-52c5f6f00ed7</t>
+  </si>
+  <si>
+    <t>relationship--7bb60df4-1c22-4b9b-b8d2-805d486ae9fa</t>
+  </si>
+  <si>
+    <t>relationship--0e2144a3-1971-40e2-9381-96702aa05be4</t>
+  </si>
+  <si>
+    <t>relationship--0e3a834c-4d76-4a14-8f0b-9b01782f7a2a</t>
+  </si>
+  <si>
+    <t>relationship--465f4881-318d-4da2-b4f0-5d289443f6fa</t>
+  </si>
+  <si>
+    <t>relationship--e1b6ebd1-cbe7-4c53-afd3-37030a935932</t>
+  </si>
+  <si>
+    <t>relationship--6cdb2e97-2d6d-4c25-bc19-5a4b3544d232</t>
+  </si>
+  <si>
+    <t>relationship--a4a38ef0-3b9c-45c0-9306-aff86b2387ae</t>
+  </si>
+  <si>
+    <t>relationship--657542f6-b8c1-4a4e-8893-4fe28a4cdee8</t>
+  </si>
+  <si>
+    <t>relationship--6e36c6de-fbf1-4a16-89da-71294bd0dc93</t>
+  </si>
+  <si>
+    <t>relationship--4370f48f-01cd-46ca-97ea-64afdd48aea4</t>
+  </si>
+  <si>
+    <t>relationship--633ed359-9c30-4a9f-a839-395bb299df98</t>
+  </si>
+  <si>
+    <t>relationship--6202b96d-be8b-4dba-b845-af6c1b249723</t>
+  </si>
+  <si>
+    <t>relationship--2b2a351f-b83e-479f-94f1-253242777b55</t>
+  </si>
+  <si>
+    <t>relationship--95c2a5c2-fd4e-4783-8d91-8da9d5d3fbe2</t>
+  </si>
+  <si>
+    <t>relationship--afcffc6b-70fb-4c03-81ca-fef5944088a2</t>
+  </si>
+  <si>
+    <t>relationship--9504d767-5432-4d80-8013-53c83f7c22f1</t>
+  </si>
+  <si>
+    <t>relationship--611edf19-465c-4f5d-85bb-aeefd6e995e2</t>
+  </si>
+  <si>
+    <t>relationship--dff55fe5-c06c-40d4-a686-5a431b3e98d8</t>
+  </si>
+  <si>
+    <t>relationship--d68069d1-821b-4e7a-ad14-ed1c1939ed38</t>
+  </si>
+  <si>
+    <t>relationship--83a81dbd-94b4-4eab-bcb0-44e580bc0fbd</t>
+  </si>
+  <si>
+    <t>relationship--e6ca9bad-b837-485a-8561-fe0c0f67a174</t>
+  </si>
+  <si>
+    <t>relationship--5bd244d1-5516-474b-b6c6-8f6e1751959e</t>
+  </si>
+  <si>
+    <t>relationship--f05c64f4-6a88-49ed-b077-8de036f40556</t>
+  </si>
+  <si>
+    <t>relationship--e0673107-5991-4109-8db8-520134cc2146</t>
+  </si>
+  <si>
+    <t>relationship--97d08a69-727a-4f0e-83b1-063f58e68ba4</t>
+  </si>
+  <si>
+    <t>relationship--6e962e55-cd15-45d1-9203-8e33bd78ab60</t>
+  </si>
+  <si>
+    <t>relationship--405625f8-e751-4bd7-85fa-258ad6f2b68a</t>
+  </si>
+  <si>
+    <t>relationship--9ed83b23-a904-429c-92a6-ce90942689de</t>
+  </si>
+  <si>
+    <t>relationship--bae03c3e-e80f-45db-87ed-892807e2178e</t>
+  </si>
+  <si>
+    <t>relationship--080ed8e8-2c28-4e8b-b6a7-45145ea0128a</t>
+  </si>
+  <si>
+    <t>relationship--8bcd799f-e5b8-4633-b7bd-b2e5f721fea6</t>
+  </si>
+  <si>
+    <t>relationship--8483e736-649f-492e-a9f5-7f4222459993</t>
+  </si>
+  <si>
+    <t>relationship--0bf70881-3dcb-4784-be1a-6291c9c92fc1</t>
+  </si>
+  <si>
+    <t>relationship--53b4c112-a429-43b5-a40a-134a823673af</t>
+  </si>
+  <si>
+    <t>relationship--29686751-4d79-46cf-8a7b-e9837d808aae</t>
+  </si>
+  <si>
+    <t>relationship--aadc9e12-57f1-4c6e-b5c4-a3ef30807211</t>
+  </si>
+  <si>
+    <t>relationship--07d2ef94-6812-42bb-ab5a-43d6355050ca</t>
+  </si>
+  <si>
+    <t>relationship--70e8cecb-6d07-45c3-9b13-019a92a70701</t>
+  </si>
+  <si>
+    <t>relationship--f8216de2-1ed0-4fbe-ad57-d72c52ecccdc</t>
+  </si>
+  <si>
+    <t>relationship--be802805-0e80-4510-88e2-36bd8e2bef66</t>
+  </si>
+  <si>
+    <t>relationship--584c2186-1549-43f8-bf0c-431e2b6b5010</t>
+  </si>
+  <si>
+    <t>relationship--90e4c5e3-7c6d-4e55-8725-d48eca01a678</t>
+  </si>
+  <si>
+    <t>relationship--e9a6f035-155a-4704-9b4f-14b4b61dd8f8</t>
+  </si>
+  <si>
+    <t>relationship--3db8866a-062d-4995-a079-92aa94987cd6</t>
+  </si>
+  <si>
+    <t>relationship--78de6c1b-d105-463b-bd2e-cc387e513a04</t>
+  </si>
+  <si>
+    <t>relationship--85f50e8e-4090-4472-a182-467c3f609cb2</t>
+  </si>
+  <si>
+    <t>relationship--8e9eda91-5e66-416f-bb44-b303c726c86a</t>
+  </si>
+  <si>
+    <t>relationship--8d0c0c6c-a6b7-4773-a0ac-0c6dad8866a1</t>
+  </si>
+  <si>
+    <t>relationship--e72dfa93-e5ae-4efe-a8ff-f7bdacfae145</t>
+  </si>
+  <si>
+    <t>relationship--d5616a46-fabb-4875-861f-d986a816162a</t>
+  </si>
+  <si>
+    <t>relationship--417e33c5-7b63-440a-9e43-94fae2304c40</t>
+  </si>
+  <si>
+    <t>relationship--2b27b61a-ed32-4cb0-b945-db8901d861b9</t>
+  </si>
+  <si>
+    <t>relationship--03bff8b0-2774-4899-a2ae-991c5caccc2f</t>
+  </si>
+  <si>
+    <t>relationship--7032ef5f-c42b-4239-91fc-996ab9c33b83</t>
+  </si>
+  <si>
+    <t>relationship--ced5e698-bb1b-4f5b-a57f-e80fdcb1def1</t>
+  </si>
+  <si>
+    <t>relationship--12b4d92f-9c0a-4b57-b5da-5644f0640104</t>
+  </si>
+  <si>
+    <t>relationship--e33d4ef5-b340-497d-9db7-f723f793d14b</t>
+  </si>
+  <si>
+    <t>relationship--6a71645c-e668-4c35-af1a-068c183f8c81</t>
+  </si>
+  <si>
+    <t>relationship--8dc5252a-2a4a-40b6-9579-2ac103aa6e5e</t>
+  </si>
+  <si>
+    <t>relationship--066972ee-074b-4c3c-992c-eb0950164778</t>
+  </si>
+  <si>
+    <t>relationship--da41731f-9712-4e17-8d67-493d30b959e3</t>
+  </si>
+  <si>
+    <t>relationship--a64f0e5e-e1eb-49c7-8f9f-809fd64cd5ad</t>
+  </si>
+  <si>
+    <t>relationship--19d74513-f877-42bb-a3dd-9cb8e098f7c8</t>
+  </si>
+  <si>
+    <t>relationship--b9cb0d82-e343-4008-89d5-12ac6796966b</t>
+  </si>
+  <si>
+    <t>relationship--8301a987-0a3b-48c4-8ebe-9775eac9700e</t>
+  </si>
+  <si>
+    <t>relationship--6082181d-42e4-4a00-88b9-fb7f05f08650</t>
+  </si>
+  <si>
+    <t>relationship--3ff626c6-8623-4924-9ad8-0cc56833003c</t>
+  </si>
+  <si>
+    <t>relationship--9a131f74-b423-4e60-9bc4-6cce5360b8bc</t>
+  </si>
+  <si>
+    <t>relationship--0e02357c-c07e-47b2-805b-c05265688163</t>
+  </si>
+  <si>
+    <t>relationship--3a8c4403-d83b-4eae-9655-968bea432709</t>
+  </si>
+  <si>
+    <t>relationship--750fef77-11a1-474a-a028-65e894b53482</t>
+  </si>
+  <si>
+    <t>relationship--fff3aef4-c045-41d2-9c1a-1c4960a5b465</t>
+  </si>
+  <si>
+    <t>relationship--7148e04c-a774-454c-8c96-5142c0ee1331</t>
+  </si>
+  <si>
+    <t>relationship--94123636-25d9-4c52-bc8e-fa2b6af78f7d</t>
+  </si>
+  <si>
+    <t>relationship--c96aa7f2-2ff5-45e4-8ce0-993e46b0f7ce</t>
+  </si>
+  <si>
+    <t>relationship--c88dccf7-073f-4b73-95b8-f6c141c2ea88</t>
+  </si>
+  <si>
+    <t>relationship--aa18ba5c-4772-4de6-8df6-97103c857633</t>
+  </si>
+  <si>
+    <t>relationship--ae0d4f48-7ca8-4e86-beb4-2fc5e34613d7</t>
+  </si>
+  <si>
+    <t>relationship--3d65f0d0-9ca6-4c8a-a0f2-a2f32cf3117d</t>
+  </si>
+  <si>
+    <t>relationship--7045ddce-4798-4f62-bbb9-657acf7e895e</t>
+  </si>
+  <si>
+    <t>relationship--3096006d-9acf-4b9c-a667-01cdc7d7c99f</t>
+  </si>
+  <si>
+    <t>relationship--168aae8a-1325-4d12-8e76-912245ef0e79</t>
+  </si>
+  <si>
+    <t>relationship--f0fb29ec-513b-4c24-922f-81bfb4d4e2a2</t>
+  </si>
+  <si>
+    <t>relationship--e2b323f7-fe5f-4725-ba72-f0dd7ba91c5a</t>
+  </si>
+  <si>
+    <t>relationship--2a6b3098-d2b8-4363-8a6b-29f869aaf8c5</t>
+  </si>
+  <si>
+    <t>relationship--9c4bfad0-d523-4ec7-8e70-8cb64f4a9043</t>
+  </si>
+  <si>
+    <t>relationship--59f9d0e9-3202-4c50-8172-f73fe9eb7131</t>
+  </si>
+  <si>
+    <t>relationship--60f81fbf-1bd9-4c2f-b5df-7f6ed6f17c3d</t>
+  </si>
+  <si>
+    <t>relationship--225cefd8-2903-4317-af4f-35fa55e94032</t>
+  </si>
+  <si>
+    <t>relationship--416d1d17-f865-4b1a-8f81-b82260aced75</t>
+  </si>
+  <si>
+    <t>relationship--b67bd861-444f-4f04-a6e1-9b0d1c3c67c4</t>
+  </si>
+  <si>
+    <t>relationship--2a77ae94-5326-4980-ae79-c7e881ae7de5</t>
+  </si>
+  <si>
+    <t>relationship--649413cf-6855-42d3-b7d2-f0a5abf6676f</t>
+  </si>
+  <si>
+    <t>relationship--18106a1c-5855-4d6b-92b8-56905db21203</t>
+  </si>
+  <si>
+    <t>relationship--d2ca5391-f68f-441c-ad33-1dc1f2402e3c</t>
+  </si>
+  <si>
+    <t>relationship--4d34b1a4-fc22-4817-b194-5b0b3dfb0814</t>
+  </si>
+  <si>
+    <t>relationship--9ee851e9-b992-4e8f-9c2b-432ec620e219</t>
+  </si>
+  <si>
+    <t>relationship--b1baa091-4cd0-4638-a837-6a07ad23bcb8</t>
+  </si>
+  <si>
+    <t>relationship--00dfae9d-7870-47fd-98b0-206114ba58d9</t>
+  </si>
+  <si>
+    <t>relationship--f939a8be-2236-4d77-86b5-287b54c7c32a</t>
+  </si>
+  <si>
+    <t>relationship--d676c970-f90d-4397-bf58-c5a03f8bfc59</t>
+  </si>
+  <si>
+    <t>relationship--efc80a10-3b08-4ba7-b038-178817d44f66</t>
+  </si>
+  <si>
+    <t>relationship--6c9b61bd-0b24-4114-84f1-86c2046aa9c6</t>
+  </si>
+  <si>
+    <t>relationship--86626dfd-325d-4c7d-9bf4-e8257116723e</t>
+  </si>
+  <si>
+    <t>relationship--0bd740fe-817a-43ab-80c1-dd570939c124</t>
+  </si>
+  <si>
+    <t>relationship--9107543d-cc94-4c75-8b4d-8e3f49490734</t>
+  </si>
+  <si>
+    <t>relationship--41f7475a-c31b-496c-8375-52b0d70258a0</t>
+  </si>
+  <si>
+    <t>relationship--c5d53690-5de6-4764-93e2-09e1b9744076</t>
+  </si>
+  <si>
+    <t>relationship--8ce2c861-8d58-4ffd-8c50-78c112daa96d</t>
+  </si>
+  <si>
+    <t>relationship--173660ca-1b8b-40c5-89a0-02813361a6fc</t>
+  </si>
+  <si>
+    <t>relationship--d959e6e3-e593-41c2-8f4c-4f95d0a732ce</t>
+  </si>
+  <si>
+    <t>relationship--9a518d2e-0857-40f8-a7f3-b2e1cdc14621</t>
+  </si>
+  <si>
+    <t>relationship--88165274-fe0a-467c-add8-8b7f67b17b80</t>
+  </si>
+  <si>
+    <t>relationship--ba38f840-9a97-4864-b29b-79af50e2d0f0</t>
+  </si>
+  <si>
+    <t>relationship--deca8f6f-dedd-43ec-8a6d-734952d9bd73</t>
+  </si>
+  <si>
+    <t>relationship--bdb96b60-ec68-4ee8-8d96-8d2a78fb7dc0</t>
+  </si>
+  <si>
+    <t>relationship--390041a9-89ff-43f9-aff4-d45d6a485a55</t>
+  </si>
+  <si>
+    <t>relationship--c9af633c-6d9d-4870-b227-32d5ec24cd56</t>
+  </si>
+  <si>
+    <t>relationship--75a13b48-8e93-4fb6-9773-f77a50243288</t>
+  </si>
+  <si>
+    <t>relationship--15f5af70-262e-41e0-8aba-fa599d341328</t>
+  </si>
+  <si>
+    <t>relationship--711996e9-34ae-4810-8d7a-21a44ffa7fe9</t>
+  </si>
+  <si>
+    <t>relationship--9a3c95c6-23e4-4c0f-8844-52d958f1dbe8</t>
+  </si>
+  <si>
+    <t>relationship--d5500959-3922-4bb2-9c2e-72df957cc5e1</t>
+  </si>
+  <si>
+    <t>relationship--7f6a069d-a281-4ca3-9c5d-7f40d7d57610</t>
+  </si>
+  <si>
+    <t>relationship--a10ca265-b361-4b4c-9de0-d1c1309a80a5</t>
+  </si>
+  <si>
+    <t>relationship--73a49bef-fe4c-459e-8fd8-836fcf3e0641</t>
+  </si>
+  <si>
+    <t>relationship--0cd4c6e2-7736-4613-b2a5-6c711975a0ae</t>
+  </si>
+  <si>
+    <t>relationship--bf56a23c-8789-41b1-af63-46b900047f5a</t>
+  </si>
+  <si>
+    <t>relationship--f3e20272-250d-4f8c-b9e6-f2d9ab1ee9d0</t>
+  </si>
+  <si>
+    <t>relationship--1afbd67d-8510-433b-a617-2720cfd43de3</t>
+  </si>
+  <si>
+    <t>relationship--950ce7a6-f20d-4429-8270-cbe702f9b8a4</t>
+  </si>
+  <si>
+    <t>relationship--d70c1641-5355-48a5-8a08-f6c589f1b7bf</t>
+  </si>
+  <si>
+    <t>relationship--f2315b08-5655-4313-8ae3-121331d6895b</t>
+  </si>
+  <si>
+    <t>relationship--8eae276b-a879-4b89-b777-a1cbc639ca44</t>
+  </si>
+  <si>
+    <t>relationship--c06b6614-aedc-4ee6-8a39-9953db7fe4c7</t>
+  </si>
+  <si>
+    <t>relationship--0a7daa8c-a8f9-4b8e-be70-9bea46ea2bd9</t>
+  </si>
+  <si>
+    <t>relationship--104478ca-397a-4f1a-88a9-cc288cc01269</t>
+  </si>
+  <si>
+    <t>relationship--b82e7c93-0bc3-4694-b8d3-f1865eacc556</t>
+  </si>
+  <si>
+    <t>relationship--5e334d35-427c-4965-8fa3-d390a2aec408</t>
+  </si>
+  <si>
+    <t>relationship--9bc4b721-8658-49f6-b490-726dbec2b451</t>
+  </si>
+  <si>
+    <t>relationship--4da5a977-b962-49e5-ab52-2e0e5f7e890a</t>
+  </si>
+  <si>
+    <t>relationship--b8c316e5-c364-4d3c-8de5-7aa98d597d2c</t>
+  </si>
+  <si>
+    <t>relationship--2e1b44f7-f38a-4868-910a-85e88baa212b</t>
+  </si>
+  <si>
+    <t>relationship--b535b75e-dae6-4781-9a69-21c2e2065f3b</t>
+  </si>
+  <si>
+    <t>relationship--7da26f74-c81f-49d8-b7e7-28e0a9ad2d2b</t>
+  </si>
+  <si>
+    <t>relationship--2cc2e74c-b0bf-4057-b099-ac8686c66a45</t>
   </si>
   <si>
     <t>27 April 2026</t>

--- a/docs/attack-excel-files/v18.1/russia-colonialism/russia-colonialism-v18.1-relationships.xlsx
+++ b/docs/attack-excel-files/v18.1/russia-colonialism/russia-colonialism-v18.1-relationships.xlsx
@@ -782,367 +782,367 @@
     <t>Царская канцелярия</t>
   </si>
   <si>
-    <t>campaign--97185b62-b756-44d3-b841-c26ff2caa435</t>
-  </si>
-  <si>
-    <t>campaign--28368dc3-bac3-40ca-9be2-53cd5b18ae5a</t>
-  </si>
-  <si>
-    <t>campaign--3e7aca06-438d-4972-b481-5eef5dddab91</t>
-  </si>
-  <si>
-    <t>campaign--42c2db2c-bca8-4f4c-90a1-feed7ccb5499</t>
-  </si>
-  <si>
-    <t>campaign--0e489ab4-57c8-4ea9-b1c1-35a091e8dcf5</t>
-  </si>
-  <si>
-    <t>campaign--3951c130-926c-4354-b30a-d9b845e20711</t>
-  </si>
-  <si>
-    <t>campaign--5df5ab6d-110b-41b0-914c-d68a42814b3f</t>
-  </si>
-  <si>
-    <t>campaign--332047f3-d991-48d5-a8d0-d626d70b1520</t>
-  </si>
-  <si>
-    <t>campaign--35760d2a-4bf9-493b-ab94-fa67c4ff8fcd</t>
-  </si>
-  <si>
-    <t>campaign--780db662-7237-47c6-9d76-e0a9c213b1ca</t>
-  </si>
-  <si>
-    <t>campaign--d38fee72-8a5f-42cd-a0e6-08b3642e49e2</t>
-  </si>
-  <si>
-    <t>campaign--ae71667a-64b0-4a35-bd4b-2212af26d6f2</t>
-  </si>
-  <si>
-    <t>campaign--1063f60a-3894-4344-97eb-1a62a8d09e50</t>
-  </si>
-  <si>
-    <t>campaign--1f2bd0e1-55a3-4605-9910-a28c81b3aba4</t>
-  </si>
-  <si>
-    <t>campaign--21ac6d95-7b1e-4b4a-a039-c789d4ded516</t>
-  </si>
-  <si>
-    <t>campaign--7fc58166-effa-406a-8ca4-a7e4fb477a96</t>
-  </si>
-  <si>
-    <t>campaign--374ff3ac-7e13-4ceb-870a-1c25a5e81f45</t>
-  </si>
-  <si>
-    <t>campaign--2514ee85-51a9-477d-893a-bb45313d0bd5</t>
-  </si>
-  <si>
-    <t>campaign--89014d54-7b08-4fba-83ac-c8722773fad8</t>
-  </si>
-  <si>
-    <t>campaign--ba097673-a412-4203-bb06-447f860a51d3</t>
-  </si>
-  <si>
-    <t>campaign--a55ffc4f-129f-4d38-8324-fdd1ebbb5a4b</t>
-  </si>
-  <si>
-    <t>campaign--01e2f625-82e2-488e-8622-00ebde701e23</t>
-  </si>
-  <si>
-    <t>campaign--fd958d24-a4bf-4243-ae08-e860c13ea805</t>
-  </si>
-  <si>
-    <t>campaign--a6face44-139d-466a-a5ff-e8c3ff709ace</t>
-  </si>
-  <si>
-    <t>campaign--a413d1f2-8330-4668-b8bd-fd8086250234</t>
-  </si>
-  <si>
-    <t>campaign--48e3bbbf-203d-40a1-bc6d-aa8b18e5598e</t>
-  </si>
-  <si>
-    <t>campaign--08d1bb96-2342-4cdb-b6b9-55a161a88419</t>
-  </si>
-  <si>
-    <t>campaign--76935537-cdec-406c-9f4a-a4cbc121cc00</t>
-  </si>
-  <si>
-    <t>campaign--f4466bbc-027a-4e44-935a-035f903ef19e</t>
-  </si>
-  <si>
-    <t>campaign--c7e7bcde-9c6c-437b-ad59-5e5bd2d5c514</t>
-  </si>
-  <si>
-    <t>campaign--236b5c9a-15f6-43ce-9667-200af4732480</t>
-  </si>
-  <si>
-    <t>campaign--b8c59485-94d3-40a6-b0fc-23d338986d1f</t>
-  </si>
-  <si>
-    <t>campaign--167376d8-aab7-4cbb-b314-230969e6a7a3</t>
-  </si>
-  <si>
-    <t>campaign--b2510237-29ac-4193-8722-444a86b52190</t>
-  </si>
-  <si>
-    <t>campaign--c8bcfd3d-d39b-4d28-9b5c-c5f3e8e0728f</t>
-  </si>
-  <si>
-    <t>campaign--8432f3de-ec66-4e20-88e9-54ed4587df9b</t>
-  </si>
-  <si>
-    <t>campaign--5bf5d20e-3e8f-4b7f-beb9-1a3189e2cadf</t>
-  </si>
-  <si>
-    <t>campaign--5f5766b1-030a-4e87-b165-48a1f821e9a6</t>
-  </si>
-  <si>
-    <t>campaign--ac432357-fb30-4c0f-9123-ff894b2784de</t>
-  </si>
-  <si>
-    <t>campaign--4bc43f67-3dc2-4c2b-9539-a42ff3e48f8f</t>
-  </si>
-  <si>
-    <t>campaign--a89eb731-49da-49ec-94fd-10f7ec7e3212</t>
-  </si>
-  <si>
-    <t>campaign--db4a09bc-80d8-443b-8be6-9a04e643eab5</t>
-  </si>
-  <si>
-    <t>campaign--0c92bef0-ae48-4178-a4e8-2845fe5e43ba</t>
-  </si>
-  <si>
-    <t>campaign--1a54b369-cecd-4acf-aeeb-addc0eee2b65</t>
-  </si>
-  <si>
-    <t>campaign--fc415691-46e4-4d5b-88ef-568d20e2f82a</t>
-  </si>
-  <si>
-    <t>campaign--30bc8d41-e4ff-476d-a84a-d5435273ad2e</t>
-  </si>
-  <si>
-    <t>campaign--37aea0f8-0538-4f63-994d-621cd042cbe7</t>
-  </si>
-  <si>
-    <t>campaign--b9035652-ec19-498f-ad70-c1e7c3af8809</t>
-  </si>
-  <si>
-    <t>campaign--25c5110f-77ed-4932-b111-1dfc5e875a95</t>
-  </si>
-  <si>
-    <t>campaign--84ee7058-67a7-46ba-b6ee-a9087bb87634</t>
-  </si>
-  <si>
-    <t>campaign--75cf364b-6744-4d5a-bb26-0abd1753609f</t>
-  </si>
-  <si>
-    <t>campaign--192a1e9c-2e3d-43d2-b6a6-175a55e941b5</t>
-  </si>
-  <si>
-    <t>campaign--071a2be9-c5af-4201-9e25-71e6c6dc63cf</t>
-  </si>
-  <si>
-    <t>campaign--ed10ebb7-caaa-481f-8655-7cc6acbade91</t>
-  </si>
-  <si>
-    <t>campaign--dc27daac-0791-47f7-aaee-d0e5c7a16918</t>
-  </si>
-  <si>
-    <t>campaign--7c31c341-4948-4d76-bc9a-d602657f0db3</t>
-  </si>
-  <si>
-    <t>campaign--f136d4ca-d08c-4b0b-9e1d-368e30dbfa5b</t>
-  </si>
-  <si>
-    <t>campaign--3f35fe1f-00d3-4e41-98a9-2e406c219312</t>
-  </si>
-  <si>
-    <t>campaign--31aacef3-25a8-4fba-ac95-bae1bb0592fb</t>
-  </si>
-  <si>
-    <t>campaign--491b0716-9561-4ea6-a89b-4ba9e0953e3c</t>
-  </si>
-  <si>
-    <t>campaign--a4455377-a120-45a5-9089-99fb95fdb59a</t>
-  </si>
-  <si>
-    <t>campaign--ea61a171-fa35-4ed1-9287-41e3ca667409</t>
-  </si>
-  <si>
-    <t>campaign--7771ca5f-0b5b-4fbb-9f0b-f37801347fca</t>
-  </si>
-  <si>
-    <t>campaign--0b3c9ce1-a0be-4440-b0f0-c762880ed332</t>
-  </si>
-  <si>
-    <t>campaign--96ec7087-d1b0-4076-a568-5f8a779eef00</t>
-  </si>
-  <si>
-    <t>campaign--46077bfe-ce3a-4542-8b5c-b8b6d8d6fdef</t>
-  </si>
-  <si>
-    <t>campaign--1e47c887-315a-4c3d-bea5-d9632702b517</t>
-  </si>
-  <si>
-    <t>campaign--61012452-31df-4e70-80b3-74be0914a200</t>
-  </si>
-  <si>
-    <t>campaign--bf409339-c5e5-4ab8-8b1a-246071ed19b5</t>
-  </si>
-  <si>
-    <t>campaign--d0eb71bc-3823-42d6-b3e5-427e2a915763</t>
-  </si>
-  <si>
-    <t>campaign--9a0c9c17-48be-4239-ae4b-ba408248d9ba</t>
-  </si>
-  <si>
-    <t>campaign--6a3d44b3-9d73-4774-a015-293e5ff7c59f</t>
-  </si>
-  <si>
-    <t>campaign--6058b9a2-6422-4498-bc1f-466e8f5404d0</t>
-  </si>
-  <si>
-    <t>campaign--a3e43158-57aa-48a2-8b22-c4338061ebe6</t>
-  </si>
-  <si>
-    <t>campaign--556f85fe-e335-4694-aa72-2e4da45a572d</t>
-  </si>
-  <si>
-    <t>campaign--3fc52fc0-1fc8-40f8-99fe-daee0cafc351</t>
-  </si>
-  <si>
-    <t>campaign--dee519da-cbc0-4a3f-8f64-811927f8fa8a</t>
-  </si>
-  <si>
-    <t>campaign--fcb5345d-ae74-4a0d-8859-00654996201a</t>
-  </si>
-  <si>
-    <t>campaign--ca069712-0be3-42d8-a175-c8e568760aba</t>
-  </si>
-  <si>
-    <t>campaign--9fd8c082-9e7d-4657-b402-c6b5164ebb7c</t>
-  </si>
-  <si>
-    <t>campaign--62313c07-9360-40f3-9a67-f106b3a9901f</t>
-  </si>
-  <si>
-    <t>campaign--a92151c2-5f7d-4c2e-a659-7a10e298595d</t>
-  </si>
-  <si>
-    <t>campaign--e2dc6026-4b3e-4088-8687-ee5e8efc0fcc</t>
-  </si>
-  <si>
-    <t>campaign--b8913d57-e3f2-43cc-989e-b5dc2cd92219</t>
-  </si>
-  <si>
-    <t>campaign--771a290d-43a0-43fb-89a5-2aaf271da029</t>
-  </si>
-  <si>
-    <t>campaign--c29e446f-6d4f-4920-91d5-fc54dedf1f5f</t>
-  </si>
-  <si>
-    <t>campaign--0bd21e62-2023-485d-9c17-c2684d1bebdb</t>
-  </si>
-  <si>
-    <t>campaign--7c688b14-67e6-476e-8096-a44c3fb95db9</t>
-  </si>
-  <si>
-    <t>campaign--567e3204-7775-46bb-b5f9-874bfeaf0c6f</t>
-  </si>
-  <si>
-    <t>campaign--dbde897a-31a7-4684-a98d-5805601ba4c2</t>
-  </si>
-  <si>
-    <t>campaign--906ac28e-dbce-42ff-9e99-9b6cc4aaa5e3</t>
-  </si>
-  <si>
-    <t>campaign--ce2366df-0b95-4d79-8f46-07ffa76c4215</t>
-  </si>
-  <si>
-    <t>campaign--efaaf655-e666-48b6-b47f-c6778bee3360</t>
-  </si>
-  <si>
-    <t>campaign--00f784da-4f20-4b91-acbe-8f9b76ff9596</t>
-  </si>
-  <si>
-    <t>campaign--59c82e4e-f119-41db-98a0-42312fac19cb</t>
-  </si>
-  <si>
-    <t>campaign--5478a268-e577-4b91-8abc-920e07341e66</t>
-  </si>
-  <si>
-    <t>campaign--b7c7a3d4-e14e-4089-805e-0d6bd5d494c2</t>
-  </si>
-  <si>
-    <t>campaign--acd8df7a-c420-435e-a7c2-1b8fd5170fab</t>
-  </si>
-  <si>
-    <t>campaign--d36ba52b-faba-4013-81c1-bc5462725fe9</t>
-  </si>
-  <si>
-    <t>campaign--cec91334-cad3-439c-9fd6-a172aa9d1c68</t>
-  </si>
-  <si>
-    <t>campaign--487d3e61-633a-4a79-8421-e58f556d93e1</t>
-  </si>
-  <si>
-    <t>campaign--dffc0208-5ef6-47c3-99a3-57d880da041e</t>
-  </si>
-  <si>
-    <t>intrusion-set--7b976569-98f0-4fa3-82fe-02d61389de3e</t>
-  </si>
-  <si>
-    <t>intrusion-set--d5113a56-7d11-4ccf-b29b-db0230a3deb5</t>
-  </si>
-  <si>
-    <t>intrusion-set--ccad1a64-f9f9-4595-8650-92f87954b4a0</t>
-  </si>
-  <si>
-    <t>intrusion-set--763a114d-2942-4a6d-9907-1170a64fae86</t>
-  </si>
-  <si>
-    <t>intrusion-set--efc55d3b-975e-4784-879d-5e1771bcdfb2</t>
-  </si>
-  <si>
-    <t>intrusion-set--d6cb53bb-bf87-46da-99d2-d218130dd4c9</t>
-  </si>
-  <si>
-    <t>tool--24a04dcd-846a-4c5b-bfcd-47828e9ddd57</t>
-  </si>
-  <si>
-    <t>tool--fb5d65db-23c3-4502-8fd9-7b40965d2ed8</t>
-  </si>
-  <si>
-    <t>tool--df0ba05b-fd65-4437-9c8f-5fbbf4498f51</t>
-  </si>
-  <si>
-    <t>tool--634cf340-6e8c-49d7-b45f-c9fb4f722daa</t>
-  </si>
-  <si>
-    <t>tool--06c48a32-5cf5-4cef-8992-72c541bfdfac</t>
-  </si>
-  <si>
-    <t>tool--e8d0468c-8a92-4294-baa2-a91bcd6f19e4</t>
-  </si>
-  <si>
-    <t>tool--88d6ef27-a088-40e6-b97f-8a49b8c508e1</t>
-  </si>
-  <si>
-    <t>tool--4d016c34-bb94-4b61-88bc-7e9cacc2185b</t>
-  </si>
-  <si>
-    <t>tool--2bf94bf0-b6e0-4e29-bef7-8745173179cb</t>
-  </si>
-  <si>
-    <t>tool--82bcdaea-f53f-45de-8281-b671db596090</t>
-  </si>
-  <si>
-    <t>tool--66dcf02c-a2aa-4a17-9e43-2e456ebdee31</t>
-  </si>
-  <si>
-    <t>tool--d0e502ca-3ba5-4364-b2ab-30d53b87c681</t>
-  </si>
-  <si>
-    <t>tool--e07eeae6-c3e5-45f1-b8f1-c3e50a179665</t>
+    <t>campaign--beb3c204-bc97-4d59-9de6-ecdb0c1a8fa6</t>
+  </si>
+  <si>
+    <t>campaign--36718563-750c-4243-ac67-2afb9313199c</t>
+  </si>
+  <si>
+    <t>campaign--c0a083ff-f66b-4fe1-bbc2-eaf9c87ecafa</t>
+  </si>
+  <si>
+    <t>campaign--36b6cac5-68cd-44e9-948e-cdadfaeb03c0</t>
+  </si>
+  <si>
+    <t>campaign--931e85ed-d20f-4aab-ad0e-c481f9b6f9a4</t>
+  </si>
+  <si>
+    <t>campaign--aa92e9bb-c0c0-404b-b04e-cf449ba5e39d</t>
+  </si>
+  <si>
+    <t>campaign--618bc33c-2bd3-40a0-aecc-7d7b87050c1b</t>
+  </si>
+  <si>
+    <t>campaign--f62ceaad-15da-4759-8904-81880a93f161</t>
+  </si>
+  <si>
+    <t>campaign--81490a22-d3ad-4dac-a642-e2eba0016b14</t>
+  </si>
+  <si>
+    <t>campaign--9631e3bc-bab9-4043-bc04-c02749a194be</t>
+  </si>
+  <si>
+    <t>campaign--4a9d685a-9b20-4f1d-8915-4ada209c8cca</t>
+  </si>
+  <si>
+    <t>campaign--528c16c6-f91f-414a-8371-eab2292b3449</t>
+  </si>
+  <si>
+    <t>campaign--7b330b89-cb3c-4f20-a141-0e7d3be39898</t>
+  </si>
+  <si>
+    <t>campaign--eddeafb4-a875-4655-84a6-c63e89eeefd0</t>
+  </si>
+  <si>
+    <t>campaign--be2b48b0-daea-4dc8-b2be-24ebe5913dc5</t>
+  </si>
+  <si>
+    <t>campaign--7b32e63c-318e-4976-9a47-235504a9ebe1</t>
+  </si>
+  <si>
+    <t>campaign--6f93731b-4153-48bc-902d-f4e0ea897aa8</t>
+  </si>
+  <si>
+    <t>campaign--5d1e342a-8efe-4664-8157-4cc7ed55477a</t>
+  </si>
+  <si>
+    <t>campaign--dd4a2a03-d604-48f7-88b6-5a4fce5d3965</t>
+  </si>
+  <si>
+    <t>campaign--fc8f8fea-2e44-4409-a72b-e75ab314ec8a</t>
+  </si>
+  <si>
+    <t>campaign--f0c6054b-c01a-4747-b587-9903218358b2</t>
+  </si>
+  <si>
+    <t>campaign--2c6e0dec-e346-4ed4-b88f-5711faad6118</t>
+  </si>
+  <si>
+    <t>campaign--17e5ae14-9fa2-4925-bb28-0cdfc14fc1d7</t>
+  </si>
+  <si>
+    <t>campaign--5b639678-3921-474c-8c9e-4015ec9f949c</t>
+  </si>
+  <si>
+    <t>campaign--d1030d85-2e68-49b2-928c-2a14317de1bd</t>
+  </si>
+  <si>
+    <t>campaign--06927989-0878-4b74-9a28-35325dfa70f2</t>
+  </si>
+  <si>
+    <t>campaign--ea29169a-53a3-40d2-bd80-07873f4c7316</t>
+  </si>
+  <si>
+    <t>campaign--561a04bb-a336-4395-b343-c56073b71789</t>
+  </si>
+  <si>
+    <t>campaign--9707df54-95c3-4aa7-b931-57ee1a5c16f6</t>
+  </si>
+  <si>
+    <t>campaign--3dfcbbbc-e0ba-4b67-8bc2-810834ae08b3</t>
+  </si>
+  <si>
+    <t>campaign--f60fcbc2-4c94-4ef8-95b5-44d6aa0b3b8d</t>
+  </si>
+  <si>
+    <t>campaign--12b79d1c-2782-49d5-9a19-c40468968332</t>
+  </si>
+  <si>
+    <t>campaign--72bd14c6-9a8d-429e-8a8f-46ab0d667364</t>
+  </si>
+  <si>
+    <t>campaign--5fa83a2b-9405-4ea4-b37e-cd9d0ce57755</t>
+  </si>
+  <si>
+    <t>campaign--cc574bdf-4d55-47c1-b2fa-6bdb93755eea</t>
+  </si>
+  <si>
+    <t>campaign--27a779bf-b31d-4bbb-ace6-71f927cbde26</t>
+  </si>
+  <si>
+    <t>campaign--61a87e18-b207-448e-ba3a-c2a8d198974b</t>
+  </si>
+  <si>
+    <t>campaign--84ae7b7b-64d5-4093-a6a9-6dfacd6c66bf</t>
+  </si>
+  <si>
+    <t>campaign--67012817-6f85-428b-a010-93c08f2b76da</t>
+  </si>
+  <si>
+    <t>campaign--5dd1d621-c811-42cf-82c2-3406994dfde6</t>
+  </si>
+  <si>
+    <t>campaign--ace5b016-3d27-4b37-b2d2-d556647b00f1</t>
+  </si>
+  <si>
+    <t>campaign--4f18507b-2f69-46a9-85d5-40f17338779f</t>
+  </si>
+  <si>
+    <t>campaign--59f53554-bb3e-47d5-b876-5384f7e36329</t>
+  </si>
+  <si>
+    <t>campaign--5bcf32f4-e373-4f37-9efc-e49505e85e22</t>
+  </si>
+  <si>
+    <t>campaign--0aa91ac6-7a07-4d24-a072-994296a51cfa</t>
+  </si>
+  <si>
+    <t>campaign--9a502692-8621-4955-85ad-e7f7eb03cca2</t>
+  </si>
+  <si>
+    <t>campaign--a2171902-2718-49d1-b854-c8226a719312</t>
+  </si>
+  <si>
+    <t>campaign--592aa280-7cce-445b-b6e9-9abb88c52a90</t>
+  </si>
+  <si>
+    <t>campaign--19a08a71-50bd-429a-be2a-499c11fa5ccc</t>
+  </si>
+  <si>
+    <t>campaign--371756b0-4caf-470c-963c-a9cbaa8ee88b</t>
+  </si>
+  <si>
+    <t>campaign--4b25ef2f-6bb6-4d1d-a732-11a375521f54</t>
+  </si>
+  <si>
+    <t>campaign--a84dbd97-d0f4-4692-a0ab-e9d979d8a010</t>
+  </si>
+  <si>
+    <t>campaign--b767d548-72af-449a-adf8-63595a15dd6e</t>
+  </si>
+  <si>
+    <t>campaign--77beb7ac-80f5-4895-a7ea-b1dd56dacba4</t>
+  </si>
+  <si>
+    <t>campaign--06dfe566-0f1e-46bb-a5dc-ec4aff46135b</t>
+  </si>
+  <si>
+    <t>campaign--0975d9fe-1c4b-49ef-98ef-23d2b4210e88</t>
+  </si>
+  <si>
+    <t>campaign--b63c414e-aa3e-40c9-bb67-1f2d9ee5f71f</t>
+  </si>
+  <si>
+    <t>campaign--5478ddf2-476b-4d6c-a3aa-7096f3d5aca8</t>
+  </si>
+  <si>
+    <t>campaign--3574027e-078d-4e16-8484-b1dbe338ce61</t>
+  </si>
+  <si>
+    <t>campaign--1ddc10f7-4e18-404e-8910-5d8680bf7a82</t>
+  </si>
+  <si>
+    <t>campaign--39aac990-a61c-41dc-b9c5-b18f149b5cf8</t>
+  </si>
+  <si>
+    <t>campaign--3568c587-8fdb-4536-8de4-ebd3429b4cbd</t>
+  </si>
+  <si>
+    <t>campaign--e4ce65e2-37dd-4c97-98b8-c68fd507b4cc</t>
+  </si>
+  <si>
+    <t>campaign--0f94ee1d-db92-4fa1-9026-3308a6277f00</t>
+  </si>
+  <si>
+    <t>campaign--59491b04-3f44-42a9-bc41-7d0f175853c0</t>
+  </si>
+  <si>
+    <t>campaign--e509ef5e-b2d6-4520-8195-26f2931f56ff</t>
+  </si>
+  <si>
+    <t>campaign--dcf07b78-3dce-40f2-8c30-1e73ee27fb0a</t>
+  </si>
+  <si>
+    <t>campaign--e325f77e-16fc-4649-8dd9-ef74d4b8663c</t>
+  </si>
+  <si>
+    <t>campaign--fd91a053-f9b7-4cc1-879c-caa2f8a041f7</t>
+  </si>
+  <si>
+    <t>campaign--f4dffb8c-e664-4427-b25f-8a0f193c7649</t>
+  </si>
+  <si>
+    <t>campaign--e2f24cd2-ae30-4dcc-8c0e-6cbb3a0464a8</t>
+  </si>
+  <si>
+    <t>campaign--a48ef2d9-78c7-4412-830d-dfe17d102cc6</t>
+  </si>
+  <si>
+    <t>campaign--3396a968-9eeb-49ec-8dcd-18ff2d01b35b</t>
+  </si>
+  <si>
+    <t>campaign--02b7be7b-141b-4c27-a0c3-3a43f03219c9</t>
+  </si>
+  <si>
+    <t>campaign--b0acd87c-70ac-4d2d-a36b-2dec78583175</t>
+  </si>
+  <si>
+    <t>campaign--c0720a94-3178-4c69-8054-087ed0662c46</t>
+  </si>
+  <si>
+    <t>campaign--63c55fc1-e70c-4fdd-902a-14d4ca487812</t>
+  </si>
+  <si>
+    <t>campaign--40149032-0db8-4fbd-b5d4-a067b866c148</t>
+  </si>
+  <si>
+    <t>campaign--bfd071be-b1d5-44da-8f9d-e43041680ae7</t>
+  </si>
+  <si>
+    <t>campaign--bd6a4377-7f19-4732-a9f2-a3e0af5594a2</t>
+  </si>
+  <si>
+    <t>campaign--f1f67736-a37e-460d-8b05-49e59aad8ec3</t>
+  </si>
+  <si>
+    <t>campaign--696708cb-0055-44d8-99cb-f7fd2f15f721</t>
+  </si>
+  <si>
+    <t>campaign--2737ed0c-704b-422c-b4bd-d03d60ae1708</t>
+  </si>
+  <si>
+    <t>campaign--5a853b42-811c-495c-8cc3-4e44a8a1725c</t>
+  </si>
+  <si>
+    <t>campaign--87706f0a-efab-41dd-b40e-09d912b278fb</t>
+  </si>
+  <si>
+    <t>campaign--ee040f1e-7348-49a8-994b-429ea4f44ee9</t>
+  </si>
+  <si>
+    <t>campaign--627bf55a-42e0-4287-8113-35f4341ecab6</t>
+  </si>
+  <si>
+    <t>campaign--de98247a-897f-403e-9754-dae2fce2e39b</t>
+  </si>
+  <si>
+    <t>campaign--09020393-e2d9-4947-8e9e-0628160d3e3f</t>
+  </si>
+  <si>
+    <t>campaign--f5d8d5a7-70b7-4fc5-8971-e0eb43a47434</t>
+  </si>
+  <si>
+    <t>campaign--b6a88759-5300-4aaa-b49d-bf2236862685</t>
+  </si>
+  <si>
+    <t>campaign--b0168a30-f171-4142-9634-414781200ed4</t>
+  </si>
+  <si>
+    <t>campaign--c5d71421-e843-4a24-8444-46ebb0ad5b3e</t>
+  </si>
+  <si>
+    <t>campaign--97256eb3-cff9-433b-a6f2-48a15cbd9b9a</t>
+  </si>
+  <si>
+    <t>campaign--0d91cd39-b6e8-4cfe-adb1-cfc73904b0ab</t>
+  </si>
+  <si>
+    <t>campaign--44e766de-62fa-4407-8edc-b12167d3326c</t>
+  </si>
+  <si>
+    <t>campaign--bb6eedd8-fddb-409d-9b1f-c3a68aa615d5</t>
+  </si>
+  <si>
+    <t>campaign--674f47b9-9ec6-4c86-b3b7-63e25a43288e</t>
+  </si>
+  <si>
+    <t>campaign--fb281d58-2cc6-4a74-94c9-102105e35802</t>
+  </si>
+  <si>
+    <t>campaign--a4877dac-0e19-420c-87e8-e72f8806a3a5</t>
+  </si>
+  <si>
+    <t>campaign--1322fb40-8292-41fa-82bb-ea1743b9ce37</t>
+  </si>
+  <si>
+    <t>campaign--dcad1425-9259-44ad-a22e-bb1ba03156cb</t>
+  </si>
+  <si>
+    <t>intrusion-set--00d5aa42-725d-45ea-8815-ccc615a4d517</t>
+  </si>
+  <si>
+    <t>intrusion-set--3fb8da0b-6311-48dc-9b3e-0a6816345b77</t>
+  </si>
+  <si>
+    <t>intrusion-set--1f6d7249-6192-46e5-b1c5-793a60706469</t>
+  </si>
+  <si>
+    <t>intrusion-set--002e0782-6856-438e-bc83-3c5ebbcba18d</t>
+  </si>
+  <si>
+    <t>intrusion-set--f2a7d9cd-c26b-4ff1-a215-41d91c2ede51</t>
+  </si>
+  <si>
+    <t>intrusion-set--13896fcc-2d95-4d93-bb1e-073c354eab10</t>
+  </si>
+  <si>
+    <t>tool--ceb165df-32e3-4d83-bdb6-db5ae496484d</t>
+  </si>
+  <si>
+    <t>tool--c245c447-66cb-48db-b15b-df8d8e0dd436</t>
+  </si>
+  <si>
+    <t>tool--1483b76f-f40e-4689-a9d1-55b8eac05837</t>
+  </si>
+  <si>
+    <t>tool--065f9ef9-fbc6-40da-9537-1f0ba3d48637</t>
+  </si>
+  <si>
+    <t>tool--bc2f8deb-bfa4-4bfe-a514-08eaffbdace0</t>
+  </si>
+  <si>
+    <t>tool--6cb97aa5-9ef0-4ccb-9e82-bbfc1ac6f9dc</t>
+  </si>
+  <si>
+    <t>tool--efbad242-63d3-40cf-9c6a-9ffe1578cc1e</t>
+  </si>
+  <si>
+    <t>tool--2ac13435-bb23-4791-b014-496ba930d1d1</t>
+  </si>
+  <si>
+    <t>tool--2d431e42-ef16-4d1a-9e90-7e5e0ffb410d</t>
+  </si>
+  <si>
+    <t>tool--6a1a7dc9-5d85-444a-b140-04e777c873f0</t>
+  </si>
+  <si>
+    <t>tool--0f891574-2d64-4b40-959a-6822e47af301</t>
+  </si>
+  <si>
+    <t>tool--2632cb38-aa7a-411c-a58d-f5ecef972484</t>
+  </si>
+  <si>
+    <t>tool--f00b45db-5e26-4a45-a418-6af97faa4a4d</t>
   </si>
   <si>
     <t>campaign</t>
@@ -1658,253 +1658,253 @@
     <t>Смена алфавита родного языка</t>
   </si>
   <si>
-    <t>attack-pattern--d67e92a1-567a-4443-b196-42eee7df7df9</t>
-  </si>
-  <si>
-    <t>attack-pattern--f87361eb-4cc0-472a-9d20-d8814c3dcb83</t>
-  </si>
-  <si>
-    <t>attack-pattern--11df0e1b-fb0b-495a-8517-fe9629386cc7</t>
-  </si>
-  <si>
-    <t>attack-pattern--69b5ecb8-ed59-476a-a8d0-692d61060065</t>
-  </si>
-  <si>
-    <t>attack-pattern--b1616020-3221-457d-9111-770be3da803f</t>
-  </si>
-  <si>
-    <t>attack-pattern--23537b01-052d-4788-a1c5-ac64ea3a5440</t>
-  </si>
-  <si>
-    <t>attack-pattern--b1ae5e87-2d91-4460-ab24-a874f71d0aa3</t>
-  </si>
-  <si>
-    <t>attack-pattern--14ddac56-e61c-489c-9f2a-0ead47acab72</t>
-  </si>
-  <si>
-    <t>attack-pattern--cfe0ba66-044c-4fae-899d-2776ecd25970</t>
-  </si>
-  <si>
-    <t>attack-pattern--7302168b-1756-4aa2-9831-57b042e5e79c</t>
-  </si>
-  <si>
-    <t>attack-pattern--0e9f8dfa-7044-47a4-99c4-b8108e0c3531</t>
-  </si>
-  <si>
-    <t>attack-pattern--541f9c2f-5e7e-40bd-8807-e27b27bf27f9</t>
-  </si>
-  <si>
-    <t>attack-pattern--d1450cbb-9ca9-4637-a3d4-415897d678b3</t>
-  </si>
-  <si>
-    <t>attack-pattern--f8863479-abf3-40aa-909f-422ff587ef75</t>
-  </si>
-  <si>
-    <t>attack-pattern--1c3cc896-6014-4a38-bb84-f755661f9f8a</t>
-  </si>
-  <si>
-    <t>attack-pattern--3d477757-3882-43e5-b3b5-5c453472af4e</t>
-  </si>
-  <si>
-    <t>attack-pattern--0a36cf96-d155-4205-badf-fce21153e3d3</t>
-  </si>
-  <si>
-    <t>attack-pattern--0f543b48-8526-45f6-9f4c-c0aabf08b950</t>
-  </si>
-  <si>
-    <t>attack-pattern--f7a7642e-6431-4d94-8930-784669743a6e</t>
-  </si>
-  <si>
-    <t>attack-pattern--d8fec2ab-fe86-4530-9801-bbbe5c3baf44</t>
-  </si>
-  <si>
-    <t>attack-pattern--77f583b6-9202-4712-9a61-f28cba87bf1b</t>
-  </si>
-  <si>
-    <t>attack-pattern--ca19f909-8e73-4014-ab69-a521482caa77</t>
-  </si>
-  <si>
-    <t>attack-pattern--e06e27d3-c18f-4bac-9bb6-17121de4850b</t>
-  </si>
-  <si>
-    <t>attack-pattern--0f207f69-c49f-4bd9-a2c8-81d5903af798</t>
-  </si>
-  <si>
-    <t>attack-pattern--d039ccb5-695e-4e9c-903d-4a25d80a5e91</t>
-  </si>
-  <si>
-    <t>attack-pattern--281cf3bf-8184-4148-8d26-8ae24ac5facd</t>
-  </si>
-  <si>
-    <t>attack-pattern--20e9f442-a9aa-49d2-86e7-10b3677d2b71</t>
-  </si>
-  <si>
-    <t>attack-pattern--7b5e8502-6625-4bfb-becf-4701773fc345</t>
-  </si>
-  <si>
-    <t>attack-pattern--01cef48e-e90c-42c2-b99f-c6ce6b48b026</t>
-  </si>
-  <si>
-    <t>attack-pattern--954103ab-7172-4bc3-80d2-6eda761140c7</t>
-  </si>
-  <si>
-    <t>attack-pattern--47a73afc-602e-4840-98f7-559a0583a02f</t>
-  </si>
-  <si>
-    <t>attack-pattern--ce173a13-3838-4451-bcde-529c8c9cbf4d</t>
-  </si>
-  <si>
-    <t>attack-pattern--0c6b2071-1b00-4c4e-ad42-c086fe85e44d</t>
-  </si>
-  <si>
-    <t>attack-pattern--3b7ebd5a-2989-4a5f-8187-7dcbb6319ecd</t>
-  </si>
-  <si>
-    <t>attack-pattern--3c2787d0-9bb3-4445-baf7-affe99ffc75d</t>
-  </si>
-  <si>
-    <t>attack-pattern--255d85ab-8ae5-4855-9d4d-398d57bfb428</t>
-  </si>
-  <si>
-    <t>attack-pattern--ab6eb169-9d35-462e-8540-e600dcfcc755</t>
-  </si>
-  <si>
-    <t>attack-pattern--a67dba4e-5c9c-4a96-8564-cc1477847aa2</t>
-  </si>
-  <si>
-    <t>attack-pattern--2665c1bf-c793-4ff8-81e1-8cdfb042a050</t>
-  </si>
-  <si>
-    <t>attack-pattern--01660591-eff8-4002-8b86-edbc8ddcff75</t>
-  </si>
-  <si>
-    <t>attack-pattern--df7b78e3-6709-4b71-ae0c-08ed1a47de6b</t>
-  </si>
-  <si>
-    <t>attack-pattern--31403032-89b6-4a29-af26-bdb2c907f869</t>
-  </si>
-  <si>
-    <t>attack-pattern--e1500254-a805-457b-9c9f-eaa7ed4441c2</t>
-  </si>
-  <si>
-    <t>attack-pattern--15b42e50-034b-48ec-a530-08f4da421ced</t>
-  </si>
-  <si>
-    <t>attack-pattern--2eccd110-1bf6-4854-a82c-0a45775e907f</t>
-  </si>
-  <si>
-    <t>attack-pattern--bbbea8cd-eb4e-4314-abc8-2293225ab5e6</t>
-  </si>
-  <si>
-    <t>attack-pattern--ba18aeed-1fa0-4221-b5c3-2951c695226d</t>
-  </si>
-  <si>
-    <t>attack-pattern--58aadf94-c0fc-45fe-b84d-86af05ac2a41</t>
-  </si>
-  <si>
-    <t>attack-pattern--f409ed58-993e-4cd3-816b-35cb16df5f13</t>
-  </si>
-  <si>
-    <t>attack-pattern--3408f6b9-9851-47a8-8c46-591cab11c267</t>
-  </si>
-  <si>
-    <t>attack-pattern--661bd189-a8b3-42ff-bf5b-33de03ae6136</t>
-  </si>
-  <si>
-    <t>attack-pattern--7ef5f9c4-8044-44bc-88a6-9395e47e160a</t>
-  </si>
-  <si>
-    <t>attack-pattern--d2982864-148c-45ed-9a9d-73124e552f59</t>
-  </si>
-  <si>
-    <t>attack-pattern--60789ba9-9b1e-4a2d-804d-b16342fe5f3d</t>
-  </si>
-  <si>
-    <t>attack-pattern--63e9746b-4223-4c4d-bb27-a4c2f724f832</t>
-  </si>
-  <si>
-    <t>attack-pattern--b6ab653b-b93b-46b8-9fc3-d24ccf9a86a1</t>
-  </si>
-  <si>
-    <t>attack-pattern--59e9ef1f-3d12-4523-a3ac-0b4c11c35573</t>
-  </si>
-  <si>
-    <t>attack-pattern--3c3ab581-f839-4439-bf70-a00298d8cbb7</t>
-  </si>
-  <si>
-    <t>attack-pattern--b7f8cff2-87c7-48c1-aeb7-5cf9187b1090</t>
-  </si>
-  <si>
-    <t>attack-pattern--40ddc318-d9d7-4035-80a9-21f5de23c666</t>
-  </si>
-  <si>
-    <t>attack-pattern--9a46e5ee-7093-4048-9d7e-501463c0424d</t>
-  </si>
-  <si>
-    <t>attack-pattern--3c78bc06-b7d9-4d72-87cc-3896a83a79c1</t>
-  </si>
-  <si>
-    <t>attack-pattern--3ec89812-91d7-48b1-aa07-b78e44175f91</t>
-  </si>
-  <si>
-    <t>attack-pattern--1a21e55e-d799-41ce-a799-461e1995bd5a</t>
-  </si>
-  <si>
-    <t>attack-pattern--5ba903c1-2421-4964-8ca4-f56dcc96a1c3</t>
-  </si>
-  <si>
-    <t>attack-pattern--f6f80852-da09-4571-bd87-ab371a289296</t>
-  </si>
-  <si>
-    <t>attack-pattern--1337b0db-4d5f-447f-83d1-3682c83da1be</t>
-  </si>
-  <si>
-    <t>attack-pattern--50e11ffa-fd63-4200-af97-d723ceb03f87</t>
-  </si>
-  <si>
-    <t>attack-pattern--3c07dbf7-3e3e-47d9-b439-53989a64f430</t>
-  </si>
-  <si>
-    <t>attack-pattern--948886a4-efe9-40cc-8153-3370afff323e</t>
-  </si>
-  <si>
-    <t>attack-pattern--c21a61e0-99df-4c01-abf2-5e46d8345613</t>
-  </si>
-  <si>
-    <t>attack-pattern--d4ba7ff5-0107-437e-853c-b8c4d37ea441</t>
-  </si>
-  <si>
-    <t>attack-pattern--c69305fb-035a-4c61-8929-2e22cea42d61</t>
-  </si>
-  <si>
-    <t>attack-pattern--39c46a2f-f777-48c7-b903-20ce80bca89b</t>
-  </si>
-  <si>
-    <t>attack-pattern--9f4aa723-88b2-42d4-b7f0-58bfc3f42435</t>
-  </si>
-  <si>
-    <t>attack-pattern--9b1b420b-4d1a-4108-a086-73ba81138b1a</t>
-  </si>
-  <si>
-    <t>attack-pattern--cfd09f3f-20c2-4148-a51e-c7533a4f6866</t>
-  </si>
-  <si>
-    <t>attack-pattern--5da8aa0b-7c9c-4638-bc17-9ed6bf1aafa6</t>
-  </si>
-  <si>
-    <t>attack-pattern--2685f739-43ca-4258-8e7f-0cf545de3477</t>
-  </si>
-  <si>
-    <t>attack-pattern--b9b7420d-58cf-49d6-9884-18e4d72f0a38</t>
-  </si>
-  <si>
-    <t>attack-pattern--1a522e5a-e65b-443f-8aae-2bc39534e85e</t>
-  </si>
-  <si>
-    <t>attack-pattern--f2121d22-b6ab-4c8d-b1a6-a65df30bd836</t>
-  </si>
-  <si>
-    <t>attack-pattern--faf29c5e-51f3-4afd-9b72-70769986b561</t>
+    <t>attack-pattern--71fb05ba-3eab-4f5c-ba49-a67390e5fc13</t>
+  </si>
+  <si>
+    <t>attack-pattern--0f49883b-8f7f-45db-b962-d3017cc85771</t>
+  </si>
+  <si>
+    <t>attack-pattern--fb59974b-817d-48bb-81f3-4dd9873bd6b4</t>
+  </si>
+  <si>
+    <t>attack-pattern--59e90492-d231-402a-a465-3f5bc479a1e8</t>
+  </si>
+  <si>
+    <t>attack-pattern--137882c2-807a-40d3-b4b1-f6a204a18347</t>
+  </si>
+  <si>
+    <t>attack-pattern--9bb95249-6747-41c3-b711-7f5094e85ae7</t>
+  </si>
+  <si>
+    <t>attack-pattern--b661aaca-a287-468b-88df-878b68349563</t>
+  </si>
+  <si>
+    <t>attack-pattern--d974ffeb-b434-47fa-9665-cff3eb08afd7</t>
+  </si>
+  <si>
+    <t>attack-pattern--261c27b8-7ad3-447b-bbc3-160ef90be57d</t>
+  </si>
+  <si>
+    <t>attack-pattern--4f945941-64c6-443a-988b-7dd2bdbb0748</t>
+  </si>
+  <si>
+    <t>attack-pattern--29ec00bf-fdfe-4900-bf0b-83e650136a16</t>
+  </si>
+  <si>
+    <t>attack-pattern--993fbcf3-8292-45af-817f-edd7d88c57ea</t>
+  </si>
+  <si>
+    <t>attack-pattern--336d16d8-fe0b-4c75-a34c-54fab8d76a2f</t>
+  </si>
+  <si>
+    <t>attack-pattern--ab499b3c-40d3-4e5a-8de3-3ff1466362c7</t>
+  </si>
+  <si>
+    <t>attack-pattern--4183c4e4-db10-432a-bca9-e1b23e3da61f</t>
+  </si>
+  <si>
+    <t>attack-pattern--1346bbf5-d81b-4d05-b377-bdc659611dce</t>
+  </si>
+  <si>
+    <t>attack-pattern--de25c05a-bf38-438b-927f-bc4dcb46653c</t>
+  </si>
+  <si>
+    <t>attack-pattern--f4d219bd-ff07-431e-9ace-0021dc1336d1</t>
+  </si>
+  <si>
+    <t>attack-pattern--49394ec7-2785-4aca-9975-684937954136</t>
+  </si>
+  <si>
+    <t>attack-pattern--18bfffe3-6edf-438e-a946-488affc66f7a</t>
+  </si>
+  <si>
+    <t>attack-pattern--f578e2ce-75c5-4a8c-8d47-63ce9a9138c0</t>
+  </si>
+  <si>
+    <t>attack-pattern--eb4e21e3-74e1-4c36-9847-f819d0da7468</t>
+  </si>
+  <si>
+    <t>attack-pattern--b99f4011-58e6-451b-81a1-1ce712a80a70</t>
+  </si>
+  <si>
+    <t>attack-pattern--107c88d2-2c1e-4f39-b5cc-0d909875c061</t>
+  </si>
+  <si>
+    <t>attack-pattern--8532007d-d463-45cc-958a-fe79d1d83608</t>
+  </si>
+  <si>
+    <t>attack-pattern--22b543df-dfb1-49fc-8d95-c374e058f540</t>
+  </si>
+  <si>
+    <t>attack-pattern--0f064151-346c-4c9a-9376-b7b632f1e384</t>
+  </si>
+  <si>
+    <t>attack-pattern--9482f472-eefe-4b92-b476-a9b5f3b343ff</t>
+  </si>
+  <si>
+    <t>attack-pattern--9d1eb227-fa81-4405-a0da-241f20f31dea</t>
+  </si>
+  <si>
+    <t>attack-pattern--b1db6118-0a31-4730-bde2-8fac46c3e137</t>
+  </si>
+  <si>
+    <t>attack-pattern--f9a845df-3e98-4ac7-9ef9-489dfd667aaf</t>
+  </si>
+  <si>
+    <t>attack-pattern--923f47cf-b68d-460e-9fe0-110a95077f6a</t>
+  </si>
+  <si>
+    <t>attack-pattern--52bef255-ae4c-4e58-b916-db73b8409467</t>
+  </si>
+  <si>
+    <t>attack-pattern--cd9deeb5-27a6-44c7-a11f-f5381bd4054a</t>
+  </si>
+  <si>
+    <t>attack-pattern--68d98ee4-53c5-4745-9d7f-483114cc6999</t>
+  </si>
+  <si>
+    <t>attack-pattern--1439ce66-b7a2-4db6-a8f7-d2ded55aa3b4</t>
+  </si>
+  <si>
+    <t>attack-pattern--35b2816a-2fa1-429f-a041-5f6ffc581e69</t>
+  </si>
+  <si>
+    <t>attack-pattern--e9a7afa4-472f-45a0-9982-44652e7f5062</t>
+  </si>
+  <si>
+    <t>attack-pattern--ef81761d-ca4c-4cf6-be70-349d2288f494</t>
+  </si>
+  <si>
+    <t>attack-pattern--1bc0c743-4448-42f5-97f0-d4e107fab546</t>
+  </si>
+  <si>
+    <t>attack-pattern--a16626c3-d9fc-4781-a7d4-10c13bd9336f</t>
+  </si>
+  <si>
+    <t>attack-pattern--7a0e5d1e-3983-4db9-b8e7-22aa583a2858</t>
+  </si>
+  <si>
+    <t>attack-pattern--1bd02aba-634a-4588-9786-fc30696e70b5</t>
+  </si>
+  <si>
+    <t>attack-pattern--5b69d1b6-c6dd-4f6d-8909-ee09462cfad8</t>
+  </si>
+  <si>
+    <t>attack-pattern--ea37d3cc-2d42-45db-bad0-d7012841e93d</t>
+  </si>
+  <si>
+    <t>attack-pattern--ccac8b90-d32e-4daa-b524-8c0134ff7d4e</t>
+  </si>
+  <si>
+    <t>attack-pattern--af62ced2-68d3-492b-98ce-c999c9827400</t>
+  </si>
+  <si>
+    <t>attack-pattern--80dfaadf-e59e-45e8-8ea6-1d438ac88184</t>
+  </si>
+  <si>
+    <t>attack-pattern--04898e9d-6eef-499f-8d56-bfd1c2af2c6b</t>
+  </si>
+  <si>
+    <t>attack-pattern--030bbee9-626f-4024-aa7f-05ef7fbb844f</t>
+  </si>
+  <si>
+    <t>attack-pattern--1fb1fa4c-bf4e-4fa8-a32f-a4896e48fef5</t>
+  </si>
+  <si>
+    <t>attack-pattern--3a5d809f-d5a5-49b8-8a87-adb7babcf139</t>
+  </si>
+  <si>
+    <t>attack-pattern--7319913c-e3a4-4b03-a99c-3680896d81b7</t>
+  </si>
+  <si>
+    <t>attack-pattern--7f0aa4ca-fe15-4b83-bab8-922d4698446f</t>
+  </si>
+  <si>
+    <t>attack-pattern--0d525dd4-9996-48c0-8b48-87019adce8e1</t>
+  </si>
+  <si>
+    <t>attack-pattern--3f65d725-4c10-41c5-b822-f324cb8e9b5a</t>
+  </si>
+  <si>
+    <t>attack-pattern--e84b6176-a783-444d-8a2a-e5f1fd0d764c</t>
+  </si>
+  <si>
+    <t>attack-pattern--3045e408-7cdd-45fa-b0e0-ac789bda69d1</t>
+  </si>
+  <si>
+    <t>attack-pattern--834b21dc-f1f6-4fc5-b05a-e75753a12b5e</t>
+  </si>
+  <si>
+    <t>attack-pattern--023c87b7-782d-4f6e-82f6-84485c8409be</t>
+  </si>
+  <si>
+    <t>attack-pattern--088dd75c-3d48-434e-95d2-19d0e3147c5a</t>
+  </si>
+  <si>
+    <t>attack-pattern--6acaa0d2-b311-43d0-bf45-42f11350a821</t>
+  </si>
+  <si>
+    <t>attack-pattern--2c6e3672-d316-4467-8f4b-c5d2837957f0</t>
+  </si>
+  <si>
+    <t>attack-pattern--c0c319d3-3928-4843-9aeb-c57677814069</t>
+  </si>
+  <si>
+    <t>attack-pattern--1179ba8e-8da5-4aa9-8165-120b23ad1fec</t>
+  </si>
+  <si>
+    <t>attack-pattern--68303848-d811-444e-9c48-90bacb503e96</t>
+  </si>
+  <si>
+    <t>attack-pattern--944cf29d-d469-4233-aac4-379f43393faf</t>
+  </si>
+  <si>
+    <t>attack-pattern--44563dbb-1be9-46bc-9a66-af5e19b2106d</t>
+  </si>
+  <si>
+    <t>attack-pattern--ef572bf1-2a59-4459-856a-70d90d0d0395</t>
+  </si>
+  <si>
+    <t>attack-pattern--c56b38dd-5f25-422e-9698-d5bba69b683f</t>
+  </si>
+  <si>
+    <t>attack-pattern--24b1fa21-90c3-464f-833f-ac108ecc78d1</t>
+  </si>
+  <si>
+    <t>attack-pattern--257839c4-791b-4968-b2dc-23e6c882655c</t>
+  </si>
+  <si>
+    <t>attack-pattern--b8de1150-a710-4046-ace7-5c0877fa0bff</t>
+  </si>
+  <si>
+    <t>attack-pattern--c1d667b7-eee5-402c-a154-9dbbb2a23436</t>
+  </si>
+  <si>
+    <t>attack-pattern--7aee84dc-e060-4d3c-ac28-c6defb82a28b</t>
+  </si>
+  <si>
+    <t>attack-pattern--5a006ee6-b55d-4072-b4d2-92a59016f7f6</t>
+  </si>
+  <si>
+    <t>attack-pattern--c393033f-0d84-45b8-bf52-eb210a212208</t>
+  </si>
+  <si>
+    <t>attack-pattern--aa1b9222-fcb9-447f-b977-fdfb30faa681</t>
+  </si>
+  <si>
+    <t>attack-pattern--0bb3bb16-2da8-4789-ba21-e514db2101f5</t>
+  </si>
+  <si>
+    <t>attack-pattern--4b194f79-84f8-4b29-9ce9-cfa85642e44f</t>
+  </si>
+  <si>
+    <t>attack-pattern--97651d27-015f-4e58-b447-bc29c4569898</t>
+  </si>
+  <si>
+    <t>attack-pattern--ed62c8ca-77f7-4c09-acb3-2258db6f7d60</t>
+  </si>
+  <si>
+    <t>attack-pattern--d735ca35-037b-4a3a-b196-89833a86103d</t>
   </si>
   <si>
     <t>technique</t>
@@ -2962,3031 +2962,3031 @@
     <t>Полный законодательный запрет на самоорганизацию: указ Столыпина «про заборону будь-яких українських організацій» (Citation: Русифікація України — Вікіпедія 2026).</t>
   </si>
   <si>
-    <t>relationship--a95066fb-1718-46d3-8e6e-49e87d4751b7</t>
-  </si>
-  <si>
-    <t>relationship--e9a22d2b-cb0b-4938-9005-5533000e7b38</t>
-  </si>
-  <si>
-    <t>relationship--565adc13-b06e-47cd-ba71-049604f1c97e</t>
-  </si>
-  <si>
-    <t>relationship--1c284d41-421a-4be5-9678-bb2ac621c866</t>
-  </si>
-  <si>
-    <t>relationship--32210d72-5a5a-447f-bc97-012c21a9d180</t>
-  </si>
-  <si>
-    <t>relationship--48fe585f-60a2-4e8c-8063-2ef406ecabbc</t>
-  </si>
-  <si>
-    <t>relationship--1aa6f707-5ad2-4cee-9940-beb43e0bbd57</t>
-  </si>
-  <si>
-    <t>relationship--6810df1c-387a-422d-8a88-f1e5ac631c8c</t>
-  </si>
-  <si>
-    <t>relationship--ebf45aa9-ab01-471e-989c-cf1348b5d70a</t>
-  </si>
-  <si>
-    <t>relationship--4807f9f0-92c6-446d-9180-7913879270a1</t>
-  </si>
-  <si>
-    <t>relationship--2fd65693-90a1-4f44-8274-b473a3bb173f</t>
-  </si>
-  <si>
-    <t>relationship--a0e6d595-4668-4dda-806b-b016e035a696</t>
-  </si>
-  <si>
-    <t>relationship--d47a8fb4-6c97-4b93-a1d6-61eb3f535597</t>
-  </si>
-  <si>
-    <t>relationship--f5c06e1b-f14f-492b-95e0-e82889dcc877</t>
-  </si>
-  <si>
-    <t>relationship--11eee327-9c1f-4151-931a-fbeb9b35bb4c</t>
-  </si>
-  <si>
-    <t>relationship--e435b9fd-332a-4d75-9476-d406f9c37a61</t>
-  </si>
-  <si>
-    <t>relationship--c13f714f-67f4-4e3f-a5fb-410a7d86df85</t>
-  </si>
-  <si>
-    <t>relationship--34d5c786-e1a6-4953-8f03-d138258da3d4</t>
-  </si>
-  <si>
-    <t>relationship--ed0e4c1e-4a29-4e56-99b3-c40191c272cc</t>
-  </si>
-  <si>
-    <t>relationship--dc8be056-141e-4424-80c7-a593fb2736fb</t>
-  </si>
-  <si>
-    <t>relationship--7ba58dbe-7676-4d12-a9da-718738083fe5</t>
-  </si>
-  <si>
-    <t>relationship--fc74cc6a-7592-4289-985b-94d3f359ade3</t>
-  </si>
-  <si>
-    <t>relationship--5541fa16-864d-4d8f-bdd9-8f442103ea16</t>
-  </si>
-  <si>
-    <t>relationship--7d115ed9-39e7-4def-b4a0-79972420802d</t>
-  </si>
-  <si>
-    <t>relationship--1bca7e42-1da9-4ea3-bb66-afa4c1df3443</t>
-  </si>
-  <si>
-    <t>relationship--bbdcb1e8-692d-41fe-88e1-d1fc06f4a8d5</t>
-  </si>
-  <si>
-    <t>relationship--dfb42873-75dc-45b8-8abd-96f5da31a2fa</t>
-  </si>
-  <si>
-    <t>relationship--48aaa29f-ac3e-47ee-982c-8541c26117c5</t>
-  </si>
-  <si>
-    <t>relationship--30d03301-95c7-4a01-86ab-fc56fab12bd0</t>
-  </si>
-  <si>
-    <t>relationship--33c28a36-b522-4c5c-b33c-28d4390bd800</t>
-  </si>
-  <si>
-    <t>relationship--463bd61c-a8d3-40ab-ace9-4515dfa76476</t>
-  </si>
-  <si>
-    <t>relationship--32ff96a6-0b0a-4ca7-8f19-3ed9dce19f80</t>
-  </si>
-  <si>
-    <t>relationship--f743c22a-ebef-4a93-847b-3b6e3122b994</t>
-  </si>
-  <si>
-    <t>relationship--619ee101-358b-4aad-b5d0-14bced2f13c8</t>
-  </si>
-  <si>
-    <t>relationship--abf8a785-6875-4d28-8fe5-01247f5425d9</t>
-  </si>
-  <si>
-    <t>relationship--0eadb0af-59ea-46cf-929c-73d9b9764492</t>
-  </si>
-  <si>
-    <t>relationship--261854c3-1617-45ff-baa8-6dbe52976c77</t>
-  </si>
-  <si>
-    <t>relationship--b027ab64-92aa-4d21-af4e-2337894240b5</t>
-  </si>
-  <si>
-    <t>relationship--b58f403d-9810-45d5-86d3-41e89f270bcf</t>
-  </si>
-  <si>
-    <t>relationship--f56b40d8-819a-40bc-a68e-c60d01db7f0f</t>
-  </si>
-  <si>
-    <t>relationship--3ef446d6-bbb7-433b-af9a-46857a3bc555</t>
-  </si>
-  <si>
-    <t>relationship--0cfbc2d3-05dd-44a8-bc82-7887467e3928</t>
-  </si>
-  <si>
-    <t>relationship--646e8a40-ca48-4925-9031-204da00b650e</t>
-  </si>
-  <si>
-    <t>relationship--a5959dbf-f0f2-45a0-bb14-5e41bdb8e585</t>
-  </si>
-  <si>
-    <t>relationship--e634e455-5505-4898-b305-982f72306fc4</t>
-  </si>
-  <si>
-    <t>relationship--3ae42177-2839-483a-80ef-2f3a2d15803c</t>
-  </si>
-  <si>
-    <t>relationship--79f23e7a-d1dc-44a2-bc4c-6d7c0604d9d9</t>
-  </si>
-  <si>
-    <t>relationship--41d16cff-028a-45b7-9773-b7ed73ac0855</t>
-  </si>
-  <si>
-    <t>relationship--26683c7f-b18d-4f0b-8240-1474c128b1ed</t>
-  </si>
-  <si>
-    <t>relationship--1116351d-6972-444b-90a0-1f8e7e66d75e</t>
-  </si>
-  <si>
-    <t>relationship--8c0281e5-c7a7-4e8c-a340-f4c9c0e727e9</t>
-  </si>
-  <si>
-    <t>relationship--9cedb62b-574a-4771-bf01-3eb83d2c19e7</t>
-  </si>
-  <si>
-    <t>relationship--2c051a16-4463-4ce0-8045-05edbecdb96e</t>
-  </si>
-  <si>
-    <t>relationship--cb40224b-fde2-4bd9-b5f4-1c7fca7631b9</t>
-  </si>
-  <si>
-    <t>relationship--ce3e3dce-c741-4765-a1f3-44e4543d4b3d</t>
-  </si>
-  <si>
-    <t>relationship--58d301f9-9b44-47c3-8013-ae1ec11c5913</t>
-  </si>
-  <si>
-    <t>relationship--97129600-dfdc-46fc-87ea-0815c54c2726</t>
-  </si>
-  <si>
-    <t>relationship--bfea3bd1-1ce5-4d9e-b016-73478a483537</t>
-  </si>
-  <si>
-    <t>relationship--87f2faef-e5fd-49df-99d1-3d1b54ca7640</t>
-  </si>
-  <si>
-    <t>relationship--fab8f5da-e65c-435e-8311-720b6c9eeabf</t>
-  </si>
-  <si>
-    <t>relationship--3aa6ec34-f393-430c-9cbd-4841f9920f0e</t>
-  </si>
-  <si>
-    <t>relationship--31366991-d83e-4eaf-88ba-c26255847e3f</t>
-  </si>
-  <si>
-    <t>relationship--d87ce476-23f9-4fc6-b13c-047097357dcf</t>
-  </si>
-  <si>
-    <t>relationship--5badbe27-c263-478a-b68d-c0c28b4f8ef1</t>
-  </si>
-  <si>
-    <t>relationship--a351e0a9-ae44-4578-8b4d-c6b47da74308</t>
-  </si>
-  <si>
-    <t>relationship--a56ff3ba-96e6-4973-bcd0-c4bef23b5d38</t>
-  </si>
-  <si>
-    <t>relationship--0ce7bddd-50d5-48be-afb7-d3e06b285ef0</t>
-  </si>
-  <si>
-    <t>relationship--05e4c4c5-0966-4337-8275-c4907b8d4673</t>
-  </si>
-  <si>
-    <t>relationship--565130fe-3386-42b6-b475-f02f8474bd39</t>
-  </si>
-  <si>
-    <t>relationship--cef88e9a-6cb7-49e6-9b5b-ba08c8ca6b88</t>
-  </si>
-  <si>
-    <t>relationship--e1ac74fc-d530-4cc3-a105-56087b595c2c</t>
-  </si>
-  <si>
-    <t>relationship--516e3400-7942-4d72-b4b0-e3b39d62f9e7</t>
-  </si>
-  <si>
-    <t>relationship--df7ec859-d883-4c8f-8b0e-372570d2a736</t>
-  </si>
-  <si>
-    <t>relationship--da299c4e-9630-4b38-b717-b6583dbe26fc</t>
-  </si>
-  <si>
-    <t>relationship--c8edbb88-14ff-4d8e-9c74-b2712da0ab11</t>
-  </si>
-  <si>
-    <t>relationship--278b8d8c-0a20-4a8f-9bad-a72df718c17c</t>
-  </si>
-  <si>
-    <t>relationship--ed38512a-db10-4611-b123-d56d3b981c1e</t>
-  </si>
-  <si>
-    <t>relationship--83dd8b38-931f-40f7-bc4b-d56173bcfe73</t>
-  </si>
-  <si>
-    <t>relationship--7f6d56c5-6612-489c-9b18-8c24dc75af58</t>
-  </si>
-  <si>
-    <t>relationship--118c7ea5-f1e1-495b-a5a2-963b25933ac6</t>
-  </si>
-  <si>
-    <t>relationship--b7c59cd1-369f-4de9-a3a4-5b5cdae3d166</t>
-  </si>
-  <si>
-    <t>relationship--b907d83f-4982-4baa-b5f8-fc364e9b33cc</t>
-  </si>
-  <si>
-    <t>relationship--7c44d0bb-7378-48de-af57-28bbb3af8b8b</t>
-  </si>
-  <si>
-    <t>relationship--eda1dbd4-3b39-44ff-90c1-96e6046320fc</t>
-  </si>
-  <si>
-    <t>relationship--3b210ccc-f8be-470c-adc2-cd060d11ffbe</t>
-  </si>
-  <si>
-    <t>relationship--7bf4e691-2470-49cd-a172-5df8af2263c5</t>
-  </si>
-  <si>
-    <t>relationship--57227651-67a7-4ede-b3bd-9309c9dede53</t>
-  </si>
-  <si>
-    <t>relationship--692ea191-a544-4a50-9449-6ac7d09a1930</t>
-  </si>
-  <si>
-    <t>relationship--6e0c35a5-3a68-4c67-af6d-bd0866e51274</t>
-  </si>
-  <si>
-    <t>relationship--c4285b2d-5078-4331-9d59-fe17df33e8d0</t>
-  </si>
-  <si>
-    <t>relationship--c55f3f86-c5b9-4fc3-82f3-3ef59966c26b</t>
-  </si>
-  <si>
-    <t>relationship--a2a349c4-fcd3-47cf-913c-db97245ac089</t>
-  </si>
-  <si>
-    <t>relationship--d12e139d-c65a-4553-832b-62ec4ad574ca</t>
-  </si>
-  <si>
-    <t>relationship--80d2485a-1628-48d9-bb5f-e5b985c816ef</t>
-  </si>
-  <si>
-    <t>relationship--c0eb327a-d351-41c7-ad63-def80454e574</t>
-  </si>
-  <si>
-    <t>relationship--b8166e54-71e5-4ec9-b871-e2bfa18c5cbf</t>
-  </si>
-  <si>
-    <t>relationship--859a06b7-36a7-4ff8-bf25-dd0593d202f3</t>
-  </si>
-  <si>
-    <t>relationship--8c419d72-e7d3-43ef-abcc-b264990cc673</t>
-  </si>
-  <si>
-    <t>relationship--7eac7055-d3e2-4b34-9559-1360309757c9</t>
-  </si>
-  <si>
-    <t>relationship--cd9f0e86-64ce-438f-9767-6b4081d8079f</t>
-  </si>
-  <si>
-    <t>relationship--22ace871-0cc2-4b40-901d-51c4fd38aebd</t>
-  </si>
-  <si>
-    <t>relationship--2ebd7677-4776-4837-9240-39ff6493c0d9</t>
-  </si>
-  <si>
-    <t>relationship--123596cd-c28b-46e5-a300-7400a612cb67</t>
-  </si>
-  <si>
-    <t>relationship--16144da2-91f9-49e6-917d-a71bbff07b37</t>
-  </si>
-  <si>
-    <t>relationship--9697c005-6797-4bf7-a837-4f028c927ee6</t>
-  </si>
-  <si>
-    <t>relationship--6e404788-5d9d-414b-a956-d54684562ead</t>
-  </si>
-  <si>
-    <t>relationship--2c434e02-6e26-4156-ae31-6b299dae7863</t>
-  </si>
-  <si>
-    <t>relationship--37a22f39-51a3-4b42-8cbf-4682cb984c5f</t>
-  </si>
-  <si>
-    <t>relationship--de3e18c5-8e55-4213-b7a5-016f634f52d6</t>
-  </si>
-  <si>
-    <t>relationship--b294a298-4572-45ba-83cd-6febe20eb9c8</t>
-  </si>
-  <si>
-    <t>relationship--2a87fd2a-b184-456a-9ff3-5287906fb03f</t>
-  </si>
-  <si>
-    <t>relationship--2984ab74-0098-40b3-910a-a4468d5b1140</t>
-  </si>
-  <si>
-    <t>relationship--f455f2ef-5c5e-4c45-ad3f-b7e6496eb027</t>
-  </si>
-  <si>
-    <t>relationship--4bc8e783-3567-4fb8-867d-b2b0591c3676</t>
-  </si>
-  <si>
-    <t>relationship--ae99f88c-b34e-48a8-b884-8751b57831c3</t>
-  </si>
-  <si>
-    <t>relationship--913af001-f7cb-4207-8322-14ef2f4f006b</t>
-  </si>
-  <si>
-    <t>relationship--fcb25d74-cfa2-45a2-af99-29eb0ad4b064</t>
-  </si>
-  <si>
-    <t>relationship--ba3d5ece-0df2-4f39-a0e6-2ab151c4f803</t>
-  </si>
-  <si>
-    <t>relationship--98d13a8f-5671-46ab-98bf-dcee471a7416</t>
-  </si>
-  <si>
-    <t>relationship--6dd55282-c047-46db-b47d-ffef75634f32</t>
-  </si>
-  <si>
-    <t>relationship--6576dbf2-9887-46d4-b7c0-077b0aa6d520</t>
-  </si>
-  <si>
-    <t>relationship--82e78eaa-a5b5-4328-a73f-d51422047701</t>
-  </si>
-  <si>
-    <t>relationship--c407b553-608e-42df-8f20-99867374029b</t>
-  </si>
-  <si>
-    <t>relationship--58cbd296-f428-4f07-9627-ef721bca5e24</t>
-  </si>
-  <si>
-    <t>relationship--4e4c1786-5c5a-49fc-bd5f-4f98209e04a8</t>
-  </si>
-  <si>
-    <t>relationship--3fd82cd0-8553-4535-9d88-2432d8d6c588</t>
-  </si>
-  <si>
-    <t>relationship--1dbbc37e-23d4-44c4-acdc-e3cac17cc385</t>
-  </si>
-  <si>
-    <t>relationship--fbde6f1d-be2f-4e5f-92a5-c9e21f6b00e6</t>
-  </si>
-  <si>
-    <t>relationship--44b541d4-16cd-4697-91ed-8959150b93ea</t>
-  </si>
-  <si>
-    <t>relationship--bc00c803-905b-483d-a214-b756ab179b45</t>
-  </si>
-  <si>
-    <t>relationship--930512ae-f088-4597-bae8-dcc756d386d6</t>
-  </si>
-  <si>
-    <t>relationship--1e3bdd39-f6fd-459b-953c-ddafac2af3ee</t>
-  </si>
-  <si>
-    <t>relationship--6cda8772-c59c-40f6-951e-7203c973239e</t>
-  </si>
-  <si>
-    <t>relationship--26435369-1682-4a9f-a340-a6ff3307ec65</t>
-  </si>
-  <si>
-    <t>relationship--46ba6b14-29ac-4278-b078-f34ba26b1be5</t>
-  </si>
-  <si>
-    <t>relationship--b0380dea-279d-4897-9888-5307871a3acb</t>
-  </si>
-  <si>
-    <t>relationship--ade84795-f059-4866-a09e-37e6ac5adf40</t>
-  </si>
-  <si>
-    <t>relationship--62bee3ce-caad-42e9-b7bd-9c2262a342cc</t>
-  </si>
-  <si>
-    <t>relationship--d7952f2c-eaf9-43a6-a7b0-b46555772b73</t>
-  </si>
-  <si>
-    <t>relationship--3d23f2db-b299-4698-8767-c4d5bc249f9c</t>
-  </si>
-  <si>
-    <t>relationship--51baad2a-4458-43c3-a534-392226563e3e</t>
-  </si>
-  <si>
-    <t>relationship--f125e8d8-5e5f-4821-9e91-21780cd1efd6</t>
-  </si>
-  <si>
-    <t>relationship--c9d89fd2-934d-49d0-bcc6-892b5bc54c05</t>
-  </si>
-  <si>
-    <t>relationship--ce4f2eda-e514-4c3d-8877-f503c4fcee9d</t>
-  </si>
-  <si>
-    <t>relationship--6c0df7e5-7d02-4aeb-961c-dc80d2bb33b6</t>
-  </si>
-  <si>
-    <t>relationship--7dc82937-c2c7-4121-b82f-1b15049d4567</t>
-  </si>
-  <si>
-    <t>relationship--1438c8ef-dd0f-46a1-a329-7a84094089a7</t>
-  </si>
-  <si>
-    <t>relationship--10b591e9-7eed-4d3f-9cb3-261d8bdf56f5</t>
-  </si>
-  <si>
-    <t>relationship--6320ca25-0dec-426b-a89f-1901840d4a9b</t>
-  </si>
-  <si>
-    <t>relationship--cc37dc30-86e3-4e5b-826c-87bc71b2f98b</t>
-  </si>
-  <si>
-    <t>relationship--434be38d-f7c2-4833-98af-4f52da9cc033</t>
-  </si>
-  <si>
-    <t>relationship--58c8f148-2f0b-40dd-9946-4e4b08b5a9e1</t>
-  </si>
-  <si>
-    <t>relationship--6e559c18-f8de-46cc-8a2c-903c7173ba23</t>
-  </si>
-  <si>
-    <t>relationship--7bccdde2-9194-47a0-a92f-44b4e77a8a1b</t>
-  </si>
-  <si>
-    <t>relationship--8cae63fe-5d4f-407d-bbdd-3ffbdacaa5f7</t>
-  </si>
-  <si>
-    <t>relationship--e15f196e-7079-436f-80ff-106dfbfcb050</t>
-  </si>
-  <si>
-    <t>relationship--5818dc97-498b-4db4-821f-eabf92cc0147</t>
-  </si>
-  <si>
-    <t>relationship--a31d3284-f6df-4832-8e81-ca077371c7a0</t>
-  </si>
-  <si>
-    <t>relationship--07d341f1-5e24-4da9-96ed-ceaeec948632</t>
-  </si>
-  <si>
-    <t>relationship--36acbe6c-f5be-48c5-8910-6f4d6a84c5b2</t>
-  </si>
-  <si>
-    <t>relationship--b079861e-56d8-44f5-9e8c-a969b05fd089</t>
-  </si>
-  <si>
-    <t>relationship--878b41f7-4aa2-4254-bda7-45809fbcf30e</t>
-  </si>
-  <si>
-    <t>relationship--05cc6a6d-7c0c-4ec8-babb-4f489f107014</t>
-  </si>
-  <si>
-    <t>relationship--8e01371e-9a5c-4f4e-b109-a7f005b94faa</t>
-  </si>
-  <si>
-    <t>relationship--5081685d-0e81-4e84-b914-876e5723e0b1</t>
-  </si>
-  <si>
-    <t>relationship--9a11a133-cf32-4216-bd62-e8d351e98517</t>
-  </si>
-  <si>
-    <t>relationship--b33a6108-0645-4a98-8bdc-2cfe83bfbd05</t>
-  </si>
-  <si>
-    <t>relationship--bf3b16c7-2687-4e50-b058-2b9980d05443</t>
-  </si>
-  <si>
-    <t>relationship--c67ab420-a3b8-4617-b942-fa34e0df8c81</t>
-  </si>
-  <si>
-    <t>relationship--c8bc29c2-0d05-4b84-b82e-576a60d9ca1b</t>
-  </si>
-  <si>
-    <t>relationship--818b14a7-3bf9-4917-974c-7283e66d21fc</t>
-  </si>
-  <si>
-    <t>relationship--d99f39d0-fb23-460a-a041-4d9557b9b445</t>
-  </si>
-  <si>
-    <t>relationship--f3c6f5e7-4e68-4633-b7d9-e2b35b32bd0d</t>
-  </si>
-  <si>
-    <t>relationship--d28c162f-cc0d-45ef-926b-5ecc38320d78</t>
-  </si>
-  <si>
-    <t>relationship--bf09b1a3-7528-424a-ad44-13d32054a3aa</t>
-  </si>
-  <si>
-    <t>relationship--2f3cdf54-d10f-43ea-8e57-ec386e7a5a04</t>
-  </si>
-  <si>
-    <t>relationship--736363d3-ad9d-49b8-8469-50f98e2ffcc6</t>
-  </si>
-  <si>
-    <t>relationship--7d80956f-0e1d-4804-83c2-3fb5e44342e0</t>
-  </si>
-  <si>
-    <t>relationship--8ed5c2d1-de73-46aa-a16a-aaed5f37518e</t>
-  </si>
-  <si>
-    <t>relationship--332abc6c-519c-49ea-8fdf-4c2ad58c5d30</t>
-  </si>
-  <si>
-    <t>relationship--65ee3d9c-ae09-4e8d-987d-6cc1d219e01f</t>
-  </si>
-  <si>
-    <t>relationship--1bee2722-fd00-4414-b078-719bb1bc13fc</t>
-  </si>
-  <si>
-    <t>relationship--e13a70ac-3b25-4075-bb54-0d44ba465878</t>
-  </si>
-  <si>
-    <t>relationship--29a3ce2b-6be4-44fb-8fae-beef5f0296a1</t>
-  </si>
-  <si>
-    <t>relationship--9c61218c-a3e3-4688-8723-8a681f5d4799</t>
-  </si>
-  <si>
-    <t>relationship--9b31e25d-8cbe-455c-954b-206d112c4a0a</t>
-  </si>
-  <si>
-    <t>relationship--da89423c-a636-491c-b7a6-20300d79e176</t>
-  </si>
-  <si>
-    <t>relationship--65d9dcda-82e0-4983-98d9-09100bf11f69</t>
-  </si>
-  <si>
-    <t>relationship--a66e5426-deea-479c-9b33-48831ef1f74f</t>
-  </si>
-  <si>
-    <t>relationship--8a7f492f-6d0f-48ef-8475-cf6d9343beae</t>
-  </si>
-  <si>
-    <t>relationship--d7cba973-52a5-4ffa-8792-fad9de0f4ff5</t>
-  </si>
-  <si>
-    <t>relationship--66c41619-1a71-4cdf-959c-b20e132a9feb</t>
-  </si>
-  <si>
-    <t>relationship--1c5a2877-55d2-47f0-852c-41cffd9ea9cd</t>
-  </si>
-  <si>
-    <t>relationship--338d5a11-cbad-444b-b042-b4aaae1152ef</t>
-  </si>
-  <si>
-    <t>relationship--15a7a091-9597-443c-9546-c8c0b6f7015e</t>
-  </si>
-  <si>
-    <t>relationship--b397365a-1c8a-4bf6-9323-b3fa37ec8120</t>
-  </si>
-  <si>
-    <t>relationship--0944d14f-213e-42c6-9227-990789faa016</t>
-  </si>
-  <si>
-    <t>relationship--93c54f83-b658-4267-9ebd-1d808cf45f79</t>
-  </si>
-  <si>
-    <t>relationship--83510ac8-d535-4650-8d81-ebdbe8b636d3</t>
-  </si>
-  <si>
-    <t>relationship--834f449c-b379-41ab-8593-fdc8a6f7da85</t>
-  </si>
-  <si>
-    <t>relationship--25bfdfd7-c584-4eee-badb-e362294f2728</t>
-  </si>
-  <si>
-    <t>relationship--6540b8e2-98fe-49f7-8a99-50d9dd1b8a11</t>
-  </si>
-  <si>
-    <t>relationship--ea9fe07e-1615-4dcf-a3bd-33abcf4ffd14</t>
-  </si>
-  <si>
-    <t>relationship--95761fd2-eff3-4bbd-a79a-d47e24029c7f</t>
-  </si>
-  <si>
-    <t>relationship--9ac65c10-b5e4-4ae1-ac04-e2577a4aff40</t>
-  </si>
-  <si>
-    <t>relationship--b8c173ac-8a9e-4765-bb1c-39b1ee53caac</t>
-  </si>
-  <si>
-    <t>relationship--117354e0-cd7d-484e-8756-87c5bb5fcd00</t>
-  </si>
-  <si>
-    <t>relationship--d435d200-8dbb-4172-80cb-ec869208eca5</t>
-  </si>
-  <si>
-    <t>relationship--eff1e690-9246-4cf9-b550-79f17cb29b68</t>
-  </si>
-  <si>
-    <t>relationship--9bae57d2-f5dc-42a0-836b-0f349e4cdc25</t>
-  </si>
-  <si>
-    <t>relationship--0156d507-7b40-45ec-8289-0f4fa5ba6163</t>
-  </si>
-  <si>
-    <t>relationship--33ab6ec3-19cf-4b49-8724-2b4af682af04</t>
-  </si>
-  <si>
-    <t>relationship--e1842498-5a34-4609-8db6-b2f82df3b197</t>
-  </si>
-  <si>
-    <t>relationship--719527aa-6dc8-4a61-a342-91d03a5c2d21</t>
-  </si>
-  <si>
-    <t>relationship--ba2437e9-e819-46a7-bab0-0878dbf9846d</t>
-  </si>
-  <si>
-    <t>relationship--818f6226-9afb-4912-b6a3-b69725ad0e2a</t>
-  </si>
-  <si>
-    <t>relationship--3a49096f-d797-4844-a514-37aadfb14943</t>
-  </si>
-  <si>
-    <t>relationship--a210a033-712a-4265-af86-ce866ebe8502</t>
-  </si>
-  <si>
-    <t>relationship--0e65dd55-8151-4a51-9adb-ad2b722c7b11</t>
-  </si>
-  <si>
-    <t>relationship--36958ad9-6617-44a9-ad62-03aa55bac03a</t>
-  </si>
-  <si>
-    <t>relationship--ace3997d-4e21-4b81-b6d6-147e08c0b0c2</t>
-  </si>
-  <si>
-    <t>relationship--65dfe9e2-f92b-41f5-a8d7-4d0cb775fd3c</t>
-  </si>
-  <si>
-    <t>relationship--57e70d24-0604-4783-99d1-8efa72bc229d</t>
-  </si>
-  <si>
-    <t>relationship--040c9390-eb5e-49cb-b5bf-d96b81a19376</t>
-  </si>
-  <si>
-    <t>relationship--d1bd4886-86ef-4466-a263-446fe6e1866f</t>
-  </si>
-  <si>
-    <t>relationship--f0b97568-130b-464d-8b32-c4d044aab10d</t>
-  </si>
-  <si>
-    <t>relationship--3dc31397-38e8-4bc1-bd09-06e562e88e3e</t>
-  </si>
-  <si>
-    <t>relationship--938ee97f-1383-42f4-a3fb-f79e9c820e3e</t>
-  </si>
-  <si>
-    <t>relationship--76049fb7-5bc2-4c9e-ba0e-297af2a4ef6b</t>
-  </si>
-  <si>
-    <t>relationship--ff825748-c271-4e23-981a-ace5d89e2f0d</t>
-  </si>
-  <si>
-    <t>relationship--c82e0390-57e7-451d-a05b-56a4cc08989b</t>
-  </si>
-  <si>
-    <t>relationship--777a2696-e49b-4777-9f59-3361cf2d959b</t>
-  </si>
-  <si>
-    <t>relationship--8bdae4af-4576-4585-9cc5-e67149a7a200</t>
-  </si>
-  <si>
-    <t>relationship--399137a2-b686-429b-a19e-996acc7a7bdb</t>
-  </si>
-  <si>
-    <t>relationship--78f7ba38-124d-49f4-aed3-9d01c6378d20</t>
-  </si>
-  <si>
-    <t>relationship--8e2c490b-78d0-4915-85f2-227774d6bb35</t>
-  </si>
-  <si>
-    <t>relationship--7d6fed15-cb67-4aeb-ba7e-4a5ac7f66e2e</t>
-  </si>
-  <si>
-    <t>relationship--93000c5d-435d-4b59-9bd9-6d18f4e88428</t>
-  </si>
-  <si>
-    <t>relationship--78cbaae0-d659-4816-9359-5700b0606cdf</t>
-  </si>
-  <si>
-    <t>relationship--ab8e5783-d185-4c0f-a17a-74ad9e6a2395</t>
-  </si>
-  <si>
-    <t>relationship--b2df047b-98d1-45d7-b379-53985bddf1c4</t>
-  </si>
-  <si>
-    <t>relationship--093ff580-0911-4ef5-aaae-92411c9b6597</t>
-  </si>
-  <si>
-    <t>relationship--16ee1bba-6e3c-440b-ba1f-56293093ae00</t>
-  </si>
-  <si>
-    <t>relationship--b884c378-1ffb-4f35-9e95-278a0657ecb7</t>
-  </si>
-  <si>
-    <t>relationship--f45365a5-32b0-417c-95f2-19c2f90abf3f</t>
-  </si>
-  <si>
-    <t>relationship--fbc3460b-ad11-409e-8859-f19a4ebe8d2e</t>
-  </si>
-  <si>
-    <t>relationship--d0393c1a-f522-4c8a-b58c-a9946069de19</t>
-  </si>
-  <si>
-    <t>relationship--155f9979-73ec-4eba-8808-38de97758784</t>
-  </si>
-  <si>
-    <t>relationship--f85f0758-4c57-4e59-a2b0-dd5977a28769</t>
-  </si>
-  <si>
-    <t>relationship--cc9b386b-845a-4409-a53c-e88fe3165ca7</t>
-  </si>
-  <si>
-    <t>relationship--c02574e7-28f8-4149-9e60-de548f2b2739</t>
-  </si>
-  <si>
-    <t>relationship--c70d52db-bc94-4b2e-af45-20f3874bfedd</t>
-  </si>
-  <si>
-    <t>relationship--e4d5e664-a09e-41aa-8901-163d02b7287b</t>
-  </si>
-  <si>
-    <t>relationship--3b3277ba-6e98-4c8e-8b72-d65d2c00ae61</t>
-  </si>
-  <si>
-    <t>relationship--190fb4f5-b465-4775-9528-46d207d120b2</t>
-  </si>
-  <si>
-    <t>relationship--12db5486-053c-48ed-bb49-48b1e4b11391</t>
-  </si>
-  <si>
-    <t>relationship--fc4c3558-5f44-4a25-898a-91cd7a53e0c4</t>
-  </si>
-  <si>
-    <t>relationship--32fbbc5a-d409-4e61-9a20-e1c8ef9a9f42</t>
-  </si>
-  <si>
-    <t>relationship--443f6959-879a-43a2-ae33-c42f99cf5108</t>
-  </si>
-  <si>
-    <t>relationship--63d649b8-b431-413e-b07d-eca5e0019b2a</t>
-  </si>
-  <si>
-    <t>relationship--8302cd38-5016-42ed-accb-70cdb1d2996e</t>
-  </si>
-  <si>
-    <t>relationship--461e13fb-702e-42e7-91b5-f27c6db3ea70</t>
-  </si>
-  <si>
-    <t>relationship--b85d0c7b-f276-4a67-a101-da016bce172a</t>
-  </si>
-  <si>
-    <t>relationship--b0d665a3-7b3c-4aa3-9687-a3a5368ac34e</t>
-  </si>
-  <si>
-    <t>relationship--3101592e-1242-464d-adcb-9c68c43f6ac1</t>
-  </si>
-  <si>
-    <t>relationship--6e72e46e-9f47-43db-9851-59d899089853</t>
-  </si>
-  <si>
-    <t>relationship--d872ba7d-f1bd-4e7d-83cb-4237e5a6ccae</t>
-  </si>
-  <si>
-    <t>relationship--205a45c2-7248-43c9-8fbc-b25eb7af9d3e</t>
-  </si>
-  <si>
-    <t>relationship--4b2a8dc7-2b7b-42ab-90c2-c202d6c481e9</t>
-  </si>
-  <si>
-    <t>relationship--bc9a8aa8-b287-4ec4-bb2d-5f64eadcc530</t>
-  </si>
-  <si>
-    <t>relationship--fa65970c-ac67-4d39-aaf4-cd3c7bbbadcd</t>
-  </si>
-  <si>
-    <t>relationship--b781b174-17d4-41fa-879e-962fa3c6472e</t>
-  </si>
-  <si>
-    <t>relationship--ec58069d-2af0-4181-bac9-4dddda88c28c</t>
-  </si>
-  <si>
-    <t>relationship--f8ae12cf-66ec-4c01-a250-46bb97f99c7d</t>
-  </si>
-  <si>
-    <t>relationship--6e8f3632-6158-4971-bf6c-f6b75abaa66d</t>
-  </si>
-  <si>
-    <t>relationship--3d819923-9d97-4a8b-a67c-30fde21645b9</t>
-  </si>
-  <si>
-    <t>relationship--f3e7964d-4204-43d9-95ba-a61a39073b86</t>
-  </si>
-  <si>
-    <t>relationship--a9a82add-18b6-4428-b7d4-a07995c91849</t>
-  </si>
-  <si>
-    <t>relationship--8df00cdb-e745-4f6f-b241-b40ee4cad23c</t>
-  </si>
-  <si>
-    <t>relationship--4f13473b-9a37-4531-b782-850ced97e89d</t>
-  </si>
-  <si>
-    <t>relationship--8b6fa31a-3839-49f7-9e18-677cc43b927d</t>
-  </si>
-  <si>
-    <t>relationship--2fb417b5-205b-4b9f-98fc-c9db2c7172b3</t>
-  </si>
-  <si>
-    <t>relationship--24a70091-a353-470d-81e3-cf75b2979c7c</t>
-  </si>
-  <si>
-    <t>relationship--63722a18-6f07-4a93-8e38-135c8fbcbb56</t>
-  </si>
-  <si>
-    <t>relationship--d43afa20-2d6c-47c9-abbb-fba45f539dc7</t>
-  </si>
-  <si>
-    <t>relationship--e513611f-dbb7-41ad-8e96-eeab94495952</t>
-  </si>
-  <si>
-    <t>relationship--4138b4da-9b4a-4810-8234-01f088b2ef84</t>
-  </si>
-  <si>
-    <t>relationship--187d585c-3c8c-452b-af29-a98dd6d0c790</t>
-  </si>
-  <si>
-    <t>relationship--a2a277a8-d68f-4890-b6ad-2f062fe5eb52</t>
-  </si>
-  <si>
-    <t>relationship--49bfcdee-0811-4e07-99d3-ea60966de109</t>
-  </si>
-  <si>
-    <t>relationship--f05621c7-ad01-4355-901d-20c3bed12c54</t>
-  </si>
-  <si>
-    <t>relationship--609ed9e0-8e20-4cf4-84b5-53571e3e2f02</t>
-  </si>
-  <si>
-    <t>relationship--8f712af0-daec-4fec-ac07-e716982da013</t>
-  </si>
-  <si>
-    <t>relationship--530d8452-141f-4f05-b35d-3196f6474b62</t>
-  </si>
-  <si>
-    <t>relationship--b53961b4-1ae8-4160-ae4d-42264492598d</t>
-  </si>
-  <si>
-    <t>relationship--a07a243a-5196-4d10-bd4c-6710b8b351e0</t>
-  </si>
-  <si>
-    <t>relationship--1bfa5390-07ec-418e-adf0-d1bb78d429e5</t>
-  </si>
-  <si>
-    <t>relationship--5f1bded5-3de0-4e81-8e96-b51d5bc64368</t>
-  </si>
-  <si>
-    <t>relationship--1bdc7cd5-2ee1-42f6-b684-ff7531fa9e4a</t>
-  </si>
-  <si>
-    <t>relationship--0ac78c44-7b00-4a46-8c4e-8fc97e87a671</t>
-  </si>
-  <si>
-    <t>relationship--4f149647-7dda-40a9-97d4-a0172656a6a2</t>
-  </si>
-  <si>
-    <t>relationship--9f70a209-0fce-4de7-8560-bd747b68f230</t>
-  </si>
-  <si>
-    <t>relationship--bd191415-4590-49eb-8995-1518efd9a587</t>
-  </si>
-  <si>
-    <t>relationship--d54dea5c-d6ff-4830-8a7e-5761b68f462d</t>
-  </si>
-  <si>
-    <t>relationship--2b77291f-cb53-4bb2-a480-2d675534486a</t>
-  </si>
-  <si>
-    <t>relationship--31992d27-7e29-464c-bfb4-5e6ec101ae9a</t>
-  </si>
-  <si>
-    <t>relationship--7f3df424-3f0a-4e8b-ad21-e2bb30e03b70</t>
-  </si>
-  <si>
-    <t>relationship--b210e0a4-77b8-45b4-8302-acc843eee7c9</t>
-  </si>
-  <si>
-    <t>relationship--d85132e9-70aa-46bf-b3b0-68deb7dccc03</t>
-  </si>
-  <si>
-    <t>relationship--ed82f8c0-0118-4b29-adbb-3ff2283b3758</t>
-  </si>
-  <si>
-    <t>relationship--75b01daa-79c8-41b0-aa84-e6776c9bfe7e</t>
-  </si>
-  <si>
-    <t>relationship--1ac1f0cb-ea14-4307-b3f4-c7e8c78acbb9</t>
-  </si>
-  <si>
-    <t>relationship--ce23341a-f769-4548-b480-775518d22c72</t>
-  </si>
-  <si>
-    <t>relationship--a3623915-8451-4484-a638-9cc79759edf8</t>
-  </si>
-  <si>
-    <t>relationship--f2f5d0fd-c627-4148-becf-ed7bf72046fd</t>
-  </si>
-  <si>
-    <t>relationship--da796365-b316-430f-ba32-e083db19acdd</t>
-  </si>
-  <si>
-    <t>relationship--819e7857-7f0e-42ce-89d3-ca6cf925d01c</t>
-  </si>
-  <si>
-    <t>relationship--a834fafe-2e75-43d6-9bdb-a572809b116d</t>
-  </si>
-  <si>
-    <t>relationship--f3b88869-903a-4db6-a5b4-fb5d2acd997d</t>
-  </si>
-  <si>
-    <t>relationship--683c17cc-8a59-4e91-b473-27b0791ae0ce</t>
-  </si>
-  <si>
-    <t>relationship--097b2e9c-ebb0-42ff-8f3f-663a11d77b7c</t>
-  </si>
-  <si>
-    <t>relationship--6c7003f5-9e62-45fc-a64d-fcbe0339eace</t>
-  </si>
-  <si>
-    <t>relationship--60cef4be-fc20-4e92-9dc0-b7ae246d89d8</t>
-  </si>
-  <si>
-    <t>relationship--5c73d2f3-61e2-46fb-bcd2-b62142a5d7e7</t>
-  </si>
-  <si>
-    <t>relationship--2b65c9dd-0df7-4429-8fb5-25b10f196fa3</t>
-  </si>
-  <si>
-    <t>relationship--be680fd1-cdf9-48f9-b32b-af03edcd5f49</t>
-  </si>
-  <si>
-    <t>relationship--24cd3805-31bf-4d10-bc4e-689fad4be8a7</t>
-  </si>
-  <si>
-    <t>relationship--a10a418b-47c7-4162-85f3-bfa1eace9d91</t>
-  </si>
-  <si>
-    <t>relationship--3b355b20-d54d-486f-8971-0cfe0534cd4a</t>
-  </si>
-  <si>
-    <t>relationship--82d16f2f-0a2c-4561-a6e8-4b9e36ac6e6d</t>
-  </si>
-  <si>
-    <t>relationship--dcecb634-8324-42b1-b91b-9dc407202d5c</t>
-  </si>
-  <si>
-    <t>relationship--2dedb174-ce09-4791-ac10-81a064e97e43</t>
-  </si>
-  <si>
-    <t>relationship--d06f3699-71e9-4994-aed3-fc6c1d4c103d</t>
-  </si>
-  <si>
-    <t>relationship--991acbe3-46b4-4ece-8191-6ca86a63cedd</t>
-  </si>
-  <si>
-    <t>relationship--5bff5a94-791a-438c-a7c4-898a49eda6a4</t>
-  </si>
-  <si>
-    <t>relationship--9d4c8082-15fb-49c3-a058-1e6f230473bc</t>
-  </si>
-  <si>
-    <t>relationship--9e8bd416-a9a5-4207-9acc-46f25aacbdb1</t>
-  </si>
-  <si>
-    <t>relationship--f1ba875e-abe4-43d3-bdca-9f5b299753f2</t>
-  </si>
-  <si>
-    <t>relationship--9583c8de-f3ff-4a8b-8163-dab5fb1e24ad</t>
-  </si>
-  <si>
-    <t>relationship--8d884304-83d9-4af2-a3e8-94c2e27ed308</t>
-  </si>
-  <si>
-    <t>relationship--40d7fbe3-8fbb-455c-9220-93e4002ef10d</t>
-  </si>
-  <si>
-    <t>relationship--6a628742-c864-4748-abd9-da2f3f180740</t>
-  </si>
-  <si>
-    <t>relationship--74b6a8d6-621f-4e0d-a039-7f3d7fb5cb26</t>
-  </si>
-  <si>
-    <t>relationship--e04e78cc-5f18-41d9-9898-c4c59b651beb</t>
-  </si>
-  <si>
-    <t>relationship--49cea33e-bc3f-4c27-a018-bd25a3cb90b8</t>
-  </si>
-  <si>
-    <t>relationship--075a9738-f9f7-4364-89d0-a7c6d1483457</t>
-  </si>
-  <si>
-    <t>relationship--1e5802f2-2fa3-4929-826c-8dc3240ca1f4</t>
-  </si>
-  <si>
-    <t>relationship--3cdc29c6-4557-4e25-a305-457aa88441ae</t>
-  </si>
-  <si>
-    <t>relationship--9b2d4f54-0818-4e04-bf2c-7464ff329b22</t>
-  </si>
-  <si>
-    <t>relationship--980e5e48-abdb-47df-be26-10b127e090d3</t>
-  </si>
-  <si>
-    <t>relationship--39aeec91-4b13-4530-bc9c-810361e46cb7</t>
-  </si>
-  <si>
-    <t>relationship--a4cad2fb-a5c1-498c-b6ca-2517937adb79</t>
-  </si>
-  <si>
-    <t>relationship--95e387fa-0515-4a56-a500-3fb7c415a376</t>
-  </si>
-  <si>
-    <t>relationship--c2b2e394-676e-4412-8781-3cc9d8f9621e</t>
-  </si>
-  <si>
-    <t>relationship--7b958cef-f8f4-49cf-a5b1-af13644c3252</t>
-  </si>
-  <si>
-    <t>relationship--cc4f6fe7-9aea-43a3-ba9a-e77eaa3b8d77</t>
-  </si>
-  <si>
-    <t>relationship--f93a4c95-eed0-426e-be95-9c603951319b</t>
-  </si>
-  <si>
-    <t>relationship--af47548c-8ed8-455d-a2db-0bc93f4030b3</t>
-  </si>
-  <si>
-    <t>relationship--c1745f80-3290-4984-9dd6-ee4299f490b1</t>
-  </si>
-  <si>
-    <t>relationship--d4e6d433-b83a-4fec-b78c-6470cedbed0e</t>
-  </si>
-  <si>
-    <t>relationship--baba5c19-c8f3-4534-ad1a-864f3e9c8af6</t>
-  </si>
-  <si>
-    <t>relationship--cf4ec701-fa7a-4fba-bd7a-851429b88cc0</t>
-  </si>
-  <si>
-    <t>relationship--6dae93ac-f5ef-4b59-82f3-78dcabd8e94e</t>
-  </si>
-  <si>
-    <t>relationship--0b279b18-ce31-4fa5-8f87-6a4a394eb886</t>
-  </si>
-  <si>
-    <t>relationship--0a58485f-695b-4ea9-808d-ab4d235463e3</t>
-  </si>
-  <si>
-    <t>relationship--848bdfbe-75d2-472f-9331-3d956b9d7322</t>
-  </si>
-  <si>
-    <t>relationship--2c5c1c46-398a-40aa-9914-2449ea6edf94</t>
-  </si>
-  <si>
-    <t>relationship--21a7018b-055f-4605-8b79-32213036025a</t>
-  </si>
-  <si>
-    <t>relationship--ad35db0d-4857-4207-a772-86ae1524bc73</t>
-  </si>
-  <si>
-    <t>relationship--c054d111-0cab-4194-b81b-602738e62f1e</t>
-  </si>
-  <si>
-    <t>relationship--335c70ce-5be3-43b9-a53f-6ccf0002bf1c</t>
-  </si>
-  <si>
-    <t>relationship--6ea1a5d4-7467-4b7d-948f-21a358049e4d</t>
-  </si>
-  <si>
-    <t>relationship--e6bad643-553c-4ba0-bc40-264d85592851</t>
-  </si>
-  <si>
-    <t>relationship--7a9d0203-aef0-41b5-bb77-00a1a902ee42</t>
-  </si>
-  <si>
-    <t>relationship--c89c0b7a-f023-479e-9753-40097186f046</t>
-  </si>
-  <si>
-    <t>relationship--e04b5366-8c23-448d-9b88-fe56bd29942d</t>
-  </si>
-  <si>
-    <t>relationship--2ed74d6a-11c8-4f33-bd08-1ec2f25bd0b7</t>
-  </si>
-  <si>
-    <t>relationship--a785db23-c56a-4693-beda-7dcf166e6227</t>
-  </si>
-  <si>
-    <t>relationship--2f92b345-b9fc-4643-898b-3904e77069bf</t>
-  </si>
-  <si>
-    <t>relationship--b1c463fa-8f1a-4b77-9a65-16e5852c003c</t>
-  </si>
-  <si>
-    <t>relationship--d374ff17-73dd-4ac7-8381-62eed7137469</t>
-  </si>
-  <si>
-    <t>relationship--72d78c0d-8e6f-437f-92a7-4c076720dece</t>
-  </si>
-  <si>
-    <t>relationship--116a18fb-8c67-4fe1-a7ca-986001ce149f</t>
-  </si>
-  <si>
-    <t>relationship--53d0fca9-36f5-4eda-8632-d72031d8d198</t>
-  </si>
-  <si>
-    <t>relationship--a125c3e6-5ea4-416d-81b4-c0169bf5d36d</t>
-  </si>
-  <si>
-    <t>relationship--eda34a23-d83c-44f9-936c-c8e3107288a3</t>
-  </si>
-  <si>
-    <t>relationship--4f5120eb-12a6-4033-8c98-af20365d4fd1</t>
-  </si>
-  <si>
-    <t>relationship--3bc86575-0c4b-490a-b373-68bec683add4</t>
-  </si>
-  <si>
-    <t>relationship--f87d3aef-083b-4d69-8745-50345d6587f3</t>
-  </si>
-  <si>
-    <t>relationship--c90f8eeb-d6b2-44fd-9b02-e3e18e6db474</t>
-  </si>
-  <si>
-    <t>relationship--36650039-0241-4c19-9659-3ca5f72971de</t>
-  </si>
-  <si>
-    <t>relationship--18089baf-d9c4-482b-ac26-91bfd97eb777</t>
-  </si>
-  <si>
-    <t>relationship--fc13aee5-9eaa-449e-ae59-330eb32fea05</t>
-  </si>
-  <si>
-    <t>relationship--c947d95f-8656-4324-b486-cd13ca0927cc</t>
-  </si>
-  <si>
-    <t>relationship--b336cb42-3bb1-435c-846f-0c00febf1277</t>
-  </si>
-  <si>
-    <t>relationship--ce900a33-70c5-4a1a-9781-c87b88e967b2</t>
-  </si>
-  <si>
-    <t>relationship--933b2afa-e26f-4aa9-ad59-5e3f5125e589</t>
-  </si>
-  <si>
-    <t>relationship--18c57bf7-ae3c-4657-9739-d786015969e2</t>
-  </si>
-  <si>
-    <t>relationship--852be3d7-aa50-47cc-8650-4d1d96e5eada</t>
-  </si>
-  <si>
-    <t>relationship--fc878e7d-9269-4bc0-9a8d-5bd96a8a21e3</t>
-  </si>
-  <si>
-    <t>relationship--cea2cea0-ad64-4fb2-9ec3-2f0703d860fe</t>
-  </si>
-  <si>
-    <t>relationship--a1b44447-6383-44a1-8be5-4c130931885d</t>
-  </si>
-  <si>
-    <t>relationship--aa2208c4-3aa8-4b41-b43b-881b9da22239</t>
-  </si>
-  <si>
-    <t>relationship--660f2aca-acdb-4d7a-a623-c1c4bd072590</t>
-  </si>
-  <si>
-    <t>relationship--16250663-d5c7-44a0-b47d-51e08be54785</t>
-  </si>
-  <si>
-    <t>relationship--b21c33d5-2489-4693-bbc8-d90ac913967f</t>
-  </si>
-  <si>
-    <t>relationship--790eea08-3f25-4d6b-b2ca-194bd4040dbc</t>
-  </si>
-  <si>
-    <t>relationship--09747095-11f6-42fe-80c9-035fe244f624</t>
-  </si>
-  <si>
-    <t>relationship--678ca8eb-6f43-4ac7-9e5f-c0d16ada12cb</t>
-  </si>
-  <si>
-    <t>relationship--507287f7-225d-4c78-8250-18934f0ad3b0</t>
-  </si>
-  <si>
-    <t>relationship--4fa18265-9a9c-4b4b-9221-f87ee590b740</t>
-  </si>
-  <si>
-    <t>relationship--9974065b-d135-4983-bc93-6d4c8a41ccfa</t>
-  </si>
-  <si>
-    <t>relationship--366bb653-b0cb-4f76-a261-cc1acf7b2786</t>
-  </si>
-  <si>
-    <t>relationship--852dfeaa-f92c-4b07-b20b-6666060cb1f6</t>
-  </si>
-  <si>
-    <t>relationship--9dbb42b0-39e3-4c8f-a726-522c83944680</t>
-  </si>
-  <si>
-    <t>relationship--45bbf762-8c52-4374-a5f3-ae6ed92beacc</t>
-  </si>
-  <si>
-    <t>relationship--6451fe6f-8f1e-474b-b36c-37bfb8d171d3</t>
-  </si>
-  <si>
-    <t>relationship--52d6dae1-ae2a-413f-9b16-93ec199212fb</t>
-  </si>
-  <si>
-    <t>relationship--68afc738-9241-447a-b99e-c7d1fd301ed0</t>
-  </si>
-  <si>
-    <t>relationship--aba19d3c-eb07-4976-b2a8-3e5e01b1baf3</t>
-  </si>
-  <si>
-    <t>relationship--57d02153-c6a4-4528-a314-c22631dd526d</t>
-  </si>
-  <si>
-    <t>relationship--8922e0b6-24f5-451e-b25b-7792c71f272b</t>
-  </si>
-  <si>
-    <t>relationship--b79e8b45-b8c8-464a-a735-141b2bc48e92</t>
-  </si>
-  <si>
-    <t>relationship--d21e5e1f-dd33-41ec-8df7-4d2d800a09a8</t>
-  </si>
-  <si>
-    <t>relationship--677dfe65-b189-4f72-ab09-4df65c1c1d7b</t>
-  </si>
-  <si>
-    <t>relationship--7162dd20-7933-48a5-884d-00783ffe735d</t>
-  </si>
-  <si>
-    <t>relationship--502fed6c-2913-48a0-bef8-448cd530e753</t>
-  </si>
-  <si>
-    <t>relationship--3c219078-acd9-4d8b-8b01-326313855dc2</t>
-  </si>
-  <si>
-    <t>relationship--01c0f813-b9e4-4596-9e78-fd93563ca609</t>
-  </si>
-  <si>
-    <t>relationship--fe7ccf7a-c024-4340-8ba2-4e919213a8c6</t>
-  </si>
-  <si>
-    <t>relationship--8088ae80-0e2d-4653-a2e1-c1c29f777a4c</t>
-  </si>
-  <si>
-    <t>relationship--90a37a3a-9577-49fc-9989-771444e7c56a</t>
-  </si>
-  <si>
-    <t>relationship--9d0a828d-f81f-4601-9850-d3564b968a54</t>
-  </si>
-  <si>
-    <t>relationship--dd1598cd-ec13-4064-a1c7-e16f7a81aa74</t>
-  </si>
-  <si>
-    <t>relationship--ecd69714-1d25-43cd-a432-f70962a54b62</t>
-  </si>
-  <si>
-    <t>relationship--106ad2d5-ed5a-4680-b28d-e40e2c73fb1a</t>
-  </si>
-  <si>
-    <t>relationship--6aee2f28-8a03-4e64-9700-7f07e73500ba</t>
-  </si>
-  <si>
-    <t>relationship--d2f0e81a-2057-4e93-ab36-c61afef37fd7</t>
-  </si>
-  <si>
-    <t>relationship--40ec47e6-77e6-42b8-8a25-7853fe687141</t>
-  </si>
-  <si>
-    <t>relationship--5536f8ea-dade-4bfb-8665-3958d824469d</t>
-  </si>
-  <si>
-    <t>relationship--5b39901b-f285-4060-a711-77c092bbeeca</t>
-  </si>
-  <si>
-    <t>relationship--0d5d3c2a-9dd4-47c5-939d-3b1ada5f714b</t>
-  </si>
-  <si>
-    <t>relationship--c356afec-73f2-4a7c-b4ac-87686f124c98</t>
-  </si>
-  <si>
-    <t>relationship--d65586b6-8843-436b-868b-5643747c1458</t>
-  </si>
-  <si>
-    <t>relationship--c9514420-06b6-411d-b29d-698d7c0c32a5</t>
-  </si>
-  <si>
-    <t>relationship--8595d180-0b01-4d71-81fc-50c503a5cc7c</t>
-  </si>
-  <si>
-    <t>relationship--c9595494-ee98-4a68-8948-aae74bc0a24e</t>
-  </si>
-  <si>
-    <t>relationship--422c3b87-86fe-48d9-a056-fed6294e1b0c</t>
-  </si>
-  <si>
-    <t>relationship--fe24862b-3be8-4d94-a070-5f31d2561b03</t>
-  </si>
-  <si>
-    <t>relationship--10e845b5-afc8-47c4-898d-65db358fd2f9</t>
-  </si>
-  <si>
-    <t>relationship--d60c19e7-f755-4610-8537-2984ee4bc95b</t>
-  </si>
-  <si>
-    <t>relationship--460e3f22-5e70-4e1a-ae77-4d4e519fa881</t>
-  </si>
-  <si>
-    <t>relationship--4b4eeb4e-46d4-4f71-96d8-d0026bba1ed8</t>
-  </si>
-  <si>
-    <t>relationship--fb629e4a-e6f2-46bb-b4c0-49f44f821092</t>
-  </si>
-  <si>
-    <t>relationship--df1ce40a-dac8-45ed-b042-05dfc77c05bb</t>
-  </si>
-  <si>
-    <t>relationship--89e96d40-fea4-40bf-8ce4-85129bc59274</t>
-  </si>
-  <si>
-    <t>relationship--675aae63-9167-444e-bfe1-06d0b895a842</t>
-  </si>
-  <si>
-    <t>relationship--0283d952-9f00-413f-ba8f-8ee476a1dbc1</t>
-  </si>
-  <si>
-    <t>relationship--95ea5184-bb3b-43a1-8782-cd81e17d7263</t>
-  </si>
-  <si>
-    <t>relationship--2d86f586-095d-4616-9fe3-7a14d4e2cae2</t>
-  </si>
-  <si>
-    <t>relationship--11324577-43b4-4627-ad35-aa562a54c341</t>
-  </si>
-  <si>
-    <t>relationship--bfbbd33a-e5e1-4852-9306-1d7c43b641ee</t>
-  </si>
-  <si>
-    <t>relationship--f35ecf84-ea47-4385-a2b3-48d5e21387d8</t>
-  </si>
-  <si>
-    <t>relationship--7104efed-9524-4ecc-b0f9-a417774f8d6a</t>
-  </si>
-  <si>
-    <t>relationship--5e7fd10d-6c05-4c29-be4d-41386fa93ee2</t>
-  </si>
-  <si>
-    <t>relationship--26ae8fdd-f418-4e90-a1cb-0514e89f5396</t>
-  </si>
-  <si>
-    <t>relationship--0c8f00b9-4929-4a91-9e67-f2287a69961d</t>
-  </si>
-  <si>
-    <t>relationship--e1d35297-ead4-43c0-b8bd-886275c5b1a1</t>
-  </si>
-  <si>
-    <t>relationship--4e84a9a4-8941-4267-aa48-5d7635ccb758</t>
-  </si>
-  <si>
-    <t>relationship--992593de-3273-45fc-815b-0f71e42c59c3</t>
-  </si>
-  <si>
-    <t>relationship--d9d53a8e-ad3d-4ae1-8626-a2e101cb53bc</t>
-  </si>
-  <si>
-    <t>relationship--42dc016f-7e38-40f2-862b-d1407135e1ba</t>
-  </si>
-  <si>
-    <t>relationship--548c662b-e702-454d-894d-aa00bd15daee</t>
-  </si>
-  <si>
-    <t>relationship--3c8c661d-e662-420b-87c9-1e78cce48160</t>
-  </si>
-  <si>
-    <t>relationship--8d5ce96b-3e5a-46b5-986e-066f30e7d102</t>
-  </si>
-  <si>
-    <t>relationship--c9b11839-0972-4c4f-a08d-5ad4edcd08a8</t>
-  </si>
-  <si>
-    <t>relationship--0715ddc8-2bc3-4465-8dec-19f8a5fca47d</t>
-  </si>
-  <si>
-    <t>relationship--18e9ee37-32eb-40c7-ba80-6603163572a4</t>
-  </si>
-  <si>
-    <t>relationship--e38c7839-a190-4247-814f-b87bc7c09c4e</t>
-  </si>
-  <si>
-    <t>relationship--cb5bb378-e4f8-4018-894a-ba6e6eb56939</t>
-  </si>
-  <si>
-    <t>relationship--624b4a09-8d37-41e3-a5f5-4d7dd67fbd34</t>
-  </si>
-  <si>
-    <t>relationship--473143d3-de77-484c-8794-06621a40f738</t>
-  </si>
-  <si>
-    <t>relationship--96c1b3a1-7e12-4e2f-9d37-f6fae16a6c22</t>
-  </si>
-  <si>
-    <t>relationship--3cb7fc74-614e-4d58-a946-c344a9a8f7e1</t>
-  </si>
-  <si>
-    <t>relationship--b8fb19c3-7a18-4353-8692-77753d25b876</t>
-  </si>
-  <si>
-    <t>relationship--4e6e6dda-1ef8-48bc-9fec-6168a81ba00a</t>
-  </si>
-  <si>
-    <t>relationship--8264538f-bef4-4f84-bf9f-021cac6c2c6d</t>
-  </si>
-  <si>
-    <t>relationship--131c51bd-34b1-4f67-b7d8-fa840fc69750</t>
-  </si>
-  <si>
-    <t>relationship--33f9b731-538b-4627-930f-eec899282ce8</t>
-  </si>
-  <si>
-    <t>relationship--a8bbf553-d68c-416e-ab2e-db8d7b010d8c</t>
-  </si>
-  <si>
-    <t>relationship--79e705c1-4fd7-4e27-b889-0fe04825fd33</t>
-  </si>
-  <si>
-    <t>relationship--1194a81b-5134-4fe9-bba4-65b9b1d80a69</t>
-  </si>
-  <si>
-    <t>relationship--2572aa85-70c9-4048-af8e-a800a6b9019a</t>
-  </si>
-  <si>
-    <t>relationship--44c1b005-058c-4fc8-9fa6-4bfb6b77ab72</t>
-  </si>
-  <si>
-    <t>relationship--9379159d-ac2b-46a4-b4e1-446d885f0b8a</t>
-  </si>
-  <si>
-    <t>relationship--fd0c1b84-2b4b-4e53-bef5-c90ddd5bf36a</t>
-  </si>
-  <si>
-    <t>relationship--a8538c78-7fe9-4005-af59-b1cb97e9bbe6</t>
-  </si>
-  <si>
-    <t>relationship--fc975dd9-2a58-413d-bef4-8f326dadc42d</t>
-  </si>
-  <si>
-    <t>relationship--cf237a49-124f-450d-9f82-6687bf7c2bbd</t>
-  </si>
-  <si>
-    <t>relationship--34433b84-24b7-46db-8a89-69d5c1842212</t>
-  </si>
-  <si>
-    <t>relationship--1056ae9d-16ed-4245-936e-fb1f0ea739fc</t>
-  </si>
-  <si>
-    <t>relationship--bb17a815-48e7-41d2-a2d7-ced0649b6a72</t>
-  </si>
-  <si>
-    <t>relationship--88d66211-d6e8-43e0-bce4-73b5ccf11cfe</t>
-  </si>
-  <si>
-    <t>relationship--ad816f19-7ef4-42ad-a0d8-6f3cdc5dc7b5</t>
-  </si>
-  <si>
-    <t>relationship--b0b9fa79-b8c6-4d56-91af-e78ae8868a18</t>
-  </si>
-  <si>
-    <t>relationship--a65db1f2-21ff-424b-a521-2050ca1f3b09</t>
-  </si>
-  <si>
-    <t>relationship--cc771afe-611a-412f-a747-fc87cc56f804</t>
-  </si>
-  <si>
-    <t>relationship--f931f4cc-b4b2-4a74-bf94-42588c3b19b9</t>
-  </si>
-  <si>
-    <t>relationship--46cbb067-12a0-4002-affb-9787f3ae6286</t>
-  </si>
-  <si>
-    <t>relationship--03eaa6f9-e266-4cda-aa1f-8e47162842b0</t>
-  </si>
-  <si>
-    <t>relationship--79c0ba76-7d1e-4ce1-a4b7-adbe4dc0495f</t>
-  </si>
-  <si>
-    <t>relationship--81eaafe9-f9b7-4ce4-a525-fdb78fc968f3</t>
-  </si>
-  <si>
-    <t>relationship--d1a55c8c-6e2b-4faf-b8f3-de995fe69739</t>
-  </si>
-  <si>
-    <t>relationship--d9c02db0-bbab-4ea0-b9ae-c95bf97f8432</t>
-  </si>
-  <si>
-    <t>relationship--ba81173b-aefd-40d5-aac2-400c5329a8bf</t>
-  </si>
-  <si>
-    <t>relationship--431549c5-c30a-400a-a674-46bda0e54599</t>
-  </si>
-  <si>
-    <t>relationship--f05c1e28-7669-45a0-8ecb-8a24b74120d2</t>
-  </si>
-  <si>
-    <t>relationship--693adc63-b1db-4758-a2d7-d21c854c50a4</t>
-  </si>
-  <si>
-    <t>relationship--1ab306f6-f695-4873-b3fa-10c2176c1305</t>
-  </si>
-  <si>
-    <t>relationship--6a9f86b8-a71d-429c-b08f-84ccfae7f31b</t>
-  </si>
-  <si>
-    <t>relationship--df29b69f-0ced-4fc0-b6c8-94434e751e36</t>
-  </si>
-  <si>
-    <t>relationship--2f8a5ca2-f944-4f76-a6ff-435cc073cef6</t>
-  </si>
-  <si>
-    <t>relationship--c8c060f6-4af2-4b4b-8340-d5f24e6448fc</t>
-  </si>
-  <si>
-    <t>relationship--62ccfc5c-2e25-4fd4-82fd-1e09115778a5</t>
-  </si>
-  <si>
-    <t>relationship--a602df81-ddcb-4bc9-ada4-23b1daf04e19</t>
-  </si>
-  <si>
-    <t>relationship--48e7cb0d-f697-4853-93ca-855cf57b6b7f</t>
-  </si>
-  <si>
-    <t>relationship--71ceb742-b2c2-4c6e-93c4-b6396eb1203a</t>
-  </si>
-  <si>
-    <t>relationship--120f6ccb-a375-455f-8b5d-4660f7d8f703</t>
-  </si>
-  <si>
-    <t>relationship--b1cfc045-f959-45e5-8a1e-4e75a6a3ac06</t>
-  </si>
-  <si>
-    <t>relationship--3a7d524e-bc71-446e-8008-02a27f3537d7</t>
-  </si>
-  <si>
-    <t>relationship--3f7db20f-12f2-4e3e-83d9-c7039d9f2862</t>
-  </si>
-  <si>
-    <t>relationship--eb5ce8c1-f59b-4ad0-b0df-63feed62464d</t>
-  </si>
-  <si>
-    <t>relationship--af84b5a3-d24a-4407-8944-31ac8f69fa7d</t>
-  </si>
-  <si>
-    <t>relationship--374ef7fd-766a-4b89-9c40-7c85da4864aa</t>
-  </si>
-  <si>
-    <t>relationship--6c3336c0-2dec-46e9-a424-b86461f6719c</t>
-  </si>
-  <si>
-    <t>relationship--e8c953da-2943-46e0-b7ae-cffe3bf274b4</t>
-  </si>
-  <si>
-    <t>relationship--6b497a64-0f53-4b22-a8f3-b8c42489ff57</t>
-  </si>
-  <si>
-    <t>relationship--2b21c131-5910-4163-8e65-5cedc0d9a624</t>
-  </si>
-  <si>
-    <t>relationship--7d51687b-6630-4fea-be92-b2aa8af5a624</t>
-  </si>
-  <si>
-    <t>relationship--1e67e6e6-b2ca-4f65-a822-a322d24f1f34</t>
-  </si>
-  <si>
-    <t>relationship--5b5be8c6-1acd-4481-b4a5-6cfaf12bf30c</t>
-  </si>
-  <si>
-    <t>relationship--b6b93397-50d8-4cbc-aa34-5a4ae18fe1f6</t>
-  </si>
-  <si>
-    <t>relationship--449039e3-2d6c-4747-950f-150777d01333</t>
-  </si>
-  <si>
-    <t>relationship--c77fe291-d151-4070-9216-0a4c3cb6ab6d</t>
-  </si>
-  <si>
-    <t>relationship--60422152-5817-4023-9554-55b6804ab0b3</t>
-  </si>
-  <si>
-    <t>relationship--30720fdc-5bbe-47fb-977a-b11b297a5789</t>
-  </si>
-  <si>
-    <t>relationship--a8711592-b934-4a3b-869b-18e5476eab29</t>
-  </si>
-  <si>
-    <t>relationship--dd35529a-4997-46ec-a5dd-da669f251d73</t>
-  </si>
-  <si>
-    <t>relationship--88d3266c-359b-4c7b-8e8f-d7629066ae51</t>
-  </si>
-  <si>
-    <t>relationship--5db7225b-a9bc-4701-87eb-4e7dd112c8ba</t>
-  </si>
-  <si>
-    <t>relationship--2f5a4e73-7bad-4088-9e28-70f12bfdf432</t>
-  </si>
-  <si>
-    <t>relationship--8353609f-ce10-446d-84f7-8c21c9f7f096</t>
-  </si>
-  <si>
-    <t>relationship--23ccab69-3f81-4c46-80fe-33f7a22e1c62</t>
-  </si>
-  <si>
-    <t>relationship--cc29b464-6b26-4da3-8915-73f02e530701</t>
-  </si>
-  <si>
-    <t>relationship--f1a8948f-16ab-451c-acc1-3238d76022c1</t>
-  </si>
-  <si>
-    <t>relationship--6fda1ee2-0726-4007-b48a-1945a93298c2</t>
-  </si>
-  <si>
-    <t>relationship--fb5eb070-ce49-4baf-8088-567ec8758a73</t>
-  </si>
-  <si>
-    <t>relationship--c33588fa-3c04-41d7-880f-4d5ba3a62257</t>
-  </si>
-  <si>
-    <t>relationship--1b293662-380b-49c4-a5cf-82d5b88fb365</t>
-  </si>
-  <si>
-    <t>relationship--c356e43d-81d8-422a-a923-9440186d5da8</t>
-  </si>
-  <si>
-    <t>relationship--f7088fba-e1b9-40e8-80ab-74732a0142b7</t>
-  </si>
-  <si>
-    <t>relationship--784277fe-fbd4-4804-b281-b35b465246f2</t>
-  </si>
-  <si>
-    <t>relationship--6b0db16c-fe90-433b-9d21-1873f4107b5e</t>
-  </si>
-  <si>
-    <t>relationship--78496c31-9c7b-41f9-885d-a11935a3c801</t>
-  </si>
-  <si>
-    <t>relationship--f1dcf389-f9cb-4c56-933a-254856a5c22c</t>
-  </si>
-  <si>
-    <t>relationship--810487dc-e56a-4f46-9916-38ebc608b03f</t>
-  </si>
-  <si>
-    <t>relationship--f3376006-b855-4134-9112-259ce1e4f288</t>
-  </si>
-  <si>
-    <t>relationship--90dcc9ee-f45d-4ea8-8061-e9f01669e772</t>
-  </si>
-  <si>
-    <t>relationship--82c5ad2b-327a-48d2-9a27-6698ca60d175</t>
-  </si>
-  <si>
-    <t>relationship--43f6f3e4-1036-4136-a44f-ad84b138390e</t>
-  </si>
-  <si>
-    <t>relationship--08322f90-a8fc-426c-85d9-787500a60d63</t>
-  </si>
-  <si>
-    <t>relationship--f1cb7b2d-0e2f-4563-8b20-e4664fcc34bb</t>
-  </si>
-  <si>
-    <t>relationship--fbe68433-0c9f-4840-94e3-d5dcd921bb10</t>
-  </si>
-  <si>
-    <t>relationship--ed94bec6-c33a-4161-8f91-bcf071c6eb46</t>
-  </si>
-  <si>
-    <t>relationship--2acd4183-f1fe-48a6-8591-b5be8c2c1488</t>
-  </si>
-  <si>
-    <t>relationship--46db6129-0cf5-41c0-b746-870a9da6c6ca</t>
-  </si>
-  <si>
-    <t>relationship--bb438ef2-f8aa-459b-92e7-15f651028dc5</t>
-  </si>
-  <si>
-    <t>relationship--8dc26f58-662b-4697-a121-4f14c80f0be0</t>
-  </si>
-  <si>
-    <t>relationship--43158157-4152-4ba8-8e5e-fa2fe3e48843</t>
-  </si>
-  <si>
-    <t>relationship--4e006450-1794-40a0-b790-0426bf3f4f6e</t>
-  </si>
-  <si>
-    <t>relationship--20b2cbd3-7083-47d5-a549-7b97aa39bd94</t>
-  </si>
-  <si>
-    <t>relationship--0fb09034-a316-4985-a7be-a8b1b6f9f165</t>
-  </si>
-  <si>
-    <t>relationship--3635be6e-c8e2-40e3-a500-2c53ae904742</t>
-  </si>
-  <si>
-    <t>relationship--2339f969-9e4a-48cd-b14d-299aa821a93f</t>
-  </si>
-  <si>
-    <t>relationship--6bc3b7e8-4234-4413-ae0e-93fad72efc1b</t>
-  </si>
-  <si>
-    <t>relationship--474974cd-7096-4155-836a-3372bb9adef3</t>
-  </si>
-  <si>
-    <t>relationship--23a630c9-f4cf-4ce9-8e27-bf98c563755c</t>
-  </si>
-  <si>
-    <t>relationship--dcaa3cde-6bee-492b-97c8-93219168c428</t>
-  </si>
-  <si>
-    <t>relationship--fef63a3e-9e07-446a-8024-4189414ee178</t>
-  </si>
-  <si>
-    <t>relationship--fab72703-5abc-424a-a91c-600f9eeec639</t>
-  </si>
-  <si>
-    <t>relationship--8c9a605b-d389-4590-9f50-126b1476878b</t>
-  </si>
-  <si>
-    <t>relationship--05993f87-bf71-48b7-843d-65a2839b8038</t>
-  </si>
-  <si>
-    <t>relationship--340d16ba-6b7f-4fde-951a-0fb9bad84f14</t>
-  </si>
-  <si>
-    <t>relationship--f77f3771-804e-45c0-80f4-aa0ba8e33152</t>
-  </si>
-  <si>
-    <t>relationship--d494703e-bdbd-4f63-9e09-a860b0d04a45</t>
-  </si>
-  <si>
-    <t>relationship--f091b18f-7bbd-436d-b795-9853f63d2c06</t>
-  </si>
-  <si>
-    <t>relationship--113a4168-01dc-4c6c-b534-60e9b6103f40</t>
-  </si>
-  <si>
-    <t>relationship--56736bee-e40d-49ea-b8e4-8d28f52e7019</t>
-  </si>
-  <si>
-    <t>relationship--a95adb07-cba8-4748-a590-4fa4597cc2e0</t>
-  </si>
-  <si>
-    <t>relationship--5165809e-c747-4c3e-b8b5-187ebb59a4e1</t>
-  </si>
-  <si>
-    <t>relationship--fa984c1e-b337-45d2-9f9a-35d3da33bb84</t>
-  </si>
-  <si>
-    <t>relationship--6bd93943-6fb5-4944-b871-3cb306b0d8f5</t>
-  </si>
-  <si>
-    <t>relationship--f37ac11b-8ba3-4ed7-ab5c-779ab658ac71</t>
-  </si>
-  <si>
-    <t>relationship--234a532e-ce20-42ae-a7d3-b9ff7d26f67e</t>
-  </si>
-  <si>
-    <t>relationship--199c76ae-e3bb-43f0-80bf-cbcc8a279774</t>
-  </si>
-  <si>
-    <t>relationship--080f2018-4093-4255-8e61-fd187c804ddc</t>
-  </si>
-  <si>
-    <t>relationship--94abd5d6-363e-4bcb-b2ba-086a4e0efd34</t>
-  </si>
-  <si>
-    <t>relationship--d9a22fc3-bce5-46e7-bf71-d6a9dc72096e</t>
-  </si>
-  <si>
-    <t>relationship--634aecb6-4c9e-411c-85fc-65a86519645e</t>
-  </si>
-  <si>
-    <t>relationship--7a66b59e-63b3-44e3-8ab7-30fb93e70030</t>
-  </si>
-  <si>
-    <t>relationship--82b33b34-5a06-4928-bd23-5bc7b7877f2c</t>
-  </si>
-  <si>
-    <t>relationship--93ecb16d-3498-42b1-b96f-5b2f99e0066d</t>
-  </si>
-  <si>
-    <t>relationship--4d1bdeb5-c434-407b-9ec3-545b82703cdb</t>
-  </si>
-  <si>
-    <t>relationship--a6589388-5be1-469d-8283-ba853387ec2d</t>
-  </si>
-  <si>
-    <t>relationship--7d27df0e-2a93-48f7-8d2b-0779279990e7</t>
-  </si>
-  <si>
-    <t>relationship--aebeed5c-1b6f-4ddd-b270-80ed5a8fe855</t>
-  </si>
-  <si>
-    <t>relationship--858b9702-4376-47fe-8a89-25ef646ca9ec</t>
-  </si>
-  <si>
-    <t>relationship--33f740b8-88b6-479e-925a-1427d3974c96</t>
-  </si>
-  <si>
-    <t>relationship--aaf29cd8-ec5a-4f55-aae4-c4058fbad0b1</t>
-  </si>
-  <si>
-    <t>relationship--928ce81b-cdb4-4a64-b856-596f0237f31a</t>
-  </si>
-  <si>
-    <t>relationship--d511b6f2-e2bd-45c2-aa81-fab304c95498</t>
-  </si>
-  <si>
-    <t>relationship--c506a666-6acd-4ed3-8446-d208a9994676</t>
-  </si>
-  <si>
-    <t>relationship--5629044e-11ea-43ce-b553-d53ba7ceebfc</t>
-  </si>
-  <si>
-    <t>relationship--63209b40-aefd-465e-bb8c-292a6db66960</t>
-  </si>
-  <si>
-    <t>relationship--8f341786-757e-478b-8d08-c03f32a9dad6</t>
-  </si>
-  <si>
-    <t>relationship--78410111-368b-4bde-a7dc-75f718d0feac</t>
-  </si>
-  <si>
-    <t>relationship--19726ca7-9360-4b05-9bda-1597046cad49</t>
-  </si>
-  <si>
-    <t>relationship--bb009c88-365d-4fab-bf01-19c7661e62af</t>
-  </si>
-  <si>
-    <t>relationship--77b46dc8-4a63-44dd-9bd7-031969ec253c</t>
-  </si>
-  <si>
-    <t>relationship--5bde57b1-9715-42f1-b049-e06f015a1772</t>
-  </si>
-  <si>
-    <t>relationship--a14a9035-fa57-4d41-89f7-891ac9fcf81f</t>
-  </si>
-  <si>
-    <t>relationship--1c1b685c-3181-4352-b249-432542879ed6</t>
-  </si>
-  <si>
-    <t>relationship--475161f8-6686-424b-9917-db6889a0fcf3</t>
-  </si>
-  <si>
-    <t>relationship--13ac5123-1a57-4b3a-8d5a-662c89bf41a2</t>
-  </si>
-  <si>
-    <t>relationship--f5209d1a-7895-4020-acae-5dc4e5d8bfc0</t>
-  </si>
-  <si>
-    <t>relationship--5ee5526e-96eb-41af-b8b8-c90b91e64049</t>
-  </si>
-  <si>
-    <t>relationship--3be37c13-b9bc-47bb-8653-fa401dabd4e7</t>
-  </si>
-  <si>
-    <t>relationship--b0c2c062-c89e-4085-8716-bad67e98026e</t>
-  </si>
-  <si>
-    <t>relationship--31fd82da-dfa8-42b5-95dd-f168e6627746</t>
-  </si>
-  <si>
-    <t>relationship--2c5e4520-1275-4ab3-a9a8-2e2b1e964c13</t>
-  </si>
-  <si>
-    <t>relationship--b55647cc-a783-4225-b64b-618bc0c73e2b</t>
-  </si>
-  <si>
-    <t>relationship--6014c6c0-0579-4b5e-a854-2e87b36442cf</t>
-  </si>
-  <si>
-    <t>relationship--9c8d906b-4588-4163-b779-c3b8321985df</t>
-  </si>
-  <si>
-    <t>relationship--1419cb9b-276d-4b72-a3f1-6788f5712c97</t>
-  </si>
-  <si>
-    <t>relationship--a0a599d6-96f3-46a9-8021-f95ca90c5c60</t>
-  </si>
-  <si>
-    <t>relationship--422caa87-ac34-4167-80a3-e3f294b52304</t>
-  </si>
-  <si>
-    <t>relationship--d95d1848-9eb8-41a1-9eb4-0dab6d9b048c</t>
-  </si>
-  <si>
-    <t>relationship--c8ddd7ea-ed8e-4c46-8d00-0188061a5430</t>
-  </si>
-  <si>
-    <t>relationship--b4237490-0e8a-46d4-95a6-1cdaa172bcc8</t>
-  </si>
-  <si>
-    <t>relationship--6d106e24-cb8f-42ae-8ea2-c24c3ac66a5e</t>
-  </si>
-  <si>
-    <t>relationship--d3e614da-a65e-49a8-b28c-1bda5c4ff9ad</t>
-  </si>
-  <si>
-    <t>relationship--673fe51c-7945-423e-9767-3b824d79a43f</t>
-  </si>
-  <si>
-    <t>relationship--b4b464b3-2e82-48ba-b3e5-8680a6803204</t>
-  </si>
-  <si>
-    <t>relationship--ec2419f7-91b8-4498-b50c-0deec7e9eed4</t>
-  </si>
-  <si>
-    <t>relationship--62fc2c5e-3c4f-4760-ba3a-320af5a52635</t>
-  </si>
-  <si>
-    <t>relationship--5c3c5267-b7aa-47e8-a640-d413fe3d0e2b</t>
-  </si>
-  <si>
-    <t>relationship--559bac5f-e601-4430-a4d1-3e40065ec036</t>
-  </si>
-  <si>
-    <t>relationship--aaed89ae-ca29-4a00-9e21-1cc9143a649e</t>
-  </si>
-  <si>
-    <t>relationship--acd4d015-7a92-4a60-8741-9e316340e075</t>
-  </si>
-  <si>
-    <t>relationship--3d963d7d-a454-4e0a-9940-35584a671824</t>
-  </si>
-  <si>
-    <t>relationship--e1c4bbc4-90c4-48de-8589-c0a639fef400</t>
-  </si>
-  <si>
-    <t>relationship--14ff5c13-bd58-4f3e-8847-116ab3781971</t>
-  </si>
-  <si>
-    <t>relationship--b8a1efd8-c26a-40b5-aee5-821ce44b4e16</t>
-  </si>
-  <si>
-    <t>relationship--8b9ecf43-5f5e-4e27-b61d-4fceafa47b81</t>
-  </si>
-  <si>
-    <t>relationship--2280f18d-76c9-4ede-885e-1f9f023d5edf</t>
-  </si>
-  <si>
-    <t>relationship--8b5ce05d-0dc5-44bb-a980-427c816728fd</t>
-  </si>
-  <si>
-    <t>relationship--84a726d6-aa58-4936-b16d-e720c1b9a864</t>
-  </si>
-  <si>
-    <t>relationship--f1d4c82a-9578-4e69-8a56-31829df9fbe5</t>
-  </si>
-  <si>
-    <t>relationship--b04fb82c-ac5f-488a-8dcd-fee6bb377ac3</t>
-  </si>
-  <si>
-    <t>relationship--21ab8f08-5ff9-4e53-8833-b03519bd6cd1</t>
-  </si>
-  <si>
-    <t>relationship--c86a5336-5315-4098-aa83-cd2f97e64823</t>
-  </si>
-  <si>
-    <t>relationship--803320d8-15ba-4348-8c32-bccf3db9f530</t>
-  </si>
-  <si>
-    <t>relationship--b413164f-24a7-4fc4-8ea9-138b0044ce12</t>
-  </si>
-  <si>
-    <t>relationship--f5b536e6-69d1-4bbe-83d9-1ba923dfcb36</t>
-  </si>
-  <si>
-    <t>relationship--7039355e-000e-46d0-8e30-1f7d9dfb4f5e</t>
-  </si>
-  <si>
-    <t>relationship--0efafd8f-ad20-4211-94bd-b94e514a4f77</t>
-  </si>
-  <si>
-    <t>relationship--95b25427-2e1f-495c-a35f-4da450c13301</t>
-  </si>
-  <si>
-    <t>relationship--a6e2c789-2ec6-48f4-bdef-117bd254f13a</t>
-  </si>
-  <si>
-    <t>relationship--af609251-5be4-4f65-90c8-fb3cc9a3dbb4</t>
-  </si>
-  <si>
-    <t>relationship--5cd48454-813b-4331-9c08-66ab490f7c61</t>
-  </si>
-  <si>
-    <t>relationship--0c4c43ea-624a-44d5-ba8b-7758a90422b9</t>
-  </si>
-  <si>
-    <t>relationship--9cf98d26-dcde-4e15-9b77-f531dfaaa42c</t>
-  </si>
-  <si>
-    <t>relationship--d62fcf47-1ed7-4e8e-89ae-ae2b35893e89</t>
-  </si>
-  <si>
-    <t>relationship--a3a14ae4-5efd-4ab9-95b0-7fe445ebaba9</t>
-  </si>
-  <si>
-    <t>relationship--02467645-18f1-44b3-9807-2febf2484815</t>
-  </si>
-  <si>
-    <t>relationship--bf8dd70b-311f-4582-b644-bef5c2fb33b6</t>
-  </si>
-  <si>
-    <t>relationship--dd9311f1-d090-402e-95ba-563ab46c7d70</t>
-  </si>
-  <si>
-    <t>relationship--f2d6a2cf-89d4-471d-954f-85ebca68df09</t>
-  </si>
-  <si>
-    <t>relationship--16305f31-01fb-4769-adda-fb68bdb5bdf5</t>
-  </si>
-  <si>
-    <t>relationship--f2506c16-b956-47b5-8994-61403315d62f</t>
-  </si>
-  <si>
-    <t>relationship--287fce25-2f71-4417-86e4-73d207d621d4</t>
-  </si>
-  <si>
-    <t>relationship--0cd1d9f5-1b62-4894-9c7a-887333274daa</t>
-  </si>
-  <si>
-    <t>relationship--bcfcbe09-5315-4558-a202-b0c3549f574c</t>
-  </si>
-  <si>
-    <t>relationship--72c5aa19-3333-497c-bc10-22276193dbe0</t>
-  </si>
-  <si>
-    <t>relationship--15c9a760-9071-47c3-8b86-207c651c3f9d</t>
-  </si>
-  <si>
-    <t>relationship--4834d7b9-4aad-4db8-b067-793cae286279</t>
-  </si>
-  <si>
-    <t>relationship--fc84144f-1d31-45d5-a091-7122aeffdb3a</t>
-  </si>
-  <si>
-    <t>relationship--ab5fb347-4be5-47d7-ac92-a21f54383f24</t>
-  </si>
-  <si>
-    <t>relationship--2fa33b37-bbe4-4bd4-8235-b137f4579659</t>
-  </si>
-  <si>
-    <t>relationship--c2dc6232-da70-47d5-8e03-23c22d15201e</t>
-  </si>
-  <si>
-    <t>relationship--69b5a3eb-88ee-4898-b5eb-bf99882e755a</t>
-  </si>
-  <si>
-    <t>relationship--8f834fe2-1ea9-4f4e-904e-03480b71fc0c</t>
-  </si>
-  <si>
-    <t>relationship--4c910602-8a1f-4a1b-ae96-78ff77141c32</t>
-  </si>
-  <si>
-    <t>relationship--bb2fb6c6-2082-4128-9aa2-6fd397d4b077</t>
-  </si>
-  <si>
-    <t>relationship--6217bbde-7bd4-4ff9-8084-1bb50aa35f0a</t>
-  </si>
-  <si>
-    <t>relationship--ae394320-962d-4311-a23d-f02679fc432f</t>
-  </si>
-  <si>
-    <t>relationship--5e9166c6-f3f3-4067-b9fb-81ac58ccea57</t>
-  </si>
-  <si>
-    <t>relationship--a77f7b5f-7b61-4700-8fda-341ffc586aa3</t>
-  </si>
-  <si>
-    <t>relationship--17249a22-d960-4c98-bd73-2176cff9a66d</t>
-  </si>
-  <si>
-    <t>relationship--2a6b25b3-2106-4cc5-9daf-69080545023a</t>
-  </si>
-  <si>
-    <t>relationship--7b1b9159-5728-4caa-b025-e233988eed18</t>
-  </si>
-  <si>
-    <t>relationship--bc9dae11-ee8d-437a-a5f2-151aad2a22b9</t>
-  </si>
-  <si>
-    <t>relationship--957f013b-288a-43a5-9b47-0b8ae24ecf5a</t>
-  </si>
-  <si>
-    <t>relationship--aa2e1b37-5b37-49f7-aa1b-6ae619b5c0f4</t>
-  </si>
-  <si>
-    <t>relationship--3f22a8b4-118a-4f55-9a26-b1ba62fa35b2</t>
-  </si>
-  <si>
-    <t>relationship--bcddaa91-a8a1-47ba-885d-b9525a1001aa</t>
-  </si>
-  <si>
-    <t>relationship--ef01b363-58f1-4d39-83d0-99ac81ffc65b</t>
-  </si>
-  <si>
-    <t>relationship--5e7fd20e-84e5-4350-b635-8cbfe36923cb</t>
-  </si>
-  <si>
-    <t>relationship--68d4e642-f528-4420-abae-afc75e93414f</t>
-  </si>
-  <si>
-    <t>relationship--aafb6322-5c65-4a69-831f-ce7c553efb7a</t>
-  </si>
-  <si>
-    <t>relationship--d5f27e9e-a55f-43aa-9040-20018524f869</t>
-  </si>
-  <si>
-    <t>relationship--3f9d7bd8-83c9-4fd9-9aa4-3b54a80bdb79</t>
-  </si>
-  <si>
-    <t>relationship--ec6b5a74-c9d6-4d5d-851d-4340a2c1e77a</t>
-  </si>
-  <si>
-    <t>relationship--1bd2d7ca-6d0d-45b7-aa5c-92d1af9ab047</t>
-  </si>
-  <si>
-    <t>relationship--1788c4e6-bd1e-42f4-bc4c-53a28ea72247</t>
-  </si>
-  <si>
-    <t>relationship--d1bd8bf5-4e79-47ca-bcd8-cb3ceed828ed</t>
-  </si>
-  <si>
-    <t>relationship--9707a4a3-85fc-4326-b941-6e3f4ba3d66e</t>
-  </si>
-  <si>
-    <t>relationship--ce616361-b9c6-41d7-9fa1-c6800c8569b7</t>
-  </si>
-  <si>
-    <t>relationship--c16c1d51-00c9-42e2-a472-267146714a16</t>
-  </si>
-  <si>
-    <t>relationship--8be9daf3-3283-4014-bb07-58b184b74d93</t>
-  </si>
-  <si>
-    <t>relationship--1e810079-efd1-4437-8550-e46be0afa71e</t>
-  </si>
-  <si>
-    <t>relationship--23db1a49-8cfc-4e88-baa9-6cdc44a115a2</t>
-  </si>
-  <si>
-    <t>relationship--cd711de5-eeb1-4125-b828-3b8a8f1b07f3</t>
-  </si>
-  <si>
-    <t>relationship--349ef81a-2f99-4a9c-9c81-e57f79f07d82</t>
-  </si>
-  <si>
-    <t>relationship--60c11da2-7800-43b7-8d1f-76c8aa05a5c9</t>
-  </si>
-  <si>
-    <t>relationship--98c02793-243e-4135-9a39-882178ad8a96</t>
-  </si>
-  <si>
-    <t>relationship--55ff4a91-8661-475f-8ad7-0f09f83c5e85</t>
-  </si>
-  <si>
-    <t>relationship--f198baec-e5e1-4737-8a14-de81017b8eea</t>
-  </si>
-  <si>
-    <t>relationship--d6938961-a091-45b1-bffc-87c242cf25a2</t>
-  </si>
-  <si>
-    <t>relationship--4cfdc688-c4fc-4bb4-a16d-fe39a1f133f7</t>
-  </si>
-  <si>
-    <t>relationship--4c8204a0-a1be-45e1-86b8-3f4cdd438ce7</t>
-  </si>
-  <si>
-    <t>relationship--7b3c83f1-d4d5-48b3-aadf-dceaea68b4ed</t>
-  </si>
-  <si>
-    <t>relationship--d9e0502c-e40e-4515-8c12-b3097dc7475a</t>
-  </si>
-  <si>
-    <t>relationship--33335b1d-f384-436a-9b2f-6977401616dd</t>
-  </si>
-  <si>
-    <t>relationship--563da1b2-2363-4bca-a36f-9427fbb0eeb1</t>
-  </si>
-  <si>
-    <t>relationship--d513bfcd-ce05-438e-ae32-b2aa913d07c8</t>
-  </si>
-  <si>
-    <t>relationship--26a2ccda-f08b-4248-a25b-0e55035acef5</t>
-  </si>
-  <si>
-    <t>relationship--74fd0492-7a79-4dda-8c2d-24e17c4bdab3</t>
-  </si>
-  <si>
-    <t>relationship--c249bddd-af15-4cad-90ed-82cdbeb66aa8</t>
-  </si>
-  <si>
-    <t>relationship--a73dab7a-cba3-4295-9a68-163953884ba6</t>
-  </si>
-  <si>
-    <t>relationship--43501e8a-b825-42ec-b6ec-e295e5cc2e08</t>
-  </si>
-  <si>
-    <t>relationship--bcbf16b1-48cf-4bc1-bb2f-5c361772e1f1</t>
-  </si>
-  <si>
-    <t>relationship--42d0b716-8699-4628-a8d2-d043f5334d2f</t>
-  </si>
-  <si>
-    <t>relationship--e91bf280-5cb2-4f22-973d-ca790c6a9765</t>
-  </si>
-  <si>
-    <t>relationship--1a85808f-513b-446c-8752-4b2ec5da5ee5</t>
-  </si>
-  <si>
-    <t>relationship--b89f2f86-e815-40bd-a82f-3bb6a732125d</t>
-  </si>
-  <si>
-    <t>relationship--fe71a8b2-0517-4fd7-bfec-9e1cd4b701c0</t>
-  </si>
-  <si>
-    <t>relationship--c0561e87-1c03-480c-86ee-6e8e79673848</t>
-  </si>
-  <si>
-    <t>relationship--3542d62b-9969-4f15-87ec-f94b5e6b4405</t>
-  </si>
-  <si>
-    <t>relationship--d217853a-a549-41ec-b95b-00caca3410b2</t>
-  </si>
-  <si>
-    <t>relationship--a2bab682-f3ac-4992-a542-5cecc03e0074</t>
-  </si>
-  <si>
-    <t>relationship--431f4e5a-5596-4a39-b84d-cd1f38d861b3</t>
-  </si>
-  <si>
-    <t>relationship--48ffcfbb-741a-478a-baa6-a36149793de8</t>
-  </si>
-  <si>
-    <t>relationship--827e00b3-a532-4a87-82e5-77f4de601e05</t>
-  </si>
-  <si>
-    <t>relationship--65222228-0b79-420f-a997-9c20f99ecaa4</t>
-  </si>
-  <si>
-    <t>relationship--231fa5f0-a19b-44f4-bc6f-dfa148cc8679</t>
-  </si>
-  <si>
-    <t>relationship--01861179-0186-4305-a71f-27f5e670b04f</t>
-  </si>
-  <si>
-    <t>relationship--5324471d-3a9d-4dcd-989c-0d95bd2d23e9</t>
-  </si>
-  <si>
-    <t>relationship--137d4968-3b9a-4eac-845b-ba164af2867e</t>
-  </si>
-  <si>
-    <t>relationship--5f10c7ac-d87d-4407-add7-7166679dd1f5</t>
-  </si>
-  <si>
-    <t>relationship--e7163b63-492c-4886-9dc2-6e859aa6d034</t>
-  </si>
-  <si>
-    <t>relationship--fc01a550-6494-40e0-8c0d-5c380763303b</t>
-  </si>
-  <si>
-    <t>relationship--822f19d2-5f87-4880-afbe-f1a2b98a3dbf</t>
-  </si>
-  <si>
-    <t>relationship--93fa1b38-db1c-4c2c-aac4-835e21431a8b</t>
-  </si>
-  <si>
-    <t>relationship--9d405089-6db2-4242-9be1-901cd852b765</t>
-  </si>
-  <si>
-    <t>relationship--391c1305-e015-4bd7-bb03-22bfba33c82b</t>
-  </si>
-  <si>
-    <t>relationship--4a68d93b-f1da-4a51-812b-5bf2f0c60a7b</t>
-  </si>
-  <si>
-    <t>relationship--7a210575-716a-406f-9d8e-172a2dbba802</t>
-  </si>
-  <si>
-    <t>relationship--e8029807-08ca-48d9-8572-6a38d99bd2c2</t>
-  </si>
-  <si>
-    <t>relationship--1e9b5938-8fed-4bc2-8d92-9525edd34e24</t>
-  </si>
-  <si>
-    <t>relationship--5268dc98-c56e-46a9-9bef-63cf230d237b</t>
-  </si>
-  <si>
-    <t>relationship--5ea6892d-4b0d-4cbd-8020-6aed168df5a4</t>
-  </si>
-  <si>
-    <t>relationship--55780959-01ec-4069-844d-6df18f57da1f</t>
-  </si>
-  <si>
-    <t>relationship--c46122a2-0e53-4c4b-8b0c-21bfd5940873</t>
-  </si>
-  <si>
-    <t>relationship--6e256514-03e4-45c9-b522-525f27ce759d</t>
-  </si>
-  <si>
-    <t>relationship--87de8c02-0bc1-4b2a-b3a5-facabf410a9b</t>
-  </si>
-  <si>
-    <t>relationship--cfa25437-a45c-4215-891f-c88fb1c6854e</t>
-  </si>
-  <si>
-    <t>relationship--7672e7ae-da3c-4880-9317-481e88285ca7</t>
-  </si>
-  <si>
-    <t>relationship--8c84f972-8d80-4970-b47e-a43e07b700a3</t>
-  </si>
-  <si>
-    <t>relationship--ae23fbce-cefd-4b11-81e8-a74bed5bef7b</t>
-  </si>
-  <si>
-    <t>relationship--f2d91af3-aff9-4b74-a087-c4e8554811b8</t>
-  </si>
-  <si>
-    <t>relationship--eff280bc-ca08-449f-a941-43ea0f060726</t>
-  </si>
-  <si>
-    <t>relationship--c56e03d1-3287-4cde-95c6-23146e302c3e</t>
-  </si>
-  <si>
-    <t>relationship--c6a6164a-b374-493d-a404-68d7cfe61825</t>
-  </si>
-  <si>
-    <t>relationship--ad667537-8c1d-4601-8f6f-4b65f4440940</t>
-  </si>
-  <si>
-    <t>relationship--0071f400-1c99-437b-a1f1-e6433c057f6f</t>
-  </si>
-  <si>
-    <t>relationship--41366efa-5b40-4d9c-a10f-da330d4c22a0</t>
-  </si>
-  <si>
-    <t>relationship--ba8dc7cc-a4a7-495c-9492-90f49e8d1153</t>
-  </si>
-  <si>
-    <t>relationship--2f06cb0c-dcb4-4cd6-bb11-95526ecd709b</t>
-  </si>
-  <si>
-    <t>relationship--43bfb130-3a03-4742-885d-1a4958c7189b</t>
-  </si>
-  <si>
-    <t>relationship--a01766a1-519b-4338-8c88-0c0e2b937dd3</t>
-  </si>
-  <si>
-    <t>relationship--43545b6d-7cb5-463e-a53d-6528245de722</t>
-  </si>
-  <si>
-    <t>relationship--3ff9678f-3704-4082-a10b-9615cb64ce97</t>
-  </si>
-  <si>
-    <t>relationship--23f4ec20-2a56-48e3-9436-dc947eb85662</t>
-  </si>
-  <si>
-    <t>relationship--26d110af-bfc4-46bd-89a6-b25ec0077a25</t>
-  </si>
-  <si>
-    <t>relationship--749eab61-1c86-4133-8036-76b4667d387a</t>
-  </si>
-  <si>
-    <t>relationship--604c0228-a8aa-45ca-b3d9-009780cd0c93</t>
-  </si>
-  <si>
-    <t>relationship--b5f73c4d-eb9d-4ccc-8058-9891de23f8e6</t>
-  </si>
-  <si>
-    <t>relationship--82c4b68f-c4a9-4899-862a-20954adc01a3</t>
-  </si>
-  <si>
-    <t>relationship--5955053a-b87b-4b43-a152-f15bd6d5c523</t>
-  </si>
-  <si>
-    <t>relationship--2893c79c-adb3-4d67-a698-f859a0bbca0f</t>
-  </si>
-  <si>
-    <t>relationship--e5e199d4-6538-431c-94a2-85eabd8a9920</t>
-  </si>
-  <si>
-    <t>relationship--e1378deb-56c4-46c7-bf35-bcf7ab3a9ce2</t>
-  </si>
-  <si>
-    <t>relationship--9d5634ce-16b9-4d9b-a3d5-45a02d743968</t>
-  </si>
-  <si>
-    <t>relationship--c84a3b83-e414-4a18-b5ab-21d88156b13b</t>
-  </si>
-  <si>
-    <t>relationship--9a4aca14-a9a7-4761-90c4-a315313fa85f</t>
-  </si>
-  <si>
-    <t>relationship--07722c0c-5fc9-4dd0-86fd-06f3bdefc0b1</t>
-  </si>
-  <si>
-    <t>relationship--25b395e7-6c6b-43f4-a5ce-1a7c43a4c4a5</t>
-  </si>
-  <si>
-    <t>relationship--e8603dba-be2c-4d39-a158-05a34a8b2248</t>
-  </si>
-  <si>
-    <t>relationship--9f66288a-6101-45f1-a2e9-b6055dc72b7d</t>
-  </si>
-  <si>
-    <t>relationship--c6689428-236d-4e35-8f40-97343e6b4e4c</t>
-  </si>
-  <si>
-    <t>relationship--a7a247e1-e55c-4946-a6fe-8e89fff30460</t>
-  </si>
-  <si>
-    <t>relationship--bbd6f1fb-1697-4bf7-94eb-9bf778bd21fa</t>
-  </si>
-  <si>
-    <t>relationship--673687e5-33e3-4e10-853a-039ec9bbba0f</t>
-  </si>
-  <si>
-    <t>relationship--d8a80fd2-e649-403f-891a-f81e07386728</t>
-  </si>
-  <si>
-    <t>relationship--a182d298-ac49-4812-83d9-7c918bfdcff8</t>
-  </si>
-  <si>
-    <t>relationship--4e3d4cda-bc26-4e9a-944b-efcfa6e7dc78</t>
-  </si>
-  <si>
-    <t>relationship--89b24472-ef28-47d1-a136-9f156a129bf5</t>
-  </si>
-  <si>
-    <t>relationship--97230a5b-b9e5-4e98-a279-1afb93b1beeb</t>
-  </si>
-  <si>
-    <t>relationship--21b7fe4a-162a-4209-98d4-d360f5c94290</t>
-  </si>
-  <si>
-    <t>relationship--a03544ee-5257-4bc5-9f3d-941053278b0d</t>
-  </si>
-  <si>
-    <t>relationship--055c5491-8ec1-46ed-89bf-d00d10057a44</t>
-  </si>
-  <si>
-    <t>relationship--beff9c5d-311e-4dc5-810a-2898c3d5ef95</t>
-  </si>
-  <si>
-    <t>relationship--eb7f7d87-f0d9-415c-9d85-ec9d6995e371</t>
-  </si>
-  <si>
-    <t>relationship--d11d5a60-b488-4beb-b1e1-6cfeee9b512d</t>
-  </si>
-  <si>
-    <t>relationship--27449a60-290d-4640-9c7c-a4a87cb036d2</t>
-  </si>
-  <si>
-    <t>relationship--e4e82c07-b0d0-4fa0-b0ff-71a24ce8c031</t>
-  </si>
-  <si>
-    <t>relationship--f08aff09-5868-4f68-9056-fde79b6714e0</t>
-  </si>
-  <si>
-    <t>relationship--0eb3e9f8-ed56-49f9-961f-45b74f24d6b6</t>
-  </si>
-  <si>
-    <t>relationship--fe1ed08d-9a16-46e1-a211-946d17efabca</t>
-  </si>
-  <si>
-    <t>relationship--fddd4820-b3a3-42ab-8143-76a8a24e1e54</t>
-  </si>
-  <si>
-    <t>relationship--ad21a81f-9db2-419a-add3-717c177a80cb</t>
-  </si>
-  <si>
-    <t>relationship--3ccacaaf-c9c6-4bcf-8000-0f6f62ffe3a1</t>
-  </si>
-  <si>
-    <t>relationship--04df6efb-a4cd-4802-b309-fc2a7d94bdfa</t>
-  </si>
-  <si>
-    <t>relationship--52ba97a8-e66d-44a9-8e11-62a829dbb246</t>
-  </si>
-  <si>
-    <t>relationship--44b4500d-0d89-47da-aaed-e949cee74c3b</t>
-  </si>
-  <si>
-    <t>relationship--62164b6b-d164-41e7-9481-6223553cf173</t>
-  </si>
-  <si>
-    <t>relationship--50cd576b-7652-4699-b71f-0e4aa10e7538</t>
-  </si>
-  <si>
-    <t>relationship--858ee4ec-8c2e-4d81-a63a-6caaa3b1724e</t>
-  </si>
-  <si>
-    <t>relationship--956b8623-ce91-4d57-ab87-e214dcd8d1e6</t>
-  </si>
-  <si>
-    <t>relationship--0fc9df02-2663-4be2-ae57-b47e321d5c5b</t>
-  </si>
-  <si>
-    <t>relationship--e5b4df88-6b23-491f-b483-8551a0ea2bf0</t>
-  </si>
-  <si>
-    <t>relationship--0644e98b-0ba5-405e-890c-fb8c222e1439</t>
-  </si>
-  <si>
-    <t>relationship--8ac25ca3-96cf-4c52-a237-b9062e106f74</t>
-  </si>
-  <si>
-    <t>relationship--3e8a36d8-88aa-468c-9c2c-dc6a2763f906</t>
-  </si>
-  <si>
-    <t>relationship--da148c65-5f4a-4a95-87a3-c6b87f8379ea</t>
-  </si>
-  <si>
-    <t>relationship--f701788a-e221-4dd1-9128-95b9a0d023c8</t>
-  </si>
-  <si>
-    <t>relationship--bf4a83fc-a160-498d-b894-772828c88b1c</t>
-  </si>
-  <si>
-    <t>relationship--57bd8188-1eec-4025-b4f3-e7efaef6549b</t>
-  </si>
-  <si>
-    <t>relationship--a936931c-9625-4d84-9987-ca3f67d5fe58</t>
-  </si>
-  <si>
-    <t>relationship--7e8e6538-c636-4e58-9203-c7b1520d6c27</t>
-  </si>
-  <si>
-    <t>relationship--969684f6-68ed-4fd1-bc86-632f849b1bbd</t>
-  </si>
-  <si>
-    <t>relationship--29b789a0-4a47-4569-b028-52c5f6f00ed7</t>
-  </si>
-  <si>
-    <t>relationship--7bb60df4-1c22-4b9b-b8d2-805d486ae9fa</t>
-  </si>
-  <si>
-    <t>relationship--0e2144a3-1971-40e2-9381-96702aa05be4</t>
-  </si>
-  <si>
-    <t>relationship--0e3a834c-4d76-4a14-8f0b-9b01782f7a2a</t>
-  </si>
-  <si>
-    <t>relationship--465f4881-318d-4da2-b4f0-5d289443f6fa</t>
-  </si>
-  <si>
-    <t>relationship--e1b6ebd1-cbe7-4c53-afd3-37030a935932</t>
-  </si>
-  <si>
-    <t>relationship--6cdb2e97-2d6d-4c25-bc19-5a4b3544d232</t>
-  </si>
-  <si>
-    <t>relationship--a4a38ef0-3b9c-45c0-9306-aff86b2387ae</t>
-  </si>
-  <si>
-    <t>relationship--657542f6-b8c1-4a4e-8893-4fe28a4cdee8</t>
-  </si>
-  <si>
-    <t>relationship--6e36c6de-fbf1-4a16-89da-71294bd0dc93</t>
-  </si>
-  <si>
-    <t>relationship--4370f48f-01cd-46ca-97ea-64afdd48aea4</t>
-  </si>
-  <si>
-    <t>relationship--633ed359-9c30-4a9f-a839-395bb299df98</t>
-  </si>
-  <si>
-    <t>relationship--6202b96d-be8b-4dba-b845-af6c1b249723</t>
-  </si>
-  <si>
-    <t>relationship--2b2a351f-b83e-479f-94f1-253242777b55</t>
-  </si>
-  <si>
-    <t>relationship--95c2a5c2-fd4e-4783-8d91-8da9d5d3fbe2</t>
-  </si>
-  <si>
-    <t>relationship--afcffc6b-70fb-4c03-81ca-fef5944088a2</t>
-  </si>
-  <si>
-    <t>relationship--9504d767-5432-4d80-8013-53c83f7c22f1</t>
-  </si>
-  <si>
-    <t>relationship--611edf19-465c-4f5d-85bb-aeefd6e995e2</t>
-  </si>
-  <si>
-    <t>relationship--dff55fe5-c06c-40d4-a686-5a431b3e98d8</t>
-  </si>
-  <si>
-    <t>relationship--d68069d1-821b-4e7a-ad14-ed1c1939ed38</t>
-  </si>
-  <si>
-    <t>relationship--83a81dbd-94b4-4eab-bcb0-44e580bc0fbd</t>
-  </si>
-  <si>
-    <t>relationship--e6ca9bad-b837-485a-8561-fe0c0f67a174</t>
-  </si>
-  <si>
-    <t>relationship--5bd244d1-5516-474b-b6c6-8f6e1751959e</t>
-  </si>
-  <si>
-    <t>relationship--f05c64f4-6a88-49ed-b077-8de036f40556</t>
-  </si>
-  <si>
-    <t>relationship--e0673107-5991-4109-8db8-520134cc2146</t>
-  </si>
-  <si>
-    <t>relationship--97d08a69-727a-4f0e-83b1-063f58e68ba4</t>
-  </si>
-  <si>
-    <t>relationship--6e962e55-cd15-45d1-9203-8e33bd78ab60</t>
-  </si>
-  <si>
-    <t>relationship--405625f8-e751-4bd7-85fa-258ad6f2b68a</t>
-  </si>
-  <si>
-    <t>relationship--9ed83b23-a904-429c-92a6-ce90942689de</t>
-  </si>
-  <si>
-    <t>relationship--bae03c3e-e80f-45db-87ed-892807e2178e</t>
-  </si>
-  <si>
-    <t>relationship--080ed8e8-2c28-4e8b-b6a7-45145ea0128a</t>
-  </si>
-  <si>
-    <t>relationship--8bcd799f-e5b8-4633-b7bd-b2e5f721fea6</t>
-  </si>
-  <si>
-    <t>relationship--8483e736-649f-492e-a9f5-7f4222459993</t>
-  </si>
-  <si>
-    <t>relationship--0bf70881-3dcb-4784-be1a-6291c9c92fc1</t>
-  </si>
-  <si>
-    <t>relationship--53b4c112-a429-43b5-a40a-134a823673af</t>
-  </si>
-  <si>
-    <t>relationship--29686751-4d79-46cf-8a7b-e9837d808aae</t>
-  </si>
-  <si>
-    <t>relationship--aadc9e12-57f1-4c6e-b5c4-a3ef30807211</t>
-  </si>
-  <si>
-    <t>relationship--07d2ef94-6812-42bb-ab5a-43d6355050ca</t>
-  </si>
-  <si>
-    <t>relationship--70e8cecb-6d07-45c3-9b13-019a92a70701</t>
-  </si>
-  <si>
-    <t>relationship--f8216de2-1ed0-4fbe-ad57-d72c52ecccdc</t>
-  </si>
-  <si>
-    <t>relationship--be802805-0e80-4510-88e2-36bd8e2bef66</t>
-  </si>
-  <si>
-    <t>relationship--584c2186-1549-43f8-bf0c-431e2b6b5010</t>
-  </si>
-  <si>
-    <t>relationship--90e4c5e3-7c6d-4e55-8725-d48eca01a678</t>
-  </si>
-  <si>
-    <t>relationship--e9a6f035-155a-4704-9b4f-14b4b61dd8f8</t>
-  </si>
-  <si>
-    <t>relationship--3db8866a-062d-4995-a079-92aa94987cd6</t>
-  </si>
-  <si>
-    <t>relationship--78de6c1b-d105-463b-bd2e-cc387e513a04</t>
-  </si>
-  <si>
-    <t>relationship--85f50e8e-4090-4472-a182-467c3f609cb2</t>
-  </si>
-  <si>
-    <t>relationship--8e9eda91-5e66-416f-bb44-b303c726c86a</t>
-  </si>
-  <si>
-    <t>relationship--8d0c0c6c-a6b7-4773-a0ac-0c6dad8866a1</t>
-  </si>
-  <si>
-    <t>relationship--e72dfa93-e5ae-4efe-a8ff-f7bdacfae145</t>
-  </si>
-  <si>
-    <t>relationship--d5616a46-fabb-4875-861f-d986a816162a</t>
-  </si>
-  <si>
-    <t>relationship--417e33c5-7b63-440a-9e43-94fae2304c40</t>
-  </si>
-  <si>
-    <t>relationship--2b27b61a-ed32-4cb0-b945-db8901d861b9</t>
-  </si>
-  <si>
-    <t>relationship--03bff8b0-2774-4899-a2ae-991c5caccc2f</t>
-  </si>
-  <si>
-    <t>relationship--7032ef5f-c42b-4239-91fc-996ab9c33b83</t>
-  </si>
-  <si>
-    <t>relationship--ced5e698-bb1b-4f5b-a57f-e80fdcb1def1</t>
-  </si>
-  <si>
-    <t>relationship--12b4d92f-9c0a-4b57-b5da-5644f0640104</t>
-  </si>
-  <si>
-    <t>relationship--e33d4ef5-b340-497d-9db7-f723f793d14b</t>
-  </si>
-  <si>
-    <t>relationship--6a71645c-e668-4c35-af1a-068c183f8c81</t>
-  </si>
-  <si>
-    <t>relationship--8dc5252a-2a4a-40b6-9579-2ac103aa6e5e</t>
-  </si>
-  <si>
-    <t>relationship--066972ee-074b-4c3c-992c-eb0950164778</t>
-  </si>
-  <si>
-    <t>relationship--da41731f-9712-4e17-8d67-493d30b959e3</t>
-  </si>
-  <si>
-    <t>relationship--a64f0e5e-e1eb-49c7-8f9f-809fd64cd5ad</t>
-  </si>
-  <si>
-    <t>relationship--19d74513-f877-42bb-a3dd-9cb8e098f7c8</t>
-  </si>
-  <si>
-    <t>relationship--b9cb0d82-e343-4008-89d5-12ac6796966b</t>
-  </si>
-  <si>
-    <t>relationship--8301a987-0a3b-48c4-8ebe-9775eac9700e</t>
-  </si>
-  <si>
-    <t>relationship--6082181d-42e4-4a00-88b9-fb7f05f08650</t>
-  </si>
-  <si>
-    <t>relationship--3ff626c6-8623-4924-9ad8-0cc56833003c</t>
-  </si>
-  <si>
-    <t>relationship--9a131f74-b423-4e60-9bc4-6cce5360b8bc</t>
-  </si>
-  <si>
-    <t>relationship--0e02357c-c07e-47b2-805b-c05265688163</t>
-  </si>
-  <si>
-    <t>relationship--3a8c4403-d83b-4eae-9655-968bea432709</t>
-  </si>
-  <si>
-    <t>relationship--750fef77-11a1-474a-a028-65e894b53482</t>
-  </si>
-  <si>
-    <t>relationship--fff3aef4-c045-41d2-9c1a-1c4960a5b465</t>
-  </si>
-  <si>
-    <t>relationship--7148e04c-a774-454c-8c96-5142c0ee1331</t>
-  </si>
-  <si>
-    <t>relationship--94123636-25d9-4c52-bc8e-fa2b6af78f7d</t>
-  </si>
-  <si>
-    <t>relationship--c96aa7f2-2ff5-45e4-8ce0-993e46b0f7ce</t>
-  </si>
-  <si>
-    <t>relationship--c88dccf7-073f-4b73-95b8-f6c141c2ea88</t>
-  </si>
-  <si>
-    <t>relationship--aa18ba5c-4772-4de6-8df6-97103c857633</t>
-  </si>
-  <si>
-    <t>relationship--ae0d4f48-7ca8-4e86-beb4-2fc5e34613d7</t>
-  </si>
-  <si>
-    <t>relationship--3d65f0d0-9ca6-4c8a-a0f2-a2f32cf3117d</t>
-  </si>
-  <si>
-    <t>relationship--7045ddce-4798-4f62-bbb9-657acf7e895e</t>
-  </si>
-  <si>
-    <t>relationship--3096006d-9acf-4b9c-a667-01cdc7d7c99f</t>
-  </si>
-  <si>
-    <t>relationship--168aae8a-1325-4d12-8e76-912245ef0e79</t>
-  </si>
-  <si>
-    <t>relationship--f0fb29ec-513b-4c24-922f-81bfb4d4e2a2</t>
-  </si>
-  <si>
-    <t>relationship--e2b323f7-fe5f-4725-ba72-f0dd7ba91c5a</t>
-  </si>
-  <si>
-    <t>relationship--2a6b3098-d2b8-4363-8a6b-29f869aaf8c5</t>
-  </si>
-  <si>
-    <t>relationship--9c4bfad0-d523-4ec7-8e70-8cb64f4a9043</t>
-  </si>
-  <si>
-    <t>relationship--59f9d0e9-3202-4c50-8172-f73fe9eb7131</t>
-  </si>
-  <si>
-    <t>relationship--60f81fbf-1bd9-4c2f-b5df-7f6ed6f17c3d</t>
-  </si>
-  <si>
-    <t>relationship--225cefd8-2903-4317-af4f-35fa55e94032</t>
-  </si>
-  <si>
-    <t>relationship--416d1d17-f865-4b1a-8f81-b82260aced75</t>
-  </si>
-  <si>
-    <t>relationship--b67bd861-444f-4f04-a6e1-9b0d1c3c67c4</t>
-  </si>
-  <si>
-    <t>relationship--2a77ae94-5326-4980-ae79-c7e881ae7de5</t>
-  </si>
-  <si>
-    <t>relationship--649413cf-6855-42d3-b7d2-f0a5abf6676f</t>
-  </si>
-  <si>
-    <t>relationship--18106a1c-5855-4d6b-92b8-56905db21203</t>
-  </si>
-  <si>
-    <t>relationship--d2ca5391-f68f-441c-ad33-1dc1f2402e3c</t>
-  </si>
-  <si>
-    <t>relationship--4d34b1a4-fc22-4817-b194-5b0b3dfb0814</t>
-  </si>
-  <si>
-    <t>relationship--9ee851e9-b992-4e8f-9c2b-432ec620e219</t>
-  </si>
-  <si>
-    <t>relationship--b1baa091-4cd0-4638-a837-6a07ad23bcb8</t>
-  </si>
-  <si>
-    <t>relationship--00dfae9d-7870-47fd-98b0-206114ba58d9</t>
-  </si>
-  <si>
-    <t>relationship--f939a8be-2236-4d77-86b5-287b54c7c32a</t>
-  </si>
-  <si>
-    <t>relationship--d676c970-f90d-4397-bf58-c5a03f8bfc59</t>
-  </si>
-  <si>
-    <t>relationship--efc80a10-3b08-4ba7-b038-178817d44f66</t>
-  </si>
-  <si>
-    <t>relationship--6c9b61bd-0b24-4114-84f1-86c2046aa9c6</t>
-  </si>
-  <si>
-    <t>relationship--86626dfd-325d-4c7d-9bf4-e8257116723e</t>
-  </si>
-  <si>
-    <t>relationship--0bd740fe-817a-43ab-80c1-dd570939c124</t>
-  </si>
-  <si>
-    <t>relationship--9107543d-cc94-4c75-8b4d-8e3f49490734</t>
-  </si>
-  <si>
-    <t>relationship--41f7475a-c31b-496c-8375-52b0d70258a0</t>
-  </si>
-  <si>
-    <t>relationship--c5d53690-5de6-4764-93e2-09e1b9744076</t>
-  </si>
-  <si>
-    <t>relationship--8ce2c861-8d58-4ffd-8c50-78c112daa96d</t>
-  </si>
-  <si>
-    <t>relationship--173660ca-1b8b-40c5-89a0-02813361a6fc</t>
-  </si>
-  <si>
-    <t>relationship--d959e6e3-e593-41c2-8f4c-4f95d0a732ce</t>
-  </si>
-  <si>
-    <t>relationship--9a518d2e-0857-40f8-a7f3-b2e1cdc14621</t>
-  </si>
-  <si>
-    <t>relationship--88165274-fe0a-467c-add8-8b7f67b17b80</t>
-  </si>
-  <si>
-    <t>relationship--ba38f840-9a97-4864-b29b-79af50e2d0f0</t>
-  </si>
-  <si>
-    <t>relationship--deca8f6f-dedd-43ec-8a6d-734952d9bd73</t>
-  </si>
-  <si>
-    <t>relationship--bdb96b60-ec68-4ee8-8d96-8d2a78fb7dc0</t>
-  </si>
-  <si>
-    <t>relationship--390041a9-89ff-43f9-aff4-d45d6a485a55</t>
-  </si>
-  <si>
-    <t>relationship--c9af633c-6d9d-4870-b227-32d5ec24cd56</t>
-  </si>
-  <si>
-    <t>relationship--75a13b48-8e93-4fb6-9773-f77a50243288</t>
-  </si>
-  <si>
-    <t>relationship--15f5af70-262e-41e0-8aba-fa599d341328</t>
-  </si>
-  <si>
-    <t>relationship--711996e9-34ae-4810-8d7a-21a44ffa7fe9</t>
-  </si>
-  <si>
-    <t>relationship--9a3c95c6-23e4-4c0f-8844-52d958f1dbe8</t>
-  </si>
-  <si>
-    <t>relationship--d5500959-3922-4bb2-9c2e-72df957cc5e1</t>
-  </si>
-  <si>
-    <t>relationship--7f6a069d-a281-4ca3-9c5d-7f40d7d57610</t>
-  </si>
-  <si>
-    <t>relationship--a10ca265-b361-4b4c-9de0-d1c1309a80a5</t>
-  </si>
-  <si>
-    <t>relationship--73a49bef-fe4c-459e-8fd8-836fcf3e0641</t>
-  </si>
-  <si>
-    <t>relationship--0cd4c6e2-7736-4613-b2a5-6c711975a0ae</t>
-  </si>
-  <si>
-    <t>relationship--bf56a23c-8789-41b1-af63-46b900047f5a</t>
-  </si>
-  <si>
-    <t>relationship--f3e20272-250d-4f8c-b9e6-f2d9ab1ee9d0</t>
-  </si>
-  <si>
-    <t>relationship--1afbd67d-8510-433b-a617-2720cfd43de3</t>
-  </si>
-  <si>
-    <t>relationship--950ce7a6-f20d-4429-8270-cbe702f9b8a4</t>
-  </si>
-  <si>
-    <t>relationship--d70c1641-5355-48a5-8a08-f6c589f1b7bf</t>
-  </si>
-  <si>
-    <t>relationship--f2315b08-5655-4313-8ae3-121331d6895b</t>
-  </si>
-  <si>
-    <t>relationship--8eae276b-a879-4b89-b777-a1cbc639ca44</t>
-  </si>
-  <si>
-    <t>relationship--c06b6614-aedc-4ee6-8a39-9953db7fe4c7</t>
-  </si>
-  <si>
-    <t>relationship--0a7daa8c-a8f9-4b8e-be70-9bea46ea2bd9</t>
-  </si>
-  <si>
-    <t>relationship--104478ca-397a-4f1a-88a9-cc288cc01269</t>
-  </si>
-  <si>
-    <t>relationship--b82e7c93-0bc3-4694-b8d3-f1865eacc556</t>
-  </si>
-  <si>
-    <t>relationship--5e334d35-427c-4965-8fa3-d390a2aec408</t>
-  </si>
-  <si>
-    <t>relationship--9bc4b721-8658-49f6-b490-726dbec2b451</t>
-  </si>
-  <si>
-    <t>relationship--4da5a977-b962-49e5-ab52-2e0e5f7e890a</t>
-  </si>
-  <si>
-    <t>relationship--b8c316e5-c364-4d3c-8de5-7aa98d597d2c</t>
-  </si>
-  <si>
-    <t>relationship--2e1b44f7-f38a-4868-910a-85e88baa212b</t>
-  </si>
-  <si>
-    <t>relationship--b535b75e-dae6-4781-9a69-21c2e2065f3b</t>
-  </si>
-  <si>
-    <t>relationship--7da26f74-c81f-49d8-b7e7-28e0a9ad2d2b</t>
-  </si>
-  <si>
-    <t>relationship--2cc2e74c-b0bf-4057-b099-ac8686c66a45</t>
+    <t>relationship--8dc2595a-ea3d-473a-a5ab-575d85961170</t>
+  </si>
+  <si>
+    <t>relationship--3c84583b-693a-411d-8a06-b9aab101e5c5</t>
+  </si>
+  <si>
+    <t>relationship--e8d1aab8-ede3-4533-8c27-28a8ab3a9367</t>
+  </si>
+  <si>
+    <t>relationship--13b55b19-53f2-4896-86bc-e1f50be71332</t>
+  </si>
+  <si>
+    <t>relationship--4679013f-4013-4366-aa96-58fb55a6aa34</t>
+  </si>
+  <si>
+    <t>relationship--b40e4178-b507-4dd4-af7e-a0d3edbfa984</t>
+  </si>
+  <si>
+    <t>relationship--26d306f5-3ef0-4f79-921b-0ed5b98c3c43</t>
+  </si>
+  <si>
+    <t>relationship--99bf693b-4903-48ad-ae82-4d5093e9f3f1</t>
+  </si>
+  <si>
+    <t>relationship--17d34dff-5105-4c32-8bd9-4a5c360275b2</t>
+  </si>
+  <si>
+    <t>relationship--6b18450a-0d29-4d28-a39e-211ed5c3e5e1</t>
+  </si>
+  <si>
+    <t>relationship--29fc4d48-e9a7-4d41-9350-759f35c10dc8</t>
+  </si>
+  <si>
+    <t>relationship--51826100-c689-4dfc-b952-79c064b32c09</t>
+  </si>
+  <si>
+    <t>relationship--85d5b58a-a850-44fa-a70b-565d0847df57</t>
+  </si>
+  <si>
+    <t>relationship--cb9711e4-244e-465f-9c39-1b1db3cec45f</t>
+  </si>
+  <si>
+    <t>relationship--f244205f-7f4f-4779-83cb-b5546f2907c6</t>
+  </si>
+  <si>
+    <t>relationship--486552f5-6661-4616-afbc-c9bb01a1ddea</t>
+  </si>
+  <si>
+    <t>relationship--e49c132f-0c7e-4890-89e3-9060f342daee</t>
+  </si>
+  <si>
+    <t>relationship--0a799f8f-4348-4756-ae8d-0053b35db49e</t>
+  </si>
+  <si>
+    <t>relationship--c0260409-7e77-4e21-b637-53e6b76e40a5</t>
+  </si>
+  <si>
+    <t>relationship--19add330-ac7a-4357-98af-9e1bc449b45a</t>
+  </si>
+  <si>
+    <t>relationship--98299ed0-aeee-4a24-b0f8-ac1ffb032879</t>
+  </si>
+  <si>
+    <t>relationship--2e08ea96-7302-4163-b951-a6992936f5d4</t>
+  </si>
+  <si>
+    <t>relationship--1282f430-f6a1-44c3-acd9-c6772a085e28</t>
+  </si>
+  <si>
+    <t>relationship--5b9db982-cb67-463e-99cb-b74e98983686</t>
+  </si>
+  <si>
+    <t>relationship--2e983734-e293-46fa-a3ca-59ab3e20acbc</t>
+  </si>
+  <si>
+    <t>relationship--206bd310-697b-48c8-9620-a8428c4b31b8</t>
+  </si>
+  <si>
+    <t>relationship--feb4f37f-6c5d-47eb-92bc-d9de34e5105c</t>
+  </si>
+  <si>
+    <t>relationship--effbdf3b-28c5-45ea-8c5a-a4aaad2d6684</t>
+  </si>
+  <si>
+    <t>relationship--dc15b305-bb0c-468e-bf55-29441ca02891</t>
+  </si>
+  <si>
+    <t>relationship--552815f9-b787-450b-b2f9-93f5e66a8957</t>
+  </si>
+  <si>
+    <t>relationship--d4bddd31-ce46-48f7-9213-fdc9abf9cab0</t>
+  </si>
+  <si>
+    <t>relationship--c2d442f7-36a3-4f01-85e9-74e5c228167b</t>
+  </si>
+  <si>
+    <t>relationship--efb14c78-9c3c-4b1a-8aa8-130ae785e59f</t>
+  </si>
+  <si>
+    <t>relationship--53ca7805-0a30-44fd-a9ed-80811c272e71</t>
+  </si>
+  <si>
+    <t>relationship--39b3a06e-b64a-48bd-8219-d1a340e8f8c8</t>
+  </si>
+  <si>
+    <t>relationship--8de2c20d-488f-44b0-a826-e2bf437c58f7</t>
+  </si>
+  <si>
+    <t>relationship--74b4b1c8-5505-4069-a9bb-b3aab4a59264</t>
+  </si>
+  <si>
+    <t>relationship--8d339651-b222-4255-89bc-21b1d1292935</t>
+  </si>
+  <si>
+    <t>relationship--cceeee86-4cc2-4d8d-a4c1-bb27c61204f7</t>
+  </si>
+  <si>
+    <t>relationship--26bd1c35-ea15-4ff8-b6f6-08ed46dfca86</t>
+  </si>
+  <si>
+    <t>relationship--67dcc9c5-8f7d-444b-b476-0a7bd878a900</t>
+  </si>
+  <si>
+    <t>relationship--b949ed45-ca02-48aa-b307-78dd8af7e422</t>
+  </si>
+  <si>
+    <t>relationship--4be45cec-a2bd-4f0a-a778-095b6752af02</t>
+  </si>
+  <si>
+    <t>relationship--f64fff70-eafe-460d-9157-da36af63b764</t>
+  </si>
+  <si>
+    <t>relationship--0fd6d8b1-cabd-4a84-8e9f-94e8957ab3c9</t>
+  </si>
+  <si>
+    <t>relationship--0b66b2f4-69a0-4687-a38d-5103d3a59aae</t>
+  </si>
+  <si>
+    <t>relationship--fb669914-1a8f-48cb-9d40-b4218be60472</t>
+  </si>
+  <si>
+    <t>relationship--bf2bf33b-0718-4a16-bc2d-39ee6fd50f41</t>
+  </si>
+  <si>
+    <t>relationship--ace8d8f7-f87c-45e9-a0c5-a6db13aaad67</t>
+  </si>
+  <si>
+    <t>relationship--47b11c13-c81d-4afd-bfef-2eec104a16bc</t>
+  </si>
+  <si>
+    <t>relationship--46c7972a-0170-46ee-a54e-00eac317d7c0</t>
+  </si>
+  <si>
+    <t>relationship--ff147538-2f19-48b9-b193-81bc3dad1108</t>
+  </si>
+  <si>
+    <t>relationship--333a50a3-d564-4dbe-849b-b11894b7ed79</t>
+  </si>
+  <si>
+    <t>relationship--0fa8a8c8-de1b-4c7a-ba1b-ddc747f84286</t>
+  </si>
+  <si>
+    <t>relationship--4a0cbdfe-b532-43ae-baeb-cf314aa4428b</t>
+  </si>
+  <si>
+    <t>relationship--cc0d240d-a816-453a-8188-cf45d9969879</t>
+  </si>
+  <si>
+    <t>relationship--720dea5e-74d9-42e5-857b-bda526769647</t>
+  </si>
+  <si>
+    <t>relationship--cc5c697e-b68b-4ee9-b89d-f6a0efd154e3</t>
+  </si>
+  <si>
+    <t>relationship--9aab33ce-0081-4870-a925-a592a1c665fa</t>
+  </si>
+  <si>
+    <t>relationship--de263284-c1a9-40e2-a6e8-7db444ed43a8</t>
+  </si>
+  <si>
+    <t>relationship--473d2c3f-29e4-4240-9378-75ef121e2fbf</t>
+  </si>
+  <si>
+    <t>relationship--5324c62e-3a35-4b7a-b14e-c89507d0ab29</t>
+  </si>
+  <si>
+    <t>relationship--9c280b9c-5ee6-4e79-8fce-a6090a5e6394</t>
+  </si>
+  <si>
+    <t>relationship--d558e7c7-08f3-41a3-8a0c-982ff50a56ce</t>
+  </si>
+  <si>
+    <t>relationship--1204277f-953e-461b-a56d-4e5a298da427</t>
+  </si>
+  <si>
+    <t>relationship--7c4d7b0e-bf38-4a39-8325-b770d26d6c2c</t>
+  </si>
+  <si>
+    <t>relationship--425d62f4-a51d-45f3-ad08-ccb9459a9c84</t>
+  </si>
+  <si>
+    <t>relationship--e99be189-029c-449f-934d-ff690bf7dcac</t>
+  </si>
+  <si>
+    <t>relationship--7624f845-91a7-4f63-80c5-88f7c0bdbcbb</t>
+  </si>
+  <si>
+    <t>relationship--2b6f8e15-69f6-4dc3-9806-553a5c2d5b38</t>
+  </si>
+  <si>
+    <t>relationship--6bda97d0-f843-4ec7-8b8d-edc2b40f02d6</t>
+  </si>
+  <si>
+    <t>relationship--7a886c7e-33be-4c26-ba00-dbc078e9cf62</t>
+  </si>
+  <si>
+    <t>relationship--065bf392-1be0-4866-b96e-3ccadf785266</t>
+  </si>
+  <si>
+    <t>relationship--c91fb938-45e3-409a-b405-61f05082eed3</t>
+  </si>
+  <si>
+    <t>relationship--c20014c6-540d-43bc-80c0-98cc844c9d15</t>
+  </si>
+  <si>
+    <t>relationship--44cfa7b6-235f-4b89-b41c-e254d74c2bc2</t>
+  </si>
+  <si>
+    <t>relationship--3eaac509-8079-41c1-84bc-679482ed864e</t>
+  </si>
+  <si>
+    <t>relationship--a5f04e72-b0a3-4439-b1b1-8a4b0e9a90d8</t>
+  </si>
+  <si>
+    <t>relationship--c387c4a8-3af7-44a3-994b-c633adf6179e</t>
+  </si>
+  <si>
+    <t>relationship--612fd961-d30f-4e77-a00e-3489d1eae79a</t>
+  </si>
+  <si>
+    <t>relationship--cbe02474-02b3-40cb-becd-610199c93a52</t>
+  </si>
+  <si>
+    <t>relationship--fa27ac74-f26e-45f6-97f6-6d221ce15f5a</t>
+  </si>
+  <si>
+    <t>relationship--f024e543-965f-4ece-91c8-34c5e94761ed</t>
+  </si>
+  <si>
+    <t>relationship--7a8d01c0-8c76-455b-94ce-7faf7a1a9ec0</t>
+  </si>
+  <si>
+    <t>relationship--9646f2db-0be1-412e-af35-3f7f8113555b</t>
+  </si>
+  <si>
+    <t>relationship--e84c607a-def4-471d-a7ef-fcdeaeb2ee9d</t>
+  </si>
+  <si>
+    <t>relationship--caf59a4b-f861-47d9-aac0-bf2f4e15b01f</t>
+  </si>
+  <si>
+    <t>relationship--69957228-a8d7-44a3-85b5-2ae21269762c</t>
+  </si>
+  <si>
+    <t>relationship--f88fa8c3-ef0b-4228-ac85-4d42e65e797f</t>
+  </si>
+  <si>
+    <t>relationship--b1497e6c-e2b6-4f63-b69a-0102358c2be6</t>
+  </si>
+  <si>
+    <t>relationship--a6563193-ff4a-4270-be28-c9b44647b975</t>
+  </si>
+  <si>
+    <t>relationship--0920fb2b-b2fe-4f8d-ac64-5f6c87f42a68</t>
+  </si>
+  <si>
+    <t>relationship--72f1a5a0-f043-4484-84c9-65cefa0f530a</t>
+  </si>
+  <si>
+    <t>relationship--447b159f-efe2-4684-a9b3-abee74d93d5c</t>
+  </si>
+  <si>
+    <t>relationship--e0fc9605-7703-469f-bb42-abfb0799181e</t>
+  </si>
+  <si>
+    <t>relationship--be80d057-d257-4b0f-a09b-f6221472a7af</t>
+  </si>
+  <si>
+    <t>relationship--f7dc890f-55e8-440d-979b-3f37dd3e16db</t>
+  </si>
+  <si>
+    <t>relationship--dbd117ad-c939-4d1a-a246-86d33f0f9b35</t>
+  </si>
+  <si>
+    <t>relationship--58dcff86-7f03-479a-af4d-3d632d0cf0d7</t>
+  </si>
+  <si>
+    <t>relationship--b5fad107-282d-4822-b74a-3ffbc0dbd25a</t>
+  </si>
+  <si>
+    <t>relationship--a0d19cd4-0b1f-4903-aba9-5ebb27785940</t>
+  </si>
+  <si>
+    <t>relationship--c242fcc7-9215-4e09-bdb1-db421f520abc</t>
+  </si>
+  <si>
+    <t>relationship--1f1f8692-7b1d-4c56-a805-b0a36e85dba1</t>
+  </si>
+  <si>
+    <t>relationship--9fb1dadb-6d3f-40e5-9828-73388e0638c5</t>
+  </si>
+  <si>
+    <t>relationship--faadc597-9690-4e02-a5ba-d30fa2c1a6ff</t>
+  </si>
+  <si>
+    <t>relationship--72fd4507-3c2b-4d2d-936d-115eb2db082e</t>
+  </si>
+  <si>
+    <t>relationship--14e5019a-ff6b-4d16-843d-f230c8b31449</t>
+  </si>
+  <si>
+    <t>relationship--07b1fe99-cf2a-4dfa-895b-1706b47ac0a8</t>
+  </si>
+  <si>
+    <t>relationship--d959c266-b1b0-4028-a8f5-588c9ac8d808</t>
+  </si>
+  <si>
+    <t>relationship--ddd78385-2e5b-4bc4-87c9-296835aba967</t>
+  </si>
+  <si>
+    <t>relationship--c6c2ecfa-e336-40b9-8a61-c559493ba53a</t>
+  </si>
+  <si>
+    <t>relationship--c1f2c61c-e583-4a90-bc1e-48c37ac7da80</t>
+  </si>
+  <si>
+    <t>relationship--a5bdba47-602d-4c72-add1-e2b9d356a805</t>
+  </si>
+  <si>
+    <t>relationship--0d4ad55d-27c9-4b5f-94b4-9f1cd82ded45</t>
+  </si>
+  <si>
+    <t>relationship--d7d13c19-848b-4855-a16b-990dfd4f1937</t>
+  </si>
+  <si>
+    <t>relationship--1d09545a-5099-447a-bf44-bbd866ca616c</t>
+  </si>
+  <si>
+    <t>relationship--1d79dbe3-a334-4517-88c2-d23da8df8638</t>
+  </si>
+  <si>
+    <t>relationship--a1bca3ae-9153-4286-bc34-699d4f20263d</t>
+  </si>
+  <si>
+    <t>relationship--d2759f49-0558-4cfc-9e2e-b70723a49996</t>
+  </si>
+  <si>
+    <t>relationship--77575e2e-6811-4cb4-9f81-5f599ef84f1c</t>
+  </si>
+  <si>
+    <t>relationship--76fa5b1e-ed9e-4086-a62f-bab667b127e8</t>
+  </si>
+  <si>
+    <t>relationship--9150447e-d6af-4287-b6b5-25ef90d0af2f</t>
+  </si>
+  <si>
+    <t>relationship--c6ec71c6-3d86-44d4-9d8d-d78b780fd5f6</t>
+  </si>
+  <si>
+    <t>relationship--9a03d005-9028-480c-ab2b-0df5fdfb0854</t>
+  </si>
+  <si>
+    <t>relationship--a3f9d96a-79a6-4d08-88de-f7f3e0494318</t>
+  </si>
+  <si>
+    <t>relationship--d5f1256b-e1a5-47d7-9825-17316c748a8a</t>
+  </si>
+  <si>
+    <t>relationship--c6dea6b1-feee-445b-bb03-35e0d8624150</t>
+  </si>
+  <si>
+    <t>relationship--9c8be662-685e-422b-8108-44f148dfaaff</t>
+  </si>
+  <si>
+    <t>relationship--e6b9443b-b2e7-42a4-b3c2-578e0cc061e8</t>
+  </si>
+  <si>
+    <t>relationship--bf022f1e-0e47-405a-8aab-9d70097d29ac</t>
+  </si>
+  <si>
+    <t>relationship--7702c830-5d58-4a9d-a1fb-07080c1fbc70</t>
+  </si>
+  <si>
+    <t>relationship--741d6d94-565a-4e73-b84b-30b951e84b9b</t>
+  </si>
+  <si>
+    <t>relationship--c7d2ac6d-d1aa-406f-87f9-d25f3aca9d54</t>
+  </si>
+  <si>
+    <t>relationship--88066d09-6cab-4c27-aaf4-714d7e357d7d</t>
+  </si>
+  <si>
+    <t>relationship--aaff9a45-eb22-419c-af24-6a60e392177b</t>
+  </si>
+  <si>
+    <t>relationship--cf6222ed-8e03-4ff2-be24-4bcdf38811d6</t>
+  </si>
+  <si>
+    <t>relationship--3650c411-4a6d-4fa6-bdc9-037fb6df7aa9</t>
+  </si>
+  <si>
+    <t>relationship--35a1ea74-eb63-499c-93e8-daf6bae1e192</t>
+  </si>
+  <si>
+    <t>relationship--a2c9cd1e-711b-4a2c-84f4-3ceae2afbc2b</t>
+  </si>
+  <si>
+    <t>relationship--340c9070-b776-42cc-a324-99b3409376e8</t>
+  </si>
+  <si>
+    <t>relationship--91da6122-40ff-4c06-a298-53a9b6dee773</t>
+  </si>
+  <si>
+    <t>relationship--d2530cd3-a018-4ab3-b89d-8976f20519d2</t>
+  </si>
+  <si>
+    <t>relationship--e84d1b2e-8258-49f2-98e4-2c0e785f8c57</t>
+  </si>
+  <si>
+    <t>relationship--c6c9a988-3680-4158-a714-1e9a24679356</t>
+  </si>
+  <si>
+    <t>relationship--5f7f4377-1e63-4127-bd77-30d1861c64ed</t>
+  </si>
+  <si>
+    <t>relationship--d0ac3428-6e0b-4691-945e-5f99e34af693</t>
+  </si>
+  <si>
+    <t>relationship--26594c8f-2a5c-4f8b-8353-1da9705fae3a</t>
+  </si>
+  <si>
+    <t>relationship--34a0151e-d7cb-4e0e-882e-b82ab87be9d9</t>
+  </si>
+  <si>
+    <t>relationship--41446641-4bde-4905-a1a3-d60c781673d7</t>
+  </si>
+  <si>
+    <t>relationship--e059c3d4-b998-477f-a02c-b99161060103</t>
+  </si>
+  <si>
+    <t>relationship--6e1474bc-6f09-48ee-a450-c3326d5040b4</t>
+  </si>
+  <si>
+    <t>relationship--b0f60820-9214-416f-a0ea-c7612fc8781a</t>
+  </si>
+  <si>
+    <t>relationship--e19c72c6-2939-4141-8960-26d74f226e49</t>
+  </si>
+  <si>
+    <t>relationship--8819d183-102a-4e3d-ae51-28d6a089cad6</t>
+  </si>
+  <si>
+    <t>relationship--04608265-f9e7-4075-8fa8-bb91cb94eb38</t>
+  </si>
+  <si>
+    <t>relationship--35148382-8ec7-42f8-8525-9f9604c75346</t>
+  </si>
+  <si>
+    <t>relationship--ba17a4a0-3889-4ca1-a103-2495b5a5fb1e</t>
+  </si>
+  <si>
+    <t>relationship--21485f15-215c-4125-91f6-3c442a9ae40d</t>
+  </si>
+  <si>
+    <t>relationship--db01fe14-080e-4fd7-b0fd-cd75c58e206c</t>
+  </si>
+  <si>
+    <t>relationship--eec52f79-e724-4c09-9db9-dcca3161c6fe</t>
+  </si>
+  <si>
+    <t>relationship--632fa03d-06cd-4ffe-ad01-0c672bd98660</t>
+  </si>
+  <si>
+    <t>relationship--09ad1b11-635e-49f6-8cd7-b4de49b53698</t>
+  </si>
+  <si>
+    <t>relationship--d8a3c857-d0bb-4d39-a8fd-a55df4fb6f08</t>
+  </si>
+  <si>
+    <t>relationship--f34acf31-e727-4bf1-b655-cbbd2faef950</t>
+  </si>
+  <si>
+    <t>relationship--e5f194bb-39f2-4186-82b0-210962e5e799</t>
+  </si>
+  <si>
+    <t>relationship--ff90a4e4-17cf-44a1-bd7f-1a76e7edcf86</t>
+  </si>
+  <si>
+    <t>relationship--f7a8f5a2-318a-44fa-b6d2-536c814b4f5b</t>
+  </si>
+  <si>
+    <t>relationship--55dc7c77-cc95-4a32-a1b4-6a865cb6f5d8</t>
+  </si>
+  <si>
+    <t>relationship--c6939d44-b491-45dc-8fa7-45ea8e05af9a</t>
+  </si>
+  <si>
+    <t>relationship--4025e60f-0e56-49b8-9907-0055c8f3419f</t>
+  </si>
+  <si>
+    <t>relationship--9be091bc-db4a-47ad-96a4-9e4710810823</t>
+  </si>
+  <si>
+    <t>relationship--b47053d1-e25b-4635-ae65-cc69b4229945</t>
+  </si>
+  <si>
+    <t>relationship--41e40288-caf3-40b0-a859-df5430a609c2</t>
+  </si>
+  <si>
+    <t>relationship--e244100a-909b-45af-99f6-04308fb91caa</t>
+  </si>
+  <si>
+    <t>relationship--a06e1699-b65d-4e31-8b76-7b1dbf1dabdc</t>
+  </si>
+  <si>
+    <t>relationship--a70f0f15-7d61-4e63-b31c-ab51f344588f</t>
+  </si>
+  <si>
+    <t>relationship--96df3b0e-fb37-47b2-9edf-82d2e274c965</t>
+  </si>
+  <si>
+    <t>relationship--4f07ca2c-3292-4bac-a169-ea3e60408256</t>
+  </si>
+  <si>
+    <t>relationship--38ac0aef-c565-4e73-a23e-8696f1040842</t>
+  </si>
+  <si>
+    <t>relationship--049bf566-251d-4c99-af14-48b3ee0ebe41</t>
+  </si>
+  <si>
+    <t>relationship--98ce83a2-f7c3-435a-9adb-f2d2dee7eb22</t>
+  </si>
+  <si>
+    <t>relationship--a1695f95-b193-4696-ae76-65301c5b3d27</t>
+  </si>
+  <si>
+    <t>relationship--7d6c88ef-01a9-462f-95fd-f1dc1d3df7e1</t>
+  </si>
+  <si>
+    <t>relationship--9cdc9871-8cc2-4457-9e4c-72a43fd878ba</t>
+  </si>
+  <si>
+    <t>relationship--35424d8e-8166-46ea-a958-1fec4d058695</t>
+  </si>
+  <si>
+    <t>relationship--97002d57-dd28-4666-8ef1-4b61dc5e54b4</t>
+  </si>
+  <si>
+    <t>relationship--fefe23e4-ea26-46f1-a365-c1a019f37d95</t>
+  </si>
+  <si>
+    <t>relationship--c8004c66-79e1-4dd2-a19d-44a3fe247aea</t>
+  </si>
+  <si>
+    <t>relationship--4915ec10-40da-49e7-9b0f-1add01f70bdf</t>
+  </si>
+  <si>
+    <t>relationship--1ce06a85-eaf8-498f-b20a-ecf3de66c2cb</t>
+  </si>
+  <si>
+    <t>relationship--452d1e7d-adff-4c97-8329-6fbba68fda8e</t>
+  </si>
+  <si>
+    <t>relationship--91146e4f-fac8-45d8-b415-e2876986f3b3</t>
+  </si>
+  <si>
+    <t>relationship--293e00a2-cd1f-4bf2-b557-f50c23fa2685</t>
+  </si>
+  <si>
+    <t>relationship--4a3f366a-cafb-46ce-9732-dfaad5dc1080</t>
+  </si>
+  <si>
+    <t>relationship--1b00a3a5-ddb9-450f-b32d-9fa28a1ba009</t>
+  </si>
+  <si>
+    <t>relationship--403c2394-0447-41aa-807f-02ab159f61e1</t>
+  </si>
+  <si>
+    <t>relationship--42a54b0e-32d0-446f-9fe6-bf079ba926e6</t>
+  </si>
+  <si>
+    <t>relationship--2448a68a-67d6-4494-9f1e-7da4ed9ef6d5</t>
+  </si>
+  <si>
+    <t>relationship--f2530ee9-11cb-4f72-a0e0-84693e6c07d1</t>
+  </si>
+  <si>
+    <t>relationship--6ebfd71f-80ca-4024-a33e-d411f93ba1b6</t>
+  </si>
+  <si>
+    <t>relationship--7356fd91-b6e6-4b7b-ab3d-cc2da25f2a3b</t>
+  </si>
+  <si>
+    <t>relationship--a0a4b16a-1fa2-47d0-ad24-562a63babe3b</t>
+  </si>
+  <si>
+    <t>relationship--9d590f0d-46e1-4cf8-a6a3-974b7a9fc32f</t>
+  </si>
+  <si>
+    <t>relationship--70660c56-d98d-4dab-9887-8a125e1fd558</t>
+  </si>
+  <si>
+    <t>relationship--3080fecb-4449-427e-b825-562b1f5429c4</t>
+  </si>
+  <si>
+    <t>relationship--ff7e7411-7631-436d-85d1-7d07c93e2e2f</t>
+  </si>
+  <si>
+    <t>relationship--8421111a-1bdd-496a-b9c9-a3d9eb196e5c</t>
+  </si>
+  <si>
+    <t>relationship--2cac0497-8b82-44d9-8cae-bb2b20c53828</t>
+  </si>
+  <si>
+    <t>relationship--5baf6c1f-8702-42f6-91ef-e7f9239b0d3c</t>
+  </si>
+  <si>
+    <t>relationship--fd6499be-35d9-403b-ad6d-55ff783b487d</t>
+  </si>
+  <si>
+    <t>relationship--ecaf9231-d8c9-4f83-84fb-2f4dcffef950</t>
+  </si>
+  <si>
+    <t>relationship--ff47682d-e1c3-4d0f-9617-2db64d5336fe</t>
+  </si>
+  <si>
+    <t>relationship--ff18bf3f-c203-4923-97be-647c6141e68d</t>
+  </si>
+  <si>
+    <t>relationship--112a1ef7-9aed-4cb1-9671-8e46450a4e10</t>
+  </si>
+  <si>
+    <t>relationship--2b6a4902-65af-4973-8a68-d99bda767670</t>
+  </si>
+  <si>
+    <t>relationship--33895acb-8526-4c63-9529-a24f57c7c984</t>
+  </si>
+  <si>
+    <t>relationship--2ef067f2-77a6-405d-8d27-b2b32780d80e</t>
+  </si>
+  <si>
+    <t>relationship--fa88292b-99c1-4074-8a12-d4964d7d65c7</t>
+  </si>
+  <si>
+    <t>relationship--3a3faa8b-465b-4954-ada2-7d65907f0157</t>
+  </si>
+  <si>
+    <t>relationship--9ad1973f-73c0-4f6c-9df5-03418c10a146</t>
+  </si>
+  <si>
+    <t>relationship--81aa0cdd-b1c5-480a-a8f6-ec07645cca95</t>
+  </si>
+  <si>
+    <t>relationship--c65136e6-32f9-4434-ba30-65679f00fc27</t>
+  </si>
+  <si>
+    <t>relationship--9c13b868-1879-4e01-a998-cc937879d3b0</t>
+  </si>
+  <si>
+    <t>relationship--4d73be4d-233e-422f-b20d-8ee7e0901aff</t>
+  </si>
+  <si>
+    <t>relationship--c8e02b88-534a-41a7-aeb0-682d58a4ec42</t>
+  </si>
+  <si>
+    <t>relationship--ceee9957-dcf0-4fad-86ba-3a5fc064f2d8</t>
+  </si>
+  <si>
+    <t>relationship--25925782-3eda-4d7a-a5ca-4038cce94ddc</t>
+  </si>
+  <si>
+    <t>relationship--bf380855-3541-4e77-85a2-beb798452793</t>
+  </si>
+  <si>
+    <t>relationship--bdee1210-8da5-42de-9f93-dd8ddc0dac63</t>
+  </si>
+  <si>
+    <t>relationship--efa244d7-20b8-4846-9556-ee08d55b2997</t>
+  </si>
+  <si>
+    <t>relationship--a5de4eea-da1f-4185-8d88-f065a22018e2</t>
+  </si>
+  <si>
+    <t>relationship--c8b2bfe4-d4bb-450c-a211-39c476dd0960</t>
+  </si>
+  <si>
+    <t>relationship--c1a17585-0bfd-4643-a957-a7e53c1e8710</t>
+  </si>
+  <si>
+    <t>relationship--73a37c72-9eb2-496b-9290-5ef2a44a8e8b</t>
+  </si>
+  <si>
+    <t>relationship--2848a711-a9aa-4fd1-a298-90b8618ad5ef</t>
+  </si>
+  <si>
+    <t>relationship--208134a5-8f6b-48c2-9631-bf2bb5e2f2b5</t>
+  </si>
+  <si>
+    <t>relationship--a7c80b03-bfdc-4680-bcf3-8df4963526ec</t>
+  </si>
+  <si>
+    <t>relationship--48797067-a677-4757-95f7-694978fb3ad0</t>
+  </si>
+  <si>
+    <t>relationship--b7032820-cc1f-411a-9669-4e033cb6c4bf</t>
+  </si>
+  <si>
+    <t>relationship--de6ac0b8-7290-49c8-a9f8-254ae4bfef2b</t>
+  </si>
+  <si>
+    <t>relationship--7b4285f3-5912-41c8-9155-6b9a1b841284</t>
+  </si>
+  <si>
+    <t>relationship--8d0cfd35-f4ff-4fb4-980e-20eb758d419b</t>
+  </si>
+  <si>
+    <t>relationship--6b17b7f1-9d6a-401a-87be-793855e793c7</t>
+  </si>
+  <si>
+    <t>relationship--0246d310-2efa-420b-a3cc-d612374fc588</t>
+  </si>
+  <si>
+    <t>relationship--944a2456-8e29-4ec5-8410-de866f447038</t>
+  </si>
+  <si>
+    <t>relationship--8a37370b-0106-4b2b-9b9e-ba64341ae42f</t>
+  </si>
+  <si>
+    <t>relationship--b89c972a-724a-4910-91cd-2c62b807d8e0</t>
+  </si>
+  <si>
+    <t>relationship--9935ac01-8b31-4f42-b729-5baf24ade44e</t>
+  </si>
+  <si>
+    <t>relationship--6086eac4-0f55-40d6-937c-d1bbbe652594</t>
+  </si>
+  <si>
+    <t>relationship--0c3af4a9-1da2-42fc-9a83-fee6a88d0896</t>
+  </si>
+  <si>
+    <t>relationship--fbec3e9a-9a8c-4b13-8dff-266db118db49</t>
+  </si>
+  <si>
+    <t>relationship--56fa56bc-79c0-406c-80c3-f2c7b0db929c</t>
+  </si>
+  <si>
+    <t>relationship--b1a47e0d-a395-4c14-96b4-08aff6329358</t>
+  </si>
+  <si>
+    <t>relationship--dc9c99f8-0b05-49b3-be6d-3d12ac743657</t>
+  </si>
+  <si>
+    <t>relationship--37195b48-a88f-4565-823c-fae4c1e37bec</t>
+  </si>
+  <si>
+    <t>relationship--0c9fa89f-5a20-4f2b-8fcf-e23197d6c524</t>
+  </si>
+  <si>
+    <t>relationship--a20788de-d039-4100-9b35-371cf615dfc8</t>
+  </si>
+  <si>
+    <t>relationship--d167789c-26a8-4b0a-a8f4-09984513c2d2</t>
+  </si>
+  <si>
+    <t>relationship--690bea0d-d155-4ef5-bd33-ba648e71f4a0</t>
+  </si>
+  <si>
+    <t>relationship--1b68bf01-b795-40fd-9d77-649764dc2945</t>
+  </si>
+  <si>
+    <t>relationship--7d3b7623-8648-400d-a0e4-aaf5e3e53dcf</t>
+  </si>
+  <si>
+    <t>relationship--40215d2f-18b6-41c9-95b2-31b3e5970c19</t>
+  </si>
+  <si>
+    <t>relationship--8c21bd6d-214b-4ed6-bfe2-04d78b11e191</t>
+  </si>
+  <si>
+    <t>relationship--49563f40-ffd6-41dc-bb16-74fba6e3ea07</t>
+  </si>
+  <si>
+    <t>relationship--d930801b-253c-4b70-9f42-ee2032047b33</t>
+  </si>
+  <si>
+    <t>relationship--5eaf5c87-ec9a-4b27-b182-5f950c02981d</t>
+  </si>
+  <si>
+    <t>relationship--42b4181c-692e-401a-a4c6-bfc6efe48d5b</t>
+  </si>
+  <si>
+    <t>relationship--99d520c9-1182-4b76-9201-fc543c885216</t>
+  </si>
+  <si>
+    <t>relationship--7044da1c-80ac-48a7-a764-7df52f7ecb7e</t>
+  </si>
+  <si>
+    <t>relationship--3c558bdf-09f9-4ef8-bd2d-9bb126ec3eff</t>
+  </si>
+  <si>
+    <t>relationship--66bde137-c075-40b9-ab52-b5cf9b3e8daf</t>
+  </si>
+  <si>
+    <t>relationship--7c23580d-69a5-4956-b5d6-cef981a93327</t>
+  </si>
+  <si>
+    <t>relationship--55760606-a78c-443c-b4e1-2fd35e1cde08</t>
+  </si>
+  <si>
+    <t>relationship--57734d21-89fc-4c80-89ab-e7211fcd5744</t>
+  </si>
+  <si>
+    <t>relationship--4fb15e85-ef3d-45ed-8097-602f89e7f66a</t>
+  </si>
+  <si>
+    <t>relationship--0b180d62-3450-4a18-a566-2b95d5570e9b</t>
+  </si>
+  <si>
+    <t>relationship--08e2b7fc-70f5-4b8b-9c5f-6f3f6ca45f95</t>
+  </si>
+  <si>
+    <t>relationship--29e15874-779e-457c-a3b0-57f3d22aa4c5</t>
+  </si>
+  <si>
+    <t>relationship--8d5fc67e-19cf-443d-a625-90faafa8b071</t>
+  </si>
+  <si>
+    <t>relationship--86273ea8-f37b-405b-a645-7483ef63632b</t>
+  </si>
+  <si>
+    <t>relationship--1e3b664b-31cd-4d9f-82ea-a61374a63058</t>
+  </si>
+  <si>
+    <t>relationship--b66acb93-03aa-4297-a817-296072208092</t>
+  </si>
+  <si>
+    <t>relationship--ac5e90cf-bc78-41d1-8ca3-537b815bc474</t>
+  </si>
+  <si>
+    <t>relationship--9639eada-10de-47b2-a413-3ee0c7801f8f</t>
+  </si>
+  <si>
+    <t>relationship--74bb8abe-dd1b-435f-8c64-e019caa81eb5</t>
+  </si>
+  <si>
+    <t>relationship--64c443e1-c8d4-4535-bccd-3a09aa043086</t>
+  </si>
+  <si>
+    <t>relationship--546392db-e9e1-48fa-a820-1d7873774713</t>
+  </si>
+  <si>
+    <t>relationship--38f1b20b-e4a1-4e07-9cc2-0e05cbc195a6</t>
+  </si>
+  <si>
+    <t>relationship--a3e0a51e-8eaf-42f5-8195-0c8fd97d705f</t>
+  </si>
+  <si>
+    <t>relationship--27720c57-1229-44e4-af67-1d487904f2ae</t>
+  </si>
+  <si>
+    <t>relationship--7a2fba3e-f2e6-452f-96d6-26db5d4c8325</t>
+  </si>
+  <si>
+    <t>relationship--9f7e3a64-1f59-4bd1-a1e9-961ea3e3fbf0</t>
+  </si>
+  <si>
+    <t>relationship--11376a19-7d5e-4967-939f-57594828d064</t>
+  </si>
+  <si>
+    <t>relationship--ca677725-78de-48d8-86a8-ec29441592b5</t>
+  </si>
+  <si>
+    <t>relationship--e1891e3d-1d6f-4408-9067-e65c792f053d</t>
+  </si>
+  <si>
+    <t>relationship--044cae79-fb64-4cb0-9c54-27889d261362</t>
+  </si>
+  <si>
+    <t>relationship--35a68fea-00c0-45bd-b225-03d013c0ddbf</t>
+  </si>
+  <si>
+    <t>relationship--ad2fc75c-50cd-49de-94be-f1ea3b9d61b9</t>
+  </si>
+  <si>
+    <t>relationship--c7c6aa56-b3f6-43e9-964b-0d7911e76d04</t>
+  </si>
+  <si>
+    <t>relationship--ef3afa47-1414-468d-bcb0-c51cbedb52f1</t>
+  </si>
+  <si>
+    <t>relationship--0794b124-b5d0-4fd9-8f21-9573518795f6</t>
+  </si>
+  <si>
+    <t>relationship--f6c699c4-44c5-4145-9ffa-3ab207f004f1</t>
+  </si>
+  <si>
+    <t>relationship--06ca61c0-2f32-4890-b2d1-8e614e02c2c8</t>
+  </si>
+  <si>
+    <t>relationship--3d893343-1182-4b4b-8fdb-6eccbd0b6899</t>
+  </si>
+  <si>
+    <t>relationship--599ba3c0-5526-4992-a2f9-6331fcdf2f00</t>
+  </si>
+  <si>
+    <t>relationship--df26f4ed-d5ca-40cf-8996-f49a059078ff</t>
+  </si>
+  <si>
+    <t>relationship--7b949c8a-9a7d-4845-8eb4-ff63d0ef8966</t>
+  </si>
+  <si>
+    <t>relationship--bdd27eb0-da4e-4e90-9335-7516b27a621d</t>
+  </si>
+  <si>
+    <t>relationship--70ed1bc9-e4a0-4ec5-8537-4bf3c9dd8403</t>
+  </si>
+  <si>
+    <t>relationship--90c22048-e6d0-4e8d-b7ab-e07a69c44018</t>
+  </si>
+  <si>
+    <t>relationship--529e4f20-ca5d-4644-ac03-01130f7ae42d</t>
+  </si>
+  <si>
+    <t>relationship--d97302c5-ac9b-430e-8f18-c082edd9462f</t>
+  </si>
+  <si>
+    <t>relationship--3dc7f2e0-f370-46b3-a88c-c839ba44bb2f</t>
+  </si>
+  <si>
+    <t>relationship--d5a34423-2ed7-4fd1-92de-2f9b12a2b858</t>
+  </si>
+  <si>
+    <t>relationship--d8032462-ccdf-4d28-a7d7-474159233342</t>
+  </si>
+  <si>
+    <t>relationship--cbcb94f6-3550-4f7f-a5b7-982581d05fd6</t>
+  </si>
+  <si>
+    <t>relationship--f14fa2b8-5385-4278-9e56-e2b45a00a6ae</t>
+  </si>
+  <si>
+    <t>relationship--4e82ba73-4753-4fce-8079-7fdf1a17a2de</t>
+  </si>
+  <si>
+    <t>relationship--9017b272-663d-40c1-bca2-3f2f31bbceaf</t>
+  </si>
+  <si>
+    <t>relationship--2f6df890-25c7-4ed0-a9c8-cc75ee944ddd</t>
+  </si>
+  <si>
+    <t>relationship--15cd66f8-c759-4577-b418-21c95b69d9fb</t>
+  </si>
+  <si>
+    <t>relationship--a909c92e-e875-4935-983a-ecd0c53d319e</t>
+  </si>
+  <si>
+    <t>relationship--00a62e08-88d7-45f6-8ac0-5de159a6c0fd</t>
+  </si>
+  <si>
+    <t>relationship--08661919-032c-4888-b1db-840a537a0da1</t>
+  </si>
+  <si>
+    <t>relationship--20e977fd-aa34-42e5-a377-3ef2faaa9301</t>
+  </si>
+  <si>
+    <t>relationship--5823d876-16a5-43ef-97ed-ffe67b504c26</t>
+  </si>
+  <si>
+    <t>relationship--c60f4eda-856b-42d7-bbb1-ba744349c38d</t>
+  </si>
+  <si>
+    <t>relationship--700566db-0df2-4fac-8d27-69ba94ec6d37</t>
+  </si>
+  <si>
+    <t>relationship--b80c9a94-cdbd-4b33-9427-a0e693ac6d2d</t>
+  </si>
+  <si>
+    <t>relationship--514414ef-679b-49b7-8266-23b02516c2b5</t>
+  </si>
+  <si>
+    <t>relationship--a4b029f5-5af6-4581-9ccc-764390506959</t>
+  </si>
+  <si>
+    <t>relationship--433bfeb9-27a6-4fe6-9c6a-d6edb94e5ad1</t>
+  </si>
+  <si>
+    <t>relationship--4a851d49-168b-4a7d-89ce-e39a1db7dab6</t>
+  </si>
+  <si>
+    <t>relationship--f60c7ca4-6671-4980-8ecd-8499a73b638f</t>
+  </si>
+  <si>
+    <t>relationship--b6ac089a-192e-4b7e-9759-96a0a2821757</t>
+  </si>
+  <si>
+    <t>relationship--84472392-d22a-4597-a5ca-47abab9cdc58</t>
+  </si>
+  <si>
+    <t>relationship--43e2f28e-cac9-4ba4-a78a-7834ab568b68</t>
+  </si>
+  <si>
+    <t>relationship--5c7cc263-7a48-4988-a248-dd0d33b72ea2</t>
+  </si>
+  <si>
+    <t>relationship--65dfd141-d3ac-49a5-9ebe-19c40fd8af3a</t>
+  </si>
+  <si>
+    <t>relationship--1ef25134-bf7e-4351-9ed6-3a073e749feb</t>
+  </si>
+  <si>
+    <t>relationship--3954182a-8d30-4972-8761-4b18404b6208</t>
+  </si>
+  <si>
+    <t>relationship--a63435d8-1f82-4d64-b613-6276265493f8</t>
+  </si>
+  <si>
+    <t>relationship--7f350d89-2b8b-4c1b-9cb1-ce457760a2ef</t>
+  </si>
+  <si>
+    <t>relationship--4181db3e-82ad-437b-8f50-6ffd69e5dcb3</t>
+  </si>
+  <si>
+    <t>relationship--5e9d5699-dabf-45d3-b9a3-5b45fa46095e</t>
+  </si>
+  <si>
+    <t>relationship--aaec9cf1-4c91-4581-a2b9-09f1f664d4a8</t>
+  </si>
+  <si>
+    <t>relationship--d4e87416-4505-4d6a-9b50-040dcdc3fe6f</t>
+  </si>
+  <si>
+    <t>relationship--3ff7c5f1-b705-49ee-b13e-b4ea206655bf</t>
+  </si>
+  <si>
+    <t>relationship--180b78be-b49a-4755-b0d3-06e6629c1d98</t>
+  </si>
+  <si>
+    <t>relationship--2105eada-5f3f-424f-8c71-3cedb373f50e</t>
+  </si>
+  <si>
+    <t>relationship--2f9966e9-6bb6-494c-b995-8451d627a22f</t>
+  </si>
+  <si>
+    <t>relationship--a022ffe0-14af-4f97-a6f7-c1781c108a0a</t>
+  </si>
+  <si>
+    <t>relationship--43189a50-6a74-4507-87f7-4afc6595a442</t>
+  </si>
+  <si>
+    <t>relationship--6a8fd142-d41f-4964-97e3-7d010a1381ee</t>
+  </si>
+  <si>
+    <t>relationship--0993c894-31dd-4a89-b9bf-f0bbd7f3a565</t>
+  </si>
+  <si>
+    <t>relationship--7daf0d22-f73a-40f1-8e10-1fa6da186fda</t>
+  </si>
+  <si>
+    <t>relationship--4bd08345-0fde-44d2-a8fc-78815defcba1</t>
+  </si>
+  <si>
+    <t>relationship--fd28f0fb-32a0-4f3e-965d-40bfe9024365</t>
+  </si>
+  <si>
+    <t>relationship--8f762573-449a-48f7-ae35-85a8a441d1ab</t>
+  </si>
+  <si>
+    <t>relationship--9c00f57c-98fb-47e8-8ab0-a927c16581fa</t>
+  </si>
+  <si>
+    <t>relationship--4ab7e704-18c1-4b25-892e-89f147232143</t>
+  </si>
+  <si>
+    <t>relationship--d38f8274-d7d2-4ce9-8e8a-57e37411cbaf</t>
+  </si>
+  <si>
+    <t>relationship--252e78d9-6f4c-498e-9311-3118c9788036</t>
+  </si>
+  <si>
+    <t>relationship--12e92db3-c98a-4a65-b141-db6351e55a5b</t>
+  </si>
+  <si>
+    <t>relationship--3815d4ca-9c10-4cf5-97f6-31e78836d3ff</t>
+  </si>
+  <si>
+    <t>relationship--3c96fbe6-d55f-4f8e-95d4-11d4d5424541</t>
+  </si>
+  <si>
+    <t>relationship--23010407-129e-48ea-b673-423a1de6678b</t>
+  </si>
+  <si>
+    <t>relationship--9223ad72-6b12-48f6-87f5-70caa6dbda05</t>
+  </si>
+  <si>
+    <t>relationship--095f5eb9-e248-4c30-bacd-984507693895</t>
+  </si>
+  <si>
+    <t>relationship--06ccfecd-217d-4047-8061-d6b04995039d</t>
+  </si>
+  <si>
+    <t>relationship--f93d69e2-1750-4b35-902d-2436cb827ed5</t>
+  </si>
+  <si>
+    <t>relationship--4f9dd980-3447-4058-a210-df218ef15247</t>
+  </si>
+  <si>
+    <t>relationship--0abec849-90db-4307-a449-259849375c2a</t>
+  </si>
+  <si>
+    <t>relationship--4e85759c-2597-434d-a8dd-6606cbdffa90</t>
+  </si>
+  <si>
+    <t>relationship--25727f21-e38d-49bc-a58a-b78871d2ada8</t>
+  </si>
+  <si>
+    <t>relationship--97f76c05-d0d6-4d44-a77d-29b7a2840db8</t>
+  </si>
+  <si>
+    <t>relationship--88b7f70e-924e-4e18-928a-a65f68a8f5d6</t>
+  </si>
+  <si>
+    <t>relationship--95d25de2-8caa-466a-ae0d-9f0be0b6a0b4</t>
+  </si>
+  <si>
+    <t>relationship--4ff31ad2-016f-4fea-a507-fc6cfd1b64f3</t>
+  </si>
+  <si>
+    <t>relationship--fdfac626-3e68-4e50-80e1-a63f79dd6b7b</t>
+  </si>
+  <si>
+    <t>relationship--cc31c996-dc24-4f4e-901b-e638eb180204</t>
+  </si>
+  <si>
+    <t>relationship--2049b2b9-3b7c-4c9c-acd6-d1e1bbafa9a7</t>
+  </si>
+  <si>
+    <t>relationship--f59a8fbf-5c24-4c1d-be26-2de7bbf1e33e</t>
+  </si>
+  <si>
+    <t>relationship--f7109b0a-7fa1-4e2c-bd67-07e17e46685f</t>
+  </si>
+  <si>
+    <t>relationship--cc49a9f2-9807-4d78-bc7d-ac235e62198a</t>
+  </si>
+  <si>
+    <t>relationship--aa3045e2-60c0-424b-84c2-07b8f0d5d35a</t>
+  </si>
+  <si>
+    <t>relationship--c2e880cc-58d2-4742-a311-32337501792d</t>
+  </si>
+  <si>
+    <t>relationship--231a596f-b1b9-4011-ad1d-10cf94db6f0c</t>
+  </si>
+  <si>
+    <t>relationship--6f64b848-ac13-4eb8-9318-4d7c5f45be56</t>
+  </si>
+  <si>
+    <t>relationship--b9c6adbe-7650-462f-94c4-8302432524f3</t>
+  </si>
+  <si>
+    <t>relationship--d2ca21ac-72b9-4080-86d1-6b0c901bdd8f</t>
+  </si>
+  <si>
+    <t>relationship--04cfa84d-6c62-467f-979a-a1cb9590396a</t>
+  </si>
+  <si>
+    <t>relationship--bc6cd040-c5fb-4739-b028-e8d644c2a85f</t>
+  </si>
+  <si>
+    <t>relationship--27614406-66ba-4f5b-bed1-6d723fa0a0d1</t>
+  </si>
+  <si>
+    <t>relationship--47e434fa-3942-4734-b3cd-f729c267c62c</t>
+  </si>
+  <si>
+    <t>relationship--0b72ae45-9902-4c2b-b9c7-ca6ebc77e050</t>
+  </si>
+  <si>
+    <t>relationship--c7ab2a45-95b5-4ef0-8cd3-6966486bd857</t>
+  </si>
+  <si>
+    <t>relationship--352b7275-17c4-4598-9242-99b9fd5462df</t>
+  </si>
+  <si>
+    <t>relationship--235469c9-a133-4ae1-b8cd-d84ab98ca05e</t>
+  </si>
+  <si>
+    <t>relationship--3a339735-3b52-46d7-9651-2909e95b9121</t>
+  </si>
+  <si>
+    <t>relationship--05f5e083-fd61-4960-8be8-db355cc4d589</t>
+  </si>
+  <si>
+    <t>relationship--86d23573-386c-4c72-9d0b-504f0f5b18cb</t>
+  </si>
+  <si>
+    <t>relationship--d24fae47-a8b1-4d20-9fad-63dc72b13c29</t>
+  </si>
+  <si>
+    <t>relationship--7766ec9d-89dd-4d56-84c0-7ed41a44be07</t>
+  </si>
+  <si>
+    <t>relationship--75e717bd-0d46-4198-a7e2-b852a613c2ec</t>
+  </si>
+  <si>
+    <t>relationship--da9c532f-0780-4f86-92d4-67e33ea0c838</t>
+  </si>
+  <si>
+    <t>relationship--258161ed-3d00-4137-8ca3-53f1bd58715b</t>
+  </si>
+  <si>
+    <t>relationship--20698dcd-a883-4174-a62e-a44cc89e73f4</t>
+  </si>
+  <si>
+    <t>relationship--be357000-c645-422a-bd5d-d59dc96409eb</t>
+  </si>
+  <si>
+    <t>relationship--d05e212b-5e25-4202-9199-1db87671695d</t>
+  </si>
+  <si>
+    <t>relationship--b9a7543d-72ce-463a-9fc2-3fb1a7ac8144</t>
+  </si>
+  <si>
+    <t>relationship--01e68948-93a9-41c0-87a0-60d988c95d45</t>
+  </si>
+  <si>
+    <t>relationship--9ec15a1e-2142-427f-957c-9f454ca27185</t>
+  </si>
+  <si>
+    <t>relationship--583da3dd-417c-486f-9e3d-7d9777c6bc9f</t>
+  </si>
+  <si>
+    <t>relationship--90383c9d-6a6c-49b6-a58d-b6120e33bb0b</t>
+  </si>
+  <si>
+    <t>relationship--e27f9eee-cb77-4f05-a2d7-d8afcc0b7da2</t>
+  </si>
+  <si>
+    <t>relationship--5e01cec4-b7f7-4ca6-b8d1-862d784336d9</t>
+  </si>
+  <si>
+    <t>relationship--b5531d6b-d983-4f9e-aa68-23d03e28718d</t>
+  </si>
+  <si>
+    <t>relationship--291af949-4353-41f7-9b6b-e00f1a404f76</t>
+  </si>
+  <si>
+    <t>relationship--491438b9-1d5c-412b-865e-74a7cb76812a</t>
+  </si>
+  <si>
+    <t>relationship--a7987141-7d2f-4218-849d-c542bfa41e77</t>
+  </si>
+  <si>
+    <t>relationship--af5c0ecc-0d86-4dc6-a451-da3530baf8ff</t>
+  </si>
+  <si>
+    <t>relationship--4b434ff1-3907-4d16-9c03-6f2d42fad159</t>
+  </si>
+  <si>
+    <t>relationship--0b0455af-0e79-429a-85a0-1b5a704aeadb</t>
+  </si>
+  <si>
+    <t>relationship--1033b6dc-8004-4dfd-a5a3-3ef672176611</t>
+  </si>
+  <si>
+    <t>relationship--f3167bf9-08a2-47fc-ba56-002650955376</t>
+  </si>
+  <si>
+    <t>relationship--de6b9069-e4d7-4324-9b75-ef40312dfdf5</t>
+  </si>
+  <si>
+    <t>relationship--45991db0-f1fb-4ed6-838e-272c3e8bbc79</t>
+  </si>
+  <si>
+    <t>relationship--959bb770-58e5-4af3-80f9-20623534aebc</t>
+  </si>
+  <si>
+    <t>relationship--eafceaa6-fd0b-4d2d-b4d4-526e3b03549f</t>
+  </si>
+  <si>
+    <t>relationship--08431f77-db43-4f2c-89a0-c7e651d226ef</t>
+  </si>
+  <si>
+    <t>relationship--86efe912-0744-4b2c-ad65-c659828d4e1b</t>
+  </si>
+  <si>
+    <t>relationship--43dddc15-dd0a-40db-9f23-a21873b7b8a9</t>
+  </si>
+  <si>
+    <t>relationship--fd294405-4be2-45c5-aebc-af9eef617ff6</t>
+  </si>
+  <si>
+    <t>relationship--1d19a9c5-9573-4dd3-b4cd-da95eb717807</t>
+  </si>
+  <si>
+    <t>relationship--57fedc56-c269-40d9-a6f0-dc27bf137cd3</t>
+  </si>
+  <si>
+    <t>relationship--0668d386-c676-40e5-8ed1-c4a19ad273f7</t>
+  </si>
+  <si>
+    <t>relationship--709c65ae-bd7c-4e98-9aae-ee50398b7c32</t>
+  </si>
+  <si>
+    <t>relationship--a568e16b-02d3-4885-8a98-5e8b66d1c95a</t>
+  </si>
+  <si>
+    <t>relationship--1f408b17-e696-4861-92d3-7dab2842f2de</t>
+  </si>
+  <si>
+    <t>relationship--abcfe226-0eda-4a82-a7dd-96fad0a1e3fb</t>
+  </si>
+  <si>
+    <t>relationship--2ab3d636-b362-436a-9417-0cf988f7c1f3</t>
+  </si>
+  <si>
+    <t>relationship--7c4d523c-17bc-4ea9-a609-457dab2a615c</t>
+  </si>
+  <si>
+    <t>relationship--574c07ae-ca7a-492e-97ae-7dc0b685de60</t>
+  </si>
+  <si>
+    <t>relationship--e5586130-f83c-4a63-be9a-b262dcbdb4ef</t>
+  </si>
+  <si>
+    <t>relationship--88eeffd7-942b-4521-9642-ac49543a0095</t>
+  </si>
+  <si>
+    <t>relationship--d65ecec1-f1e7-4426-b6a6-cc087b91ce1b</t>
+  </si>
+  <si>
+    <t>relationship--655093be-3fb7-49af-a674-c30efecac38a</t>
+  </si>
+  <si>
+    <t>relationship--8941cca8-a5ac-4ba2-b62f-a03d6a22c082</t>
+  </si>
+  <si>
+    <t>relationship--8414dd92-1184-40ae-ab8d-d6dc65c650f1</t>
+  </si>
+  <si>
+    <t>relationship--918e6e3a-c07f-47f7-869c-c0e926c40fdc</t>
+  </si>
+  <si>
+    <t>relationship--ebf36ebc-6156-471d-90fe-b05dc9a0f300</t>
+  </si>
+  <si>
+    <t>relationship--0fb2f5b8-1b20-40b5-bcd2-821997e699cd</t>
+  </si>
+  <si>
+    <t>relationship--d3a9709d-a46f-4227-81d7-e6e5634a0302</t>
+  </si>
+  <si>
+    <t>relationship--43dfaf4c-6172-4636-abf7-58f7389a313a</t>
+  </si>
+  <si>
+    <t>relationship--a08de99e-babc-4c73-89e1-511da33d178f</t>
+  </si>
+  <si>
+    <t>relationship--3011b642-e89d-469c-8b87-c26a5ebc20e6</t>
+  </si>
+  <si>
+    <t>relationship--a2903297-c386-4f6f-88ee-56095925a8f8</t>
+  </si>
+  <si>
+    <t>relationship--82a68c0d-d200-4dd4-a31f-f90f19781a7b</t>
+  </si>
+  <si>
+    <t>relationship--0a7ae2be-d586-49b2-848a-d35fe6221dae</t>
+  </si>
+  <si>
+    <t>relationship--11c2c981-2861-4e11-bfe4-b9ea03bc55a6</t>
+  </si>
+  <si>
+    <t>relationship--30653f54-1144-451f-8a73-c772d9d37ae6</t>
+  </si>
+  <si>
+    <t>relationship--35876fdc-630e-4b12-82e5-f2ba7505da18</t>
+  </si>
+  <si>
+    <t>relationship--fabbb758-2eab-47c2-ab4b-48f37124af6d</t>
+  </si>
+  <si>
+    <t>relationship--c2a6ad46-9494-4602-8b49-6c5b61184028</t>
+  </si>
+  <si>
+    <t>relationship--71a5e70d-1844-487e-b58b-f12411b871be</t>
+  </si>
+  <si>
+    <t>relationship--6798f2aa-824f-4d90-aa8e-70f8b94b420b</t>
+  </si>
+  <si>
+    <t>relationship--ed0e3ac8-f813-4f09-87e7-0e63b84b673e</t>
+  </si>
+  <si>
+    <t>relationship--8d6c12cc-a7c3-440e-848a-372df4adbb25</t>
+  </si>
+  <si>
+    <t>relationship--6fdde582-d2f6-4b14-8062-f78006b5701d</t>
+  </si>
+  <si>
+    <t>relationship--e6a4a3da-8c38-4691-991c-e3796a099deb</t>
+  </si>
+  <si>
+    <t>relationship--3096411a-1b3e-4a34-81c0-218ae5fe4adf</t>
+  </si>
+  <si>
+    <t>relationship--ced6ed26-c661-4748-9b09-bdde45a8cad7</t>
+  </si>
+  <si>
+    <t>relationship--b6a532d9-6d35-402a-a5ae-4059ac805ac3</t>
+  </si>
+  <si>
+    <t>relationship--aadefadb-f9c7-4491-bbe8-31bded74968d</t>
+  </si>
+  <si>
+    <t>relationship--69cc82b3-ffb5-4f25-96de-20027f593d4b</t>
+  </si>
+  <si>
+    <t>relationship--ffef303a-cd51-484e-961a-4d2e74561851</t>
+  </si>
+  <si>
+    <t>relationship--e791d20c-3b75-408b-8439-7b02f4f2ed99</t>
+  </si>
+  <si>
+    <t>relationship--61f30394-7383-4183-b4a9-9557fa3674d3</t>
+  </si>
+  <si>
+    <t>relationship--4a6ba4ff-17ca-4cba-be0a-960a419db326</t>
+  </si>
+  <si>
+    <t>relationship--cba22c5b-84c1-4ee0-bc04-5a7842d90260</t>
+  </si>
+  <si>
+    <t>relationship--7c42a1f4-61f0-48a5-b148-aa0fb254753c</t>
+  </si>
+  <si>
+    <t>relationship--4c351522-0db6-4628-8576-fcb1c918fe5a</t>
+  </si>
+  <si>
+    <t>relationship--fee636b9-8da2-429f-9e0e-ccee4a7aada4</t>
+  </si>
+  <si>
+    <t>relationship--01949f0b-1cd3-4cdf-8890-e660d4b1b002</t>
+  </si>
+  <si>
+    <t>relationship--f73b86c1-baf5-47c5-ab38-720ee4d38172</t>
+  </si>
+  <si>
+    <t>relationship--8d9b024c-b400-4d09-9992-305245b00999</t>
+  </si>
+  <si>
+    <t>relationship--ee383f12-0a29-4bcd-88fc-b270e25a8201</t>
+  </si>
+  <si>
+    <t>relationship--a7432903-d603-4c02-b8d8-c8b425495628</t>
+  </si>
+  <si>
+    <t>relationship--b5752c8c-5814-4f12-ad6d-6051527219a7</t>
+  </si>
+  <si>
+    <t>relationship--c43baead-a761-49ff-84dc-58b22b15f5b8</t>
+  </si>
+  <si>
+    <t>relationship--87b25443-0dea-4375-99a5-b94fb037d3bf</t>
+  </si>
+  <si>
+    <t>relationship--9c17190e-df04-4cd2-a234-7a52469eabaa</t>
+  </si>
+  <si>
+    <t>relationship--5c59de0f-3849-497f-b2c4-73ff653bf302</t>
+  </si>
+  <si>
+    <t>relationship--80d37829-bc10-4193-974e-51176265bbc1</t>
+  </si>
+  <si>
+    <t>relationship--72685b4b-6062-4d74-9dff-4ba13c620c3a</t>
+  </si>
+  <si>
+    <t>relationship--b956b0db-8923-4f1b-a132-a0b090c6faa4</t>
+  </si>
+  <si>
+    <t>relationship--92bc94b1-d96e-49a3-b565-41edd55ac1ce</t>
+  </si>
+  <si>
+    <t>relationship--6b56ab98-8f9e-4d10-ae19-f48614840db6</t>
+  </si>
+  <si>
+    <t>relationship--5cccbf85-8e7b-4202-825b-331ac6eae594</t>
+  </si>
+  <si>
+    <t>relationship--2f5ca869-38ec-4c06-818d-8655b76c805f</t>
+  </si>
+  <si>
+    <t>relationship--12ba04d4-ec0b-430a-b6df-2ddea91c69d0</t>
+  </si>
+  <si>
+    <t>relationship--0884b721-8174-4470-bc1f-a330b2786d76</t>
+  </si>
+  <si>
+    <t>relationship--90fb7c60-7e16-44c3-a166-664bca42c0fd</t>
+  </si>
+  <si>
+    <t>relationship--96f90891-6551-4cc6-9042-37d2a4d7e08c</t>
+  </si>
+  <si>
+    <t>relationship--851cf535-c9d2-49b2-a01b-8189f820bda4</t>
+  </si>
+  <si>
+    <t>relationship--084aacff-f792-4a32-ba5e-4d390bba382a</t>
+  </si>
+  <si>
+    <t>relationship--e3ff212d-f813-46c7-a0fc-63a87a9b59d2</t>
+  </si>
+  <si>
+    <t>relationship--d3729e6e-3661-423f-ac0b-896242799742</t>
+  </si>
+  <si>
+    <t>relationship--251f7f4b-204e-4044-815f-74c94a6c6e5f</t>
+  </si>
+  <si>
+    <t>relationship--900bfeca-3c4a-4433-ab82-bd0bccd965f2</t>
+  </si>
+  <si>
+    <t>relationship--8c6dd965-f936-4ab4-822d-e38fe4b8f507</t>
+  </si>
+  <si>
+    <t>relationship--8235112b-b5ec-4181-98d4-403d2c40b7f6</t>
+  </si>
+  <si>
+    <t>relationship--cb62dc54-a96f-4c3b-a98e-5d196c2cc946</t>
+  </si>
+  <si>
+    <t>relationship--11861601-4c67-4455-ac91-ed19ab83b4c6</t>
+  </si>
+  <si>
+    <t>relationship--f6cdd3fd-a62d-4c09-a929-a7cff02c8579</t>
+  </si>
+  <si>
+    <t>relationship--cb4a3549-90b2-4c43-ae2a-fbca42126ff3</t>
+  </si>
+  <si>
+    <t>relationship--bcc1e041-da1f-4e57-9da6-449bfe43ff21</t>
+  </si>
+  <si>
+    <t>relationship--edfe3629-f7d7-4d8e-aa00-03b897589245</t>
+  </si>
+  <si>
+    <t>relationship--8ea680dc-bff6-4ea7-aeaa-813b362e863b</t>
+  </si>
+  <si>
+    <t>relationship--0e3bada6-26c1-478e-b673-530a946b63a1</t>
+  </si>
+  <si>
+    <t>relationship--f8f30c4f-ade4-4ef6-809c-16441ae862fd</t>
+  </si>
+  <si>
+    <t>relationship--c74f3bd5-e2cc-4165-a13e-66aa9601020d</t>
+  </si>
+  <si>
+    <t>relationship--1b5f59bf-00a0-4591-aa28-34ec03227d11</t>
+  </si>
+  <si>
+    <t>relationship--e32ef710-fa95-4857-a572-ef8bf0ced122</t>
+  </si>
+  <si>
+    <t>relationship--bdcb59cc-0d4b-4949-9ed1-814dac7c109d</t>
+  </si>
+  <si>
+    <t>relationship--5b6e78da-8a5d-43b4-87f6-a137c2411154</t>
+  </si>
+  <si>
+    <t>relationship--08393427-0327-4be9-ba5d-b2d757d8429b</t>
+  </si>
+  <si>
+    <t>relationship--4bc25d1c-7ba4-4464-9649-9b102c81968d</t>
+  </si>
+  <si>
+    <t>relationship--044dd6f3-d305-4803-886a-bf251b50c63b</t>
+  </si>
+  <si>
+    <t>relationship--3207582f-bb47-4628-bb8b-a8415b710ecf</t>
+  </si>
+  <si>
+    <t>relationship--02db7bda-1389-4971-94b4-f5154d094834</t>
+  </si>
+  <si>
+    <t>relationship--68a655d6-368e-4bde-b810-441a7d0143a4</t>
+  </si>
+  <si>
+    <t>relationship--4f48545a-1720-4006-ad9b-a0876ce4fb93</t>
+  </si>
+  <si>
+    <t>relationship--5fe344b0-9d81-4826-83a3-4f7d42f8d05d</t>
+  </si>
+  <si>
+    <t>relationship--2034b1d3-f0d9-4534-94b2-1afa913bb74b</t>
+  </si>
+  <si>
+    <t>relationship--ebde01ec-dbde-4310-ae56-948845e6137a</t>
+  </si>
+  <si>
+    <t>relationship--4671fecf-c19a-4ef8-b4a5-112cce6c2afc</t>
+  </si>
+  <si>
+    <t>relationship--82ec8041-50fd-4c17-9373-89a3e9071401</t>
+  </si>
+  <si>
+    <t>relationship--b8b78b5e-6b6d-4458-bbf9-9c21c51b8fc7</t>
+  </si>
+  <si>
+    <t>relationship--615fc71e-ac1b-4e9d-b2fe-96a1e6c13c58</t>
+  </si>
+  <si>
+    <t>relationship--703fa5b0-f848-4353-bf22-201af51d8233</t>
+  </si>
+  <si>
+    <t>relationship--a2e4776f-1771-4854-8df3-adf479cd901a</t>
+  </si>
+  <si>
+    <t>relationship--89259abe-68a3-48ba-8c45-fabf1c94e6e2</t>
+  </si>
+  <si>
+    <t>relationship--c5ec8ce7-84d4-4b5e-8b35-a6680e2faf08</t>
+  </si>
+  <si>
+    <t>relationship--b81c034a-adc9-418d-8398-26bdaab02d06</t>
+  </si>
+  <si>
+    <t>relationship--c51c8fb8-7bc7-4614-8461-28ae5ad941dc</t>
+  </si>
+  <si>
+    <t>relationship--26d73e2f-3be0-4fba-add6-3e1a575b8053</t>
+  </si>
+  <si>
+    <t>relationship--739cabcb-a62f-48fd-a999-929201109e6f</t>
+  </si>
+  <si>
+    <t>relationship--70ba336b-e238-42bf-80bc-2f53600905d2</t>
+  </si>
+  <si>
+    <t>relationship--b97a0648-7bd5-4e4a-9531-dc0bcf6d1ee8</t>
+  </si>
+  <si>
+    <t>relationship--7d2f8b54-1b5f-479b-9630-41282662f087</t>
+  </si>
+  <si>
+    <t>relationship--c19892b7-f97d-4022-ab3c-f363305e5bca</t>
+  </si>
+  <si>
+    <t>relationship--b063da00-31f5-437f-87ab-ba8018cdc4d1</t>
+  </si>
+  <si>
+    <t>relationship--d74c4298-814d-4531-921e-b37122dd9188</t>
+  </si>
+  <si>
+    <t>relationship--ebbc3b5d-4031-49b2-94d8-c73c10858461</t>
+  </si>
+  <si>
+    <t>relationship--91357c89-cfb1-4e8a-823b-6b4873bb7a8c</t>
+  </si>
+  <si>
+    <t>relationship--30f6e137-c0bb-4e15-bb46-c8f4b5f475b2</t>
+  </si>
+  <si>
+    <t>relationship--306c747f-107d-48fe-a8ee-9c67ec12a606</t>
+  </si>
+  <si>
+    <t>relationship--100feae9-07ed-494f-b4de-ff4709a5d15c</t>
+  </si>
+  <si>
+    <t>relationship--74012a50-25e4-4557-9d61-af86c1745636</t>
+  </si>
+  <si>
+    <t>relationship--2b6265e7-35bc-4a43-a171-d15f262419f8</t>
+  </si>
+  <si>
+    <t>relationship--9c2918bd-5d1a-4e8b-b55e-6700135f26bc</t>
+  </si>
+  <si>
+    <t>relationship--c0498a3b-8a68-465b-9417-d45acb1b423f</t>
+  </si>
+  <si>
+    <t>relationship--9d1ec8a1-3a3d-4f2d-8962-f6ea3194708e</t>
+  </si>
+  <si>
+    <t>relationship--09d55dfa-87a5-4494-b14a-8e6bf1f50e2f</t>
+  </si>
+  <si>
+    <t>relationship--678da5f6-64dc-4aa1-82f4-92ca4c77bc81</t>
+  </si>
+  <si>
+    <t>relationship--b38afac2-fe75-4142-bb93-7949b359bf7c</t>
+  </si>
+  <si>
+    <t>relationship--7ce72926-1403-446d-b9f7-93a779ffdc11</t>
+  </si>
+  <si>
+    <t>relationship--029f5417-a746-4e46-aee5-bcb78254c116</t>
+  </si>
+  <si>
+    <t>relationship--3756af38-5b2c-473e-9a37-f0204a180d2d</t>
+  </si>
+  <si>
+    <t>relationship--25df0b26-dc61-425b-9cef-32e7033ade88</t>
+  </si>
+  <si>
+    <t>relationship--55fa8a55-9b53-43cb-a768-0df4b9ab9a53</t>
+  </si>
+  <si>
+    <t>relationship--a418690a-e774-48a9-8340-f9a469fafcf4</t>
+  </si>
+  <si>
+    <t>relationship--ed16e650-05ac-4b91-8868-4ea7da1767e5</t>
+  </si>
+  <si>
+    <t>relationship--867dfb14-8c2b-4b8e-80bc-b44b5ce930e4</t>
+  </si>
+  <si>
+    <t>relationship--d4552e65-5900-4e1b-a1da-4de41096a501</t>
+  </si>
+  <si>
+    <t>relationship--36f9bd5a-2ed7-4bbe-903e-5fa84bc577bf</t>
+  </si>
+  <si>
+    <t>relationship--e64f7ded-c734-4617-b6d8-9425cbb85a1c</t>
+  </si>
+  <si>
+    <t>relationship--a89f2ce4-3ddf-4036-aae6-a1d9a19f3f87</t>
+  </si>
+  <si>
+    <t>relationship--c3510d35-f037-4f98-93e4-ec5a76c83ee5</t>
+  </si>
+  <si>
+    <t>relationship--6de7d78b-70c3-41cd-b5a0-b77032eb651f</t>
+  </si>
+  <si>
+    <t>relationship--a3ed486b-05a4-4cf9-b3b8-0fc4edf3e576</t>
+  </si>
+  <si>
+    <t>relationship--a21d52f0-d24b-476e-889d-a490ff8ecbff</t>
+  </si>
+  <si>
+    <t>relationship--d04aeb4f-0390-438a-a143-562419138113</t>
+  </si>
+  <si>
+    <t>relationship--bd629b95-20ab-4d0d-b12d-f9e85429d9dc</t>
+  </si>
+  <si>
+    <t>relationship--82dc59af-b787-4c95-b846-766fe2160d2b</t>
+  </si>
+  <si>
+    <t>relationship--521cf47d-9086-4747-b0c1-2f620e803e60</t>
+  </si>
+  <si>
+    <t>relationship--fcb84ba0-e7ff-411b-802f-2f1563797d7c</t>
+  </si>
+  <si>
+    <t>relationship--68cb7141-e68c-41f7-83d7-804773a49f2b</t>
+  </si>
+  <si>
+    <t>relationship--caab10d5-b2f5-4474-b142-0c5a76bb6f07</t>
+  </si>
+  <si>
+    <t>relationship--aa80aa04-c950-4990-bcd7-9b32d2fcd8c9</t>
+  </si>
+  <si>
+    <t>relationship--9c5dd875-ae43-4311-9802-2562e0f47a69</t>
+  </si>
+  <si>
+    <t>relationship--7f156f01-6712-424f-b5a6-7c83a8f6aaf7</t>
+  </si>
+  <si>
+    <t>relationship--9f3b7f7e-ac56-423a-8119-892cd8f3f8f0</t>
+  </si>
+  <si>
+    <t>relationship--779120b1-4823-4492-8e9b-8d462864f874</t>
+  </si>
+  <si>
+    <t>relationship--6f127d0e-fe13-41c0-946c-e27af93ffb4c</t>
+  </si>
+  <si>
+    <t>relationship--6b23876b-1f22-4086-a026-f9d071166757</t>
+  </si>
+  <si>
+    <t>relationship--534f1f64-3f68-4dde-b513-e26e831eccbb</t>
+  </si>
+  <si>
+    <t>relationship--679e5fc0-ce50-4618-989d-1f5c097c54d4</t>
+  </si>
+  <si>
+    <t>relationship--3285406a-4aca-47bd-a15b-1071f608eb2b</t>
+  </si>
+  <si>
+    <t>relationship--3ceb3db6-d2f6-4945-8711-2dfcadff20a8</t>
+  </si>
+  <si>
+    <t>relationship--5d023aa5-7d83-45e2-82c7-1d00556c6889</t>
+  </si>
+  <si>
+    <t>relationship--57dd14aa-e289-4836-a61c-5968a06c5771</t>
+  </si>
+  <si>
+    <t>relationship--09334bd2-619a-45c8-9216-10c476d79b96</t>
+  </si>
+  <si>
+    <t>relationship--064a1e85-e6ab-4143-a04d-f6451b648c61</t>
+  </si>
+  <si>
+    <t>relationship--1c6ae487-3cbe-4899-9211-cfe2f910ef5b</t>
+  </si>
+  <si>
+    <t>relationship--0fa04fbe-c06c-490c-9df9-c13435fc3fe2</t>
+  </si>
+  <si>
+    <t>relationship--a5bd1af5-a1f0-49ad-bd9e-35cf4d9fffff</t>
+  </si>
+  <si>
+    <t>relationship--e362f3dd-97e3-44cb-8754-b5f966e0eaee</t>
+  </si>
+  <si>
+    <t>relationship--f7afc586-97c5-4899-ac48-c7e9b0c3d838</t>
+  </si>
+  <si>
+    <t>relationship--32b2c924-b17e-40ed-9297-2c13f77d727d</t>
+  </si>
+  <si>
+    <t>relationship--9bd3f60d-0f98-416a-a54c-fd403a141c05</t>
+  </si>
+  <si>
+    <t>relationship--6a2054b6-ed02-443a-9a0c-adff96ec5fec</t>
+  </si>
+  <si>
+    <t>relationship--c2948a00-e0ac-4817-a1ee-43f2303cbf8f</t>
+  </si>
+  <si>
+    <t>relationship--e913fb5b-9ffc-4d66-bf59-f9b3f68b200b</t>
+  </si>
+  <si>
+    <t>relationship--f26ed8c2-db66-4248-9502-344887c5bd11</t>
+  </si>
+  <si>
+    <t>relationship--cd9d2bc9-2ab4-4738-b950-b130b3eb07f8</t>
+  </si>
+  <si>
+    <t>relationship--6e6bc5a8-3af4-455d-8123-550e49eea384</t>
+  </si>
+  <si>
+    <t>relationship--9b68254d-8d09-43ca-a758-debeb8c556bc</t>
+  </si>
+  <si>
+    <t>relationship--502b99ce-6b87-4d98-93d0-f5d83bf6039d</t>
+  </si>
+  <si>
+    <t>relationship--027bdceb-00a3-41a0-97f4-e29f8b53124e</t>
+  </si>
+  <si>
+    <t>relationship--05910ab0-7d69-4c1b-8654-33f28b265357</t>
+  </si>
+  <si>
+    <t>relationship--54a21f37-a99c-4de1-afb5-8d71c53916e6</t>
+  </si>
+  <si>
+    <t>relationship--c29fd3b2-45e4-42f6-b246-31b7bb7d77e1</t>
+  </si>
+  <si>
+    <t>relationship--311acc10-4a5a-4344-88a6-bec6ec319526</t>
+  </si>
+  <si>
+    <t>relationship--8d005776-9c08-450e-a7dd-75fdf03017ef</t>
+  </si>
+  <si>
+    <t>relationship--da050063-c065-4f64-b603-131c66564b27</t>
+  </si>
+  <si>
+    <t>relationship--7b77da04-ab8c-4853-ba78-ea68f918045f</t>
+  </si>
+  <si>
+    <t>relationship--d968e9cf-bac9-4fb8-bbac-8c2d02c54083</t>
+  </si>
+  <si>
+    <t>relationship--8a7e5e2f-2743-4768-bbc1-d3e89f312afa</t>
+  </si>
+  <si>
+    <t>relationship--daaa48ef-0c36-4443-b4a5-48114ee2269f</t>
+  </si>
+  <si>
+    <t>relationship--769748a7-f54a-4f41-9094-ad4f900591bf</t>
+  </si>
+  <si>
+    <t>relationship--ec87abc6-9641-4378-bc37-f1922bfa6e68</t>
+  </si>
+  <si>
+    <t>relationship--f123e402-c95a-4a58-a035-6769d33fba66</t>
+  </si>
+  <si>
+    <t>relationship--caa25457-ebc1-40b0-a2b4-774edffb669b</t>
+  </si>
+  <si>
+    <t>relationship--3e901e91-7d1a-4367-96d1-10be8c0b2df9</t>
+  </si>
+  <si>
+    <t>relationship--77cbf7e0-4ec3-4601-bfa7-e8e423f7ab0b</t>
+  </si>
+  <si>
+    <t>relationship--2c0a3765-6c13-410f-88d3-4fc78b67c0b4</t>
+  </si>
+  <si>
+    <t>relationship--bec6de6d-8e8d-4b94-a2c9-505039cde2e9</t>
+  </si>
+  <si>
+    <t>relationship--3a1ab7c1-8c43-48bd-94e3-915f6bde530f</t>
+  </si>
+  <si>
+    <t>relationship--68f9fe2a-e37e-44a7-a84f-197229636901</t>
+  </si>
+  <si>
+    <t>relationship--39580415-eb7f-4b71-b66a-b4e8f0df0f55</t>
+  </si>
+  <si>
+    <t>relationship--f49caced-62b5-4b68-b4dd-9fe6a7292e55</t>
+  </si>
+  <si>
+    <t>relationship--58b2abb6-02a7-45b3-8b5f-ec850122407a</t>
+  </si>
+  <si>
+    <t>relationship--d9035eff-e382-4c9d-aabc-937a7a051226</t>
+  </si>
+  <si>
+    <t>relationship--20d559c7-dba2-42fc-99f4-a6edaa1a32d4</t>
+  </si>
+  <si>
+    <t>relationship--6e948f4a-29cd-40a3-8f09-e0e70a92ec4e</t>
+  </si>
+  <si>
+    <t>relationship--0dfe276a-ab5f-4f02-8e44-434fa746e9ae</t>
+  </si>
+  <si>
+    <t>relationship--3f2d01b8-8530-4c17-8d6e-7d42d400a7e2</t>
+  </si>
+  <si>
+    <t>relationship--d9aec82b-c059-4c8a-bdf5-a7db19f9021c</t>
+  </si>
+  <si>
+    <t>relationship--8c5450b9-b74f-4d36-adf4-ac1da91a3111</t>
+  </si>
+  <si>
+    <t>relationship--532c2ae2-b015-410f-8ec4-63524e3e6c9f</t>
+  </si>
+  <si>
+    <t>relationship--dd7f3637-6aab-4fa1-95ad-c7004e880c76</t>
+  </si>
+  <si>
+    <t>relationship--b73f3df6-f349-49a0-85da-c9bb9849bfb0</t>
+  </si>
+  <si>
+    <t>relationship--8a035471-857e-40ba-953b-0aaa72176ee8</t>
+  </si>
+  <si>
+    <t>relationship--2328e2b4-4bc6-4432-afaf-43eaa9f10b9c</t>
+  </si>
+  <si>
+    <t>relationship--9c72f6da-453c-404e-87df-1a6c2b00e71c</t>
+  </si>
+  <si>
+    <t>relationship--8c006b00-a342-47c9-8e1b-2c6e44da94b5</t>
+  </si>
+  <si>
+    <t>relationship--dbd05fa7-67b6-402c-8c1c-1cd01026667b</t>
+  </si>
+  <si>
+    <t>relationship--82dfe3d2-cf42-4e0b-9d66-e20ec755ae3f</t>
+  </si>
+  <si>
+    <t>relationship--94e1f217-42f2-459a-a545-6908dbcc290f</t>
+  </si>
+  <si>
+    <t>relationship--c5b0e284-95f9-484c-92a6-3c060abd3bb4</t>
+  </si>
+  <si>
+    <t>relationship--4bef2a92-999b-40f7-b07e-43f35b20d3e9</t>
+  </si>
+  <si>
+    <t>relationship--c74aea9a-311e-4db8-bb79-230d25ed68cf</t>
+  </si>
+  <si>
+    <t>relationship--04be9262-c441-4b42-b94d-14faaaebd38c</t>
+  </si>
+  <si>
+    <t>relationship--969b8098-2f06-4c38-8172-a89ec340e80b</t>
+  </si>
+  <si>
+    <t>relationship--abf89ac4-e487-46e2-af8f-d97fd28f9695</t>
+  </si>
+  <si>
+    <t>relationship--a78f2573-bbf4-4faa-9f9d-efd9b2eff2b4</t>
+  </si>
+  <si>
+    <t>relationship--30e23b40-3719-422e-8520-1098b0016763</t>
+  </si>
+  <si>
+    <t>relationship--f48a15c2-ca8b-406b-84c5-6a2b6d21e93e</t>
+  </si>
+  <si>
+    <t>relationship--68d08496-2634-4207-ad5b-6e899bf802c8</t>
+  </si>
+  <si>
+    <t>relationship--b81f5723-5eba-4b15-b4f6-ba50840ad359</t>
+  </si>
+  <si>
+    <t>relationship--20f8a015-6548-49f3-a4e7-ae8c18417d23</t>
+  </si>
+  <si>
+    <t>relationship--299ffd4d-f82f-400e-a5aa-111a2ed09a8e</t>
+  </si>
+  <si>
+    <t>relationship--fc089b4a-0138-40d6-9e18-8fb7f03754fe</t>
+  </si>
+  <si>
+    <t>relationship--94ece72b-0f70-4993-b29a-dc24e5911e26</t>
+  </si>
+  <si>
+    <t>relationship--4d66a077-ef73-4411-aa65-a000fc5271d6</t>
+  </si>
+  <si>
+    <t>relationship--a85e51c1-c058-48fe-9670-ccb343a427f7</t>
+  </si>
+  <si>
+    <t>relationship--42c06f0f-9fa8-42b2-958e-14c55d447edb</t>
+  </si>
+  <si>
+    <t>relationship--6d2a64e6-e6a8-4c2c-8466-9c794ab85ea3</t>
+  </si>
+  <si>
+    <t>relationship--48b3a397-9487-43c5-93be-840d9196be1d</t>
+  </si>
+  <si>
+    <t>relationship--14002f20-00de-43de-8846-9e4815c6e6cb</t>
+  </si>
+  <si>
+    <t>relationship--c57997d0-9295-450d-b1d5-ef17bb026f14</t>
+  </si>
+  <si>
+    <t>relationship--0b66ea38-98f1-4ded-92aa-a87c70f1456e</t>
+  </si>
+  <si>
+    <t>relationship--d215e283-3d59-40e6-8460-f6a5da0c3967</t>
+  </si>
+  <si>
+    <t>relationship--56987cf9-8e22-4398-b818-5e7e27a195a2</t>
+  </si>
+  <si>
+    <t>relationship--748c50e4-9e83-48d8-b5dc-e2b72bd60247</t>
+  </si>
+  <si>
+    <t>relationship--316fd0c6-cab7-458c-84fd-fc6221f0663d</t>
+  </si>
+  <si>
+    <t>relationship--5788d123-f09b-4def-b333-893909521114</t>
+  </si>
+  <si>
+    <t>relationship--87da0ac6-947a-4f13-ba8f-bf23651d0427</t>
+  </si>
+  <si>
+    <t>relationship--92b40284-268e-45ba-b499-59bfaec55a0d</t>
+  </si>
+  <si>
+    <t>relationship--a5a8f704-0810-4bc8-b776-cbf441cf5f34</t>
+  </si>
+  <si>
+    <t>relationship--376b9c98-bbe9-4576-a7d5-b88d5d27e52c</t>
+  </si>
+  <si>
+    <t>relationship--0c7ca6c4-073f-403b-b328-1ef45fbce413</t>
+  </si>
+  <si>
+    <t>relationship--cc188f87-1d9f-4bbf-85c6-65ca54bdb76e</t>
+  </si>
+  <si>
+    <t>relationship--aca7b73d-4397-49c6-ad6e-2dd43056b078</t>
+  </si>
+  <si>
+    <t>relationship--92c2486f-7771-4d54-a3d4-a3421a1f2862</t>
+  </si>
+  <si>
+    <t>relationship--72148f06-d607-4671-b336-5a1536c25116</t>
+  </si>
+  <si>
+    <t>relationship--130c2ac9-f262-45c6-b77d-a2d8065683ea</t>
+  </si>
+  <si>
+    <t>relationship--86ec4c0b-7618-4d32-b98b-611a70b99238</t>
+  </si>
+  <si>
+    <t>relationship--b5f35d59-43c2-4e81-a3ec-c1161e36756d</t>
+  </si>
+  <si>
+    <t>relationship--99f14310-68be-4f34-acd2-67392f36d34b</t>
+  </si>
+  <si>
+    <t>relationship--3e8ddd9f-eda0-4019-b81e-7d6e0d60d2f9</t>
+  </si>
+  <si>
+    <t>relationship--82e32f3e-a764-4f88-afe1-d73d333891c8</t>
+  </si>
+  <si>
+    <t>relationship--66dca3ec-bcc9-4ed2-85dc-db0ec33168d1</t>
+  </si>
+  <si>
+    <t>relationship--5f096b88-2f2c-448a-b3a3-02097ce270a6</t>
+  </si>
+  <si>
+    <t>relationship--7279c43e-1e6e-45bd-b7cd-e797a5a43d24</t>
+  </si>
+  <si>
+    <t>relationship--a29b2824-45ad-45db-9742-9732ea3157cc</t>
+  </si>
+  <si>
+    <t>relationship--8191fabf-06ec-4790-8c02-3ed087bd1233</t>
+  </si>
+  <si>
+    <t>relationship--800ed080-994d-40de-82c1-16acaf0780ef</t>
+  </si>
+  <si>
+    <t>relationship--b4d332cc-909c-49b4-9495-853695c6e489</t>
+  </si>
+  <si>
+    <t>relationship--5479e1aa-31ef-46a0-8c84-04a8c6334045</t>
+  </si>
+  <si>
+    <t>relationship--55aacf60-9343-4762-9ca2-f1773ee2dbcd</t>
+  </si>
+  <si>
+    <t>relationship--00596951-f6ae-40c9-97d7-51de0a6b565b</t>
+  </si>
+  <si>
+    <t>relationship--229059fd-4439-4e29-9463-17e8651b60c0</t>
+  </si>
+  <si>
+    <t>relationship--b20a86bf-287d-44b3-bd3e-dc4030002891</t>
+  </si>
+  <si>
+    <t>relationship--f59f0908-a79b-47ec-a443-28e4f9f953b4</t>
+  </si>
+  <si>
+    <t>relationship--d0c58f4e-6a94-48fa-bef4-95ec61771e85</t>
+  </si>
+  <si>
+    <t>relationship--670733a5-9130-456a-9a29-3e3600d71854</t>
+  </si>
+  <si>
+    <t>relationship--d8e97d51-3c1b-414f-a9a9-dc5b64a0fffe</t>
+  </si>
+  <si>
+    <t>relationship--5b7fd894-b2fd-4aa4-9032-4af292a067bd</t>
+  </si>
+  <si>
+    <t>relationship--2c99dc15-cc14-4132-a24b-bdacddbb235a</t>
+  </si>
+  <si>
+    <t>relationship--7ed2f4dd-e17e-41b2-bc15-3c562eb565d8</t>
+  </si>
+  <si>
+    <t>relationship--76697244-576a-4797-b6d3-5bd6c753160b</t>
+  </si>
+  <si>
+    <t>relationship--84a7c21b-4146-4b53-9fb1-ac91bfb7b2ee</t>
+  </si>
+  <si>
+    <t>relationship--09eee7ad-efd2-4e3b-ab1a-ff2d5b8245a1</t>
+  </si>
+  <si>
+    <t>relationship--4e7ccf87-166e-40b2-baf7-409667f91e97</t>
+  </si>
+  <si>
+    <t>relationship--9a726b46-0b15-4802-a454-931b29750f3b</t>
+  </si>
+  <si>
+    <t>relationship--0e881f78-62ee-436c-8548-f9c3ce45e1be</t>
+  </si>
+  <si>
+    <t>relationship--363efa53-2bc0-4a84-a2a2-642c4a154b99</t>
+  </si>
+  <si>
+    <t>relationship--9283d9e2-6fad-48e2-b81f-4791c4c918ad</t>
+  </si>
+  <si>
+    <t>relationship--f8dbb330-c03b-4d8b-8f09-f5eca322caa0</t>
+  </si>
+  <si>
+    <t>relationship--f85871a1-f01a-41ce-b0d5-6d7e5b6fc53c</t>
+  </si>
+  <si>
+    <t>relationship--2ea43e52-206a-4f84-997a-d1055440a2b8</t>
+  </si>
+  <si>
+    <t>relationship--f8488d36-b4db-4b51-b9db-a1fb22f47055</t>
+  </si>
+  <si>
+    <t>relationship--9e64984f-6623-44a1-958a-e1226e7db177</t>
+  </si>
+  <si>
+    <t>relationship--ca908ca9-1b02-438c-9233-fa17ce3950dd</t>
+  </si>
+  <si>
+    <t>relationship--51d72dd2-c0d4-4e6b-a926-deca764f5143</t>
+  </si>
+  <si>
+    <t>relationship--f16b12ff-361d-4554-b263-667f9b3dc56a</t>
+  </si>
+  <si>
+    <t>relationship--522fdb89-48f3-4736-9f85-a9d09be3c5f2</t>
+  </si>
+  <si>
+    <t>relationship--65b7e52d-99cc-45f4-af04-6757248b78b0</t>
+  </si>
+  <si>
+    <t>relationship--06d9c953-145a-4483-b984-94e089da5add</t>
+  </si>
+  <si>
+    <t>relationship--e2514085-8eee-4a3c-ba89-8455fc03c02b</t>
+  </si>
+  <si>
+    <t>relationship--bbed2f44-88a2-4dd4-a6c2-f10b83a66748</t>
+  </si>
+  <si>
+    <t>relationship--d4014cf0-2ae5-45f8-afdb-81ba5b2474f9</t>
+  </si>
+  <si>
+    <t>relationship--2ab71617-01d2-49c4-b3c0-4ffa82beea2d</t>
+  </si>
+  <si>
+    <t>relationship--e776d33f-87d3-4836-849f-4130197f473f</t>
+  </si>
+  <si>
+    <t>relationship--60cce790-bf5c-4690-bc5a-3ac63124aacb</t>
+  </si>
+  <si>
+    <t>relationship--05dde170-efe6-4def-908e-c6530f75c2b9</t>
+  </si>
+  <si>
+    <t>relationship--d646627e-6cb4-4875-8b83-73d90c69c5af</t>
+  </si>
+  <si>
+    <t>relationship--53fff489-b21c-4c86-8813-3f760348a14e</t>
+  </si>
+  <si>
+    <t>relationship--9e44cf99-695b-4716-b18d-796934094dab</t>
+  </si>
+  <si>
+    <t>relationship--f1265f46-e9f4-4ff7-a5fc-c077c5e98486</t>
+  </si>
+  <si>
+    <t>relationship--6f536c3e-03c0-4191-bc9f-ad9b2fc58b86</t>
+  </si>
+  <si>
+    <t>relationship--d9408c42-9534-4c31-9ed4-d1c2b408fce2</t>
+  </si>
+  <si>
+    <t>relationship--30f2ede4-96f1-443a-9238-ba6e6337dcc2</t>
+  </si>
+  <si>
+    <t>relationship--5e2c4902-c553-42fe-be38-65d2124b3a72</t>
+  </si>
+  <si>
+    <t>relationship--90ea2161-72d3-4e45-bdee-ff03cca959ad</t>
+  </si>
+  <si>
+    <t>relationship--9f6df441-2b5b-4e98-a769-4e01d473b561</t>
+  </si>
+  <si>
+    <t>relationship--d1faf29f-4646-4999-8612-238216e90c34</t>
+  </si>
+  <si>
+    <t>relationship--8f3cebb8-5a4c-40ad-bfda-eabc54424cdd</t>
+  </si>
+  <si>
+    <t>relationship--6fe997fb-a0ae-4c8c-a942-c25747c87864</t>
+  </si>
+  <si>
+    <t>relationship--0d3f2953-a543-448a-8e53-97420eda03cd</t>
+  </si>
+  <si>
+    <t>relationship--0df8f055-9e58-4a1d-b29c-0b66772ea766</t>
+  </si>
+  <si>
+    <t>relationship--633708db-156f-4b9f-a067-4752f8700b9c</t>
+  </si>
+  <si>
+    <t>relationship--a66260b8-c4ca-4462-bf3c-fcf19e787c9d</t>
+  </si>
+  <si>
+    <t>relationship--fc8cf2da-f266-443c-a83c-94c6ddd45fa8</t>
+  </si>
+  <si>
+    <t>relationship--2719f96e-0d89-4eec-b6da-4e7d5c973c7b</t>
+  </si>
+  <si>
+    <t>relationship--c9ab5858-9197-464a-8d00-8471cd67d48d</t>
+  </si>
+  <si>
+    <t>relationship--daf0a4d5-dea0-43cc-b1a6-fbc842dcbf02</t>
+  </si>
+  <si>
+    <t>relationship--bfcc0f69-d518-409c-9a96-46b635739144</t>
+  </si>
+  <si>
+    <t>relationship--d0a94c00-6142-4f67-b726-42723428e9e9</t>
+  </si>
+  <si>
+    <t>relationship--a8fac3b8-243e-4d5a-b4e7-67aa9b609767</t>
+  </si>
+  <si>
+    <t>relationship--6333146b-75b1-4448-b636-99e9d993ab8b</t>
+  </si>
+  <si>
+    <t>relationship--a338f362-f7f3-419a-b01e-1dbbab5cd5b2</t>
+  </si>
+  <si>
+    <t>relationship--5e15e7a8-f5ad-45f7-b3c7-ba394e55d1ee</t>
+  </si>
+  <si>
+    <t>relationship--7f128905-efc8-4d5d-9d2d-f1e3b184e62f</t>
+  </si>
+  <si>
+    <t>relationship--9c98a24f-1276-4b15-b335-19ce4e396590</t>
+  </si>
+  <si>
+    <t>relationship--8cfc4447-4b2f-4da9-9436-8294977035f8</t>
+  </si>
+  <si>
+    <t>relationship--9cce0756-e414-47b5-9ddb-fc35764061c4</t>
+  </si>
+  <si>
+    <t>relationship--3150b3ca-4a8e-4ba9-b61e-3571b75308e4</t>
+  </si>
+  <si>
+    <t>relationship--daa2b9cc-1867-43bb-8d89-9bf1e3088a9a</t>
+  </si>
+  <si>
+    <t>relationship--35c06343-36f8-4364-902c-5dffd8fdab30</t>
+  </si>
+  <si>
+    <t>relationship--fbe54f7b-dcf3-475f-ab52-d231e609a596</t>
+  </si>
+  <si>
+    <t>relationship--1eb9591f-0fba-4d0f-ae3a-7a9201d14a66</t>
+  </si>
+  <si>
+    <t>relationship--c7d8a464-a45c-4ef1-9891-731e41a36859</t>
+  </si>
+  <si>
+    <t>relationship--dc050f02-458f-4657-8d9b-5b3c21a5bb13</t>
+  </si>
+  <si>
+    <t>relationship--aa9eb727-03bb-4a54-955c-5f974856da12</t>
+  </si>
+  <si>
+    <t>relationship--3cd75a2d-d0e2-46c3-81ae-a1bbd37da6d2</t>
+  </si>
+  <si>
+    <t>relationship--efdf65fb-87d6-4f49-a218-0729cbeda7f2</t>
+  </si>
+  <si>
+    <t>relationship--f8dcd40e-1d06-4f44-a76e-7d5ba8546ce5</t>
+  </si>
+  <si>
+    <t>relationship--77c3d5b9-49bc-4bf2-b377-69e2481777a7</t>
+  </si>
+  <si>
+    <t>relationship--f7ba946e-3445-42c0-800c-384482de48f7</t>
+  </si>
+  <si>
+    <t>relationship--882c19c3-32a5-45ba-8d87-b7ae05464529</t>
+  </si>
+  <si>
+    <t>relationship--0c498660-baa4-4b56-9f9f-5da20757e52c</t>
+  </si>
+  <si>
+    <t>relationship--d8b6c99d-7ea9-4115-a161-58b8288517af</t>
+  </si>
+  <si>
+    <t>relationship--0370eab8-1f78-4e7e-9a43-5e854c096175</t>
+  </si>
+  <si>
+    <t>relationship--40e6e927-26d8-4a53-9a39-562850a77ae6</t>
+  </si>
+  <si>
+    <t>relationship--94f3c49d-188c-4725-8931-378a7c9bd42b</t>
+  </si>
+  <si>
+    <t>relationship--36a12f19-d0b9-4f59-9699-3be9def17e0d</t>
+  </si>
+  <si>
+    <t>relationship--5d53e412-ce44-4a3f-9e8e-ab2578741f04</t>
+  </si>
+  <si>
+    <t>relationship--711aa43b-6813-4fb9-9561-2a5475fed2dc</t>
+  </si>
+  <si>
+    <t>relationship--e9e8d50e-7d51-42a4-8312-700e58d90cc6</t>
+  </si>
+  <si>
+    <t>relationship--40ade569-6090-43f5-b71d-a73c6ee331d0</t>
+  </si>
+  <si>
+    <t>relationship--59b4d189-d57c-4c25-912c-da3eac3935d7</t>
+  </si>
+  <si>
+    <t>relationship--5dc280b6-ad46-4eb4-bd59-c0eec3938586</t>
+  </si>
+  <si>
+    <t>relationship--9f796ff7-1407-4783-be07-f9e77236376b</t>
+  </si>
+  <si>
+    <t>relationship--828c5a4e-c77e-46e9-a017-5afda757901d</t>
+  </si>
+  <si>
+    <t>relationship--22aa4145-ca0f-42d3-a693-0ccb175ca09c</t>
+  </si>
+  <si>
+    <t>relationship--83b819c1-7d01-44de-b61e-e8f32d4bd50c</t>
+  </si>
+  <si>
+    <t>relationship--082e12b3-5cac-4e3b-935a-b3f2aaedafe3</t>
+  </si>
+  <si>
+    <t>relationship--b50a765d-8def-4040-8c8c-ce25f592c050</t>
+  </si>
+  <si>
+    <t>relationship--e76bcde7-0d9d-4190-9819-4b77cd700714</t>
+  </si>
+  <si>
+    <t>relationship--b9c85a70-daa2-4e16-a294-1567f0898dd7</t>
+  </si>
+  <si>
+    <t>relationship--441033b7-c60c-4c3e-b4d3-e26d3ec6fb68</t>
+  </si>
+  <si>
+    <t>relationship--116af3a9-24e5-4886-894a-a91490a9a477</t>
+  </si>
+  <si>
+    <t>relationship--b1f65d92-35bc-46cb-998b-9c4f2cc6236f</t>
+  </si>
+  <si>
+    <t>relationship--216f04f8-646b-42b9-97a6-18dcf91c23d6</t>
+  </si>
+  <si>
+    <t>relationship--ea7b89a8-3a82-48af-95c4-fc0acda776c6</t>
+  </si>
+  <si>
+    <t>relationship--05aba7b5-d0cd-4fea-a518-04d20ee394bd</t>
+  </si>
+  <si>
+    <t>relationship--880bd43a-eb5c-4601-83a1-b14701b903d5</t>
+  </si>
+  <si>
+    <t>relationship--b1f54bc2-9e1f-46fc-81bf-6f1a639d314c</t>
+  </si>
+  <si>
+    <t>relationship--394f8a14-cd2b-40c7-8b99-377d117c91a0</t>
+  </si>
+  <si>
+    <t>relationship--2b9cfb6a-c6d3-475d-a2b8-32c382636825</t>
+  </si>
+  <si>
+    <t>relationship--068429d2-940b-4cc9-8e01-544e28d28140</t>
+  </si>
+  <si>
+    <t>relationship--2c197396-1567-4ba5-b652-ddcc53676c4b</t>
+  </si>
+  <si>
+    <t>relationship--000a7b7b-b69e-4e6b-8b11-825be421600e</t>
+  </si>
+  <si>
+    <t>relationship--6d7b6a67-ff04-41c7-aa81-0117620c0dc8</t>
+  </si>
+  <si>
+    <t>relationship--1cf1b7f4-3e14-4c4a-b328-1af6f2bf4dcd</t>
+  </si>
+  <si>
+    <t>relationship--2299e07f-541b-4421-bd11-4ffc91b977f5</t>
+  </si>
+  <si>
+    <t>relationship--47b73fa8-3f8f-4f25-8213-bf363e417d87</t>
+  </si>
+  <si>
+    <t>relationship--be02b2c4-4b58-436b-a726-3f377f5db0ad</t>
+  </si>
+  <si>
+    <t>relationship--7754990e-37eb-498c-91cd-c94018b1f4de</t>
+  </si>
+  <si>
+    <t>relationship--73fb2605-368d-4e7d-b76b-1b171bf6c428</t>
+  </si>
+  <si>
+    <t>relationship--cb354cd3-cc23-48c9-a933-b4592cbe36d1</t>
+  </si>
+  <si>
+    <t>relationship--7b89c335-642f-460c-a3c9-f184a722687f</t>
+  </si>
+  <si>
+    <t>relationship--32e32a50-83a8-4cae-933f-e7d0bc721672</t>
+  </si>
+  <si>
+    <t>relationship--671ec298-b979-419d-a141-8995a9f22cab</t>
+  </si>
+  <si>
+    <t>relationship--b73d6596-ff9a-4e10-9001-86645589ef80</t>
+  </si>
+  <si>
+    <t>relationship--17f4e651-2edc-40ae-b24a-2459922e2a05</t>
+  </si>
+  <si>
+    <t>relationship--8d658ebc-bf8f-4620-8630-b15943c990e5</t>
+  </si>
+  <si>
+    <t>relationship--2fe01f88-0caf-4125-8a5f-d2c56ed1c8e1</t>
+  </si>
+  <si>
+    <t>relationship--b5f12a30-4546-421d-896a-6ee9d8103cf8</t>
+  </si>
+  <si>
+    <t>relationship--6aac1e45-a96b-4357-91f2-a0ca8fe3b2d9</t>
+  </si>
+  <si>
+    <t>relationship--a0059280-c87e-4e5d-a68e-2ce66f9049dd</t>
+  </si>
+  <si>
+    <t>relationship--ed1f01db-1e4b-4333-aed8-8feb930cbd25</t>
+  </si>
+  <si>
+    <t>relationship--dcb15ec2-4ba3-45b3-bab6-d0a35b53efd5</t>
+  </si>
+  <si>
+    <t>relationship--bcf1261b-1d44-4642-bbb1-4e51ddb8ef2a</t>
+  </si>
+  <si>
+    <t>relationship--dbd00edc-0858-4977-a104-b41e28f12a0f</t>
+  </si>
+  <si>
+    <t>relationship--f57639bf-201d-4950-a5cd-fe88131263d2</t>
+  </si>
+  <si>
+    <t>relationship--1aef3932-9976-42c8-980e-1d9efff3d421</t>
+  </si>
+  <si>
+    <t>relationship--1e4b2641-38f4-4e96-abdb-d938ae6c6238</t>
+  </si>
+  <si>
+    <t>relationship--e287ae25-2e74-46aa-9b98-26c6a19bf65c</t>
+  </si>
+  <si>
+    <t>relationship--d2a67c7f-869e-478d-9871-59136624729a</t>
+  </si>
+  <si>
+    <t>relationship--6acb8cbb-4f84-4909-9b4e-2c8202d04abe</t>
+  </si>
+  <si>
+    <t>relationship--66666a90-5cb2-4740-aafe-9a5299fbe3f9</t>
+  </si>
+  <si>
+    <t>relationship--66ca0d56-9c4d-41db-900c-9dfcff7fe057</t>
+  </si>
+  <si>
+    <t>relationship--4bfd2c7b-9c17-466b-9bbc-bdc63032c3e5</t>
+  </si>
+  <si>
+    <t>relationship--d07b4055-b125-4228-992e-6e802c7a93e5</t>
+  </si>
+  <si>
+    <t>relationship--560be8a7-57ae-4dd3-bba0-c198ef86b643</t>
+  </si>
+  <si>
+    <t>relationship--fd809d03-b56d-4cb1-ab27-0df8bdb16010</t>
+  </si>
+  <si>
+    <t>relationship--db6ed9ba-d766-4ba6-ab10-829dba38cc29</t>
+  </si>
+  <si>
+    <t>relationship--9898f608-301d-4ee1-9af7-76120f8f33a1</t>
+  </si>
+  <si>
+    <t>relationship--ba8b2cb4-a978-4bfc-90ff-0f052f754ffa</t>
+  </si>
+  <si>
+    <t>relationship--87a11c30-2455-4c22-b451-f0891145a71e</t>
+  </si>
+  <si>
+    <t>relationship--aded852e-212a-467f-b078-ea92938e146a</t>
+  </si>
+  <si>
+    <t>relationship--3c2dfcb9-c806-406e-b98e-8c858d3c84ce</t>
+  </si>
+  <si>
+    <t>relationship--3ead08d2-96ee-4dba-a512-7c74ce81420b</t>
+  </si>
+  <si>
+    <t>relationship--fbff1298-e133-43b5-8048-44a12db54c6b</t>
+  </si>
+  <si>
+    <t>relationship--95320403-f9e3-4539-9622-7123db51532a</t>
+  </si>
+  <si>
+    <t>relationship--1c07b56c-b0f8-4d44-adf0-61fab799bb51</t>
+  </si>
+  <si>
+    <t>relationship--371bf0de-ef2b-4d23-9f3a-fa4e4bd70675</t>
+  </si>
+  <si>
+    <t>relationship--4e7f0703-4a4a-4100-ace3-c5e0f236041c</t>
+  </si>
+  <si>
+    <t>relationship--832eaa6e-6def-41bc-af18-64e083bb5bb9</t>
+  </si>
+  <si>
+    <t>relationship--227fe652-ed44-4899-a63d-6f4f0340ccc8</t>
+  </si>
+  <si>
+    <t>relationship--4dbc7d46-2c40-4cf8-b932-0ef494b70824</t>
+  </si>
+  <si>
+    <t>relationship--6bf0493a-2765-4878-8bc9-7da8aaa08690</t>
+  </si>
+  <si>
+    <t>relationship--5a545a86-385a-452f-b672-07daffb240a6</t>
+  </si>
+  <si>
+    <t>relationship--58454603-5adb-4d47-8073-b0fd3ff41b48</t>
+  </si>
+  <si>
+    <t>relationship--6114c657-8545-4b80-b759-ec9eb97496b5</t>
+  </si>
+  <si>
+    <t>relationship--cb3c049e-0fc6-407d-bcd1-5c181f383e6a</t>
+  </si>
+  <si>
+    <t>relationship--c92e04c5-1ab3-4d20-8240-2dfcfe12818d</t>
+  </si>
+  <si>
+    <t>relationship--d31acd52-174a-4a02-b0da-3ae9e90e726f</t>
+  </si>
+  <si>
+    <t>relationship--8c2f592b-0f60-438c-ae97-e0a43726e484</t>
+  </si>
+  <si>
+    <t>relationship--bcefa2a4-d79c-476a-9079-c86e034cf032</t>
+  </si>
+  <si>
+    <t>relationship--350248bf-2314-4746-ace1-022505408aa3</t>
+  </si>
+  <si>
+    <t>relationship--89ee6808-4eb6-4311-8f59-81b5849af53d</t>
+  </si>
+  <si>
+    <t>relationship--9d6bd921-7587-4be6-986e-3eba7dec6aeb</t>
+  </si>
+  <si>
+    <t>relationship--2faffb4d-f7bf-46fa-a07e-d77f0ea7a683</t>
+  </si>
+  <si>
+    <t>relationship--ea9a6b8b-2bf5-4ec6-b6ce-bc9d1c084186</t>
+  </si>
+  <si>
+    <t>relationship--4bf236fc-b663-4ee3-b41c-dee2b4de2579</t>
+  </si>
+  <si>
+    <t>relationship--b47641a3-817f-41bc-a3b7-ddf0b8b09215</t>
+  </si>
+  <si>
+    <t>relationship--f45ac9f8-f7e0-4858-bb3a-6765e3d37fc7</t>
+  </si>
+  <si>
+    <t>relationship--888de46e-4ebe-4057-adca-05da7851d732</t>
+  </si>
+  <si>
+    <t>relationship--098053f3-ecc7-4a8e-b48a-076c3a6c4248</t>
+  </si>
+  <si>
+    <t>relationship--11a6a9a8-2bf7-406f-af05-38bf00996763</t>
+  </si>
+  <si>
+    <t>relationship--eb103c6c-e029-410d-b091-baccb8e3baed</t>
+  </si>
+  <si>
+    <t>relationship--1bda8ee5-4aed-411d-92cb-0d686c7bf109</t>
+  </si>
+  <si>
+    <t>relationship--f6c605eb-71f9-4e45-a469-1c13eea0057c</t>
+  </si>
+  <si>
+    <t>relationship--34778cd5-5f2e-4850-8ca5-277697ec6f26</t>
+  </si>
+  <si>
+    <t>relationship--8479afda-003f-45ee-88a5-42cb2601f60d</t>
+  </si>
+  <si>
+    <t>relationship--0b860690-4b4b-4de0-b97f-0f03e5bae7b1</t>
+  </si>
+  <si>
+    <t>relationship--8d99c363-5696-4ec1-93d2-76a1efc2be24</t>
+  </si>
+  <si>
+    <t>relationship--97a46902-0296-4c08-8573-7a1a141108c4</t>
+  </si>
+  <si>
+    <t>relationship--2e336a93-79a2-48d4-9cb2-80cc70b0a788</t>
+  </si>
+  <si>
+    <t>relationship--91608beb-1733-48fb-aaae-5245f2c2ab5f</t>
+  </si>
+  <si>
+    <t>relationship--28c14042-3560-4fa2-ae10-93ff029006c1</t>
+  </si>
+  <si>
+    <t>relationship--6d2bfe6f-2e24-4a26-a4ec-7d97ba3e3ee1</t>
+  </si>
+  <si>
+    <t>relationship--606777db-3c58-4fc6-87fc-84295bbd7c08</t>
+  </si>
+  <si>
+    <t>relationship--71021127-3d72-4d1d-8eda-4cd4758cb2ef</t>
+  </si>
+  <si>
+    <t>relationship--39024a63-5cf2-404a-8955-e00e9fd0cc74</t>
+  </si>
+  <si>
+    <t>relationship--4786afb9-7ece-4b67-9b03-5f06d6a87640</t>
+  </si>
+  <si>
+    <t>relationship--d8704b08-6efe-48d2-9fe1-b11e6e9b239f</t>
+  </si>
+  <si>
+    <t>relationship--a5590456-58a3-4763-8656-c6c698745e04</t>
+  </si>
+  <si>
+    <t>relationship--c276cc79-9a85-4b84-a7f6-cb2d4d8ddce2</t>
+  </si>
+  <si>
+    <t>relationship--0e91cd31-618f-4d5f-9783-6456a1bf170b</t>
+  </si>
+  <si>
+    <t>relationship--d10aca3c-9c26-482f-abc8-ab07765940b3</t>
+  </si>
+  <si>
+    <t>relationship--f6182e0f-3db8-4362-85ee-6f5cc00b0073</t>
+  </si>
+  <si>
+    <t>relationship--a749cb84-86d9-404c-903a-78bf514e0165</t>
+  </si>
+  <si>
+    <t>relationship--621f3b93-d229-4d3d-9e6c-98224c3a8ca4</t>
+  </si>
+  <si>
+    <t>relationship--6a2b063b-ac17-40ef-a680-2be97a56779b</t>
+  </si>
+  <si>
+    <t>relationship--c12e5a55-f163-4252-8415-90c4173c4357</t>
+  </si>
+  <si>
+    <t>relationship--f1caf9f5-5188-4fe6-973b-f611211d04c9</t>
+  </si>
+  <si>
+    <t>relationship--11031d92-5798-45c9-8451-acf7e7338360</t>
+  </si>
+  <si>
+    <t>relationship--1aa34e58-85eb-48cd-8374-01cc00b65152</t>
+  </si>
+  <si>
+    <t>relationship--9a451426-b708-4bd0-b4f7-c66ef3274f01</t>
+  </si>
+  <si>
+    <t>relationship--4fa88cf6-6bc2-4738-a61a-02f7e74410d5</t>
+  </si>
+  <si>
+    <t>relationship--476ee537-2472-458d-881c-64b3f4f9255d</t>
+  </si>
+  <si>
+    <t>relationship--070a0e74-189d-4a2b-a541-7deb1b750704</t>
+  </si>
+  <si>
+    <t>relationship--6ec59964-2d4f-47a8-a276-945647c64424</t>
+  </si>
+  <si>
+    <t>relationship--b817bccc-ef96-4808-b3e9-fca648d47d91</t>
+  </si>
+  <si>
+    <t>relationship--5afb96a6-107e-4f01-9ea4-0714279d56ea</t>
+  </si>
+  <si>
+    <t>relationship--af335d81-3aa2-42f2-8fd6-7f1a104bf891</t>
+  </si>
+  <si>
+    <t>relationship--cda4575c-0391-4246-8c83-dcade4e0c409</t>
+  </si>
+  <si>
+    <t>relationship--a30d0a72-891d-452e-87b8-656803733bf9</t>
+  </si>
+  <si>
+    <t>relationship--f3c93591-35f1-42e0-b9a6-9069194543df</t>
+  </si>
+  <si>
+    <t>relationship--05fbff25-57d7-40fd-9873-2d11967342f9</t>
+  </si>
+  <si>
+    <t>relationship--4dc049b7-3fff-462d-bfa0-9d54c502b9c7</t>
+  </si>
+  <si>
+    <t>relationship--bef86b86-c298-4799-b9fe-ddef9bd0ac3f</t>
+  </si>
+  <si>
+    <t>relationship--2dccb134-959a-441e-9567-ca71764282da</t>
+  </si>
+  <si>
+    <t>relationship--fc6886a0-507b-4f42-9116-9babce24c66c</t>
+  </si>
+  <si>
+    <t>relationship--cb4841e5-fcbf-4238-97ab-ac1491674c04</t>
+  </si>
+  <si>
+    <t>relationship--fa1031d5-eb45-4a63-939d-c75bbb0c0e41</t>
+  </si>
+  <si>
+    <t>relationship--4b7736ca-d14a-4f63-b42d-38ac979d394f</t>
+  </si>
+  <si>
+    <t>relationship--0cc787a2-e033-46f6-b624-51f5e2f0490b</t>
+  </si>
+  <si>
+    <t>relationship--6f5fe5a3-3a8e-47e0-99b6-a8d515a90518</t>
+  </si>
+  <si>
+    <t>relationship--55fb6563-517e-40fa-9886-67d2f81c628c</t>
+  </si>
+  <si>
+    <t>relationship--474ecfda-ac24-4ecc-8354-046d96c042d0</t>
+  </si>
+  <si>
+    <t>relationship--edef7abf-cd62-4d73-ac53-91defb58eab5</t>
+  </si>
+  <si>
+    <t>relationship--93de474b-1c3b-4541-9f3e-b92dce277007</t>
+  </si>
+  <si>
+    <t>relationship--79a4fe06-b6e4-46f4-a39a-0e9f0eca392d</t>
+  </si>
+  <si>
+    <t>relationship--f3ed7ecf-0230-44e4-85bd-3034a52c0ff1</t>
+  </si>
+  <si>
+    <t>relationship--644c5915-567b-49d8-9972-fe404438e5fb</t>
+  </si>
+  <si>
+    <t>relationship--3f899c83-638c-4849-932d-b26081165ff5</t>
+  </si>
+  <si>
+    <t>relationship--3bb0fad7-3142-46fc-b8c7-2ec840c329f9</t>
+  </si>
+  <si>
+    <t>relationship--871b5ea1-0a83-41a1-8063-9fa059ad485b</t>
+  </si>
+  <si>
+    <t>relationship--78583edd-dabe-4257-afa5-6277798a3cd3</t>
+  </si>
+  <si>
+    <t>relationship--9be2642e-ce3d-4789-9abd-eb74d7bd03f7</t>
+  </si>
+  <si>
+    <t>relationship--94712f84-0253-436e-b21d-289210e1defb</t>
+  </si>
+  <si>
+    <t>relationship--c73dedd6-8bae-492c-a165-31fb9afd51d8</t>
+  </si>
+  <si>
+    <t>relationship--f2b648a4-0b24-46eb-84eb-25e7d0ee66f0</t>
+  </si>
+  <si>
+    <t>relationship--dd1bdb48-a2e6-4fb8-8df1-1681eec3f2a8</t>
+  </si>
+  <si>
+    <t>relationship--e56f09db-7b44-4ba2-89a6-5cccf25898cd</t>
+  </si>
+  <si>
+    <t>relationship--7f39f7d4-cb35-4494-8690-597ca5e703e3</t>
+  </si>
+  <si>
+    <t>relationship--48560cde-91cf-43a4-bea6-9eb20f8414e1</t>
+  </si>
+  <si>
+    <t>relationship--e0d04d2e-7d69-4faa-b211-a0e0c94f2162</t>
+  </si>
+  <si>
+    <t>relationship--7db6debd-6a95-4272-8894-61c4b24f6059</t>
+  </si>
+  <si>
+    <t>relationship--a1925a59-fd14-4698-9847-6bf720ac2140</t>
+  </si>
+  <si>
+    <t>relationship--ce446af8-353b-40f8-b5af-63f9c61bbe60</t>
+  </si>
+  <si>
+    <t>relationship--6643128f-179c-4803-8c05-acd5ce1d7113</t>
+  </si>
+  <si>
+    <t>relationship--29b6a613-4df6-479a-ac3f-0c4d90d4231b</t>
+  </si>
+  <si>
+    <t>relationship--a6a374a1-49e1-4fa7-b837-9d2c855646d6</t>
+  </si>
+  <si>
+    <t>relationship--6a04fb16-d247-4703-b70b-933427dc6b47</t>
+  </si>
+  <si>
+    <t>relationship--e10761b8-38e0-40c2-b491-48a76b7646f1</t>
+  </si>
+  <si>
+    <t>relationship--b53f022a-ff91-4a2f-87c0-1a0f50a03000</t>
+  </si>
+  <si>
+    <t>relationship--4d654486-4763-4c37-936f-52e5f24ff8b6</t>
+  </si>
+  <si>
+    <t>relationship--cf099842-4240-4d4e-a249-ba214c3823b9</t>
+  </si>
+  <si>
+    <t>relationship--7be0184f-af80-4e3e-aec0-8bb363d21a54</t>
+  </si>
+  <si>
+    <t>relationship--876b6e5e-60fe-4d5c-bae7-31eff45f261c</t>
+  </si>
+  <si>
+    <t>relationship--1717dd61-13b5-4346-839d-d6bdd20f4e29</t>
+  </si>
+  <si>
+    <t>relationship--6d6d6c18-9ff1-4a46-8662-d9beaaca9d63</t>
+  </si>
+  <si>
+    <t>relationship--ea862a9a-c106-424d-a9a7-ef7629cc9199</t>
+  </si>
+  <si>
+    <t>relationship--f29daea4-3b0d-48fc-86a6-8c53545c246a</t>
+  </si>
+  <si>
+    <t>relationship--035b8dc2-d73b-4409-bfa1-cf3d701630be</t>
+  </si>
+  <si>
+    <t>relationship--459b3155-fbc5-4213-90bc-35d637128985</t>
+  </si>
+  <si>
+    <t>relationship--904dead1-b87a-49a5-be62-70b0b0fec3fc</t>
+  </si>
+  <si>
+    <t>relationship--2328cd3f-30f3-43db-a812-fd5a9013a5f5</t>
+  </si>
+  <si>
+    <t>relationship--76cffb3c-73f3-4a6b-b472-dcd422cf8591</t>
+  </si>
+  <si>
+    <t>relationship--08955afe-f5b2-415b-b89d-cfedbc995ed3</t>
+  </si>
+  <si>
+    <t>relationship--9ea0825a-9469-43a8-b230-20f6b8b06d4a</t>
+  </si>
+  <si>
+    <t>relationship--4b496da7-3950-4445-9e90-1528dedef982</t>
+  </si>
+  <si>
+    <t>relationship--fcc56dd6-5d05-4ee0-80d3-6ea7c0bf08f9</t>
+  </si>
+  <si>
+    <t>relationship--06b14ac1-7b3b-4dc1-b994-4f9f9b34ecd9</t>
+  </si>
+  <si>
+    <t>relationship--9668dac7-82df-4bc6-8926-5447ff4e8d4e</t>
+  </si>
+  <si>
+    <t>relationship--f027dd94-b25c-4645-ba72-7ebb97256db4</t>
+  </si>
+  <si>
+    <t>relationship--6f13c2bf-ae08-488e-b7e2-d5ed14019131</t>
+  </si>
+  <si>
+    <t>relationship--5dc08eb4-7b37-4029-9a23-cdbc6e8c12d2</t>
+  </si>
+  <si>
+    <t>relationship--f4c4c0f7-c3a0-4706-b1d1-01b1ade0399c</t>
+  </si>
+  <si>
+    <t>relationship--28f1db21-1311-46c1-b61c-18e27b2dd2ad</t>
+  </si>
+  <si>
+    <t>relationship--85879eb1-2ad3-4e34-b4c8-2b92b8c16004</t>
+  </si>
+  <si>
+    <t>relationship--a6a460d5-d66c-4645-9faf-50ff3a1ae761</t>
+  </si>
+  <si>
+    <t>relationship--ea5777fb-7134-40ad-8225-e40b20f6b3fe</t>
+  </si>
+  <si>
+    <t>relationship--e24b8e58-bef9-4025-9699-9f0f21096e9b</t>
+  </si>
+  <si>
+    <t>relationship--aebd94e5-71c8-41d7-9f5c-502f466308fd</t>
+  </si>
+  <si>
+    <t>relationship--9c2d4a8d-05cd-4bf7-ac8d-b035158fcaa8</t>
+  </si>
+  <si>
+    <t>relationship--ad659c12-7af0-4cd5-b6cf-9146f1b135a9</t>
+  </si>
+  <si>
+    <t>relationship--756baf2a-6726-4d50-a686-eef3b149952f</t>
+  </si>
+  <si>
+    <t>relationship--3011cf6e-fbd4-4eec-b6e3-03d0d51d3733</t>
   </si>
   <si>
     <t>27 April 2026</t>
@@ -6493,34 +6493,34 @@
     <t>https://attack.mitre.org/campaigns/C0041/</t>
   </si>
   <si>
-    <t>https://uk.wikipedia.org/wiki/%25D0%2586%25D0%25B2%25D0%25B0%25D0%25BD_%25D0%259C%25D0%25B0%25D0%25B7%25D0%25B5%25D0%25BF%25D0%25B0</t>
-  </si>
-  <si>
-    <t>https://uk.wikipedia.org/wiki/%25D0%2586%25D1%2581%25D1%2582%25D0%25BE%25D1%2580%25D1%2596%25D1%258F_%25D0%2594%25D0%25BE%25D0%25BD%25D0%25B5%25D1%2586%25D1%258C%25D0%25BA%25D0%25BE%25D1%2597_%25D0%25BE%25D0%25B1%25D0%25BB%25D0%25B0%25D1%2581%25D1%2582%25D1%2596</t>
-  </si>
-  <si>
-    <t>https://uk.wikipedia.org/wiki/%25D0%2586%25D1%2581%25D1%2582%25D0%25BE%25D1%2580%25D1%2596%25D1%258F_%25D0%25A3%25D0%25BA%25D1%2580%25D0%25B0%25D1%2597%25D0%25BD%25D0%25B8</t>
-  </si>
-  <si>
-    <t>https://uk.wikipedia.org/wiki/%25D0%2590%25D0%25B7%25D0%25BE%25D0%25B2%25D1%2581%25D1%258C%25D0%25BA%25D1%2596_%25D0%25BF%25D0%25BE%25D1%2585%25D0%25BE%25D0%25B4%25D0%25B8_%281695%25E2%2580%25941696%29</t>
-  </si>
-  <si>
-    <t>https://ru.wikipedia.org/wiki/%25D0%2590%25D0%25BD%25D0%25B4%25D1%2580%25D1%2583%25D1%2581%25D0%25BE%25D0%25B2%25D1%2581%25D0%25BA%25D0%25BE%25D0%25B5_%25D0%25BF%25D0%25B5%25D1%2580%25D0%25B5%25D0%25BC%25D0%25B8%25D1%2580%25D0%25B8%25D0%25B5</t>
-  </si>
-  <si>
-    <t>https://uk.wikipedia.org/wiki/%25D0%2590%25D0%25BD%25D0%25B5%25D0%25BA%25D1%2581%25D1%2596%25D1%258F_%25D0%259A%25D0%25B8%25D1%2597%25D0%25B2%25D1%2581%25D1%258C%25D0%25BA%25D0%25BE%25D1%2597_%25D0%25BC%25D0%25B8%25D1%2582%25D1%2580%25D0%25BE%25D0%25BF%25D0%25BE%25D0%25BB%25D1%2596%25D1%2597_%25D0%259C%25D0%25BE%25D1%2581%25D0%25BA%25D0%25BE%25D0%25B2%25D1%2581%25D1%258C%25D0%25BA%25D0%25B8%25D0%25BC_%25D0%25BF%25D0%25B0%25D1%2582%25D1%2580%25D1%2596%25D0%25B0%25D1%2580%25D1%2585%25D0%25B0%25D1%2582%25D0%25BE%25D0%25BC</t>
-  </si>
-  <si>
-    <t>https://ru.wikipedia.org/wiki/%25D0%2590%25D0%25BD%25D0%25BD%25D0%25B5%25D0%25BA%25D1%2581%25D0%25B8%25D1%258F_%25D0%2591%25D0%25B5%25D1%2581%25D1%2581%25D0%25B0%25D1%2580%25D0%25B0%25D0%25B1%25D0%25B8%25D0%25B8_%25D0%25A0%25D0%25BE%25D1%2581%25D1%2581%25D0%25B8%25D0%25B9%25D1%2581%25D0%25BA%25D0%25BE%25D0%25B9_%25D0%25B8%25D0%25BC%25D0%25BF%25D0%25B5%25D1%2580%25D0%25B8%25D0%25B5%25D0%25B9_%281812%29</t>
-  </si>
-  <si>
-    <t>https://uk.wikipedia.org/wiki/%25D0%2590%25D0%25BD%25D1%2582%25D0%25B8%25D0%25BA%25D1%2580%25D1%2596%25D0%25BF%25D0%25BE%25D1%2581%25D0%25BD%25D0%25B8%25D1%2586%25D1%258C%25D0%25BA%25D0%25B8%25D0%25B9_%25D1%2580%25D1%2583%25D1%2585_%25D0%25B2_%25D0%25A3%25D0%25BA%25D1%2580%25D0%25B0%25D1%2597%25D0%25BD%25D1%2596_%281789-1861%29</t>
-  </si>
-  <si>
-    <t>https://uk.wikipedia.org/wiki/%25D0%2591%25D0%25B0%25D1%2582%25D1%2583%25D1%2580%25D0%25B8%25D0%25BD%25D1%2581%25D1%258C%25D0%25BA%25D0%25B0_%25D1%2582%25D1%2580%25D0%25B0%25D0%25B3%25D0%25B5%25D0%25B4%25D1%2596%25D1%258F</t>
-  </si>
-  <si>
-    <t>https://uk.wikipedia.org/wiki/%25D0%2592%25D1%2581%25D0%25B5%25D1%2581%25D0%25BE%25D1%258E%25D0%25B7%25D0%25BD%25D0%25B8%25D0%25B9_%25D1%2580%25D0%25B5%25D1%2584%25D0%25B5%25D1%2580%25D0%25B5%25D0%25BD%25D0%25B4%25D1%2583%25D0%25BC_%25D0%25BF%25D1%2580%25D0%25BE_%25D0%25B7%25D0%25B1%25D0%25B5%25D1%2580%25D0%25B5%25D0%25B6%25D0%25B5%25D0%25BD%25D0%25BD%25D1%258F_%25D0%25A1%25D0%25A0%25D0%25A1%25D0%25A0</t>
+    <t>https://uk.wikipedia.org/wiki/%D0%86%D0%B2%D0%B0%D0%BD_%D0%9C%D0%B0%D0%B7%D0%B5%D0%BF%D0%B0</t>
+  </si>
+  <si>
+    <t>https://uk.wikipedia.org/wiki/%D0%86%D1%81%D1%82%D0%BE%D1%80%D1%96%D1%8F_%D0%94%D0%BE%D0%BD%D0%B5%D1%86%D1%8C%D0%BA%D0%BE%D1%97_%D0%BE%D0%B1%D0%BB%D0%B0%D1%81%D1%82%D1%96</t>
+  </si>
+  <si>
+    <t>https://uk.wikipedia.org/wiki/%D0%86%D1%81%D1%82%D0%BE%D1%80%D1%96%D1%8F_%D0%A3%D0%BA%D1%80%D0%B0%D1%97%D0%BD%D0%B8</t>
+  </si>
+  <si>
+    <t>https://uk.wikipedia.org/wiki/%D0%90%D0%B7%D0%BE%D0%B2%D1%81%D1%8C%D0%BA%D1%96_%D0%BF%D0%BE%D1%85%D0%BE%D0%B4%D0%B8_%281695%E2%80%941696%29</t>
+  </si>
+  <si>
+    <t>https://ru.wikipedia.org/wiki/%D0%90%D0%BD%D0%B4%D1%80%D1%83%D1%81%D0%BE%D0%B2%D1%81%D0%BA%D0%BE%D0%B5_%D0%BF%D0%B5%D1%80%D0%B5%D0%BC%D0%B8%D1%80%D0%B8%D0%B5</t>
+  </si>
+  <si>
+    <t>https://uk.wikipedia.org/wiki/%D0%90%D0%BD%D0%B5%D0%BA%D1%81%D1%96%D1%8F_%D0%9A%D0%B8%D1%97%D0%B2%D1%81%D1%8C%D0%BA%D0%BE%D1%97_%D0%BC%D0%B8%D1%82%D1%80%D0%BE%D0%BF%D0%BE%D0%BB%D1%96%D1%97_%D0%9C%D0%BE%D1%81%D0%BA%D0%BE%D0%B2%D1%81%D1%8C%D0%BA%D0%B8%D0%BC_%D0%BF%D0%B0%D1%82%D1%80%D1%96%D0%B0%D1%80%D1%85%D0%B0%D1%82%D0%BE%D0%BC</t>
+  </si>
+  <si>
+    <t>https://ru.wikipedia.org/wiki/%D0%90%D0%BD%D0%BD%D0%B5%D0%BA%D1%81%D0%B8%D1%8F_%D0%91%D0%B5%D1%81%D1%81%D0%B0%D1%80%D0%B0%D0%B1%D0%B8%D0%B8_%D0%A0%D0%BE%D1%81%D1%81%D0%B8%D0%B9%D1%81%D0%BA%D0%BE%D0%B9_%D0%B8%D0%BC%D0%BF%D0%B5%D1%80%D0%B8%D0%B5%D0%B9_%281812%29</t>
+  </si>
+  <si>
+    <t>https://uk.wikipedia.org/wiki/%D0%90%D0%BD%D1%82%D0%B8%D0%BA%D1%80%D1%96%D0%BF%D0%BE%D1%81%D0%BD%D0%B8%D1%86%D1%8C%D0%BA%D0%B8%D0%B9_%D1%80%D1%83%D1%85_%D0%B2_%D0%A3%D0%BA%D1%80%D0%B0%D1%97%D0%BD%D1%96_%281789-1861%29</t>
+  </si>
+  <si>
+    <t>https://uk.wikipedia.org/wiki/%D0%91%D0%B0%D1%82%D1%83%D1%80%D0%B8%D0%BD%D1%81%D1%8C%D0%BA%D0%B0_%D1%82%D1%80%D0%B0%D0%B3%D0%B5%D0%B4%D1%96%D1%8F</t>
+  </si>
+  <si>
+    <t>https://uk.wikipedia.org/wiki/%D0%92%D1%81%D0%B5%D1%81%D0%BE%D1%8E%D0%B7%D0%BD%D0%B8%D0%B9_%D1%80%D0%B5%D1%84%D0%B5%D1%80%D0%B5%D0%BD%D0%B4%D1%83%D0%BC_%D0%BF%D1%80%D0%BE_%D0%B7%D0%B1%D0%B5%D1%80%D0%B5%D0%B6%D0%B5%D0%BD%D0%BD%D1%8F_%D0%A1%D0%A0%D0%A1%D0%A0</t>
   </si>
   <si>
     <t>https://museum.khpg.org/ru/1628664422</t>
@@ -6529,82 +6529,82 @@
     <t>https://www.obozrevatel.com/novosti-obschestvo/dvojnoe-prestuplenie-sssr-kak-sovetyi-skryivali-chernobyilskuyu-katastrofu.htm</t>
   </si>
   <si>
-    <t>https://uk.wikipedia.org/wiki/%25D0%25A0%25D0%25BE%25D1%2581%25D1%2596%25D0%25B9%25D1%2581%25D1%258C%25D0%25BA%25D0%25B0_%25D0%25B4%25D0%25B5%25D0%25B7%25D1%2596%25D0%25BD%25D1%2584%25D0%25BE%25D1%2580%25D0%25BC%25D0%25B0%25D1%2586%25D1%2596%25D1%258F_%25D0%25BF%25D1%2596%25D0%25B4_%25D1%2587%25D0%25B0%25D1%2581_%25D1%2580%25D0%25BE%25D1%2581%25D1%2596%25D0%25B9%25D1%2581%25D1%258C%25D0%25BA%25D0%25BE-%25D1%2583%25D0%25BA%25D1%2580%25D0%25B0%25D1%2597%25D0%25BD%25D1%2581%25D1%258C%25D0%25BA%25D0%25BE%25D1%2597_%25D0%25B2%25D1%2596%25D0%25B9%25D0%25BD%25D0%25B8</t>
-  </si>
-  <si>
-    <t>https://uk.wikipedia.org/wiki/%25D0%2594%25D1%2580%25D1%2583%25D0%25B3%25D0%25B0_%25D0%259C%25D0%25B0%25D0%25BB%25D0%25BE%25D1%2580%25D0%25BE%25D1%2581%25D1%2596%25D0%25B9%25D1%2581%25D1%258C%25D0%25BA%25D0%25B0_%25D0%25BA%25D0%25BE%25D0%25BB%25D0%25B5%25D0%25B3%25D1%2596%25D1%258F</t>
-  </si>
-  <si>
-    <t>https://uk.wikipedia.org/wiki/%25D0%2597%25D0%25B0%25D0%25B4%25D1%2583%25D0%25BD%25D0%25B0%25D0%25B9%25D1%2581%25D1%258C%25D0%25BA%25D0%25B0_%25D0%25A1%25D1%2596%25D1%2587</t>
-  </si>
-  <si>
-    <t>https://uk.wikipedia.org/wiki/%25D0%2597%25D0%25B0%25D0%25BF%25D0%25BE%25D1%2580%25D0%25BE%25D0%25B7%25D1%258C%25D0%25BA%25D0%25B0_%25D0%25A1%25D1%2596%25D1%2587</t>
+    <t>https://uk.wikipedia.org/wiki/%D0%A0%D0%BE%D1%81%D1%96%D0%B9%D1%81%D1%8C%D0%BA%D0%B0_%D0%B4%D0%B5%D0%B7%D1%96%D0%BD%D1%84%D0%BE%D1%80%D0%BC%D0%B0%D1%86%D1%96%D1%8F_%D0%BF%D1%96%D0%B4_%D1%87%D0%B0%D1%81_%D1%80%D0%BE%D1%81%D1%96%D0%B9%D1%81%D1%8C%D0%BA%D0%BE-%D1%83%D0%BA%D1%80%D0%B0%D1%97%D0%BD%D1%81%D1%8C%D0%BA%D0%BE%D1%97_%D0%B2%D1%96%D0%B9%D0%BD%D0%B8</t>
+  </si>
+  <si>
+    <t>https://uk.wikipedia.org/wiki/%D0%94%D1%80%D1%83%D0%B3%D0%B0_%D0%9C%D0%B0%D0%BB%D0%BE%D1%80%D0%BE%D1%81%D1%96%D0%B9%D1%81%D1%8C%D0%BA%D0%B0_%D0%BA%D0%BE%D0%BB%D0%B5%D0%B3%D1%96%D1%8F</t>
+  </si>
+  <si>
+    <t>https://uk.wikipedia.org/wiki/%D0%97%D0%B0%D0%B4%D1%83%D0%BD%D0%B0%D0%B9%D1%81%D1%8C%D0%BA%D0%B0_%D0%A1%D1%96%D1%87</t>
+  </si>
+  <si>
+    <t>https://uk.wikipedia.org/wiki/%D0%97%D0%B0%D0%BF%D0%BE%D1%80%D0%BE%D0%B7%D1%8C%D0%BA%D0%B0_%D0%A1%D1%96%D1%87</t>
   </si>
   <si>
     <t>https://ridl.io/ru/karatelnaja-psihiatrija-v-rossii-nazad-v-sssr/</t>
   </si>
   <si>
-    <t>https://ru.wikipedia.org/wiki/%25D0%259A%25D0%25B5%25D0%25BD%25D0%25B3%25D0%25B8%25D1%2580%25D1%2581%25D0%25BA%25D0%25BE%25D0%25B5_%25D0%25B2%25D0%25BE%25D1%2581%25D1%2581%25D1%2582%25D0%25B0%25D0%25BD%25D0%25B8%25D0%25B5_%25D0%25B7%25D0%25B0%25D0%25BA%25D0%25BB%25D1%258E%25D1%2587%25D1%2591%25D0%25BD%25D0%25BD%25D1%258B%25D1%2585</t>
+    <t>https://ru.wikipedia.org/wiki/%D0%9A%D0%B5%D0%BD%D0%B3%D0%B8%D1%80%D1%81%D0%BA%D0%BE%D0%B5_%D0%B2%D0%BE%D1%81%D1%81%D1%82%D0%B0%D0%BD%D0%B8%D0%B5_%D0%B7%D0%B0%D0%BA%D0%BB%D1%8E%D1%87%D1%91%D0%BD%D0%BD%D1%8B%D1%85</t>
   </si>
   <si>
     <t>https://ru.wikipedia.org/wiki/%D0%9A%D0%B8%D0%B5%D0%B2%D1%81%D0%BA%D0%B8%D0%B9_%D1%81%D0%B8%D0%BD%D0%BE%D0%BF%D1%81%D0%B8%D1%81</t>
   </si>
   <si>
-    <t>https://uk.wikipedia.org/wiki/%25D0%259A%25D0%25B8%25D1%2580%25D0%25B8%25D0%25BB%25D0%25BE-%25D0%259C%25D0%25B5%25D1%2584%25D0%25BE%25D0%25B4%25D1%2596%25D1%2597%25D0%25B2%25D1%2581%25D1%258C%25D0%25BA%25D0%25B5_%25D1%2582%25D0%25BE%25D0%25B2%25D0%25B0%25D1%2580%25D0%25B8%25D1%2581%25D1%2582%25D0%25B2%25D0%25BE</t>
-  </si>
-  <si>
-    <t>https://uk.wikipedia.org/wiki/%25D0%259A%25D0%25B8%25D1%2597%25D0%25B2%25D1%2581%25D1%258C%25D0%25BA%25D0%25B0_%25D0%25BA%25D0%25BE%25D0%25B7%25D0%25B0%25D1%2587%25D1%2587%25D0%25B8%25D0%25BD%25D0%25B0</t>
-  </si>
-  <si>
-    <t>https://uk.wikipedia.org/wiki/%25D0%259A%25D0%25BE%25D0%25BD%25D0%25BE%25D1%2582%25D0%25BE%25D0%25BF%25D1%2581%25D1%258C%25D0%25BA%25D1%2596_%25D1%2581%25D1%2582%25D0%25B0%25D1%2582%25D1%2582%25D1%2596</t>
-  </si>
-  <si>
-    <t>https://uk.wikipedia.org/wiki/%25D0%259A%25D0%25BE%25D1%2582%25D0%25BB%25D0%25B5%25D1%2582%25D0%25B0_%25D0%25BF%25D0%25BE-%25D0%25BA%25D0%25B8%25D1%2597%25D0%25B2%25D1%2581%25D1%258C%25D0%25BA%25D0%25B8_%28%25D0%25BF%25D1%2580%25D0%25BE%25D0%25BC%25D0%25BE%25D0%25B2%25D0%25B0%29</t>
-  </si>
-  <si>
-    <t>https://ru.wikipedia.org/wiki/%25D0%259A%25D1%2580%25D1%258B%25D0%25BC%25D1%2581%25D0%25BA%25D0%25B0%25D1%258F_%25D0%25B2%25D0%25BE%25D0%25B9%25D0%25BD%25D0%25B0</t>
-  </si>
-  <si>
-    <t>https://uk.wikipedia.org/wiki/%25D0%259B%25D0%25B8%25D1%2581%25D1%2582%25D0%25BE%25D0%25BF%25D0%25B0%25D0%25B4%25D0%25BE%25D0%25B2%25D0%25B5_%25D0%25BF%25D0%25BE%25D0%25B2%25D1%2581%25D1%2582%25D0%25B0%25D0%25BD%25D0%25BD%25D1%258F_%281830%25E2%2580%25941831%29</t>
-  </si>
-  <si>
-    <t>https://uk.wikipedia.org/wiki/%25D0%259B%25D1%2583%25D0%25B1%25D0%25B5%25D0%25BD%25D1%2581%25D1%258C%25D0%25BA%25D0%25B8%25D0%25B9_%25D0%25B4%25D0%25BE%25D0%25B3%25D0%25BE%25D0%25B2%25D1%2596%25D1%2580</t>
-  </si>
-  <si>
-    <t>https://uk.wikipedia.org/wiki/%25D0%259B%25D1%2596%25D0%25BA%25D0%25B2%25D1%2596%25D0%25B4%25D0%25B0%25D1%2586%25D1%2596%25D1%258F_%25D0%2597%25D0%25B0%25D0%25BF%25D0%25BE%25D1%2580%25D0%25BE%25D0%25B7%25D1%258C%25D0%25BA%25D0%25BE%25D1%2597_%25D0%25A1%25D1%2596%25D1%2587%25D1%2596_%281775%29</t>
-  </si>
-  <si>
-    <t>https://uk.wikipedia.org/wiki/%25D0%259B%25D1%2596%25D0%25BA%25D0%25B2%25D1%2596%25D0%25B4%25D0%25B0%25D1%2586%25D1%2596%25D1%258F_%25D0%25B0%25D0%25B2%25D1%2582%25D0%25BE%25D0%25BD%25D0%25BE%25D0%25BC%25D1%2596%25D1%2597_%25D0%2593%25D0%25B5%25D1%2582%25D1%258C%25D0%25BC%25D0%25B0%25D0%25BD%25D1%2589%25D0%25B8%25D0%25BD%25D0%25B8</t>
-  </si>
-  <si>
-    <t>https://uk.wikipedia.org/wiki/%25D0%259B%25D1%2596%25D0%25BA%25D0%25B2%25D1%2596%25D0%25B4%25D0%25B0%25D1%2586%25D1%2596%25D1%258F_%25D0%25BA%25D0%25BE%25D0%25B7%25D0%25B0%25D1%2586%25D1%2582%25D0%25B2%25D0%25B0_%25D0%25BD%25D0%25B0_%25D0%259F%25D1%2580%25D0%25B0%25D0%25B2%25D0%25BE%25D0%25B1%25D0%25B5%25D1%2580%25D0%25B5%25D0%25B6%25D0%25BD%25D1%2596%25D0%25B9_%25D0%25A3%25D0%25BA%25D1%2580%25D0%25B0%25D1%2597%25D0%25BD%25D1%2596_%281699%29</t>
-  </si>
-  <si>
-    <t>https://ru.wikipedia.org/wiki/%25D0%259C%25D0%25B0%25D0%25B7%25D0%25B5%25D0%25BF%25D0%25B0%2C_%25D0%2598%25D0%25B2%25D0%25B0%25D0%25BD_%25D0%25A1%25D1%2582%25D0%25B5%25D0%25BF%25D0%25B0%25D0%25BD%25D0%25BE%25D0%25B2%25D0%25B8%25D1%2587</t>
-  </si>
-  <si>
-    <t>https://uk.wikipedia.org/wiki/%25D0%259C%25D0%25B0%25D0%25BB%25D0%25BE%25D1%2580%25D0%25BE%25D1%2581%25D1%2596%25D0%25B9%25D1%2581%25D1%258C%25D0%25BA%25D0%25B5_%25D0%25B3%25D0%25B5%25D0%25BD%25D0%25B5%25D1%2580%25D0%25B0%25D0%25BB-%25D0%25B3%25D1%2583%25D0%25B1%25D0%25B5%25D1%2580%25D0%25BD%25D0%25B0%25D1%2582%25D0%25BE%25D1%2580%25D1%2581%25D1%2582%25D0%25B2%25D0%25BE</t>
-  </si>
-  <si>
-    <t>https://uk.wikipedia.org/wiki/%25D0%259C%25D0%25B0%25D0%25BB%25D0%25BE%25D1%2580%25D0%25BE%25D1%2581%25D1%2596%25D0%25B9%25D1%2581%25D1%258C%25D0%25BA%25D0%25B8%25D0%25B9_%25D0%25BF%25D1%2580%25D0%25B8%25D0%25BA%25D0%25B0%25D0%25B7</t>
+    <t>https://uk.wikipedia.org/wiki/%D0%9A%D0%B8%D1%80%D0%B8%D0%BB%D0%BE-%D0%9C%D0%B5%D1%84%D0%BE%D0%B4%D1%96%D1%97%D0%B2%D1%81%D1%8C%D0%BA%D0%B5_%D1%82%D0%BE%D0%B2%D0%B0%D1%80%D0%B8%D1%81%D1%82%D0%B2%D0%BE</t>
+  </si>
+  <si>
+    <t>https://uk.wikipedia.org/wiki/%D0%9A%D0%B8%D1%97%D0%B2%D1%81%D1%8C%D0%BA%D0%B0_%D0%BA%D0%BE%D0%B7%D0%B0%D1%87%D1%87%D0%B8%D0%BD%D0%B0</t>
+  </si>
+  <si>
+    <t>https://uk.wikipedia.org/wiki/%D0%9A%D0%BE%D0%BD%D0%BE%D1%82%D0%BE%D0%BF%D1%81%D1%8C%D0%BA%D1%96_%D1%81%D1%82%D0%B0%D1%82%D1%82%D1%96</t>
+  </si>
+  <si>
+    <t>https://uk.wikipedia.org/wiki/%D0%9A%D0%BE%D1%82%D0%BB%D0%B5%D1%82%D0%B0_%D0%BF%D0%BE-%D0%BA%D0%B8%D1%97%D0%B2%D1%81%D1%8C%D0%BA%D0%B8_%28%D0%BF%D1%80%D0%BE%D0%BC%D0%BE%D0%B2%D0%B0%29</t>
+  </si>
+  <si>
+    <t>https://ru.wikipedia.org/wiki/%D0%9A%D1%80%D1%8B%D0%BC%D1%81%D0%BA%D0%B0%D1%8F_%D0%B2%D0%BE%D0%B9%D0%BD%D0%B0</t>
+  </si>
+  <si>
+    <t>https://uk.wikipedia.org/wiki/%D0%9B%D0%B8%D1%81%D1%82%D0%BE%D0%BF%D0%B0%D0%B4%D0%BE%D0%B2%D0%B5_%D0%BF%D0%BE%D0%B2%D1%81%D1%82%D0%B0%D0%BD%D0%BD%D1%8F_%281830%E2%80%941831%29</t>
+  </si>
+  <si>
+    <t>https://uk.wikipedia.org/wiki/%D0%9B%D1%83%D0%B1%D0%B5%D0%BD%D1%81%D1%8C%D0%BA%D0%B8%D0%B9_%D0%B4%D0%BE%D0%B3%D0%BE%D0%B2%D1%96%D1%80</t>
+  </si>
+  <si>
+    <t>https://uk.wikipedia.org/wiki/%D0%9B%D1%96%D0%BA%D0%B2%D1%96%D0%B4%D0%B0%D1%86%D1%96%D1%8F_%D0%97%D0%B0%D0%BF%D0%BE%D1%80%D0%BE%D0%B7%D1%8C%D0%BA%D0%BE%D1%97_%D0%A1%D1%96%D1%87%D1%96_%281775%29</t>
+  </si>
+  <si>
+    <t>https://uk.wikipedia.org/wiki/%D0%9B%D1%96%D0%BA%D0%B2%D1%96%D0%B4%D0%B0%D1%86%D1%96%D1%8F_%D0%B0%D0%B2%D1%82%D0%BE%D0%BD%D0%BE%D0%BC%D1%96%D1%97_%D0%93%D0%B5%D1%82%D1%8C%D0%BC%D0%B0%D0%BD%D1%89%D0%B8%D0%BD%D0%B8</t>
+  </si>
+  <si>
+    <t>https://uk.wikipedia.org/wiki/%D0%9B%D1%96%D0%BA%D0%B2%D1%96%D0%B4%D0%B0%D1%86%D1%96%D1%8F_%D0%BA%D0%BE%D0%B7%D0%B0%D1%86%D1%82%D0%B2%D0%B0_%D0%BD%D0%B0_%D0%9F%D1%80%D0%B0%D0%B2%D0%BE%D0%B1%D0%B5%D1%80%D0%B5%D0%B6%D0%BD%D1%96%D0%B9_%D0%A3%D0%BA%D1%80%D0%B0%D1%97%D0%BD%D1%96_%281699%29</t>
+  </si>
+  <si>
+    <t>https://ru.wikipedia.org/wiki/%D0%9C%D0%B0%D0%B7%D0%B5%D0%BF%D0%B0%2C_%D0%98%D0%B2%D0%B0%D0%BD_%D0%A1%D1%82%D0%B5%D0%BF%D0%B0%D0%BD%D0%BE%D0%B2%D0%B8%D1%87</t>
+  </si>
+  <si>
+    <t>https://uk.wikipedia.org/wiki/%D0%9C%D0%B0%D0%BB%D0%BE%D1%80%D0%BE%D1%81%D1%96%D0%B9%D1%81%D1%8C%D0%BA%D0%B5_%D0%B3%D0%B5%D0%BD%D0%B5%D1%80%D0%B0%D0%BB-%D0%B3%D1%83%D0%B1%D0%B5%D1%80%D0%BD%D0%B0%D1%82%D0%BE%D1%80%D1%81%D1%82%D0%B2%D0%BE</t>
+  </si>
+  <si>
+    <t>https://uk.wikipedia.org/wiki/%D0%9C%D0%B0%D0%BB%D0%BE%D1%80%D0%BE%D1%81%D1%96%D0%B9%D1%81%D1%8C%D0%BA%D0%B8%D0%B9_%D0%BF%D1%80%D0%B8%D0%BA%D0%B0%D0%B7</t>
   </si>
   <si>
     <t>https://uk.wikipedia.org/wiki/%D0%9C%D0%BE%D1%81%D0%BA%D0%BE%D0%B2%D1%81%D1%8C%D0%BA%D0%BE-%D1%83%D0%BA%D1%80%D0%B0%D1%97%D0%BD%D1%81%D1%8C%D0%BA%D0%B0_%D0%B2%D1%96%D0%B9%D0%BD%D0%B0_%281658%E2%80%941659%29</t>
   </si>
   <si>
-    <t>https://uk.wikipedia.org/wiki/%25D0%259C%25D0%25BE%25D1%2581%25D0%25BA%25D0%25BE%25D0%25B2%25D1%2581%25D1%258C%25D0%25BA%25D1%2596_%25D1%2581%25D1%2582%25D0%25B0%25D1%2582%25D1%2582%25D1%2596_%281665%29</t>
-  </si>
-  <si>
-    <t>https://uk.wikipedia.org/wiki/%25D0%259D%25D0%25B0%25D1%2580%25D0%25BE%25D0%25B4%25D0%25BD%25D0%25B8%25D0%25B9_%25D1%2580%25D1%2583%25D1%2585_%25D0%25A3%25D0%25BA%25D1%2580%25D0%25B0%25D1%2597%25D0%25BD%25D0%25B8</t>
+    <t>https://uk.wikipedia.org/wiki/%D0%9C%D0%BE%D1%81%D0%BA%D0%BE%D0%B2%D1%81%D1%8C%D0%BA%D1%96_%D1%81%D1%82%D0%B0%D1%82%D1%82%D1%96_%281665%29</t>
+  </si>
+  <si>
+    <t>https://uk.wikipedia.org/wiki/%D0%9D%D0%B0%D1%80%D0%BE%D0%B4%D0%BD%D0%B8%D0%B9_%D1%80%D1%83%D1%85_%D0%A3%D0%BA%D1%80%D0%B0%D1%97%D0%BD%D0%B8</t>
   </si>
   <si>
     <t>http://resource.history.org.ua/publ/journal_1998_6_22</t>
   </si>
   <si>
-    <t>https://ru.wikipedia.org/wiki/%25D0%259D%25D0%25BE%25D1%2580%25D0%25B8%25D0%25BB%25D1%258C%25D1%2581%25D0%25BA%25D0%25BE%25D0%25B5_%25D0%25B2%25D0%25BE%25D1%2581%25D1%2581%25D1%2582%25D0%25B0%25D0%25BD%25D0%25B8%25D0%25B5</t>
-  </si>
-  <si>
-    <t>https://uk.wikipedia.org/wiki/%25D0%259F%25D0%25B5%25D1%2580%25D0%25B5%25D0%25BF%25D0%25B8%25D1%2581_%25D0%25BD%25D0%25B0%25D1%2581%25D0%25B5%25D0%25BB%25D0%25B5%25D0%25BD%25D0%25BD%25D1%258F_%25D0%25A0%25D0%25BE%25D1%2581%25D1%2596%25D0%25B9%25D1%2581%25D1%258C%25D0%25BA%25D0%25BE%25D1%2597_%25D1%2596%25D0%25BC%25D0%25BF%25D0%25B5%25D1%2580%25D1%2596%25D1%2597_%281897%29</t>
+    <t>https://ru.wikipedia.org/wiki/%D0%9D%D0%BE%D1%80%D0%B8%D0%BB%D1%8C%D1%81%D0%BA%D0%BE%D0%B5_%D0%B2%D0%BE%D1%81%D1%81%D1%82%D0%B0%D0%BD%D0%B8%D0%B5</t>
+  </si>
+  <si>
+    <t>https://uk.wikipedia.org/wiki/%D0%9F%D0%B5%D1%80%D0%B5%D0%BF%D0%B8%D1%81_%D0%BD%D0%B0%D1%81%D0%B5%D0%BB%D0%B5%D0%BD%D0%BD%D1%8F_%D0%A0%D0%BE%D1%81%D1%96%D0%B9%D1%81%D1%8C%D0%BA%D0%BE%D1%97_%D1%96%D0%BC%D0%BF%D0%B5%D1%80%D1%96%D1%97_%281897%29</t>
   </si>
   <si>
     <t>https://uk.wikipedia.org/wiki/%D0%9F%D0%B5%D1%80%D0%B5%D1%8F%D1%81%D0%BB%D0%B0%D0%B2%D1%81%D1%8C%D0%BA%D0%B0_%D1%80%D0%B0%D0%B4%D0%B0</t>
@@ -6613,85 +6613,85 @@
     <t>https://uk.wikipedia.org/wiki/%D0%9F%D0%B5%D1%80%D0%B5%D1%8F%D1%81%D0%BB%D0%B0%D0%B2%D1%81%D1%8C%D0%BA%D1%96_%D1%81%D1%82%D0%B0%D1%82%D1%82%D1%96_%281659%29</t>
   </si>
   <si>
-    <t>https://ru.wikipedia.org/wiki/%25D0%259F%25D0%25B8%25D1%2581%25D1%258C%25D0%25BC%25D0%25BE-%25D0%25BF%25D1%2580%25D0%25BE%25D1%2582%25D0%25B5%25D1%2581%25D1%2582_139</t>
-  </si>
-  <si>
-    <t>https://uk.wikipedia.org/wiki/%25D0%259F%25D0%25BE%25D0%25B2%25D1%2581%25D1%2582%25D0%25B0%25D0%25BD%25D0%25BD%25D1%258F_%25D0%25B1%25D1%2583%25D0%25B7%25D1%258C%25D0%25BA%25D0%25B8%25D1%2585_%25D0%25BA%25D0%25BE%25D0%25B7%25D0%25B0%25D0%25BA%25D1%2596%25D0%25B2_%281817%29</t>
-  </si>
-  <si>
-    <t>https://uk.wikipedia.org/wiki/%25D0%259F%25D0%25BE%25D0%25B4%25D1%2596%25D0%25BB%25D0%25B8_%25D0%25A0%25D0%25B5%25D1%2587%25D1%2596_%25D0%259F%25D0%25BE%25D1%2581%25D0%25BF%25D0%25BE%25D0%25BB%25D0%25B8%25D1%2582%25D0%25BE%25D1%2597</t>
-  </si>
-  <si>
-    <t>https://ru.wikipedia.org/wiki/%25D0%259F%25D0%25BE%25D0%25BB%25D1%258C%25D1%2581%25D0%25BA%25D0%25BE%25D0%25B5_%25D0%25B2%25D0%25BE%25D1%2581%25D1%2581%25D1%2582%25D0%25B0%25D0%25BD%25D0%25B8%25D0%25B5_%281863%25E2%2580%25941864%29</t>
-  </si>
-  <si>
-    <t>https://uk.wikipedia.org/wiki/%25D0%259F%25D0%25BE%25D1%2585%25D1%2596%25D0%25B4_%25D0%259F%25D0%25B8%25D0%25BB%25D0%25B8%25D0%25BF%25D0%25B0_%25D0%259E%25D1%2580%25D0%25BB%25D0%25B8%25D0%25BA%25D0%25B0_%25D0%25BD%25D0%25B0_%25D0%259F%25D1%2580%25D0%25B0%25D0%25B2%25D0%25BE%25D0%25B1%25D0%25B5%25D1%2580%25D0%25B5%25D0%25B6%25D0%25BD%25D1%2583_%25D0%25A3%25D0%25BA%25D1%2580%25D0%25B0%25D1%2597%25D0%25BD%25D1%2583_%281711%29</t>
-  </si>
-  <si>
-    <t>https://uk.wikipedia.org/wiki/%25D0%259F%25D1%2580%25D0%25B0%25D0%25B2%25D0%25BB%25D1%2596%25D0%25BD%25D0%25BD%25D1%258F_%25D0%25B3%25D0%25B5%25D1%2582%25D1%258C%25D0%25BC%25D0%25B0%25D0%25BD%25D1%2581%25D1%258C%25D0%25BA%25D0%25BE%25D0%25B3%25D0%25BE_%25D1%2583%25D1%2580%25D1%258F%25D0%25B4%25D1%2583</t>
-  </si>
-  <si>
-    <t>https://uk.wikipedia.org/wiki/%25D0%259F%25D1%2596%25D0%25B2%25D0%25BD%25D1%2596%25D1%2587%25D0%25BD%25D0%25B0_%25D0%25B2%25D1%2596%25D0%25B9%25D0%25BD%25D0%25B0_%281700%25E2%2580%25941721%29</t>
-  </si>
-  <si>
-    <t>https://uk.wikipedia.org/wiki/%25D0%25A0%25D0%25B5%25D1%2588%25D0%25B5%25D1%2582%25D0%25B8%25D0%25BB%25D1%2596%25D0%25B2%25D1%2581%25D1%258C%25D0%25BA%25D1%2596_%25D1%2581%25D1%2582%25D0%25B0%25D1%2582%25D1%2582%25D1%2596</t>
-  </si>
-  <si>
-    <t>https://ru.wikipedia.org/wiki/%25D0%25A0%25D0%25BE%25D1%2581%25D1%2581%25D0%25B8%25D0%25B9%25D1%2581%25D0%25BA%25D0%25B8%25D0%25B5_%25D1%2583%25D0%25B4%25D0%25B0%25D1%2580%25D1%258B_%25D0%25BF%25D0%25BE_%25D1%2583%25D0%25BA%25D1%2580%25D0%25B0%25D0%25B8%25D0%25BD%25D1%2581%25D0%25BA%25D0%25BE%25D0%25B9_%25D1%258D%25D0%25BD%25D0%25B5%25D1%2580%25D0%25B3%25D0%25BE%25D1%2581%25D0%25B8%25D1%2581%25D1%2582%25D0%25B5%25D0%25BC%25D0%25B5</t>
+    <t>https://ru.wikipedia.org/wiki/%D0%9F%D0%B8%D1%81%D1%8C%D0%BC%D0%BE-%D0%BF%D1%80%D0%BE%D1%82%D0%B5%D1%81%D1%82_139</t>
+  </si>
+  <si>
+    <t>https://uk.wikipedia.org/wiki/%D0%9F%D0%BE%D0%B2%D1%81%D1%82%D0%B0%D0%BD%D0%BD%D1%8F_%D0%B1%D1%83%D0%B7%D1%8C%D0%BA%D0%B8%D1%85_%D0%BA%D0%BE%D0%B7%D0%B0%D0%BA%D1%96%D0%B2_%281817%29</t>
+  </si>
+  <si>
+    <t>https://uk.wikipedia.org/wiki/%D0%9F%D0%BE%D0%B4%D1%96%D0%BB%D0%B8_%D0%A0%D0%B5%D1%87%D1%96_%D0%9F%D0%BE%D1%81%D0%BF%D0%BE%D0%BB%D0%B8%D1%82%D0%BE%D1%97</t>
+  </si>
+  <si>
+    <t>https://ru.wikipedia.org/wiki/%D0%9F%D0%BE%D0%BB%D1%8C%D1%81%D0%BA%D0%BE%D0%B5_%D0%B2%D0%BE%D1%81%D1%81%D1%82%D0%B0%D0%BD%D0%B8%D0%B5_%281863%E2%80%941864%29</t>
+  </si>
+  <si>
+    <t>https://uk.wikipedia.org/wiki/%D0%9F%D0%BE%D1%85%D1%96%D0%B4_%D0%9F%D0%B8%D0%BB%D0%B8%D0%BF%D0%B0_%D0%9E%D1%80%D0%BB%D0%B8%D0%BA%D0%B0_%D0%BD%D0%B0_%D0%9F%D1%80%D0%B0%D0%B2%D0%BE%D0%B1%D0%B5%D1%80%D0%B5%D0%B6%D0%BD%D1%83_%D0%A3%D0%BA%D1%80%D0%B0%D1%97%D0%BD%D1%83_%281711%29</t>
+  </si>
+  <si>
+    <t>https://uk.wikipedia.org/wiki/%D0%9F%D1%80%D0%B0%D0%B2%D0%BB%D1%96%D0%BD%D0%BD%D1%8F_%D0%B3%D0%B5%D1%82%D1%8C%D0%BC%D0%B0%D0%BD%D1%81%D1%8C%D0%BA%D0%BE%D0%B3%D0%BE_%D1%83%D1%80%D1%8F%D0%B4%D1%83</t>
+  </si>
+  <si>
+    <t>https://uk.wikipedia.org/wiki/%D0%9F%D1%96%D0%B2%D0%BD%D1%96%D1%87%D0%BD%D0%B0_%D0%B2%D1%96%D0%B9%D0%BD%D0%B0_%281700%E2%80%941721%29</t>
+  </si>
+  <si>
+    <t>https://uk.wikipedia.org/wiki/%D0%A0%D0%B5%D1%88%D0%B5%D1%82%D0%B8%D0%BB%D1%96%D0%B2%D1%81%D1%8C%D0%BA%D1%96_%D1%81%D1%82%D0%B0%D1%82%D1%82%D1%96</t>
+  </si>
+  <si>
+    <t>https://ru.wikipedia.org/wiki/%D0%A0%D0%BE%D1%81%D1%81%D0%B8%D0%B9%D1%81%D0%BA%D0%B8%D0%B5_%D1%83%D0%B4%D0%B0%D1%80%D1%8B_%D0%BF%D0%BE_%D1%83%D0%BA%D1%80%D0%B0%D0%B8%D0%BD%D1%81%D0%BA%D0%BE%D0%B9_%D1%8D%D0%BD%D0%B5%D1%80%D0%B3%D0%BE%D1%81%D0%B8%D1%81%D1%82%D0%B5%D0%BC%D0%B5</t>
   </si>
   <si>
     <t>https://web.archive.org/web/20160304195659/http%3A//www.memo.ru/2010/09/27/rch.pdf</t>
   </si>
   <si>
-    <t>https://uk.wikipedia.org/wiki/%25D0%25A0%25D0%25BE%25D1%2581%25D1%2596%25D0%25B9%25D1%2581%25D1%258C%25D0%25BA%25D0%25BE-%25D1%2582%25D1%2583%25D1%2580%25D0%25B5%25D1%2586%25D1%258C%25D0%25BA%25D0%25B0_%25D0%25B2%25D1%2596%25D0%25B9%25D0%25BD%25D0%25B0_%281806%25E2%2580%25941812%29</t>
-  </si>
-  <si>
-    <t>https://uk.wikipedia.org/wiki/%25D0%25A0%25D0%25BE%25D1%2581%25D1%2596%25D0%25B9%25D1%2581%25D1%258C%25D0%25BA%25D0%25BE-%25D1%2583%25D0%25BA%25D1%2580%25D0%25B0%25D1%2597%25D0%25BD%25D1%2581%25D1%258C%25D0%25BA%25D0%25B0_%25D0%25B2%25D1%2596%25D0%25B9%25D0%25BD%25D0%25B0_%28%25D0%25B7_2014%29</t>
-  </si>
-  <si>
-    <t>https://uk.wikipedia.org/wiki/%25D0%25A0%25D1%2583%25D1%2581%25D0%25B8%25D1%2584%25D1%2596%25D0%25BA%25D0%25B0%25D1%2586%25D1%2596%25D1%258F_%25D0%25A3%25D0%25BA%25D1%2580%25D0%25B0%25D1%2597%25D0%25BD%25D0%25B8</t>
-  </si>
-  <si>
-    <t>https://ru.wikipedia.org/wiki/%25D0%25A0%25D1%2583%25D1%2581%25D1%2581%25D0%25BA%25D0%25BE-%25D1%2582%25D1%2583%25D1%2580%25D0%25B5%25D1%2586%25D0%25BA%25D0%25B0%25D1%258F_%25D0%25B2%25D0%25BE%25D0%25B9%25D0%25BD%25D0%25B0_%281877%25E2%2580%25941878%29</t>
-  </si>
-  <si>
-    <t>https://ru.wikipedia.org/wiki/%25D0%25A0%25D1%2583%25D1%2581%25D1%2581%25D0%25BA%25D0%25BE-%25D1%2582%25D1%2583%25D1%2580%25D0%25B5%25D1%2586%25D0%25BA%25D0%25B0%25D1%258F_%25D0%25B2%25D0%25BE%25D0%25B9%25D0%25BD%25D0%25B0_%281768%25E2%2580%25941774%29</t>
+    <t>https://uk.wikipedia.org/wiki/%D0%A0%D0%BE%D1%81%D1%96%D0%B9%D1%81%D1%8C%D0%BA%D0%BE-%D1%82%D1%83%D1%80%D0%B5%D1%86%D1%8C%D0%BA%D0%B0_%D0%B2%D1%96%D0%B9%D0%BD%D0%B0_%281806%E2%80%941812%29</t>
+  </si>
+  <si>
+    <t>https://uk.wikipedia.org/wiki/%D0%A0%D0%BE%D1%81%D1%96%D0%B9%D1%81%D1%8C%D0%BA%D0%BE-%D1%83%D0%BA%D1%80%D0%B0%D1%97%D0%BD%D1%81%D1%8C%D0%BA%D0%B0_%D0%B2%D1%96%D0%B9%D0%BD%D0%B0_%28%D0%B7_2014%29</t>
+  </si>
+  <si>
+    <t>https://uk.wikipedia.org/wiki/%D0%A0%D1%83%D1%81%D0%B8%D1%84%D1%96%D0%BA%D0%B0%D1%86%D1%96%D1%8F_%D0%A3%D0%BA%D1%80%D0%B0%D1%97%D0%BD%D0%B8</t>
+  </si>
+  <si>
+    <t>https://ru.wikipedia.org/wiki/%D0%A0%D1%83%D1%81%D1%81%D0%BA%D0%BE-%D1%82%D1%83%D1%80%D0%B5%D1%86%D0%BA%D0%B0%D1%8F_%D0%B2%D0%BE%D0%B9%D0%BD%D0%B0_%281877%E2%80%941878%29</t>
+  </si>
+  <si>
+    <t>https://ru.wikipedia.org/wiki/%D0%A0%D1%83%D1%81%D1%81%D0%BA%D0%BE-%D1%82%D1%83%D1%80%D0%B5%D1%86%D0%BA%D0%B0%D1%8F_%D0%B2%D0%BE%D0%B9%D0%BD%D0%B0_%281768%E2%80%941774%29</t>
   </si>
   <si>
     <t>https://uk.wikipedia.org/wiki/%D0%A0%D1%83%D1%97%D0%BD%D0%B0</t>
   </si>
   <si>
-    <t>https://uk.wikipedia.org/wiki/%25D0%25A0%25D1%2596%25D1%2588%25D0%25B8%25D1%2582%25D0%25B5%25D0%25BB%25D1%258C%25D0%25BD%25D1%2596_%25D0%25BF%25D1%2583%25D0%25BD%25D0%25BA%25D1%2582%25D0%25B8</t>
-  </si>
-  <si>
-    <t>https://uk.wikipedia.org/wiki/%25D0%25A1%25D0%25B5%25D1%2580%25D0%25BF%25D0%25BD%25D0%25B5%25D0%25B2%25D0%25B8%25D0%25B9_%25D0%25BF%25D1%2583%25D1%2582%25D1%2587</t>
-  </si>
-  <si>
-    <t>https://uk.wikipedia.org/wiki/%25D0%25A1%25D0%25BA%25D0%25B0%25D1%2581%25D1%2583%25D0%25B2%25D0%25B0%25D0%25BD%25D0%25BD%25D1%258F_%25D0%25BA%25D0%25BE%25D0%25B7%25D0%25B0%25D1%2586%25D1%258C%25D0%25BA%25D0%25BE%25D0%25B3%25D0%25BE_%25D1%2583%25D1%2581%25D1%2582%25D1%2580%25D0%25BE%25D1%258E_%25D0%25B2_%25D0%25A1%25D0%25BB%25D0%25BE%25D0%25B1%25D1%2596%25D0%25B4%25D1%2581%25D1%258C%25D0%25BA%25D1%2596%25D0%25B9_%25D0%25A3%25D0%25BA%25D1%2580%25D0%25B0%25D1%2597%25D0%25BD%25D1%2596</t>
-  </si>
-  <si>
-    <t>https://uk.wikipedia.org/wiki/%25D0%25A1%25D0%25BC%25D1%2583%25D0%25B3%25D0%25B0_%25D0%25BE%25D1%2581%25D1%2596%25D0%25BB%25D0%25BE%25D1%2581%25D1%2582%25D1%2596</t>
-  </si>
-  <si>
-    <t>https://uk.wikipedia.org/wiki/%25D0%25A1%25D1%2582%25D0%25BE%25D0%25BB%25D0%25B8%25D0%25BF%25D1%2596%25D0%25BD%25D1%2581%25D1%258C%25D0%25BA%25D0%25B0_%25D1%2580%25D0%25B5%25D1%2584%25D0%25BE%25D1%2580%25D0%25BC%25D0%25B0</t>
-  </si>
-  <si>
-    <t>https://uk.wikipedia.org/wiki/%25D0%25A3%25D0%25B4%25D0%25B0%25D1%2580%25D0%25B8_%25D0%25BF%25D0%25BE_%25D0%25BE%25D0%25B1%2527%25D1%2594%25D0%25BA%25D1%2582%25D0%25B0%25D1%2585_%25D0%25BA%25D1%2580%25D0%25B8%25D1%2582%25D0%25B8%25D1%2587%25D0%25BD%25D0%25BE%25D1%2597_%25D1%2596%25D0%25BD%25D1%2584%25D1%2580%25D0%25B0%25D1%2581%25D1%2582%25D1%2580%25D1%2583%25D0%25BA%25D1%2582%25D1%2583%25D1%2580%25D0%25B8_%25D0%25A3%25D0%25BA%25D1%2580%25D0%25B0%25D1%2597%25D0%25BD%25D0%25B8_%25D0%25BF%25D1%2596%25D0%25B4_%25D1%2587%25D0%25B0%25D1%2581_%25D1%2580%25D0%25BE%25D1%2581%25D1%2596%25D0%25B9%25D1%2581%25D1%258C%25D0%25BA%25D0%25BE-%25D1%2583%25D0%25BA%25D1%2580%25D0%25B0%25D1%2597%25D0%25BD%25D1%2581%25D1%258C%25D0%25BA%25D0%25BE%25D1%2597_%25D0%25B2%25D1%2596%25D0%25B9%25D0%25BD%25D0%25B8</t>
-  </si>
-  <si>
-    <t>https://uk.wikipedia.org/wiki/%25D0%25A3%25D0%25BA%25D1%2580%25D0%25B0%25D1%2597%25D0%25BD%25D0%25B0_%25D0%25B2_%25D0%259F%25D0%25B5%25D1%2580%25D1%2588%25D1%2596%25D0%25B9_%25D1%2581%25D0%25B2%25D1%2596%25D1%2582%25D0%25BE%25D0%25B2%25D1%2596%25D0%25B9_%25D0%25B2%25D1%2596%25D0%25B9%25D0%25BD%25D1%2596</t>
+    <t>https://uk.wikipedia.org/wiki/%D0%A0%D1%96%D1%88%D0%B8%D1%82%D0%B5%D0%BB%D1%8C%D0%BD%D1%96_%D0%BF%D1%83%D0%BD%D0%BA%D1%82%D0%B8</t>
+  </si>
+  <si>
+    <t>https://uk.wikipedia.org/wiki/%D0%A1%D0%B5%D1%80%D0%BF%D0%BD%D0%B5%D0%B2%D0%B8%D0%B9_%D0%BF%D1%83%D1%82%D1%87</t>
+  </si>
+  <si>
+    <t>https://uk.wikipedia.org/wiki/%D0%A1%D0%BA%D0%B0%D1%81%D1%83%D0%B2%D0%B0%D0%BD%D0%BD%D1%8F_%D0%BA%D0%BE%D0%B7%D0%B0%D1%86%D1%8C%D0%BA%D0%BE%D0%B3%D0%BE_%D1%83%D1%81%D1%82%D1%80%D0%BE%D1%8E_%D0%B2_%D0%A1%D0%BB%D0%BE%D0%B1%D1%96%D0%B4%D1%81%D1%8C%D0%BA%D1%96%D0%B9_%D0%A3%D0%BA%D1%80%D0%B0%D1%97%D0%BD%D1%96</t>
+  </si>
+  <si>
+    <t>https://uk.wikipedia.org/wiki/%D0%A1%D0%BC%D1%83%D0%B3%D0%B0_%D0%BE%D1%81%D1%96%D0%BB%D0%BE%D1%81%D1%82%D1%96</t>
+  </si>
+  <si>
+    <t>https://uk.wikipedia.org/wiki/%D0%A1%D1%82%D0%BE%D0%BB%D0%B8%D0%BF%D1%96%D0%BD%D1%81%D1%8C%D0%BA%D0%B0_%D1%80%D0%B5%D1%84%D0%BE%D1%80%D0%BC%D0%B0</t>
+  </si>
+  <si>
+    <t>https://uk.wikipedia.org/wiki/%D0%A3%D0%B4%D0%B0%D1%80%D0%B8_%D0%BF%D0%BE_%D0%BE%D0%B1%27%D1%94%D0%BA%D1%82%D0%B0%D1%85_%D0%BA%D1%80%D0%B8%D1%82%D0%B8%D1%87%D0%BD%D0%BE%D1%97_%D1%96%D0%BD%D1%84%D1%80%D0%B0%D1%81%D1%82%D1%80%D1%83%D0%BA%D1%82%D1%83%D1%80%D0%B8_%D0%A3%D0%BA%D1%80%D0%B0%D1%97%D0%BD%D0%B8_%D0%BF%D1%96%D0%B4_%D1%87%D0%B0%D1%81_%D1%80%D0%BE%D1%81%D1%96%D0%B9%D1%81%D1%8C%D0%BA%D0%BE-%D1%83%D0%BA%D1%80%D0%B0%D1%97%D0%BD%D1%81%D1%8C%D0%BA%D0%BE%D1%97_%D0%B2%D1%96%D0%B9%D0%BD%D0%B8</t>
+  </si>
+  <si>
+    <t>https://uk.wikipedia.org/wiki/%D0%A3%D0%BA%D1%80%D0%B0%D1%97%D0%BD%D0%B0_%D0%B2_%D0%9F%D0%B5%D1%80%D1%88%D1%96%D0%B9_%D1%81%D0%B2%D1%96%D1%82%D0%BE%D0%B2%D1%96%D0%B9_%D0%B2%D1%96%D0%B9%D0%BD%D1%96</t>
   </si>
   <si>
     <t>http://resource.history.org.ua/item/0016476</t>
   </si>
   <si>
-    <t>https://uk.wikipedia.org/wiki/%25D0%25A3%25D0%25BA%25D1%2580%25D0%25B0%25D1%2597%25D0%25BD%25D0%25B0_%25D1%2583_%25D0%25B2%25D1%2596%25D0%25B9%25D0%25BD%25D0%25B0%25D1%2585_%25D0%259D%25D0%25B0%25D0%25BF%25D0%25BE%25D0%25BB%25D0%25B5%25D0%25BE%25D0%25BD%25D0%25B0</t>
+    <t>https://uk.wikipedia.org/wiki/%D0%A3%D0%BA%D1%80%D0%B0%D1%97%D0%BD%D0%B0_%D1%83_%D0%B2%D1%96%D0%B9%D0%BD%D0%B0%D1%85_%D0%9D%D0%B0%D0%BF%D0%BE%D0%BB%D0%B5%D0%BE%D0%BD%D0%B0</t>
   </si>
   <si>
     <t>https://beda.media/ru/articles/war-in-chechnya-chronicle-part1-ru</t>
   </si>
   <si>
-    <t>https://uk.wikipedia.org/wiki/%25D0%25A7%25D0%25BE%25D1%2580%25D0%25BD%25D0%25BE%25D1%2581%25D0%25BE%25D1%2582%25D0%25B5%25D0%25BD%25D1%2586%25D1%2596</t>
+    <t>https://uk.wikipedia.org/wiki/%D0%A7%D0%BE%D1%80%D0%BD%D0%BE%D1%81%D0%BE%D1%82%D0%B5%D0%BD%D1%86%D1%96</t>
   </si>
 </sst>
 </file>
